--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="2083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="2084">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20738077163696</t>
+    <t xml:space="preserve">6.20738124847412</t>
   </si>
   <si>
     <t xml:space="preserve">BAMI.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">6.25302362442017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98424005508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89802694320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6545991897583</t>
+    <t xml:space="preserve">5.98423957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89802598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65459871292114</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795719146729</t>
@@ -68,76 +68,76 @@
     <t xml:space="preserve">5.27424573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94206857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40450191497803</t>
+    <t xml:space="preserve">4.9420690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40450143814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.85839128494263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6149640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28785991668701</t>
+    <t xml:space="preserve">4.61496496200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28786039352417</t>
   </si>
   <si>
     <t xml:space="preserve">4.55410718917847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19910955429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95568346977234</t>
+    <t xml:space="preserve">4.19911003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9556839466095</t>
   </si>
   <si>
     <t xml:space="preserve">4.32082366943359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57946443557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50339317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05203914642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11289691925049</t>
+    <t xml:space="preserve">4.57946395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50339365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0520396232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11289644241333</t>
   </si>
   <si>
     <t xml:space="preserve">3.87961292266846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52715110778809</t>
+    <t xml:space="preserve">3.52715158462524</t>
   </si>
   <si>
     <t xml:space="preserve">3.2228672504425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58040070533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26851058006287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64379286766052</t>
+    <t xml:space="preserve">3.5804009437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26851081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6437931060791</t>
   </si>
   <si>
     <t xml:space="preserve">3.91004133224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04443264007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14332437515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91511344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818489074707</t>
+    <t xml:space="preserve">4.04443216323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14332485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91511297225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818536758423</t>
   </si>
   <si>
     <t xml:space="preserve">4.08246850967407</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">3.74775671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84157824516296</t>
+    <t xml:space="preserve">3.84157776832581</t>
   </si>
   <si>
     <t xml:space="preserve">3.92018342018127</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">4.22700262069702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04950475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88468408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86693429946899</t>
+    <t xml:space="preserve">4.04950428009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88468432426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86693477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.7604353427887</t>
@@ -176,49 +176,49 @@
     <t xml:space="preserve">3.69957828521729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03682565689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38768792152405</t>
+    <t xml:space="preserve">4.03682613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9480767250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38768815994263</t>
   </si>
   <si>
     <t xml:space="preserve">3.47136545181274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6767578125</t>
+    <t xml:space="preserve">3.67675733566284</t>
   </si>
   <si>
     <t xml:space="preserve">3.69197106361389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51447343826294</t>
+    <t xml:space="preserve">3.51447319984436</t>
   </si>
   <si>
     <t xml:space="preserve">3.38261699676514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27611756324768</t>
+    <t xml:space="preserve">3.27611827850342</t>
   </si>
   <si>
     <t xml:space="preserve">3.06565427780151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365622520447</t>
+    <t xml:space="preserve">2.92365646362305</t>
   </si>
   <si>
     <t xml:space="preserve">2.70812153816223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49005198478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40586709976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22431135177612</t>
+    <t xml:space="preserve">2.49005222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40586733818054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2243115901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.46672344207764</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">3.13856601715088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20092058181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2450897693634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11778044700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23469686508179</t>
+    <t xml:space="preserve">3.14116311073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20092082023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11778020858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23469662666321</t>
   </si>
   <si>
     <t xml:space="preserve">3.19052886962891</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">3.32823038101196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20351910591125</t>
+    <t xml:space="preserve">3.20351934432983</t>
   </si>
   <si>
     <t xml:space="preserve">2.96968603134155</t>
@@ -275,25 +275,25 @@
     <t xml:space="preserve">2.75663709640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86835789680481</t>
+    <t xml:space="preserve">2.86835837364197</t>
   </si>
   <si>
     <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84497451782227</t>
+    <t xml:space="preserve">2.84497475624084</t>
   </si>
   <si>
     <t xml:space="preserve">2.59607172012329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51500940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28637218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378625869751</t>
+    <t xml:space="preserve">2.51500964164734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28637194633484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378602027893</t>
   </si>
   <si>
     <t xml:space="preserve">2.32274627685547</t>
@@ -314,22 +314,22 @@
     <t xml:space="preserve">2.24480175971985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24999761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27493977546692</t>
+    <t xml:space="preserve">2.24999785423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2749400138855</t>
   </si>
   <si>
     <t xml:space="preserve">2.47343921661377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4703209400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48902797698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49422383308411</t>
+    <t xml:space="preserve">2.47032117843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48902821540833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49422407150269</t>
   </si>
   <si>
     <t xml:space="preserve">2.31131434440613</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">2.2902045249939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22156810760498</t>
+    <t xml:space="preserve">2.22156834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433287620544</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">1.83636593818665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71590256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83776676654816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07449102401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01846146583557</t>
+    <t xml:space="preserve">1.7159024477005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83776664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07449078559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01846122741699</t>
   </si>
   <si>
     <t xml:space="preserve">2.02546525001526</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">1.50158977508545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52540218830109</t>
+    <t xml:space="preserve">1.52540230751038</t>
   </si>
   <si>
     <t xml:space="preserve">1.45676624774933</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">1.40073668956757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31459140777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28167414665222</t>
+    <t xml:space="preserve">1.31459152698517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28167402744293</t>
   </si>
   <si>
     <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57022607326508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66687667369843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55621838569641</t>
+    <t xml:space="preserve">1.57022619247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66687679290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55621826648712</t>
   </si>
   <si>
     <t xml:space="preserve">1.64166355133057</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">1.66267454624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6878879070282</t>
+    <t xml:space="preserve">1.68788778781891</t>
   </si>
   <si>
     <t xml:space="preserve">1.67528092861176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66407525539398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72990989685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70329582691193</t>
+    <t xml:space="preserve">1.66407513618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7299097776413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70329570770264</t>
   </si>
   <si>
     <t xml:space="preserve">1.71730327606201</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">1.70749819278717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76352763175964</t>
+    <t xml:space="preserve">1.76352739334106</t>
   </si>
   <si>
     <t xml:space="preserve">1.50579214096069</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">1.55201649665833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63045763969421</t>
+    <t xml:space="preserve">1.63045752048492</t>
   </si>
   <si>
     <t xml:space="preserve">1.59964120388031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5926376581192</t>
+    <t xml:space="preserve">1.59263753890991</t>
   </si>
   <si>
     <t xml:space="preserve">1.58143162727356</t>
@@ -491,19 +491,19 @@
     <t xml:space="preserve">1.4539647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48758256435394</t>
+    <t xml:space="preserve">1.48758244514465</t>
   </si>
   <si>
     <t xml:space="preserve">1.58003115653992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53520739078522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559722423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56742441654205</t>
+    <t xml:space="preserve">1.53520727157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559710502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56742453575134</t>
   </si>
   <si>
     <t xml:space="preserve">1.56182146072388</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">1.60384356975555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68088412284851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63886189460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65707147121429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65847229957581</t>
+    <t xml:space="preserve">1.68088436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63886177539825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65707159042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6584724187851</t>
   </si>
   <si>
     <t xml:space="preserve">1.64306426048279</t>
@@ -530,25 +530,25 @@
     <t xml:space="preserve">1.59403848648071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60944640636444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57582890987396</t>
+    <t xml:space="preserve">1.60944652557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57582879066467</t>
   </si>
   <si>
     <t xml:space="preserve">1.50018906593323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46657156944275</t>
+    <t xml:space="preserve">1.46657145023346</t>
   </si>
   <si>
     <t xml:space="preserve">1.40003621578217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45116317272186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47357499599457</t>
+    <t xml:space="preserve">1.45116341114044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47357511520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.43995726108551</t>
@@ -575,34 +575,34 @@
     <t xml:space="preserve">1.50299048423767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55061554908752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65286946296692</t>
+    <t xml:space="preserve">1.55061566829681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65286934375763</t>
   </si>
   <si>
     <t xml:space="preserve">1.78593909740448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79994678497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84617114067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317480564117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82235848903656</t>
+    <t xml:space="preserve">1.79994666576385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8461709022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8531745672226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196877479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82235860824585</t>
   </si>
   <si>
     <t xml:space="preserve">1.85737681388855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86297988891602</t>
+    <t xml:space="preserve">1.86298012733459</t>
   </si>
   <si>
     <t xml:space="preserve">1.92040991783142</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">1.61224806308746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50999414920807</t>
+    <t xml:space="preserve">1.50999402999878</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543919563293</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">1.60664510726929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5127956867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42735075950623</t>
+    <t xml:space="preserve">1.51279580593109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42735087871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.35451233386993</t>
@@ -641,40 +641,40 @@
     <t xml:space="preserve">1.30408596992493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31178998947144</t>
+    <t xml:space="preserve">1.31178987026215</t>
   </si>
   <si>
     <t xml:space="preserve">1.32649779319763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29988360404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31739282608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25085783004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30268526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35871458053589</t>
+    <t xml:space="preserve">1.29988372325897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31739294528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2508579492569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30268502235413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35871469974518</t>
   </si>
   <si>
     <t xml:space="preserve">1.39233231544495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28867781162262</t>
+    <t xml:space="preserve">1.28867769241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.40493893623352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49458611011505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64026260375977</t>
+    <t xml:space="preserve">1.49458599090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64026284217834</t>
   </si>
   <si>
     <t xml:space="preserve">1.56462287902832</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">1.53380692005157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679483294487</t>
+    <t xml:space="preserve">1.67948341369629</t>
   </si>
   <si>
     <t xml:space="preserve">1.69769310951233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6514687538147</t>
+    <t xml:space="preserve">1.65146863460541</t>
   </si>
   <si>
     <t xml:space="preserve">1.72290623188019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77893543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310102939606</t>
+    <t xml:space="preserve">1.77893567085266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310114860535</t>
   </si>
   <si>
     <t xml:space="preserve">1.60524427890778</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">1.75092089176178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87698709964752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9050018787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643959522247</t>
+    <t xml:space="preserve">1.8769873380661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90500211715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643935680389</t>
   </si>
   <si>
     <t xml:space="preserve">2.03106832504272</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">1.95122611522675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94982528686523</t>
+    <t xml:space="preserve">1.94982552528381</t>
   </si>
   <si>
     <t xml:space="preserve">1.9064028263092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94702398777008</t>
+    <t xml:space="preserve">1.94702422618866</t>
   </si>
   <si>
     <t xml:space="preserve">1.89799845218658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94142091274261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93581819534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01706123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97363805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02266407012939</t>
+    <t xml:space="preserve">1.94142138957977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93581795692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01706099510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97363829612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02266383171082</t>
   </si>
   <si>
     <t xml:space="preserve">2.08849859237671</t>
@@ -758,34 +758,34 @@
     <t xml:space="preserve">2.02126312255859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86017823219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89099478721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78033661842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67388045787811</t>
+    <t xml:space="preserve">1.86017847061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89099454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78033649921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6738805770874</t>
   </si>
   <si>
     <t xml:space="preserve">1.74251639842987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73831427097321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64586567878723</t>
+    <t xml:space="preserve">1.7383143901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64586555957794</t>
   </si>
   <si>
     <t xml:space="preserve">1.75512325763702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84056806564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77753496170044</t>
+    <t xml:space="preserve">1.84056782722473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77753508090973</t>
   </si>
   <si>
     <t xml:space="preserve">1.7817370891571</t>
@@ -797,25 +797,25 @@
     <t xml:space="preserve">1.6220531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51419639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006792545319</t>
+    <t xml:space="preserve">1.51419627666473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6500678062439</t>
   </si>
   <si>
     <t xml:space="preserve">1.71870374679565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71450173854828</t>
+    <t xml:space="preserve">1.71450185775757</t>
   </si>
   <si>
     <t xml:space="preserve">1.68228471279144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69349050521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69629216194153</t>
+    <t xml:space="preserve">1.6934906244278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69629204273224</t>
   </si>
   <si>
     <t xml:space="preserve">1.80975198745728</t>
@@ -827,22 +827,22 @@
     <t xml:space="preserve">1.76072597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80695044994354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86858260631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85597622394562</t>
+    <t xml:space="preserve">1.80695033073425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8685827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8559764623642</t>
   </si>
   <si>
     <t xml:space="preserve">1.91620779037476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90780365467072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91480684280396</t>
+    <t xml:space="preserve">1.90780341625214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91480708122253</t>
   </si>
   <si>
     <t xml:space="preserve">1.88539147377014</t>
@@ -851,31 +851,31 @@
     <t xml:space="preserve">1.88819324970245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94562339782715</t>
+    <t xml:space="preserve">1.94562363624573</t>
   </si>
   <si>
     <t xml:space="preserve">1.90360105037689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89939916133881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87978875637054</t>
+    <t xml:space="preserve">1.89939892292023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87978851795197</t>
   </si>
   <si>
     <t xml:space="preserve">1.8671817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76212704181671</t>
+    <t xml:space="preserve">1.76212692260742</t>
   </si>
   <si>
     <t xml:space="preserve">1.95542860031128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86157929897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8699836730957</t>
+    <t xml:space="preserve">1.86157917976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86998355388641</t>
   </si>
   <si>
     <t xml:space="preserve">2.00445413589478</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">1.98204231262207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96383285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88259017467499</t>
+    <t xml:space="preserve">1.96383261680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88258993625641</t>
   </si>
   <si>
     <t xml:space="preserve">1.93021535873413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97784018516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0941014289856</t>
+    <t xml:space="preserve">1.97783994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09410166740417</t>
   </si>
   <si>
     <t xml:space="preserve">2.17814564704895</t>
@@ -917,25 +917,25 @@
     <t xml:space="preserve">2.12491750717163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99464905261993</t>
+    <t xml:space="preserve">1.99464929103851</t>
   </si>
   <si>
     <t xml:space="preserve">2.00305342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90220046043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99885129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95262730121613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95402765274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9344174861908</t>
+    <t xml:space="preserve">1.90220069885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99885153770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95262706279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95402789115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93441724777222</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920412540436</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">1.91060495376587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88679242134094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95823001861572</t>
+    <t xml:space="preserve">1.88679218292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9582302570343</t>
   </si>
   <si>
     <t xml:space="preserve">1.94422292709351</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">2.06048369407654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05207920074463</t>
+    <t xml:space="preserve">2.05207943916321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10950970649719</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">2.14452791213989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18795084953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2061607837677</t>
+    <t xml:space="preserve">2.18795108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20616054534912</t>
   </si>
   <si>
     <t xml:space="preserve">2.20896172523499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19915699958801</t>
+    <t xml:space="preserve">2.19915676116943</t>
   </si>
   <si>
     <t xml:space="preserve">2.19635510444641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14172673225403</t>
+    <t xml:space="preserve">2.14172649383545</t>
   </si>
   <si>
     <t xml:space="preserve">2.2033588886261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19215297698975</t>
+    <t xml:space="preserve">2.19215321540833</t>
   </si>
   <si>
     <t xml:space="preserve">2.15573382377625</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">2.16413831710815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16273736953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20756101608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997283935547</t>
+    <t xml:space="preserve">2.16273760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20756077766418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997307777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.28320074081421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34063100814819</t>
+    <t xml:space="preserve">2.34063124656677</t>
   </si>
   <si>
     <t xml:space="preserve">2.35884070396423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33082604408264</t>
+    <t xml:space="preserve">2.33082580566406</t>
   </si>
   <si>
     <t xml:space="preserve">2.30561280250549</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">2.26499128341675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29720854759216</t>
+    <t xml:space="preserve">2.29720830917358</t>
   </si>
   <si>
     <t xml:space="preserve">2.30981516838074</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">2.26078915596008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22016763687134</t>
+    <t xml:space="preserve">2.22016787528992</t>
   </si>
   <si>
     <t xml:space="preserve">2.23277449607849</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">2.26219010353088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21036243438721</t>
+    <t xml:space="preserve">2.21036219596863</t>
   </si>
   <si>
     <t xml:space="preserve">2.15993618965149</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">2.30141043663025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3112154006958</t>
+    <t xml:space="preserve">2.31121563911438</t>
   </si>
   <si>
     <t xml:space="preserve">2.33782958984375</t>
@@ -1112,25 +1112,25 @@
     <t xml:space="preserve">2.4568920135498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43307995796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43027806282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24117851257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17954635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13192129135132</t>
+    <t xml:space="preserve">2.43307971954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43027830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24117875099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17954659461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1319215297699</t>
   </si>
   <si>
     <t xml:space="preserve">2.23417520523071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20475959777832</t>
+    <t xml:space="preserve">2.2047598361969</t>
   </si>
   <si>
     <t xml:space="preserve">2.19075226783752</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">2.2019579410553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18374848365784</t>
+    <t xml:space="preserve">2.18374872207642</t>
   </si>
   <si>
     <t xml:space="preserve">2.21456480026245</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">2.10250616073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1333224773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10810899734497</t>
+    <t xml:space="preserve">2.13332223892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10810875892639</t>
   </si>
   <si>
     <t xml:space="preserve">2.09129977226257</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">1.88959395885468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87558627128601</t>
+    <t xml:space="preserve">1.8755863904953</t>
   </si>
   <si>
     <t xml:space="preserve">2.01566028594971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97924113273621</t>
+    <t xml:space="preserve">1.97924089431763</t>
   </si>
   <si>
     <t xml:space="preserve">1.9694356918335</t>
@@ -1211,46 +1211,46 @@
     <t xml:space="preserve">1.76492822170258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.752321600914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77193200588226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78313815593719</t>
+    <t xml:space="preserve">1.75232183933258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77193188667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78313791751862</t>
   </si>
   <si>
     <t xml:space="preserve">1.8265608549118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86438059806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177385807037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395399570465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86578154563904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84897232055664</t>
+    <t xml:space="preserve">1.86438083648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177397727966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395411491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86578130722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84897255897522</t>
   </si>
   <si>
     <t xml:space="preserve">1.8839910030365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99745082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04787707328796</t>
+    <t xml:space="preserve">1.99745059013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04787731170654</t>
   </si>
   <si>
     <t xml:space="preserve">2.0436749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99604952335358</t>
+    <t xml:space="preserve">1.99604976177216</t>
   </si>
   <si>
     <t xml:space="preserve">2.08429646492004</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">2.15013098716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17114162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1872501373291</t>
+    <t xml:space="preserve">2.17114186286926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18724989891052</t>
   </si>
   <si>
     <t xml:space="preserve">2.12701869010925</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">2.10355615615845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10320615768433</t>
+    <t xml:space="preserve">2.10320639610291</t>
   </si>
   <si>
     <t xml:space="preserve">2.0282666683197</t>
@@ -1292,37 +1292,37 @@
     <t xml:space="preserve">2.16028642654419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10600781440735</t>
+    <t xml:space="preserve">2.10600757598877</t>
   </si>
   <si>
     <t xml:space="preserve">2.03772187232971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1172137260437</t>
+    <t xml:space="preserve">2.11721396446228</t>
   </si>
   <si>
     <t xml:space="preserve">2.0800940990448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11266112327576</t>
+    <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
     <t xml:space="preserve">2.12736892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18584966659546</t>
+    <t xml:space="preserve">2.15258240699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18584990501404</t>
   </si>
   <si>
     <t xml:space="preserve">2.14207673072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425392150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19005227088928</t>
+    <t xml:space="preserve">2.19425415992737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1900520324707</t>
   </si>
   <si>
     <t xml:space="preserve">2.2030086517334</t>
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">2.17604446411133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18865132331848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01005744934082</t>
+    <t xml:space="preserve">2.1886510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01005721092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.08709788322449</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">2.07624220848083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06643676757812</t>
+    <t xml:space="preserve">2.0664370059967</t>
   </si>
   <si>
     <t xml:space="preserve">2.11441206932068</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">2.13822436332703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12036538124084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12071561813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9634827375412</t>
+    <t xml:space="preserve">2.12036514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12071537971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96348297595978</t>
   </si>
   <si>
     <t xml:space="preserve">1.98274278640747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9872955083847</t>
+    <t xml:space="preserve">1.98729526996613</t>
   </si>
   <si>
     <t xml:space="preserve">1.97293758392334</t>
@@ -1379,40 +1379,40 @@
     <t xml:space="preserve">1.96838510036469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94107103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03421998023987</t>
+    <t xml:space="preserve">1.9410707950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03422021865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.00620532035828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01601028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03492021560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10915923118591</t>
+    <t xml:space="preserve">2.01601004600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03491997718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10915946960449</t>
   </si>
   <si>
     <t xml:space="preserve">2.10775852203369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14382767677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12421751022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14662909507751</t>
+    <t xml:space="preserve">2.14382743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12421727180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14662933349609</t>
   </si>
   <si>
     <t xml:space="preserve">2.11791372299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888547897339</t>
+    <t xml:space="preserve">2.15888571739197</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857507705688</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">2.08289575576782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14347767829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453062057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07028913497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09970426559448</t>
+    <t xml:space="preserve">2.14347743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453085899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07028889656067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0997040271759</t>
   </si>
   <si>
     <t xml:space="preserve">1.86087870597839</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">1.82165813446045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57687938213348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47077357769012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51839852333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55446755886078</t>
+    <t xml:space="preserve">1.57687950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47077345848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51839864253998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55446767807007</t>
   </si>
   <si>
     <t xml:space="preserve">1.68578684329987</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">1.6364107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59649002552032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68018364906311</t>
+    <t xml:space="preserve">1.59648990631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6801837682724</t>
   </si>
   <si>
     <t xml:space="preserve">1.61259806156158</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">1.71170020103455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69874322414398</t>
+    <t xml:space="preserve">1.69874334335327</t>
   </si>
   <si>
     <t xml:space="preserve">1.7246572971344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69138956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67808270454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81990706920624</t>
+    <t xml:space="preserve">1.69138967990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67808258533478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81990718841553</t>
   </si>
   <si>
     <t xml:space="preserve">1.7880402803421</t>
@@ -1499,22 +1499,22 @@
     <t xml:space="preserve">1.84792220592499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78068649768829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73481261730194</t>
+    <t xml:space="preserve">1.78068661689758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73481249809265</t>
   </si>
   <si>
     <t xml:space="preserve">1.70364594459534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77403295040131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80589985847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82586061954498</t>
+    <t xml:space="preserve">1.7740330696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80589997768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8258603811264</t>
   </si>
   <si>
     <t xml:space="preserve">1.87173426151276</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">1.89274561405182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87243509292603</t>
+    <t xml:space="preserve">1.87243485450745</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823272705078</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">1.85912799835205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83286416530609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81605517864227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85072338581085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601570129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85807752609253</t>
+    <t xml:space="preserve">1.83286428451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81605529785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85072314739227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85807728767395</t>
   </si>
   <si>
     <t xml:space="preserve">1.85387516021729</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">1.76807975769043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75337207317352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64901721477509</t>
+    <t xml:space="preserve">1.75337219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64901733398438</t>
   </si>
   <si>
     <t xml:space="preserve">1.64621591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66337478160858</t>
+    <t xml:space="preserve">1.66337490081787</t>
   </si>
   <si>
     <t xml:space="preserve">1.65216898918152</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">1.57092618942261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53030490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4697231054306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42630004882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42524981498718</t>
+    <t xml:space="preserve">1.53030478954315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46972298622131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42630016803741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42524969577789</t>
   </si>
   <si>
     <t xml:space="preserve">1.45501530170441</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">1.44415974617004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43925714492798</t>
+    <t xml:space="preserve">1.43925702571869</t>
   </si>
   <si>
     <t xml:space="preserve">1.40704011917114</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">1.43120276927948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40178716182709</t>
+    <t xml:space="preserve">1.4017870426178</t>
   </si>
   <si>
     <t xml:space="preserve">1.358154296875</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">1.37132108211517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50719273090363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49493634700775</t>
+    <t xml:space="preserve">1.50719261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49493646621704</t>
   </si>
   <si>
     <t xml:space="preserve">1.54326176643372</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">1.62625539302826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62415421009064</t>
+    <t xml:space="preserve">1.62415409088135</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715054512024</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">1.48688185214996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40143716335297</t>
+    <t xml:space="preserve">1.40143704414368</t>
   </si>
   <si>
     <t xml:space="preserve">1.37356245517731</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">1.40283787250519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41439390182495</t>
+    <t xml:space="preserve">1.41439378261566</t>
   </si>
   <si>
     <t xml:space="preserve">1.38602900505066</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">1.29638171195984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31108963489532</t>
+    <t xml:space="preserve">1.31108951568604</t>
   </si>
   <si>
     <t xml:space="preserve">1.30520665645599</t>
@@ -1691,40 +1691,40 @@
     <t xml:space="preserve">1.30758774280548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29960346221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22550463676453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2067346572876</t>
+    <t xml:space="preserve">1.29960358142853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22550451755524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20673477649689</t>
   </si>
   <si>
     <t xml:space="preserve">1.1690548658371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14692318439484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09229445457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134433746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08977317810059</t>
+    <t xml:space="preserve">1.14692330360413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09229457378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134445667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08977329730988</t>
   </si>
   <si>
     <t xml:space="preserve">1.14440190792084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16345191001892</t>
+    <t xml:space="preserve">1.16345202922821</t>
   </si>
   <si>
     <t xml:space="preserve">1.16331195831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19608902931213</t>
+    <t xml:space="preserve">1.19608914852142</t>
   </si>
   <si>
     <t xml:space="preserve">1.23965203762054</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">1.22410380840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25477993488312</t>
+    <t xml:space="preserve">1.25478005409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.29217982292175</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">1.28139400482178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27046823501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26640617847443</t>
+    <t xml:space="preserve">1.27046835422516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26640605926514</t>
   </si>
   <si>
     <t xml:space="preserve">1.23923182487488</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">1.26262426376343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19412815570831</t>
+    <t xml:space="preserve">1.19412803649902</t>
   </si>
   <si>
     <t xml:space="preserve">1.28517603874207</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">1.32341611385345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38770985603333</t>
+    <t xml:space="preserve">1.38770997524261</t>
   </si>
   <si>
     <t xml:space="preserve">1.41194272041321</t>
@@ -1784,25 +1784,25 @@
     <t xml:space="preserve">1.47147405147552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.448361992836</t>
+    <t xml:space="preserve">1.44836187362671</t>
   </si>
   <si>
     <t xml:space="preserve">1.53940963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54571306705475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55796933174133</t>
+    <t xml:space="preserve">1.54571318626404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55796945095062</t>
   </si>
   <si>
     <t xml:space="preserve">1.47917795181274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46376979351044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44801163673401</t>
+    <t xml:space="preserve">1.46376991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4480117559433</t>
   </si>
   <si>
     <t xml:space="preserve">1.48478090763092</t>
@@ -1820,16 +1820,16 @@
     <t xml:space="preserve">1.40458881855011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39401316642761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4315527677536</t>
+    <t xml:space="preserve">1.39401304721832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43155288696289</t>
   </si>
   <si>
     <t xml:space="preserve">1.39443337917328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35605323314667</t>
+    <t xml:space="preserve">1.35605335235596</t>
   </si>
   <si>
     <t xml:space="preserve">1.32285571098328</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">1.43330383300781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44170832633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41509437561035</t>
+    <t xml:space="preserve">1.44170844554901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41509425640106</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209792137146</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">1.29344034194946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33168029785156</t>
+    <t xml:space="preserve">1.33168041706085</t>
   </si>
   <si>
     <t xml:space="preserve">1.32551717758179</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">1.25996267795563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26864731311798</t>
+    <t xml:space="preserve">1.26864743232727</t>
   </si>
   <si>
     <t xml:space="preserve">1.24721598625183</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">1.1518257856369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1934278011322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21892094612122</t>
+    <t xml:space="preserve">1.19342768192291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21892106533051</t>
   </si>
   <si>
     <t xml:space="preserve">1.22914636135101</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">1.29400062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31851351261139</t>
+    <t xml:space="preserve">1.31851363182068</t>
   </si>
   <si>
     <t xml:space="preserve">1.31417119503021</t>
@@ -1949,28 +1949,28 @@
     <t xml:space="preserve">1.3601154088974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40879094600677</t>
+    <t xml:space="preserve">1.40879082679749</t>
   </si>
   <si>
     <t xml:space="preserve">1.47287464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49318540096283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46412014961243</t>
+    <t xml:space="preserve">1.49318528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46412026882172</t>
   </si>
   <si>
     <t xml:space="preserve">1.43505489826202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41544449329376</t>
+    <t xml:space="preserve">1.41544437408447</t>
   </si>
   <si>
     <t xml:space="preserve">1.37566351890564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38378798961639</t>
+    <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.35675370693207</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">1.40318810939789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37720429897308</t>
+    <t xml:space="preserve">1.37720441818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015241622925</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">1.39149177074432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38112640380859</t>
+    <t xml:space="preserve">1.38112652301788</t>
   </si>
   <si>
     <t xml:space="preserve">1.32103478908539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30296516418457</t>
+    <t xml:space="preserve">1.30296528339386</t>
   </si>
   <si>
     <t xml:space="preserve">1.28615641593933</t>
@@ -2012,16 +2012,16 @@
     <t xml:space="preserve">1.28993844985962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32824850082397</t>
+    <t xml:space="preserve">1.32824862003326</t>
   </si>
   <si>
     <t xml:space="preserve">1.33175039291382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.359414935112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36606860160828</t>
+    <t xml:space="preserve">1.35941505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36606848239899</t>
   </si>
   <si>
     <t xml:space="preserve">1.3664186000824</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">1.37587368488312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37727439403534</t>
+    <t xml:space="preserve">1.37727451324463</t>
   </si>
   <si>
     <t xml:space="preserve">1.37622380256653</t>
@@ -2042,34 +2042,34 @@
     <t xml:space="preserve">1.43575513362885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45956766605377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828291893005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43855667114258</t>
+    <t xml:space="preserve">1.45956778526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828279972076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43855655193329</t>
   </si>
   <si>
     <t xml:space="preserve">1.49178457260132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48127925395966</t>
+    <t xml:space="preserve">1.48127913475037</t>
   </si>
   <si>
     <t xml:space="preserve">1.44205856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38077628612518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38532853126526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2722190618515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24595534801483</t>
+    <t xml:space="preserve">1.38077616691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38532865047455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27221894264221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24595546722412</t>
   </si>
   <si>
     <t xml:space="preserve">1.19973111152649</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">1.19798016548157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24945735931396</t>
+    <t xml:space="preserve">1.24945724010468</t>
   </si>
   <si>
     <t xml:space="preserve">1.20918595790863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19587910175323</t>
+    <t xml:space="preserve">1.19587898254395</t>
   </si>
   <si>
     <t xml:space="preserve">1.18082106113434</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">1.13914906978607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1493045091629</t>
+    <t xml:space="preserve">1.14930462837219</t>
   </si>
   <si>
     <t xml:space="preserve">1.16261148452759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15350663661957</t>
+    <t xml:space="preserve">1.15350675582886</t>
   </si>
   <si>
     <t xml:space="preserve">1.19377779960632</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">1.18432295322418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19482851028442</t>
+    <t xml:space="preserve">1.19482839107513</t>
   </si>
   <si>
     <t xml:space="preserve">1.16821432113647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1710159778595</t>
+    <t xml:space="preserve">1.17101585865021</t>
   </si>
   <si>
     <t xml:space="preserve">1.1570086479187</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">1.20323300361633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25365948677063</t>
+    <t xml:space="preserve">1.25365936756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.24560511112213</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">1.23790109157562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23474955558777</t>
+    <t xml:space="preserve">1.23474943637848</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875688552856</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">1.26451504230499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24105274677277</t>
+    <t xml:space="preserve">1.24105262756348</t>
   </si>
   <si>
     <t xml:space="preserve">1.23825120925903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31949400901794</t>
+    <t xml:space="preserve">1.31949412822723</t>
   </si>
   <si>
     <t xml:space="preserve">1.36256670951843</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">1.33350145816803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33630275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34295654296875</t>
+    <t xml:space="preserve">1.33630287647247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34295642375946</t>
   </si>
   <si>
     <t xml:space="preserve">1.31214022636414</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">1.32439661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914377212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22634506225586</t>
+    <t xml:space="preserve">1.31914365291595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22634494304657</t>
   </si>
   <si>
     <t xml:space="preserve">1.23159766197205</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">1.23720073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23124754428864</t>
+    <t xml:space="preserve">1.23124766349792</t>
   </si>
   <si>
     <t xml:space="preserve">1.21163725852966</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">1.17241668701172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18222165107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18817484378815</t>
+    <t xml:space="preserve">1.18222177028656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18817496299744</t>
   </si>
   <si>
     <t xml:space="preserve">1.1846729516983</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">1.26731646060944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15175569057465</t>
+    <t xml:space="preserve">1.15175580978394</t>
   </si>
   <si>
     <t xml:space="preserve">1.13529717922211</t>
@@ -2246,25 +2246,25 @@
     <t xml:space="preserve">1.18047082424164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1342465877533</t>
+    <t xml:space="preserve">1.13424646854401</t>
   </si>
   <si>
     <t xml:space="preserve">1.18012058734894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20603430271149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17521822452545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18992590904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21583950519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21653997898102</t>
+    <t xml:space="preserve">1.20603442192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17521810531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18992578983307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21583938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21653985977173</t>
   </si>
   <si>
     <t xml:space="preserve">1.23404908180237</t>
@@ -2291,37 +2291,37 @@
     <t xml:space="preserve">1.30548655986786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32474684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31844341754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35171091556549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31424117088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34050512313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36816966533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35066032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29743254184723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31003892421722</t>
+    <t xml:space="preserve">1.324746966362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31844353675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3517107963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31424129009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34050524234772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36816954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35066044330597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29743242263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31003904342651</t>
   </si>
   <si>
     <t xml:space="preserve">1.33980464935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33210051059723</t>
+    <t xml:space="preserve">1.33210062980652</t>
   </si>
   <si>
     <t xml:space="preserve">1.29007852077484</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">1.27081847190857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27537083625793</t>
+    <t xml:space="preserve">1.27537071704865</t>
   </si>
   <si>
     <t xml:space="preserve">1.2876273393631</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">1.31249034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32789838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28307485580444</t>
+    <t xml:space="preserve">1.32789850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28307497501373</t>
   </si>
   <si>
     <t xml:space="preserve">1.30968880653381</t>
@@ -2354,16 +2354,16 @@
     <t xml:space="preserve">1.50929379463196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50859344005585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49598670005798</t>
+    <t xml:space="preserve">1.50859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49598681926727</t>
   </si>
   <si>
     <t xml:space="preserve">1.47707676887512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4686723947525</t>
+    <t xml:space="preserve">1.46867227554321</t>
   </si>
   <si>
     <t xml:space="preserve">1.42314863204956</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">1.42665028572083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47777712345123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49528634548187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49388575553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44766139984131</t>
+    <t xml:space="preserve">1.47777724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49528646469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49388563632965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44766128063202</t>
   </si>
   <si>
     <t xml:space="preserve">1.42104756832123</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">1.44135808944702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45536541938782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46517074108124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43085241317749</t>
+    <t xml:space="preserve">1.45536553859711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46517062187195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43085253238678</t>
   </si>
   <si>
     <t xml:space="preserve">1.41824591159821</t>
@@ -2417,16 +2417,16 @@
     <t xml:space="preserve">1.37412285804749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41474401950836</t>
+    <t xml:space="preserve">1.41474413871765</t>
   </si>
   <si>
     <t xml:space="preserve">1.4035382270813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4098414182663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45326435565948</t>
+    <t xml:space="preserve">1.40984153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45326447486877</t>
   </si>
   <si>
     <t xml:space="preserve">1.42034721374512</t>
@@ -2435,16 +2435,16 @@
     <t xml:space="preserve">1.36851978302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37797462940216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38637924194336</t>
+    <t xml:space="preserve">1.37797474861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38637936115265</t>
   </si>
   <si>
     <t xml:space="preserve">1.4616687297821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42595016956329</t>
+    <t xml:space="preserve">1.42594993114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.43435442447662</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">1.38287723064423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36886978149414</t>
+    <t xml:space="preserve">1.36886990070343</t>
   </si>
   <si>
     <t xml:space="preserve">1.39373314380646</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">1.35836458206177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37307214736938</t>
+    <t xml:space="preserve">1.37307238578796</t>
   </si>
   <si>
     <t xml:space="preserve">1.46727168560028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5204998254776</t>
+    <t xml:space="preserve">1.52049970626831</t>
   </si>
   <si>
     <t xml:space="preserve">1.54641330242157</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">1.38848030567169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30128443241119</t>
+    <t xml:space="preserve">1.30128455162048</t>
   </si>
   <si>
     <t xml:space="preserve">1.1423008441925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09397542476654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05755627155304</t>
+    <t xml:space="preserve">1.09397554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05755615234375</t>
   </si>
   <si>
     <t xml:space="preserve">0.905926525592804</t>
@@ -2513,37 +2513,37 @@
     <t xml:space="preserve">0.926937580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772156059741974</t>
+    <t xml:space="preserve">0.772156119346619</t>
   </si>
   <si>
     <t xml:space="preserve">0.88841724395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818030118942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874409854412079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874760031700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885966002941132</t>
+    <t xml:space="preserve">0.818030178546906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874409973621368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874760091304779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885965943336487</t>
   </si>
   <si>
     <t xml:space="preserve">0.877561628818512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870207726955414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926587402820587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912930309772491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925886929035187</t>
+    <t xml:space="preserve">0.870207607746124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926587283611298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912930190563202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925886988639832</t>
   </si>
   <si>
     <t xml:space="preserve">0.880713224411011</t>
@@ -2552,28 +2552,28 @@
     <t xml:space="preserve">0.84919661283493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840442061424255</t>
+    <t xml:space="preserve">0.840442180633545</t>
   </si>
   <si>
     <t xml:space="preserve">0.823633134365082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846044957637787</t>
+    <t xml:space="preserve">0.846044838428497</t>
   </si>
   <si>
     <t xml:space="preserve">0.830987095832825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851297736167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829936444759369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85304868221283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820131301879883</t>
+    <t xml:space="preserve">0.851297795772552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829936504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853048741817474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820131421089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.777408838272095</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">0.778809666633606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753246188163757</t>
+    <t xml:space="preserve">0.753246247768402</t>
   </si>
   <si>
     <t xml:space="preserve">0.751845479011536</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">0.771805882453918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743791282176971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768304109573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789665460586548</t>
+    <t xml:space="preserve">0.743791222572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768304049968719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789665400981903</t>
   </si>
   <si>
     <t xml:space="preserve">0.809625864028931</t>
@@ -2609,22 +2609,22 @@
     <t xml:space="preserve">0.779860138893127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766553163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611144542694</t>
+    <t xml:space="preserve">0.766553103923798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611084938049</t>
   </si>
   <si>
     <t xml:space="preserve">0.776008248329163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765152454376221</t>
+    <t xml:space="preserve">0.765152394771576</t>
   </si>
   <si>
     <t xml:space="preserve">0.803672730922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812077105045319</t>
+    <t xml:space="preserve">0.812077045440674</t>
   </si>
   <si>
     <t xml:space="preserve">0.807874917984009</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">0.781260907649994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819080770015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759199261665344</t>
+    <t xml:space="preserve">0.819080889225006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759199321269989</t>
   </si>
   <si>
     <t xml:space="preserve">0.756047666072845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730484247207642</t>
+    <t xml:space="preserve">0.730484187602997</t>
   </si>
   <si>
     <t xml:space="preserve">0.736087143421173</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">0.779159724712372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815228819847107</t>
+    <t xml:space="preserve">0.815228760242462</t>
   </si>
   <si>
     <t xml:space="preserve">0.805773913860321</t>
@@ -2672,22 +2672,22 @@
     <t xml:space="preserve">0.89296954870224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931840121746063</t>
+    <t xml:space="preserve">0.931840062141418</t>
   </si>
   <si>
     <t xml:space="preserve">0.994873464107513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00853061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979115009307861</t>
+    <t xml:space="preserve">1.00853049755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979115128517151</t>
   </si>
   <si>
     <t xml:space="preserve">0.966858565807343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891218781471252</t>
+    <t xml:space="preserve">0.891218721866608</t>
   </si>
   <si>
     <t xml:space="preserve">0.895070791244507</t>
@@ -2696,10 +2696,10 @@
     <t xml:space="preserve">0.901724278926849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967909097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964407205581665</t>
+    <t xml:space="preserve">0.967908978462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96440726518631</t>
   </si>
   <si>
     <t xml:space="preserve">0.94689804315567</t>
@@ -2708,79 +2708,79 @@
     <t xml:space="preserve">0.936392605304718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938493549823761</t>
+    <t xml:space="preserve">0.938493669033051</t>
   </si>
   <si>
     <t xml:space="preserve">0.965107679367065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913980782032013</t>
+    <t xml:space="preserve">0.913980662822723</t>
   </si>
   <si>
     <t xml:space="preserve">0.934641599655151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899623274803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953551650047302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930089116096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909078180789948</t>
+    <t xml:space="preserve">0.899623155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953551530838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930089235305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909078240394592</t>
   </si>
   <si>
     <t xml:space="preserve">0.954602062702179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943746209144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983317196369171</t>
+    <t xml:space="preserve">0.943746328353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983317315578461</t>
   </si>
   <si>
     <t xml:space="preserve">0.97316187620163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951450526714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916432082653046</t>
+    <t xml:space="preserve">0.951450407505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91643214225769</t>
   </si>
   <si>
     <t xml:space="preserve">0.933941185474396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948298573493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957403421401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97351199388504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980866014957428</t>
+    <t xml:space="preserve">0.948298692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957403540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97351211309433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980865895748138</t>
   </si>
   <si>
     <t xml:space="preserve">1.033043384552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03759574890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00012600421906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998725414276123</t>
+    <t xml:space="preserve">1.03759586811066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00012612342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998725295066833</t>
   </si>
   <si>
     <t xml:space="preserve">0.960905253887177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967208743095398</t>
+    <t xml:space="preserve">0.967208623886108</t>
   </si>
   <si>
     <t xml:space="preserve">0.944096624851227</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">0.893670082092285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890168309211731</t>
+    <t xml:space="preserve">0.890168249607086</t>
   </si>
   <si>
     <t xml:space="preserve">0.874059736728668</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">0.890868544578552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91538143157959</t>
+    <t xml:space="preserve">0.915381491184235</t>
   </si>
   <si>
     <t xml:space="preserve">0.978764712810516</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">1.00572907924652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997324526309967</t>
+    <t xml:space="preserve">0.997324645519257</t>
   </si>
   <si>
     <t xml:space="preserve">0.981566309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00923073291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98681902885437</t>
+    <t xml:space="preserve">1.0092306137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98681914806366</t>
   </si>
   <si>
     <t xml:space="preserve">0.987519443035126</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">0.996624231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999775946140289</t>
+    <t xml:space="preserve">0.999775826931</t>
   </si>
   <si>
     <t xml:space="preserve">1.00467824935913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988920092582703</t>
+    <t xml:space="preserve">0.988919973373413</t>
   </si>
   <si>
     <t xml:space="preserve">0.985768616199493</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">0.958103895187378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994523048400879</t>
+    <t xml:space="preserve">0.994522988796234</t>
   </si>
   <si>
     <t xml:space="preserve">0.978414714336395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986118733882904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03724551200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02148735523224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01903593540192</t>
+    <t xml:space="preserve">0.986118614673615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03724539279938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02148723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01903605461121</t>
   </si>
   <si>
     <t xml:space="preserve">1.01203227043152</t>
@@ -2885,31 +2885,31 @@
     <t xml:space="preserve">0.97386223077774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916782140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922735393047333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888067066669464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939544200897217</t>
+    <t xml:space="preserve">0.916782200336456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922735333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888067007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939544320106506</t>
   </si>
   <si>
     <t xml:space="preserve">0.961605727672577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972811698913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05405449867249</t>
+    <t xml:space="preserve">0.972811818122864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0540543794632</t>
   </si>
   <si>
     <t xml:space="preserve">1.11113452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09957849979401</t>
+    <t xml:space="preserve">1.09957838058472</t>
   </si>
   <si>
     <t xml:space="preserve">1.16121077537537</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">1.16961514949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15910959243774</t>
+    <t xml:space="preserve">1.15910947322845</t>
   </si>
   <si>
     <t xml:space="preserve">1.12339091300964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12829339504242</t>
+    <t xml:space="preserve">1.12829327583313</t>
   </si>
   <si>
     <t xml:space="preserve">1.12794327735901</t>
@@ -2939,25 +2939,25 @@
     <t xml:space="preserve">1.13564741611481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545238018036</t>
+    <t xml:space="preserve">1.17066562175751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545249938965</t>
   </si>
   <si>
     <t xml:space="preserve">1.15280640125275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17591845989227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1556077003479</t>
+    <t xml:space="preserve">1.17591857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15560781955719</t>
   </si>
   <si>
     <t xml:space="preserve">1.13214552402496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08522093296051</t>
+    <t xml:space="preserve">1.08522081375122</t>
   </si>
   <si>
     <t xml:space="preserve">1.05965733528137</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">1.15490758419037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15455722808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066291332245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2512081861496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25611054897308</t>
+    <t xml:space="preserve">1.15455734729767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25120806694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25611078739166</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502059936523</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">1.32684803009033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35801434516907</t>
+    <t xml:space="preserve">1.35801422595978</t>
   </si>
   <si>
     <t xml:space="preserve">1.3233460187912</t>
@@ -3026,25 +3026,25 @@
     <t xml:space="preserve">1.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26941764354706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24315392971039</t>
+    <t xml:space="preserve">1.26941776275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2431538105011</t>
   </si>
   <si>
     <t xml:space="preserve">1.25435972213745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2725692987442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26136350631714</t>
+    <t xml:space="preserve">1.27256941795349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26136338710785</t>
   </si>
   <si>
     <t xml:space="preserve">1.2666163444519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26416480541229</t>
+    <t xml:space="preserve">1.26416492462158</t>
   </si>
   <si>
     <t xml:space="preserve">1.2652153968811</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">1.25821173191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32964944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957037448883</t>
+    <t xml:space="preserve">1.32964932918549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957049369812</t>
   </si>
   <si>
     <t xml:space="preserve">1.34505748748779</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">1.31073939800262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31774306297302</t>
+    <t xml:space="preserve">1.31774318218231</t>
   </si>
   <si>
     <t xml:space="preserve">1.2806236743927</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">1.24735605716705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26696634292603</t>
+    <t xml:space="preserve">1.26696646213531</t>
   </si>
   <si>
     <t xml:space="preserve">1.25015759468079</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">1.29112911224365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27432024478912</t>
+    <t xml:space="preserve">1.27432012557983</t>
   </si>
   <si>
     <t xml:space="preserve">1.29953348636627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34820914268494</t>
+    <t xml:space="preserve">1.34820902347565</t>
   </si>
   <si>
     <t xml:space="preserve">1.42174768447876</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">1.48898303508759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50088930130005</t>
+    <t xml:space="preserve">1.50088918209076</t>
   </si>
   <si>
     <t xml:space="preserve">1.51629745960236</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">1.54361176490784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60594475269318</t>
+    <t xml:space="preserve">1.60594463348389</t>
   </si>
   <si>
     <t xml:space="preserve">1.62695562839508</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">1.59053647518158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59193754196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909369945526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70119488239288</t>
+    <t xml:space="preserve">1.59193742275238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909381866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70119476318359</t>
   </si>
   <si>
     <t xml:space="preserve">1.72360634803772</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">1.71029949188232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70469677448273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71100008487701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881970882416</t>
+    <t xml:space="preserve">1.70469665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71099996566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881994724274</t>
   </si>
   <si>
     <t xml:space="preserve">1.70539689064026</t>
@@ -3191,28 +3191,28 @@
     <t xml:space="preserve">1.68998885154724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65356969833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63536012172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64936780929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63466000556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62835669517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6654759645462</t>
+    <t xml:space="preserve">1.65356957912445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63536024093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64936769008636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63465988636017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62835657596588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66547584533691</t>
   </si>
   <si>
     <t xml:space="preserve">1.71505236625671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61877381801605</t>
+    <t xml:space="preserve">1.61877369880676</t>
   </si>
   <si>
     <t xml:space="preserve">1.5993744134903</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">1.6130256652832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62308478355408</t>
+    <t xml:space="preserve">1.62308466434479</t>
   </si>
   <si>
     <t xml:space="preserve">1.65613567829132</t>
@@ -3230,22 +3230,22 @@
     <t xml:space="preserve">1.67337942123413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71936333179474</t>
+    <t xml:space="preserve">1.71936321258545</t>
   </si>
   <si>
     <t xml:space="preserve">1.71289694309235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70283770561218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73445188999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71145975589752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74522924423218</t>
+    <t xml:space="preserve">1.70283782482147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73445177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71145987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74522912502289</t>
   </si>
   <si>
     <t xml:space="preserve">1.76893961429596</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">1.81707894802094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83504140377045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85587763786316</t>
+    <t xml:space="preserve">1.83504104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85587751865387</t>
   </si>
   <si>
     <t xml:space="preserve">1.86449980735779</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">1.92126107215881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95934128761292</t>
+    <t xml:space="preserve">1.95934104919434</t>
   </si>
   <si>
     <t xml:space="preserve">1.97299265861511</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">1.98377025127411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9406601190567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96508944034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99742162227631</t>
+    <t xml:space="preserve">1.94066035747528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650890827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9974217414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.02400588989258</t>
@@ -3296,43 +3296,43 @@
     <t xml:space="preserve">2.08579683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08795213699341</t>
+    <t xml:space="preserve">2.08795237541199</t>
   </si>
   <si>
     <t xml:space="preserve">2.10375905036926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12531399726868</t>
+    <t xml:space="preserve">2.1253137588501</t>
   </si>
   <si>
     <t xml:space="preserve">2.13465452194214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1540539264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15189838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18423104286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17201638221741</t>
+    <t xml:space="preserve">2.15405368804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15189814567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18423080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17201662063599</t>
   </si>
   <si>
     <t xml:space="preserve">2.17991971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17560911178589</t>
+    <t xml:space="preserve">2.17560887336731</t>
   </si>
   <si>
     <t xml:space="preserve">2.17632746696472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16052055358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12818813323975</t>
+    <t xml:space="preserve">2.16052031517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12818789482117</t>
   </si>
   <si>
     <t xml:space="preserve">2.08938932418823</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">2.08292269706726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04771614074707</t>
+    <t xml:space="preserve">2.04771637916565</t>
   </si>
   <si>
     <t xml:space="preserve">2.04196834564209</t>
@@ -3356,10 +3356,10 @@
     <t xml:space="preserve">2.01897621154785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04053139686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98305153846741</t>
+    <t xml:space="preserve">2.04053115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98305177688599</t>
   </si>
   <si>
     <t xml:space="preserve">1.96652626991272</t>
@@ -3368,43 +3368,43 @@
     <t xml:space="preserve">1.94928228855133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9521564245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90114307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83288586139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93922340869904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93634915351868</t>
+    <t xml:space="preserve">1.95215618610382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90114295482635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83288598060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93922317028046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93634939193726</t>
   </si>
   <si>
     <t xml:space="preserve">1.91766846179962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88821005821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749158382416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84653735160828</t>
+    <t xml:space="preserve">1.8882098197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749182224274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84653723239899</t>
   </si>
   <si>
     <t xml:space="preserve">1.7876204252243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8264194726944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8752772808075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85803294181824</t>
+    <t xml:space="preserve">1.82641935348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87527704238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85803306102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.90258014202118</t>
@@ -3419,25 +3419,25 @@
     <t xml:space="preserve">1.82067120075226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81348621845245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82857489585876</t>
+    <t xml:space="preserve">1.81348633766174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82857477664948</t>
   </si>
   <si>
     <t xml:space="preserve">1.96724474430084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97371113300323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95718586444855</t>
+    <t xml:space="preserve">1.97371137142181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95718562602997</t>
   </si>
   <si>
     <t xml:space="preserve">2.03190946578979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00676226615906</t>
+    <t xml:space="preserve">2.00676202774048</t>
   </si>
   <si>
     <t xml:space="preserve">2.00388813018799</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">1.94209730625153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97802233695984</t>
+    <t xml:space="preserve">1.97802209854126</t>
   </si>
   <si>
     <t xml:space="preserve">2.01107311248779</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">1.99957704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01753950119019</t>
+    <t xml:space="preserve">2.01753973960876</t>
   </si>
   <si>
     <t xml:space="preserve">2.03262805938721</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">2.03119111061096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99167346954346</t>
+    <t xml:space="preserve">1.99167382717133</t>
   </si>
   <si>
     <t xml:space="preserve">2.01322865486145</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">1.95000100135803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93778657913208</t>
+    <t xml:space="preserve">1.9377863407135</t>
   </si>
   <si>
     <t xml:space="preserve">1.96868193149567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92269825935364</t>
+    <t xml:space="preserve">1.92269802093506</t>
   </si>
   <si>
     <t xml:space="preserve">1.94712698459625</t>
@@ -3500,16 +3500,16 @@
     <t xml:space="preserve">1.92916429042816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83073019981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84078919887543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92054235935211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97586679458618</t>
+    <t xml:space="preserve">1.83073008060455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84078931808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92054259777069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97586667537689</t>
   </si>
   <si>
     <t xml:space="preserve">1.92341661453247</t>
@@ -3521,40 +3521,40 @@
     <t xml:space="preserve">1.94425284862518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91838717460632</t>
+    <t xml:space="preserve">1.91838693618774</t>
   </si>
   <si>
     <t xml:space="preserve">2.02616143226624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02831697463989</t>
+    <t xml:space="preserve">2.02831721305847</t>
   </si>
   <si>
     <t xml:space="preserve">2.0218505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03047251701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994212150574</t>
+    <t xml:space="preserve">2.03047227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994188308716</t>
   </si>
   <si>
     <t xml:space="preserve">2.04340577125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10016679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12387728691101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09226298332214</t>
+    <t xml:space="preserve">2.10016655921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12387704849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
     <t xml:space="preserve">2.1231586933136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13034319877625</t>
+    <t xml:space="preserve">2.13034343719482</t>
   </si>
   <si>
     <t xml:space="preserve">2.14758729934692</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">2.08148574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92988324165344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93563091754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083723545074</t>
+    <t xml:space="preserve">1.92988300323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93563067913055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97083735466003</t>
   </si>
   <si>
     <t xml:space="preserve">2.00963592529297</t>
@@ -3581,34 +3581,34 @@
     <t xml:space="preserve">2.08364129066467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0376570224762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00317001342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98592567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95143795013428</t>
+    <t xml:space="preserve">2.03765749931335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00316977500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9859254360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143818855286</t>
   </si>
   <si>
     <t xml:space="preserve">1.90042436122894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88318061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85372233390808</t>
+    <t xml:space="preserve">1.88318049907684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85372221469879</t>
   </si>
   <si>
     <t xml:space="preserve">1.74594759941101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77540600299835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77181363105774</t>
+    <t xml:space="preserve">1.77540612220764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77181386947632</t>
   </si>
   <si>
     <t xml:space="preserve">1.8084568977356</t>
@@ -3620,31 +3620,31 @@
     <t xml:space="preserve">1.88533616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92557179927826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8896472454071</t>
+    <t xml:space="preserve">1.92557203769684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88964700698853</t>
   </si>
   <si>
     <t xml:space="preserve">1.88677287101746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86737358570099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395821094513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89036548137665</t>
+    <t xml:space="preserve">1.86737370491028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395797252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89036571979523</t>
   </si>
   <si>
     <t xml:space="preserve">1.8544408082962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84797441959381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79767942428589</t>
+    <t xml:space="preserve">1.84797430038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79767966270447</t>
   </si>
   <si>
     <t xml:space="preserve">1.85659635066986</t>
@@ -3653,28 +3653,28 @@
     <t xml:space="preserve">1.85875177383423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84725570678711</t>
+    <t xml:space="preserve">1.8472558259964</t>
   </si>
   <si>
     <t xml:space="preserve">1.85515940189362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8860547542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97874057292938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00101399421692</t>
+    <t xml:space="preserve">1.88605463504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683222770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97874081134796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0010142326355</t>
   </si>
   <si>
     <t xml:space="preserve">2.02544283866882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06280469894409</t>
+    <t xml:space="preserve">2.06280493736267</t>
   </si>
   <si>
     <t xml:space="preserve">2.05849385261536</t>
@@ -3686,34 +3686,34 @@
     <t xml:space="preserve">2.0563383102417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05274605751038</t>
+    <t xml:space="preserve">2.0527458190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.02113199234009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00460648536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01251029968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99526607990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89970588684082</t>
+    <t xml:space="preserve">2.0046067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01251006126404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99526584148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8997061252594</t>
   </si>
   <si>
     <t xml:space="preserve">1.87958800792694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93131995201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221506595612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91192042827606</t>
+    <t xml:space="preserve">1.93131971359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221530437469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91192030906677</t>
   </si>
   <si>
     <t xml:space="preserve">2.02041339874268</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">2.06855273246765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10447788238525</t>
+    <t xml:space="preserve">2.1044774055481</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645630836487</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">2.15118002891541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3250560760498</t>
+    <t xml:space="preserve">2.32505631446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.32361936569214</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">2.55928635597229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.527672290802</t>
+    <t xml:space="preserve">2.52767252922058</t>
   </si>
   <si>
     <t xml:space="preserve">2.57509326934814</t>
@@ -3761,10 +3761,10 @@
     <t xml:space="preserve">2.52336168289185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51042819023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41343140602112</t>
+    <t xml:space="preserve">2.5104284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343116760254</t>
   </si>
   <si>
     <t xml:space="preserve">2.21584486961365</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">2.21368932723999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496047973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120195388794</t>
+    <t xml:space="preserve">2.06496071815491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120219230652</t>
   </si>
   <si>
     <t xml:space="preserve">1.66475737094879</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">1.74954009056091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79480540752411</t>
+    <t xml:space="preserve">1.7948055267334</t>
   </si>
   <si>
     <t xml:space="preserve">1.83575987815857</t>
@@ -3806,16 +3806,16 @@
     <t xml:space="preserve">1.95862281322479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879969120026</t>
+    <t xml:space="preserve">1.98879945278168</t>
   </si>
   <si>
     <t xml:space="preserve">1.9557489156723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359313488007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06208634376526</t>
+    <t xml:space="preserve">1.95359337329865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06208610534668</t>
   </si>
   <si>
     <t xml:space="preserve">1.93275690078735</t>
@@ -3851,13 +3851,13 @@
     <t xml:space="preserve">2.35257959365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35181331634521</t>
+    <t xml:space="preserve">2.35181355476379</t>
   </si>
   <si>
     <t xml:space="preserve">2.36713457107544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.321937084198</t>
+    <t xml:space="preserve">2.32193684577942</t>
   </si>
   <si>
     <t xml:space="preserve">2.35104727745056</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">2.21085786819458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13731598854065</t>
+    <t xml:space="preserve">2.13731575012207</t>
   </si>
   <si>
     <t xml:space="preserve">2.15876579284668</t>
@@ -3890,28 +3890,28 @@
     <t xml:space="preserve">2.25069308280945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23307347297668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21545386314392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28286790847778</t>
+    <t xml:space="preserve">2.23307371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2154541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2828676700592</t>
   </si>
   <si>
     <t xml:space="preserve">2.26448249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31351041793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38092374801636</t>
+    <t xml:space="preserve">2.31351017951965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38092398643494</t>
   </si>
   <si>
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45523190498352</t>
+    <t xml:space="preserve">2.45523166656494</t>
   </si>
   <si>
     <t xml:space="preserve">2.47285151481628</t>
@@ -3932,19 +3932,19 @@
     <t xml:space="preserve">2.47438359260559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41309857368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43071794509888</t>
+    <t xml:space="preserve">2.41309881210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43071818351746</t>
   </si>
   <si>
     <t xml:space="preserve">2.37709355354309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09058594703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98793339729309</t>
+    <t xml:space="preserve">2.09058618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98793363571167</t>
   </si>
   <si>
     <t xml:space="preserve">2.0116810798645</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">2.21315598487854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1993670463562</t>
+    <t xml:space="preserve">2.19936680793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.13501763343811</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">2.0315990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99406182765961</t>
+    <t xml:space="preserve">1.99406206607819</t>
   </si>
   <si>
     <t xml:space="preserve">1.90290057659149</t>
@@ -4001,13 +4001,13 @@
     <t xml:space="preserve">1.98563539981842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91592359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86842751502991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472073078156</t>
+    <t xml:space="preserve">1.91592335700989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8684276342392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472084999084</t>
   </si>
   <si>
     <t xml:space="preserve">1.73743093013763</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">1.77420198917389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83012437820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92435050010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87915241718292</t>
+    <t xml:space="preserve">1.83012449741364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92435026168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8791526556015</t>
   </si>
   <si>
     <t xml:space="preserve">1.80331230163574</t>
@@ -4031,19 +4031,19 @@
     <t xml:space="preserve">1.79718387126923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8538726568222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79641771316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84544575214386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86306512355804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92894685268402</t>
+    <t xml:space="preserve">1.85387253761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79641759395599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84544563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86306500434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92894661426544</t>
   </si>
   <si>
     <t xml:space="preserve">1.92051994800568</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">1.95652496814728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99176359176636</t>
+    <t xml:space="preserve">1.99176383018494</t>
   </si>
   <si>
     <t xml:space="preserve">2.07220029830933</t>
@@ -4094,25 +4094,25 @@
     <t xml:space="preserve">1.90826284885406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86076688766479</t>
+    <t xml:space="preserve">1.86076700687408</t>
   </si>
   <si>
     <t xml:space="preserve">1.80944073200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86612963676453</t>
+    <t xml:space="preserve">1.86612951755524</t>
   </si>
   <si>
     <t xml:space="preserve">1.89830422401428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90213465690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87149202823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96878206729889</t>
+    <t xml:space="preserve">1.90213441848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8714919090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96878182888031</t>
   </si>
   <si>
     <t xml:space="preserve">1.90060234069824</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">1.99712634086609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06070947647095</t>
+    <t xml:space="preserve">2.06070971488953</t>
   </si>
   <si>
     <t xml:space="preserve">2.12199449539185</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">2.21392202377319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15799951553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12965512275696</t>
+    <t xml:space="preserve">2.15799927711487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12965536117554</t>
   </si>
   <si>
     <t xml:space="preserve">2.0928840637207</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">2.07143425941467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02700281143188</t>
+    <t xml:space="preserve">2.02700257301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.06377363204956</t>
@@ -4190,7 +4190,7 @@
     <t xml:space="preserve">2.11893033981323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17485284805298</t>
+    <t xml:space="preserve">2.17485308647156</t>
   </si>
   <si>
     <t xml:space="preserve">2.17255449295044</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">2.3173406124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34415292739868</t>
+    <t xml:space="preserve">2.3441526889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.34491896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37173128128052</t>
+    <t xml:space="preserve">2.37173104286194</t>
   </si>
   <si>
     <t xml:space="preserve">2.41922688484192</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">2.41769456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45140194892883</t>
+    <t xml:space="preserve">2.45140171051025</t>
   </si>
   <si>
     <t xml:space="preserve">2.45906209945679</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">2.55175590515137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52187967300415</t>
+    <t xml:space="preserve">2.52187943458557</t>
   </si>
   <si>
     <t xml:space="preserve">2.53796672821045</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">2.40390586853027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41080045700073</t>
+    <t xml:space="preserve">2.41080021858215</t>
   </si>
   <si>
     <t xml:space="preserve">2.40313982963562</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">2.46672296524048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5686092376709</t>
+    <t xml:space="preserve">2.56860947608948</t>
   </si>
   <si>
     <t xml:space="preserve">2.59465551376343</t>
@@ -4331,19 +4331,19 @@
     <t xml:space="preserve">2.56477904319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57703590393066</t>
+    <t xml:space="preserve">2.57703614234924</t>
   </si>
   <si>
     <t xml:space="preserve">2.55405426025391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62376594543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67739033699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77774453163147</t>
+    <t xml:space="preserve">2.62376570701599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67739009857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77774429321289</t>
   </si>
   <si>
     <t xml:space="preserve">2.78923559188843</t>
@@ -4364,16 +4364,16 @@
     <t xml:space="preserve">2.82141017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94014978408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92176413536072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93172311782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89725017547607</t>
+    <t xml:space="preserve">2.94014954566956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9217643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93172287940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89725041389465</t>
   </si>
   <si>
     <t xml:space="preserve">2.92636060714722</t>
@@ -4382,19 +4382,19 @@
     <t xml:space="preserve">2.95700335502625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99453997612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00756335258484</t>
+    <t xml:space="preserve">2.99454021453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00756359100342</t>
   </si>
   <si>
     <t xml:space="preserve">3.07038044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09106397628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07957339286804</t>
+    <t xml:space="preserve">3.09106421470642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07957315444946</t>
   </si>
   <si>
     <t xml:space="preserve">3.16154193878174</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">3.29024076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22435927391052</t>
+    <t xml:space="preserve">3.2243595123291</t>
   </si>
   <si>
     <t xml:space="preserve">3.22052884101868</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">3.22282695770264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10255527496338</t>
+    <t xml:space="preserve">3.1025550365448</t>
   </si>
   <si>
     <t xml:space="preserve">3.04280209541321</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">3.11634421348572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05812382698059</t>
+    <t xml:space="preserve">3.05812358856201</t>
   </si>
   <si>
     <t xml:space="preserve">3.12860155105591</t>
@@ -4454,10 +4454,10 @@
     <t xml:space="preserve">3.16000986099243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16077589988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11711001396179</t>
+    <t xml:space="preserve">3.16077613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11711025238037</t>
   </si>
   <si>
     <t xml:space="preserve">3.15081715583801</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">3.23355197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17150044441223</t>
+    <t xml:space="preserve">3.17150068283081</t>
   </si>
   <si>
     <t xml:space="preserve">3.07727527618408</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">2.71186327934265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70573449134827</t>
+    <t xml:space="preserve">2.70573472976685</t>
   </si>
   <si>
     <t xml:space="preserve">2.80991911888123</t>
@@ -4514,13 +4514,13 @@
     <t xml:space="preserve">2.65900468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75782656669617</t>
+    <t xml:space="preserve">2.75782680511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.79996037483215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76165723800659</t>
+    <t xml:space="preserve">2.76165747642517</t>
   </si>
   <si>
     <t xml:space="preserve">2.7785108089447</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">2.75476264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82370853424072</t>
+    <t xml:space="preserve">2.82370829582214</t>
   </si>
   <si>
     <t xml:space="preserve">2.83979558944702</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">2.84132790565491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83519887924194</t>
+    <t xml:space="preserve">2.83519911766052</t>
   </si>
   <si>
     <t xml:space="preserve">2.93019104003906</t>
@@ -6261,6 +6261,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1499996185303</t>
   </si>
 </sst>
 </file>
@@ -71287,7 +71290,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6501736111</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>8458465</v>
@@ -71308,6 +71311,32 @@
         <v>2082</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.649525463</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>6293323</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>12.5600004196167</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>12.1499996185303</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>2083</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="2084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="2085">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">6.25302362442017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98424053192139</t>
+    <t xml:space="preserve">5.98424005508423</t>
   </si>
   <si>
     <t xml:space="preserve">5.89802598953247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65459871292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53795719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65967082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89295434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27424573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9420690536499</t>
+    <t xml:space="preserve">5.6545991897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53795766830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65967130661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89295387268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.274245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94206857681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.40450191497803</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">4.6149640083313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28786039352417</t>
+    <t xml:space="preserve">4.28785991668701</t>
   </si>
   <si>
     <t xml:space="preserve">4.55410718917847</t>
@@ -98,76 +98,76 @@
     <t xml:space="preserve">4.57946443557739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50339365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0520396232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11289691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961268424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52715110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22286772727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5804009437561</t>
+    <t xml:space="preserve">4.50339317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05203914642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11289644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961220741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52715134620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22286748886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040118217468</t>
   </si>
   <si>
     <t xml:space="preserve">3.26851034164429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64379286766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004109382629</t>
+    <t xml:space="preserve">3.6437931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004133224487</t>
   </si>
   <si>
     <t xml:space="preserve">4.04443311691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14332485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9151132106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818536758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08246850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7198646068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64632964134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74775624275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84157800674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92018342018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04950523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88468456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86693429946899</t>
+    <t xml:space="preserve">4.1433253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91511273384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818512916565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08246898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71986436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.646329164505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74775671958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84157705307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92018365859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22700262069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04950475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88468432426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86693453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.7604353427887</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">3.9480767250061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38768792152405</t>
+    <t xml:space="preserve">3.38768815994263</t>
   </si>
   <si>
     <t xml:space="preserve">3.4713659286499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67675709724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197106361389</t>
+    <t xml:space="preserve">3.67675757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197082519531</t>
   </si>
   <si>
     <t xml:space="preserve">3.5144727230072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38261675834656</t>
+    <t xml:space="preserve">3.38261699676514</t>
   </si>
   <si>
     <t xml:space="preserve">3.27611756324768</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">3.06565427780151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365622520447</t>
+    <t xml:space="preserve">2.92365574836731</t>
   </si>
   <si>
     <t xml:space="preserve">2.70812177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49005174636841</t>
+    <t xml:space="preserve">2.49005150794983</t>
   </si>
   <si>
     <t xml:space="preserve">2.40586709976196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2243115901947</t>
+    <t xml:space="preserve">2.22431111335754</t>
   </si>
   <si>
     <t xml:space="preserve">2.46672320365906</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">2.700514793396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91097712516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02508354187012</t>
+    <t xml:space="preserve">2.91097736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0250837802887</t>
   </si>
   <si>
     <t xml:space="preserve">3.16454696655273</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">3.22690272331238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1385657787323</t>
+    <t xml:space="preserve">3.13856554031372</t>
   </si>
   <si>
     <t xml:space="preserve">3.14116311073303</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">3.23469686508179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19052886962891</t>
+    <t xml:space="preserve">3.19052863121033</t>
   </si>
   <si>
     <t xml:space="preserve">3.32823061943054</t>
@@ -269,82 +269,82 @@
     <t xml:space="preserve">3.20351910591125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96968650817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75663757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86835789680481</t>
+    <t xml:space="preserve">2.96968603134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75663733482361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86835813522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84497451782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59607148170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51500940322876</t>
+    <t xml:space="preserve">2.84497475624084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59607172012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51500964164734</t>
   </si>
   <si>
     <t xml:space="preserve">2.28637218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32378602027893</t>
+    <t xml:space="preserve">2.32378578186035</t>
   </si>
   <si>
     <t xml:space="preserve">2.32274651527405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39237666130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23544859886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24584102630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22089910507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24480175971985</t>
+    <t xml:space="preserve">2.39237642288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23544836044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24584078788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22089886665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24480199813843</t>
   </si>
   <si>
     <t xml:space="preserve">2.24999785423279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27493977546692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47343921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47032117843628</t>
+    <t xml:space="preserve">2.2749400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47343945503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4703209400177</t>
   </si>
   <si>
     <t xml:space="preserve">2.48902797698975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49422407150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31131482124329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16581773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16685724258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05461692810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15853524208069</t>
+    <t xml:space="preserve">2.49422383308411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31131458282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16581749916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16685700416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05461668968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15853548049927</t>
   </si>
   <si>
     <t xml:space="preserve">2.29020476341248</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">2.22156858444214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15433311462402</t>
+    <t xml:space="preserve">2.15433287620544</t>
   </si>
   <si>
     <t xml:space="preserve">2.04227423667908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83636569976807</t>
+    <t xml:space="preserve">1.83636581897736</t>
   </si>
   <si>
     <t xml:space="preserve">1.7159024477005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83776652812958</t>
+    <t xml:space="preserve">1.83776664733887</t>
   </si>
   <si>
     <t xml:space="preserve">2.07449102401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01846170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02546525001526</t>
+    <t xml:space="preserve">2.01846146583557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02546501159668</t>
   </si>
   <si>
     <t xml:space="preserve">1.993248462677</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">2.12211608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62765598297119</t>
+    <t xml:space="preserve">1.62765622138977</t>
   </si>
   <si>
     <t xml:space="preserve">1.52680313587189</t>
@@ -398,22 +398,22 @@
     <t xml:space="preserve">1.50158989429474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52540230751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45676624774933</t>
+    <t xml:space="preserve">1.52540242671967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45676612854004</t>
   </si>
   <si>
     <t xml:space="preserve">1.40073668956757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31459152698517</t>
+    <t xml:space="preserve">1.31459140777588</t>
   </si>
   <si>
     <t xml:space="preserve">1.28167402744293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51699769496918</t>
+    <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
     <t xml:space="preserve">1.5702258348465</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">1.66687667369843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55621862411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64166355133057</t>
+    <t xml:space="preserve">1.55621838569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64166367053986</t>
   </si>
   <si>
     <t xml:space="preserve">1.66267454624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68788778781891</t>
+    <t xml:space="preserve">1.6878879070282</t>
   </si>
   <si>
     <t xml:space="preserve">1.67528116703033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66407513618469</t>
+    <t xml:space="preserve">1.6640750169754</t>
   </si>
   <si>
     <t xml:space="preserve">1.72990989685059</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">1.7593252658844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70749807357788</t>
+    <t xml:space="preserve">1.70749819278717</t>
   </si>
   <si>
     <t xml:space="preserve">1.76352739334106</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">1.5926376581192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58143186569214</t>
+    <t xml:space="preserve">1.58143174648285</t>
   </si>
   <si>
     <t xml:space="preserve">1.56882524490356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100538253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52820372581482</t>
+    <t xml:space="preserve">1.53100550174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52820384502411</t>
   </si>
   <si>
     <t xml:space="preserve">1.4539647102356</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">1.53520739078522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51559734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56742453575134</t>
+    <t xml:space="preserve">1.51559722423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56742441654205</t>
   </si>
   <si>
     <t xml:space="preserve">1.56182157993317</t>
@@ -515,22 +515,22 @@
     <t xml:space="preserve">1.68088436126709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63886177539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65707147121429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65847218036652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64306426048279</t>
+    <t xml:space="preserve">1.63886189460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.657071352005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6584724187851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6430641412735</t>
   </si>
   <si>
     <t xml:space="preserve">1.59403860569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60944640636444</t>
+    <t xml:space="preserve">1.60944652557373</t>
   </si>
   <si>
     <t xml:space="preserve">1.57582890987396</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">1.50018894672394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46657133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40003633499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45116341114044</t>
+    <t xml:space="preserve">1.46657145023346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40003645420074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45116329193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.47357523441315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4399573802948</t>
+    <t xml:space="preserve">1.43995749950409</t>
   </si>
   <si>
     <t xml:space="preserve">1.40633952617645</t>
@@ -560,40 +560,40 @@
     <t xml:space="preserve">1.37832498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3965345621109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40774047374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46797204017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48057878017426</t>
+    <t xml:space="preserve">1.39653444290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40774023532867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46797215938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48057889938354</t>
   </si>
   <si>
     <t xml:space="preserve">1.50299036502838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55061554908752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65286910533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78593921661377</t>
+    <t xml:space="preserve">1.55061542987823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65286922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78593933582306</t>
   </si>
   <si>
     <t xml:space="preserve">1.79994654655457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84617078304291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317468643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196901321411</t>
+    <t xml:space="preserve">1.8461709022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8531745672226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196877479553</t>
   </si>
   <si>
     <t xml:space="preserve">1.82235860824585</t>
@@ -602,40 +602,40 @@
     <t xml:space="preserve">1.85737705230713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86297988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041003704071</t>
+    <t xml:space="preserve">1.86298000812531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041015625</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379620552063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80835127830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67107892036438</t>
+    <t xml:space="preserve">1.80835139751434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67107880115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.61224794387817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50999414920807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59543919563293</t>
+    <t xml:space="preserve">1.50999402999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59543931484222</t>
   </si>
   <si>
     <t xml:space="preserve">1.60664486885071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51279580593109</t>
+    <t xml:space="preserve">1.5127956867218</t>
   </si>
   <si>
     <t xml:space="preserve">1.42735087871552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35451245307922</t>
+    <t xml:space="preserve">1.35451233386993</t>
   </si>
   <si>
     <t xml:space="preserve">1.30408585071564</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">1.31739294528961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2508579492569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30268526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35871481895447</t>
+    <t xml:space="preserve">1.25085783004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30268514156342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35871458053589</t>
   </si>
   <si>
     <t xml:space="preserve">1.39233231544495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28867793083191</t>
+    <t xml:space="preserve">1.28867781162262</t>
   </si>
   <si>
     <t xml:space="preserve">1.40493905544281</t>
@@ -674,25 +674,25 @@
     <t xml:space="preserve">1.49458622932434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64026272296906</t>
+    <t xml:space="preserve">1.64026284217834</t>
   </si>
   <si>
     <t xml:space="preserve">1.56462299823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53380656242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.679483294487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69769310951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6514687538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72290623188019</t>
+    <t xml:space="preserve">1.533806681633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67948341369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69769299030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65146863460541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7229061126709</t>
   </si>
   <si>
     <t xml:space="preserve">1.77893567085266</t>
@@ -701,19 +701,19 @@
     <t xml:space="preserve">1.71310102939606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60524451732635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092101097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87698721885681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90500223636627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643971443176</t>
+    <t xml:space="preserve">1.60524439811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092089176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8769873380661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90500199794769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643935680389</t>
   </si>
   <si>
     <t xml:space="preserve">2.03106832504272</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">1.94982540607452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90640258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94702410697937</t>
+    <t xml:space="preserve">1.90640246868134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94702422618866</t>
   </si>
   <si>
     <t xml:space="preserve">1.89799821376801</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">1.93581795692444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01706099510193</t>
+    <t xml:space="preserve">2.01706075668335</t>
   </si>
   <si>
     <t xml:space="preserve">1.97363793849945</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">2.08849883079529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00585508346558</t>
+    <t xml:space="preserve">2.00585532188416</t>
   </si>
   <si>
     <t xml:space="preserve">2.02126312255859</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">1.86017835140228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8909946680069</t>
+    <t xml:space="preserve">1.89099478721619</t>
   </si>
   <si>
     <t xml:space="preserve">1.78033626079559</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">1.67388033866882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74251627922058</t>
+    <t xml:space="preserve">1.74251651763916</t>
   </si>
   <si>
     <t xml:space="preserve">1.73831450939178</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">1.77753508090973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78173696994781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68368554115295</t>
+    <t xml:space="preserve">1.78173720836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68368566036224</t>
   </si>
   <si>
     <t xml:space="preserve">1.62205302715302</t>
@@ -803,22 +803,22 @@
     <t xml:space="preserve">1.65006756782532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71870410442352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71450173854828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68228471279144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69349050521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69629216194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8097517490387</t>
+    <t xml:space="preserve">1.71870398521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71450185775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68228483200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69349074363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69629204273224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80975198745728</t>
   </si>
   <si>
     <t xml:space="preserve">1.81535482406616</t>
@@ -827,34 +827,34 @@
     <t xml:space="preserve">1.7607262134552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80695021152496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86858296394348</t>
+    <t xml:space="preserve">1.80695033073425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86858284473419</t>
   </si>
   <si>
     <t xml:space="preserve">1.85597622394562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91620790958405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90780353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91480720043182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88539159297943</t>
+    <t xml:space="preserve">1.91620779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90780341625214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91480708122253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88539171218872</t>
   </si>
   <si>
     <t xml:space="preserve">1.88819336891174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94562351703644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90360105037689</t>
+    <t xml:space="preserve">1.94562339782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90360128879547</t>
   </si>
   <si>
     <t xml:space="preserve">1.89939892292023</t>
@@ -863,34 +863,34 @@
     <t xml:space="preserve">1.87978875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86718225479126</t>
+    <t xml:space="preserve">1.86718201637268</t>
   </si>
   <si>
     <t xml:space="preserve">1.76212704181671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95542871952057</t>
+    <t xml:space="preserve">1.95542848110199</t>
   </si>
   <si>
     <t xml:space="preserve">1.86157917976379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86998343467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00445461273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04647612571716</t>
+    <t xml:space="preserve">1.86998355388641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00445437431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04647636413574</t>
   </si>
   <si>
     <t xml:space="preserve">1.9190092086792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87838804721832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98204231262207</t>
+    <t xml:space="preserve">1.87838780879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98204219341278</t>
   </si>
   <si>
     <t xml:space="preserve">1.96383285522461</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">1.88259017467499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93021512031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97784042358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09410166740417</t>
+    <t xml:space="preserve">1.93021500110626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97784030437469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0941014289856</t>
   </si>
   <si>
     <t xml:space="preserve">2.17814564704895</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">2.11371159553528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12491774559021</t>
+    <t xml:space="preserve">2.12491750717163</t>
   </si>
   <si>
     <t xml:space="preserve">1.99464917182922</t>
@@ -923,46 +923,46 @@
     <t xml:space="preserve">2.00305342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90220046043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99885153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95262718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95402765274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9344174861908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920412540436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91060507297516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88679206371307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95823001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94422280788422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99184787273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06048369407654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207943916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10950946807861</t>
+    <t xml:space="preserve">1.90220057964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99885141849518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95262706279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95402777194977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93441760540009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920424461365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91060495376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88679218292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95823013782501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94422268867493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99184775352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06048393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207920074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10950970649719</t>
   </si>
   <si>
     <t xml:space="preserve">2.14592862129211</t>
@@ -971,64 +971,64 @@
     <t xml:space="preserve">2.0955023765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16974115371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14452791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18795108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20616054534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20896172523499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19915699958801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19635486602783</t>
+    <t xml:space="preserve">2.16974139213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14452815055847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18795084953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20616030693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20896196365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19915676116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19635510444641</t>
   </si>
   <si>
     <t xml:space="preserve">2.14172649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2033588886261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19215297698975</t>
+    <t xml:space="preserve">2.20335865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19215321540833</t>
   </si>
   <si>
     <t xml:space="preserve">2.15573382377625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16413807868958</t>
+    <t xml:space="preserve">2.16413831710815</t>
   </si>
   <si>
     <t xml:space="preserve">2.16273760795593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20756077766418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997260093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28320050239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34063100814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35884070396423</t>
+    <t xml:space="preserve">2.20756101608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997283935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28320074081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34063124656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35884046554565</t>
   </si>
   <si>
     <t xml:space="preserve">2.33082604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30561256408691</t>
+    <t xml:space="preserve">2.30561280250549</t>
   </si>
   <si>
     <t xml:space="preserve">2.26499152183533</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">2.29720830917358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30981516838074</t>
+    <t xml:space="preserve">2.30981492996216</t>
   </si>
   <si>
     <t xml:space="preserve">2.27339577674866</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">2.21036267280579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15993595123291</t>
+    <t xml:space="preserve">2.15993618965149</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713453292847</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">2.10110521316528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13052082061768</t>
+    <t xml:space="preserve">2.1305205821991</t>
   </si>
   <si>
     <t xml:space="preserve">2.18935132026672</t>
@@ -1085,46 +1085,46 @@
     <t xml:space="preserve">2.29300594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30421209335327</t>
+    <t xml:space="preserve">2.30421185493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.30141043663025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31121563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33782982826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28180027008057</t>
+    <t xml:space="preserve">2.31121587753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33782958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28180003166199</t>
   </si>
   <si>
     <t xml:space="preserve">2.33642888069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43448066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45409083366394</t>
+    <t xml:space="preserve">2.43448042869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45409059524536</t>
   </si>
   <si>
     <t xml:space="preserve">2.45689225196838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43307971954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43027806282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24117875099182</t>
+    <t xml:space="preserve">2.4330792427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43027830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2411789894104</t>
   </si>
   <si>
     <t xml:space="preserve">2.17954611778259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13192129135132</t>
+    <t xml:space="preserve">2.1319215297699</t>
   </si>
   <si>
     <t xml:space="preserve">2.23417520523071</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">2.20475959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19075226783752</t>
+    <t xml:space="preserve">2.1907525062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.15153169631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2019579410553</t>
+    <t xml:space="preserve">2.20195817947388</t>
   </si>
   <si>
     <t xml:space="preserve">2.18374872207642</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">2.21456480026245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17674493789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16834044456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09690260887146</t>
+    <t xml:space="preserve">2.17674469947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16834020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09690284729004</t>
   </si>
   <si>
     <t xml:space="preserve">2.1025059223175</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">2.13332200050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10810875892639</t>
+    <t xml:space="preserve">2.10810899734497</t>
   </si>
   <si>
     <t xml:space="preserve">2.09130001068115</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">2.04507565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9708366394043</t>
+    <t xml:space="preserve">1.97083652019501</t>
   </si>
   <si>
     <t xml:space="preserve">1.91200566291809</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">1.88959360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87558627128601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566028594971</t>
+    <t xml:space="preserve">1.8755863904953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566004753113</t>
   </si>
   <si>
     <t xml:space="preserve">1.97924101352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96943581104279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92321157455444</t>
+    <t xml:space="preserve">1.9694356918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92321169376373</t>
   </si>
   <si>
     <t xml:space="preserve">1.96523380279541</t>
@@ -1217,34 +1217,34 @@
     <t xml:space="preserve">1.77193200588226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78313791751862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8265608549118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86438047885895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177385807037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395423412323</t>
+    <t xml:space="preserve">1.78313779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82656061649323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86438059806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177397727966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395399570465</t>
   </si>
   <si>
     <t xml:space="preserve">1.86578142642975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84897255897522</t>
+    <t xml:space="preserve">1.84897232055664</t>
   </si>
   <si>
     <t xml:space="preserve">1.8839910030365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99745047092438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04787707328796</t>
+    <t xml:space="preserve">1.99745059013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04787731170654</t>
   </si>
   <si>
     <t xml:space="preserve">2.0436749458313</t>
@@ -1253,28 +1253,28 @@
     <t xml:space="preserve">1.99604976177216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11931467056274</t>
+    <t xml:space="preserve">2.08429646492004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11931443214417</t>
   </si>
   <si>
     <t xml:space="preserve">2.15013074874878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17114210128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18725061416626</t>
+    <t xml:space="preserve">2.17114186286926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18725037574768</t>
   </si>
   <si>
     <t xml:space="preserve">2.12701892852783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14557838439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10355663299561</t>
+    <t xml:space="preserve">2.14557814598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10355639457703</t>
   </si>
   <si>
     <t xml:space="preserve">2.10320615768433</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">2.0282666683197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04927778244019</t>
+    <t xml:space="preserve">2.04927802085876</t>
   </si>
   <si>
     <t xml:space="preserve">2.1536328792572</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">2.10600781440735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03772187232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1172137260437</t>
+    <t xml:space="preserve">2.03772163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11721348762512</t>
   </si>
   <si>
     <t xml:space="preserve">2.0800940990448</t>
@@ -1313,40 +1313,40 @@
     <t xml:space="preserve">2.15258193016052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18584966659546</t>
+    <t xml:space="preserve">2.18584942817688</t>
   </si>
   <si>
     <t xml:space="preserve">2.14207673072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425415992737</t>
+    <t xml:space="preserve">2.19425392150879</t>
   </si>
   <si>
     <t xml:space="preserve">2.1900520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2030086517334</t>
+    <t xml:space="preserve">2.20300889015198</t>
   </si>
   <si>
     <t xml:space="preserve">2.17604470252991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18865132331848</t>
+    <t xml:space="preserve">2.1886510848999</t>
   </si>
   <si>
     <t xml:space="preserve">2.01005697250366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08709764480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12771940231323</t>
+    <t xml:space="preserve">2.08709788322449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12771892547607</t>
   </si>
   <si>
     <t xml:space="preserve">2.07624197006226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0664370059967</t>
+    <t xml:space="preserve">2.06643676757812</t>
   </si>
   <si>
     <t xml:space="preserve">2.11441230773926</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">2.08394622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13822460174561</t>
+    <t xml:space="preserve">2.13822436332703</t>
   </si>
   <si>
     <t xml:space="preserve">2.12036514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12071561813354</t>
+    <t xml:space="preserve">2.12071537971497</t>
   </si>
   <si>
     <t xml:space="preserve">1.96348261833191</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">1.98274302482605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98729526996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293770313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96838545799255</t>
+    <t xml:space="preserve">1.98729538917542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96838521957397</t>
   </si>
   <si>
     <t xml:space="preserve">1.94107115268707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03422021865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00620532035828</t>
+    <t xml:space="preserve">2.03421974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0062050819397</t>
   </si>
   <si>
     <t xml:space="preserve">2.01601052284241</t>
@@ -1397,25 +1397,25 @@
     <t xml:space="preserve">2.10915923118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10775852203369</t>
+    <t xml:space="preserve">2.10775876045227</t>
   </si>
   <si>
     <t xml:space="preserve">2.14382767677307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12421751022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14662909507751</t>
+    <t xml:space="preserve">2.12421727180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14662933349609</t>
   </si>
   <si>
     <t xml:space="preserve">2.11791396141052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13857507705688</t>
+    <t xml:space="preserve">2.15888547897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13857460021973</t>
   </si>
   <si>
     <t xml:space="preserve">2.14487838745117</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">2.08289575576782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14347720146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453085899353</t>
+    <t xml:space="preserve">2.14347743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453062057495</t>
   </si>
   <si>
     <t xml:space="preserve">2.07028889656067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09970450401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86087894439697</t>
+    <t xml:space="preserve">2.0997040271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86087882518768</t>
   </si>
   <si>
     <t xml:space="preserve">1.87523627281189</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">1.47077357769012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51839876174927</t>
+    <t xml:space="preserve">1.51839864253998</t>
   </si>
   <si>
     <t xml:space="preserve">1.55446767807007</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">1.68018364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61259818077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71170043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69874346256256</t>
+    <t xml:space="preserve">1.61259829998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71170020103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69874358177185</t>
   </si>
   <si>
     <t xml:space="preserve">1.7246572971344</t>
@@ -1487,43 +1487,43 @@
     <t xml:space="preserve">1.69138967990875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67808270454407</t>
+    <t xml:space="preserve">1.67808258533478</t>
   </si>
   <si>
     <t xml:space="preserve">1.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78804039955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84792172908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78068673610687</t>
+    <t xml:space="preserve">1.78804063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84792184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068661689758</t>
   </si>
   <si>
     <t xml:space="preserve">1.73481249809265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70364594459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7740330696106</t>
+    <t xml:space="preserve">1.70364582538605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77403318881989</t>
   </si>
   <si>
     <t xml:space="preserve">1.80589997768402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82586026191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173449993134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87243497371674</t>
+    <t xml:space="preserve">1.8258603811264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173438072205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274573326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87243485450745</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823260784149</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">1.81605517864227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85072326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601546287537</t>
+    <t xml:space="preserve">1.85072338581085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601558208466</t>
   </si>
   <si>
     <t xml:space="preserve">1.85807740688324</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">1.85387527942657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76807999610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75337207317352</t>
+    <t xml:space="preserve">1.76807975769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75337219238281</t>
   </si>
   <si>
     <t xml:space="preserve">1.64901745319366</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">1.66337490081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65216910839081</t>
+    <t xml:space="preserve">1.65216898918152</t>
   </si>
   <si>
     <t xml:space="preserve">1.61960172653198</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">1.57092642784119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53030478954315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46972286701202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42630016803741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42524969577789</t>
+    <t xml:space="preserve">1.53030467033386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46972298622131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42630004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42524981498718</t>
   </si>
   <si>
     <t xml:space="preserve">1.45501530170441</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">1.44380939006805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43190312385559</t>
+    <t xml:space="preserve">1.43190336227417</t>
   </si>
   <si>
     <t xml:space="preserve">1.44415962696075</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">1.43120276927948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40178728103638</t>
+    <t xml:space="preserve">1.40178716182709</t>
   </si>
   <si>
     <t xml:space="preserve">1.35815441608429</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">1.37132120132446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50719261169434</t>
+    <t xml:space="preserve">1.50719249248505</t>
   </si>
   <si>
     <t xml:space="preserve">1.49493634700775</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">1.53555774688721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55026543140411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61084735393524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61539959907532</t>
+    <t xml:space="preserve">1.55026531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61084723472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61539971828461</t>
   </si>
   <si>
     <t xml:space="preserve">1.61610007286072</t>
@@ -1646,49 +1646,49 @@
     <t xml:space="preserve">1.62415432929993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61715054512024</t>
+    <t xml:space="preserve">1.61715066432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.64446496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64866733551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48688209056854</t>
+    <t xml:space="preserve">1.64866721630096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48688197135925</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143716335297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37356233596802</t>
+    <t xml:space="preserve">1.37356245517731</t>
   </si>
   <si>
     <t xml:space="preserve">1.40283787250519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41439390182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38602888584137</t>
+    <t xml:space="preserve">1.41439402103424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38602900505066</t>
   </si>
   <si>
     <t xml:space="preserve">1.29638183116913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31108951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30520641803741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31136977672577</t>
+    <t xml:space="preserve">1.31108963489532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3052065372467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31136965751648</t>
   </si>
   <si>
     <t xml:space="preserve">1.3166925907135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30758762359619</t>
+    <t xml:space="preserve">1.30758774280548</t>
   </si>
   <si>
     <t xml:space="preserve">1.29960358142853</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">1.1690548658371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14692330360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09229457378387</t>
+    <t xml:space="preserve">1.14692318439484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09229445457458</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134445667267</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">1.0897730588913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14440178871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16345202922821</t>
+    <t xml:space="preserve">1.14440190792084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16345191001892</t>
   </si>
   <si>
     <t xml:space="preserve">1.1633118391037</t>
@@ -1736,28 +1736,28 @@
     <t xml:space="preserve">1.22410380840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25477993488312</t>
+    <t xml:space="preserve">1.25478005409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28139412403107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27046811580658</t>
+    <t xml:space="preserve">1.28139400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27046835422516</t>
   </si>
   <si>
     <t xml:space="preserve">1.26640605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23923194408417</t>
+    <t xml:space="preserve">1.23923182487488</t>
   </si>
   <si>
     <t xml:space="preserve">1.2260650396347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22256302833557</t>
+    <t xml:space="preserve">1.22256290912628</t>
   </si>
   <si>
     <t xml:space="preserve">1.26262426376343</t>
@@ -1766,31 +1766,31 @@
     <t xml:space="preserve">1.19412815570831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28517615795135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32341611385345</t>
+    <t xml:space="preserve">1.28517603874207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32341599464417</t>
   </si>
   <si>
     <t xml:space="preserve">1.38770985603333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41194260120392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47392523288727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147405147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836187362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53940951824188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54571306705475</t>
+    <t xml:space="preserve">1.41194272041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47392511367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147393226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836175441742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53940963745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54571294784546</t>
   </si>
   <si>
     <t xml:space="preserve">1.55796945095062</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">1.48478090763092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49913847446442</t>
+    <t xml:space="preserve">1.49913859367371</t>
   </si>
   <si>
     <t xml:space="preserve">1.47007322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44345927238464</t>
+    <t xml:space="preserve">1.44345939159393</t>
   </si>
   <si>
     <t xml:space="preserve">1.40458881855011</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">1.3940132856369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43155300617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39443325996399</t>
+    <t xml:space="preserve">1.43155288696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39443337917328</t>
   </si>
   <si>
     <t xml:space="preserve">1.35605323314667</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">1.32285571098328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39177191257477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37118124961853</t>
+    <t xml:space="preserve">1.39177203178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37118113040924</t>
   </si>
   <si>
     <t xml:space="preserve">1.43330383300781</t>
@@ -1847,16 +1847,16 @@
     <t xml:space="preserve">1.44170844554901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41509437561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209792137146</t>
+    <t xml:space="preserve">1.41509413719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209780216217</t>
   </si>
   <si>
     <t xml:space="preserve">1.42454922199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38224697113037</t>
+    <t xml:space="preserve">1.38224709033966</t>
   </si>
   <si>
     <t xml:space="preserve">1.34918963909149</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">1.29344034194946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33168041706085</t>
+    <t xml:space="preserve">1.33168029785156</t>
   </si>
   <si>
     <t xml:space="preserve">1.32551717758179</t>
@@ -1877,40 +1877,40 @@
     <t xml:space="preserve">1.2948409318924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25996279716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26864719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24721586704254</t>
+    <t xml:space="preserve">1.25996267795563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26864731311798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24721598625183</t>
   </si>
   <si>
     <t xml:space="preserve">1.27845251560211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26206386089325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24917709827423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24525499343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18474316596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15182590484619</t>
+    <t xml:space="preserve">1.26206398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24917697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24525511264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474304676056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1518257856369</t>
   </si>
   <si>
     <t xml:space="preserve">1.19342768192291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21892094612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2291464805603</t>
+    <t xml:space="preserve">1.21892106533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22914659976959</t>
   </si>
   <si>
     <t xml:space="preserve">1.20897603034973</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">1.29400050640106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31851351261139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31417119503021</t>
+    <t xml:space="preserve">1.3185133934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31417107582092</t>
   </si>
   <si>
     <t xml:space="preserve">1.2770516872406</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">1.36571836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3850485086441</t>
+    <t xml:space="preserve">1.38504838943481</t>
   </si>
   <si>
     <t xml:space="preserve">1.37706434726715</t>
@@ -1940,28 +1940,28 @@
     <t xml:space="preserve">1.35969519615173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32775819301605</t>
+    <t xml:space="preserve">1.32775843143463</t>
   </si>
   <si>
     <t xml:space="preserve">1.3147314786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36011552810669</t>
+    <t xml:space="preserve">1.3601154088974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40879082679749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47287440299988</t>
+    <t xml:space="preserve">1.47287452220917</t>
   </si>
   <si>
     <t xml:space="preserve">1.49318528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46412014961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43505477905273</t>
+    <t xml:space="preserve">1.46412003040314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43505465984344</t>
   </si>
   <si>
     <t xml:space="preserve">1.41544449329376</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35675346851349</t>
+    <t xml:space="preserve">1.35675358772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.34372663497925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40318787097931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37720441818237</t>
+    <t xml:space="preserve">1.4031879901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37720429897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">1.39149188995361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38112640380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3210346698761</t>
+    <t xml:space="preserve">1.38112652301788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32103478908539</t>
   </si>
   <si>
     <t xml:space="preserve">1.30296528339386</t>
@@ -2006,52 +2006,52 @@
     <t xml:space="preserve">1.32019436359406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28937804698944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28993844985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824850082397</t>
+    <t xml:space="preserve">1.28937816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28993856906891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824873924255</t>
   </si>
   <si>
     <t xml:space="preserve">1.33175051212311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.359414935112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36606848239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36641871929169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36221647262573</t>
+    <t xml:space="preserve">1.35941505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36606860160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3664186000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36221659183502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37587368488312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37727451324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37622392177582</t>
+    <t xml:space="preserve">1.37727439403534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37622380256653</t>
   </si>
   <si>
     <t xml:space="preserve">1.43575513362885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45956778526306</t>
+    <t xml:space="preserve">1.45956766605377</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828279972076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43855667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49178469181061</t>
+    <t xml:space="preserve">1.43855655193329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4917848110199</t>
   </si>
   <si>
     <t xml:space="preserve">1.48127913475037</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">1.27221918106079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24595534801483</t>
+    <t xml:space="preserve">1.24595546722412</t>
   </si>
   <si>
     <t xml:space="preserve">1.1997309923172</t>
@@ -2078,25 +2078,25 @@
     <t xml:space="preserve">1.19062626361847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19798004627228</t>
+    <t xml:space="preserve">1.19797992706299</t>
   </si>
   <si>
     <t xml:space="preserve">1.24945724010468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20918595790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19587898254395</t>
+    <t xml:space="preserve">1.20918607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19587910175323</t>
   </si>
   <si>
     <t xml:space="preserve">1.18082106113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15525782108307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17171633243561</t>
+    <t xml:space="preserve">1.15525770187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17171621322632</t>
   </si>
   <si>
     <t xml:space="preserve">1.14370167255402</t>
@@ -2114,79 +2114,79 @@
     <t xml:space="preserve">1.15350663661957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19377791881561</t>
+    <t xml:space="preserve">1.19377779960632</t>
   </si>
   <si>
     <t xml:space="preserve">1.16716396808624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14160025119781</t>
+    <t xml:space="preserve">1.1416003704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.18432295322418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19482827186584</t>
+    <t xml:space="preserve">1.19482839107513</t>
   </si>
   <si>
     <t xml:space="preserve">1.16821444034576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17101585865021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15700852870941</t>
+    <t xml:space="preserve">1.1710159778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1570086479187</t>
   </si>
   <si>
     <t xml:space="preserve">1.20323288440704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25365948677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24560511112213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23790121078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23474943637848</t>
+    <t xml:space="preserve">1.25365936756134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24560499191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23790109157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23474955558777</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451504230499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24105286598206</t>
+    <t xml:space="preserve">1.26451516151428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24105262756348</t>
   </si>
   <si>
     <t xml:space="preserve">1.23825120925903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31949388980865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36256659030914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36992061138153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33525240421295</t>
+    <t xml:space="preserve">1.31949400901794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36256670951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36992049217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33525228500366</t>
   </si>
   <si>
     <t xml:space="preserve">1.32264566421509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33350145816803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33630275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34295642375946</t>
+    <t xml:space="preserve">1.33350133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33630287647247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34295630455017</t>
   </si>
   <si>
     <t xml:space="preserve">1.31214010715485</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">1.31914377212524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22634494304657</t>
+    <t xml:space="preserve">1.22634506225586</t>
   </si>
   <si>
     <t xml:space="preserve">1.23159766197205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23720061779022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23124742507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21163725852966</t>
+    <t xml:space="preserve">1.23720073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23124754428864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21163737773895</t>
   </si>
   <si>
     <t xml:space="preserve">1.17241668701172</t>
@@ -2225,25 +2225,25 @@
     <t xml:space="preserve">1.18817484378815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18467307090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18607401847839</t>
+    <t xml:space="preserve">1.1846729516983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18607378005981</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210333824158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26731646060944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15175592899323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13529706001282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18047094345093</t>
+    <t xml:space="preserve">1.26731657981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15175580978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1352972984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18047082424164</t>
   </si>
   <si>
     <t xml:space="preserve">1.1342465877533</t>
@@ -2255,40 +2255,40 @@
     <t xml:space="preserve">1.20603430271149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17521822452545</t>
+    <t xml:space="preserve">1.17521810531616</t>
   </si>
   <si>
     <t xml:space="preserve">1.18992578983307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21583950519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21653985977173</t>
+    <t xml:space="preserve">1.21583938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21653962135315</t>
   </si>
   <si>
     <t xml:space="preserve">1.23404896259308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27467048168182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.286576628685</t>
+    <t xml:space="preserve">1.27467036247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28657674789429</t>
   </si>
   <si>
     <t xml:space="preserve">1.32579731941223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28132379055023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27186894416809</t>
+    <t xml:space="preserve">1.28132390975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27186906337738</t>
   </si>
   <si>
     <t xml:space="preserve">1.26906752586365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30548667907715</t>
+    <t xml:space="preserve">1.30548655986786</t>
   </si>
   <si>
     <t xml:space="preserve">1.32474672794342</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">1.31844353675842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35171103477478</t>
+    <t xml:space="preserve">1.35171091556549</t>
   </si>
   <si>
     <t xml:space="preserve">1.31424117088318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34050524234772</t>
+    <t xml:space="preserve">1.34050512313843</t>
   </si>
   <si>
     <t xml:space="preserve">1.36816966533661</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">1.35066044330597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29743254184723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3100391626358</t>
+    <t xml:space="preserve">1.29743242263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31003904342651</t>
   </si>
   <si>
     <t xml:space="preserve">1.33980464935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33210074901581</t>
+    <t xml:space="preserve">1.33210062980652</t>
   </si>
   <si>
     <t xml:space="preserve">1.29007863998413</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">1.28307485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30968880653381</t>
+    <t xml:space="preserve">1.3096889257431</t>
   </si>
   <si>
     <t xml:space="preserve">1.42384886741638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50929391384125</t>
+    <t xml:space="preserve">1.50929379463196</t>
   </si>
   <si>
     <t xml:space="preserve">1.50859344005585</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">1.47707688808441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46867251396179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42314851284027</t>
+    <t xml:space="preserve">1.4686723947525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42314863204956</t>
   </si>
   <si>
     <t xml:space="preserve">1.42665040493011</t>
@@ -2381,19 +2381,19 @@
     <t xml:space="preserve">1.49388563632965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44766128063202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42104744911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264295578003</t>
+    <t xml:space="preserve">1.44766139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42104732990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264307498932</t>
   </si>
   <si>
     <t xml:space="preserve">1.41754543781281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41614484786987</t>
+    <t xml:space="preserve">1.41614496707916</t>
   </si>
   <si>
     <t xml:space="preserve">1.44135808944702</t>
@@ -2402,22 +2402,22 @@
     <t xml:space="preserve">1.45536541938782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46517074108124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43085253238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4182460308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38813006877899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3741227388382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41474390029907</t>
+    <t xml:space="preserve">1.46517062187195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43085241317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41824591159821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38813018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37412285804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41474401950836</t>
   </si>
   <si>
     <t xml:space="preserve">1.40353810787201</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">1.40984153747559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45326447486877</t>
+    <t xml:space="preserve">1.45326459407806</t>
   </si>
   <si>
     <t xml:space="preserve">1.42034709453583</t>
@@ -2438,31 +2438,31 @@
     <t xml:space="preserve">1.37797474861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38637912273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46166861057281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.425950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43435454368591</t>
+    <t xml:space="preserve">1.38637924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46166884899139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42595016956329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43435442447662</t>
   </si>
   <si>
     <t xml:space="preserve">1.43365395069122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38287723064423</t>
+    <t xml:space="preserve">1.38287734985352</t>
   </si>
   <si>
     <t xml:space="preserve">1.36886990070343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39373314380646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36431753635406</t>
+    <t xml:space="preserve">1.39373302459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36431765556335</t>
   </si>
   <si>
     <t xml:space="preserve">1.29568147659302</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">1.37307214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727168560028</t>
+    <t xml:space="preserve">1.46727180480957</t>
   </si>
   <si>
     <t xml:space="preserve">1.52049970626831</t>
@@ -2483,46 +2483,46 @@
     <t xml:space="preserve">1.54641318321228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72010469436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626069068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38848030567169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3012843132019</t>
+    <t xml:space="preserve">1.72010481357574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626080989838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3884801864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128443241119</t>
   </si>
   <si>
     <t xml:space="preserve">1.1423008441925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09397554397583</t>
+    <t xml:space="preserve">1.09397542476654</t>
   </si>
   <si>
     <t xml:space="preserve">1.05755627155304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905926406383514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861102938652039</t>
+    <t xml:space="preserve">0.905926465988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861102879047394</t>
   </si>
   <si>
     <t xml:space="preserve">0.926937639713287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772156178951263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88841724395752</t>
+    <t xml:space="preserve">0.772156119346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888417065143585</t>
   </si>
   <si>
     <t xml:space="preserve">0.818030178546906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874409794807434</t>
+    <t xml:space="preserve">0.874409854412079</t>
   </si>
   <si>
     <t xml:space="preserve">0.874760091304779</t>
@@ -2537,19 +2537,19 @@
     <t xml:space="preserve">0.870207607746124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926587343215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912930130958557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925886929035187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8807133436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84919673204422</t>
+    <t xml:space="preserve">0.926587283611298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912930190563202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925886988639832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880713284015656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849196672439575</t>
   </si>
   <si>
     <t xml:space="preserve">0.840442180633545</t>
@@ -2558,22 +2558,22 @@
     <t xml:space="preserve">0.823633253574371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846045017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83098703622818</t>
+    <t xml:space="preserve">0.846044957637787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830987095832825</t>
   </si>
   <si>
     <t xml:space="preserve">0.851297736167908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829936504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85304868221283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820131361484528</t>
+    <t xml:space="preserve">0.829936444759369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853048801422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820131421089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.777408957481384</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">0.778809607028961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753246247768402</t>
+    <t xml:space="preserve">0.753246188163757</t>
   </si>
   <si>
     <t xml:space="preserve">0.751845479011536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771805942058563</t>
+    <t xml:space="preserve">0.771805882453918</t>
   </si>
   <si>
     <t xml:space="preserve">0.743791282176971</t>
@@ -2609,16 +2609,16 @@
     <t xml:space="preserve">0.779860138893127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766553163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611144542694</t>
+    <t xml:space="preserve">0.766553103923798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611084938049</t>
   </si>
   <si>
     <t xml:space="preserve">0.776008188724518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765152394771576</t>
+    <t xml:space="preserve">0.765152335166931</t>
   </si>
   <si>
     <t xml:space="preserve">0.803672790527344</t>
@@ -2627,34 +2627,34 @@
     <t xml:space="preserve">0.812077164649963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807874798774719</t>
+    <t xml:space="preserve">0.807874917984009</t>
   </si>
   <si>
     <t xml:space="preserve">0.785463213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781260907649994</t>
+    <t xml:space="preserve">0.781260848045349</t>
   </si>
   <si>
     <t xml:space="preserve">0.819080770015717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759199380874634</t>
+    <t xml:space="preserve">0.759199321269989</t>
   </si>
   <si>
     <t xml:space="preserve">0.756047666072845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730484127998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736087203025818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743441045284271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779159784317017</t>
+    <t xml:space="preserve">0.730484187602997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736087143421173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743440985679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779159843921661</t>
   </si>
   <si>
     <t xml:space="preserve">0.815228760242462</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">0.805773913860321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858301401138306</t>
+    <t xml:space="preserve">0.85830146074295</t>
   </si>
   <si>
     <t xml:space="preserve">0.872308909893036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892969608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931839942932129</t>
+    <t xml:space="preserve">0.89296966791153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931840062141418</t>
   </si>
   <si>
     <t xml:space="preserve">0.994873344898224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00853049755096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979115009307861</t>
+    <t xml:space="preserve">1.00853037834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979115068912506</t>
   </si>
   <si>
     <t xml:space="preserve">0.966858565807343</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">0.967908978462219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964407205581665</t>
+    <t xml:space="preserve">0.96440726518631</t>
   </si>
   <si>
     <t xml:space="preserve">0.946898102760315</t>
@@ -2708,16 +2708,16 @@
     <t xml:space="preserve">0.936392486095428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938493609428406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965107560157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913980782032013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934641480445862</t>
+    <t xml:space="preserve">0.938493669033051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965107500553131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913980603218079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934641540050507</t>
   </si>
   <si>
     <t xml:space="preserve">0.899623215198517</t>
@@ -2732,55 +2732,55 @@
     <t xml:space="preserve">0.909078121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954602062702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943746268749237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983317196369171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973161816596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951450407505035</t>
+    <t xml:space="preserve">0.954602122306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943746387958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983317136764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97316187620163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95145046710968</t>
   </si>
   <si>
     <t xml:space="preserve">0.916432082653046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933941304683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948298692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957403600215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973512053489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980865895748138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.033043384552</t>
+    <t xml:space="preserve">0.933941245079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948298752307892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957403540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97351211309433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980866014957428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03304326534271</t>
   </si>
   <si>
     <t xml:space="preserve">1.03759574890137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00012588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998725235462189</t>
+    <t xml:space="preserve">1.00012600421906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998725295066833</t>
   </si>
   <si>
     <t xml:space="preserve">0.960905373096466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967208743095398</t>
+    <t xml:space="preserve">0.967208802700043</t>
   </si>
   <si>
     <t xml:space="preserve">0.944096684455872</t>
@@ -2792,28 +2792,28 @@
     <t xml:space="preserve">0.890168130397797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874059736728668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913280427455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927637934684753</t>
+    <t xml:space="preserve">0.874059796333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913280308246613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927637815475464</t>
   </si>
   <si>
     <t xml:space="preserve">0.907677412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890868484973907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915381491184235</t>
+    <t xml:space="preserve">0.890868604183197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915381550788879</t>
   </si>
   <si>
     <t xml:space="preserve">0.978764891624451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971060752868652</t>
+    <t xml:space="preserve">0.971060693264008</t>
   </si>
   <si>
     <t xml:space="preserve">1.00572896003723</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">0.997324585914612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98156613111496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00923085212708</t>
+    <t xml:space="preserve">0.981566250324249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00923073291779</t>
   </si>
   <si>
     <t xml:space="preserve">0.986818969249725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987519323825836</t>
+    <t xml:space="preserve">0.987519443035126</t>
   </si>
   <si>
     <t xml:space="preserve">1.00712978839874</t>
@@ -2843,73 +2843,73 @@
     <t xml:space="preserve">0.999775767326355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00467836856842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988920211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985768556594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970360398292542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958103954792023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994523167610168</t>
+    <t xml:space="preserve">1.00467848777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988920152187347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985768496990204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970360338687897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958103895187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994523048400879</t>
   </si>
   <si>
     <t xml:space="preserve">0.978414475917816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986118674278259</t>
+    <t xml:space="preserve">0.986118733882904</t>
   </si>
   <si>
     <t xml:space="preserve">1.03724551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02148735523224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01903593540192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01203238964081</t>
+    <t xml:space="preserve">1.02148723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01903605461121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01203227043152</t>
   </si>
   <si>
     <t xml:space="preserve">0.995573580265045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973862171173096</t>
+    <t xml:space="preserve">0.973862290382385</t>
   </si>
   <si>
     <t xml:space="preserve">0.916782200336456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922735393047333</t>
+    <t xml:space="preserve">0.922735273838043</t>
   </si>
   <si>
     <t xml:space="preserve">0.888067126274109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939544260501862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961605787277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972811758518219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0540543794632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11113440990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09957849979401</t>
+    <t xml:space="preserve">0.939544200897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961605846881866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972811698913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05405449867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09957838058472</t>
   </si>
   <si>
     <t xml:space="preserve">1.16121077537537</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">1.15910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12339091300964</t>
+    <t xml:space="preserve">1.12339079380035</t>
   </si>
   <si>
     <t xml:space="preserve">1.12829339504242</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">1.14545249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15280628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17591845989227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15560781955719</t>
+    <t xml:space="preserve">1.15280640125275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17591857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15560793876648</t>
   </si>
   <si>
     <t xml:space="preserve">1.13214552402496</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">1.08522081375122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965733528137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08627128601074</t>
+    <t xml:space="preserve">1.05965721607208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08627140522003</t>
   </si>
   <si>
     <t xml:space="preserve">1.12899374961853</t>
@@ -2972,34 +2972,34 @@
     <t xml:space="preserve">1.15000486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15210604667664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15490758419037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15455734729767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25120794773102</t>
+    <t xml:space="preserve">1.15210592746735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15490746498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15455722808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066315174103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25120806694031</t>
   </si>
   <si>
     <t xml:space="preserve">1.25611054897308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27502059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3079377412796</t>
+    <t xml:space="preserve">1.27502071857452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
     <t xml:space="preserve">1.32684791088104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35801434516907</t>
+    <t xml:space="preserve">1.35801422595978</t>
   </si>
   <si>
     <t xml:space="preserve">1.32334613800049</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">1.31879365444183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29603171348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31389105319977</t>
+    <t xml:space="preserve">1.29603159427643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31389117240906</t>
   </si>
   <si>
     <t xml:space="preserve">1.30723762512207</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">1.29498112201691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28482580184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2802734375</t>
+    <t xml:space="preserve">1.28482568264008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28027331829071</t>
   </si>
   <si>
     <t xml:space="preserve">1.26941764354706</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">1.2431538105011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25435972213745</t>
+    <t xml:space="preserve">1.25435960292816</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26136338710785</t>
+    <t xml:space="preserve">1.26136326789856</t>
   </si>
   <si>
     <t xml:space="preserve">1.26661622524261</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">1.26626598834991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25856196880341</t>
+    <t xml:space="preserve">1.2585620880127</t>
   </si>
   <si>
     <t xml:space="preserve">1.25821173191071</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">1.32964932918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36957037448883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3450573682785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34925973415375</t>
+    <t xml:space="preserve">1.36957049369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34505748748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34925961494446</t>
   </si>
   <si>
     <t xml:space="preserve">1.33455193042755</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">1.31529188156128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31809329986572</t>
+    <t xml:space="preserve">1.31809318065643</t>
   </si>
   <si>
     <t xml:space="preserve">1.31073939800262</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">1.31774306297302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28062355518341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24735617637634</t>
+    <t xml:space="preserve">1.2806236743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24735605716705</t>
   </si>
   <si>
     <t xml:space="preserve">1.26696646213531</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">1.25015759468079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29112923145294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27432024478912</t>
+    <t xml:space="preserve">1.29112911224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27432012557983</t>
   </si>
   <si>
     <t xml:space="preserve">1.29953348636627</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">1.42174780368805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52260076999664</t>
+    <t xml:space="preserve">1.52260088920593</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190053462982</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">1.48898315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50088942050934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51629734039307</t>
+    <t xml:space="preserve">1.50088953971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51629745960236</t>
   </si>
   <si>
     <t xml:space="preserve">1.50789332389832</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">1.54851448535919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54361188411713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60594475269318</t>
+    <t xml:space="preserve">1.54361176490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60594487190247</t>
   </si>
   <si>
     <t xml:space="preserve">1.62695550918579</t>
@@ -3161,61 +3161,61 @@
     <t xml:space="preserve">1.59053635597229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5919371843338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909369945526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70119488239288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72360646724701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71029937267303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70469665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71099996566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881958961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70539689064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68998897075653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65356981754303</t>
+    <t xml:space="preserve">1.59193730354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909358024597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7011946439743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7236065864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71029925346375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70469653606415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71100008487701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881970882416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70539700984955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68998885154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65356969833374</t>
   </si>
   <si>
     <t xml:space="preserve">1.63536012172699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64936769008636</t>
+    <t xml:space="preserve">1.64936757087708</t>
   </si>
   <si>
     <t xml:space="preserve">1.63466000556946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62835645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6654759645462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71505236625671</t>
+    <t xml:space="preserve">1.62835669517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66547608375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.715052485466</t>
   </si>
   <si>
     <t xml:space="preserve">1.61877369880676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59937417507172</t>
+    <t xml:space="preserve">1.59937429428101</t>
   </si>
   <si>
     <t xml:space="preserve">1.61302554607391</t>
@@ -3224,22 +3224,22 @@
     <t xml:space="preserve">1.62308478355408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65613567829132</t>
+    <t xml:space="preserve">1.65613579750061</t>
   </si>
   <si>
     <t xml:space="preserve">1.67337954044342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71936309337616</t>
+    <t xml:space="preserve">1.71936321258545</t>
   </si>
   <si>
     <t xml:space="preserve">1.71289670467377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70283782482147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73445188999176</t>
+    <t xml:space="preserve">1.70283770561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73445177078247</t>
   </si>
   <si>
     <t xml:space="preserve">1.71145987510681</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">1.74522924423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893961429596</t>
+    <t xml:space="preserve">1.76893973350525</t>
   </si>
   <si>
     <t xml:space="preserve">1.76822102069855</t>
@@ -3263,31 +3263,31 @@
     <t xml:space="preserve">1.85587751865387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8644996881485</t>
+    <t xml:space="preserve">1.86449980735779</t>
   </si>
   <si>
     <t xml:space="preserve">1.92126083374023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95934116840363</t>
+    <t xml:space="preserve">1.95934128761292</t>
   </si>
   <si>
     <t xml:space="preserve">1.9729927778244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98377025127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94066047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96508920192719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9974217414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02400588989258</t>
+    <t xml:space="preserve">1.98377013206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94066035747528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650890827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99742186069489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02400612831116</t>
   </si>
   <si>
     <t xml:space="preserve">2.03334641456604</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">2.15189814567566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423080444336</t>
+    <t xml:space="preserve">2.18423104286194</t>
   </si>
   <si>
     <t xml:space="preserve">2.17201662063599</t>
@@ -3329,13 +3329,13 @@
     <t xml:space="preserve">2.17632746696472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16052055358887</t>
+    <t xml:space="preserve">2.16052031517029</t>
   </si>
   <si>
     <t xml:space="preserve">2.12818789482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08938908576965</t>
+    <t xml:space="preserve">2.08938932418823</t>
   </si>
   <si>
     <t xml:space="preserve">2.0807671546936</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">2.05346465110779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08292293548584</t>
+    <t xml:space="preserve">2.08292269706726</t>
   </si>
   <si>
     <t xml:space="preserve">2.04771637916565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04196882247925</t>
+    <t xml:space="preserve">2.04196858406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.01897644996643</t>
@@ -3359,43 +3359,43 @@
     <t xml:space="preserve">2.04053139686584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98305153846741</t>
+    <t xml:space="preserve">1.9830516576767</t>
   </si>
   <si>
     <t xml:space="preserve">1.96652626991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94928228855133</t>
+    <t xml:space="preserve">1.94928240776062</t>
   </si>
   <si>
     <t xml:space="preserve">1.95215630531311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90114295482635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8328857421875</t>
+    <t xml:space="preserve">1.90114283561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83288586139679</t>
   </si>
   <si>
     <t xml:space="preserve">1.93922317028046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93634915351868</t>
+    <t xml:space="preserve">1.93634927272797</t>
   </si>
   <si>
     <t xml:space="preserve">1.91766822338104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88821005821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749158382416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84653699398041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78762030601501</t>
+    <t xml:space="preserve">1.88821017742157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749170303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8465371131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78762018680573</t>
   </si>
   <si>
     <t xml:space="preserve">1.82641923427582</t>
@@ -3407,31 +3407,31 @@
     <t xml:space="preserve">1.8580334186554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90258014202118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87743246555328</t>
+    <t xml:space="preserve">1.90258002281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87743234634399</t>
   </si>
   <si>
     <t xml:space="preserve">1.89108407497406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82067120075226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81348645687103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82857477664948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96724486351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97371137142181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95718574523926</t>
+    <t xml:space="preserve">1.82067131996155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81348657608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82857489585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96724474430084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9737114906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95718562602997</t>
   </si>
   <si>
     <t xml:space="preserve">2.03190970420837</t>
@@ -3443,16 +3443,16 @@
     <t xml:space="preserve">2.00388789176941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97155570983887</t>
+    <t xml:space="preserve">1.97155582904816</t>
   </si>
   <si>
     <t xml:space="preserve">1.93347537517548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90904664993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94209742546082</t>
+    <t xml:space="preserve">1.90904653072357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9420975446701</t>
   </si>
   <si>
     <t xml:space="preserve">1.97802233695984</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">2.01107311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99957716464996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01753973960876</t>
+    <t xml:space="preserve">1.99957728385925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01753950119019</t>
   </si>
   <si>
     <t xml:space="preserve">2.03262805938721</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">2.03119087219238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99167370796204</t>
+    <t xml:space="preserve">1.99167358875275</t>
   </si>
   <si>
     <t xml:space="preserve">2.01322841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945940494537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95000100135803</t>
+    <t xml:space="preserve">1.97945928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95000088214874</t>
   </si>
   <si>
     <t xml:space="preserve">1.93778645992279</t>
@@ -3491,25 +3491,25 @@
     <t xml:space="preserve">1.96868169307709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92269814014435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94712674617767</t>
+    <t xml:space="preserve">1.92269825935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94712686538696</t>
   </si>
   <si>
     <t xml:space="preserve">1.92916452884674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83073055744171</t>
+    <t xml:space="preserve">1.83073043823242</t>
   </si>
   <si>
     <t xml:space="preserve">1.84078931808472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9205424785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9758665561676</t>
+    <t xml:space="preserve">1.92054259777069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97586667537689</t>
   </si>
   <si>
     <t xml:space="preserve">1.9234162569046</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">1.94353449344635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94425284862518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91838681697845</t>
+    <t xml:space="preserve">1.94425296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91838693618774</t>
   </si>
   <si>
     <t xml:space="preserve">2.02616143226624</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12315821647644</t>
+    <t xml:space="preserve">2.12315845489502</t>
   </si>
   <si>
     <t xml:space="preserve">2.1303436756134</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">2.1475875377655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1095073223114</t>
+    <t xml:space="preserve">2.10950708389282</t>
   </si>
   <si>
     <t xml:space="preserve">2.08148574829102</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">1.97083735466003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00963568687439</t>
+    <t xml:space="preserve">2.00963592529297</t>
   </si>
   <si>
     <t xml:space="preserve">2.08364129066467</t>
@@ -3584,16 +3584,16 @@
     <t xml:space="preserve">2.03765726089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00316977500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9859254360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9514377117157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042424201965</t>
+    <t xml:space="preserve">2.00316953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98592555522919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143783092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042436122894</t>
   </si>
   <si>
     <t xml:space="preserve">1.88318061828613</t>
@@ -3602,13 +3602,13 @@
     <t xml:space="preserve">1.8537220954895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74594759941101</t>
+    <t xml:space="preserve">1.7459477186203</t>
   </si>
   <si>
     <t xml:space="preserve">1.77540600299835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77181363105774</t>
+    <t xml:space="preserve">1.77181375026703</t>
   </si>
   <si>
     <t xml:space="preserve">1.80845677852631</t>
@@ -3620,28 +3620,28 @@
     <t xml:space="preserve">1.8853360414505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92557191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8896472454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88677299022675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8673734664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395785331726</t>
+    <t xml:space="preserve">1.92557215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88964712619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88677322864532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86737334728241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.89036560058594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8544408082962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84797441959381</t>
+    <t xml:space="preserve">1.85444092750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84797430038452</t>
   </si>
   <si>
     <t xml:space="preserve">1.79767954349518</t>
@@ -3656,13 +3656,13 @@
     <t xml:space="preserve">1.84725594520569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85515940189362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88605463504791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683210849762</t>
+    <t xml:space="preserve">1.85515928268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8860547542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683198928833</t>
   </si>
   <si>
     <t xml:space="preserve">1.97874081134796</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">2.0010142326355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02544283866882</t>
+    <t xml:space="preserve">2.0254430770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280493736267</t>
@@ -3695,16 +3695,16 @@
     <t xml:space="preserve">2.00460648536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01251006126404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99526607990265</t>
+    <t xml:space="preserve">2.01251029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99526619911194</t>
   </si>
   <si>
     <t xml:space="preserve">1.89970588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87958812713623</t>
+    <t xml:space="preserve">1.87958824634552</t>
   </si>
   <si>
     <t xml:space="preserve">1.93131995201111</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">2.02041339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06855297088623</t>
+    <t xml:space="preserve">2.06855273246765</t>
   </si>
   <si>
     <t xml:space="preserve">2.10447764396667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07645630836487</t>
+    <t xml:space="preserve">2.07645654678345</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657430648804</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">2.15117979049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32505631446838</t>
+    <t xml:space="preserve">2.3250560760498</t>
   </si>
   <si>
     <t xml:space="preserve">2.32361936569214</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">2.60814428329468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928635597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.527672290802</t>
+    <t xml:space="preserve">2.55928611755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52767252922058</t>
   </si>
   <si>
     <t xml:space="preserve">2.57509350776672</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">2.21368932723999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496024131775</t>
+    <t xml:space="preserve">2.06496047973633</t>
   </si>
   <si>
     <t xml:space="preserve">1.91120195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66475760936737</t>
+    <t xml:space="preserve">1.66475749015808</t>
   </si>
   <si>
     <t xml:space="preserve">1.74954009056091</t>
@@ -3791,10 +3791,10 @@
     <t xml:space="preserve">1.79480540752411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83575987815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90186178684235</t>
+    <t xml:space="preserve">1.83575975894928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90186154842377</t>
   </si>
   <si>
     <t xml:space="preserve">2.0678346157074</t>
@@ -3809,19 +3809,19 @@
     <t xml:space="preserve">1.98879945278168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95574879646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359337329865</t>
+    <t xml:space="preserve">1.95574867725372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359325408936</t>
   </si>
   <si>
     <t xml:space="preserve">2.06208634376526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93275701999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99095523357391</t>
+    <t xml:space="preserve">1.93275713920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99095511436462</t>
   </si>
   <si>
     <t xml:space="preserve">1.98664402961731</t>
@@ -6264,6 +6264,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.2049999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0100002288818</t>
   </si>
 </sst>
 </file>
@@ -71342,7 +71345,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6501388889</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>5898601</v>
@@ -71363,6 +71366,32 @@
         <v>2083</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6494675926</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>8938152</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>12.1549997329712</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>11.8299999237061</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>11.8950004577637</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>12.0100002288818</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>2084</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="2086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="2087">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20738077163696</t>
+    <t xml:space="preserve">6.2073802947998</t>
   </si>
   <si>
     <t xml:space="preserve">BAMI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25302410125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98424053192139</t>
+    <t xml:space="preserve">6.25302457809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98424005508423</t>
   </si>
   <si>
     <t xml:space="preserve">5.89802646636963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65459871292114</t>
+    <t xml:space="preserve">5.65459966659546</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967178344727</t>
+    <t xml:space="preserve">5.65967130661011</t>
   </si>
   <si>
     <t xml:space="preserve">5.89295434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27424478530884</t>
+    <t xml:space="preserve">5.27424573898315</t>
   </si>
   <si>
     <t xml:space="preserve">4.9420690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40450143814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85839080810547</t>
+    <t xml:space="preserve">4.40450191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85839176177979</t>
   </si>
   <si>
     <t xml:space="preserve">4.61496448516846</t>
@@ -86,46 +86,46 @@
     <t xml:space="preserve">4.55410718917847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19911050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9556839466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32082366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57946395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50339365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0520396232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11289691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961292266846</t>
+    <t xml:space="preserve">4.19911003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95568346977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32082414627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57946443557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50339317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05204010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11289739608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961268424988</t>
   </si>
   <si>
     <t xml:space="preserve">3.52715110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22286772727966</t>
+    <t xml:space="preserve">3.2228672504425</t>
   </si>
   <si>
     <t xml:space="preserve">3.58040118217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26851105690002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64379286766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004133224487</t>
+    <t xml:space="preserve">3.26851081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6437931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004109382629</t>
   </si>
   <si>
     <t xml:space="preserve">4.04443264007568</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">3.77818584442139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08246850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71986436843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64632892608643</t>
+    <t xml:space="preserve">4.08246898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71986413002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.646329164505</t>
   </si>
   <si>
     <t xml:space="preserve">3.74775624275208</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">3.92018342018127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04950475692749</t>
+    <t xml:space="preserve">4.22700262069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04950428009033</t>
   </si>
   <si>
     <t xml:space="preserve">3.88468432426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86693429946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7604353427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69957828521729</t>
+    <t xml:space="preserve">3.86693406105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76043462753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69957804679871</t>
   </si>
   <si>
     <t xml:space="preserve">4.03682613372803</t>
@@ -182,34 +182,34 @@
     <t xml:space="preserve">3.9480767250061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38768792152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47136545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197130203247</t>
+    <t xml:space="preserve">3.38768839836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47136616706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67675733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197154045105</t>
   </si>
   <si>
     <t xml:space="preserve">3.5144727230072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38261699676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27611756324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06565427780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365622520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812177658081</t>
+    <t xml:space="preserve">3.38261675834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27611780166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06565451622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365646362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812201499939</t>
   </si>
   <si>
     <t xml:space="preserve">2.49005150794983</t>
@@ -218,28 +218,28 @@
     <t xml:space="preserve">2.40586733818054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2243115901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46672368049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72080016136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70051503181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91097712516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02508330345154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16454672813416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22690272331238</t>
+    <t xml:space="preserve">2.22431135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46672320365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72079992294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.700514793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91097736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02508354187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16454648971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22690296173096</t>
   </si>
   <si>
     <t xml:space="preserve">3.1385657787323</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.14116334915161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20092105865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2450897693634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11778020858765</t>
+    <t xml:space="preserve">3.20092058181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11778044700623</t>
   </si>
   <si>
     <t xml:space="preserve">3.23469686508179</t>
@@ -263,40 +263,40 @@
     <t xml:space="preserve">3.19052886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32823038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20351910591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96968603134155</t>
+    <t xml:space="preserve">3.32823014259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20351958274841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96968626976013</t>
   </si>
   <si>
     <t xml:space="preserve">2.75663733482361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86835813522339</t>
+    <t xml:space="preserve">2.86835789680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84497475624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59607172012329</t>
+    <t xml:space="preserve">2.84497427940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59607148170471</t>
   </si>
   <si>
     <t xml:space="preserve">2.51500964164734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28637218475342</t>
+    <t xml:space="preserve">2.286372423172</t>
   </si>
   <si>
     <t xml:space="preserve">2.32378602027893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32274651527405</t>
+    <t xml:space="preserve">2.32274627685547</t>
   </si>
   <si>
     <t xml:space="preserve">2.39237642288208</t>
@@ -305,115 +305,115 @@
     <t xml:space="preserve">2.23544836044312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24584126472473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22089910507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24480199813843</t>
+    <t xml:space="preserve">2.24584102630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22089886665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24480175971985</t>
   </si>
   <si>
     <t xml:space="preserve">2.24999785423279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27494025230408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47343921661377</t>
+    <t xml:space="preserve">2.2749400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47343897819519</t>
   </si>
   <si>
     <t xml:space="preserve">2.47032117843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48902797698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49422383308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31131434440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16581773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16685700416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05461692810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15853524208069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29020476341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22156834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433311462402</t>
+    <t xml:space="preserve">2.48902821540833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49422407150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31131458282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16581797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16685724258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05461716651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15853548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2902045249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22156858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433287620544</t>
   </si>
   <si>
     <t xml:space="preserve">2.04227423667908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83636605739594</t>
+    <t xml:space="preserve">1.83636593818665</t>
   </si>
   <si>
     <t xml:space="preserve">1.71590256690979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83776664733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07449078559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01846146583557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02546548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99324822425842</t>
+    <t xml:space="preserve">1.83776676654816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07449102401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01846170425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02546525001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.993248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.12211608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62765598297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5268030166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55481767654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50439131259918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50158965587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540218830109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45676612854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40073680877686</t>
+    <t xml:space="preserve">1.6276558637619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52680325508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55481791496277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50439119338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50158977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540230751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45676624774933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40073668956757</t>
   </si>
   <si>
     <t xml:space="preserve">1.31459152698517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28167402744293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51699793338776</t>
+    <t xml:space="preserve">1.28167414665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
     <t xml:space="preserve">1.57022595405579</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">1.666876912117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5562185049057</t>
+    <t xml:space="preserve">1.55621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">1.64166367053986</t>
@@ -431,22 +431,22 @@
     <t xml:space="preserve">1.66267454624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68788778781891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67528116703033</t>
+    <t xml:space="preserve">1.68788766860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67528104782104</t>
   </si>
   <si>
     <t xml:space="preserve">1.66407513618469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7299097776413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70329594612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71730315685272</t>
+    <t xml:space="preserve">1.72990989685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70329582691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71730327606201</t>
   </si>
   <si>
     <t xml:space="preserve">1.7593252658844</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">1.70749819278717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76352739334106</t>
+    <t xml:space="preserve">1.76352751255035</t>
   </si>
   <si>
     <t xml:space="preserve">1.5057920217514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49738776683807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55201637744904</t>
+    <t xml:space="preserve">1.49738764762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55201649665833</t>
   </si>
   <si>
     <t xml:space="preserve">1.63045752048492</t>
@@ -473,103 +473,103 @@
     <t xml:space="preserve">1.59964120388031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59263777732849</t>
+    <t xml:space="preserve">1.5926376581192</t>
   </si>
   <si>
     <t xml:space="preserve">1.58143174648285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56882512569427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53100538253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52820360660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45396482944489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48758256435394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58003115653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53520727157593</t>
+    <t xml:space="preserve">1.56882524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53100526332855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52820372581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45396459102631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48758244514465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58003127574921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53520739078522</t>
   </si>
   <si>
     <t xml:space="preserve">1.51559722423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56742465496063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56182146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60384345054626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6808842420578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63886177539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65707182884216</t>
+    <t xml:space="preserve">1.56742453575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56182169914246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60384356975555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68088436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63886189460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65707147121429</t>
   </si>
   <si>
     <t xml:space="preserve">1.65847218036652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6430641412735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59403848648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60944652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57582890987396</t>
+    <t xml:space="preserve">1.64306426048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59403860569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60944640636444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57582879066467</t>
   </si>
   <si>
     <t xml:space="preserve">1.50018906593323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46657156944275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40003633499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45116317272186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47357499599457</t>
+    <t xml:space="preserve">1.46657133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40003621578217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45116341114044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47357511520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.4399573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40633964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37832486629486</t>
+    <t xml:space="preserve">1.40633952617645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37832498550415</t>
   </si>
   <si>
     <t xml:space="preserve">1.3965345621109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40774035453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46797204017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48057889938354</t>
+    <t xml:space="preserve">1.40774047374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4679719209671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48057878017426</t>
   </si>
   <si>
     <t xml:space="preserve">1.50299048423767</t>
@@ -578,67 +578,67 @@
     <t xml:space="preserve">1.55061566829681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65286946296692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78593933582306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79994666576385</t>
+    <t xml:space="preserve">1.65286934375763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78593921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79994678497314</t>
   </si>
   <si>
     <t xml:space="preserve">1.84617102146149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85317480564117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196889400482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82235848903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737693309784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86297976970673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041015625</t>
+    <t xml:space="preserve">1.85317468643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82235836982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737681388855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86297988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041027545929</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379608631134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80835103988647</t>
+    <t xml:space="preserve">1.80835127830505</t>
   </si>
   <si>
     <t xml:space="preserve">1.67107892036438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61224818229675</t>
+    <t xml:space="preserve">1.61224794387817</t>
   </si>
   <si>
     <t xml:space="preserve">1.50999414920807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59543907642365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60664498806</t>
+    <t xml:space="preserve">1.59543919563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60664510726929</t>
   </si>
   <si>
     <t xml:space="preserve">1.51279580593109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42735087871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35451233386993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30408585071564</t>
+    <t xml:space="preserve">1.42735075950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35451245307922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30408596992493</t>
   </si>
   <si>
     <t xml:space="preserve">1.31178998947144</t>
@@ -647,22 +647,22 @@
     <t xml:space="preserve">1.32649767398834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29988372325897</t>
+    <t xml:space="preserve">1.29988360404968</t>
   </si>
   <si>
     <t xml:space="preserve">1.31739294528961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25085783004761</t>
+    <t xml:space="preserve">1.25085806846619</t>
   </si>
   <si>
     <t xml:space="preserve">1.30268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35871458053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39233243465424</t>
+    <t xml:space="preserve">1.35871481895447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39233231544495</t>
   </si>
   <si>
     <t xml:space="preserve">1.28867781162262</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">1.49458622932434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64026284217834</t>
+    <t xml:space="preserve">1.64026272296906</t>
   </si>
   <si>
     <t xml:space="preserve">1.56462287902832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53380680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.679483294487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69769310951233</t>
+    <t xml:space="preserve">1.533806681633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67948341369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69769299030304</t>
   </si>
   <si>
     <t xml:space="preserve">1.65146863460541</t>
@@ -698,43 +698,43 @@
     <t xml:space="preserve">1.77893567085266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71310102939606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60524427890778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092113018036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8769873380661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90500211715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643959522247</t>
+    <t xml:space="preserve">1.71310114860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60524451732635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092101097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87698698043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90500199794769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643971443176</t>
   </si>
   <si>
     <t xml:space="preserve">2.0310685634613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9512265920639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94982552528381</t>
+    <t xml:space="preserve">1.95122635364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94982540607452</t>
   </si>
   <si>
     <t xml:space="preserve">1.90640258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94702422618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89799845218658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142138957977</t>
+    <t xml:space="preserve">1.94702410697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89799821376801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9414210319519</t>
   </si>
   <si>
     <t xml:space="preserve">1.93581819534302</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.01706099510193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97363781929016</t>
+    <t xml:space="preserve">1.97363817691803</t>
   </si>
   <si>
     <t xml:space="preserve">2.02266383171082</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">1.86017835140228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89099478721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78033661842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6738805770874</t>
+    <t xml:space="preserve">1.8909946680069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78033649921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67388045787811</t>
   </si>
   <si>
     <t xml:space="preserve">1.74251651763916</t>
@@ -776,106 +776,106 @@
     <t xml:space="preserve">1.7383143901825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64586579799652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75512313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84056830406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77753496170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7817370891571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68368566036224</t>
+    <t xml:space="preserve">1.64586555957794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75512325763702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84056806564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77753508090973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78173720836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68368554115295</t>
   </si>
   <si>
     <t xml:space="preserve">1.62205302715302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51419651508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006792545319</t>
+    <t xml:space="preserve">1.51419639587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6500678062439</t>
   </si>
   <si>
     <t xml:space="preserve">1.71870386600494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71450173854828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68228483200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69349086284637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69629228115082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80975186824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81535470485687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072609424591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80695044994354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8685827255249</t>
+    <t xml:space="preserve">1.71450161933899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68228471279144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6934906244278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69629216194153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80975222587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81535482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80695033073425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86858296394348</t>
   </si>
   <si>
     <t xml:space="preserve">1.85597622394562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91620779037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90780341625214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91480684280396</t>
+    <t xml:space="preserve">1.91620790958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90780353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91480720043182</t>
   </si>
   <si>
     <t xml:space="preserve">1.88539159297943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88819324970245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94562339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90360128879547</t>
+    <t xml:space="preserve">1.88819313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94562351703644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90360105037689</t>
   </si>
   <si>
     <t xml:space="preserve">1.89939892292023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87978851795197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86718189716339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76212668418884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542860031128</t>
+    <t xml:space="preserve">1.87978875637054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86718225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76212680339813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95542848110199</t>
   </si>
   <si>
     <t xml:space="preserve">1.86157917976379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86998355388641</t>
+    <t xml:space="preserve">1.86998343467712</t>
   </si>
   <si>
     <t xml:space="preserve">2.00445437431335</t>
@@ -884,16 +884,16 @@
     <t xml:space="preserve">2.04647636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91900908946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87838792800903</t>
+    <t xml:space="preserve">1.91900944709778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87838804721832</t>
   </si>
   <si>
     <t xml:space="preserve">1.98204231262207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96383261680603</t>
+    <t xml:space="preserve">1.96383285522461</t>
   </si>
   <si>
     <t xml:space="preserve">1.88259017467499</t>
@@ -902,55 +902,55 @@
     <t xml:space="preserve">1.93021535873413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97783994674683</t>
+    <t xml:space="preserve">1.97784042358398</t>
   </si>
   <si>
     <t xml:space="preserve">2.0941014289856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17814564704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1137113571167</t>
+    <t xml:space="preserve">2.17814540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11371159553528</t>
   </si>
   <si>
     <t xml:space="preserve">2.12491774559021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99464929103851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00305342674255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90220069885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99885153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95262706279755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95402789115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9344174861908</t>
+    <t xml:space="preserve">1.99464917182922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00305366516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90220046043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99885129928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95262694358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95402765274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93441736698151</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920412540436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91060471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88679242134094</t>
+    <t xml:space="preserve">1.91060507297516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88679230213165</t>
   </si>
   <si>
     <t xml:space="preserve">1.95823001861572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94422245025635</t>
+    <t xml:space="preserve">1.94422256946564</t>
   </si>
   <si>
     <t xml:space="preserve">1.99184787273407</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">2.05207943916321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10950922966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14592885971069</t>
+    <t xml:space="preserve">2.10950946807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14592862129211</t>
   </si>
   <si>
     <t xml:space="preserve">2.0955023765564</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">2.14452791213989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18795084953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20616030693054</t>
+    <t xml:space="preserve">2.18795108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20616054534912</t>
   </si>
   <si>
     <t xml:space="preserve">2.20896172523499</t>
@@ -989,61 +989,61 @@
     <t xml:space="preserve">2.19915699958801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19635510444641</t>
+    <t xml:space="preserve">2.19635534286499</t>
   </si>
   <si>
     <t xml:space="preserve">2.14172673225403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20335912704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19215321540833</t>
+    <t xml:space="preserve">2.2033588886261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19215297698975</t>
   </si>
   <si>
     <t xml:space="preserve">2.15573382377625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16413807868958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16273736953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20756101608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997283935547</t>
+    <t xml:space="preserve">2.16413831710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16273760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20756077766418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997260093689</t>
   </si>
   <si>
     <t xml:space="preserve">2.28320074081421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34063124656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35884046554565</t>
+    <t xml:space="preserve">2.34063100814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35884070396423</t>
   </si>
   <si>
     <t xml:space="preserve">2.33082604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30561280250549</t>
+    <t xml:space="preserve">2.30561256408691</t>
   </si>
   <si>
     <t xml:space="preserve">2.26499128341675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29720830917358</t>
+    <t xml:space="preserve">2.29720854759216</t>
   </si>
   <si>
     <t xml:space="preserve">2.30981516838074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27339553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32242131233215</t>
+    <t xml:space="preserve">2.27339577674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32242155075073</t>
   </si>
   <si>
     <t xml:space="preserve">2.2271716594696</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">2.22016763687134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23277449607849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2621898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21036243438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15993618965149</t>
+    <t xml:space="preserve">2.23277425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26219010353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21036267280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15993595123291</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713453292847</t>
@@ -1073,28 +1073,28 @@
     <t xml:space="preserve">2.10110521316528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1305205821991</t>
+    <t xml:space="preserve">2.13052082061768</t>
   </si>
   <si>
     <t xml:space="preserve">2.18935132026672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2551863193512</t>
+    <t xml:space="preserve">2.25518608093262</t>
   </si>
   <si>
     <t xml:space="preserve">2.29300594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30421185493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30141067504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3112154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33782958984375</t>
+    <t xml:space="preserve">2.30421209335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30141043663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31121563911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33782982826233</t>
   </si>
   <si>
     <t xml:space="preserve">2.28180003166199</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.33642888069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43448042869568</t>
+    <t xml:space="preserve">2.43448066711426</t>
   </si>
   <si>
     <t xml:space="preserve">2.45409083366394</t>
@@ -1112,67 +1112,67 @@
     <t xml:space="preserve">2.4568920135498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43307948112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43027853965759</t>
+    <t xml:space="preserve">2.43307971954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43027806282043</t>
   </si>
   <si>
     <t xml:space="preserve">2.24117875099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17954635620117</t>
+    <t xml:space="preserve">2.17954611778259</t>
   </si>
   <si>
     <t xml:space="preserve">2.13192129135132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23417496681213</t>
+    <t xml:space="preserve">2.23417520523071</t>
   </si>
   <si>
     <t xml:space="preserve">2.20475959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1907525062561</t>
+    <t xml:space="preserve">2.19075226783752</t>
   </si>
   <si>
     <t xml:space="preserve">2.15153169631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20195817947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18374872207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21456456184387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17674469947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16834020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09690308570862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10250616073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13332200050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10810852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09130001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0450758934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083675861359</t>
+    <t xml:space="preserve">2.2019579410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18374848365784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21456480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17674493789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1683406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09690260887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1025059223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13332223892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10810875892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09129977226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04507565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9708366394043</t>
   </si>
   <si>
     <t xml:space="preserve">1.91200566291809</t>
@@ -1181,52 +1181,52 @@
     <t xml:space="preserve">1.9274138212204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8895937204361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8755863904953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566028594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97924089431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9694356918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92321145534515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96523368358612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181086540222</t>
+    <t xml:space="preserve">1.88959383964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87558627128601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566004753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9792412519455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96943581104279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92321157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96523380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181074619293</t>
   </si>
   <si>
     <t xml:space="preserve">1.83496522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76492810249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75232183933258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77193188667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78313791751862</t>
+    <t xml:space="preserve">1.76492822170258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75232172012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77193200588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78313803672791</t>
   </si>
   <si>
     <t xml:space="preserve">1.8265608549118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86438059806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177397727966</t>
+    <t xml:space="preserve">1.86438071727753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177385807037</t>
   </si>
   <si>
     <t xml:space="preserve">1.81395399570465</t>
@@ -1235,70 +1235,70 @@
     <t xml:space="preserve">1.86578142642975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84897267818451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88399088382721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99745059013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04787731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0436749458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99605000019073</t>
+    <t xml:space="preserve">1.84897255897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8839910030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99745047092438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04787707328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04367470741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99604976177216</t>
   </si>
   <si>
     <t xml:space="preserve">2.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11931443214417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15013122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17114186286926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18725037574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12701869010925</t>
+    <t xml:space="preserve">2.11931467056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15013098716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17114210128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18725061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12701892852783</t>
   </si>
   <si>
     <t xml:space="preserve">2.14557838439941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10355615615845</t>
+    <t xml:space="preserve">2.10355639457703</t>
   </si>
   <si>
     <t xml:space="preserve">2.10320615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0282666683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04927802085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363264083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16028618812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10600757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03772163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1172137260437</t>
+    <t xml:space="preserve">2.02826690673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04927778244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1536328792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16028642654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10600781440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03772187232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11721348762512</t>
   </si>
   <si>
     <t xml:space="preserve">2.0800940990448</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">2.12736892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18584990501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14207673072815</t>
+    <t xml:space="preserve">2.15258193016052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18584966659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14207696914673</t>
   </si>
   <si>
     <t xml:space="preserve">2.19425415992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19005227088928</t>
+    <t xml:space="preserve">2.1900520324707</t>
   </si>
   <si>
     <t xml:space="preserve">2.2030086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17604470252991</t>
+    <t xml:space="preserve">2.17604446411133</t>
   </si>
   <si>
     <t xml:space="preserve">2.18865132331848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01005721092224</t>
+    <t xml:space="preserve">2.01005697250366</t>
   </si>
   <si>
     <t xml:space="preserve">2.08709788322449</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">2.12771916389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07624220848083</t>
+    <t xml:space="preserve">2.07624197006226</t>
   </si>
   <si>
     <t xml:space="preserve">2.0664370059967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1144118309021</t>
+    <t xml:space="preserve">2.11441230773926</t>
   </si>
   <si>
     <t xml:space="preserve">2.08394622802734</t>
@@ -1361,211 +1361,211 @@
     <t xml:space="preserve">2.12036514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12071561813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9634827375412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98274302482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9872955083847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96838533878326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94107103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03421950340271</t>
+    <t xml:space="preserve">2.12071537971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96348261833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98274278640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98729526996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293770313263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96838545799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94107115268707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03422021865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.00620532035828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01601052284241</t>
+    <t xml:space="preserve">2.01601028442383</t>
   </si>
   <si>
     <t xml:space="preserve">2.03492021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10915946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10775852203369</t>
+    <t xml:space="preserve">2.10915923118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10775876045227</t>
   </si>
   <si>
     <t xml:space="preserve">2.14382767677307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12421703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14662933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11791372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15888547897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13857483863831</t>
+    <t xml:space="preserve">2.12421751022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14662909507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11791396141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15888524055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13857507705688</t>
   </si>
   <si>
     <t xml:space="preserve">2.14487814903259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08289551734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14347720146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453062057495</t>
+    <t xml:space="preserve">2.08289575576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14347743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453085899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.07028889656067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09970426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86087882518768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87523639202118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84442007541656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82165825366974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57687938213348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47077369689941</t>
+    <t xml:space="preserve">2.09970450401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86087894439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87523627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84442019462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82165813446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57687950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47077357769012</t>
   </si>
   <si>
     <t xml:space="preserve">1.51839852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55446743965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578684329987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641047477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59648990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68018364906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61259818077087</t>
+    <t xml:space="preserve">1.55446755886078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6364107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59648978710175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6801837682724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61259806156158</t>
   </si>
   <si>
     <t xml:space="preserve">1.71170020103455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69874334335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72465717792511</t>
+    <t xml:space="preserve">1.69874322414398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7246572971344</t>
   </si>
   <si>
     <t xml:space="preserve">1.69138967990875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67808258533478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81990730762482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804051876068</t>
+    <t xml:space="preserve">1.67808270454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81990742683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7880402803421</t>
   </si>
   <si>
     <t xml:space="preserve">1.84792172908783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78068685531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73481249809265</t>
+    <t xml:space="preserve">1.78068673610687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73481225967407</t>
   </si>
   <si>
     <t xml:space="preserve">1.70364594459534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77403283119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80589985847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82586050033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173449993134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87243521213531</t>
+    <t xml:space="preserve">1.7740330696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80589997768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8258603811264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173426151276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274573326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87243497371674</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823260784149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85912775993347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8328640460968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81605529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85072338581085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601582050323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85807716846466</t>
+    <t xml:space="preserve">1.85912799835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83286416530609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81605494022369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85072314739227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601593971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85807764530182</t>
   </si>
   <si>
     <t xml:space="preserve">1.853875041008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76807999610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75337219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64901733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64621591567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337478160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65216910839081</t>
+    <t xml:space="preserve">1.76807975769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7533723115921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64901745319366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64621603488922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65216898918152</t>
   </si>
   <si>
     <t xml:space="preserve">1.61960172653198</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">1.5709263086319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53030467033386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46972298622131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42630004882812</t>
+    <t xml:space="preserve">1.53030490875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4697231054306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42630016803741</t>
   </si>
   <si>
     <t xml:space="preserve">1.42524969577789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4550154209137</t>
+    <t xml:space="preserve">1.45501530170441</t>
   </si>
   <si>
     <t xml:space="preserve">1.44380939006805</t>
@@ -1598,43 +1598,43 @@
     <t xml:space="preserve">1.44415962696075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43925702571869</t>
+    <t xml:space="preserve">1.43925714492798</t>
   </si>
   <si>
     <t xml:space="preserve">1.40704011917114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43120265007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40178716182709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.358154296875</t>
+    <t xml:space="preserve">1.43120276927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40178728103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35815441608429</t>
   </si>
   <si>
     <t xml:space="preserve">1.37132120132446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50719285011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49493646621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54326188564301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53555762767792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55026531219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61084735393524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61539971828461</t>
+    <t xml:space="preserve">1.50719273090363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49493634700775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54326164722443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53555774688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55026566982269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61084723472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61539947986603</t>
   </si>
   <si>
     <t xml:space="preserve">1.61609995365143</t>
@@ -1643,34 +1643,34 @@
     <t xml:space="preserve">1.62625539302826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62415409088135</t>
+    <t xml:space="preserve">1.62415421009064</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715066432953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64446485042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64866709709167</t>
+    <t xml:space="preserve">1.64446496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64866733551025</t>
   </si>
   <si>
     <t xml:space="preserve">1.48688209056854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40143692493439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37356245517731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4028377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41439390182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38602900505066</t>
+    <t xml:space="preserve">1.40143716335297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37356233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40283799171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41439402103424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38602888584137</t>
   </si>
   <si>
     <t xml:space="preserve">1.29638183116913</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">1.31108951568604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3052065372467</t>
+    <t xml:space="preserve">1.30520641803741</t>
   </si>
   <si>
     <t xml:space="preserve">1.31136965751648</t>
@@ -1691,64 +1691,64 @@
     <t xml:space="preserve">1.30758774280548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29960346221924</t>
+    <t xml:space="preserve">1.29960358142853</t>
   </si>
   <si>
     <t xml:space="preserve">1.22550463676453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2067346572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16905498504639</t>
+    <t xml:space="preserve">1.20673477649689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16905474662781</t>
   </si>
   <si>
     <t xml:space="preserve">1.14692330360413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09229445457458</t>
+    <t xml:space="preserve">1.09229457378387</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134445667267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08977317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14440190792084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16345191001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1633118391037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19608914852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23965215682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21317803859711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2241039276123</t>
+    <t xml:space="preserve">1.0897730588913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14440178871155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16345202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16331195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19608902931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23965203762054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2131781578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22410380840302</t>
   </si>
   <si>
     <t xml:space="preserve">1.25477993488312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29217982292175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28139388561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27046835422516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26640617847443</t>
+    <t xml:space="preserve">1.29217970371246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28139400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27046811580658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26640605926514</t>
   </si>
   <si>
     <t xml:space="preserve">1.23923182487488</t>
@@ -1760,10 +1760,10 @@
     <t xml:space="preserve">1.22256302833557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26262402534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19412803649902</t>
+    <t xml:space="preserve">1.26262414455414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19412815570831</t>
   </si>
   <si>
     <t xml:space="preserve">1.28517603874207</t>
@@ -1772,46 +1772,46 @@
     <t xml:space="preserve">1.32341611385345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38770997524261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41194260120392</t>
+    <t xml:space="preserve">1.38770985603333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41194272041321</t>
   </si>
   <si>
     <t xml:space="preserve">1.47392523288727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47147405147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836163520813</t>
+    <t xml:space="preserve">1.47147417068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836187362671</t>
   </si>
   <si>
     <t xml:space="preserve">1.53940963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54571318626404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55796945095062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47917795181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376991271973</t>
+    <t xml:space="preserve">1.54571306705475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55796933174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47917783260345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376979351044</t>
   </si>
   <si>
     <t xml:space="preserve">1.44801163673401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48478078842163</t>
+    <t xml:space="preserve">1.48478090763092</t>
   </si>
   <si>
     <t xml:space="preserve">1.49913847446442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4700733423233</t>
+    <t xml:space="preserve">1.47007322311401</t>
   </si>
   <si>
     <t xml:space="preserve">1.44345927238464</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">1.39401316642761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4315527677536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39443349838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35605323314667</t>
+    <t xml:space="preserve">1.43155300617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39443325996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35605335235596</t>
   </si>
   <si>
     <t xml:space="preserve">1.32285583019257</t>
@@ -1841,58 +1841,58 @@
     <t xml:space="preserve">1.37118124961853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43330383300781</t>
+    <t xml:space="preserve">1.43330371379852</t>
   </si>
   <si>
     <t xml:space="preserve">1.44170844554901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41509437561035</t>
+    <t xml:space="preserve">1.41509425640106</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209792137146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4245491027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38224709033966</t>
+    <t xml:space="preserve">1.42454922199249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38224697113037</t>
   </si>
   <si>
     <t xml:space="preserve">1.34918963909149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29344046115875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33168029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32551729679108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30058407783508</t>
+    <t xml:space="preserve">1.29344034194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33168041706085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551717758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30058419704437</t>
   </si>
   <si>
     <t xml:space="preserve">1.2948409318924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25996267795563</t>
+    <t xml:space="preserve">1.25996279716492</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864731311798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24721610546112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845239639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26206374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24917697906494</t>
+    <t xml:space="preserve">1.24721586704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845251560211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26206386089325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24917709827423</t>
   </si>
   <si>
     <t xml:space="preserve">1.24525499343872</t>
@@ -1901,13 +1901,13 @@
     <t xml:space="preserve">1.18474316596985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1518257856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1934278011322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21892118453979</t>
+    <t xml:space="preserve">1.15182602405548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19342768192291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21892094612122</t>
   </si>
   <si>
     <t xml:space="preserve">1.2291464805603</t>
@@ -1916,16 +1916,16 @@
     <t xml:space="preserve">1.20897591114044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29400074481964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3185133934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3141713142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27705156803131</t>
+    <t xml:space="preserve">1.29400050640106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31851363182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31417119503021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2770516872406</t>
   </si>
   <si>
     <t xml:space="preserve">1.36571836471558</t>
@@ -1937,40 +1937,40 @@
     <t xml:space="preserve">1.37706422805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969507694244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32775831222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147314786911</t>
+    <t xml:space="preserve">1.35969531536102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32775819301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31473159790039</t>
   </si>
   <si>
     <t xml:space="preserve">1.36011552810669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40879082679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47287464141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49318540096283</t>
+    <t xml:space="preserve">1.40879094600677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47287452220917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49318528175354</t>
   </si>
   <si>
     <t xml:space="preserve">1.46412014961243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43505489826202</t>
+    <t xml:space="preserve">1.43505477905273</t>
   </si>
   <si>
     <t xml:space="preserve">1.41544449329376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37566351890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38378775119781</t>
+    <t xml:space="preserve">1.37566363811493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.35675370693207</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">1.34372675418854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40318810939789</t>
+    <t xml:space="preserve">1.4031879901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.37720441818237</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">1.38112640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32103490829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30296528339386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28615641593933</t>
+    <t xml:space="preserve">1.3210346698761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30296516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28615653514862</t>
   </si>
   <si>
     <t xml:space="preserve">1.32019436359406</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">1.32824862003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33175039291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.359414935112</t>
+    <t xml:space="preserve">1.33175051212311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35941505432129</t>
   </si>
   <si>
     <t xml:space="preserve">1.36606848239899</t>
@@ -2027,55 +2027,55 @@
     <t xml:space="preserve">1.3664186000824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221671104431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37587356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37727439403534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37622368335724</t>
+    <t xml:space="preserve">1.36221647262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37587368488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37727451324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37622392177582</t>
   </si>
   <si>
     <t xml:space="preserve">1.43575501441956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45956790447235</t>
+    <t xml:space="preserve">1.45956778526306</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828279972076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43855655193329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49178469181061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48127901554108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44205868244171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38077616691589</t>
+    <t xml:space="preserve">1.43855667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49178457260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48127925395966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44205856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38077628612518</t>
   </si>
   <si>
     <t xml:space="preserve">1.38532865047455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27221918106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24595546722412</t>
+    <t xml:space="preserve">1.2722190618515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24595534801483</t>
   </si>
   <si>
     <t xml:space="preserve">1.1997309923172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19062638282776</t>
+    <t xml:space="preserve">1.19062626361847</t>
   </si>
   <si>
     <t xml:space="preserve">1.19798016548157</t>
@@ -2090,34 +2090,34 @@
     <t xml:space="preserve">1.19587910175323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18082106113434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15525758266449</t>
+    <t xml:space="preserve">1.18082118034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15525782108307</t>
   </si>
   <si>
     <t xml:space="preserve">1.17171633243561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14370155334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13914906978607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1493045091629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16261148452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15350651741028</t>
+    <t xml:space="preserve">1.14370167255402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13914918899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14930462837219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16261160373688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15350663661957</t>
   </si>
   <si>
     <t xml:space="preserve">1.19377791881561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16716384887695</t>
+    <t xml:space="preserve">1.16716396808624</t>
   </si>
   <si>
     <t xml:space="preserve">1.1416003704071</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">1.16821444034576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1710159778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15700852870941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20323300361633</t>
+    <t xml:space="preserve">1.17101585865021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15700840950012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20323288440704</t>
   </si>
   <si>
     <t xml:space="preserve">1.25365936756134</t>
@@ -2147,22 +2147,22 @@
     <t xml:space="preserve">1.24560511112213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23790109157562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23474943637848</t>
+    <t xml:space="preserve">1.23790121078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23474955558777</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451504230499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24105262756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23825120925903</t>
+    <t xml:space="preserve">1.26451516151428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24105274677277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23825132846832</t>
   </si>
   <si>
     <t xml:space="preserve">1.31949400901794</t>
@@ -2174,40 +2174,40 @@
     <t xml:space="preserve">1.36992061138153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33525228500366</t>
+    <t xml:space="preserve">1.33525240421295</t>
   </si>
   <si>
     <t xml:space="preserve">1.32264566421509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33350145816803</t>
+    <t xml:space="preserve">1.33350157737732</t>
   </si>
   <si>
     <t xml:space="preserve">1.33630275726318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34295654296875</t>
+    <t xml:space="preserve">1.34295642375946</t>
   </si>
   <si>
     <t xml:space="preserve">1.31214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3457578420639</t>
+    <t xml:space="preserve">1.34575772285461</t>
   </si>
   <si>
     <t xml:space="preserve">1.32439661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914389133453</t>
+    <t xml:space="preserve">1.31914377212524</t>
   </si>
   <si>
     <t xml:space="preserve">1.22634494304657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23159766197205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2372008562088</t>
+    <t xml:space="preserve">1.23159778118134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23720073699951</t>
   </si>
   <si>
     <t xml:space="preserve">1.23124754428864</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">1.21163725852966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17241680622101</t>
+    <t xml:space="preserve">1.17241668701172</t>
   </si>
   <si>
     <t xml:space="preserve">1.18222177028656</t>
@@ -2225,61 +2225,61 @@
     <t xml:space="preserve">1.18817484378815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1846729516983</t>
+    <t xml:space="preserve">1.18467307090759</t>
   </si>
   <si>
     <t xml:space="preserve">1.1860738992691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24210333824158</t>
+    <t xml:space="preserve">1.24210321903229</t>
   </si>
   <si>
     <t xml:space="preserve">1.26731646060944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15175580978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13529717922211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18047082424164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13424646854401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18012058734894</t>
+    <t xml:space="preserve">1.15175592899323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13529706001282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18047094345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1342465877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18012070655823</t>
   </si>
   <si>
     <t xml:space="preserve">1.20603430271149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17521810531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18992578983307</t>
+    <t xml:space="preserve">1.17521822452545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18992590904236</t>
   </si>
   <si>
     <t xml:space="preserve">1.21583950519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21653974056244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23404908180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27467036247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.286576628685</t>
+    <t xml:space="preserve">1.21653985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23404896259308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27467048168182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28657674789429</t>
   </si>
   <si>
     <t xml:space="preserve">1.32579731941223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28132379055023</t>
+    <t xml:space="preserve">1.28132367134094</t>
   </si>
   <si>
     <t xml:space="preserve">1.27186894416809</t>
@@ -2288,19 +2288,19 @@
     <t xml:space="preserve">1.26906752586365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30548655986786</t>
+    <t xml:space="preserve">1.30548667907715</t>
   </si>
   <si>
     <t xml:space="preserve">1.32474672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31844353675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3517107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31424129009247</t>
+    <t xml:space="preserve">1.31844341754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35171091556549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31424117088318</t>
   </si>
   <si>
     <t xml:space="preserve">1.34050512313843</t>
@@ -2309,22 +2309,22 @@
     <t xml:space="preserve">1.36816966533661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35066044330597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29743254184723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31003904342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33980464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33210051059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29007875919342</t>
+    <t xml:space="preserve">1.35066032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29743242263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31003892421722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33980476856232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33210062980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29007863998413</t>
   </si>
   <si>
     <t xml:space="preserve">1.27081847190857</t>
@@ -2333,88 +2333,88 @@
     <t xml:space="preserve">1.27537083625793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2876273393631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31249034404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32789826393127</t>
+    <t xml:space="preserve">1.28762722015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31249022483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32789850234985</t>
   </si>
   <si>
     <t xml:space="preserve">1.28307485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3096889257431</t>
+    <t xml:space="preserve">1.30968880653381</t>
   </si>
   <si>
     <t xml:space="preserve">1.42384886741638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50929391384125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50859344005585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49598681926727</t>
+    <t xml:space="preserve">1.50929379463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49598670005798</t>
   </si>
   <si>
     <t xml:space="preserve">1.47707676887512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4686723947525</t>
+    <t xml:space="preserve">1.46867251396179</t>
   </si>
   <si>
     <t xml:space="preserve">1.42314851284027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42665016651154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47777712345123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49528658390045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49388551712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44766139984131</t>
+    <t xml:space="preserve">1.42665028572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47777724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49528646469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49388575553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44766128063202</t>
   </si>
   <si>
     <t xml:space="preserve">1.42104744911194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41264307498932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41754567623138</t>
+    <t xml:space="preserve">1.41264283657074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41754543781281</t>
   </si>
   <si>
     <t xml:space="preserve">1.41614496707916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44135797023773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536553859711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46517050266266</t>
+    <t xml:space="preserve">1.44135808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536541938782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46517074108124</t>
   </si>
   <si>
     <t xml:space="preserve">1.43085253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41824615001678</t>
+    <t xml:space="preserve">1.4182460308075</t>
   </si>
   <si>
     <t xml:space="preserve">1.38813006877899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37412285804749</t>
+    <t xml:space="preserve">1.3741227388382</t>
   </si>
   <si>
     <t xml:space="preserve">1.41474401950836</t>
@@ -2423,31 +2423,31 @@
     <t xml:space="preserve">1.40353810787201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4098414182663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4532642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42034733295441</t>
+    <t xml:space="preserve">1.40984153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45326447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42034709453583</t>
   </si>
   <si>
     <t xml:space="preserve">1.36851978302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37797474861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38637936115265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4616687297821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42594993114471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43435442447662</t>
+    <t xml:space="preserve">1.37797462940216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38637924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46166861057281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.425950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43435454368591</t>
   </si>
   <si>
     <t xml:space="preserve">1.43365395069122</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">1.36886978149414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39373326301575</t>
+    <t xml:space="preserve">1.39373314380646</t>
   </si>
   <si>
     <t xml:space="preserve">1.36431753635406</t>
@@ -2468,37 +2468,37 @@
     <t xml:space="preserve">1.29568147659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35836434364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37307214736938</t>
+    <t xml:space="preserve">1.35836446285248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37307238578796</t>
   </si>
   <si>
     <t xml:space="preserve">1.46727180480957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52049970626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54641342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72010469436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626069068909</t>
+    <t xml:space="preserve">1.5204998254776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54641318321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72010481357574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4462605714798</t>
   </si>
   <si>
     <t xml:space="preserve">1.38848030567169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3012843132019</t>
+    <t xml:space="preserve">1.30128443241119</t>
   </si>
   <si>
     <t xml:space="preserve">1.1423008441925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09397542476654</t>
+    <t xml:space="preserve">1.09397554397583</t>
   </si>
   <si>
     <t xml:space="preserve">1.05755627155304</t>
@@ -2516,46 +2516,46 @@
     <t xml:space="preserve">0.772156119346619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88841724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81803023815155</t>
+    <t xml:space="preserve">0.888417363166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818030178546906</t>
   </si>
   <si>
     <t xml:space="preserve">0.874409914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874760031700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885965943336487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877561569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870207667350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926587402820587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912930250167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925886988639832</t>
+    <t xml:space="preserve">0.874760091304779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885966002941132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877561628818512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870207726955414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926587343215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912930190563202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925886929035187</t>
   </si>
   <si>
     <t xml:space="preserve">0.880713224411011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849196672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8404421210289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633253574371</t>
+    <t xml:space="preserve">0.84919661283493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840442180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633193969727</t>
   </si>
   <si>
     <t xml:space="preserve">0.846044957637787</t>
@@ -2567,67 +2567,67 @@
     <t xml:space="preserve">0.851297795772552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829936444759369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853048741817474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820131421089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777408838272095</t>
+    <t xml:space="preserve">0.829936563968658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853048801422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820131361484528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777408957481384</t>
   </si>
   <si>
     <t xml:space="preserve">0.778459489345551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778809666633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753246188163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751845419406891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771806001663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743791282176971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768304169178009</t>
+    <t xml:space="preserve">0.778809547424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753246247768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751845479011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771805942058563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743791222572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768304109573364</t>
   </si>
   <si>
     <t xml:space="preserve">0.789665341377258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809625804424286</t>
+    <t xml:space="preserve">0.809625864028931</t>
   </si>
   <si>
     <t xml:space="preserve">0.779860138893127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766553103923798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611144542694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776008188724518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765152335166931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803672671318054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812077045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807874917984009</t>
+    <t xml:space="preserve">0.766553163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611084938049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776008248329163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765152454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803672730922699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812077105045319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807874798774719</t>
   </si>
   <si>
     <t xml:space="preserve">0.785463154315948</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">0.756047666072845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730484187602997</t>
+    <t xml:space="preserve">0.730484127998352</t>
   </si>
   <si>
     <t xml:space="preserve">0.736087203025818</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">0.815228760242462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805773854255676</t>
+    <t xml:space="preserve">0.805773913860321</t>
   </si>
   <si>
     <t xml:space="preserve">0.858301401138306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872308731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89296966791153</t>
+    <t xml:space="preserve">0.872308790683746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892969608306885</t>
   </si>
   <si>
     <t xml:space="preserve">0.931840062141418</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">0.979115009307861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966858506202698</t>
+    <t xml:space="preserve">0.966858565807343</t>
   </si>
   <si>
     <t xml:space="preserve">0.891218781471252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895070850849152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901724278926849</t>
+    <t xml:space="preserve">0.895070791244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901724338531494</t>
   </si>
   <si>
     <t xml:space="preserve">0.967909097671509</t>
@@ -2708,22 +2708,22 @@
     <t xml:space="preserve">0.936392486095428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938493669033051</t>
+    <t xml:space="preserve">0.938493490219116</t>
   </si>
   <si>
     <t xml:space="preserve">0.965107679367065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913980722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934641540050507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899623274803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953551530838013</t>
+    <t xml:space="preserve">0.913980782032013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934641599655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899623095989227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953551650047302</t>
   </si>
   <si>
     <t xml:space="preserve">0.930089175701141</t>
@@ -2735,142 +2735,142 @@
     <t xml:space="preserve">0.954602062702179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943746328353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983317315578461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973161995410919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951450526714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916432023048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933941185474396</t>
+    <t xml:space="preserve">0.943746387958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983317196369171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973161816596985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951450407505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916432082653046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933941304683685</t>
   </si>
   <si>
     <t xml:space="preserve">0.948298692703247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957403421401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97351211309433</t>
+    <t xml:space="preserve">0.957403600215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973512053489685</t>
   </si>
   <si>
     <t xml:space="preserve">0.980865895748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03304326534271</t>
+    <t xml:space="preserve">1.033043384552</t>
   </si>
   <si>
     <t xml:space="preserve">1.03759574890137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00012612342834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998725295066833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960905432701111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967208743095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944096624851227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89367014169693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890168309211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874059796333313</t>
+    <t xml:space="preserve">1.00012600421906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998725235462189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960905373096466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967208683490753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944096565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893669962882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890168249607086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874059736728668</t>
   </si>
   <si>
     <t xml:space="preserve">0.913280427455902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927637994289398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907677352428436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890868544578552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915381491184235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978764712810516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971060812473297</t>
+    <t xml:space="preserve">0.927637934684753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907677412033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890868604183197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915381371974945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978764832019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971060872077942</t>
   </si>
   <si>
     <t xml:space="preserve">1.00572896003723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997324645519257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981566190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00923073291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986818909645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987519502639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00712954998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996624112129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999775946140289</t>
+    <t xml:space="preserve">0.997324585914612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98156613111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00923085212708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986819088459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987519443035126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00712978839874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996624231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999775886535645</t>
   </si>
   <si>
     <t xml:space="preserve">1.00467824935913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988919973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985768496990204</t>
+    <t xml:space="preserve">0.988920211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985768556594849</t>
   </si>
   <si>
     <t xml:space="preserve">0.970360398292542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958103895187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994523048400879</t>
+    <t xml:space="preserve">0.958103954792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994523167610168</t>
   </si>
   <si>
     <t xml:space="preserve">0.978414595127106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986118614673615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03724539279938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02148723602295</t>
+    <t xml:space="preserve">0.986118674278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03724551200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02148735523224</t>
   </si>
   <si>
     <t xml:space="preserve">1.01903593540192</t>
@@ -2879,43 +2879,43 @@
     <t xml:space="preserve">1.01203227043152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995573699474335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97386223077774</t>
+    <t xml:space="preserve">0.995573580265045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973862171173096</t>
   </si>
   <si>
     <t xml:space="preserve">0.916782200336456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922735393047333</t>
+    <t xml:space="preserve">0.922735273838043</t>
   </si>
   <si>
     <t xml:space="preserve">0.888067126274109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939544141292572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961605727672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972811698913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05405426025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11113452911377</t>
+    <t xml:space="preserve">0.939544260501862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961605787277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972811758518219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0540543794632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11113440990448</t>
   </si>
   <si>
     <t xml:space="preserve">1.09957849979401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16121065616608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18502330780029</t>
+    <t xml:space="preserve">1.16121077537537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.185023188591</t>
   </si>
   <si>
     <t xml:space="preserve">1.16961514949799</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">1.15910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12339103221893</t>
+    <t xml:space="preserve">1.12339091300964</t>
   </si>
   <si>
     <t xml:space="preserve">1.12829339504242</t>
@@ -2933,34 +2933,34 @@
     <t xml:space="preserve">1.12794327735901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16016030311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13564741611481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15280640125275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17591857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1556077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13214540481567</t>
+    <t xml:space="preserve">1.16016018390656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13564729690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17066562175751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545238018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15280628204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17591845989227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15560781955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13214552402496</t>
   </si>
   <si>
     <t xml:space="preserve">1.08522081375122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965721607208</t>
+    <t xml:space="preserve">1.05965733528137</t>
   </si>
   <si>
     <t xml:space="preserve">1.08627128601074</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">1.12899374961853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1500049829483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15210592746735</t>
+    <t xml:space="preserve">1.15000486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15210604667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.15490758419037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15455722808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066315174103</t>
+    <t xml:space="preserve">1.15455734729767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066291332245</t>
   </si>
   <si>
     <t xml:space="preserve">1.2512081861496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25611066818237</t>
+    <t xml:space="preserve">1.25611054897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502059936523</t>
@@ -2996,28 +2996,28 @@
     <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32684779167175</t>
+    <t xml:space="preserve">1.32684791088104</t>
   </si>
   <si>
     <t xml:space="preserve">1.35801434516907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32334613800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31879377365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29603159427643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31389117240906</t>
+    <t xml:space="preserve">1.3233460187912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31879365444183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29603171348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31389105319977</t>
   </si>
   <si>
     <t xml:space="preserve">1.30723762512207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2949812412262</t>
+    <t xml:space="preserve">1.29498112201691</t>
   </si>
   <si>
     <t xml:space="preserve">1.28482580184937</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">1.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26941752433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24315369129181</t>
+    <t xml:space="preserve">1.26941764354706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2431538105011</t>
   </si>
   <si>
     <t xml:space="preserve">1.25435972213745</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">1.27256941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26136338710785</t>
+    <t xml:space="preserve">1.26136350631714</t>
   </si>
   <si>
     <t xml:space="preserve">1.26661622524261</t>
@@ -3047,16 +3047,16 @@
     <t xml:space="preserve">1.26416480541229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2652153968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26766681671143</t>
+    <t xml:space="preserve">1.26521551609039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26766669750214</t>
   </si>
   <si>
     <t xml:space="preserve">1.26626598834991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2585620880127</t>
+    <t xml:space="preserve">1.25856196880341</t>
   </si>
   <si>
     <t xml:space="preserve">1.25821173191071</t>
@@ -3065,31 +3065,31 @@
     <t xml:space="preserve">1.32964932918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36957061290741</t>
+    <t xml:space="preserve">1.36957037448883</t>
   </si>
   <si>
     <t xml:space="preserve">1.34505748748779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34925961494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33455193042755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31529176235199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31809318065643</t>
+    <t xml:space="preserve">1.34925973415375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33455204963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31529188156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31809329986572</t>
   </si>
   <si>
     <t xml:space="preserve">1.31073939800262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31774306297302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2806236743927</t>
+    <t xml:space="preserve">1.3177433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28062355518341</t>
   </si>
   <si>
     <t xml:space="preserve">1.24735617637634</t>
@@ -3098,73 +3098,73 @@
     <t xml:space="preserve">1.26696634292603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2501574754715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29112911224365</t>
+    <t xml:space="preserve">1.25015759468079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29112923145294</t>
   </si>
   <si>
     <t xml:space="preserve">1.27432024478912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29953360557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34820914268494</t>
+    <t xml:space="preserve">1.29953348636627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34820902347565</t>
   </si>
   <si>
     <t xml:space="preserve">1.42174768447876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52260076999664</t>
+    <t xml:space="preserve">1.52260088920593</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190053462982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53240597248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48898303508759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50088918209076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51629745960236</t>
+    <t xml:space="preserve">1.53240585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4980880022049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48898315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50088942050934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51629734039307</t>
   </si>
   <si>
     <t xml:space="preserve">1.50789320468903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51979959011078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54851448535919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54361200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60594475269318</t>
+    <t xml:space="preserve">1.5197993516922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5485143661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54361188411713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60594463348389</t>
   </si>
   <si>
     <t xml:space="preserve">1.62695562839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62065255641937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59053659439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59193754196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909381866455</t>
+    <t xml:space="preserve">1.62065231800079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59053647518158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59193730354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909393787384</t>
   </si>
   <si>
     <t xml:space="preserve">1.70119476318359</t>
@@ -3173,46 +3173,46 @@
     <t xml:space="preserve">1.72360646724701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71029961109161</t>
+    <t xml:space="preserve">1.71029949188232</t>
   </si>
   <si>
     <t xml:space="preserve">1.70469665527344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71099996566772</t>
+    <t xml:space="preserve">1.71099984645844</t>
   </si>
   <si>
     <t xml:space="preserve">1.74881982803345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70539712905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68998885154724</t>
+    <t xml:space="preserve">1.70539689064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68998908996582</t>
   </si>
   <si>
     <t xml:space="preserve">1.65356981754303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63536036014557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64936757087708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63465976715088</t>
+    <t xml:space="preserve">1.63536012172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64936769008636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63466000556946</t>
   </si>
   <si>
     <t xml:space="preserve">1.62835645675659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66547608375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71505236625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61877381801605</t>
+    <t xml:space="preserve">1.6654759645462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71505224704742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61877369880676</t>
   </si>
   <si>
     <t xml:space="preserve">1.59937429428101</t>
@@ -3224,76 +3224,76 @@
     <t xml:space="preserve">1.62308478355408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65613567829132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67337942123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71936321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71289682388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70283782482147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73445177078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71145987510681</t>
+    <t xml:space="preserve">1.65613543987274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67337930202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71936333179474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71289670467377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70283794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73445188999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71145975589752</t>
   </si>
   <si>
     <t xml:space="preserve">1.74522912502289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893973350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76822113990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81707894802094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83504104614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85587751865387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86449980735779</t>
+    <t xml:space="preserve">1.76893961429596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76822102069855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81707882881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83504128456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85587775707245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86449944972992</t>
   </si>
   <si>
     <t xml:space="preserve">1.92126083374023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95934104919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97299265861511</t>
+    <t xml:space="preserve">1.95934116840363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9729927778244</t>
   </si>
   <si>
     <t xml:space="preserve">1.98377025127411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94066035747528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96508920192719</t>
+    <t xml:space="preserve">1.94066047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96508944034576</t>
   </si>
   <si>
     <t xml:space="preserve">1.9974217414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02400612831116</t>
+    <t xml:space="preserve">2.02400588989258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03334641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08579707145691</t>
+    <t xml:space="preserve">2.08579683303833</t>
   </si>
   <si>
     <t xml:space="preserve">2.08795213699341</t>
@@ -3305,16 +3305,16 @@
     <t xml:space="preserve">2.12531399726868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13465452194214</t>
+    <t xml:space="preserve">2.13465476036072</t>
   </si>
   <si>
     <t xml:space="preserve">2.1540539264679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15189838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18423104286194</t>
+    <t xml:space="preserve">2.15189814567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18423080444336</t>
   </si>
   <si>
     <t xml:space="preserve">2.17201638221741</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">2.17560887336731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17632746696472</t>
+    <t xml:space="preserve">2.17632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">2.16052055358887</t>
@@ -3335,16 +3335,16 @@
     <t xml:space="preserve">2.12818789482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08938932418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0807671546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05346441268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08292269706726</t>
+    <t xml:space="preserve">2.08938908576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076739311218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05346465110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08292293548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.04771637916565</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">2.01897644996643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04053163528442</t>
+    <t xml:space="preserve">2.04053139686584</t>
   </si>
   <si>
     <t xml:space="preserve">1.98305153846741</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">1.96652626991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94928228855133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9521564245224</t>
+    <t xml:space="preserve">1.94928205013275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95215630531311</t>
   </si>
   <si>
     <t xml:space="preserve">1.90114295482635</t>
@@ -3377,16 +3377,16 @@
     <t xml:space="preserve">1.83288598060608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93922317028046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93634915351868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91766822338104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8882098197937</t>
+    <t xml:space="preserve">1.93922340869904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93634939193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91766846179962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88821005821228</t>
   </si>
   <si>
     <t xml:space="preserve">1.88749158382416</t>
@@ -3395,43 +3395,43 @@
     <t xml:space="preserve">1.84653723239899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7876204252243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82641935348511</t>
+    <t xml:space="preserve">1.78762054443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8264194726944</t>
   </si>
   <si>
     <t xml:space="preserve">1.8752772808075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85803306102753</t>
+    <t xml:space="preserve">1.85803318023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.90258014202118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87743234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89108383655548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82067143917084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81348645687103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82857501506805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96724474430084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97371137142181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95718586444855</t>
+    <t xml:space="preserve">1.87743258476257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89108407497406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82067120075226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81348633766174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82857477664948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96724486351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97371113300323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95718574523926</t>
   </si>
   <si>
     <t xml:space="preserve">2.03190946578979</t>
@@ -3440,106 +3440,106 @@
     <t xml:space="preserve">2.00676202774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00388789176941</t>
+    <t xml:space="preserve">2.00388813018799</t>
   </si>
   <si>
     <t xml:space="preserve">1.97155570983887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93347549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90904629230499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94209730625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97802233695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01107287406921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957680702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01753926277161</t>
+    <t xml:space="preserve">1.93347537517548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90904664993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94209742546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01107311248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957716464996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01753973960876</t>
   </si>
   <si>
     <t xml:space="preserve">2.03262782096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03119087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99167382717133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01322865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97945928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95000100135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9377863407135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96868169307709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92269790172577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94712722301483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92916452884674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83073008060455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84078931808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92054259777069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97586667537689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92341661453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94353425502777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94425296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91838693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616119384766</t>
+    <t xml:space="preserve">2.03119111061096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99167370796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01322841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97945916652679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95000076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93778645992279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96868193149567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92269814014435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94712674617767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92916440963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83073031902313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84078919887543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92054224014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9758665561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9234162569046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94353449344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94425284862518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91838681697845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616167068481</t>
   </si>
   <si>
     <t xml:space="preserve">2.02831721305847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02185034751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047227859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994188308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04340577125549</t>
+    <t xml:space="preserve">2.0218505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047251701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994212150574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04340553283691</t>
   </si>
   <si>
     <t xml:space="preserve">2.10016655921936</t>
@@ -3551,130 +3551,130 @@
     <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1231586933136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13034343719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1475875377655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10950708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08148598670959</t>
+    <t xml:space="preserve">2.12315845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1303436756134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14758729934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1095073223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08148574829102</t>
   </si>
   <si>
     <t xml:space="preserve">1.92988300323486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93563091754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083723545074</t>
+    <t xml:space="preserve">1.93563079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97083735466003</t>
   </si>
   <si>
     <t xml:space="preserve">2.00963592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08364129066467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03765749931335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00316977500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98592531681061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95143795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042459964752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88318049907684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85372233390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74594759941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540612220764</t>
+    <t xml:space="preserve">2.08364152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03765726089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00316953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98592567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9514377117157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042424201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88318061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85372221469879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74594748020172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540600299835</t>
   </si>
   <si>
     <t xml:space="preserve">1.77181363105774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80845665931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83001172542572</t>
+    <t xml:space="preserve">1.80845677852631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8300119638443</t>
   </si>
   <si>
     <t xml:space="preserve">1.88533616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92557203769684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88964700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88677310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86737370491028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89036571979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8544408082962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84797430038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79767942428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85659611225128</t>
+    <t xml:space="preserve">1.92557168006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8896472454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88677299022675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86737358570099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89036560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85444068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84797441959381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79767954349518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85659658908844</t>
   </si>
   <si>
     <t xml:space="preserve">1.85875177383423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8472558259964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85515916347504</t>
+    <t xml:space="preserve">1.84725570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85515940189362</t>
   </si>
   <si>
     <t xml:space="preserve">1.88605463504791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89683222770691</t>
+    <t xml:space="preserve">1.89683210849762</t>
   </si>
   <si>
     <t xml:space="preserve">1.97874081134796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00101399421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0254430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06280493736267</t>
+    <t xml:space="preserve">2.0010142326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02544283866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06280469894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.05849385261536</t>
@@ -3686,31 +3686,31 @@
     <t xml:space="preserve">2.0563383102417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0527458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02113199234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0046067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01250982284546</t>
+    <t xml:space="preserve">2.05274605751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02113223075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00460648536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01251006126404</t>
   </si>
   <si>
     <t xml:space="preserve">1.99526607990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8997061252594</t>
+    <t xml:space="preserve">1.89970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">1.87958812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93131971359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221530437469</t>
+    <t xml:space="preserve">1.93131995201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221518516541</t>
   </si>
   <si>
     <t xml:space="preserve">1.91192042827606</t>
@@ -3719,28 +3719,28 @@
     <t xml:space="preserve">2.02041339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06855273246765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1044774055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07645630836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657430648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15118002891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32505655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32361936569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55138278007507</t>
+    <t xml:space="preserve">2.06855297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10447788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07645606994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09657406806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15117979049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32505631446838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32361912727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55138301849365</t>
   </si>
   <si>
     <t xml:space="preserve">2.53485751152039</t>
@@ -3761,55 +3761,55 @@
     <t xml:space="preserve">2.52336144447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5104284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41343116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21584486961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26398420333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21368956565857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496047973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120219230652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66475737094879</t>
+    <t xml:space="preserve">2.51042866706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343140602112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21584463119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26398396492004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21368908882141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496024131775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120195388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66475749015808</t>
   </si>
   <si>
     <t xml:space="preserve">1.74954009056091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79480528831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575987815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90186166763306</t>
+    <t xml:space="preserve">1.79480540752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90186154842377</t>
   </si>
   <si>
     <t xml:space="preserve">2.06783437728882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96077835559845</t>
+    <t xml:space="preserve">1.96077823638916</t>
   </si>
   <si>
     <t xml:space="preserve">1.95862281322479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879945278168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9557489156723</t>
+    <t xml:space="preserve">1.98879969120026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95574879646301</t>
   </si>
   <si>
     <t xml:space="preserve">1.95359337329865</t>
@@ -3818,64 +3818,64 @@
     <t xml:space="preserve">2.06208634376526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93275666236877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99095511436462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98664438724518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9478452205658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16626858711243</t>
+    <t xml:space="preserve">1.93275701999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99095523357391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98664402961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94784510135651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16626834869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.12459564208984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19572710990906</t>
+    <t xml:space="preserve">2.19572687149048</t>
   </si>
   <si>
     <t xml:space="preserve">2.19860076904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23077535629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33036351203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35257959365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35181331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36713457107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.321937084198</t>
+    <t xml:space="preserve">2.2307755947113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33036375045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35257935523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35181355476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36713480949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32193684577942</t>
   </si>
   <si>
     <t xml:space="preserve">2.35104727745056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31887269020081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27597308158875</t>
+    <t xml:space="preserve">2.31887245178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27597332000732</t>
   </si>
   <si>
     <t xml:space="preserve">2.33572626113892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24839472770691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23383975028992</t>
+    <t xml:space="preserve">2.24839496612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23383951187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.21085786819458</t>
@@ -3887,22 +3887,22 @@
     <t xml:space="preserve">2.1587655544281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25069308280945</t>
+    <t xml:space="preserve">2.25069332122803</t>
   </si>
   <si>
     <t xml:space="preserve">2.23307371139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2154541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2828676700592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26448249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31351041793823</t>
+    <t xml:space="preserve">2.21545433998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28286790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26448225975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31351017951965</t>
   </si>
   <si>
     <t xml:space="preserve">2.38092374801636</t>
@@ -3911,10 +3911,10 @@
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45523166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47285127639771</t>
+    <t xml:space="preserve">2.45523190498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47285151481628</t>
   </si>
   <si>
     <t xml:space="preserve">2.45293354988098</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">2.48664045333862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46365857124329</t>
+    <t xml:space="preserve">2.46365880966187</t>
   </si>
   <si>
     <t xml:space="preserve">2.47438359260559</t>
@@ -3935,19 +3935,19 @@
     <t xml:space="preserve">2.41309857368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43071818351746</t>
+    <t xml:space="preserve">2.43071794509888</t>
   </si>
   <si>
     <t xml:space="preserve">2.37709355354309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09058618545532</t>
+    <t xml:space="preserve">2.09058594703674</t>
   </si>
   <si>
     <t xml:space="preserve">1.98793339729309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01168131828308</t>
+    <t xml:space="preserve">2.01168155670166</t>
   </si>
   <si>
     <t xml:space="preserve">2.08062720298767</t>
@@ -3956,22 +3956,22 @@
     <t xml:space="preserve">2.02623653411865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07832908630371</t>
+    <t xml:space="preserve">2.07832884788513</t>
   </si>
   <si>
     <t xml:space="preserve">2.16795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21315622329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1993670463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13501739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20089912414551</t>
+    <t xml:space="preserve">2.21315598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19936680793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13501763343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20089888572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.14267826080322</t>
@@ -3986,22 +3986,22 @@
     <t xml:space="preserve">2.0315990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99406182765961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90290057659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86919391155243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98410332202911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98563539981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91592359542847</t>
+    <t xml:space="preserve">1.99406206607819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9029004573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86919379234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98410308361053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98563516139984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91592347621918</t>
   </si>
   <si>
     <t xml:space="preserve">1.8684276342392</t>
@@ -4010,25 +4010,25 @@
     <t xml:space="preserve">1.83472084999084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73743093013763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77420198917389</t>
+    <t xml:space="preserve">1.73743081092834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7742018699646</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012449741364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92435026168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87915241718292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79718363285065</t>
+    <t xml:space="preserve">1.92435014247894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87915253639221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80331254005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79718387126923</t>
   </si>
   <si>
     <t xml:space="preserve">1.85387253761292</t>
@@ -4037,19 +4037,19 @@
     <t xml:space="preserve">1.79641759395599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84544575214386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86306524276733</t>
+    <t xml:space="preserve">1.84544563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86306512355804</t>
   </si>
   <si>
     <t xml:space="preserve">1.92894661426544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92051994800568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96954822540283</t>
+    <t xml:space="preserve">1.92052006721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96954798698425</t>
   </si>
   <si>
     <t xml:space="preserve">2.06837034225464</t>
@@ -4058,22 +4058,22 @@
     <t xml:space="preserve">2.00095653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03466320037842</t>
+    <t xml:space="preserve">2.034663438797</t>
   </si>
   <si>
     <t xml:space="preserve">1.98869955539703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9718462228775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95652496814728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99176383018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07220029830933</t>
+    <t xml:space="preserve">1.97184610366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95652484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99176371097565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07220053672791</t>
   </si>
   <si>
     <t xml:space="preserve">2.06530594825745</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">2.02240633964539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01397943496704</t>
+    <t xml:space="preserve">2.01397967338562</t>
   </si>
   <si>
     <t xml:space="preserve">1.94273579120636</t>
@@ -4100,10 +4100,10 @@
     <t xml:space="preserve">1.80944073200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86612951755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8983039855957</t>
+    <t xml:space="preserve">1.86612975597382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89830410480499</t>
   </si>
   <si>
     <t xml:space="preserve">1.90213441848755</t>
@@ -4112,13 +4112,13 @@
     <t xml:space="preserve">1.8714919090271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96878182888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90060234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90673089027405</t>
+    <t xml:space="preserve">1.9687819480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90060222148895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90673077106476</t>
   </si>
   <si>
     <t xml:space="preserve">1.89907014369965</t>
@@ -4148,16 +4148,16 @@
     <t xml:space="preserve">2.15799951553345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12965512275696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0928840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07143449783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02700257301331</t>
+    <t xml:space="preserve">2.12965536117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09288430213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07143425941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02700281143188</t>
   </si>
   <si>
     <t xml:space="preserve">2.06377363204956</t>
@@ -4172,13 +4172,13 @@
     <t xml:space="preserve">2.10820531845093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03006720542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04155778884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07986116409302</t>
+    <t xml:space="preserve">2.0300669670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04155802726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07986092567444</t>
   </si>
   <si>
     <t xml:space="preserve">2.05151653289795</t>
@@ -4190,7 +4190,7 @@
     <t xml:space="preserve">2.11893033981323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17485308647156</t>
+    <t xml:space="preserve">2.17485284805298</t>
   </si>
   <si>
     <t xml:space="preserve">2.17255449295044</t>
@@ -4199,31 +4199,31 @@
     <t xml:space="preserve">2.17332077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19323825836182</t>
+    <t xml:space="preserve">2.1932384967804</t>
   </si>
   <si>
     <t xml:space="preserve">2.22617888450623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21698617935181</t>
+    <t xml:space="preserve">2.21698641777039</t>
   </si>
   <si>
     <t xml:space="preserve">2.3173406124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3441526889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34491872787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37173104286194</t>
+    <t xml:space="preserve">2.34415292739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34491896629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37173128128052</t>
   </si>
   <si>
     <t xml:space="preserve">2.41922688484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220876693726</t>
+    <t xml:space="preserve">2.44220900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.37785959243774</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">2.42152523994446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35564351081848</t>
+    <t xml:space="preserve">2.35564374923706</t>
   </si>
   <si>
     <t xml:space="preserve">2.36177229881287</t>
@@ -4244,34 +4244,34 @@
     <t xml:space="preserve">2.45140171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45906209945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970460891724</t>
+    <t xml:space="preserve">2.45906233787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970484733582</t>
   </si>
   <si>
     <t xml:space="preserve">2.51268672943115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56171488761902</t>
+    <t xml:space="preserve">2.56171464920044</t>
   </si>
   <si>
     <t xml:space="preserve">2.58086633682251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53949928283691</t>
+    <t xml:space="preserve">2.53949904441833</t>
   </si>
   <si>
     <t xml:space="preserve">2.55175590515137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52187943458557</t>
+    <t xml:space="preserve">2.52187967300415</t>
   </si>
   <si>
     <t xml:space="preserve">2.53796672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53720092773438</t>
+    <t xml:space="preserve">2.5372006893158</t>
   </si>
   <si>
     <t xml:space="preserve">2.4759156703949</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">2.44450712203979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41386437416077</t>
+    <t xml:space="preserve">2.41386461257935</t>
   </si>
   <si>
     <t xml:space="preserve">2.40390586853027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41080045700073</t>
+    <t xml:space="preserve">2.41080021858215</t>
   </si>
   <si>
     <t xml:space="preserve">2.40313982963562</t>
@@ -4298,13 +4298,13 @@
     <t xml:space="preserve">2.4207592010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51881551742554</t>
+    <t xml:space="preserve">2.51881527900696</t>
   </si>
   <si>
     <t xml:space="preserve">2.50349378585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44527316093445</t>
+    <t xml:space="preserve">2.44527292251587</t>
   </si>
   <si>
     <t xml:space="preserve">2.48817253112793</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">2.5686092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59465551376343</t>
+    <t xml:space="preserve">2.59465527534485</t>
   </si>
   <si>
     <t xml:space="preserve">2.5793342590332</t>
@@ -4328,10 +4328,10 @@
     <t xml:space="preserve">2.56477904319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57703614234924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55405402183533</t>
+    <t xml:space="preserve">2.57703590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55405426025391</t>
   </si>
   <si>
     <t xml:space="preserve">2.62376570701599</t>
@@ -4340,10 +4340,10 @@
     <t xml:space="preserve">2.67739009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77774453163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78923535346985</t>
+    <t xml:space="preserve">2.77774405479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78923559188843</t>
   </si>
   <si>
     <t xml:space="preserve">2.77468037605286</t>
@@ -4352,37 +4352,37 @@
     <t xml:space="preserve">2.75859308242798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72335410118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74020719528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8214099407196</t>
+    <t xml:space="preserve">2.72335386276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74020743370056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82141017913818</t>
   </si>
   <si>
     <t xml:space="preserve">2.94014978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92176413536072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93172287940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89725017547607</t>
+    <t xml:space="preserve">2.9217643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93172311782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89725041389465</t>
   </si>
   <si>
     <t xml:space="preserve">2.92636060714722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95700335502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99454045295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00756335258484</t>
+    <t xml:space="preserve">2.95700311660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99453997612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00756359100342</t>
   </si>
   <si>
     <t xml:space="preserve">3.07038044929504</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">3.09106421470642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07957339286804</t>
+    <t xml:space="preserve">3.07957315444946</t>
   </si>
   <si>
     <t xml:space="preserve">3.16154193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19831323623657</t>
+    <t xml:space="preserve">3.19831299781799</t>
   </si>
   <si>
     <t xml:space="preserve">3.14315676689148</t>
@@ -4409,10 +4409,10 @@
     <t xml:space="preserve">3.29024076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2243595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22052884101868</t>
+    <t xml:space="preserve">3.22435927391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22052907943726</t>
   </si>
   <si>
     <t xml:space="preserve">3.18145966529846</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">3.18682217597961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1676709651947</t>
+    <t xml:space="preserve">3.16767048835754</t>
   </si>
   <si>
     <t xml:space="preserve">3.14085817337036</t>
@@ -4430,64 +4430,64 @@
     <t xml:space="preserve">3.19448280334473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22282695770264</t>
+    <t xml:space="preserve">3.22282719612122</t>
   </si>
   <si>
     <t xml:space="preserve">3.10255527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04280209541321</t>
+    <t xml:space="preserve">3.04280233383179</t>
   </si>
   <si>
     <t xml:space="preserve">3.11634421348572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05812358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12860131263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16000986099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16077613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11711049079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15081691741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22359347343445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18912029266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23355174064636</t>
+    <t xml:space="preserve">3.05812382698059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12860155105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16001009941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16077589988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11711025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15081715583801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22359323501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18912053108215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23355221748352</t>
   </si>
   <si>
     <t xml:space="preserve">3.17150068283081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07727527618408</t>
+    <t xml:space="preserve">3.0772750377655</t>
   </si>
   <si>
     <t xml:space="preserve">2.82830452919006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88116312026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67585802078247</t>
+    <t xml:space="preserve">2.8811628818512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67585825920105</t>
   </si>
   <si>
     <t xml:space="preserve">2.71186304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70573449134827</t>
+    <t xml:space="preserve">2.70573472976685</t>
   </si>
   <si>
     <t xml:space="preserve">2.80991911888123</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">2.80379056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71952342987061</t>
+    <t xml:space="preserve">2.71952366828918</t>
   </si>
   <si>
     <t xml:space="preserve">2.60691261291504</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">2.65900468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75782680511475</t>
+    <t xml:space="preserve">2.75782656669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.79996037483215</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">2.75476264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82370829582214</t>
+    <t xml:space="preserve">2.82370853424072</t>
   </si>
   <si>
     <t xml:space="preserve">2.83979558944702</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">2.93019104003906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01828813552856</t>
+    <t xml:space="preserve">3.01828837394714</t>
   </si>
   <si>
     <t xml:space="preserve">3.08033919334412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11098194122314</t>
+    <t xml:space="preserve">3.11098170280457</t>
   </si>
   <si>
     <t xml:space="preserve">3.24427700042725</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">3.03609204292297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11466789245605</t>
+    <t xml:space="preserve">3.11466765403748</t>
   </si>
   <si>
     <t xml:space="preserve">2.98505854606628</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">3.0109806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04905319213867</t>
+    <t xml:space="preserve">3.04905295372009</t>
   </si>
   <si>
     <t xml:space="preserve">3.27910900115967</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.1567907333374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1106173992157</t>
+    <t xml:space="preserve">3.11061716079712</t>
   </si>
   <si>
     <t xml:space="preserve">3.16003108024597</t>
@@ -4598,52 +4598,52 @@
     <t xml:space="preserve">3.1738018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16732168197632</t>
+    <t xml:space="preserve">3.16732144355774</t>
   </si>
   <si>
     <t xml:space="preserve">3.13572931289673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17947220802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1584107875824</t>
+    <t xml:space="preserve">3.17947196960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15841054916382</t>
   </si>
   <si>
     <t xml:space="preserve">3.21754479408264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21025419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631563186646</t>
+    <t xml:space="preserve">3.21025443077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631539344788</t>
   </si>
   <si>
     <t xml:space="preserve">3.09684634208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09441637992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05472373962402</t>
+    <t xml:space="preserve">3.09441614151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05472350120544</t>
   </si>
   <si>
     <t xml:space="preserve">3.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96318697929382</t>
+    <t xml:space="preserve">2.9631872177124</t>
   </si>
   <si>
     <t xml:space="preserve">3.03771233558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11142754554749</t>
+    <t xml:space="preserve">3.11142778396606</t>
   </si>
   <si>
     <t xml:space="preserve">3.06768441200256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11304759979248</t>
+    <t xml:space="preserve">3.1130473613739</t>
   </si>
   <si>
     <t xml:space="preserve">3.09765625</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">3.07983541488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10251688957214</t>
+    <t xml:space="preserve">3.10251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">3.09198594093323</t>
@@ -4664,22 +4664,22 @@
     <t xml:space="preserve">3.14626002311707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16165137290955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508690834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26776838302612</t>
+    <t xml:space="preserve">3.16165113449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26776814460754</t>
   </si>
   <si>
     <t xml:space="preserve">3.24751687049866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31556177139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29612040519714</t>
+    <t xml:space="preserve">3.31556153297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29612016677856</t>
   </si>
   <si>
     <t xml:space="preserve">3.22888588905334</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">3.22240519523621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27586936950684</t>
+    <t xml:space="preserve">3.27586913108826</t>
   </si>
   <si>
     <t xml:space="preserve">3.31070137023926</t>
@@ -4700,10 +4700,10 @@
     <t xml:space="preserve">3.44274067878723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50673508644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44031047821045</t>
+    <t xml:space="preserve">3.50673484802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44031071662903</t>
   </si>
   <si>
     <t xml:space="preserve">3.44355058670044</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">3.34553384780884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42005896568298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46947264671326</t>
+    <t xml:space="preserve">3.42005920410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46947240829468</t>
   </si>
   <si>
     <t xml:space="preserve">3.4978244304657</t>
@@ -4724,64 +4724,64 @@
     <t xml:space="preserve">3.57883048057556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61852312088013</t>
+    <t xml:space="preserve">3.61852288246155</t>
   </si>
   <si>
     <t xml:space="preserve">3.54075741767883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61042189598083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62500309944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58531045913696</t>
+    <t xml:space="preserve">3.61042237281799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62500333786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58531069755554</t>
   </si>
   <si>
     <t xml:space="preserve">3.60475182533264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5942211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59503173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5934112071991</t>
+    <t xml:space="preserve">3.59422135353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59503149986267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59341096878052</t>
   </si>
   <si>
     <t xml:space="preserve">3.63391423225403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63634443283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63553428649902</t>
+    <t xml:space="preserve">3.63634419441223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63553380966187</t>
   </si>
   <si>
     <t xml:space="preserve">3.68413734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64606499671936</t>
+    <t xml:space="preserve">3.64606475830078</t>
   </si>
   <si>
     <t xml:space="preserve">3.58774065971375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50511503219604</t>
+    <t xml:space="preserve">3.50511527061462</t>
   </si>
   <si>
     <t xml:space="preserve">3.48162317276001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56505918502808</t>
+    <t xml:space="preserve">3.56505942344666</t>
   </si>
   <si>
     <t xml:space="preserve">3.2410364151001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41762900352478</t>
+    <t xml:space="preserve">3.4176287651062</t>
   </si>
   <si>
     <t xml:space="preserve">3.51807570457458</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">3.54480767250061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52293634414673</t>
+    <t xml:space="preserve">3.52293610572815</t>
   </si>
   <si>
     <t xml:space="preserve">3.55857872962952</t>
@@ -4811,10 +4811,10 @@
     <t xml:space="preserve">3.51564574241638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56667923927307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5764000415802</t>
+    <t xml:space="preserve">3.56667900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57639980316162</t>
   </si>
   <si>
     <t xml:space="preserve">3.60556244850159</t>
@@ -4823,22 +4823,22 @@
     <t xml:space="preserve">3.57720994949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54318761825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49944496154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46380186080933</t>
+    <t xml:space="preserve">3.54318785667419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49944472312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46380233764648</t>
   </si>
   <si>
     <t xml:space="preserve">3.35687470436096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28883004188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32123208045959</t>
+    <t xml:space="preserve">3.28882956504822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32123184204102</t>
   </si>
   <si>
     <t xml:space="preserve">3.3852264881134</t>
@@ -4847,28 +4847,28 @@
     <t xml:space="preserve">3.45651173591614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48324370384216</t>
+    <t xml:space="preserve">3.48324346542358</t>
   </si>
   <si>
     <t xml:space="preserve">3.53994727134705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62743377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70843911170959</t>
+    <t xml:space="preserve">3.62743353843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70843958854675</t>
   </si>
   <si>
     <t xml:space="preserve">3.77243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7521824836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82670736312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75137233734131</t>
+    <t xml:space="preserve">3.75218224525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82670712471008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75137257575989</t>
   </si>
   <si>
     <t xml:space="preserve">3.6898078918457</t>
@@ -4880,7 +4880,7 @@
     <t xml:space="preserve">3.67360663414001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68251729011536</t>
+    <t xml:space="preserve">3.68251752853394</t>
   </si>
   <si>
     <t xml:space="preserve">3.66712641716003</t>
@@ -4904,37 +4904,37 @@
     <t xml:space="preserve">3.84776902198792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84938907623291</t>
+    <t xml:space="preserve">3.84938883781433</t>
   </si>
   <si>
     <t xml:space="preserve">3.926344871521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97818756103516</t>
+    <t xml:space="preserve">3.97818779945374</t>
   </si>
   <si>
     <t xml:space="preserve">3.97089743614197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80078530311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8396680355072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76838350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402588844299</t>
+    <t xml:space="preserve">3.800785779953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83966827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76838326454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402612686157</t>
   </si>
   <si>
     <t xml:space="preserve">3.80726599693298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79349517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82589721679688</t>
+    <t xml:space="preserve">3.79349541664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82589745521545</t>
   </si>
   <si>
     <t xml:space="preserve">3.90690302848816</t>
@@ -4943,25 +4943,25 @@
     <t xml:space="preserve">3.95793676376343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9417359828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94659614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97251749038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94011545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99114871025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10698747634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.119948387146</t>
+    <t xml:space="preserve">3.94173574447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94659638404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97251772880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94011521339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99114942550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10698699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11994791030884</t>
   </si>
   <si>
     <t xml:space="preserve">4.30950117111206</t>
@@ -4979,16 +4979,16 @@
     <t xml:space="preserve">4.27223873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31274127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1393895149231</t>
+    <t xml:space="preserve">4.31274175643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13938903808594</t>
   </si>
   <si>
     <t xml:space="preserve">4.11346769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13128900527954</t>
+    <t xml:space="preserve">4.13128852844238</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642860412598</t>
@@ -5000,22 +5000,22 @@
     <t xml:space="preserve">4.09888648986816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12318849563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11022710800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18637275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14100980758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15721082687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99357891082764</t>
+    <t xml:space="preserve">4.12318801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11022758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18637323379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14100933074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15721035003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99357914924622</t>
   </si>
   <si>
     <t xml:space="preserve">4.04137229919434</t>
@@ -5024,25 +5024,25 @@
     <t xml:space="preserve">4.07296466827393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05676317214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90204286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83480834960938</t>
+    <t xml:space="preserve">4.05676364898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90204238891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83480858802795</t>
   </si>
   <si>
     <t xml:space="preserve">3.87045049667358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89961290359497</t>
+    <t xml:space="preserve">3.89961266517639</t>
   </si>
   <si>
     <t xml:space="preserve">3.84290862083435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81617665290833</t>
+    <t xml:space="preserve">3.81617712974548</t>
   </si>
   <si>
     <t xml:space="preserve">3.86072969436646</t>
@@ -5051,55 +5051,55 @@
     <t xml:space="preserve">3.8826014995575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87288093566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94335603713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9441659450531</t>
+    <t xml:space="preserve">3.87288117408752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94335556030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94416570663452</t>
   </si>
   <si>
     <t xml:space="preserve">4.10374689102173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1750316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14749002456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9457859992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95064616203308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88422155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88584160804749</t>
+    <t xml:space="preserve">4.17503213882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14748954772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94578576087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9506459236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88422179222107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88584184646606</t>
   </si>
   <si>
     <t xml:space="preserve">3.83318781852722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88665175437927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93687534332275</t>
+    <t xml:space="preserve">3.88665151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93687510490417</t>
   </si>
   <si>
     <t xml:space="preserve">3.96927738189697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94821619987488</t>
+    <t xml:space="preserve">3.94821572303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.01707077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87774157524109</t>
+    <t xml:space="preserve">3.87774133682251</t>
   </si>
   <si>
     <t xml:space="preserve">3.99762940406799</t>
@@ -5111,13 +5111,13 @@
     <t xml:space="preserve">4.00573015213013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06486463546753</t>
+    <t xml:space="preserve">4.06486415863037</t>
   </si>
   <si>
     <t xml:space="preserve">4.0745849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0681037902832</t>
+    <t xml:space="preserve">4.06810426712036</t>
   </si>
   <si>
     <t xml:space="preserve">4.08592557907104</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">4.13614892959595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00897026062012</t>
+    <t xml:space="preserve">4.00896978378296</t>
   </si>
   <si>
     <t xml:space="preserve">3.98223829269409</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">3.98547863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.996009349823</t>
+    <t xml:space="preserve">3.99600958824158</t>
   </si>
   <si>
     <t xml:space="preserve">4.03408193588257</t>
@@ -5153,16 +5153,16 @@
     <t xml:space="preserve">4.19933366775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42614936828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47961330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40670824050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36782550811768</t>
+    <t xml:space="preserve">4.42614984512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47961282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40670776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36782503128052</t>
   </si>
   <si>
     <t xml:space="preserve">4.35324430465698</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">4.49581432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51363515853882</t>
+    <t xml:space="preserve">4.51363563537598</t>
   </si>
   <si>
     <t xml:space="preserve">4.50553464889526</t>
@@ -5186,19 +5186,19 @@
     <t xml:space="preserve">4.45531129837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47313213348389</t>
+    <t xml:space="preserve">4.47313261032104</t>
   </si>
   <si>
     <t xml:space="preserve">4.54765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57682037353516</t>
+    <t xml:space="preserve">4.576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">4.61570262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69994831085205</t>
+    <t xml:space="preserve">4.69994878768921</t>
   </si>
   <si>
     <t xml:space="preserve">4.81335639953613</t>
@@ -5213,31 +5213,31 @@
     <t xml:space="preserve">4.88302135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95916652679443</t>
+    <t xml:space="preserve">4.95916700363159</t>
   </si>
   <si>
     <t xml:space="preserve">5.01101016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96240663528442</t>
+    <t xml:space="preserve">4.96240711212158</t>
   </si>
   <si>
     <t xml:space="preserve">4.99642944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04989290237427</t>
+    <t xml:space="preserve">5.04989337921143</t>
   </si>
   <si>
     <t xml:space="preserve">5.15358066558838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12927865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0709547996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1017370223999</t>
+    <t xml:space="preserve">5.1292781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07095432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10173654556274</t>
   </si>
   <si>
     <t xml:space="preserve">5.05151319503784</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">4.98832845687866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92838430404663</t>
+    <t xml:space="preserve">4.92838478088379</t>
   </si>
   <si>
     <t xml:space="preserve">4.98670864105225</t>
@@ -5264,13 +5264,13 @@
     <t xml:space="preserve">5.14709997177124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17626142501831</t>
+    <t xml:space="preserve">5.17626190185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43019151687622</t>
+    <t xml:space="preserve">5.43019199371338</t>
   </si>
   <si>
     <t xml:space="preserve">5.42486476898193</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">5.51897811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47280979156494</t>
+    <t xml:space="preserve">5.47280931472778</t>
   </si>
   <si>
     <t xml:space="preserve">5.49056673049927</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">5.74449634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80131959915161</t>
+    <t xml:space="preserve">5.80132007598877</t>
   </si>
   <si>
     <t xml:space="preserve">5.96646308898926</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">5.75515079498291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75337553024292</t>
+    <t xml:space="preserve">5.75337505340576</t>
   </si>
   <si>
     <t xml:space="preserve">5.79421710968018</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">5.86347055435181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84571313858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7143087387085</t>
+    <t xml:space="preserve">5.84571361541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71430921554565</t>
   </si>
   <si>
     <t xml:space="preserve">5.66813945770264</t>
@@ -5354,7 +5354,7 @@
     <t xml:space="preserve">5.7622537612915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77645969390869</t>
+    <t xml:space="preserve">5.77646017074585</t>
   </si>
   <si>
     <t xml:space="preserve">5.7160849571228</t>
@@ -5378,34 +5378,34 @@
     <t xml:space="preserve">5.35383558273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40355539321899</t>
+    <t xml:space="preserve">5.40355587005615</t>
   </si>
   <si>
     <t xml:space="preserve">5.48346376419067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38402318954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5047721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43729496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4088830947876</t>
+    <t xml:space="preserve">5.38402271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50477266311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43729448318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40888261795044</t>
   </si>
   <si>
     <t xml:space="preserve">5.3502836227417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33962965011597</t>
+    <t xml:space="preserve">5.33962917327881</t>
   </si>
   <si>
     <t xml:space="preserve">5.51009941101074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57757806777954</t>
+    <t xml:space="preserve">5.57757759094238</t>
   </si>
   <si>
     <t xml:space="preserve">5.61309242248535</t>
@@ -5423,10 +5423,10 @@
     <t xml:space="preserve">5.52075386047363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53673553466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57935285568237</t>
+    <t xml:space="preserve">5.53673601150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57935333251953</t>
   </si>
   <si>
     <t xml:space="preserve">5.6113166809082</t>
@@ -5456,13 +5456,13 @@
     <t xml:space="preserve">5.19401931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08569955825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19046831130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11233520507812</t>
+    <t xml:space="preserve">5.08570003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19046783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11233568191528</t>
   </si>
   <si>
     <t xml:space="preserve">5.14785003662109</t>
@@ -5483,10 +5483,10 @@
     <t xml:space="preserve">5.33075094223022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24906730651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34318065643311</t>
+    <t xml:space="preserve">5.2490668296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34318113327026</t>
   </si>
   <si>
     <t xml:space="preserve">5.401780128479</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">5.45505237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46570634841919</t>
+    <t xml:space="preserve">5.46570682525635</t>
   </si>
   <si>
     <t xml:space="preserve">5.30056285858154</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">5.304114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33785390853882</t>
+    <t xml:space="preserve">5.33785343170166</t>
   </si>
   <si>
     <t xml:space="preserve">5.49411821365356</t>
@@ -5543,13 +5543,13 @@
     <t xml:space="preserve">5.38757371902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39822864532471</t>
+    <t xml:space="preserve">5.39822816848755</t>
   </si>
   <si>
     <t xml:space="preserve">5.57225036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53140878677368</t>
+    <t xml:space="preserve">5.53140830993652</t>
   </si>
   <si>
     <t xml:space="preserve">5.37869548797607</t>
@@ -5558,13 +5558,13 @@
     <t xml:space="preserve">5.14252281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28813314437866</t>
+    <t xml:space="preserve">5.2881326675415</t>
   </si>
   <si>
     <t xml:space="preserve">5.26327276229858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32719898223877</t>
+    <t xml:space="preserve">5.32719945907593</t>
   </si>
   <si>
     <t xml:space="preserve">5.46925783157349</t>
@@ -5585,25 +5585,25 @@
     <t xml:space="preserve">5.51187562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40000438690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40533113479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49766969680786</t>
+    <t xml:space="preserve">5.4000039100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4053316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4976692199707</t>
   </si>
   <si>
     <t xml:space="preserve">5.50122117996216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48879146575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64150381088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78001165390015</t>
+    <t xml:space="preserve">5.48879098892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64150428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78001117706299</t>
   </si>
   <si>
     <t xml:space="preserve">6.10674619674683</t>
@@ -5612,13 +5612,13 @@
     <t xml:space="preserve">5.96291160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06057739257812</t>
+    <t xml:space="preserve">6.06057691574097</t>
   </si>
   <si>
     <t xml:space="preserve">6.01973533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00197839736938</t>
+    <t xml:space="preserve">6.00197792053223</t>
   </si>
   <si>
     <t xml:space="preserve">6.1848783493042</t>
@@ -6270,6 +6270,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.3149995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0550003051758</t>
   </si>
 </sst>
 </file>
@@ -71426,7 +71429,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6527662037</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>5428329</v>
@@ -71447,6 +71450,32 @@
         <v>2057</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6525810185</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>7019119</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>11.8800001144409</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>12.0550003051758</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>2086</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="2087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="2088">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,124 +38,124 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2073802947998</t>
+    <t xml:space="preserve">6.20738124847412</t>
   </si>
   <si>
     <t xml:space="preserve">BAMI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25302457809448</t>
+    <t xml:space="preserve">6.25302362442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.98424005508423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89802646636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65459966659546</t>
+    <t xml:space="preserve">5.89802598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6545991897583</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89295434951782</t>
+    <t xml:space="preserve">5.65967082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89295387268066</t>
   </si>
   <si>
     <t xml:space="preserve">5.27424573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9420690536499</t>
+    <t xml:space="preserve">4.94206857681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.40450191497803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85839176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61496448516846</t>
+    <t xml:space="preserve">4.85839128494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6149640083313</t>
   </si>
   <si>
     <t xml:space="preserve">4.28785991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55410718917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95568346977234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32082414627075</t>
+    <t xml:space="preserve">4.55410766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95568370819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32082366943359</t>
   </si>
   <si>
     <t xml:space="preserve">4.57946443557739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50339317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05204010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11289739608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961268424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52715110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2228672504425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26851081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6437931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004109382629</t>
+    <t xml:space="preserve">4.50339365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0520396232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11289691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961220741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52715134620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22286748886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5804009437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26851058006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64379262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004180908203</t>
   </si>
   <si>
     <t xml:space="preserve">4.04443264007568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14332485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91511297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08246898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71986413002014</t>
+    <t xml:space="preserve">4.14332580566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91511249542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818536758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08246803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71986436843872</t>
   </si>
   <si>
     <t xml:space="preserve">3.646329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74775624275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84157776832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92018342018127</t>
+    <t xml:space="preserve">3.74775648117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84157752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92018365859985</t>
   </si>
   <si>
     <t xml:space="preserve">4.22700262069702</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">4.04950428009033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88468432426453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86693406105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76043462753296</t>
+    <t xml:space="preserve">3.88468480110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86693453788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7604353427887</t>
   </si>
   <si>
     <t xml:space="preserve">3.69957804679871</t>
@@ -179,124 +179,124 @@
     <t xml:space="preserve">4.03682613372803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9480767250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38768839836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47136616706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67675733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197154045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5144727230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38261675834656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27611780166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06565451622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365646362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812201499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49005150794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40586733818054</t>
+    <t xml:space="preserve">3.94807624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38768815994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4713659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67675685882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197130203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51447248458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38261651992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27611756324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06565427780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365622520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812177658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49005174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40586709976196</t>
   </si>
   <si>
     <t xml:space="preserve">2.22431135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46672320365906</t>
+    <t xml:space="preserve">2.46672368049622</t>
   </si>
   <si>
     <t xml:space="preserve">2.72079992294312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.700514793396</t>
+    <t xml:space="preserve">2.70051455497742</t>
   </si>
   <si>
     <t xml:space="preserve">2.91097736358643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02508354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16454648971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22690296173096</t>
+    <t xml:space="preserve">3.0250837802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16454672813416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22690272331238</t>
   </si>
   <si>
     <t xml:space="preserve">3.1385657787323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20092058181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11778044700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23469686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19052886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32823014259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20351958274841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96968626976013</t>
+    <t xml:space="preserve">3.14116311073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20092082023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508905410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777997016907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23469662666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19052863121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3282299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20351934432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96968579292297</t>
   </si>
   <si>
     <t xml:space="preserve">2.75663733482361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86835789680481</t>
+    <t xml:space="preserve">2.86835813522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84497427940369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59607148170471</t>
+    <t xml:space="preserve">2.84497475624084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59607124328613</t>
   </si>
   <si>
     <t xml:space="preserve">2.51500964164734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.286372423172</t>
+    <t xml:space="preserve">2.28637218475342</t>
   </si>
   <si>
     <t xml:space="preserve">2.32378602027893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32274627685547</t>
+    <t xml:space="preserve">2.32274651527405</t>
   </si>
   <si>
     <t xml:space="preserve">2.39237642288208</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">2.24584102630615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22089886665344</t>
+    <t xml:space="preserve">2.22089910507202</t>
   </si>
   <si>
     <t xml:space="preserve">2.24480175971985</t>
@@ -323,46 +323,46 @@
     <t xml:space="preserve">2.47343897819519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47032117843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48902821540833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49422407150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31131458282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16581797599792</t>
+    <t xml:space="preserve">2.4703209400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48902797698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49422383308411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31131434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16581749916077</t>
   </si>
   <si>
     <t xml:space="preserve">2.16685724258423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05461716651917</t>
+    <t xml:space="preserve">2.05461692810059</t>
   </si>
   <si>
     <t xml:space="preserve">2.15853548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2902045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22156858444214</t>
+    <t xml:space="preserve">2.29020476341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22156834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433287620544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04227423667908</t>
+    <t xml:space="preserve">2.0422739982605</t>
   </si>
   <si>
     <t xml:space="preserve">1.83636593818665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71590256690979</t>
+    <t xml:space="preserve">1.7159024477005</t>
   </si>
   <si>
     <t xml:space="preserve">1.83776676654816</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">2.07449102401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01846170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02546525001526</t>
+    <t xml:space="preserve">2.01846146583557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02546548843384</t>
   </si>
   <si>
     <t xml:space="preserve">1.993248462677</t>
@@ -383,31 +383,31 @@
     <t xml:space="preserve">2.12211608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6276558637619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52680325508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55481791496277</t>
+    <t xml:space="preserve">1.62765598297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5268030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55481767654419</t>
   </si>
   <si>
     <t xml:space="preserve">1.50439119338989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50158977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540230751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45676624774933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40073668956757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31459152698517</t>
+    <t xml:space="preserve">1.50158989429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540242671967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45676612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40073680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31459140777588</t>
   </si>
   <si>
     <t xml:space="preserve">1.28167414665222</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">1.666876912117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55621862411499</t>
+    <t xml:space="preserve">1.55621838569641</t>
   </si>
   <si>
     <t xml:space="preserve">1.64166367053986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66267454624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68788766860962</t>
+    <t xml:space="preserve">1.66267442703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6878879070282</t>
   </si>
   <si>
     <t xml:space="preserve">1.67528104782104</t>
@@ -452,67 +452,67 @@
     <t xml:space="preserve">1.7593252658844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70749819278717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76352751255035</t>
+    <t xml:space="preserve">1.70749807357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76352739334106</t>
   </si>
   <si>
     <t xml:space="preserve">1.5057920217514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49738764762878</t>
+    <t xml:space="preserve">1.49738752841949</t>
   </si>
   <si>
     <t xml:space="preserve">1.55201649665833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63045752048492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59964120388031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5926376581192</t>
+    <t xml:space="preserve">1.63045763969421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5996413230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59263753890991</t>
   </si>
   <si>
     <t xml:space="preserve">1.58143174648285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56882524490356</t>
+    <t xml:space="preserve">1.56882512569427</t>
   </si>
   <si>
     <t xml:space="preserve">1.53100526332855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52820372581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45396459102631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48758244514465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58003127574921</t>
+    <t xml:space="preserve">1.52820384502411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4539647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48758256435394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58003115653992</t>
   </si>
   <si>
     <t xml:space="preserve">1.53520739078522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51559722423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56742453575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56182169914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60384356975555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68088436126709</t>
+    <t xml:space="preserve">1.51559710502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56742417812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56182134151459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60384345054626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68088412284851</t>
   </si>
   <si>
     <t xml:space="preserve">1.63886189460754</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">1.65707147121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65847218036652</t>
+    <t xml:space="preserve">1.65847229957581</t>
   </si>
   <si>
     <t xml:space="preserve">1.64306426048279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59403860569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60944640636444</t>
+    <t xml:space="preserve">1.59403848648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60944652557373</t>
   </si>
   <si>
     <t xml:space="preserve">1.57582879066467</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">1.50018906593323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46657133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40003621578217</t>
+    <t xml:space="preserve">1.46657145023346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40003633499146</t>
   </si>
   <si>
     <t xml:space="preserve">1.45116341114044</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">1.47357511520386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4399573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40633952617645</t>
+    <t xml:space="preserve">1.43995749950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40633964538574</t>
   </si>
   <si>
     <t xml:space="preserve">1.37832498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3965345621109</t>
+    <t xml:space="preserve">1.39653444290161</t>
   </si>
   <si>
     <t xml:space="preserve">1.40774047374725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4679719209671</t>
+    <t xml:space="preserve">1.46797215938568</t>
   </si>
   <si>
     <t xml:space="preserve">1.48057878017426</t>
@@ -575,40 +575,40 @@
     <t xml:space="preserve">1.50299048423767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55061566829681</t>
+    <t xml:space="preserve">1.55061554908752</t>
   </si>
   <si>
     <t xml:space="preserve">1.65286934375763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78593921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79994678497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84617102146149</t>
+    <t xml:space="preserve">1.78593945503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79994666576385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84617078304291</t>
   </si>
   <si>
     <t xml:space="preserve">1.85317468643188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84196901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82235836982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737681388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86297988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041027545929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89379608631134</t>
+    <t xml:space="preserve">1.84196877479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82235825061798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86298000812531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89379596710205</t>
   </si>
   <si>
     <t xml:space="preserve">1.80835127830505</t>
@@ -617,52 +617,52 @@
     <t xml:space="preserve">1.67107892036438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61224794387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50999414920807</t>
+    <t xml:space="preserve">1.61224806308746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50999402999878</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543919563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60664510726929</t>
+    <t xml:space="preserve">1.60664522647858</t>
   </si>
   <si>
     <t xml:space="preserve">1.51279580593109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42735075950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35451245307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30408596992493</t>
+    <t xml:space="preserve">1.42735087871552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35451233386993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30408585071564</t>
   </si>
   <si>
     <t xml:space="preserve">1.31178998947144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32649767398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29988360404968</t>
+    <t xml:space="preserve">1.32649779319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29988372325897</t>
   </si>
   <si>
     <t xml:space="preserve">1.31739294528961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25085806846619</t>
+    <t xml:space="preserve">1.2508579492569</t>
   </si>
   <si>
     <t xml:space="preserve">1.30268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35871481895447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39233231544495</t>
+    <t xml:space="preserve">1.35871458053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39233243465424</t>
   </si>
   <si>
     <t xml:space="preserve">1.28867781162262</t>
@@ -674,61 +674,61 @@
     <t xml:space="preserve">1.49458622932434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64026272296906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56462287902832</t>
+    <t xml:space="preserve">1.64026284217834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56462299823761</t>
   </si>
   <si>
     <t xml:space="preserve">1.533806681633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67948341369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69769299030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65146863460541</t>
+    <t xml:space="preserve">1.679483294487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69769287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65146851539612</t>
   </si>
   <si>
     <t xml:space="preserve">1.72290623188019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77893567085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310114860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60524451732635</t>
+    <t xml:space="preserve">1.77893555164337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310102939606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60524439811707</t>
   </si>
   <si>
     <t xml:space="preserve">1.75092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87698698043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90500199794769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643971443176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0310685634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95122635364532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94982540607452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90640258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94702410697937</t>
+    <t xml:space="preserve">1.87698709964752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90500223636627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643959522247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03106832504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95122611522675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9498256444931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90640246868134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94702398777008</t>
   </si>
   <si>
     <t xml:space="preserve">1.89799821376801</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">1.97363817691803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02266383171082</t>
+    <t xml:space="preserve">2.02266407012939</t>
   </si>
   <si>
     <t xml:space="preserve">2.08849859237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00585508346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02126312255859</t>
+    <t xml:space="preserve">2.00585532188416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02126288414001</t>
   </si>
   <si>
     <t xml:space="preserve">1.86017835140228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8909946680069</t>
+    <t xml:space="preserve">1.89099478721619</t>
   </si>
   <si>
     <t xml:space="preserve">1.78033649921417</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">1.74251651763916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7383143901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64586555957794</t>
+    <t xml:space="preserve">1.73831450939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64586567878723</t>
   </si>
   <si>
     <t xml:space="preserve">1.75512325763702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84056806564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77753508090973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78173720836639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68368554115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62205302715302</t>
+    <t xml:space="preserve">1.84056794643402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77753484249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78173696994781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68368566036224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6220531463623</t>
   </si>
   <si>
     <t xml:space="preserve">1.51419639587402</t>
@@ -803,58 +803,58 @@
     <t xml:space="preserve">1.6500678062439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71870386600494</t>
+    <t xml:space="preserve">1.71870398521423</t>
   </si>
   <si>
     <t xml:space="preserve">1.71450161933899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68228471279144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6934906244278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69629216194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80975222587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81535482406616</t>
+    <t xml:space="preserve">1.68228495121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69349086284637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69629228115082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80975198745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81535470485687</t>
   </si>
   <si>
     <t xml:space="preserve">1.76072597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80695033073425</t>
+    <t xml:space="preserve">1.80695044994354</t>
   </si>
   <si>
     <t xml:space="preserve">1.86858296394348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85597622394562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91620790958405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90780353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91480720043182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88539159297943</t>
+    <t xml:space="preserve">1.8559764623642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91620802879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90780341625214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91480731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88539171218872</t>
   </si>
   <si>
     <t xml:space="preserve">1.88819313049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94562351703644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90360105037689</t>
+    <t xml:space="preserve">1.94562339782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90360128879547</t>
   </si>
   <si>
     <t xml:space="preserve">1.89939892292023</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">1.87978875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86718225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76212680339813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542848110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86157917976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86998343467712</t>
+    <t xml:space="preserve">1.86718201637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76212692260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95542871952057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86157929897308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86998355388641</t>
   </si>
   <si>
     <t xml:space="preserve">2.00445437431335</t>
@@ -884,31 +884,31 @@
     <t xml:space="preserve">2.04647636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91900944709778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87838804721832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98204231262207</t>
+    <t xml:space="preserve">1.9190092086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87838780879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98204243183136</t>
   </si>
   <si>
     <t xml:space="preserve">1.96383285522461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88259017467499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93021535873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97784042358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0941014289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17814540863037</t>
+    <t xml:space="preserve">1.8825900554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93021500110626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97784006595612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09410166740417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17814564704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.11371159553528</t>
@@ -920,55 +920,55 @@
     <t xml:space="preserve">1.99464917182922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00305366516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90220046043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99885129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95262694358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95402765274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93441736698151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920412540436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91060507297516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88679230213165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95823001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94422256946564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99184787273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06048369407654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207943916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10950946807861</t>
+    <t xml:space="preserve">2.00305342674255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90220057964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99885141849518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95262706279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95402777194977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9344174861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920424461365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91060495376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88679242134094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95823013782501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94422245025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99184775352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06048393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207920074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10950970649719</t>
   </si>
   <si>
     <t xml:space="preserve">2.14592862129211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0955023765564</t>
+    <t xml:space="preserve">2.09550213813782</t>
   </si>
   <si>
     <t xml:space="preserve">2.16974139213562</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">2.18795108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20616054534912</t>
+    <t xml:space="preserve">2.20616006851196</t>
   </si>
   <si>
     <t xml:space="preserve">2.20896172523499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19915699958801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19635534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14172673225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2033588886261</t>
+    <t xml:space="preserve">2.19915676116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19635510444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14172649383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20335865020752</t>
   </si>
   <si>
     <t xml:space="preserve">2.19215297698975</t>
@@ -1010,22 +1010,22 @@
     <t xml:space="preserve">2.16273760795593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20756077766418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997260093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28320074081421</t>
+    <t xml:space="preserve">2.20756101608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997283935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28320097923279</t>
   </si>
   <si>
     <t xml:space="preserve">2.34063100814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35884070396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33082604408264</t>
+    <t xml:space="preserve">2.35884046554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33082580566406</t>
   </si>
   <si>
     <t xml:space="preserve">2.30561256408691</t>
@@ -1034,85 +1034,85 @@
     <t xml:space="preserve">2.26499128341675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29720854759216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30981516838074</t>
+    <t xml:space="preserve">2.29720830917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30981492996216</t>
   </si>
   <si>
     <t xml:space="preserve">2.27339577674866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32242155075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2271716594696</t>
+    <t xml:space="preserve">2.32242131233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22717142105103</t>
   </si>
   <si>
     <t xml:space="preserve">2.26078915596008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22016763687134</t>
+    <t xml:space="preserve">2.22016787528992</t>
   </si>
   <si>
     <t xml:space="preserve">2.23277425765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26219010353088</t>
+    <t xml:space="preserve">2.2621898651123</t>
   </si>
   <si>
     <t xml:space="preserve">2.21036267280579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15993595123291</t>
+    <t xml:space="preserve">2.15993642807007</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10110521316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13052082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18935132026672</t>
+    <t xml:space="preserve">2.1011049747467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1305205821991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1893515586853</t>
   </si>
   <si>
     <t xml:space="preserve">2.25518608093262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29300594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30421209335327</t>
+    <t xml:space="preserve">2.29300618171692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30421185493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.30141043663025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31121563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33782982826233</t>
+    <t xml:space="preserve">2.3112154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33783006668091</t>
   </si>
   <si>
     <t xml:space="preserve">2.28180003166199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33642888069153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43448066711426</t>
+    <t xml:space="preserve">2.33642911911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43448042869568</t>
   </si>
   <si>
     <t xml:space="preserve">2.45409083366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4568920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43307971954346</t>
+    <t xml:space="preserve">2.45689225196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43307948112488</t>
   </si>
   <si>
     <t xml:space="preserve">2.43027806282043</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">2.24117875099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17954611778259</t>
+    <t xml:space="preserve">2.17954635620117</t>
   </si>
   <si>
     <t xml:space="preserve">2.13192129135132</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">2.19075226783752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15153169631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2019579410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18374848365784</t>
+    <t xml:space="preserve">2.151531457901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20195817947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18374872207642</t>
   </si>
   <si>
     <t xml:space="preserve">2.21456480026245</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">2.17674493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1683406829834</t>
+    <t xml:space="preserve">2.16834044456482</t>
   </si>
   <si>
     <t xml:space="preserve">2.09690260887146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1025059223175</t>
+    <t xml:space="preserve">2.10250568389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.13332223892212</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">2.10810875892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09129977226257</t>
+    <t xml:space="preserve">2.09130001068115</t>
   </si>
   <si>
     <t xml:space="preserve">2.04507565498352</t>
@@ -1184,67 +1184,67 @@
     <t xml:space="preserve">1.88959383964539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87558627128601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566004753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9792412519455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96943581104279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92321157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96523380279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181074619293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83496522903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76492822170258</t>
+    <t xml:space="preserve">1.8755863904953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566028594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97924077510834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96943593025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92321145534515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96523356437683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181098461151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83496499061584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.764927983284</t>
   </si>
   <si>
     <t xml:space="preserve">1.75232172012329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77193200588226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78313803672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8265608549118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86438071727753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177385807037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395399570465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86578142642975</t>
+    <t xml:space="preserve">1.77193188667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78313791751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82656073570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86438047885895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177421569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395387649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86578130722046</t>
   </si>
   <si>
     <t xml:space="preserve">1.84897255897522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8839910030365</t>
+    <t xml:space="preserve">1.88399076461792</t>
   </si>
   <si>
     <t xml:space="preserve">1.99745047092438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04787707328796</t>
+    <t xml:space="preserve">2.04787731170654</t>
   </si>
   <si>
     <t xml:space="preserve">2.04367470741272</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.11931467056274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15013098716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17114210128784</t>
+    <t xml:space="preserve">2.15013074874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17114186286926</t>
   </si>
   <si>
     <t xml:space="preserve">2.18725061416626</t>
@@ -1274,28 +1274,28 @@
     <t xml:space="preserve">2.14557838439941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10355639457703</t>
+    <t xml:space="preserve">2.10355663299561</t>
   </si>
   <si>
     <t xml:space="preserve">2.10320615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02826690673828</t>
+    <t xml:space="preserve">2.0282666683197</t>
   </si>
   <si>
     <t xml:space="preserve">2.04927778244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1536328792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16028642654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10600781440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03772187232971</t>
+    <t xml:space="preserve">2.15363264083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16028618812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10600757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03772163391113</t>
   </si>
   <si>
     <t xml:space="preserve">2.11721348762512</t>
@@ -1310,34 +1310,34 @@
     <t xml:space="preserve">2.12736892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15258193016052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18584966659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14207696914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19425415992737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1900520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2030086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17604446411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18865132331848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01005697250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08709788322449</t>
+    <t xml:space="preserve">2.15258240699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18584990501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14207673072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19425392150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19005179405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20300889015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17604470252991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1886510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01005721092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08709764480591</t>
   </si>
   <si>
     <t xml:space="preserve">2.12771916389465</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">2.0664370059967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11441230773926</t>
+    <t xml:space="preserve">2.11441206932068</t>
   </si>
   <si>
     <t xml:space="preserve">2.08394622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13822460174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12036514282227</t>
+    <t xml:space="preserve">2.13822436332703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12036490440369</t>
   </si>
   <si>
     <t xml:space="preserve">2.12071537971497</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">1.98274278640747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98729526996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293770313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96838545799255</t>
+    <t xml:space="preserve">1.98729515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293794155121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96838521957397</t>
   </si>
   <si>
     <t xml:space="preserve">1.94107115268707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03422021865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00620532035828</t>
+    <t xml:space="preserve">2.03421998023987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0062050819397</t>
   </si>
   <si>
     <t xml:space="preserve">2.01601028442383</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.14382767677307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12421751022339</t>
+    <t xml:space="preserve">2.12421727180481</t>
   </si>
   <si>
     <t xml:space="preserve">2.14662909507751</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">2.11791396141052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13857507705688</t>
+    <t xml:space="preserve">2.15888547897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13857483863831</t>
   </si>
   <si>
     <t xml:space="preserve">2.14487814903259</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">2.05453085899353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07028889656067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09970450401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86087894439697</t>
+    <t xml:space="preserve">2.07028913497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09970426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86087882518768</t>
   </si>
   <si>
     <t xml:space="preserve">1.87523627281189</t>
@@ -1445,85 +1445,85 @@
     <t xml:space="preserve">1.84442019462585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82165813446045</t>
+    <t xml:space="preserve">1.82165825366974</t>
   </si>
   <si>
     <t xml:space="preserve">1.57687950134277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47077357769012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51839852333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55446755886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6364107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59648978710175</t>
+    <t xml:space="preserve">1.47077345848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51839864253998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55446779727936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578684329987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641047477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59648966789246</t>
   </si>
   <si>
     <t xml:space="preserve">1.6801837682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61259806156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71170020103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69874322414398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7246572971344</t>
+    <t xml:space="preserve">1.61259818077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71170008182526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69874358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72465717792511</t>
   </si>
   <si>
     <t xml:space="preserve">1.69138967990875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67808270454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81990742683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7880402803421</t>
+    <t xml:space="preserve">1.67808258533478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81990718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804039955139</t>
   </si>
   <si>
     <t xml:space="preserve">1.84792172908783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78068673610687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73481225967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70364594459534</t>
+    <t xml:space="preserve">1.78068685531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73481273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70364606380463</t>
   </si>
   <si>
     <t xml:space="preserve">1.7740330696106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80589997768402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8258603811264</t>
+    <t xml:space="preserve">1.80589985847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82586026191711</t>
   </si>
   <si>
     <t xml:space="preserve">1.87173426151276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89274573326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87243497371674</t>
+    <t xml:space="preserve">1.89274549484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87243485450745</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823260784149</t>
@@ -1532,34 +1532,34 @@
     <t xml:space="preserve">1.85912799835205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83286416530609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81605494022369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85072314739227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601593971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85807764530182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.853875041008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76807975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7533723115921</t>
+    <t xml:space="preserve">1.8328640460968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81605517864227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85072338581085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601570129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85807752609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85387527942657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76807999610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75337219238281</t>
   </si>
   <si>
     <t xml:space="preserve">1.64901745319366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64621603488922</t>
+    <t xml:space="preserve">1.64621591567993</t>
   </si>
   <si>
     <t xml:space="preserve">1.66337490081787</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">1.65216898918152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61960172653198</t>
+    <t xml:space="preserve">1.61960184574127</t>
   </si>
   <si>
     <t xml:space="preserve">1.5709263086319</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">1.45501530170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44380939006805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43190312385559</t>
+    <t xml:space="preserve">1.44380962848663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43190324306488</t>
   </si>
   <si>
     <t xml:space="preserve">1.44415962696075</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">1.43120276927948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40178728103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35815441608429</t>
+    <t xml:space="preserve">1.40178716182709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.358154296875</t>
   </si>
   <si>
     <t xml:space="preserve">1.37132120132446</t>
@@ -1619,34 +1619,34 @@
     <t xml:space="preserve">1.50719273090363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49493634700775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54326164722443</t>
+    <t xml:space="preserve">1.49493646621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54326152801514</t>
   </si>
   <si>
     <t xml:space="preserve">1.53555774688721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55026566982269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61084723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61539947986603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61609995365143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62625539302826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62415421009064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61715066432953</t>
+    <t xml:space="preserve">1.55026543140411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61084711551666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6153998374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61610007286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62625527381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62415432929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61715054512024</t>
   </si>
   <si>
     <t xml:space="preserve">1.64446496963501</t>
@@ -1655,43 +1655,43 @@
     <t xml:space="preserve">1.64866733551025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48688209056854</t>
+    <t xml:space="preserve">1.48688197135925</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143716335297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37356233596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40283799171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41439402103424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38602888584137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29638183116913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31108951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30520641803741</t>
+    <t xml:space="preserve">1.37356245517731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40283787250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41439390182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38602912425995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29638195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31108963489532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3052065372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.31136965751648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3166925907135</t>
+    <t xml:space="preserve">1.31669247150421</t>
   </si>
   <si>
     <t xml:space="preserve">1.30758774280548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29960358142853</t>
+    <t xml:space="preserve">1.29960346221924</t>
   </si>
   <si>
     <t xml:space="preserve">1.22550463676453</t>
@@ -1703,34 +1703,34 @@
     <t xml:space="preserve">1.16905474662781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14692330360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09229457378387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134445667267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0897730588913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14440178871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16345202922821</t>
+    <t xml:space="preserve">1.14692318439484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09229445457458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134457588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08977317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14440190792084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16345191001892</t>
   </si>
   <si>
     <t xml:space="preserve">1.16331195831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19608902931213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23965203762054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2131781578064</t>
+    <t xml:space="preserve">1.19608914852142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23965191841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21317803859711</t>
   </si>
   <si>
     <t xml:space="preserve">1.22410380840302</t>
@@ -1739,16 +1739,16 @@
     <t xml:space="preserve">1.25477993488312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29217970371246</t>
+    <t xml:space="preserve">1.29217946529388</t>
   </si>
   <si>
     <t xml:space="preserve">1.28139400482178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27046811580658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26640605926514</t>
+    <t xml:space="preserve">1.27046835422516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26640617847443</t>
   </si>
   <si>
     <t xml:space="preserve">1.23923182487488</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">1.22606492042542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22256302833557</t>
+    <t xml:space="preserve">1.22256290912628</t>
   </si>
   <si>
     <t xml:space="preserve">1.26262414455414</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">1.28517603874207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32341611385345</t>
+    <t xml:space="preserve">1.32341599464417</t>
   </si>
   <si>
     <t xml:space="preserve">1.38770985603333</t>
@@ -1781,25 +1781,25 @@
     <t xml:space="preserve">1.47392523288727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47147417068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836187362671</t>
+    <t xml:space="preserve">1.47147405147552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836175441742</t>
   </si>
   <si>
     <t xml:space="preserve">1.53940963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54571306705475</t>
+    <t xml:space="preserve">1.54571294784546</t>
   </si>
   <si>
     <t xml:space="preserve">1.55796933174133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47917783260345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376979351044</t>
+    <t xml:space="preserve">1.47917795181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376991271973</t>
   </si>
   <si>
     <t xml:space="preserve">1.44801163673401</t>
@@ -1808,31 +1808,31 @@
     <t xml:space="preserve">1.48478090763092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49913847446442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47007322311401</t>
+    <t xml:space="preserve">1.49913859367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47007310390472</t>
   </si>
   <si>
     <t xml:space="preserve">1.44345927238464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40458881855011</t>
+    <t xml:space="preserve">1.4045889377594</t>
   </si>
   <si>
     <t xml:space="preserve">1.39401316642761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43155300617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39443325996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35605335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32285583019257</t>
+    <t xml:space="preserve">1.4315527677536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39443337917328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35605323314667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32285571098328</t>
   </si>
   <si>
     <t xml:space="preserve">1.39177203178406</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">1.37118124961853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43330371379852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44170844554901</t>
+    <t xml:space="preserve">1.4333039522171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44170832633972</t>
   </si>
   <si>
     <t xml:space="preserve">1.41509425640106</t>
@@ -1853,10 +1853,10 @@
     <t xml:space="preserve">1.42209792137146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42454922199249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38224697113037</t>
+    <t xml:space="preserve">1.42454934120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38224709033966</t>
   </si>
   <si>
     <t xml:space="preserve">1.34918963909149</t>
@@ -1865,49 +1865,49 @@
     <t xml:space="preserve">1.29344034194946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33168041706085</t>
+    <t xml:space="preserve">1.33168053627014</t>
   </si>
   <si>
     <t xml:space="preserve">1.32551717758179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30058419704437</t>
+    <t xml:space="preserve">1.30058395862579</t>
   </si>
   <si>
     <t xml:space="preserve">1.2948409318924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25996279716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26864731311798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24721586704254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845251560211</t>
+    <t xml:space="preserve">1.25996267795563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26864743232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24721610546112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845239639282</t>
   </si>
   <si>
     <t xml:space="preserve">1.26206386089325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24917709827423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24525499343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18474316596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15182602405548</t>
+    <t xml:space="preserve">1.24917697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24525511264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474304676056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1518257856369</t>
   </si>
   <si>
     <t xml:space="preserve">1.19342768192291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21892094612122</t>
+    <t xml:space="preserve">1.21892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">1.2291464805603</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">1.20897591114044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29400050640106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31851363182068</t>
+    <t xml:space="preserve">1.29400062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31851351261139</t>
   </si>
   <si>
     <t xml:space="preserve">1.31417119503021</t>
@@ -1937,25 +1937,25 @@
     <t xml:space="preserve">1.37706422805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969531536102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32775819301605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31473159790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36011552810669</t>
+    <t xml:space="preserve">1.35969519615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32775843143463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3147314786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3601154088974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40879094600677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47287452220917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49318528175354</t>
+    <t xml:space="preserve">1.47287464141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49318540096283</t>
   </si>
   <si>
     <t xml:space="preserve">1.46412014961243</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">1.41544449329376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37566363811493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3837878704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35675370693207</t>
+    <t xml:space="preserve">1.37566351890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38378775119781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35675358772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.34372675418854</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">1.4031879901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37720441818237</t>
+    <t xml:space="preserve">1.37720429897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
@@ -1994,22 +1994,22 @@
     <t xml:space="preserve">1.38112640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3210346698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30296516418457</t>
+    <t xml:space="preserve">1.32103490829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30296528339386</t>
   </si>
   <si>
     <t xml:space="preserve">1.28615653514862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32019436359406</t>
+    <t xml:space="preserve">1.32019424438477</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937804698944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28993833065033</t>
+    <t xml:space="preserve">1.28993856906891</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824862003326</t>
@@ -2021,25 +2021,25 @@
     <t xml:space="preserve">1.35941505432129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36606848239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3664186000824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36221647262573</t>
+    <t xml:space="preserve">1.36606860160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36641871929169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36221659183502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37587368488312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37727451324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37622392177582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43575501441956</t>
+    <t xml:space="preserve">1.37727439403534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37622380256653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43575513362885</t>
   </si>
   <si>
     <t xml:space="preserve">1.45956778526306</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">1.48828279972076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43855667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49178457260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48127925395966</t>
+    <t xml:space="preserve">1.43855655193329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49178469181061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48127901554108</t>
   </si>
   <si>
     <t xml:space="preserve">1.44205856323242</t>
@@ -2063,43 +2063,43 @@
     <t xml:space="preserve">1.38077628612518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532865047455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2722190618515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24595534801483</t>
+    <t xml:space="preserve">1.38532876968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27221918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24595546722412</t>
   </si>
   <si>
     <t xml:space="preserve">1.1997309923172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19062626361847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19798016548157</t>
+    <t xml:space="preserve">1.19062614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19798004627228</t>
   </si>
   <si>
     <t xml:space="preserve">1.24945724010468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20918595790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19587910175323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18082118034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15525782108307</t>
+    <t xml:space="preserve">1.20918607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19587898254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18082106113434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15525758266449</t>
   </si>
   <si>
     <t xml:space="preserve">1.17171633243561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14370167255402</t>
+    <t xml:space="preserve">1.14370155334473</t>
   </si>
   <si>
     <t xml:space="preserve">1.13914918899536</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">1.14930462837219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16261160373688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15350663661957</t>
+    <t xml:space="preserve">1.16261148452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15350651741028</t>
   </si>
   <si>
     <t xml:space="preserve">1.19377791881561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16716396808624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1416003704071</t>
+    <t xml:space="preserve">1.16716384887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14160048961639</t>
   </si>
   <si>
     <t xml:space="preserve">1.18432295322418</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">1.19482851028442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16821444034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101585865021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15700840950012</t>
+    <t xml:space="preserve">1.16821455955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1710159778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1570086479187</t>
   </si>
   <si>
     <t xml:space="preserve">1.20323288440704</t>
@@ -2144,52 +2144,52 @@
     <t xml:space="preserve">1.25365936756134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24560511112213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23790121078491</t>
+    <t xml:space="preserve">1.24560499191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23790109157562</t>
   </si>
   <si>
     <t xml:space="preserve">1.23474955558777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24875688552856</t>
+    <t xml:space="preserve">1.24875676631927</t>
   </si>
   <si>
     <t xml:space="preserve">1.26451516151428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24105274677277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23825132846832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31949400901794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36256670951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36992061138153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33525240421295</t>
+    <t xml:space="preserve">1.24105262756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23825120925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31949388980865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36256659030914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36992037296295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33525228500366</t>
   </si>
   <si>
     <t xml:space="preserve">1.32264566421509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33350157737732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33630275726318</t>
+    <t xml:space="preserve">1.33350133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33630287647247</t>
   </si>
   <si>
     <t xml:space="preserve">1.34295642375946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31214022636414</t>
+    <t xml:space="preserve">1.31214010715485</t>
   </si>
   <si>
     <t xml:space="preserve">1.34575772285461</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">1.31914377212524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22634494304657</t>
+    <t xml:space="preserve">1.22634506225586</t>
   </si>
   <si>
     <t xml:space="preserve">1.23159778118134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23720073699951</t>
+    <t xml:space="preserve">1.23720061779022</t>
   </si>
   <si>
     <t xml:space="preserve">1.23124754428864</t>
@@ -2216,34 +2216,34 @@
     <t xml:space="preserve">1.21163725852966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17241668701172</t>
+    <t xml:space="preserve">1.17241680622101</t>
   </si>
   <si>
     <t xml:space="preserve">1.18222177028656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18817484378815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18467307090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1860738992691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24210321903229</t>
+    <t xml:space="preserve">1.18817496299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1846729516983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18607378005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24210333824158</t>
   </si>
   <si>
     <t xml:space="preserve">1.26731646060944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15175592899323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13529706001282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18047094345093</t>
+    <t xml:space="preserve">1.15175580978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13529717922211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18047082424164</t>
   </si>
   <si>
     <t xml:space="preserve">1.1342465877533</t>
@@ -2261,25 +2261,25 @@
     <t xml:space="preserve">1.18992590904236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21583950519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21653985977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23404896259308</t>
+    <t xml:space="preserve">1.21583938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21653974056244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23404908180237</t>
   </si>
   <si>
     <t xml:space="preserve">1.27467048168182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28657674789429</t>
+    <t xml:space="preserve">1.286576628685</t>
   </si>
   <si>
     <t xml:space="preserve">1.32579731941223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28132367134094</t>
+    <t xml:space="preserve">1.28132390975952</t>
   </si>
   <si>
     <t xml:space="preserve">1.27186894416809</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">1.34050512313843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36816966533661</t>
+    <t xml:space="preserve">1.36816954612732</t>
   </si>
   <si>
     <t xml:space="preserve">1.35066032409668</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">1.29743242263794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31003892421722</t>
+    <t xml:space="preserve">1.31003904342651</t>
   </si>
   <si>
     <t xml:space="preserve">1.33980476856232</t>
@@ -2324,22 +2324,22 @@
     <t xml:space="preserve">1.33210062980652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29007863998413</t>
+    <t xml:space="preserve">1.29007852077484</t>
   </si>
   <si>
     <t xml:space="preserve">1.27081847190857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27537083625793</t>
+    <t xml:space="preserve">1.27537071704865</t>
   </si>
   <si>
     <t xml:space="preserve">1.28762722015381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31249022483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32789850234985</t>
+    <t xml:space="preserve">1.31249034404755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32789838314056</t>
   </si>
   <si>
     <t xml:space="preserve">1.28307485580444</t>
@@ -2348,19 +2348,19 @@
     <t xml:space="preserve">1.30968880653381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42384886741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50929379463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50859355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49598670005798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47707676887512</t>
+    <t xml:space="preserve">1.42384898662567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50929367542267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50859332084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47707688808441</t>
   </si>
   <si>
     <t xml:space="preserve">1.46867251396179</t>
@@ -2375,46 +2375,46 @@
     <t xml:space="preserve">1.47777724266052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49528646469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49388575553894</t>
+    <t xml:space="preserve">1.49528658390045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49388563632965</t>
   </si>
   <si>
     <t xml:space="preserve">1.44766128063202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42104744911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264283657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41754543781281</t>
+    <t xml:space="preserve">1.42104732990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264307498932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41754555702209</t>
   </si>
   <si>
     <t xml:space="preserve">1.41614496707916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44135808944702</t>
+    <t xml:space="preserve">1.44135820865631</t>
   </si>
   <si>
     <t xml:space="preserve">1.45536541938782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46517074108124</t>
+    <t xml:space="preserve">1.46517062187195</t>
   </si>
   <si>
     <t xml:space="preserve">1.43085253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4182460308075</t>
+    <t xml:space="preserve">1.41824615001678</t>
   </si>
   <si>
     <t xml:space="preserve">1.38813006877899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3741227388382</t>
+    <t xml:space="preserve">1.37412285804749</t>
   </si>
   <si>
     <t xml:space="preserve">1.41474401950836</t>
@@ -2426,70 +2426,70 @@
     <t xml:space="preserve">1.40984153747559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45326447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42034709453583</t>
+    <t xml:space="preserve">1.45326435565948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42034697532654</t>
   </si>
   <si>
     <t xml:space="preserve">1.36851978302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37797462940216</t>
+    <t xml:space="preserve">1.37797474861145</t>
   </si>
   <si>
     <t xml:space="preserve">1.38637924194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46166861057281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.425950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43435454368591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43365395069122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287723064423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36886978149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39373314380646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36431753635406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29568147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35836446285248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37307238578796</t>
+    <t xml:space="preserve">1.4616687297821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42594993114471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43435442447662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43365406990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287734985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36886990070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39373302459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36431765556335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29568159580231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35836458206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37307226657867</t>
   </si>
   <si>
     <t xml:space="preserve">1.46727180480957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5204998254776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54641318321228</t>
+    <t xml:space="preserve">1.52049958705902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54641342163086</t>
   </si>
   <si>
     <t xml:space="preserve">1.72010481357574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4462605714798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38848030567169</t>
+    <t xml:space="preserve">1.44626069068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3884801864624</t>
   </si>
   <si>
     <t xml:space="preserve">1.30128443241119</t>
@@ -2504,31 +2504,31 @@
     <t xml:space="preserve">1.05755627155304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905926525592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861103057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926937520503998</t>
+    <t xml:space="preserve">0.905926465988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861102998256683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926937639713287</t>
   </si>
   <si>
     <t xml:space="preserve">0.772156119346619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888417363166809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818030178546906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874409914016724</t>
+    <t xml:space="preserve">0.888417184352875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818030297756195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874409854412079</t>
   </si>
   <si>
     <t xml:space="preserve">0.874760091304779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.885966002941132</t>
+    <t xml:space="preserve">0.885965943336487</t>
   </si>
   <si>
     <t xml:space="preserve">0.877561628818512</t>
@@ -2540,67 +2540,67 @@
     <t xml:space="preserve">0.926587343215942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912930190563202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925886929035187</t>
+    <t xml:space="preserve">0.912930130958557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925887107849121</t>
   </si>
   <si>
     <t xml:space="preserve">0.880713224411011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84919661283493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840442180633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633193969727</t>
+    <t xml:space="preserve">0.849196672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840442061424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633253574371</t>
   </si>
   <si>
     <t xml:space="preserve">0.846044957637787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83098703622818</t>
+    <t xml:space="preserve">0.830986976623535</t>
   </si>
   <si>
     <t xml:space="preserve">0.851297795772552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829936563968658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853048801422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820131361484528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777408957481384</t>
+    <t xml:space="preserve">0.829936385154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853048622608185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820131421089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777408838272095</t>
   </si>
   <si>
     <t xml:space="preserve">0.778459489345551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778809547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753246247768402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751845479011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771805942058563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743791222572327</t>
+    <t xml:space="preserve">0.778809607028961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753246188163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751845419406891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771805882453918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743791282176971</t>
   </si>
   <si>
     <t xml:space="preserve">0.768304109573364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789665341377258</t>
+    <t xml:space="preserve">0.789665400981903</t>
   </si>
   <si>
     <t xml:space="preserve">0.809625864028931</t>
@@ -2609,10 +2609,10 @@
     <t xml:space="preserve">0.779860138893127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766553163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611084938049</t>
+    <t xml:space="preserve">0.766553103923798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611144542694</t>
   </si>
   <si>
     <t xml:space="preserve">0.776008248329163</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">0.803672730922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812077105045319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807874798774719</t>
+    <t xml:space="preserve">0.812077164649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807874917984009</t>
   </si>
   <si>
     <t xml:space="preserve">0.785463154315948</t>
@@ -2636,43 +2636,43 @@
     <t xml:space="preserve">0.781260907649994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819080829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759199261665344</t>
+    <t xml:space="preserve">0.819080770015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759199321269989</t>
   </si>
   <si>
     <t xml:space="preserve">0.756047666072845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730484127998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736087203025818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743441045284271</t>
+    <t xml:space="preserve">0.730484187602997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736087143421173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743440985679626</t>
   </si>
   <si>
     <t xml:space="preserve">0.779159724712372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815228760242462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805773913860321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858301401138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872308790683746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892969608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931840062141418</t>
+    <t xml:space="preserve">0.815228819847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805773794651031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85830146074295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872308850288391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892969727516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931840121746063</t>
   </si>
   <si>
     <t xml:space="preserve">0.994873344898224</t>
@@ -2681,13 +2681,13 @@
     <t xml:space="preserve">1.00853049755096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979115009307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966858565807343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891218781471252</t>
+    <t xml:space="preserve">0.979115068912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966858446598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891218841075897</t>
   </si>
   <si>
     <t xml:space="preserve">0.895070791244507</t>
@@ -2699,28 +2699,28 @@
     <t xml:space="preserve">0.967909097671509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964407205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94689804315567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936392486095428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938493490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965107679367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913980782032013</t>
+    <t xml:space="preserve">0.96440714597702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946897983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936392545700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938493549823761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965107500553131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913980722427368</t>
   </si>
   <si>
     <t xml:space="preserve">0.934641599655151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899623095989227</t>
+    <t xml:space="preserve">0.899623215198517</t>
   </si>
   <si>
     <t xml:space="preserve">0.953551650047302</t>
@@ -2732,43 +2732,43 @@
     <t xml:space="preserve">0.909078121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954602062702179</t>
+    <t xml:space="preserve">0.954602122306824</t>
   </si>
   <si>
     <t xml:space="preserve">0.943746387958527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983317196369171</t>
+    <t xml:space="preserve">0.983317255973816</t>
   </si>
   <si>
     <t xml:space="preserve">0.973161816596985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951450407505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916432082653046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933941304683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948298692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957403600215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973512053489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980865895748138</t>
+    <t xml:space="preserve">0.95145046710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916432023048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933941245079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948298752307892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957403659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97351199388504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980866014957428</t>
   </si>
   <si>
     <t xml:space="preserve">1.033043384552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03759574890137</t>
+    <t xml:space="preserve">1.03759586811066</t>
   </si>
   <si>
     <t xml:space="preserve">1.00012600421906</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">0.998725235462189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960905373096466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967208683490753</t>
+    <t xml:space="preserve">0.960905492305756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967208743095398</t>
   </si>
   <si>
     <t xml:space="preserve">0.944096565246582</t>
@@ -2795,37 +2795,37 @@
     <t xml:space="preserve">0.874059736728668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913280427455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927637934684753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907677412033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890868604183197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915381371974945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978764832019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971060872077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00572896003723</t>
+    <t xml:space="preserve">0.913280367851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927637875080109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907677352428436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890868484973907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91538143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978764772415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971060812473297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00572907924652</t>
   </si>
   <si>
     <t xml:space="preserve">0.997324585914612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98156613111496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00923085212708</t>
+    <t xml:space="preserve">0.981566250324249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00923073291779</t>
   </si>
   <si>
     <t xml:space="preserve">0.986819088459015</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">0.987519443035126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00712978839874</t>
+    <t xml:space="preserve">1.00712966918945</t>
   </si>
   <si>
     <t xml:space="preserve">0.996624231338501</t>
@@ -2843,28 +2843,28 @@
     <t xml:space="preserve">0.999775886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00467824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988920211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985768556594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970360398292542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958103954792023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994523167610168</t>
+    <t xml:space="preserve">1.00467848777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988920032978058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985768496990204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970360338687897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958104014396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994523048400879</t>
   </si>
   <si>
     <t xml:space="preserve">0.978414595127106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986118674278259</t>
+    <t xml:space="preserve">0.986118733882904</t>
   </si>
   <si>
     <t xml:space="preserve">1.03724551200867</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">1.01903593540192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01203227043152</t>
+    <t xml:space="preserve">1.0120325088501</t>
   </si>
   <si>
     <t xml:space="preserve">0.995573580265045</t>
@@ -2885,40 +2885,40 @@
     <t xml:space="preserve">0.973862171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916782200336456</t>
+    <t xml:space="preserve">0.916782259941101</t>
   </si>
   <si>
     <t xml:space="preserve">0.922735273838043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888067126274109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939544260501862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961605787277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972811758518219</t>
+    <t xml:space="preserve">0.888066947460175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939544081687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961605727672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972811698913574</t>
   </si>
   <si>
     <t xml:space="preserve">1.0540543794632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11113440990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09957849979401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16121077537537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.185023188591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16961514949799</t>
+    <t xml:space="preserve">1.11113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09957838058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16121065616608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18502330780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16961526870728</t>
   </si>
   <si>
     <t xml:space="preserve">1.15910959243774</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">1.12339091300964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12829339504242</t>
+    <t xml:space="preserve">1.12829327583313</t>
   </si>
   <si>
     <t xml:space="preserve">1.12794327735901</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">1.13564729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17066562175751</t>
+    <t xml:space="preserve">1.1706657409668</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545238018036</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">1.17591845989227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15560781955719</t>
+    <t xml:space="preserve">1.1556077003479</t>
   </si>
   <si>
     <t xml:space="preserve">1.13214552402496</t>
@@ -2972,22 +2972,22 @@
     <t xml:space="preserve">1.15000486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15210604667664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15490758419037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15455734729767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066291332245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2512081861496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25611054897308</t>
+    <t xml:space="preserve">1.15210592746735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15490746498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15455722808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25120806694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25611066818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502059936523</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32684791088104</t>
+    <t xml:space="preserve">1.32684779167175</t>
   </si>
   <si>
     <t xml:space="preserve">1.35801434516907</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">1.3233460187912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31879365444183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29603171348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31389105319977</t>
+    <t xml:space="preserve">1.31879353523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29603159427643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31389117240906</t>
   </si>
   <si>
     <t xml:space="preserve">1.30723762512207</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">1.29498112201691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28482580184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2802734375</t>
+    <t xml:space="preserve">1.28482568264008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28027331829071</t>
   </si>
   <si>
     <t xml:space="preserve">1.26941764354706</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">1.26661622524261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26416480541229</t>
+    <t xml:space="preserve">1.26416492462158</t>
   </si>
   <si>
     <t xml:space="preserve">1.26521551609039</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">1.26766669750214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26626598834991</t>
+    <t xml:space="preserve">1.26626586914062</t>
   </si>
   <si>
     <t xml:space="preserve">1.25856196880341</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">1.36957037448883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34505748748779</t>
+    <t xml:space="preserve">1.3450573682785</t>
   </si>
   <si>
     <t xml:space="preserve">1.34925973415375</t>
@@ -3077,19 +3077,19 @@
     <t xml:space="preserve">1.33455204963684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31529188156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31809329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31073939800262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3177433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28062355518341</t>
+    <t xml:space="preserve">1.31529176235199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31809318065643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31073951721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31774306297302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2806236743927</t>
   </si>
   <si>
     <t xml:space="preserve">1.24735617637634</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">1.26696634292603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25015759468079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29112923145294</t>
+    <t xml:space="preserve">1.2501574754715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29112911224365</t>
   </si>
   <si>
     <t xml:space="preserve">1.27432024478912</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">1.52190053462982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53240585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4980880022049</t>
+    <t xml:space="preserve">1.53240573406219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49808776378632</t>
   </si>
   <si>
     <t xml:space="preserve">1.48898315429688</t>
@@ -3134,28 +3134,28 @@
     <t xml:space="preserve">1.50088942050934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51629734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50789320468903</t>
+    <t xml:space="preserve">1.51629745960236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50789332389832</t>
   </si>
   <si>
     <t xml:space="preserve">1.5197993516922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5485143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54361188411713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60594463348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62695562839508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62065231800079</t>
+    <t xml:space="preserve">1.54851448535919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54361176490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60594475269318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62695574760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6206521987915</t>
   </si>
   <si>
     <t xml:space="preserve">1.59053647518158</t>
@@ -3164,58 +3164,58 @@
     <t xml:space="preserve">1.59193730354309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69909393787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70119476318359</t>
+    <t xml:space="preserve">1.69909381866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7011946439743</t>
   </si>
   <si>
     <t xml:space="preserve">1.72360646724701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71029949188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70469665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71099984645844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881982803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70539689064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68998908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65356981754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63536012172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64936769008636</t>
+    <t xml:space="preserve">1.71029937267303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70469653606415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71100008487701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881970882416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70539700984955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68998885154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65356957912445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63536024093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64936757087708</t>
   </si>
   <si>
     <t xml:space="preserve">1.63466000556946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62835645675659</t>
+    <t xml:space="preserve">1.62835669517517</t>
   </si>
   <si>
     <t xml:space="preserve">1.6654759645462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71505224704742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61877369880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59937429428101</t>
+    <t xml:space="preserve">1.71505236625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61877381801605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5993744134903</t>
   </si>
   <si>
     <t xml:space="preserve">1.6130256652832</t>
@@ -3224,31 +3224,31 @@
     <t xml:space="preserve">1.62308478355408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65613543987274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67337930202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71936333179474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71289670467377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70283794403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73445188999176</t>
+    <t xml:space="preserve">1.65613567829132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67337942123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71936321258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71289694309235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70283758640289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73445177078247</t>
   </si>
   <si>
     <t xml:space="preserve">1.71145975589752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74522912502289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893961429596</t>
+    <t xml:space="preserve">1.7452290058136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893949508667</t>
   </si>
   <si>
     <t xml:space="preserve">1.76822102069855</t>
@@ -3257,40 +3257,40 @@
     <t xml:space="preserve">1.81707882881165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83504128456116</t>
+    <t xml:space="preserve">1.83504116535187</t>
   </si>
   <si>
     <t xml:space="preserve">1.85587775707245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86449944972992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95934116840363</t>
+    <t xml:space="preserve">1.86449956893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126107215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95934128761292</t>
   </si>
   <si>
     <t xml:space="preserve">1.9729927778244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98377025127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94066047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96508944034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9974217414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02400588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03334641456604</t>
+    <t xml:space="preserve">1.98377013206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94066035747528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650890827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99742162227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02400612831116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03334665298462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08579683303833</t>
@@ -3299,22 +3299,22 @@
     <t xml:space="preserve">2.08795213699341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10375928878784</t>
+    <t xml:space="preserve">2.10375881195068</t>
   </si>
   <si>
     <t xml:space="preserve">2.12531399726868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13465476036072</t>
+    <t xml:space="preserve">2.13465452194214</t>
   </si>
   <si>
     <t xml:space="preserve">2.1540539264679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15189814567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18423080444336</t>
+    <t xml:space="preserve">2.15189838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18423104286194</t>
   </si>
   <si>
     <t xml:space="preserve">2.17201638221741</t>
@@ -3323,28 +3323,28 @@
     <t xml:space="preserve">2.17991971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17560887336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17632722854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16052055358887</t>
+    <t xml:space="preserve">2.17560911178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17632746696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16052031517029</t>
   </si>
   <si>
     <t xml:space="preserve">2.12818789482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08938908576965</t>
+    <t xml:space="preserve">2.08938932418823</t>
   </si>
   <si>
     <t xml:space="preserve">2.08076739311218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05346465110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08292293548584</t>
+    <t xml:space="preserve">2.05346441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08292269706726</t>
   </si>
   <si>
     <t xml:space="preserve">2.04771637916565</t>
@@ -3356,46 +3356,46 @@
     <t xml:space="preserve">2.01897644996643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04053139686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98305153846741</t>
+    <t xml:space="preserve">2.04053115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9830516576767</t>
   </si>
   <si>
     <t xml:space="preserve">1.96652626991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94928205013275</t>
+    <t xml:space="preserve">1.94928240776062</t>
   </si>
   <si>
     <t xml:space="preserve">1.95215630531311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90114295482635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83288598060608</t>
+    <t xml:space="preserve">1.90114283561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83288586139679</t>
   </si>
   <si>
     <t xml:space="preserve">1.93922340869904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93634939193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91766846179962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88821005821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749158382416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84653723239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78762054443359</t>
+    <t xml:space="preserve">1.93634951114655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91766822338104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88821017742157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749146461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84653735160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78762018680573</t>
   </si>
   <si>
     <t xml:space="preserve">1.8264194726944</t>
@@ -3404,34 +3404,34 @@
     <t xml:space="preserve">1.8752772808075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85803318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90258014202118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87743258476257</t>
+    <t xml:space="preserve">1.85803306102753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90258026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87743234634399</t>
   </si>
   <si>
     <t xml:space="preserve">1.89108407497406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82067120075226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81348633766174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82857477664948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96724486351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97371113300323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95718574523926</t>
+    <t xml:space="preserve">1.82067143917084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81348621845245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82857489585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96724474430084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97371125221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95718562602997</t>
   </si>
   <si>
     <t xml:space="preserve">2.03190946578979</t>
@@ -3443,43 +3443,43 @@
     <t xml:space="preserve">2.00388813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97155570983887</t>
+    <t xml:space="preserve">1.97155559062958</t>
   </si>
   <si>
     <t xml:space="preserve">1.93347537517548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90904664993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94209742546082</t>
+    <t xml:space="preserve">1.90904676914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94209730625153</t>
   </si>
   <si>
     <t xml:space="preserve">1.97802209854126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01107311248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957716464996</t>
+    <t xml:space="preserve">2.01107335090637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957728385925</t>
   </si>
   <si>
     <t xml:space="preserve">2.01753973960876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03262782096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03119111061096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99167370796204</t>
+    <t xml:space="preserve">2.03262805938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03119087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99167382717133</t>
   </si>
   <si>
     <t xml:space="preserve">2.01322841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945916652679</t>
+    <t xml:space="preserve">1.97945928573608</t>
   </si>
   <si>
     <t xml:space="preserve">1.95000076293945</t>
@@ -3491,49 +3491,49 @@
     <t xml:space="preserve">1.96868193149567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92269814014435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94712674617767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92916440963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83073031902313</t>
+    <t xml:space="preserve">1.92269825935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94712662696838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92916429042816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83073043823242</t>
   </si>
   <si>
     <t xml:space="preserve">1.84078919887543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92054224014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9758665561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9234162569046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94353449344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94425284862518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91838681697845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616167068481</t>
+    <t xml:space="preserve">1.92054259777069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97586667537689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92341649532318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94353425502777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94425296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91838693618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616143226624</t>
   </si>
   <si>
     <t xml:space="preserve">2.02831721305847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0218505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047251701355</t>
+    <t xml:space="preserve">2.02185034751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047227859497</t>
   </si>
   <si>
     <t xml:space="preserve">1.93994212150574</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">2.04340553283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10016655921936</t>
+    <t xml:space="preserve">2.10016679763794</t>
   </si>
   <si>
     <t xml:space="preserve">2.12387704849243</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12315845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1303436756134</t>
+    <t xml:space="preserve">2.1231586933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13034343719482</t>
   </si>
   <si>
     <t xml:space="preserve">2.14758729934692</t>
@@ -3572,10 +3572,10 @@
     <t xml:space="preserve">1.93563079833984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97083735466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00963592529297</t>
+    <t xml:space="preserve">1.97083711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00963616371155</t>
   </si>
   <si>
     <t xml:space="preserve">2.08364152908325</t>
@@ -3587,40 +3587,40 @@
     <t xml:space="preserve">2.00316953659058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98592567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9514377117157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042424201965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88318061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85372221469879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74594748020172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540600299835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77181363105774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80845677852631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8300119638443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88533616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92557168006897</t>
+    <t xml:space="preserve">1.98592579364777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143783092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042436122894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88318085670471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85372197628021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7459477186203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540612220764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77181375026703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80845701694489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83001184463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88533627986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92557191848755</t>
   </si>
   <si>
     <t xml:space="preserve">1.8896472454071</t>
@@ -3632,25 +3632,25 @@
     <t xml:space="preserve">1.86737358570099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89395809173584</t>
+    <t xml:space="preserve">1.89395797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.89036560058594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85444068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84797441959381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79767954349518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85659658908844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85875177383423</t>
+    <t xml:space="preserve">1.8544408082962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84797430038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7976793050766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85659635066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85875153541565</t>
   </si>
   <si>
     <t xml:space="preserve">1.84725570678711</t>
@@ -3659,10 +3659,10 @@
     <t xml:space="preserve">1.85515940189362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88605463504791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683210849762</t>
+    <t xml:space="preserve">1.8860547542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683198928833</t>
   </si>
   <si>
     <t xml:space="preserve">1.97874081134796</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">2.0010142326355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02544283866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06280469894409</t>
+    <t xml:space="preserve">2.0254430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06280493736267</t>
   </si>
   <si>
     <t xml:space="preserve">2.05849385261536</t>
@@ -3683,28 +3683,28 @@
     <t xml:space="preserve">2.06424164772034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0563383102417</t>
+    <t xml:space="preserve">2.05633854866028</t>
   </si>
   <si>
     <t xml:space="preserve">2.05274605751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02113223075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00460648536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01251006126404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99526607990265</t>
+    <t xml:space="preserve">2.02113199234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0046067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01251029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99526596069336</t>
   </si>
   <si>
     <t xml:space="preserve">1.89970588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87958812713623</t>
+    <t xml:space="preserve">1.87958824634552</t>
   </si>
   <si>
     <t xml:space="preserve">1.93131995201111</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">2.02041339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06855297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10447788238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07645606994629</t>
+    <t xml:space="preserve">2.06855273246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10447764396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07645654678345</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657406806946</t>
@@ -3737,28 +3737,28 @@
     <t xml:space="preserve">2.32505631446838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32361912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55138301849365</t>
+    <t xml:space="preserve">2.32361936569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55138278007507</t>
   </si>
   <si>
     <t xml:space="preserve">2.53485751152039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6081440448761</t>
+    <t xml:space="preserve">2.60814428329468</t>
   </si>
   <si>
     <t xml:space="preserve">2.55928635597229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.527672290802</t>
+    <t xml:space="preserve">2.52767252922058</t>
   </si>
   <si>
     <t xml:space="preserve">2.57509326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52336144447327</t>
+    <t xml:space="preserve">2.52336168289185</t>
   </si>
   <si>
     <t xml:space="preserve">2.51042866706848</t>
@@ -3770,13 +3770,13 @@
     <t xml:space="preserve">2.21584463119507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26398396492004</t>
+    <t xml:space="preserve">2.26398372650146</t>
   </si>
   <si>
     <t xml:space="preserve">2.21368908882141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496024131775</t>
+    <t xml:space="preserve">2.06496047973633</t>
   </si>
   <si>
     <t xml:space="preserve">1.91120195388794</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">1.66475749015808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74954009056091</t>
+    <t xml:space="preserve">1.7495402097702</t>
   </si>
   <si>
     <t xml:space="preserve">1.79480540752411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83575963973999</t>
+    <t xml:space="preserve">1.83575987815857</t>
   </si>
   <si>
     <t xml:space="preserve">1.90186154842377</t>
@@ -3806,31 +3806,31 @@
     <t xml:space="preserve">1.95862281322479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879969120026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95574879646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359337329865</t>
+    <t xml:space="preserve">1.98879945278168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95574867725372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359325408936</t>
   </si>
   <si>
     <t xml:space="preserve">2.06208634376526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93275701999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99095523357391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98664402961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784510135651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16626834869385</t>
+    <t xml:space="preserve">1.93275713920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99095511436462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98664426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94784533977509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16626858711243</t>
   </si>
   <si>
     <t xml:space="preserve">2.12459564208984</t>
@@ -3842,22 +3842,22 @@
     <t xml:space="preserve">2.19860076904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2307755947113</t>
+    <t xml:space="preserve">2.23077535629272</t>
   </si>
   <si>
     <t xml:space="preserve">2.33036375045776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35257935523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35181355476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36713480949402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32193684577942</t>
+    <t xml:space="preserve">2.35257983207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35181331634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36713457107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.321937084198</t>
   </si>
   <si>
     <t xml:space="preserve">2.35104727745056</t>
@@ -3866,43 +3866,43 @@
     <t xml:space="preserve">2.31887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27597332000732</t>
+    <t xml:space="preserve">2.27597308158875</t>
   </si>
   <si>
     <t xml:space="preserve">2.33572626113892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24839496612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23383951187134</t>
+    <t xml:space="preserve">2.24839472770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23383975028992</t>
   </si>
   <si>
     <t xml:space="preserve">2.21085786819458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13731575012207</t>
+    <t xml:space="preserve">2.13731598854065</t>
   </si>
   <si>
     <t xml:space="preserve">2.1587655544281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25069332122803</t>
+    <t xml:space="preserve">2.25069308280945</t>
   </si>
   <si>
     <t xml:space="preserve">2.23307371139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21545433998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28286790847778</t>
+    <t xml:space="preserve">2.2154541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2828676700592</t>
   </si>
   <si>
     <t xml:space="preserve">2.26448225975037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31351017951965</t>
+    <t xml:space="preserve">2.31351041793823</t>
   </si>
   <si>
     <t xml:space="preserve">2.38092374801636</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">2.45523190498352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47285151481628</t>
+    <t xml:space="preserve">2.47285127639771</t>
   </si>
   <si>
     <t xml:space="preserve">2.45293354988098</t>
@@ -3923,19 +3923,19 @@
     <t xml:space="preserve">2.4820442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48664045333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46365880966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47438359260559</t>
+    <t xml:space="preserve">2.4866406917572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46365857124329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47438335418701</t>
   </si>
   <si>
     <t xml:space="preserve">2.41309857368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43071794509888</t>
+    <t xml:space="preserve">2.43071818351746</t>
   </si>
   <si>
     <t xml:space="preserve">2.37709355354309</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.98793339729309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01168155670166</t>
+    <t xml:space="preserve">2.01168131828308</t>
   </si>
   <si>
     <t xml:space="preserve">2.08062720298767</t>
@@ -3956,16 +3956,16 @@
     <t xml:space="preserve">2.02623653411865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07832884788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16795825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19936680793762</t>
+    <t xml:space="preserve">2.07832908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1679584980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315622329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1993670463562</t>
   </si>
   <si>
     <t xml:space="preserve">2.13501763343811</t>
@@ -3986,22 +3986,22 @@
     <t xml:space="preserve">2.0315990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99406206607819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9029004573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86919379234314</t>
+    <t xml:space="preserve">1.99406182765961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90290057659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86919391155243</t>
   </si>
   <si>
     <t xml:space="preserve">1.98410308361053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98563516139984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91592347621918</t>
+    <t xml:space="preserve">1.98563539981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91592359542847</t>
   </si>
   <si>
     <t xml:space="preserve">1.8684276342392</t>
@@ -4016,37 +4016,37 @@
     <t xml:space="preserve">1.7742018699646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83012449741364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92435014247894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87915253639221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80331254005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79718387126923</t>
+    <t xml:space="preserve">1.83012437820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92435026168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87915241718292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80331230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79718363285065</t>
   </si>
   <si>
     <t xml:space="preserve">1.85387253761292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79641759395599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84544563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86306512355804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92894661426544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92052006721497</t>
+    <t xml:space="preserve">1.79641771316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84544575214386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86306524276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92894685268402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92051994800568</t>
   </si>
   <si>
     <t xml:space="preserve">1.96954798698425</t>
@@ -4058,25 +4058,25 @@
     <t xml:space="preserve">2.00095653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.034663438797</t>
+    <t xml:space="preserve">2.03466320037842</t>
   </si>
   <si>
     <t xml:space="preserve">1.98869955539703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97184610366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95652484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99176371097565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07220053672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06530594825745</t>
+    <t xml:space="preserve">1.9718462228775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9565247297287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99176383018494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07220029830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06530570983887</t>
   </si>
   <si>
     <t xml:space="preserve">2.02240633964539</t>
@@ -4088,37 +4088,37 @@
     <t xml:space="preserve">1.94273579120636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87762033939362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90826284885406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86076700687408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80944073200226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86612975597382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89830410480499</t>
+    <t xml:space="preserve">1.87762045860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90826308727264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86076688766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80944085121155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86612951755524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8983039855957</t>
   </si>
   <si>
     <t xml:space="preserve">1.90213441848755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8714919090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9687819480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90060222148895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90673077106476</t>
+    <t xml:space="preserve">1.87149202823639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96878206729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90060234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90673089027405</t>
   </si>
   <si>
     <t xml:space="preserve">1.89907014369965</t>
@@ -4139,25 +4139,25 @@
     <t xml:space="preserve">2.15033888816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1901741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21392202377319</t>
+    <t xml:space="preserve">2.19017386436462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21392226219177</t>
   </si>
   <si>
     <t xml:space="preserve">2.15799951553345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12965536117554</t>
+    <t xml:space="preserve">2.12965512275696</t>
   </si>
   <si>
     <t xml:space="preserve">2.09288430213928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07143425941467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02700281143188</t>
+    <t xml:space="preserve">2.07143449783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02700257301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.06377363204956</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">2.10820531845093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0300669670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04155802726746</t>
+    <t xml:space="preserve">2.03006720542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04155778884888</t>
   </si>
   <si>
     <t xml:space="preserve">2.07986092567444</t>
@@ -4190,7 +4190,7 @@
     <t xml:space="preserve">2.11893033981323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17485284805298</t>
+    <t xml:space="preserve">2.17485308647156</t>
   </si>
   <si>
     <t xml:space="preserve">2.17255449295044</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">2.17332077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1932384967804</t>
+    <t xml:space="preserve">2.19323825836182</t>
   </si>
   <si>
     <t xml:space="preserve">2.22617888450623</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">2.3173406124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34415292739868</t>
+    <t xml:space="preserve">2.3441526889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.34491896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37173128128052</t>
+    <t xml:space="preserve">2.37173104286194</t>
   </si>
   <si>
     <t xml:space="preserve">2.41922688484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220900535583</t>
+    <t xml:space="preserve">2.44220876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.37785959243774</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">2.35564374923706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36177229881287</t>
+    <t xml:space="preserve">2.36177253723145</t>
   </si>
   <si>
     <t xml:space="preserve">2.41769480705261</t>
@@ -4247,13 +4247,13 @@
     <t xml:space="preserve">2.45906233787537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48970484733582</t>
+    <t xml:space="preserve">2.48970460891724</t>
   </si>
   <si>
     <t xml:space="preserve">2.51268672943115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56171464920044</t>
+    <t xml:space="preserve">2.56171488761902</t>
   </si>
   <si>
     <t xml:space="preserve">2.58086633682251</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">2.53949904441833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55175590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52187967300415</t>
+    <t xml:space="preserve">2.55175614356995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52187943458557</t>
   </si>
   <si>
     <t xml:space="preserve">2.53796672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5372006893158</t>
+    <t xml:space="preserve">2.53720092773438</t>
   </si>
   <si>
     <t xml:space="preserve">2.4759156703949</t>
@@ -4283,10 +4283,10 @@
     <t xml:space="preserve">2.44450712203979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41386461257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40390586853027</t>
+    <t xml:space="preserve">2.41386437416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40390563011169</t>
   </si>
   <si>
     <t xml:space="preserve">2.41080021858215</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">2.40313982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4207592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51881527900696</t>
+    <t xml:space="preserve">2.42075896263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51881551742554</t>
   </si>
   <si>
     <t xml:space="preserve">2.50349378585815</t>
@@ -4316,22 +4316,22 @@
     <t xml:space="preserve">2.5686092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59465527534485</t>
+    <t xml:space="preserve">2.59465575218201</t>
   </si>
   <si>
     <t xml:space="preserve">2.5793342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58393049240112</t>
+    <t xml:space="preserve">2.5839307308197</t>
   </si>
   <si>
     <t xml:space="preserve">2.56477904319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57703590393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55405426025391</t>
+    <t xml:space="preserve">2.57703614234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55405402183533</t>
   </si>
   <si>
     <t xml:space="preserve">2.62376570701599</t>
@@ -4340,19 +4340,19 @@
     <t xml:space="preserve">2.67739009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77774405479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78923559188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77468037605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75859308242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72335386276245</t>
+    <t xml:space="preserve">2.77774453163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78923535346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77468013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7585928440094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72335410118103</t>
   </si>
   <si>
     <t xml:space="preserve">2.74020743370056</t>
@@ -4364,25 +4364,25 @@
     <t xml:space="preserve">2.94014978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9217643737793</t>
+    <t xml:space="preserve">2.92176413536072</t>
   </si>
   <si>
     <t xml:space="preserve">2.93172311782837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89725041389465</t>
+    <t xml:space="preserve">2.89725017547607</t>
   </si>
   <si>
     <t xml:space="preserve">2.92636060714722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95700311660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99453997612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00756359100342</t>
+    <t xml:space="preserve">2.95700335502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99454021453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00756335258484</t>
   </si>
   <si>
     <t xml:space="preserve">3.07038044929504</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">3.09106421470642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07957315444946</t>
+    <t xml:space="preserve">3.07957339286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.16154193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19831299781799</t>
+    <t xml:space="preserve">3.19831323623657</t>
   </si>
   <si>
     <t xml:space="preserve">3.14315676689148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22895550727844</t>
+    <t xml:space="preserve">3.22895574569702</t>
   </si>
   <si>
     <t xml:space="preserve">3.29024076461792</t>
@@ -4412,16 +4412,16 @@
     <t xml:space="preserve">3.22435927391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22052907943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18145966529846</t>
+    <t xml:space="preserve">3.22052884101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18145990371704</t>
   </si>
   <si>
     <t xml:space="preserve">3.18682217597961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16767048835754</t>
+    <t xml:space="preserve">3.16767072677612</t>
   </si>
   <si>
     <t xml:space="preserve">3.14085817337036</t>
@@ -4430,22 +4430,22 @@
     <t xml:space="preserve">3.19448280334473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22282719612122</t>
+    <t xml:space="preserve">3.22282695770264</t>
   </si>
   <si>
     <t xml:space="preserve">3.10255527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04280233383179</t>
+    <t xml:space="preserve">3.04280209541321</t>
   </si>
   <si>
     <t xml:space="preserve">3.11634421348572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05812382698059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12860155105591</t>
+    <t xml:space="preserve">3.05812358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12860131263733</t>
   </si>
   <si>
     <t xml:space="preserve">3.16001009941101</t>
@@ -4457,28 +4457,28 @@
     <t xml:space="preserve">3.11711025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15081715583801</t>
+    <t xml:space="preserve">3.15081691741943</t>
   </si>
   <si>
     <t xml:space="preserve">3.22359323501587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18912053108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23355221748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17150068283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0772750377655</t>
+    <t xml:space="preserve">3.18912029266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23355197906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17150044441223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07727527618408</t>
   </si>
   <si>
     <t xml:space="preserve">2.82830452919006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8811628818512</t>
+    <t xml:space="preserve">2.88116312026978</t>
   </si>
   <si>
     <t xml:space="preserve">2.67585825920105</t>
@@ -4487,19 +4487,19 @@
     <t xml:space="preserve">2.71186304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70573472976685</t>
+    <t xml:space="preserve">2.70573449134827</t>
   </si>
   <si>
     <t xml:space="preserve">2.80991911888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039708137512</t>
+    <t xml:space="preserve">2.88039684295654</t>
   </si>
   <si>
     <t xml:space="preserve">2.80379056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71952366828918</t>
+    <t xml:space="preserve">2.71952342987061</t>
   </si>
   <si>
     <t xml:space="preserve">2.60691261291504</t>
@@ -4508,10 +4508,10 @@
     <t xml:space="preserve">2.63372468948364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65900468826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75782656669617</t>
+    <t xml:space="preserve">2.65900444984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75782680511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.79996037483215</t>
@@ -4526,10 +4526,10 @@
     <t xml:space="preserve">2.75476264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82370853424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83979558944702</t>
+    <t xml:space="preserve">2.82370829582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8397958278656</t>
   </si>
   <si>
     <t xml:space="preserve">2.84132790565491</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">2.93019104003906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01828837394714</t>
+    <t xml:space="preserve">3.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">3.08033919334412</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">3.03609204292297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11466765403748</t>
+    <t xml:space="preserve">3.11466789245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.98505854606628</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">3.0109806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04905295372009</t>
+    <t xml:space="preserve">3.04905319213867</t>
   </si>
   <si>
     <t xml:space="preserve">3.27910900115967</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.1567907333374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11061716079712</t>
+    <t xml:space="preserve">3.1106173992157</t>
   </si>
   <si>
     <t xml:space="preserve">3.16003108024597</t>
@@ -4598,52 +4598,52 @@
     <t xml:space="preserve">3.1738018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16732144355774</t>
+    <t xml:space="preserve">3.16732168197632</t>
   </si>
   <si>
     <t xml:space="preserve">3.13572931289673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17947196960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15841054916382</t>
+    <t xml:space="preserve">3.17947220802307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1584107875824</t>
   </si>
   <si>
     <t xml:space="preserve">3.21754479408264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21025443077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631539344788</t>
+    <t xml:space="preserve">3.21025419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631563186646</t>
   </si>
   <si>
     <t xml:space="preserve">3.09684634208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09441614151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05472350120544</t>
+    <t xml:space="preserve">3.09441637992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05472373962402</t>
   </si>
   <si>
     <t xml:space="preserve">3.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631872177124</t>
+    <t xml:space="preserve">2.96318697929382</t>
   </si>
   <si>
     <t xml:space="preserve">3.03771233558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11142778396606</t>
+    <t xml:space="preserve">3.11142754554749</t>
   </si>
   <si>
     <t xml:space="preserve">3.06768441200256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1130473613739</t>
+    <t xml:space="preserve">3.11304759979248</t>
   </si>
   <si>
     <t xml:space="preserve">3.09765625</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">3.07983541488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10251665115356</t>
+    <t xml:space="preserve">3.10251688957214</t>
   </si>
   <si>
     <t xml:space="preserve">3.09198594093323</t>
@@ -4664,22 +4664,22 @@
     <t xml:space="preserve">3.14626002311707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16165113449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26776814460754</t>
+    <t xml:space="preserve">3.16165137290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508690834045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26776838302612</t>
   </si>
   <si>
     <t xml:space="preserve">3.24751687049866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31556153297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29612016677856</t>
+    <t xml:space="preserve">3.31556177139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29612040519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.22888588905334</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">3.22240519523621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27586913108826</t>
+    <t xml:space="preserve">3.27586936950684</t>
   </si>
   <si>
     <t xml:space="preserve">3.31070137023926</t>
@@ -4700,10 +4700,10 @@
     <t xml:space="preserve">3.44274067878723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50673484802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44031071662903</t>
+    <t xml:space="preserve">3.50673508644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44031047821045</t>
   </si>
   <si>
     <t xml:space="preserve">3.44355058670044</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">3.34553384780884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42005920410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46947240829468</t>
+    <t xml:space="preserve">3.42005896568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46947264671326</t>
   </si>
   <si>
     <t xml:space="preserve">3.4978244304657</t>
@@ -4724,64 +4724,64 @@
     <t xml:space="preserve">3.57883048057556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61852288246155</t>
+    <t xml:space="preserve">3.61852312088013</t>
   </si>
   <si>
     <t xml:space="preserve">3.54075741767883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61042237281799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62500333786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58531069755554</t>
+    <t xml:space="preserve">3.61042189598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62500309944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58531045913696</t>
   </si>
   <si>
     <t xml:space="preserve">3.60475182533264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59422135353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59503149986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59341096878052</t>
+    <t xml:space="preserve">3.5942211151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59503173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5934112071991</t>
   </si>
   <si>
     <t xml:space="preserve">3.63391423225403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63634419441223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63553380966187</t>
+    <t xml:space="preserve">3.63634443283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63553428649902</t>
   </si>
   <si>
     <t xml:space="preserve">3.68413734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64606475830078</t>
+    <t xml:space="preserve">3.64606499671936</t>
   </si>
   <si>
     <t xml:space="preserve">3.58774065971375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50511527061462</t>
+    <t xml:space="preserve">3.50511503219604</t>
   </si>
   <si>
     <t xml:space="preserve">3.48162317276001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56505942344666</t>
+    <t xml:space="preserve">3.56505918502808</t>
   </si>
   <si>
     <t xml:space="preserve">3.2410364151001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4176287651062</t>
+    <t xml:space="preserve">3.41762900352478</t>
   </si>
   <si>
     <t xml:space="preserve">3.51807570457458</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">3.54480767250061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52293610572815</t>
+    <t xml:space="preserve">3.52293634414673</t>
   </si>
   <si>
     <t xml:space="preserve">3.55857872962952</t>
@@ -4811,10 +4811,10 @@
     <t xml:space="preserve">3.51564574241638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56667900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57639980316162</t>
+    <t xml:space="preserve">3.56667923927307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5764000415802</t>
   </si>
   <si>
     <t xml:space="preserve">3.60556244850159</t>
@@ -4823,22 +4823,22 @@
     <t xml:space="preserve">3.57720994949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54318785667419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49944472312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46380233764648</t>
+    <t xml:space="preserve">3.54318761825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49944496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46380186080933</t>
   </si>
   <si>
     <t xml:space="preserve">3.35687470436096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28882956504822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32123184204102</t>
+    <t xml:space="preserve">3.28883004188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32123208045959</t>
   </si>
   <si>
     <t xml:space="preserve">3.3852264881134</t>
@@ -4847,28 +4847,28 @@
     <t xml:space="preserve">3.45651173591614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48324346542358</t>
+    <t xml:space="preserve">3.48324370384216</t>
   </si>
   <si>
     <t xml:space="preserve">3.53994727134705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62743353843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70843958854675</t>
+    <t xml:space="preserve">3.62743377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70843911170959</t>
   </si>
   <si>
     <t xml:space="preserve">3.77243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75218224525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82670712471008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75137257575989</t>
+    <t xml:space="preserve">3.7521824836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82670736312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75137233734131</t>
   </si>
   <si>
     <t xml:space="preserve">3.6898078918457</t>
@@ -4880,7 +4880,7 @@
     <t xml:space="preserve">3.67360663414001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68251752853394</t>
+    <t xml:space="preserve">3.68251729011536</t>
   </si>
   <si>
     <t xml:space="preserve">3.66712641716003</t>
@@ -4904,37 +4904,37 @@
     <t xml:space="preserve">3.84776902198792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84938883781433</t>
+    <t xml:space="preserve">3.84938907623291</t>
   </si>
   <si>
     <t xml:space="preserve">3.926344871521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97818779945374</t>
+    <t xml:space="preserve">3.97818756103516</t>
   </si>
   <si>
     <t xml:space="preserve">3.97089743614197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.800785779953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83966827392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76838326454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402612686157</t>
+    <t xml:space="preserve">3.80078530311584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8396680355072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76838350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402588844299</t>
   </si>
   <si>
     <t xml:space="preserve">3.80726599693298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79349541664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82589745521545</t>
+    <t xml:space="preserve">3.79349517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82589721679688</t>
   </si>
   <si>
     <t xml:space="preserve">3.90690302848816</t>
@@ -4943,25 +4943,25 @@
     <t xml:space="preserve">3.95793676376343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94173574447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94659638404846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97251772880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94011521339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99114942550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10698699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11994791030884</t>
+    <t xml:space="preserve">3.9417359828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94659614562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97251749038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94011545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99114871025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10698747634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.119948387146</t>
   </si>
   <si>
     <t xml:space="preserve">4.30950117111206</t>
@@ -4979,16 +4979,16 @@
     <t xml:space="preserve">4.27223873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31274175643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13938903808594</t>
+    <t xml:space="preserve">4.31274127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1393895149231</t>
   </si>
   <si>
     <t xml:space="preserve">4.11346769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13128852844238</t>
+    <t xml:space="preserve">4.13128900527954</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642860412598</t>
@@ -5000,22 +5000,22 @@
     <t xml:space="preserve">4.09888648986816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12318801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11022758483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18637323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14100933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15721035003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99357914924622</t>
+    <t xml:space="preserve">4.12318849563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11022710800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18637275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14100980758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15721082687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99357891082764</t>
   </si>
   <si>
     <t xml:space="preserve">4.04137229919434</t>
@@ -5024,25 +5024,25 @@
     <t xml:space="preserve">4.07296466827393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05676364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90204238891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83480858802795</t>
+    <t xml:space="preserve">4.05676317214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90204286575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83480834960938</t>
   </si>
   <si>
     <t xml:space="preserve">3.87045049667358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89961266517639</t>
+    <t xml:space="preserve">3.89961290359497</t>
   </si>
   <si>
     <t xml:space="preserve">3.84290862083435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81617712974548</t>
+    <t xml:space="preserve">3.81617665290833</t>
   </si>
   <si>
     <t xml:space="preserve">3.86072969436646</t>
@@ -5051,55 +5051,55 @@
     <t xml:space="preserve">3.8826014995575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87288117408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94335556030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94416570663452</t>
+    <t xml:space="preserve">3.87288093566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94335603713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9441659450531</t>
   </si>
   <si>
     <t xml:space="preserve">4.10374689102173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17503213882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14748954772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94578576087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9506459236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88422179222107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88584184646606</t>
+    <t xml:space="preserve">4.1750316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14749002456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9457859992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95064616203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88422155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88584160804749</t>
   </si>
   <si>
     <t xml:space="preserve">3.83318781852722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88665151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93687510490417</t>
+    <t xml:space="preserve">3.88665175437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93687534332275</t>
   </si>
   <si>
     <t xml:space="preserve">3.96927738189697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94821572303772</t>
+    <t xml:space="preserve">3.94821619987488</t>
   </si>
   <si>
     <t xml:space="preserve">4.01707077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87774133682251</t>
+    <t xml:space="preserve">3.87774157524109</t>
   </si>
   <si>
     <t xml:space="preserve">3.99762940406799</t>
@@ -5111,13 +5111,13 @@
     <t xml:space="preserve">4.00573015213013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06486415863037</t>
+    <t xml:space="preserve">4.06486463546753</t>
   </si>
   <si>
     <t xml:space="preserve">4.0745849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06810426712036</t>
+    <t xml:space="preserve">4.0681037902832</t>
   </si>
   <si>
     <t xml:space="preserve">4.08592557907104</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">4.13614892959595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00896978378296</t>
+    <t xml:space="preserve">4.00897026062012</t>
   </si>
   <si>
     <t xml:space="preserve">3.98223829269409</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">3.98547863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99600958824158</t>
+    <t xml:space="preserve">3.996009349823</t>
   </si>
   <si>
     <t xml:space="preserve">4.03408193588257</t>
@@ -5153,16 +5153,16 @@
     <t xml:space="preserve">4.19933366775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42614984512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47961282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40670776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36782503128052</t>
+    <t xml:space="preserve">4.42614936828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47961330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40670824050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36782550811768</t>
   </si>
   <si>
     <t xml:space="preserve">4.35324430465698</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">4.49581432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51363563537598</t>
+    <t xml:space="preserve">4.51363515853882</t>
   </si>
   <si>
     <t xml:space="preserve">4.50553464889526</t>
@@ -5186,19 +5186,19 @@
     <t xml:space="preserve">4.45531129837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47313261032104</t>
+    <t xml:space="preserve">4.47313213348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.54765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.576819896698</t>
+    <t xml:space="preserve">4.57682037353516</t>
   </si>
   <si>
     <t xml:space="preserve">4.61570262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69994878768921</t>
+    <t xml:space="preserve">4.69994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">4.81335639953613</t>
@@ -5213,31 +5213,31 @@
     <t xml:space="preserve">4.88302135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95916700363159</t>
+    <t xml:space="preserve">4.95916652679443</t>
   </si>
   <si>
     <t xml:space="preserve">5.01101016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96240711212158</t>
+    <t xml:space="preserve">4.96240663528442</t>
   </si>
   <si>
     <t xml:space="preserve">4.99642944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04989337921143</t>
+    <t xml:space="preserve">5.04989290237427</t>
   </si>
   <si>
     <t xml:space="preserve">5.15358066558838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1292781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07095432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10173654556274</t>
+    <t xml:space="preserve">5.12927865982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0709547996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1017370223999</t>
   </si>
   <si>
     <t xml:space="preserve">5.05151319503784</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">4.98832845687866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92838478088379</t>
+    <t xml:space="preserve">4.92838430404663</t>
   </si>
   <si>
     <t xml:space="preserve">4.98670864105225</t>
@@ -5264,13 +5264,13 @@
     <t xml:space="preserve">5.14709997177124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17626190185547</t>
+    <t xml:space="preserve">5.17626142501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43019199371338</t>
+    <t xml:space="preserve">5.43019151687622</t>
   </si>
   <si>
     <t xml:space="preserve">5.42486476898193</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">5.51897811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47280931472778</t>
+    <t xml:space="preserve">5.47280979156494</t>
   </si>
   <si>
     <t xml:space="preserve">5.49056673049927</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">5.74449634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80132007598877</t>
+    <t xml:space="preserve">5.80131959915161</t>
   </si>
   <si>
     <t xml:space="preserve">5.96646308898926</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">5.75515079498291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75337505340576</t>
+    <t xml:space="preserve">5.75337553024292</t>
   </si>
   <si>
     <t xml:space="preserve">5.79421710968018</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">5.86347055435181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84571361541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71430921554565</t>
+    <t xml:space="preserve">5.84571313858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7143087387085</t>
   </si>
   <si>
     <t xml:space="preserve">5.66813945770264</t>
@@ -5354,7 +5354,7 @@
     <t xml:space="preserve">5.7622537612915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77646017074585</t>
+    <t xml:space="preserve">5.77645969390869</t>
   </si>
   <si>
     <t xml:space="preserve">5.7160849571228</t>
@@ -5378,34 +5378,34 @@
     <t xml:space="preserve">5.35383558273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40355587005615</t>
+    <t xml:space="preserve">5.40355539321899</t>
   </si>
   <si>
     <t xml:space="preserve">5.48346376419067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38402271270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50477266311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43729448318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40888261795044</t>
+    <t xml:space="preserve">5.38402318954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5047721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43729496002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4088830947876</t>
   </si>
   <si>
     <t xml:space="preserve">5.3502836227417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33962917327881</t>
+    <t xml:space="preserve">5.33962965011597</t>
   </si>
   <si>
     <t xml:space="preserve">5.51009941101074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57757759094238</t>
+    <t xml:space="preserve">5.57757806777954</t>
   </si>
   <si>
     <t xml:space="preserve">5.61309242248535</t>
@@ -5423,10 +5423,10 @@
     <t xml:space="preserve">5.52075386047363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53673601150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57935333251953</t>
+    <t xml:space="preserve">5.53673553466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57935285568237</t>
   </si>
   <si>
     <t xml:space="preserve">5.6113166809082</t>
@@ -5456,13 +5456,13 @@
     <t xml:space="preserve">5.19401931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08570003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19046783447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11233568191528</t>
+    <t xml:space="preserve">5.08569955825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19046831130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11233520507812</t>
   </si>
   <si>
     <t xml:space="preserve">5.14785003662109</t>
@@ -5483,10 +5483,10 @@
     <t xml:space="preserve">5.33075094223022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2490668296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34318113327026</t>
+    <t xml:space="preserve">5.24906730651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34318065643311</t>
   </si>
   <si>
     <t xml:space="preserve">5.401780128479</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">5.45505237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46570682525635</t>
+    <t xml:space="preserve">5.46570634841919</t>
   </si>
   <si>
     <t xml:space="preserve">5.30056285858154</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">5.304114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33785343170166</t>
+    <t xml:space="preserve">5.33785390853882</t>
   </si>
   <si>
     <t xml:space="preserve">5.49411821365356</t>
@@ -5543,13 +5543,13 @@
     <t xml:space="preserve">5.38757371902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39822816848755</t>
+    <t xml:space="preserve">5.39822864532471</t>
   </si>
   <si>
     <t xml:space="preserve">5.57225036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53140830993652</t>
+    <t xml:space="preserve">5.53140878677368</t>
   </si>
   <si>
     <t xml:space="preserve">5.37869548797607</t>
@@ -5558,13 +5558,13 @@
     <t xml:space="preserve">5.14252281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2881326675415</t>
+    <t xml:space="preserve">5.28813314437866</t>
   </si>
   <si>
     <t xml:space="preserve">5.26327276229858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32719945907593</t>
+    <t xml:space="preserve">5.32719898223877</t>
   </si>
   <si>
     <t xml:space="preserve">5.46925783157349</t>
@@ -5585,25 +5585,25 @@
     <t xml:space="preserve">5.51187562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4000039100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4053316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4976692199707</t>
+    <t xml:space="preserve">5.40000438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40533113479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49766969680786</t>
   </si>
   <si>
     <t xml:space="preserve">5.50122117996216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48879098892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64150428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78001117706299</t>
+    <t xml:space="preserve">5.48879146575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64150381088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78001165390015</t>
   </si>
   <si>
     <t xml:space="preserve">6.10674619674683</t>
@@ -5612,13 +5612,13 @@
     <t xml:space="preserve">5.96291160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06057691574097</t>
+    <t xml:space="preserve">6.06057739257812</t>
   </si>
   <si>
     <t xml:space="preserve">6.01973533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00197792053223</t>
+    <t xml:space="preserve">6.00197839736938</t>
   </si>
   <si>
     <t xml:space="preserve">6.1848783493042</t>
@@ -6273,6 +6273,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.0550003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1599998474121</t>
   </si>
 </sst>
 </file>
@@ -71455,7 +71458,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6525810185</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>7019119</v>
@@ -71476,6 +71479,32 @@
         <v>2086</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6500694444</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>5160843</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>12.1899995803833</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>11.9899997711182</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>12.1199998855591</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2087</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="2088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="2089">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,100 +38,100 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20738124847412</t>
+    <t xml:space="preserve">6.20737981796265</t>
   </si>
   <si>
     <t xml:space="preserve">BAMI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25302362442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98424005508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89802598953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6545991897583</t>
+    <t xml:space="preserve">6.25302267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98423957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89802551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65459871292114</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967082977295</t>
+    <t xml:space="preserve">5.65967130661011</t>
   </si>
   <si>
     <t xml:space="preserve">5.89295387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27424573898315</t>
+    <t xml:space="preserve">5.27424478530884</t>
   </si>
   <si>
     <t xml:space="preserve">4.94206857681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40450191497803</t>
+    <t xml:space="preserve">4.40450143814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.85839128494263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6149640083313</t>
+    <t xml:space="preserve">4.61496448516846</t>
   </si>
   <si>
     <t xml:space="preserve">4.28785991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55410766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911050796509</t>
+    <t xml:space="preserve">4.55410718917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">3.95568370819092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32082366943359</t>
+    <t xml:space="preserve">4.32082462310791</t>
   </si>
   <si>
     <t xml:space="preserve">4.57946443557739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50339365005493</t>
+    <t xml:space="preserve">4.50339412689209</t>
   </si>
   <si>
     <t xml:space="preserve">4.0520396232605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11289691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961220741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52715134620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22286748886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5804009437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26851058006287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64379262924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004180908203</t>
+    <t xml:space="preserve">4.11289739608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8796124458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52715158462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22286796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040118217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2685112953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64379286766052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004157066345</t>
   </si>
   <si>
     <t xml:space="preserve">4.04443264007568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14332580566406</t>
+    <t xml:space="preserve">4.14332485198975</t>
   </si>
   <si>
     <t xml:space="preserve">3.91511249542236</t>
@@ -143,61 +143,61 @@
     <t xml:space="preserve">4.08246803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71986436843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.646329164505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74775648117065</t>
+    <t xml:space="preserve">3.71986389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64632868766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74775671958923</t>
   </si>
   <si>
     <t xml:space="preserve">3.84157752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92018365859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22700262069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04950428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88468480110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86693453788757</t>
+    <t xml:space="preserve">3.92018389701843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22700214385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04950475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88468432426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86693429946899</t>
   </si>
   <si>
     <t xml:space="preserve">3.7604353427887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69957804679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03682613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38768815994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4713659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67675685882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51447248458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38261651992798</t>
+    <t xml:space="preserve">3.69957852363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03682565689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807696342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38768792152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47136616706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67675709724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197177886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5144727230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38261699676514</t>
   </si>
   <si>
     <t xml:space="preserve">3.27611756324768</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.06565427780151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365622520447</t>
+    <t xml:space="preserve">2.92365598678589</t>
   </si>
   <si>
     <t xml:space="preserve">2.70812177658081</t>
@@ -215,28 +215,28 @@
     <t xml:space="preserve">2.49005174636841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40586709976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22431135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46672368049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72079992294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70051455497742</t>
+    <t xml:space="preserve">2.40586686134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2243115901947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72080016136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.700514793396</t>
   </si>
   <si>
     <t xml:space="preserve">2.91097736358643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0250837802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16454672813416</t>
+    <t xml:space="preserve">3.02508354187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16454648971558</t>
   </si>
   <si>
     <t xml:space="preserve">3.22690272331238</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.14116311073303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20092082023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508905410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11777997016907</t>
+    <t xml:space="preserve">3.20092105865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508929252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11778020858765</t>
   </si>
   <si>
     <t xml:space="preserve">3.23469662666321</t>
@@ -263,34 +263,34 @@
     <t xml:space="preserve">3.19052863121033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3282299041748</t>
+    <t xml:space="preserve">3.32823038101196</t>
   </si>
   <si>
     <t xml:space="preserve">3.20351934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96968579292297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75663733482361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86835813522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72805738449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84497475624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59607124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51500964164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28637218475342</t>
+    <t xml:space="preserve">2.96968603134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75663709640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86835789680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72805762290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84497451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59607148170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51500940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28637194633484</t>
   </si>
   <si>
     <t xml:space="preserve">2.32378602027893</t>
@@ -305,25 +305,25 @@
     <t xml:space="preserve">2.23544836044312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24584102630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22089910507202</t>
+    <t xml:space="preserve">2.24584150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22089886665344</t>
   </si>
   <si>
     <t xml:space="preserve">2.24480175971985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24999785423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2749400138855</t>
+    <t xml:space="preserve">2.24999761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27493977546692</t>
   </si>
   <si>
     <t xml:space="preserve">2.47343897819519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4703209400177</t>
+    <t xml:space="preserve">2.47032117843628</t>
   </si>
   <si>
     <t xml:space="preserve">2.48902797698975</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.49422383308411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31131434440613</t>
+    <t xml:space="preserve">2.31131458282471</t>
   </si>
   <si>
     <t xml:space="preserve">2.16581749916077</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">2.15853548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29020476341248</t>
+    <t xml:space="preserve">2.2902045249939</t>
   </si>
   <si>
     <t xml:space="preserve">2.22156834602356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15433287620544</t>
+    <t xml:space="preserve">2.15433311462402</t>
   </si>
   <si>
     <t xml:space="preserve">2.0422739982605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83636593818665</t>
+    <t xml:space="preserve">1.83636558055878</t>
   </si>
   <si>
     <t xml:space="preserve">1.7159024477005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83776676654816</t>
+    <t xml:space="preserve">1.83776664733887</t>
   </si>
   <si>
     <t xml:space="preserve">2.07449102401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01846146583557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02546548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.993248462677</t>
+    <t xml:space="preserve">2.01846170425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02546525001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99324822425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.12211608886719</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">1.55481767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439119338989</t>
+    <t xml:space="preserve">1.50439131259918</t>
   </si>
   <si>
     <t xml:space="preserve">1.50158989429474</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">1.52540242671967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45676612854004</t>
+    <t xml:space="preserve">1.45676624774933</t>
   </si>
   <si>
     <t xml:space="preserve">1.40073680877686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31459140777588</t>
+    <t xml:space="preserve">1.31459152698517</t>
   </si>
   <si>
     <t xml:space="preserve">1.28167414665222</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57022595405579</t>
+    <t xml:space="preserve">1.57022607326508</t>
   </si>
   <si>
     <t xml:space="preserve">1.666876912117</t>
@@ -425,37 +425,37 @@
     <t xml:space="preserve">1.55621838569641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64166367053986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66267442703247</t>
+    <t xml:space="preserve">1.64166378974915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66267454624176</t>
   </si>
   <si>
     <t xml:space="preserve">1.6878879070282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67528104782104</t>
+    <t xml:space="preserve">1.67528116703033</t>
   </si>
   <si>
     <t xml:space="preserve">1.66407513618469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72990989685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70329582691193</t>
+    <t xml:space="preserve">1.72991001605988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70329570770264</t>
   </si>
   <si>
     <t xml:space="preserve">1.71730327606201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7593252658844</t>
+    <t xml:space="preserve">1.75932538509369</t>
   </si>
   <si>
     <t xml:space="preserve">1.70749807357788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76352739334106</t>
+    <t xml:space="preserve">1.76352751255035</t>
   </si>
   <si>
     <t xml:space="preserve">1.5057920217514</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">1.49738752841949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55201649665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63045763969421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5996413230896</t>
+    <t xml:space="preserve">1.55201637744904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63045752048492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59964144229889</t>
   </si>
   <si>
     <t xml:space="preserve">1.59263753890991</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">1.58143174648285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56882512569427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53100526332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52820384502411</t>
+    <t xml:space="preserve">1.56882524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53100538253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52820372581482</t>
   </si>
   <si>
     <t xml:space="preserve">1.4539647102356</t>
@@ -494,37 +494,37 @@
     <t xml:space="preserve">1.48758256435394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58003115653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53520739078522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559710502625</t>
+    <t xml:space="preserve">1.58003091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53520750999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559722423553</t>
   </si>
   <si>
     <t xml:space="preserve">1.56742417812347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56182134151459</t>
+    <t xml:space="preserve">1.56182146072388</t>
   </si>
   <si>
     <t xml:space="preserve">1.60384345054626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68088412284851</t>
+    <t xml:space="preserve">1.6808842420578</t>
   </si>
   <si>
     <t xml:space="preserve">1.63886189460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65707147121429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65847229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64306426048279</t>
+    <t xml:space="preserve">1.65707159042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6584724187851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6430641412735</t>
   </si>
   <si>
     <t xml:space="preserve">1.59403848648071</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">1.60944652557373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57582879066467</t>
+    <t xml:space="preserve">1.57582890987396</t>
   </si>
   <si>
     <t xml:space="preserve">1.50018906593323</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">1.39653444290161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40774047374725</t>
+    <t xml:space="preserve">1.40774035453796</t>
   </si>
   <si>
     <t xml:space="preserve">1.46797215938568</t>
@@ -572,25 +572,25 @@
     <t xml:space="preserve">1.48057878017426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50299048423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55061554908752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65286934375763</t>
+    <t xml:space="preserve">1.50299036502838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55061542987823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65286946296692</t>
   </si>
   <si>
     <t xml:space="preserve">1.78593945503235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79994666576385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84617078304291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317468643188</t>
+    <t xml:space="preserve">1.79994654655457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8461709022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8531745672226</t>
   </si>
   <si>
     <t xml:space="preserve">1.84196877479553</t>
@@ -599,25 +599,25 @@
     <t xml:space="preserve">1.82235825061798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85737705230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86298000812531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041015625</t>
+    <t xml:space="preserve">1.85737669467926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86297988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041003704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379596710205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80835127830505</t>
+    <t xml:space="preserve">1.80835115909576</t>
   </si>
   <si>
     <t xml:space="preserve">1.67107892036438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61224806308746</t>
+    <t xml:space="preserve">1.61224830150604</t>
   </si>
   <si>
     <t xml:space="preserve">1.50999402999878</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">1.59543919563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60664522647858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51279580593109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42735087871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35451233386993</t>
+    <t xml:space="preserve">1.60664510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5127956867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42735075950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35451245307922</t>
   </si>
   <si>
     <t xml:space="preserve">1.30408585071564</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">1.2508579492569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30268526077271</t>
+    <t xml:space="preserve">1.30268514156342</t>
   </si>
   <si>
     <t xml:space="preserve">1.35871458053589</t>
@@ -668,19 +668,19 @@
     <t xml:space="preserve">1.28867781162262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40493893623352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49458622932434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64026284217834</t>
+    <t xml:space="preserve">1.40493905544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49458611011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64026272296906</t>
   </si>
   <si>
     <t xml:space="preserve">1.56462299823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.533806681633</t>
+    <t xml:space="preserve">1.53380680084229</t>
   </si>
   <si>
     <t xml:space="preserve">1.679483294487</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">1.69769287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65146851539612</t>
+    <t xml:space="preserve">1.65146863460541</t>
   </si>
   <si>
     <t xml:space="preserve">1.72290623188019</t>
@@ -698,70 +698,70 @@
     <t xml:space="preserve">1.77893555164337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71310102939606</t>
+    <t xml:space="preserve">1.71310126781464</t>
   </si>
   <si>
     <t xml:space="preserve">1.60524439811707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75092101097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87698709964752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90500223636627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643959522247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03106832504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95122611522675</t>
+    <t xml:space="preserve">1.75092089176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87698721885681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90500211715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643947601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03106808662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95122623443604</t>
   </si>
   <si>
     <t xml:space="preserve">1.9498256444931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90640246868134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94702398777008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89799821376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9414210319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93581819534302</t>
+    <t xml:space="preserve">1.90640258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94702386856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89799833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142115116119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93581795692444</t>
   </si>
   <si>
     <t xml:space="preserve">2.01706099510193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97363817691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02266407012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849859237671</t>
+    <t xml:space="preserve">1.97363781929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02266383171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849835395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.00585532188416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02126288414001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86017835140228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89099478721619</t>
+    <t xml:space="preserve">2.02126312255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86017823219299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8909946680069</t>
   </si>
   <si>
     <t xml:space="preserve">1.78033649921417</t>
@@ -770,79 +770,79 @@
     <t xml:space="preserve">1.67388045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74251651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73831450939178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64586567878723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75512325763702</t>
+    <t xml:space="preserve">1.74251639842987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73831462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64586555957794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75512313842773</t>
   </si>
   <si>
     <t xml:space="preserve">1.84056794643402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77753484249115</t>
+    <t xml:space="preserve">1.77753496170044</t>
   </si>
   <si>
     <t xml:space="preserve">1.78173696994781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68368566036224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6220531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51419639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500678062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71870398521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71450161933899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68228495121002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69349086284637</t>
+    <t xml:space="preserve">1.68368554115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62205302715302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51419651508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006768703461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71870386600494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71450185775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68228483200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69349074363708</t>
   </si>
   <si>
     <t xml:space="preserve">1.69629228115082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80975198745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81535470485687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80695044994354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86858296394348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8559764623642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91620802879333</t>
+    <t xml:space="preserve">1.80975210666656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81535506248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072609424591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80695033073425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86858308315277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85597634315491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91620767116547</t>
   </si>
   <si>
     <t xml:space="preserve">1.90780341625214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91480731964111</t>
+    <t xml:space="preserve">1.91480708122253</t>
   </si>
   <si>
     <t xml:space="preserve">1.88539171218872</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">1.88819313049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94562339782715</t>
+    <t xml:space="preserve">1.94562351703644</t>
   </si>
   <si>
     <t xml:space="preserve">1.90360128879547</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">1.89939892292023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87978875637054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86718201637268</t>
+    <t xml:space="preserve">1.87978863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86718225479126</t>
   </si>
   <si>
     <t xml:space="preserve">1.76212692260742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95542871952057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86157929897308</t>
+    <t xml:space="preserve">1.95542860031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8615790605545</t>
   </si>
   <si>
     <t xml:space="preserve">1.86998355388641</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">1.87838780879974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98204243183136</t>
+    <t xml:space="preserve">1.98204267024994</t>
   </si>
   <si>
     <t xml:space="preserve">1.96383285522461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8825900554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93021500110626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97784006595612</t>
+    <t xml:space="preserve">1.88259017467499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93021512031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97784042358398</t>
   </si>
   <si>
     <t xml:space="preserve">2.09410166740417</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">2.11371159553528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12491774559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99464917182922</t>
+    <t xml:space="preserve">2.12491750717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99464893341064</t>
   </si>
   <si>
     <t xml:space="preserve">2.00305342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90220057964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99885141849518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95262706279755</t>
+    <t xml:space="preserve">1.90220069885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99885153770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95262718200684</t>
   </si>
   <si>
     <t xml:space="preserve">1.95402777194977</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">1.9344174861908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90920424461365</t>
+    <t xml:space="preserve">1.90920400619507</t>
   </si>
   <si>
     <t xml:space="preserve">1.91060495376587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88679242134094</t>
+    <t xml:space="preserve">1.88679230213165</t>
   </si>
   <si>
     <t xml:space="preserve">1.95823013782501</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">1.94422245025635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99184775352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06048393249512</t>
+    <t xml:space="preserve">1.99184763431549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06048369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.05207920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10950970649719</t>
+    <t xml:space="preserve">2.10950946807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.14592862129211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09550213813782</t>
+    <t xml:space="preserve">2.0955023765564</t>
   </si>
   <si>
     <t xml:space="preserve">2.16974139213562</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">2.18795108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20616006851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20896172523499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19915676116943</t>
+    <t xml:space="preserve">2.20616054534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20896196365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19915699958801</t>
   </si>
   <si>
     <t xml:space="preserve">2.19635510444641</t>
@@ -998,22 +998,22 @@
     <t xml:space="preserve">2.20335865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19215297698975</t>
+    <t xml:space="preserve">2.19215321540833</t>
   </si>
   <si>
     <t xml:space="preserve">2.15573382377625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16413831710815</t>
+    <t xml:space="preserve">2.16413807868958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16273760795593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20756101608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997283935547</t>
+    <t xml:space="preserve">2.20756125450134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997307777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.28320097923279</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">2.34063100814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35884046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33082580566406</t>
+    <t xml:space="preserve">2.35884070396423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33082604408264</t>
   </si>
   <si>
     <t xml:space="preserve">2.30561256408691</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">2.29720830917358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30981492996216</t>
+    <t xml:space="preserve">2.30981516838074</t>
   </si>
   <si>
     <t xml:space="preserve">2.27339577674866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32242131233215</t>
+    <t xml:space="preserve">2.32242155075073</t>
   </si>
   <si>
     <t xml:space="preserve">2.22717142105103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26078915596008</t>
+    <t xml:space="preserve">2.2607889175415</t>
   </si>
   <si>
     <t xml:space="preserve">2.22016787528992</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">2.23277425765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2621898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21036267280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15993642807007</t>
+    <t xml:space="preserve">2.26218962669373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21036243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15993595123291</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713453292847</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">2.1305205821991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1893515586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25518608093262</t>
+    <t xml:space="preserve">2.18935132026672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2551863193512</t>
   </si>
   <si>
     <t xml:space="preserve">2.29300618171692</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">2.3112154006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33783006668091</t>
+    <t xml:space="preserve">2.33782982826233</t>
   </si>
   <si>
     <t xml:space="preserve">2.28180003166199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33642911911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43448042869568</t>
+    <t xml:space="preserve">2.33642888069153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4344801902771</t>
   </si>
   <si>
     <t xml:space="preserve">2.45409083366394</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.43307948112488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43027806282043</t>
+    <t xml:space="preserve">2.43027830123901</t>
   </si>
   <si>
     <t xml:space="preserve">2.24117875099182</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">2.17954635620117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13192129135132</t>
+    <t xml:space="preserve">2.13192105293274</t>
   </si>
   <si>
     <t xml:space="preserve">2.23417520523071</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">2.19075226783752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.151531457901</t>
+    <t xml:space="preserve">2.15153169631958</t>
   </si>
   <si>
     <t xml:space="preserve">2.20195817947388</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">2.18374872207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21456480026245</t>
+    <t xml:space="preserve">2.21456456184387</t>
   </si>
   <si>
     <t xml:space="preserve">2.17674493789673</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">2.16834044456482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09690260887146</t>
+    <t xml:space="preserve">2.09690284729004</t>
   </si>
   <si>
     <t xml:space="preserve">2.10250568389893</t>
@@ -1163,85 +1163,85 @@
     <t xml:space="preserve">2.13332223892212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10810875892639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09130001068115</t>
+    <t xml:space="preserve">2.10810852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09130024909973</t>
   </si>
   <si>
     <t xml:space="preserve">2.04507565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9708366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91200566291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9274138212204</t>
+    <t xml:space="preserve">1.97083628177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9120055437088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92741394042969</t>
   </si>
   <si>
     <t xml:space="preserve">1.88959383964539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8755863904953</t>
+    <t xml:space="preserve">1.87558650970459</t>
   </si>
   <si>
     <t xml:space="preserve">2.01566028594971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97924077510834</t>
+    <t xml:space="preserve">1.97924101352692</t>
   </si>
   <si>
     <t xml:space="preserve">1.96943593025208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92321145534515</t>
+    <t xml:space="preserve">1.92321157455444</t>
   </si>
   <si>
     <t xml:space="preserve">1.96523356437683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92181098461151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83496499061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.764927983284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75232172012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77193188667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78313791751862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82656073570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86438047885895</t>
+    <t xml:space="preserve">1.92181086540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83496475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76492810249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.752321600914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77193200588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78313779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82656097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86438035964966</t>
   </si>
   <si>
     <t xml:space="preserve">1.85177421569824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81395387649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86578130722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84897255897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88399076461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99745047092438</t>
+    <t xml:space="preserve">1.81395423412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86578118801117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84897267818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8839910030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99745059013367</t>
   </si>
   <si>
     <t xml:space="preserve">2.04787731170654</t>
@@ -1250,28 +1250,28 @@
     <t xml:space="preserve">2.04367470741272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99604976177216</t>
+    <t xml:space="preserve">1.99605000019073</t>
   </si>
   <si>
     <t xml:space="preserve">2.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11931467056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15013074874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17114186286926</t>
+    <t xml:space="preserve">2.11931490898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15013098716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17114210128784</t>
   </si>
   <si>
     <t xml:space="preserve">2.18725061416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12701892852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14557838439941</t>
+    <t xml:space="preserve">2.12701869010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14557862281799</t>
   </si>
   <si>
     <t xml:space="preserve">2.10355663299561</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">2.15363264083862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16028618812561</t>
+    <t xml:space="preserve">2.16028642654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.10600757598877</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">2.03772163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11721348762512</t>
+    <t xml:space="preserve">2.1172137260437</t>
   </si>
   <si>
     <t xml:space="preserve">2.0800940990448</t>
@@ -1307,25 +1307,25 @@
     <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12736892700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15258240699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18584990501404</t>
+    <t xml:space="preserve">2.12736868858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1525821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18584966659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.14207673072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425392150879</t>
+    <t xml:space="preserve">2.19425368309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.19005179405212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20300889015198</t>
+    <t xml:space="preserve">2.2030086517334</t>
   </si>
   <si>
     <t xml:space="preserve">2.17604470252991</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">2.1886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01005721092224</t>
+    <t xml:space="preserve">2.01005697250366</t>
   </si>
   <si>
     <t xml:space="preserve">2.08709764480591</t>
@@ -1355,49 +1355,49 @@
     <t xml:space="preserve">2.08394622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13822436332703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12036490440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12071537971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96348261833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98274278640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98729515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293794155121</t>
+    <t xml:space="preserve">2.13822460174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12036514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12071561813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9634827375412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98274314403534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98729526996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293758392334</t>
   </si>
   <si>
     <t xml:space="preserve">1.96838521957397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94107115268707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03421998023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0062050819397</t>
+    <t xml:space="preserve">1.94107091426849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03421974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00620532035828</t>
   </si>
   <si>
     <t xml:space="preserve">2.01601028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03492021560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10915923118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10775876045227</t>
+    <t xml:space="preserve">2.03491997718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10915946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10775852203369</t>
   </si>
   <si>
     <t xml:space="preserve">2.14382767677307</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.11791396141052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888547897339</t>
+    <t xml:space="preserve">2.15888595581055</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857483863831</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.08289575576782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14347743988037</t>
+    <t xml:space="preserve">2.14347720146179</t>
   </si>
   <si>
     <t xml:space="preserve">2.05453085899353</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">2.07028913497925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09970426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86087882518768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87523627281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84442019462585</t>
+    <t xml:space="preserve">2.09970450401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8608785867691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8752361536026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84442007541656</t>
   </si>
   <si>
     <t xml:space="preserve">1.82165825366974</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">1.51839864253998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55446779727936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578684329987</t>
+    <t xml:space="preserve">1.55446767807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578672409058</t>
   </si>
   <si>
     <t xml:space="preserve">1.63641047477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59648966789246</t>
+    <t xml:space="preserve">1.59648954868317</t>
   </si>
   <si>
     <t xml:space="preserve">1.6801837682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61259818077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71170008182526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69874358177185</t>
+    <t xml:space="preserve">1.61259841918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71170020103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69874346256256</t>
   </si>
   <si>
     <t xml:space="preserve">1.72465717792511</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">1.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78804039955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84792172908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78068685531616</t>
+    <t xml:space="preserve">1.78804051876068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84792184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068673610687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73481273651123</t>
@@ -1508,64 +1508,64 @@
     <t xml:space="preserve">1.70364606380463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7740330696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80589985847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82586026191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173426151276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274549484253</t>
+    <t xml:space="preserve">1.77403318881989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80589973926544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82586050033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173438072205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274573326111</t>
   </si>
   <si>
     <t xml:space="preserve">1.87243485450745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86823260784149</t>
+    <t xml:space="preserve">1.8682324886322</t>
   </si>
   <si>
     <t xml:space="preserve">1.85912799835205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8328640460968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81605517864227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85072338581085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601570129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85807752609253</t>
+    <t xml:space="preserve">1.83286416530609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81605529785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85072326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85807716846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.85387527942657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76807999610901</t>
+    <t xml:space="preserve">1.76807987689972</t>
   </si>
   <si>
     <t xml:space="preserve">1.75337219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64901745319366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64621591567993</t>
+    <t xml:space="preserve">1.64901733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64621603488922</t>
   </si>
   <si>
     <t xml:space="preserve">1.66337490081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65216898918152</t>
+    <t xml:space="preserve">1.65216910839081</t>
   </si>
   <si>
     <t xml:space="preserve">1.61960184574127</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">1.53030490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4697231054306</t>
+    <t xml:space="preserve">1.46972298622131</t>
   </si>
   <si>
     <t xml:space="preserve">1.42630016803741</t>
@@ -1589,22 +1589,22 @@
     <t xml:space="preserve">1.45501530170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44380962848663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43190324306488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44415962696075</t>
+    <t xml:space="preserve">1.44380939006805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43190336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44415950775146</t>
   </si>
   <si>
     <t xml:space="preserve">1.43925714492798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40704011917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120276927948</t>
+    <t xml:space="preserve">1.40704023838043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120288848877</t>
   </si>
   <si>
     <t xml:space="preserve">1.40178716182709</t>
@@ -1613,37 +1613,37 @@
     <t xml:space="preserve">1.358154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37132120132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50719273090363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49493646621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54326152801514</t>
+    <t xml:space="preserve">1.37132132053375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50719285011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49493634700775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54326176643372</t>
   </si>
   <si>
     <t xml:space="preserve">1.53555774688721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55026543140411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61084711551666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6153998374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61610007286072</t>
+    <t xml:space="preserve">1.55026531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61084723472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61539971828461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61609995365143</t>
   </si>
   <si>
     <t xml:space="preserve">1.62625527381897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62415432929993</t>
+    <t xml:space="preserve">1.62415421009064</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715054512024</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">1.64446496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64866733551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48688197135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40143716335297</t>
+    <t xml:space="preserve">1.64866709709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48688209056854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40143704414368</t>
   </si>
   <si>
     <t xml:space="preserve">1.37356245517731</t>
@@ -1670,22 +1670,22 @@
     <t xml:space="preserve">1.41439390182495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38602912425995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29638195037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31108963489532</t>
+    <t xml:space="preserve">1.38602900505066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29638183116913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31108951568604</t>
   </si>
   <si>
     <t xml:space="preserve">1.3052065372467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31136965751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31669247150421</t>
+    <t xml:space="preserve">1.31136977672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3166925907135</t>
   </si>
   <si>
     <t xml:space="preserve">1.30758774280548</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">1.22550463676453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20673477649689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16905474662781</t>
+    <t xml:space="preserve">1.2067346572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1690548658371</t>
   </si>
   <si>
     <t xml:space="preserve">1.14692318439484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09229445457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134457588196</t>
+    <t xml:space="preserve">1.09229457378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134445667267</t>
   </si>
   <si>
     <t xml:space="preserve">1.08977317810059</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">1.21317803859711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22410380840302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25477993488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29217946529388</t>
+    <t xml:space="preserve">1.2241039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25478005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29217958450317</t>
   </si>
   <si>
     <t xml:space="preserve">1.28139400482178</t>
@@ -1763,28 +1763,28 @@
     <t xml:space="preserve">1.26262414455414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19412815570831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28517603874207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32341599464417</t>
+    <t xml:space="preserve">1.19412803649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28517615795135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32341611385345</t>
   </si>
   <si>
     <t xml:space="preserve">1.38770985603333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41194272041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47392523288727</t>
+    <t xml:space="preserve">1.41194260120392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47392535209656</t>
   </si>
   <si>
     <t xml:space="preserve">1.47147405147552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44836175441742</t>
+    <t xml:space="preserve">1.448361992836</t>
   </si>
   <si>
     <t xml:space="preserve">1.53940963745117</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">1.54571294784546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55796933174133</t>
+    <t xml:space="preserve">1.55796945095062</t>
   </si>
   <si>
     <t xml:space="preserve">1.47917795181274</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">1.46376991271973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44801163673401</t>
+    <t xml:space="preserve">1.4480117559433</t>
   </si>
   <si>
     <t xml:space="preserve">1.48478090763092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49913859367371</t>
+    <t xml:space="preserve">1.49913847446442</t>
   </si>
   <si>
     <t xml:space="preserve">1.47007310390472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44345927238464</t>
+    <t xml:space="preserve">1.44345915317535</t>
   </si>
   <si>
     <t xml:space="preserve">1.4045889377594</t>
@@ -1823,58 +1823,58 @@
     <t xml:space="preserve">1.39401316642761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4315527677536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39443337917328</t>
+    <t xml:space="preserve">1.43155288696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39443349838257</t>
   </si>
   <si>
     <t xml:space="preserve">1.35605323314667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32285571098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39177203178406</t>
+    <t xml:space="preserve">1.32285583019257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39177215099335</t>
   </si>
   <si>
     <t xml:space="preserve">1.37118124961853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4333039522171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44170832633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41509425640106</t>
+    <t xml:space="preserve">1.43330383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44170820713043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41509413719177</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209792137146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42454934120178</t>
+    <t xml:space="preserve">1.42454922199249</t>
   </si>
   <si>
     <t xml:space="preserve">1.38224709033966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34918963909149</t>
+    <t xml:space="preserve">1.34918975830078</t>
   </si>
   <si>
     <t xml:space="preserve">1.29344034194946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33168053627014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32551717758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30058395862579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2948409318924</t>
+    <t xml:space="preserve">1.33168029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551729679108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3005838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29484105110168</t>
   </si>
   <si>
     <t xml:space="preserve">1.25996267795563</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">1.26864743232727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24721610546112</t>
+    <t xml:space="preserve">1.24721598625183</t>
   </si>
   <si>
     <t xml:space="preserve">1.27845239639282</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">1.24917697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24525511264801</t>
+    <t xml:space="preserve">1.24525499343872</t>
   </si>
   <si>
     <t xml:space="preserve">1.18474304676056</t>
@@ -1907,22 +1907,22 @@
     <t xml:space="preserve">1.19342768192291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21892118453979</t>
+    <t xml:space="preserve">1.21892106533051</t>
   </si>
   <si>
     <t xml:space="preserve">1.2291464805603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20897591114044</t>
+    <t xml:space="preserve">1.20897579193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.29400062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31851351261139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31417119503021</t>
+    <t xml:space="preserve">1.3185133934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31417107582092</t>
   </si>
   <si>
     <t xml:space="preserve">1.2770516872406</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">1.3850485086441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37706422805786</t>
+    <t xml:space="preserve">1.37706434726715</t>
   </si>
   <si>
     <t xml:space="preserve">1.35969519615173</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">1.3147314786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3601154088974</t>
+    <t xml:space="preserve">1.36011528968811</t>
   </si>
   <si>
     <t xml:space="preserve">1.40879094600677</t>
@@ -1964,34 +1964,34 @@
     <t xml:space="preserve">1.43505477905273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41544449329376</t>
+    <t xml:space="preserve">1.41544437408447</t>
   </si>
   <si>
     <t xml:space="preserve">1.37566351890564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38378775119781</t>
+    <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.35675358772278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34372675418854</t>
+    <t xml:space="preserve">1.34372663497925</t>
   </si>
   <si>
     <t xml:space="preserve">1.4031879901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37720429897308</t>
+    <t xml:space="preserve">1.37720441818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39149188995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38112640380859</t>
+    <t xml:space="preserve">1.3914920091629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38112652301788</t>
   </si>
   <si>
     <t xml:space="preserve">1.32103490829468</t>
@@ -2003,37 +2003,37 @@
     <t xml:space="preserve">1.28615653514862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32019424438477</t>
+    <t xml:space="preserve">1.32019436359406</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937804698944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28993856906891</t>
+    <t xml:space="preserve">1.28993844985962</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824862003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33175051212311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35941505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36606860160828</t>
+    <t xml:space="preserve">1.33175039291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.359414935112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36606848239899</t>
   </si>
   <si>
     <t xml:space="preserve">1.36641871929169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221659183502</t>
+    <t xml:space="preserve">1.36221647262573</t>
   </si>
   <si>
     <t xml:space="preserve">1.37587368488312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37727439403534</t>
+    <t xml:space="preserve">1.37727451324463</t>
   </si>
   <si>
     <t xml:space="preserve">1.37622380256653</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">1.48828279972076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43855655193329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49178469181061</t>
+    <t xml:space="preserve">1.43855667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49178457260132</t>
   </si>
   <si>
     <t xml:space="preserve">1.48127901554108</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">1.44205856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38077628612518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38532876968384</t>
+    <t xml:space="preserve">1.38077640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38532865047455</t>
   </si>
   <si>
     <t xml:space="preserve">1.27221918106079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24595546722412</t>
+    <t xml:space="preserve">1.24595522880554</t>
   </si>
   <si>
     <t xml:space="preserve">1.1997309923172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19062614440918</t>
+    <t xml:space="preserve">1.19062626361847</t>
   </si>
   <si>
     <t xml:space="preserve">1.19798004627228</t>
@@ -2093,31 +2093,31 @@
     <t xml:space="preserve">1.18082106113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15525758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17171633243561</t>
+    <t xml:space="preserve">1.15525770187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1717164516449</t>
   </si>
   <si>
     <t xml:space="preserve">1.14370155334473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13914918899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14930462837219</t>
+    <t xml:space="preserve">1.13914906978607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14930438995361</t>
   </si>
   <si>
     <t xml:space="preserve">1.16261148452759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15350651741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19377791881561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16716384887695</t>
+    <t xml:space="preserve">1.15350663661957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19377779960632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16716372966766</t>
   </si>
   <si>
     <t xml:space="preserve">1.14160048961639</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">1.18432295322418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19482851028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16821455955505</t>
+    <t xml:space="preserve">1.19482839107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16821444034576</t>
   </si>
   <si>
     <t xml:space="preserve">1.1710159778595</t>
@@ -2144,37 +2144,37 @@
     <t xml:space="preserve">1.25365936756134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24560499191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23790109157562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23474955558777</t>
+    <t xml:space="preserve">1.24560511112213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23790121078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23474943637848</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875676631927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451516151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24105262756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23825120925903</t>
+    <t xml:space="preserve">1.26451504230499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24105274677277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23825132846832</t>
   </si>
   <si>
     <t xml:space="preserve">1.31949388980865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36256659030914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36992037296295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33525228500366</t>
+    <t xml:space="preserve">1.36256670951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36992049217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33525240421295</t>
   </si>
   <si>
     <t xml:space="preserve">1.32264566421509</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">1.33350133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33630287647247</t>
+    <t xml:space="preserve">1.33630275726318</t>
   </si>
   <si>
     <t xml:space="preserve">1.34295642375946</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">1.31214010715485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34575772285461</t>
+    <t xml:space="preserve">1.3457578420639</t>
   </si>
   <si>
     <t xml:space="preserve">1.32439661026001</t>
@@ -2204,37 +2204,37 @@
     <t xml:space="preserve">1.22634506225586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23159778118134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23720061779022</t>
+    <t xml:space="preserve">1.23159766197205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23720073699951</t>
   </si>
   <si>
     <t xml:space="preserve">1.23124754428864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163725852966</t>
+    <t xml:space="preserve">1.21163737773895</t>
   </si>
   <si>
     <t xml:space="preserve">1.17241680622101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18222177028656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18817496299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1846729516983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18607378005981</t>
+    <t xml:space="preserve">1.18222188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18817484378815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18467307090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1860738992691</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210333824158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26731646060944</t>
+    <t xml:space="preserve">1.26731657981873</t>
   </si>
   <si>
     <t xml:space="preserve">1.15175580978394</t>
@@ -2243,34 +2243,34 @@
     <t xml:space="preserve">1.13529717922211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18047082424164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1342465877533</t>
+    <t xml:space="preserve">1.18047094345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13424670696259</t>
   </si>
   <si>
     <t xml:space="preserve">1.18012070655823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20603430271149</t>
+    <t xml:space="preserve">1.2060341835022</t>
   </si>
   <si>
     <t xml:space="preserve">1.17521822452545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18992590904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21583938598633</t>
+    <t xml:space="preserve">1.18992602825165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21583950519562</t>
   </si>
   <si>
     <t xml:space="preserve">1.21653974056244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23404908180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27467048168182</t>
+    <t xml:space="preserve">1.23404896259308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27467036247253</t>
   </si>
   <si>
     <t xml:space="preserve">1.286576628685</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">1.28132390975952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27186894416809</t>
+    <t xml:space="preserve">1.2718688249588</t>
   </si>
   <si>
     <t xml:space="preserve">1.26906752586365</t>
@@ -2291,19 +2291,19 @@
     <t xml:space="preserve">1.30548667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32474672794342</t>
+    <t xml:space="preserve">1.32474684715271</t>
   </si>
   <si>
     <t xml:space="preserve">1.31844341754913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35171091556549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31424117088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34050512313843</t>
+    <t xml:space="preserve">1.35171103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31424129009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34050500392914</t>
   </si>
   <si>
     <t xml:space="preserve">1.36816954612732</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">1.31003904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33980476856232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33210062980652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29007852077484</t>
+    <t xml:space="preserve">1.33980464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33210051059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29007840156555</t>
   </si>
   <si>
     <t xml:space="preserve">1.27081847190857</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">1.50859332084656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49598693847656</t>
+    <t xml:space="preserve">1.49598681926727</t>
   </si>
   <si>
     <t xml:space="preserve">1.47707688808441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46867251396179</t>
+    <t xml:space="preserve">1.4686723947525</t>
   </si>
   <si>
     <t xml:space="preserve">1.42314851284027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42665028572083</t>
+    <t xml:space="preserve">1.42665016651154</t>
   </si>
   <si>
     <t xml:space="preserve">1.47777724266052</t>
@@ -2381,22 +2381,22 @@
     <t xml:space="preserve">1.49388563632965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44766128063202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42104732990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264307498932</t>
+    <t xml:space="preserve">1.44766139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42104756832123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264295578003</t>
   </si>
   <si>
     <t xml:space="preserve">1.41754555702209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41614496707916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44135820865631</t>
+    <t xml:space="preserve">1.41614484786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44135808944702</t>
   </si>
   <si>
     <t xml:space="preserve">1.45536541938782</t>
@@ -2408,28 +2408,28 @@
     <t xml:space="preserve">1.43085253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41824615001678</t>
+    <t xml:space="preserve">1.4182460308075</t>
   </si>
   <si>
     <t xml:space="preserve">1.38813006877899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37412285804749</t>
+    <t xml:space="preserve">1.3741227388382</t>
   </si>
   <si>
     <t xml:space="preserve">1.41474401950836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40353810787201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40984153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45326435565948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42034697532654</t>
+    <t xml:space="preserve">1.4035382270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40984165668488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45326447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42034709453583</t>
   </si>
   <si>
     <t xml:space="preserve">1.36851978302002</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">1.37797474861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38637924194336</t>
+    <t xml:space="preserve">1.38637912273407</t>
   </si>
   <si>
     <t xml:space="preserve">1.4616687297821</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">1.43365406990051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38287734985352</t>
+    <t xml:space="preserve">1.38287723064423</t>
   </si>
   <si>
     <t xml:space="preserve">1.36886990070343</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">1.29568159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35836458206177</t>
+    <t xml:space="preserve">1.35836446285248</t>
   </si>
   <si>
     <t xml:space="preserve">1.37307226657867</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">1.52049958705902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54641342163086</t>
+    <t xml:space="preserve">1.54641330242157</t>
   </si>
   <si>
     <t xml:space="preserve">1.72010481357574</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">1.30128443241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1423008441925</t>
+    <t xml:space="preserve">1.14230096340179</t>
   </si>
   <si>
     <t xml:space="preserve">1.09397554397583</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">1.05755627155304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905926465988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861102998256683</t>
+    <t xml:space="preserve">0.905926525592804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861102938652039</t>
   </si>
   <si>
     <t xml:space="preserve">0.926937639713287</t>
@@ -2516,64 +2516,64 @@
     <t xml:space="preserve">0.772156119346619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888417184352875</t>
+    <t xml:space="preserve">0.88841724395752</t>
   </si>
   <si>
     <t xml:space="preserve">0.818030297756195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874409854412079</t>
+    <t xml:space="preserve">0.874409914016724</t>
   </si>
   <si>
     <t xml:space="preserve">0.874760091304779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.885965943336487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877561628818512</t>
+    <t xml:space="preserve">0.885966002941132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877561569213867</t>
   </si>
   <si>
     <t xml:space="preserve">0.870207726955414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926587343215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912930130958557</t>
+    <t xml:space="preserve">0.926587283611298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912930250167847</t>
   </si>
   <si>
     <t xml:space="preserve">0.925887107849121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880713224411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849196672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840442061424255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633253574371</t>
+    <t xml:space="preserve">0.880713284015656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84919673204422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8404421210289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633193969727</t>
   </si>
   <si>
     <t xml:space="preserve">0.846044957637787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830986976623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851297795772552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829936385154724</t>
+    <t xml:space="preserve">0.83098703622818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851297736167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829936444759369</t>
   </si>
   <si>
     <t xml:space="preserve">0.853048622608185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820131421089172</t>
+    <t xml:space="preserve">0.820131361484528</t>
   </si>
   <si>
     <t xml:space="preserve">0.777408838272095</t>
@@ -2582,49 +2582,49 @@
     <t xml:space="preserve">0.778459489345551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778809607028961</t>
+    <t xml:space="preserve">0.778809666633606</t>
   </si>
   <si>
     <t xml:space="preserve">0.753246188163757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751845419406891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771805882453918</t>
+    <t xml:space="preserve">0.751845479011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771805942058563</t>
   </si>
   <si>
     <t xml:space="preserve">0.743791282176971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768304109573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789665400981903</t>
+    <t xml:space="preserve">0.768304228782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789665341377258</t>
   </si>
   <si>
     <t xml:space="preserve">0.809625864028931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779860138893127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766553103923798</t>
+    <t xml:space="preserve">0.779860198497772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766553223133087</t>
   </si>
   <si>
     <t xml:space="preserve">0.781611144542694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776008248329163</t>
+    <t xml:space="preserve">0.776008188724518</t>
   </si>
   <si>
     <t xml:space="preserve">0.765152454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803672730922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812077164649963</t>
+    <t xml:space="preserve">0.803672611713409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812077105045319</t>
   </si>
   <si>
     <t xml:space="preserve">0.807874917984009</t>
@@ -2633,49 +2633,49 @@
     <t xml:space="preserve">0.785463154315948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781260907649994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819080770015717</t>
+    <t xml:space="preserve">0.781260967254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819080829620361</t>
   </si>
   <si>
     <t xml:space="preserve">0.759199321269989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756047666072845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730484187602997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736087143421173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743440985679626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779159724712372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815228819847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805773794651031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85830146074295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872308850288391</t>
+    <t xml:space="preserve">0.756047606468201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730484247207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736087203025818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743441045284271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779159784317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815228760242462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805773854255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858301520347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872308731079102</t>
   </si>
   <si>
     <t xml:space="preserve">0.892969727516174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931840121746063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994873344898224</t>
+    <t xml:space="preserve">0.931840062141418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994873404502869</t>
   </si>
   <si>
     <t xml:space="preserve">1.00853049755096</t>
@@ -2687,19 +2687,19 @@
     <t xml:space="preserve">0.966858446598053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891218841075897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895070791244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901724338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967909097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96440714597702</t>
+    <t xml:space="preserve">0.891218721866608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895070850849152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901724278926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967908978462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96440726518631</t>
   </si>
   <si>
     <t xml:space="preserve">0.946897983551025</t>
@@ -2708,58 +2708,58 @@
     <t xml:space="preserve">0.936392545700073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938493549823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965107500553131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913980722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934641599655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899623215198517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953551650047302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930089175701141</t>
+    <t xml:space="preserve">0.938493609428406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965107560157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913980782032013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934641540050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899623155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953551590442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930089116096497</t>
   </si>
   <si>
     <t xml:space="preserve">0.909078121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954602122306824</t>
+    <t xml:space="preserve">0.954602003097534</t>
   </si>
   <si>
     <t xml:space="preserve">0.943746387958527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983317255973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973161816596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95145046710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916432023048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933941245079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948298752307892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957403659820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97351199388504</t>
+    <t xml:space="preserve">0.983317196369171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97316187620163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951450526714325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916432082653046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93394136428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948298811912537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957403540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973511934280396</t>
   </si>
   <si>
     <t xml:space="preserve">0.980866014957428</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">1.033043384552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03759586811066</t>
+    <t xml:space="preserve">1.03759574890137</t>
   </si>
   <si>
     <t xml:space="preserve">1.00012600421906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998725235462189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960905492305756</t>
+    <t xml:space="preserve">0.998725295066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960905432701111</t>
   </si>
   <si>
     <t xml:space="preserve">0.967208743095398</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">0.944096565246582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.893669962882996</t>
+    <t xml:space="preserve">0.89367002248764</t>
   </si>
   <si>
     <t xml:space="preserve">0.890168249607086</t>
@@ -2795,22 +2795,22 @@
     <t xml:space="preserve">0.874059736728668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913280367851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927637875080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907677352428436</t>
+    <t xml:space="preserve">0.913280487060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927637815475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907677531242371</t>
   </si>
   <si>
     <t xml:space="preserve">0.890868484973907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91538143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978764772415161</t>
+    <t xml:space="preserve">0.915381550788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978764832019806</t>
   </si>
   <si>
     <t xml:space="preserve">0.971060812473297</t>
@@ -2819,34 +2819,34 @@
     <t xml:space="preserve">1.00572907924652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997324585914612</t>
+    <t xml:space="preserve">0.997324466705322</t>
   </si>
   <si>
     <t xml:space="preserve">0.981566250324249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00923073291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986819088459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987519443035126</t>
+    <t xml:space="preserve">1.00923085212708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986818909645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987519323825836</t>
   </si>
   <si>
     <t xml:space="preserve">1.00712966918945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996624231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999775886535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00467848777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988920032978058</t>
+    <t xml:space="preserve">0.996624112129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999775826931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00467836856842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988920211791992</t>
   </si>
   <si>
     <t xml:space="preserve">0.985768496990204</t>
@@ -2855,28 +2855,28 @@
     <t xml:space="preserve">0.970360338687897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958104014396667</t>
+    <t xml:space="preserve">0.958103835582733</t>
   </si>
   <si>
     <t xml:space="preserve">0.994523048400879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978414595127106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986118733882904</t>
+    <t xml:space="preserve">0.978414535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98611855506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.03724551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02148735523224</t>
+    <t xml:space="preserve">1.02148723602295</t>
   </si>
   <si>
     <t xml:space="preserve">1.01903593540192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0120325088501</t>
+    <t xml:space="preserve">1.01203238964081</t>
   </si>
   <si>
     <t xml:space="preserve">0.995573580265045</t>
@@ -2888,34 +2888,34 @@
     <t xml:space="preserve">0.916782259941101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922735273838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888066947460175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939544081687927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961605727672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972811698913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0540543794632</t>
+    <t xml:space="preserve">0.922735393047333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888067007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939544141292572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961605787277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972811758518219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05405426025391</t>
   </si>
   <si>
     <t xml:space="preserve">1.11113452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09957838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16121065616608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18502330780029</t>
+    <t xml:space="preserve">1.09957849979401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16121077537537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.185023188591</t>
   </si>
   <si>
     <t xml:space="preserve">1.16961526870728</t>
@@ -2924,16 +2924,16 @@
     <t xml:space="preserve">1.15910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12339091300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12829327583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12794327735901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16016018390656</t>
+    <t xml:space="preserve">1.12339079380035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12829339504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1279433965683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16016006469727</t>
   </si>
   <si>
     <t xml:space="preserve">1.13564729690552</t>
@@ -2960,31 +2960,31 @@
     <t xml:space="preserve">1.08522081375122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965733528137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08627128601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12899374961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15000486373901</t>
+    <t xml:space="preserve">1.05965745449066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08627140522003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12899386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15000474452972</t>
   </si>
   <si>
     <t xml:space="preserve">1.15210592746735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15490746498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15455722808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25120806694031</t>
+    <t xml:space="preserve">1.15490758419037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15455734729767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066291332245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2512081861496</t>
   </si>
   <si>
     <t xml:space="preserve">1.25611066818237</t>
@@ -2996,19 +2996,19 @@
     <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32684779167175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35801434516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3233460187912</t>
+    <t xml:space="preserve">1.32684791088104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35801422595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32334613800049</t>
   </si>
   <si>
     <t xml:space="preserve">1.31879353523254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29603159427643</t>
+    <t xml:space="preserve">1.29603171348572</t>
   </si>
   <si>
     <t xml:space="preserve">1.31389117240906</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">1.29498112201691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28482568264008</t>
+    <t xml:space="preserve">1.28482580184937</t>
   </si>
   <si>
     <t xml:space="preserve">1.28027331829071</t>
@@ -3038,37 +3038,37 @@
     <t xml:space="preserve">1.27256941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26136350631714</t>
+    <t xml:space="preserve">1.26136338710785</t>
   </si>
   <si>
     <t xml:space="preserve">1.26661622524261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26416492462158</t>
+    <t xml:space="preserve">1.26416480541229</t>
   </si>
   <si>
     <t xml:space="preserve">1.26521551609039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26766669750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26626586914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25856196880341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25821173191071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32964932918549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957037448883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3450573682785</t>
+    <t xml:space="preserve">1.26766681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2662661075592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2585620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25821185112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3296492099762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957025527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34505748748779</t>
   </si>
   <si>
     <t xml:space="preserve">1.34925973415375</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">1.31809318065643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31073951721191</t>
+    <t xml:space="preserve">1.31073939800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.31774306297302</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">1.24735617637634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26696634292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2501574754715</t>
+    <t xml:space="preserve">1.26696646213531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25015735626221</t>
   </si>
   <si>
     <t xml:space="preserve">1.29112911224365</t>
@@ -3110,10 +3110,10 @@
     <t xml:space="preserve">1.29953348636627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34820902347565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42174768447876</t>
+    <t xml:space="preserve">1.34820914268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42174792289734</t>
   </si>
   <si>
     <t xml:space="preserve">1.52260088920593</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">1.52190053462982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53240573406219</t>
+    <t xml:space="preserve">1.53240597248077</t>
   </si>
   <si>
     <t xml:space="preserve">1.49808776378632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48898315429688</t>
+    <t xml:space="preserve">1.48898327350616</t>
   </si>
   <si>
     <t xml:space="preserve">1.50088942050934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51629745960236</t>
+    <t xml:space="preserve">1.51629757881165</t>
   </si>
   <si>
     <t xml:space="preserve">1.50789332389832</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">1.54851448535919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54361176490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60594475269318</t>
+    <t xml:space="preserve">1.54361188411713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60594463348389</t>
   </si>
   <si>
     <t xml:space="preserve">1.62695574760437</t>
@@ -3167,43 +3167,43 @@
     <t xml:space="preserve">1.69909381866455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7011946439743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72360646724701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71029937267303</t>
+    <t xml:space="preserve">1.70119452476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7236065864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71029961109161</t>
   </si>
   <si>
     <t xml:space="preserve">1.70469653606415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71100008487701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881970882416</t>
+    <t xml:space="preserve">1.71100032329559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881982803345</t>
   </si>
   <si>
     <t xml:space="preserve">1.70539700984955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68998885154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65356957912445</t>
+    <t xml:space="preserve">1.68998873233795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65356969833374</t>
   </si>
   <si>
     <t xml:space="preserve">1.63536024093628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64936757087708</t>
+    <t xml:space="preserve">1.6493673324585</t>
   </si>
   <si>
     <t xml:space="preserve">1.63466000556946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62835669517517</t>
+    <t xml:space="preserve">1.62835657596588</t>
   </si>
   <si>
     <t xml:space="preserve">1.6654759645462</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">1.62308478355408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65613567829132</t>
+    <t xml:space="preserve">1.65613555908203</t>
   </si>
   <si>
     <t xml:space="preserve">1.67337942123413</t>
@@ -3233,28 +3233,28 @@
     <t xml:space="preserve">1.71936321258545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71289694309235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70283758640289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73445177078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71145975589752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7452290058136</t>
+    <t xml:space="preserve">1.71289670467377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70283782482147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73445165157318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71145987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74522912502289</t>
   </si>
   <si>
     <t xml:space="preserve">1.76893949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76822102069855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81707882881165</t>
+    <t xml:space="preserve">1.76822090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81707894802094</t>
   </si>
   <si>
     <t xml:space="preserve">1.83504116535187</t>
@@ -3263,46 +3263,46 @@
     <t xml:space="preserve">1.85587775707245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86449956893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126107215881</t>
+    <t xml:space="preserve">1.86449980735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126083374023</t>
   </si>
   <si>
     <t xml:space="preserve">1.95934128761292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9729927778244</t>
+    <t xml:space="preserve">1.97299289703369</t>
   </si>
   <si>
     <t xml:space="preserve">1.98377013206482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94066035747528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9650890827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99742162227631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02400612831116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03334665298462</t>
+    <t xml:space="preserve">1.94066047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96508884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99742150306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02400588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03334641456604</t>
   </si>
   <si>
     <t xml:space="preserve">2.08579683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08795213699341</t>
+    <t xml:space="preserve">2.08795237541199</t>
   </si>
   <si>
     <t xml:space="preserve">2.10375881195068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12531399726868</t>
+    <t xml:space="preserve">2.12531423568726</t>
   </si>
   <si>
     <t xml:space="preserve">2.13465452194214</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">2.15189838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423104286194</t>
+    <t xml:space="preserve">2.18423080444336</t>
   </si>
   <si>
     <t xml:space="preserve">2.17201638221741</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">2.17991971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17560911178589</t>
+    <t xml:space="preserve">2.17560887336731</t>
   </si>
   <si>
     <t xml:space="preserve">2.17632746696472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16052031517029</t>
+    <t xml:space="preserve">2.16052055358887</t>
   </si>
   <si>
     <t xml:space="preserve">2.12818789482117</t>
@@ -3338,10 +3338,10 @@
     <t xml:space="preserve">2.08938932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08076739311218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05346441268921</t>
+    <t xml:space="preserve">2.08076691627502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05346465110779</t>
   </si>
   <si>
     <t xml:space="preserve">2.08292269706726</t>
@@ -3356,19 +3356,19 @@
     <t xml:space="preserve">2.01897644996643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04053115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9830516576767</t>
+    <t xml:space="preserve">2.04053163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98305141925812</t>
   </si>
   <si>
     <t xml:space="preserve">1.96652626991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94928240776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95215630531311</t>
+    <t xml:space="preserve">1.94928252696991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9521564245224</t>
   </si>
   <si>
     <t xml:space="preserve">1.90114283561707</t>
@@ -3377,64 +3377,64 @@
     <t xml:space="preserve">1.83288586139679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93922340869904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93634951114655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91766822338104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88821017742157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749146461487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84653735160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78762018680573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8264194726944</t>
+    <t xml:space="preserve">1.93922328948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93634939193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91766834259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88820993900299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749170303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84653723239899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7876204252243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82641935348511</t>
   </si>
   <si>
     <t xml:space="preserve">1.8752772808075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85803306102753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90258026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87743234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89108407497406</t>
+    <t xml:space="preserve">1.85803294181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90258002281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87743246555328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89108383655548</t>
   </si>
   <si>
     <t xml:space="preserve">1.82067143917084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81348621845245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82857489585876</t>
+    <t xml:space="preserve">1.81348645687103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82857477664948</t>
   </si>
   <si>
     <t xml:space="preserve">1.96724474430084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97371125221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95718562602997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03190946578979</t>
+    <t xml:space="preserve">1.97371113300323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95718574523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03190922737122</t>
   </si>
   <si>
     <t xml:space="preserve">2.00676202774048</t>
@@ -3443,25 +3443,25 @@
     <t xml:space="preserve">2.00388813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97155559062958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93347537517548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90904676914215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94209730625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97802209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01107335090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957728385925</t>
+    <t xml:space="preserve">1.97155570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93347561359406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90904653072357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94209718704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97802197933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01107311248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957716464996</t>
   </si>
   <si>
     <t xml:space="preserve">2.01753973960876</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">2.03262805938721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03119087219238</t>
+    <t xml:space="preserve">2.03119111061096</t>
   </si>
   <si>
     <t xml:space="preserve">1.99167382717133</t>
@@ -3479,22 +3479,22 @@
     <t xml:space="preserve">2.01322841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945928573608</t>
+    <t xml:space="preserve">1.97945940494537</t>
   </si>
   <si>
     <t xml:space="preserve">1.95000076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93778645992279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96868193149567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92269825935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94712662696838</t>
+    <t xml:space="preserve">1.93778657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96868169307709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92269814014435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94712686538696</t>
   </si>
   <si>
     <t xml:space="preserve">1.92916429042816</t>
@@ -3503,28 +3503,28 @@
     <t xml:space="preserve">1.83073043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84078919887543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92054259777069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97586667537689</t>
+    <t xml:space="preserve">1.84078943729401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9205424785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97586679458618</t>
   </si>
   <si>
     <t xml:space="preserve">1.92341649532318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94353425502777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94425296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91838693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616143226624</t>
+    <t xml:space="preserve">1.94353437423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9442526102066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91838705539703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616167068481</t>
   </si>
   <si>
     <t xml:space="preserve">2.02831721305847</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">2.02185034751892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03047227859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994212150574</t>
+    <t xml:space="preserve">2.03047251701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994176387787</t>
   </si>
   <si>
     <t xml:space="preserve">2.04340553283691</t>
@@ -3551,28 +3551,28 @@
     <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1231586933136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13034343719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14758729934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1095073223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08148574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92988300323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93563079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083711624146</t>
+    <t xml:space="preserve">2.12315845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1303436756134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1475875377655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10950708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08148598670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92988276481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93563091754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97083723545074</t>
   </si>
   <si>
     <t xml:space="preserve">2.00963616371155</t>
@@ -3581,55 +3581,55 @@
     <t xml:space="preserve">2.08364152908325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03765726089478</t>
+    <t xml:space="preserve">2.03765749931335</t>
   </si>
   <si>
     <t xml:space="preserve">2.00316953659058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98592579364777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95143783092499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042436122894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88318085670471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85372197628021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7459477186203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540612220764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77181375026703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80845701694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83001184463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88533627986908</t>
+    <t xml:space="preserve">1.98592555522919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042459964752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88318049907684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8537220954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74594783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77181363105774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8084568977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83001172542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88533616065979</t>
   </si>
   <si>
     <t xml:space="preserve">1.92557191848755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8896472454071</t>
+    <t xml:space="preserve">1.88964736461639</t>
   </si>
   <si>
     <t xml:space="preserve">1.88677299022675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86737358570099</t>
+    <t xml:space="preserve">1.8673734664917</t>
   </si>
   <si>
     <t xml:space="preserve">1.89395797252655</t>
@@ -3638,52 +3638,52 @@
     <t xml:space="preserve">1.89036560058594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8544408082962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84797430038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7976793050766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85659635066986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85875153541565</t>
+    <t xml:space="preserve">1.85444056987762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84797418117523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79767954349518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85659646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85875141620636</t>
   </si>
   <si>
     <t xml:space="preserve">1.84725570678711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85515940189362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8860547542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97874081134796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0010142326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0254430770874</t>
+    <t xml:space="preserve">1.85515928268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88605463504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683210849762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97874045372009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00101399421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02544283866882</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280493736267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05849385261536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06424164772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05633854866028</t>
+    <t xml:space="preserve">2.05849409103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06424188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0563383102417</t>
   </si>
   <si>
     <t xml:space="preserve">2.05274605751038</t>
@@ -3692,19 +3692,19 @@
     <t xml:space="preserve">2.02113199234009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0046067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01251029968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99526596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89970588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87958824634552</t>
+    <t xml:space="preserve">2.00460648536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01251006126404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99526607990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8997061252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87958812713623</t>
   </si>
   <si>
     <t xml:space="preserve">1.93131995201111</t>
@@ -3713,10 +3713,10 @@
     <t xml:space="preserve">1.96221518516541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91192042827606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02041339874268</t>
+    <t xml:space="preserve">1.91192030906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02041363716125</t>
   </si>
   <si>
     <t xml:space="preserve">2.06855273246765</t>
@@ -3731,16 +3731,16 @@
     <t xml:space="preserve">2.09657406806946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15117979049683</t>
+    <t xml:space="preserve">2.15118002891541</t>
   </si>
   <si>
     <t xml:space="preserve">2.32505631446838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32361936569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55138278007507</t>
+    <t xml:space="preserve">2.32361912727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55138301849365</t>
   </si>
   <si>
     <t xml:space="preserve">2.53485751152039</t>
@@ -3758,40 +3758,40 @@
     <t xml:space="preserve">2.57509326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52336168289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51042866706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41343140602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21584463119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26398372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21368908882141</t>
+    <t xml:space="preserve">2.52336144447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5104284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21584486961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26398396492004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21368932723999</t>
   </si>
   <si>
     <t xml:space="preserve">2.06496047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120195388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66475749015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7495402097702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79480540752411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575987815857</t>
+    <t xml:space="preserve">1.91120183467865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66475737094879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74954009056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79480528831482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575975894928</t>
   </si>
   <si>
     <t xml:space="preserve">1.90186154842377</t>
@@ -3803,43 +3803,43 @@
     <t xml:space="preserve">1.96077823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95862281322479</t>
+    <t xml:space="preserve">1.95862293243408</t>
   </si>
   <si>
     <t xml:space="preserve">1.98879945278168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95574867725372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359325408936</t>
+    <t xml:space="preserve">1.95574855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359337329865</t>
   </si>
   <si>
     <t xml:space="preserve">2.06208634376526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93275713920593</t>
+    <t xml:space="preserve">1.93275690078735</t>
   </si>
   <si>
     <t xml:space="preserve">1.99095511436462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664426803589</t>
+    <t xml:space="preserve">1.98664450645447</t>
   </si>
   <si>
     <t xml:space="preserve">1.94784533977509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16626858711243</t>
+    <t xml:space="preserve">2.16626834869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.12459564208984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19572687149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19860076904297</t>
+    <t xml:space="preserve">2.1957266330719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19860053062439</t>
   </si>
   <si>
     <t xml:space="preserve">2.23077535629272</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">2.35181331634521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36713457107544</t>
+    <t xml:space="preserve">2.36713480949402</t>
   </si>
   <si>
     <t xml:space="preserve">2.321937084198</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">2.35104727745056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31887245178223</t>
+    <t xml:space="preserve">2.31887269020081</t>
   </si>
   <si>
     <t xml:space="preserve">2.27597308158875</t>
@@ -3878,22 +3878,22 @@
     <t xml:space="preserve">2.23383975028992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21085786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13731598854065</t>
+    <t xml:space="preserve">2.210857629776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13731575012207</t>
   </si>
   <si>
     <t xml:space="preserve">2.1587655544281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25069308280945</t>
+    <t xml:space="preserve">2.25069332122803</t>
   </si>
   <si>
     <t xml:space="preserve">2.23307371139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2154541015625</t>
+    <t xml:space="preserve">2.21545433998108</t>
   </si>
   <si>
     <t xml:space="preserve">2.2828676700592</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">2.26448225975037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31351041793823</t>
+    <t xml:space="preserve">2.31351017951965</t>
   </si>
   <si>
     <t xml:space="preserve">2.38092374801636</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45523190498352</t>
+    <t xml:space="preserve">2.4552321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.47285127639771</t>
@@ -3923,13 +3923,13 @@
     <t xml:space="preserve">2.4820442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4866406917572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46365857124329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47438335418701</t>
+    <t xml:space="preserve">2.48664093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46365880966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47438359260559</t>
   </si>
   <si>
     <t xml:space="preserve">2.41309857368469</t>
@@ -3938,43 +3938,43 @@
     <t xml:space="preserve">2.43071818351746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37709355354309</t>
+    <t xml:space="preserve">2.37709331512451</t>
   </si>
   <si>
     <t xml:space="preserve">2.09058594703674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98793339729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01168131828308</t>
+    <t xml:space="preserve">1.98793351650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01168155670166</t>
   </si>
   <si>
     <t xml:space="preserve">2.08062720298767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02623653411865</t>
+    <t xml:space="preserve">2.02623677253723</t>
   </si>
   <si>
     <t xml:space="preserve">2.07832908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1679584980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315622329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1993670463562</t>
+    <t xml:space="preserve">2.16795802116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19936680793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.13501763343811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20089888572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14267826080322</t>
+    <t xml:space="preserve">2.20089912414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14267802238464</t>
   </si>
   <si>
     <t xml:space="preserve">2.14191222190857</t>
@@ -3983,19 +3983,19 @@
     <t xml:space="preserve">2.14650845527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0315990447998</t>
+    <t xml:space="preserve">2.03159880638123</t>
   </si>
   <si>
     <t xml:space="preserve">1.99406182765961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90290057659149</t>
+    <t xml:space="preserve">1.90290069580078</t>
   </si>
   <si>
     <t xml:space="preserve">1.86919391155243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98410308361053</t>
+    <t xml:space="preserve">1.98410332202911</t>
   </si>
   <si>
     <t xml:space="preserve">1.98563539981842</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">1.8684276342392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83472084999084</t>
+    <t xml:space="preserve">1.83472096920013</t>
   </si>
   <si>
     <t xml:space="preserve">1.73743081092834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7742018699646</t>
+    <t xml:space="preserve">1.77420198917389</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012437820435</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">1.80331230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79718363285065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85387253761292</t>
+    <t xml:space="preserve">1.79718387126923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8538726568222</t>
   </si>
   <si>
     <t xml:space="preserve">1.79641771316528</t>
@@ -4043,16 +4043,16 @@
     <t xml:space="preserve">1.86306524276733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92894685268402</t>
+    <t xml:space="preserve">1.92894661426544</t>
   </si>
   <si>
     <t xml:space="preserve">1.92051994800568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96954798698425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837034225464</t>
+    <t xml:space="preserve">1.96954786777496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837010383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.00095653533936</t>
@@ -4061,10 +4061,10 @@
     <t xml:space="preserve">2.03466320037842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98869955539703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9718462228775</t>
+    <t xml:space="preserve">1.98869943618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97184610366821</t>
   </si>
   <si>
     <t xml:space="preserve">1.9565247297287</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">2.01397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94273579120636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87762045860291</t>
+    <t xml:space="preserve">1.94273567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87762057781219</t>
   </si>
   <si>
     <t xml:space="preserve">1.90826308727264</t>
@@ -4100,34 +4100,34 @@
     <t xml:space="preserve">1.80944085121155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86612951755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8983039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90213441848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87149202823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96878206729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90060234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90673089027405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89907014369965</t>
+    <t xml:space="preserve">1.86612963676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89830386638641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90213453769684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87149214744568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96878182888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90060222148895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90673077106476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89907026290894</t>
   </si>
   <si>
     <t xml:space="preserve">1.99712634086609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06070971488953</t>
+    <t xml:space="preserve">2.06070947647095</t>
   </si>
   <si>
     <t xml:space="preserve">2.12199449539185</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">2.19017386436462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21392226219177</t>
+    <t xml:space="preserve">2.21392202377319</t>
   </si>
   <si>
     <t xml:space="preserve">2.15799951553345</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">2.09288430213928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07143449783325</t>
+    <t xml:space="preserve">2.07143425941467</t>
   </si>
   <si>
     <t xml:space="preserve">2.02700257301331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06377363204956</t>
+    <t xml:space="preserve">2.06377387046814</t>
   </si>
   <si>
     <t xml:space="preserve">2.1319534778595</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">2.17791700363159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10820531845093</t>
+    <t xml:space="preserve">2.10820555686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.03006720542908</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">2.07986092567444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05151653289795</t>
+    <t xml:space="preserve">2.05151677131653</t>
   </si>
   <si>
     <t xml:space="preserve">2.05304884910583</t>
@@ -4190,10 +4190,10 @@
     <t xml:space="preserve">2.11893033981323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17485308647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17255449295044</t>
+    <t xml:space="preserve">2.17485284805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17255473136902</t>
   </si>
   <si>
     <t xml:space="preserve">2.17332077026367</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">2.19323825836182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22617888450623</t>
+    <t xml:space="preserve">2.2261791229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.21698641777039</t>
@@ -4211,13 +4211,13 @@
     <t xml:space="preserve">2.3173406124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3441526889801</t>
+    <t xml:space="preserve">2.34415292739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.34491896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37173104286194</t>
+    <t xml:space="preserve">2.37173128128052</t>
   </si>
   <si>
     <t xml:space="preserve">2.41922688484192</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">2.44220876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37785959243774</t>
+    <t xml:space="preserve">2.37785983085632</t>
   </si>
   <si>
     <t xml:space="preserve">2.42152523994446</t>
@@ -4235,25 +4235,25 @@
     <t xml:space="preserve">2.35564374923706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36177253723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41769480705261</t>
+    <t xml:space="preserve">2.36177229881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41769504547119</t>
   </si>
   <si>
     <t xml:space="preserve">2.45140171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45906233787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970460891724</t>
+    <t xml:space="preserve">2.45906209945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970484733582</t>
   </si>
   <si>
     <t xml:space="preserve">2.51268672943115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56171488761902</t>
+    <t xml:space="preserve">2.56171464920044</t>
   </si>
   <si>
     <t xml:space="preserve">2.58086633682251</t>
@@ -4265,13 +4265,13 @@
     <t xml:space="preserve">2.55175614356995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52187943458557</t>
+    <t xml:space="preserve">2.52187919616699</t>
   </si>
   <si>
     <t xml:space="preserve">2.53796672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53720092773438</t>
+    <t xml:space="preserve">2.5372006893158</t>
   </si>
   <si>
     <t xml:space="preserve">2.4759156703949</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">2.44450712203979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41386437416077</t>
+    <t xml:space="preserve">2.41386461257935</t>
   </si>
   <si>
     <t xml:space="preserve">2.40390563011169</t>
@@ -4292,13 +4292,13 @@
     <t xml:space="preserve">2.41080021858215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40313982963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42075896263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51881551742554</t>
+    <t xml:space="preserve">2.40313959121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4207592010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51881527900696</t>
   </si>
   <si>
     <t xml:space="preserve">2.50349378585815</t>
@@ -4316,13 +4316,13 @@
     <t xml:space="preserve">2.5686092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59465575218201</t>
+    <t xml:space="preserve">2.59465551376343</t>
   </si>
   <si>
     <t xml:space="preserve">2.5793342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5839307308197</t>
+    <t xml:space="preserve">2.58393049240112</t>
   </si>
   <si>
     <t xml:space="preserve">2.56477904319763</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">2.57703614234924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55405402183533</t>
+    <t xml:space="preserve">2.55405426025391</t>
   </si>
   <si>
     <t xml:space="preserve">2.62376570701599</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">2.78923535346985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77468013763428</t>
+    <t xml:space="preserve">2.77468037605286</t>
   </si>
   <si>
     <t xml:space="preserve">2.7585928440094</t>
@@ -4370,22 +4370,22 @@
     <t xml:space="preserve">2.93172311782837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89725017547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92636060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95700335502625</t>
+    <t xml:space="preserve">2.89725041389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9263608455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95700311660767</t>
   </si>
   <si>
     <t xml:space="preserve">2.99454021453857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00756335258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07038044929504</t>
+    <t xml:space="preserve">3.00756359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07038021087646</t>
   </si>
   <si>
     <t xml:space="preserve">3.09106421470642</t>
@@ -4397,25 +4397,25 @@
     <t xml:space="preserve">3.16154193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19831323623657</t>
+    <t xml:space="preserve">3.19831299781799</t>
   </si>
   <si>
     <t xml:space="preserve">3.14315676689148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22895574569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29024076461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22435927391052</t>
+    <t xml:space="preserve">3.22895550727844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29024052619934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2243595123291</t>
   </si>
   <si>
     <t xml:space="preserve">3.22052884101868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18145990371704</t>
+    <t xml:space="preserve">3.18145966529846</t>
   </si>
   <si>
     <t xml:space="preserve">3.18682217597961</t>
@@ -4424,19 +4424,19 @@
     <t xml:space="preserve">3.16767072677612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14085817337036</t>
+    <t xml:space="preserve">3.14085841178894</t>
   </si>
   <si>
     <t xml:space="preserve">3.19448280334473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22282695770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10255527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04280209541321</t>
+    <t xml:space="preserve">3.22282671928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10255551338196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04280185699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.11634421348572</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">3.05812358856201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12860131263733</t>
+    <t xml:space="preserve">3.12860155105591</t>
   </si>
   <si>
     <t xml:space="preserve">3.16001009941101</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">3.11711025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15081691741943</t>
+    <t xml:space="preserve">3.15081715583801</t>
   </si>
   <si>
     <t xml:space="preserve">3.22359323501587</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">3.23355197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17150044441223</t>
+    <t xml:space="preserve">3.17150092124939</t>
   </si>
   <si>
     <t xml:space="preserve">3.07727527618408</t>
@@ -4478,13 +4478,13 @@
     <t xml:space="preserve">2.82830452919006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88116312026978</t>
+    <t xml:space="preserve">2.8811628818512</t>
   </si>
   <si>
     <t xml:space="preserve">2.67585825920105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71186304092407</t>
+    <t xml:space="preserve">2.71186280250549</t>
   </si>
   <si>
     <t xml:space="preserve">2.70573449134827</t>
@@ -4493,13 +4493,13 @@
     <t xml:space="preserve">2.80991911888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039684295654</t>
+    <t xml:space="preserve">2.88039708137512</t>
   </si>
   <si>
     <t xml:space="preserve">2.80379056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71952342987061</t>
+    <t xml:space="preserve">2.71952366828918</t>
   </si>
   <si>
     <t xml:space="preserve">2.60691261291504</t>
@@ -4508,16 +4508,16 @@
     <t xml:space="preserve">2.63372468948364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65900444984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75782680511475</t>
+    <t xml:space="preserve">2.65900468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75782656669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.79996037483215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76165747642517</t>
+    <t xml:space="preserve">2.76165723800659</t>
   </si>
   <si>
     <t xml:space="preserve">2.77851057052612</t>
@@ -4526,13 +4526,13 @@
     <t xml:space="preserve">2.75476264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82370829582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8397958278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84132790565491</t>
+    <t xml:space="preserve">2.82370853424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83979558944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84132766723633</t>
   </si>
   <si>
     <t xml:space="preserve">2.83519911766052</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">2.93019104003906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01828813552856</t>
+    <t xml:space="preserve">3.01828837394714</t>
   </si>
   <si>
     <t xml:space="preserve">3.08033919334412</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">3.11098170280457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24427700042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31637167930603</t>
+    <t xml:space="preserve">3.24427676200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31637191772461</t>
   </si>
   <si>
     <t xml:space="preserve">3.21511483192444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03609204292297</t>
+    <t xml:space="preserve">3.03609228134155</t>
   </si>
   <si>
     <t xml:space="preserve">3.11466789245605</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">3.0109806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04905319213867</t>
+    <t xml:space="preserve">3.04905295372009</t>
   </si>
   <si>
     <t xml:space="preserve">3.27910900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1567907333374</t>
+    <t xml:space="preserve">3.15679049491882</t>
   </si>
   <si>
     <t xml:space="preserve">3.1106173992157</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.1738018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16732168197632</t>
+    <t xml:space="preserve">3.16732144355774</t>
   </si>
   <si>
     <t xml:space="preserve">3.13572931289673</t>
@@ -4610,10 +4610,10 @@
     <t xml:space="preserve">3.1584107875824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21754479408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025419235229</t>
+    <t xml:space="preserve">3.21754455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025443077087</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631563186646</t>
@@ -4625,13 +4625,13 @@
     <t xml:space="preserve">3.09441637992859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05472373962402</t>
+    <t xml:space="preserve">3.05472350120544</t>
   </si>
   <si>
     <t xml:space="preserve">3.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96318697929382</t>
+    <t xml:space="preserve">2.9631872177124</t>
   </si>
   <si>
     <t xml:space="preserve">3.03771233558655</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">3.11142754554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06768441200256</t>
+    <t xml:space="preserve">3.06768465042114</t>
   </si>
   <si>
     <t xml:space="preserve">3.11304759979248</t>
@@ -4658,13 +4658,13 @@
     <t xml:space="preserve">3.10251688957214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09198594093323</t>
+    <t xml:space="preserve">3.09198617935181</t>
   </si>
   <si>
     <t xml:space="preserve">3.14626002311707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16165137290955</t>
+    <t xml:space="preserve">3.16165113449097</t>
   </si>
   <si>
     <t xml:space="preserve">3.24508690834045</t>
@@ -4688,13 +4688,13 @@
     <t xml:space="preserve">3.22240519523621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27586936950684</t>
+    <t xml:space="preserve">3.27586913108826</t>
   </si>
   <si>
     <t xml:space="preserve">3.31070137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4022376537323</t>
+    <t xml:space="preserve">3.40223789215088</t>
   </si>
   <si>
     <t xml:space="preserve">3.44274067878723</t>
@@ -4703,16 +4703,16 @@
     <t xml:space="preserve">3.50673508644104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44031047821045</t>
+    <t xml:space="preserve">3.44031071662903</t>
   </si>
   <si>
     <t xml:space="preserve">3.44355058670044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34553384780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42005896568298</t>
+    <t xml:space="preserve">3.34553408622742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42005920410156</t>
   </si>
   <si>
     <t xml:space="preserve">3.46947264671326</t>
@@ -4730,22 +4730,22 @@
     <t xml:space="preserve">3.54075741767883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61042189598083</t>
+    <t xml:space="preserve">3.61042213439941</t>
   </si>
   <si>
     <t xml:space="preserve">3.62500309944153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58531045913696</t>
+    <t xml:space="preserve">3.58531069755554</t>
   </si>
   <si>
     <t xml:space="preserve">3.60475182533264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5942211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59503173828125</t>
+    <t xml:space="preserve">3.59422135353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59503149986267</t>
   </si>
   <si>
     <t xml:space="preserve">3.5934112071991</t>
@@ -4754,10 +4754,10 @@
     <t xml:space="preserve">3.63391423225403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63634443283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63553428649902</t>
+    <t xml:space="preserve">3.63634419441223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63553404808044</t>
   </si>
   <si>
     <t xml:space="preserve">3.68413734436035</t>
@@ -4775,10 +4775,10 @@
     <t xml:space="preserve">3.48162317276001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56505918502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2410364151001</t>
+    <t xml:space="preserve">3.56505942344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24103665351868</t>
   </si>
   <si>
     <t xml:space="preserve">3.41762900352478</t>
@@ -4799,19 +4799,19 @@
     <t xml:space="preserve">3.54480767250061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52293634414673</t>
+    <t xml:space="preserve">3.52293610572815</t>
   </si>
   <si>
     <t xml:space="preserve">3.55857872962952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5415678024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51564574241638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56667923927307</t>
+    <t xml:space="preserve">3.54156804084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5156455039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56667947769165</t>
   </si>
   <si>
     <t xml:space="preserve">3.5764000415802</t>
@@ -4823,16 +4823,16 @@
     <t xml:space="preserve">3.57720994949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54318761825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49944496154785</t>
+    <t xml:space="preserve">3.54318737983704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49944472312927</t>
   </si>
   <si>
     <t xml:space="preserve">3.46380186080933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35687470436096</t>
+    <t xml:space="preserve">3.35687494277954</t>
   </si>
   <si>
     <t xml:space="preserve">3.28883004188538</t>
@@ -4850,40 +4850,40 @@
     <t xml:space="preserve">3.48324370384216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53994727134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62743377685547</t>
+    <t xml:space="preserve">3.53994750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62743353843689</t>
   </si>
   <si>
     <t xml:space="preserve">3.70843911170959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77243375778198</t>
+    <t xml:space="preserve">3.7724335193634</t>
   </si>
   <si>
     <t xml:space="preserve">3.7521824836731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82670736312866</t>
+    <t xml:space="preserve">3.82670760154724</t>
   </si>
   <si>
     <t xml:space="preserve">3.75137233734131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6898078918457</t>
+    <t xml:space="preserve">3.68980765342712</t>
   </si>
   <si>
     <t xml:space="preserve">3.74084162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67360663414001</t>
+    <t xml:space="preserve">3.67360687255859</t>
   </si>
   <si>
     <t xml:space="preserve">3.68251729011536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66712641716003</t>
+    <t xml:space="preserve">3.66712594032288</t>
   </si>
   <si>
     <t xml:space="preserve">3.72626042366028</t>
@@ -4892,10 +4892,10 @@
     <t xml:space="preserve">3.8550591468811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74570178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84452867507935</t>
+    <t xml:space="preserve">3.74570202827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84452843666077</t>
   </si>
   <si>
     <t xml:space="preserve">3.84614896774292</t>
@@ -4904,19 +4904,19 @@
     <t xml:space="preserve">3.84776902198792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84938907623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.926344871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97818756103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97089743614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80078530311584</t>
+    <t xml:space="preserve">3.84938931465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92634463310242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97818803787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97089791297913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80078554153442</t>
   </si>
   <si>
     <t xml:space="preserve">3.8396680355072</t>
@@ -4931,19 +4931,19 @@
     <t xml:space="preserve">3.80726599693298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79349517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82589721679688</t>
+    <t xml:space="preserve">3.79349541664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82589745521545</t>
   </si>
   <si>
     <t xml:space="preserve">3.90690302848816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95793676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9417359828949</t>
+    <t xml:space="preserve">3.95793700218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94173574447632</t>
   </si>
   <si>
     <t xml:space="preserve">3.94659614562988</t>
@@ -4952,19 +4952,19 @@
     <t xml:space="preserve">3.97251749038696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94011545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99114871025085</t>
+    <t xml:space="preserve">3.94011521339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99114894866943</t>
   </si>
   <si>
     <t xml:space="preserve">4.10698747634888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.119948387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30950117111206</t>
+    <t xml:space="preserve">4.11994791030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30950164794922</t>
   </si>
   <si>
     <t xml:space="preserve">4.28357934951782</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">4.31112098693848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25279712677002</t>
+    <t xml:space="preserve">4.25279760360718</t>
   </si>
   <si>
     <t xml:space="preserve">4.27223873138428</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">4.13128900527954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642860412598</t>
+    <t xml:space="preserve">4.12642812728882</t>
   </si>
   <si>
     <t xml:space="preserve">4.08916568756104</t>
@@ -5006,16 +5006,16 @@
     <t xml:space="preserve">4.11022710800171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18637275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14100980758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15721082687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99357891082764</t>
+    <t xml:space="preserve">4.18637323379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14100933074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15721035003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99357914924622</t>
   </si>
   <si>
     <t xml:space="preserve">4.04137229919434</t>
@@ -5024,22 +5024,22 @@
     <t xml:space="preserve">4.07296466827393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05676317214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90204286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83480834960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87045049667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89961290359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84290862083435</t>
+    <t xml:space="preserve">4.05676364898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90204262733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8348081111908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.870450258255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89961266517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84290838241577</t>
   </si>
   <si>
     <t xml:space="preserve">3.81617665290833</t>
@@ -5048,13 +5048,13 @@
     <t xml:space="preserve">3.86072969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8826014995575</t>
+    <t xml:space="preserve">3.88260173797607</t>
   </si>
   <si>
     <t xml:space="preserve">3.87288093566895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94335603713989</t>
+    <t xml:space="preserve">3.94335579872131</t>
   </si>
   <si>
     <t xml:space="preserve">3.9441659450531</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">4.10374689102173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1750316619873</t>
+    <t xml:space="preserve">4.17503118515015</t>
   </si>
   <si>
     <t xml:space="preserve">4.14749002456665</t>
@@ -5072,34 +5072,34 @@
     <t xml:space="preserve">3.9457859992981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95064616203308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88422155380249</t>
+    <t xml:space="preserve">3.9506459236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88422131538391</t>
   </si>
   <si>
     <t xml:space="preserve">3.88584160804749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83318781852722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88665175437927</t>
+    <t xml:space="preserve">3.8331880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88665151596069</t>
   </si>
   <si>
     <t xml:space="preserve">3.93687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96927738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94821619987488</t>
+    <t xml:space="preserve">3.96927785873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94821572303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.01707077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87774157524109</t>
+    <t xml:space="preserve">3.87774133682251</t>
   </si>
   <si>
     <t xml:space="preserve">3.99762940406799</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">4.0745849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0681037902832</t>
+    <t xml:space="preserve">4.06810426712036</t>
   </si>
   <si>
     <t xml:space="preserve">4.08592557907104</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">4.20581388473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29978036880493</t>
+    <t xml:space="preserve">4.29978084564209</t>
   </si>
   <si>
     <t xml:space="preserve">4.13290929794312</t>
@@ -5141,7 +5141,7 @@
     <t xml:space="preserve">3.98223829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98547863960266</t>
+    <t xml:space="preserve">3.98547887802124</t>
   </si>
   <si>
     <t xml:space="preserve">3.996009349823</t>
@@ -5153,13 +5153,13 @@
     <t xml:space="preserve">4.19933366775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42614936828613</t>
+    <t xml:space="preserve">4.42614984512329</t>
   </si>
   <si>
     <t xml:space="preserve">4.47961330413818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40670824050903</t>
+    <t xml:space="preserve">4.40670776367188</t>
   </si>
   <si>
     <t xml:space="preserve">4.36782550811768</t>
@@ -5192,7 +5192,7 @@
     <t xml:space="preserve">4.54765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57682037353516</t>
+    <t xml:space="preserve">4.576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">4.61570262908936</t>
@@ -5207,16 +5207,16 @@
     <t xml:space="preserve">4.85385942459106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8489990234375</t>
+    <t xml:space="preserve">4.84899854660034</t>
   </si>
   <si>
     <t xml:space="preserve">4.88302135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95916652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01101016998291</t>
+    <t xml:space="preserve">4.95916700363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01100969314575</t>
   </si>
   <si>
     <t xml:space="preserve">4.96240663528442</t>
@@ -5237,19 +5237,19 @@
     <t xml:space="preserve">5.0709547996521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1017370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05151319503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1714015007019</t>
+    <t xml:space="preserve">5.10173654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05151271820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17140102386475</t>
   </si>
   <si>
     <t xml:space="preserve">4.98832845687866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92838430404663</t>
+    <t xml:space="preserve">4.92838478088379</t>
   </si>
   <si>
     <t xml:space="preserve">4.98670864105225</t>
@@ -5261,10 +5261,10 @@
     <t xml:space="preserve">5.06285381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14709997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17626142501831</t>
+    <t xml:space="preserve">5.14709949493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17626190185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130989074707</t>
@@ -6276,6 +6276,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.1599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1850004196167</t>
   </si>
 </sst>
 </file>
@@ -71484,7 +71487,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6500694444</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>5160843</v>
@@ -71505,6 +71508,32 @@
         <v>2087</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.651099537</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>3438289</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>12.2299995422363</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>12.0150003433228</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>12.1850004196167</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>2088</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="2090">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20737981796265</t>
+    <t xml:space="preserve">6.2073802947998</t>
   </si>
   <si>
     <t xml:space="preserve">BAMI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25302267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98423957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89802551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65459871292114</t>
+    <t xml:space="preserve">6.25302362442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98424053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89802646636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6545991897583</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89295387268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27424478530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94206857681274</t>
+    <t xml:space="preserve">5.65967178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89295434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.274245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9420690536499</t>
   </si>
   <si>
     <t xml:space="preserve">4.40450143814087</t>
@@ -80,88 +80,88 @@
     <t xml:space="preserve">4.61496448516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28785991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55410718917847</t>
+    <t xml:space="preserve">4.28786039352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55410766601562</t>
   </si>
   <si>
     <t xml:space="preserve">4.19911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95568370819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32082462310791</t>
+    <t xml:space="preserve">3.9556839466095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32082366943359</t>
   </si>
   <si>
     <t xml:space="preserve">4.57946443557739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50339412689209</t>
+    <t xml:space="preserve">4.50339365005493</t>
   </si>
   <si>
     <t xml:space="preserve">4.0520396232605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11289739608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8796124458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52715158462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22286796569824</t>
+    <t xml:space="preserve">4.11289691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961316108704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52715110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22286772727966</t>
   </si>
   <si>
     <t xml:space="preserve">3.58040118217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2685112953186</t>
+    <t xml:space="preserve">3.26851081848145</t>
   </si>
   <si>
     <t xml:space="preserve">3.64379286766052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91004157066345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04443264007568</t>
+    <t xml:space="preserve">3.91004109382629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04443216323853</t>
   </si>
   <si>
     <t xml:space="preserve">4.14332485198975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91511249542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818536758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08246803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71986389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64632868766785</t>
+    <t xml:space="preserve">3.91511297225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818560600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08246850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71986436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.646329164505</t>
   </si>
   <si>
     <t xml:space="preserve">3.74775671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84157752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92018389701843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22700214385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04950475692749</t>
+    <t xml:space="preserve">3.84157705307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9201831817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22700309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04950428009033</t>
   </si>
   <si>
     <t xml:space="preserve">3.88468432426453</t>
@@ -170,73 +170,73 @@
     <t xml:space="preserve">3.86693429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7604353427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69957852363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03682565689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807696342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38768792152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47136616706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67675709724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197177886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5144727230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38261699676514</t>
+    <t xml:space="preserve">3.76043581962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69957828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03682518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9480767250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38768815994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47136569023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67675805091858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197106361389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51447296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38261747360229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27611756324768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06565427780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365598678589</t>
+    <t xml:space="preserve">3.06565451622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365646362305</t>
   </si>
   <si>
     <t xml:space="preserve">2.70812177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49005174636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40586686134338</t>
+    <t xml:space="preserve">2.49005150794983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40586709976196</t>
   </si>
   <si>
     <t xml:space="preserve">2.2243115901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46672344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72080016136169</t>
+    <t xml:space="preserve">2.46672320365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72079992294312</t>
   </si>
   <si>
     <t xml:space="preserve">2.700514793396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91097736358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02508354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16454648971558</t>
+    <t xml:space="preserve">2.91097712516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02508330345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16454672813416</t>
   </si>
   <si>
     <t xml:space="preserve">3.22690272331238</t>
@@ -251,46 +251,46 @@
     <t xml:space="preserve">3.20092105865479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24508929252625</t>
+    <t xml:space="preserve">3.2450897693634</t>
   </si>
   <si>
     <t xml:space="preserve">3.11778020858765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23469662666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19052863121033</t>
+    <t xml:space="preserve">3.23469686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19052886962891</t>
   </si>
   <si>
     <t xml:space="preserve">3.32823038101196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20351934432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96968603134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75663709640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86835789680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72805762290955</t>
+    <t xml:space="preserve">3.20351910591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96968626976013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75663733482361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86835813522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
     <t xml:space="preserve">2.84497451782227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59607148170471</t>
+    <t xml:space="preserve">2.59607172012329</t>
   </si>
   <si>
     <t xml:space="preserve">2.51500940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28637194633484</t>
+    <t xml:space="preserve">2.28637218475342</t>
   </si>
   <si>
     <t xml:space="preserve">2.32378602027893</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">2.32274651527405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39237642288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23544836044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24584150314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22089886665344</t>
+    <t xml:space="preserve">2.39237666130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23544859886169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24584126472473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2208993434906</t>
   </si>
   <si>
     <t xml:space="preserve">2.24480175971985</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.24999761581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27493977546692</t>
+    <t xml:space="preserve">2.2749400138855</t>
   </si>
   <si>
     <t xml:space="preserve">2.47343897819519</t>
@@ -329,22 +329,22 @@
     <t xml:space="preserve">2.48902797698975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49422383308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31131458282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16581749916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16685724258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05461692810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15853548049927</t>
+    <t xml:space="preserve">2.49422407150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31131434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16581773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16685700416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05461668968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15853524208069</t>
   </si>
   <si>
     <t xml:space="preserve">2.2902045249939</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">2.0422739982605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83636558055878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7159024477005</t>
+    <t xml:space="preserve">1.83636605739594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71590256690979</t>
   </si>
   <si>
     <t xml:space="preserve">1.83776664733887</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">2.07449102401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01846170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02546525001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99324822425842</t>
+    <t xml:space="preserve">2.01846146583557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02546548843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99324834346771</t>
   </si>
   <si>
     <t xml:space="preserve">2.12211608886719</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">1.62765598297119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5268030166626</t>
+    <t xml:space="preserve">1.52680313587189</t>
   </si>
   <si>
     <t xml:space="preserve">1.55481767654419</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">1.50439131259918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50158989429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540242671967</t>
+    <t xml:space="preserve">1.50158977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540230751038</t>
   </si>
   <si>
     <t xml:space="preserve">1.45676624774933</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">1.40073680877686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31459152698517</t>
+    <t xml:space="preserve">1.31459140777588</t>
   </si>
   <si>
     <t xml:space="preserve">1.28167414665222</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57022607326508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.666876912117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55621838569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64166378974915</t>
+    <t xml:space="preserve">1.5702258348465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66687679290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55621862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64166367053986</t>
   </si>
   <si>
     <t xml:space="preserve">1.66267454624176</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">1.6878879070282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67528116703033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66407513618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72991001605988</t>
+    <t xml:space="preserve">1.67528128623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6640750169754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72990965843201</t>
   </si>
   <si>
     <t xml:space="preserve">1.70329570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71730327606201</t>
+    <t xml:space="preserve">1.71730303764343</t>
   </si>
   <si>
     <t xml:space="preserve">1.75932538509369</t>
@@ -458,28 +458,28 @@
     <t xml:space="preserve">1.76352751255035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5057920217514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49738752841949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55201637744904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63045752048492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59964144229889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59263753890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58143174648285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56882524490356</t>
+    <t xml:space="preserve">1.50579190254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49738764762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55201649665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63045740127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59964108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59263777732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58143186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56882512569427</t>
   </si>
   <si>
     <t xml:space="preserve">1.53100538253784</t>
@@ -494,34 +494,34 @@
     <t xml:space="preserve">1.48758256435394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58003091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53520750999451</t>
+    <t xml:space="preserve">1.58003115653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53520739078522</t>
   </si>
   <si>
     <t xml:space="preserve">1.51559722423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56742417812347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56182146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60384345054626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6808842420578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63886189460754</t>
+    <t xml:space="preserve">1.56742441654205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56182157993317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60384333133698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68088412284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63886177539825</t>
   </si>
   <si>
     <t xml:space="preserve">1.65707159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6584724187851</t>
+    <t xml:space="preserve">1.65847229957581</t>
   </si>
   <si>
     <t xml:space="preserve">1.6430641412735</t>
@@ -542,91 +542,91 @@
     <t xml:space="preserve">1.46657145023346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40003633499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45116341114044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47357511520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43995749950409</t>
+    <t xml:space="preserve">1.40003645420074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45116329193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47357487678528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4399573802948</t>
   </si>
   <si>
     <t xml:space="preserve">1.40633964538574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37832498550415</t>
+    <t xml:space="preserve">1.37832486629486</t>
   </si>
   <si>
     <t xml:space="preserve">1.39653444290161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40774035453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46797215938568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48057878017426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50299036502838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55061542987823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65286946296692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78593945503235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79994654655457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8461709022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8531745672226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196877479553</t>
+    <t xml:space="preserve">1.40774047374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46797204017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48057866096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50299048423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55061554908752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65286934375763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78593933582306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79994666576385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84617078304291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317480564117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196889400482</t>
   </si>
   <si>
     <t xml:space="preserve">1.82235825061798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85737669467926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86297988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041003704071</t>
+    <t xml:space="preserve">1.85737705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86297976970673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041027545929</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379596710205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80835115909576</t>
+    <t xml:space="preserve">1.80835103988647</t>
   </si>
   <si>
     <t xml:space="preserve">1.67107892036438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61224830150604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50999402999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59543919563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60664510726929</t>
+    <t xml:space="preserve">1.61224818229675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50999414920807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59543907642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60664498806</t>
   </si>
   <si>
     <t xml:space="preserve">1.5127956867218</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">1.31178998947144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32649779319763</t>
+    <t xml:space="preserve">1.32649767398834</t>
   </si>
   <si>
     <t xml:space="preserve">1.29988372325897</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">1.2508579492569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30268514156342</t>
+    <t xml:space="preserve">1.30268526077271</t>
   </si>
   <si>
     <t xml:space="preserve">1.35871458053589</t>
@@ -671,175 +671,175 @@
     <t xml:space="preserve">1.40493905544281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49458611011505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64026272296906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56462299823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53380680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.679483294487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65146863460541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72290623188019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77893555164337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310126781464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60524439811707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092089176178</t>
+    <t xml:space="preserve">1.49458634853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64026284217834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56462287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.533806681633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67948317527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69769310951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6514687538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72290635108948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77893579006195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310114860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60524427890778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092113018036</t>
   </si>
   <si>
     <t xml:space="preserve">1.87698721885681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90500211715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643947601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03106808662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95122623443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9498256444931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90640258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94702386856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89799833297729</t>
+    <t xml:space="preserve">1.90500199794769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643959522247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0310685634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95122611522675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94982552528381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90640270709991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94702422618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89799821376801</t>
   </si>
   <si>
     <t xml:space="preserve">1.94142115116119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93581795692444</t>
+    <t xml:space="preserve">1.9358184337616</t>
   </si>
   <si>
     <t xml:space="preserve">2.01706099510193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97363781929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02266383171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849835395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00585532188416</t>
+    <t xml:space="preserve">1.97363805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02266359329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849859237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00585508346558</t>
   </si>
   <si>
     <t xml:space="preserve">2.02126312255859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86017823219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8909946680069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78033649921417</t>
+    <t xml:space="preserve">1.86017858982086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89099478721619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78033638000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.67388045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74251639842987</t>
+    <t xml:space="preserve">1.74251651763916</t>
   </si>
   <si>
     <t xml:space="preserve">1.73831462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64586555957794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75512313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84056794643402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77753496170044</t>
+    <t xml:space="preserve">1.64586567878723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75512301921844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84056830406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77753508090973</t>
   </si>
   <si>
     <t xml:space="preserve">1.78173696994781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68368554115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62205302715302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51419651508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006768703461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71870386600494</t>
+    <t xml:space="preserve">1.68368566036224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6220531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51419627666473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6500678062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71870398521423</t>
   </si>
   <si>
     <t xml:space="preserve">1.71450185775757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68228483200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69349074363708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69629228115082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80975210666656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81535506248474</t>
+    <t xml:space="preserve">1.68228495121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6934906244278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69629216194153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80975186824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81535470485687</t>
   </si>
   <si>
     <t xml:space="preserve">1.76072609424591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80695033073425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86858308315277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85597634315491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91620767116547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90780341625214</t>
+    <t xml:space="preserve">1.80695044994354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86858296394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85597622394562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91620790958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90780353546143</t>
   </si>
   <si>
     <t xml:space="preserve">1.91480708122253</t>
@@ -851,148 +851,148 @@
     <t xml:space="preserve">1.88819313049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94562351703644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90360128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89939892292023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87978863716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86718225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76212692260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542860031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8615790605545</t>
+    <t xml:space="preserve">1.94562363624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9036009311676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89939868450165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87978851795197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86718213558197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76212680339813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95542848110199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86157917976379</t>
   </si>
   <si>
     <t xml:space="preserve">1.86998355388641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445437431335</t>
+    <t xml:space="preserve">2.00445413589478</t>
   </si>
   <si>
     <t xml:space="preserve">2.04647636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9190092086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87838780879974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98204267024994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96383285522461</t>
+    <t xml:space="preserve">1.91900932788849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87838792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98204231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96383261680603</t>
   </si>
   <si>
     <t xml:space="preserve">1.88259017467499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93021512031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97784042358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09410166740417</t>
+    <t xml:space="preserve">1.93021547794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97783994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09410119056702</t>
   </si>
   <si>
     <t xml:space="preserve">2.17814564704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11371159553528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12491750717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99464893341064</t>
+    <t xml:space="preserve">2.11371183395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12491774559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99464917182922</t>
   </si>
   <si>
     <t xml:space="preserve">2.00305342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90220069885254</t>
+    <t xml:space="preserve">1.90220057964325</t>
   </si>
   <si>
     <t xml:space="preserve">1.99885153770447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95262718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95402777194977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9344174861908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91060495376587</t>
+    <t xml:space="preserve">1.95262694358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95402765274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93441760540009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920436382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91060471534729</t>
   </si>
   <si>
     <t xml:space="preserve">1.88679230213165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95823013782501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94422245025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99184763431549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06048369407654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207920074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10950946807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14592862129211</t>
+    <t xml:space="preserve">1.95822989940643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94422256946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99184775352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06048393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207943916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10950970649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14592838287354</t>
   </si>
   <si>
     <t xml:space="preserve">2.0955023765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16974139213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14452791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18795108795166</t>
+    <t xml:space="preserve">2.16974115371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14452767372131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18795084953308</t>
   </si>
   <si>
     <t xml:space="preserve">2.20616054534912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20896196365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19915699958801</t>
+    <t xml:space="preserve">2.20896172523499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19915652275085</t>
   </si>
   <si>
     <t xml:space="preserve">2.19635510444641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14172649383545</t>
+    <t xml:space="preserve">2.14172673225403</t>
   </si>
   <si>
     <t xml:space="preserve">2.20335865020752</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">2.16273760795593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20756125450134</t>
+    <t xml:space="preserve">2.20756101608276</t>
   </si>
   <si>
     <t xml:space="preserve">2.22997307777405</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">2.33082604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30561256408691</t>
+    <t xml:space="preserve">2.30561280250549</t>
   </si>
   <si>
     <t xml:space="preserve">2.26499128341675</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">2.30981516838074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27339577674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32242155075073</t>
+    <t xml:space="preserve">2.27339553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32242131233215</t>
   </si>
   <si>
     <t xml:space="preserve">2.22717142105103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2607889175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22016787528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23277425765991</t>
+    <t xml:space="preserve">2.26078915596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22016763687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23277449607849</t>
   </si>
   <si>
     <t xml:space="preserve">2.26218962669373</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">2.15713453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1011049747467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305205821991</t>
+    <t xml:space="preserve">2.10110521316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13052082061768</t>
   </si>
   <si>
     <t xml:space="preserve">2.18935132026672</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">2.30141043663025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3112154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33782982826233</t>
+    <t xml:space="preserve">2.31121563911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33782958984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.28180003166199</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">2.33642888069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4344801902771</t>
+    <t xml:space="preserve">2.43448042869568</t>
   </si>
   <si>
     <t xml:space="preserve">2.45409083366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45689225196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43307948112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43027830123901</t>
+    <t xml:space="preserve">2.4568920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43307971954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43027853965759</t>
   </si>
   <si>
     <t xml:space="preserve">2.24117875099182</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">2.13192105293274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23417520523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20475959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19075226783752</t>
+    <t xml:space="preserve">2.23417496681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2047598361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1907525062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.15153169631958</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">2.20195817947388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18374872207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21456456184387</t>
+    <t xml:space="preserve">2.18374848365784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21456480026245</t>
   </si>
   <si>
     <t xml:space="preserve">2.17674493789673</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">2.09690284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10250568389893</t>
+    <t xml:space="preserve">2.10250616073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.13332223892212</t>
@@ -1166,82 +1166,82 @@
     <t xml:space="preserve">2.10810852050781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09130024909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04507565498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083628177643</t>
+    <t xml:space="preserve">2.09129977226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0450758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9708366394043</t>
   </si>
   <si>
     <t xml:space="preserve">1.9120055437088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92741394042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88959383964539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87558650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566028594971</t>
+    <t xml:space="preserve">1.9274138212204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8895937204361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8755863904953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566004753113</t>
   </si>
   <si>
     <t xml:space="preserve">1.97924101352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96943593025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92321157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96523356437683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181086540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83496475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76492810249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.752321600914</t>
+    <t xml:space="preserve">1.96943581104279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92321145534515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96523344516754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9218111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83496499061584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76492822170258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75232183933258</t>
   </si>
   <si>
     <t xml:space="preserve">1.77193200588226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78313779830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82656097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86438035964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395423412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86578118801117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84897267818451</t>
+    <t xml:space="preserve">1.78313791751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8265608549118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86438059806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177397727966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395387649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86578154563904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84897243976593</t>
   </si>
   <si>
     <t xml:space="preserve">1.8839910030365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99745059013367</t>
+    <t xml:space="preserve">1.99745070934296</t>
   </si>
   <si>
     <t xml:space="preserve">2.04787731170654</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">2.04367470741272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99605000019073</t>
+    <t xml:space="preserve">1.99604988098145</t>
   </si>
   <si>
     <t xml:space="preserve">2.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11931490898132</t>
+    <t xml:space="preserve">2.11931467056274</t>
   </si>
   <si>
     <t xml:space="preserve">2.15013098716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17114210128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18725061416626</t>
+    <t xml:space="preserve">2.17114186286926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18725037574768</t>
   </si>
   <si>
     <t xml:space="preserve">2.12701869010925</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">2.0282666683197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04927778244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363264083862</t>
+    <t xml:space="preserve">2.04927802085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1536328792572</t>
   </si>
   <si>
     <t xml:space="preserve">2.16028642654419</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">2.03772163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1172137260437</t>
+    <t xml:space="preserve">2.11721348762512</t>
   </si>
   <si>
     <t xml:space="preserve">2.0800940990448</t>
@@ -1307,22 +1307,22 @@
     <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12736868858337</t>
+    <t xml:space="preserve">2.12736892700195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18584966659546</t>
+    <t xml:space="preserve">2.18584990501404</t>
   </si>
   <si>
     <t xml:space="preserve">2.14207673072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425368309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19005179405212</t>
+    <t xml:space="preserve">2.19425415992737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19005227088928</t>
   </si>
   <si>
     <t xml:space="preserve">2.2030086517334</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">2.1886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01005697250366</t>
+    <t xml:space="preserve">2.01005744934082</t>
   </si>
   <si>
     <t xml:space="preserve">2.08709764480591</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">2.12771916389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07624197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0664370059967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11441206932068</t>
+    <t xml:space="preserve">2.07624220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06643676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11441230773926</t>
   </si>
   <si>
     <t xml:space="preserve">2.08394622802734</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">1.9634827375412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98274314403534</t>
+    <t xml:space="preserve">1.98274302482605</t>
   </si>
   <si>
     <t xml:space="preserve">1.98729526996613</t>
@@ -1376,31 +1376,31 @@
     <t xml:space="preserve">1.97293758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96838521957397</t>
+    <t xml:space="preserve">1.96838533878326</t>
   </si>
   <si>
     <t xml:space="preserve">1.94107091426849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03421974182129</t>
+    <t xml:space="preserve">2.03421998023987</t>
   </si>
   <si>
     <t xml:space="preserve">2.00620532035828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01601028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03491997718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10915946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10775852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14382767677307</t>
+    <t xml:space="preserve">2.01601052284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03492045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10915899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10775828361511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14382743835449</t>
   </si>
   <si>
     <t xml:space="preserve">2.12421727180481</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">2.14662909507751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11791396141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15888595581055</t>
+    <t xml:space="preserve">2.11791372299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15888524055481</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857483863831</t>
@@ -1421,124 +1421,124 @@
     <t xml:space="preserve">2.14487814903259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08289575576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14347720146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453085899353</t>
+    <t xml:space="preserve">2.08289527893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14347743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453038215637</t>
   </si>
   <si>
     <t xml:space="preserve">2.07028913497925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09970450401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8608785867691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8752361536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84442007541656</t>
+    <t xml:space="preserve">2.09970426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86087882518768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87523639202118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84442031383514</t>
   </si>
   <si>
     <t xml:space="preserve">1.82165825366974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57687950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47077345848083</t>
+    <t xml:space="preserve">1.57687926292419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47077357769012</t>
   </si>
   <si>
     <t xml:space="preserve">1.51839864253998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55446767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578672409058</t>
+    <t xml:space="preserve">1.55446755886078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578696250916</t>
   </si>
   <si>
     <t xml:space="preserve">1.63641047477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59648954868317</t>
+    <t xml:space="preserve">1.59648978710175</t>
   </si>
   <si>
     <t xml:space="preserve">1.6801837682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61259841918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71170020103455</t>
+    <t xml:space="preserve">1.61259829998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71170043945312</t>
   </si>
   <si>
     <t xml:space="preserve">1.69874346256256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72465717792511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69138967990875</t>
+    <t xml:space="preserve">1.72465705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69138956069946</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808258533478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81990718841553</t>
+    <t xml:space="preserve">1.81990706920624</t>
   </si>
   <si>
     <t xml:space="preserve">1.78804051876068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84792184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78068673610687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73481273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70364606380463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77403318881989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80589973926544</t>
+    <t xml:space="preserve">1.84792160987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068649768829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73481249809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70364582538605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7740330696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80590009689331</t>
   </si>
   <si>
     <t xml:space="preserve">1.82586050033569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87173438072205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274573326111</t>
+    <t xml:space="preserve">1.87173449993134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274549484253</t>
   </si>
   <si>
     <t xml:space="preserve">1.87243485450745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8682324886322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85912799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83286416530609</t>
+    <t xml:space="preserve">1.86823272705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85912775993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8328640460968</t>
   </si>
   <si>
     <t xml:space="preserve">1.81605529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85072326660156</t>
+    <t xml:space="preserve">1.85072338581085</t>
   </si>
   <si>
     <t xml:space="preserve">1.83601582050323</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">1.85807716846466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85387527942657</t>
+    <t xml:space="preserve">1.853875041008</t>
   </si>
   <si>
     <t xml:space="preserve">1.76807987689972</t>
@@ -1556,28 +1556,28 @@
     <t xml:space="preserve">1.75337219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64901733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64621603488922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65216910839081</t>
+    <t xml:space="preserve">1.64901745319366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64621615409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337478160858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65216898918152</t>
   </si>
   <si>
     <t xml:space="preserve">1.61960184574127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5709263086319</t>
+    <t xml:space="preserve">1.57092618942261</t>
   </si>
   <si>
     <t xml:space="preserve">1.53030490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46972298622131</t>
+    <t xml:space="preserve">1.4697231054306</t>
   </si>
   <si>
     <t xml:space="preserve">1.42630016803741</t>
@@ -1586,46 +1586,46 @@
     <t xml:space="preserve">1.42524969577789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45501530170441</t>
+    <t xml:space="preserve">1.4550154209137</t>
   </si>
   <si>
     <t xml:space="preserve">1.44380939006805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43190336227417</t>
+    <t xml:space="preserve">1.43190312385559</t>
   </si>
   <si>
     <t xml:space="preserve">1.44415950775146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43925714492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40704023838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40178716182709</t>
+    <t xml:space="preserve">1.43925702571869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40704011917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120276927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40178728103638</t>
   </si>
   <si>
     <t xml:space="preserve">1.358154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37132132053375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50719285011292</t>
+    <t xml:space="preserve">1.37132120132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50719273090363</t>
   </si>
   <si>
     <t xml:space="preserve">1.49493634700775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54326176643372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53555774688721</t>
+    <t xml:space="preserve">1.54326188564301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53555762767792</t>
   </si>
   <si>
     <t xml:space="preserve">1.55026531219482</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">1.61084723472595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61539971828461</t>
+    <t xml:space="preserve">1.61539959907532</t>
   </si>
   <si>
     <t xml:space="preserve">1.61609995365143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62625527381897</t>
+    <t xml:space="preserve">1.62625539302826</t>
   </si>
   <si>
     <t xml:space="preserve">1.62415421009064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61715054512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64446496963501</t>
+    <t xml:space="preserve">1.61715078353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64446485042572</t>
   </si>
   <si>
     <t xml:space="preserve">1.64866709709167</t>
@@ -1676,151 +1676,151 @@
     <t xml:space="preserve">1.29638183116913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31108951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3052065372467</t>
+    <t xml:space="preserve">1.31108963489532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30520641803741</t>
   </si>
   <si>
     <t xml:space="preserve">1.31136977672577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3166925907135</t>
+    <t xml:space="preserve">1.31669247150421</t>
   </si>
   <si>
     <t xml:space="preserve">1.30758774280548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29960346221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22550463676453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2067346572876</t>
+    <t xml:space="preserve">1.29960370063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22550439834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20673477649689</t>
   </si>
   <si>
     <t xml:space="preserve">1.1690548658371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14692318439484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09229457378387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134445667267</t>
+    <t xml:space="preserve">1.14692330360413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09229445457458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134457588196</t>
   </si>
   <si>
     <t xml:space="preserve">1.08977317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14440190792084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16345191001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16331195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19608914852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23965191841125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21317803859711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2241039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25478005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28139400482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27046835422516</t>
+    <t xml:space="preserve">1.14440178871155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16345202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16331171989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19608926773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23965203762054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21317791938782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22410380840302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25477993488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29217970371246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28139388561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27046823501587</t>
   </si>
   <si>
     <t xml:space="preserve">1.26640617847443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23923182487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22606492042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256290912628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26262414455414</t>
+    <t xml:space="preserve">1.23923170566559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22606480121613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256302833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26262402534485</t>
   </si>
   <si>
     <t xml:space="preserve">1.19412803649902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28517615795135</t>
+    <t xml:space="preserve">1.28517591953278</t>
   </si>
   <si>
     <t xml:space="preserve">1.32341611385345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38770985603333</t>
+    <t xml:space="preserve">1.38770997524261</t>
   </si>
   <si>
     <t xml:space="preserve">1.41194260120392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47392535209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147405147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.448361992836</t>
+    <t xml:space="preserve">1.47392511367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147393226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836175441742</t>
   </si>
   <si>
     <t xml:space="preserve">1.53940963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54571294784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55796945095062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47917795181274</t>
+    <t xml:space="preserve">1.54571306705475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55796933174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47917807102203</t>
   </si>
   <si>
     <t xml:space="preserve">1.46376991271973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4480117559433</t>
+    <t xml:space="preserve">1.44801163673401</t>
   </si>
   <si>
     <t xml:space="preserve">1.48478090763092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49913847446442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47007310390472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44345915317535</t>
+    <t xml:space="preserve">1.49913859367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47007322311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44345927238464</t>
   </si>
   <si>
     <t xml:space="preserve">1.4045889377594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39401316642761</t>
+    <t xml:space="preserve">1.39401304721832</t>
   </si>
   <si>
     <t xml:space="preserve">1.43155288696289</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">1.39443349838257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35605323314667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32285583019257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39177215099335</t>
+    <t xml:space="preserve">1.35605311393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32285571098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39177203178406</t>
   </si>
   <si>
     <t xml:space="preserve">1.37118124961853</t>
@@ -1844,43 +1844,43 @@
     <t xml:space="preserve">1.43330383300781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44170820713043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41509413719177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209792137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42454922199249</t>
+    <t xml:space="preserve">1.44170832633972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41509425640106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209804058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42454934120178</t>
   </si>
   <si>
     <t xml:space="preserve">1.38224709033966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34918975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29344034194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33168029785156</t>
+    <t xml:space="preserve">1.34918963909149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29344046115875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33168041706085</t>
   </si>
   <si>
     <t xml:space="preserve">1.32551729679108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3005838394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29484105110168</t>
+    <t xml:space="preserve">1.30058407783508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2948409318924</t>
   </si>
   <si>
     <t xml:space="preserve">1.25996267795563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26864743232727</t>
+    <t xml:space="preserve">1.26864731311798</t>
   </si>
   <si>
     <t xml:space="preserve">1.24721598625183</t>
@@ -1889,16 +1889,16 @@
     <t xml:space="preserve">1.27845239639282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26206386089325</t>
+    <t xml:space="preserve">1.26206374168396</t>
   </si>
   <si>
     <t xml:space="preserve">1.24917697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24525499343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18474304676056</t>
+    <t xml:space="preserve">1.24525511264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474316596985</t>
   </si>
   <si>
     <t xml:space="preserve">1.1518257856369</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">1.19342768192291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21892106533051</t>
+    <t xml:space="preserve">1.21892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">1.2291464805603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20897579193115</t>
+    <t xml:space="preserve">1.20897591114044</t>
   </si>
   <si>
     <t xml:space="preserve">1.29400062561035</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">1.3185133934021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31417107582092</t>
+    <t xml:space="preserve">1.31417119503021</t>
   </si>
   <si>
     <t xml:space="preserve">1.2770516872406</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">1.37706434726715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969519615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32775843143463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147314786911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36011528968811</t>
+    <t xml:space="preserve">1.35969507694244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32775831222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31473159790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3601154088974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40879094600677</t>
@@ -1955,16 +1955,16 @@
     <t xml:space="preserve">1.47287464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49318540096283</t>
+    <t xml:space="preserve">1.49318528175354</t>
   </si>
   <si>
     <t xml:space="preserve">1.46412014961243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43505477905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41544437408447</t>
+    <t xml:space="preserve">1.43505489826202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41544425487518</t>
   </si>
   <si>
     <t xml:space="preserve">1.37566351890564</t>
@@ -1976,34 +1976,34 @@
     <t xml:space="preserve">1.35675358772278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34372663497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4031879901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37720441818237</t>
+    <t xml:space="preserve">1.34372675418854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40318810939789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37720429897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3914920091629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38112652301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32103490829468</t>
+    <t xml:space="preserve">1.39149177074432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38112640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32103478908539</t>
   </si>
   <si>
     <t xml:space="preserve">1.30296528339386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28615653514862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32019436359406</t>
+    <t xml:space="preserve">1.28615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32019424438477</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937804698944</t>
@@ -2021,19 +2021,19 @@
     <t xml:space="preserve">1.359414935112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36606848239899</t>
+    <t xml:space="preserve">1.36606860160828</t>
   </si>
   <si>
     <t xml:space="preserve">1.36641871929169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37587368488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37727451324463</t>
+    <t xml:space="preserve">1.36221659183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37587380409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37727439403534</t>
   </si>
   <si>
     <t xml:space="preserve">1.37622380256653</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">1.43855667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49178457260132</t>
+    <t xml:space="preserve">1.4917848110199</t>
   </si>
   <si>
     <t xml:space="preserve">1.48127901554108</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">1.44205856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38077640533447</t>
+    <t xml:space="preserve">1.38077616691589</t>
   </si>
   <si>
     <t xml:space="preserve">1.38532865047455</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">1.27221918106079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24595522880554</t>
+    <t xml:space="preserve">1.24595546722412</t>
   </si>
   <si>
     <t xml:space="preserve">1.1997309923172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19062626361847</t>
+    <t xml:space="preserve">1.19062638282776</t>
   </si>
   <si>
     <t xml:space="preserve">1.19798004627228</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">1.20918607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19587898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18082106113434</t>
+    <t xml:space="preserve">1.19587886333466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18082118034363</t>
   </si>
   <si>
     <t xml:space="preserve">1.15525770187378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1717164516449</t>
+    <t xml:space="preserve">1.17171609401703</t>
   </si>
   <si>
     <t xml:space="preserve">1.14370155334473</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">1.13914906978607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14930438995361</t>
+    <t xml:space="preserve">1.1493045091629</t>
   </si>
   <si>
     <t xml:space="preserve">1.16261148452759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15350663661957</t>
+    <t xml:space="preserve">1.15350675582886</t>
   </si>
   <si>
     <t xml:space="preserve">1.19377779960632</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">1.1710159778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1570086479187</t>
+    <t xml:space="preserve">1.15700852870941</t>
   </si>
   <si>
     <t xml:space="preserve">1.20323288440704</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">1.25365936756134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24560511112213</t>
+    <t xml:space="preserve">1.24560523033142</t>
   </si>
   <si>
     <t xml:space="preserve">1.23790121078491</t>
@@ -2153,25 +2153,25 @@
     <t xml:space="preserve">1.23474943637848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24875676631927</t>
+    <t xml:space="preserve">1.24875688552856</t>
   </si>
   <si>
     <t xml:space="preserve">1.26451504230499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24105274677277</t>
+    <t xml:space="preserve">1.24105262756348</t>
   </si>
   <si>
     <t xml:space="preserve">1.23825132846832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31949388980865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36256670951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36992049217224</t>
+    <t xml:space="preserve">1.31949400901794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36256682872772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36992061138153</t>
   </si>
   <si>
     <t xml:space="preserve">1.33525240421295</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">1.32264566421509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33350133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33630275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34295642375946</t>
+    <t xml:space="preserve">1.33350145816803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33630287647247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34295654296875</t>
   </si>
   <si>
     <t xml:space="preserve">1.31214010715485</t>
@@ -2198,19 +2198,19 @@
     <t xml:space="preserve">1.32439661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914377212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22634506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23159766197205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23720073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23124754428864</t>
+    <t xml:space="preserve">1.31914365291595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22634494304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23159778118134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2372008562088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23124766349792</t>
   </si>
   <si>
     <t xml:space="preserve">1.21163737773895</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">1.17241680622101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18222188949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18817484378815</t>
+    <t xml:space="preserve">1.18222165107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18817496299744</t>
   </si>
   <si>
     <t xml:space="preserve">1.18467307090759</t>
@@ -2243,34 +2243,34 @@
     <t xml:space="preserve">1.13529717922211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18047094345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13424670696259</t>
+    <t xml:space="preserve">1.18047106266022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1342465877533</t>
   </si>
   <si>
     <t xml:space="preserve">1.18012070655823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2060341835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17521822452545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18992602825165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21583950519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21653974056244</t>
+    <t xml:space="preserve">1.20603430271149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17521798610687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18992590904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21583938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21653985977173</t>
   </si>
   <si>
     <t xml:space="preserve">1.23404896259308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27467036247253</t>
+    <t xml:space="preserve">1.27467060089111</t>
   </si>
   <si>
     <t xml:space="preserve">1.286576628685</t>
@@ -2282,31 +2282,31 @@
     <t xml:space="preserve">1.28132390975952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2718688249588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26906752586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30548667907715</t>
+    <t xml:space="preserve">1.27186906337738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26906740665436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30548655986786</t>
   </si>
   <si>
     <t xml:space="preserve">1.32474684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31844341754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35171103477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31424129009247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34050500392914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36816954612732</t>
+    <t xml:space="preserve">1.31844353675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3517107963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31424117088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34050512313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36816966533661</t>
   </si>
   <si>
     <t xml:space="preserve">1.35066032409668</t>
@@ -2318,19 +2318,19 @@
     <t xml:space="preserve">1.31003904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33980464935303</t>
+    <t xml:space="preserve">1.33980476856232</t>
   </si>
   <si>
     <t xml:space="preserve">1.33210051059723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29007840156555</t>
+    <t xml:space="preserve">1.29007863998413</t>
   </si>
   <si>
     <t xml:space="preserve">1.27081847190857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27537071704865</t>
+    <t xml:space="preserve">1.27537083625793</t>
   </si>
   <si>
     <t xml:space="preserve">1.28762722015381</t>
@@ -2339,67 +2339,67 @@
     <t xml:space="preserve">1.31249034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32789838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28307485580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30968880653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42384898662567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50929367542267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50859332084656</t>
+    <t xml:space="preserve">1.32789850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28307497501373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3096889257431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42384874820709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50929379463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50859344005585</t>
   </si>
   <si>
     <t xml:space="preserve">1.49598681926727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47707688808441</t>
+    <t xml:space="preserve">1.47707676887512</t>
   </si>
   <si>
     <t xml:space="preserve">1.4686723947525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42314851284027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42665016651154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47777724266052</t>
+    <t xml:space="preserve">1.42314863204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42665040493011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47777712345123</t>
   </si>
   <si>
     <t xml:space="preserve">1.49528658390045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49388563632965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44766139984131</t>
+    <t xml:space="preserve">1.49388551712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44766128063202</t>
   </si>
   <si>
     <t xml:space="preserve">1.42104756832123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41264295578003</t>
+    <t xml:space="preserve">1.41264307498932</t>
   </si>
   <si>
     <t xml:space="preserve">1.41754555702209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41614484786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44135808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536541938782</t>
+    <t xml:space="preserve">1.41614496707916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44135797023773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536553859711</t>
   </si>
   <si>
     <t xml:space="preserve">1.46517062187195</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">1.4182460308075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38813006877899</t>
+    <t xml:space="preserve">1.38813018798828</t>
   </si>
   <si>
     <t xml:space="preserve">1.3741227388382</t>
@@ -2420,28 +2420,28 @@
     <t xml:space="preserve">1.41474401950836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4035382270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40984165668488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45326447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42034709453583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36851978302002</t>
+    <t xml:space="preserve">1.40353810787201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4098414182663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45326435565948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42034721374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36851990222931</t>
   </si>
   <si>
     <t xml:space="preserve">1.37797474861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38637912273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4616687297821</t>
+    <t xml:space="preserve">1.38637924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46166861057281</t>
   </si>
   <si>
     <t xml:space="preserve">1.42594993114471</t>
@@ -2462,103 +2462,103 @@
     <t xml:space="preserve">1.39373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36431765556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29568159580231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35836446285248</t>
+    <t xml:space="preserve">1.36431741714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29568147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35836434364319</t>
   </si>
   <si>
     <t xml:space="preserve">1.37307226657867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727180480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52049958705902</t>
+    <t xml:space="preserve">1.46727192401886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52049970626831</t>
   </si>
   <si>
     <t xml:space="preserve">1.54641330242157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72010481357574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626069068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3884801864624</t>
+    <t xml:space="preserve">1.72010457515717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626080989838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38848030567169</t>
   </si>
   <si>
     <t xml:space="preserve">1.30128443241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14230096340179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09397554397583</t>
+    <t xml:space="preserve">1.1423008441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09397542476654</t>
   </si>
   <si>
     <t xml:space="preserve">1.05755627155304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905926525592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861102938652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926937639713287</t>
+    <t xml:space="preserve">0.905926465988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861102998256683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926937520503998</t>
   </si>
   <si>
     <t xml:space="preserve">0.772156119346619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88841724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818030297756195</t>
+    <t xml:space="preserve">0.888417303562164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81803023815155</t>
   </si>
   <si>
     <t xml:space="preserve">0.874409914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874760091304779</t>
+    <t xml:space="preserve">0.874760031700134</t>
   </si>
   <si>
     <t xml:space="preserve">0.885966002941132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877561569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870207726955414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926587283611298</t>
+    <t xml:space="preserve">0.877561509609222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870207786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926587402820587</t>
   </si>
   <si>
     <t xml:space="preserve">0.912930250167847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925887107849121</t>
+    <t xml:space="preserve">0.925886988639832</t>
   </si>
   <si>
     <t xml:space="preserve">0.880713284015656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84919673204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8404421210289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633193969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846044957637787</t>
+    <t xml:space="preserve">0.849196672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840442061424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633253574371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846044898033142</t>
   </si>
   <si>
     <t xml:space="preserve">0.83098703622818</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">0.829936444759369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853048622608185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820131361484528</t>
+    <t xml:space="preserve">0.853048801422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820131421089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.777408838272095</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">0.778459489345551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778809666633606</t>
+    <t xml:space="preserve">0.778809607028961</t>
   </si>
   <si>
     <t xml:space="preserve">0.753246188163757</t>
@@ -2597,40 +2597,40 @@
     <t xml:space="preserve">0.743791282176971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768304228782654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789665341377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809625864028931</t>
+    <t xml:space="preserve">0.768304109573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789665281772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809625804424286</t>
   </si>
   <si>
     <t xml:space="preserve">0.779860198497772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766553223133087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611144542694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776008188724518</t>
+    <t xml:space="preserve">0.766553103923798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611084938049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776008248329163</t>
   </si>
   <si>
     <t xml:space="preserve">0.765152454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803672611713409</t>
+    <t xml:space="preserve">0.803672730922699</t>
   </si>
   <si>
     <t xml:space="preserve">0.812077105045319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807874917984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785463154315948</t>
+    <t xml:space="preserve">0.807874858379364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785463094711304</t>
   </si>
   <si>
     <t xml:space="preserve">0.781260967254639</t>
@@ -2645,61 +2645,61 @@
     <t xml:space="preserve">0.756047606468201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730484247207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736087203025818</t>
+    <t xml:space="preserve">0.730484127998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736087143421173</t>
   </si>
   <si>
     <t xml:space="preserve">0.743441045284271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779159784317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815228760242462</t>
+    <t xml:space="preserve">0.779159724712372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815228700637817</t>
   </si>
   <si>
     <t xml:space="preserve">0.805773854255676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858301520347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872308731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892969727516174</t>
+    <t xml:space="preserve">0.858301401138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872308671474457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89296966791153</t>
   </si>
   <si>
     <t xml:space="preserve">0.931840062141418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994873404502869</t>
+    <t xml:space="preserve">0.99487316608429</t>
   </si>
   <si>
     <t xml:space="preserve">1.00853049755096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979115068912506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966858446598053</t>
+    <t xml:space="preserve">0.979114949703217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966858625411987</t>
   </si>
   <si>
     <t xml:space="preserve">0.891218721866608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895070850849152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901724278926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967908978462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96440726518631</t>
+    <t xml:space="preserve">0.895070791244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901724338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967909216880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964407205581665</t>
   </si>
   <si>
     <t xml:space="preserve">0.946897983551025</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">0.938493609428406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965107560157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913980782032013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934641540050507</t>
+    <t xml:space="preserve">0.96510773897171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913980722427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934641659259796</t>
   </si>
   <si>
     <t xml:space="preserve">0.899623155593872</t>
@@ -2726,43 +2726,43 @@
     <t xml:space="preserve">0.953551590442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930089116096497</t>
+    <t xml:space="preserve">0.930089294910431</t>
   </si>
   <si>
     <t xml:space="preserve">0.909078121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954602003097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943746387958527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983317196369171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97316187620163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951450526714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916432082653046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93394136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948298811912537</t>
+    <t xml:space="preserve">0.954602181911469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943746268749237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983317255973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973161995410919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95145046710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916432023048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933941185474396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948298692703247</t>
   </si>
   <si>
     <t xml:space="preserve">0.957403540611267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973511934280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980866014957428</t>
+    <t xml:space="preserve">0.97351211309433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980865836143494</t>
   </si>
   <si>
     <t xml:space="preserve">1.033043384552</t>
@@ -2771,37 +2771,37 @@
     <t xml:space="preserve">1.03759574890137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00012600421906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998725295066833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960905432701111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967208743095398</t>
+    <t xml:space="preserve">1.00012624263763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998725354671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9609055519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967208802700043</t>
   </si>
   <si>
     <t xml:space="preserve">0.944096565246582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89367002248764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890168249607086</t>
+    <t xml:space="preserve">0.893670082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890168190002441</t>
   </si>
   <si>
     <t xml:space="preserve">0.874059736728668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913280487060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927637815475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907677531242371</t>
+    <t xml:space="preserve">0.913280427455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927637994289398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907677352428436</t>
   </si>
   <si>
     <t xml:space="preserve">0.890868484973907</t>
@@ -2816,55 +2816,55 @@
     <t xml:space="preserve">0.971060812473297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00572907924652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997324466705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981566250324249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00923085212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986818909645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987519323825836</t>
+    <t xml:space="preserve">1.00572896003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997324585914612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981566190719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00923073291779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98681902885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987519383430481</t>
   </si>
   <si>
     <t xml:space="preserve">1.00712966918945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996624112129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999775826931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00467836856842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988920211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985768496990204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970360338687897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958103835582733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994523048400879</t>
+    <t xml:space="preserve">0.996624171733856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999775946140289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00467848777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988919973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985768616199493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970360398292542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958103954792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994522929191589</t>
   </si>
   <si>
     <t xml:space="preserve">0.978414535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98611855506897</t>
+    <t xml:space="preserve">0.986118614673615</t>
   </si>
   <si>
     <t xml:space="preserve">1.03724551200867</t>
@@ -2873,103 +2873,103 @@
     <t xml:space="preserve">1.02148723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01903593540192</t>
+    <t xml:space="preserve">1.01903605461121</t>
   </si>
   <si>
     <t xml:space="preserve">1.01203238964081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995573580265045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973862171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916782259941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922735393047333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888067007064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939544141292572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961605787277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972811758518219</t>
+    <t xml:space="preserve">0.99557363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973862290382385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916782200336456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922735333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888067185878754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939544200897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961605727672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972811818122864</t>
   </si>
   <si>
     <t xml:space="preserve">1.05405426025391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11113452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09957849979401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16121077537537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.185023188591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16961526870728</t>
+    <t xml:space="preserve">1.11113440990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09957826137543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16121065616608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18502342700958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1696150302887</t>
   </si>
   <si>
     <t xml:space="preserve">1.15910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12339079380035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12829339504242</t>
+    <t xml:space="preserve">1.12339091300964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12829351425171</t>
   </si>
   <si>
     <t xml:space="preserve">1.1279433965683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16016006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13564729690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1706657409668</t>
+    <t xml:space="preserve">1.16016018390656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13564741611481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17066562175751</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545238018036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15280628204346</t>
+    <t xml:space="preserve">1.15280640125275</t>
   </si>
   <si>
     <t xml:space="preserve">1.17591845989227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1556077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13214552402496</t>
+    <t xml:space="preserve">1.15560781955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13214540481567</t>
   </si>
   <si>
     <t xml:space="preserve">1.08522081375122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965745449066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08627140522003</t>
+    <t xml:space="preserve">1.05965733528137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08627128601074</t>
   </si>
   <si>
     <t xml:space="preserve">1.12899386882782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15000474452972</t>
+    <t xml:space="preserve">1.1500049829483</t>
   </si>
   <si>
     <t xml:space="preserve">1.15210592746735</t>
@@ -2981,34 +2981,34 @@
     <t xml:space="preserve">1.15455734729767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066291332245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2512081861496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25611066818237</t>
+    <t xml:space="preserve">1.26066303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25120806694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25611054897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30793786048889</t>
+    <t xml:space="preserve">1.30793797969818</t>
   </si>
   <si>
     <t xml:space="preserve">1.32684791088104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35801422595978</t>
+    <t xml:space="preserve">1.35801434516907</t>
   </si>
   <si>
     <t xml:space="preserve">1.32334613800049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31879353523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29603171348572</t>
+    <t xml:space="preserve">1.31879365444183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29603159427643</t>
   </si>
   <si>
     <t xml:space="preserve">1.31389117240906</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">1.28482580184937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28027331829071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26941764354706</t>
+    <t xml:space="preserve">1.2802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26941752433777</t>
   </si>
   <si>
     <t xml:space="preserve">1.2431538105011</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">1.25435972213745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27256941795349</t>
+    <t xml:space="preserve">1.2725692987442</t>
   </si>
   <si>
     <t xml:space="preserve">1.26136338710785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26661622524261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26416480541229</t>
+    <t xml:space="preserve">1.26661610603333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26416492462158</t>
   </si>
   <si>
     <t xml:space="preserve">1.26521551609039</t>
@@ -3053,40 +3053,40 @@
     <t xml:space="preserve">1.26766681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2662661075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2585620880127</t>
+    <t xml:space="preserve">1.26626598834991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25856196880341</t>
   </si>
   <si>
     <t xml:space="preserve">1.25821185112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3296492099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957025527954</t>
+    <t xml:space="preserve">1.32964932918549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957049369812</t>
   </si>
   <si>
     <t xml:space="preserve">1.34505748748779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34925973415375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33455204963684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31529176235199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31809318065643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31073939800262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31774306297302</t>
+    <t xml:space="preserve">1.34925961494446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33455193042755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31529188156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31809306144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31073951721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31774294376373</t>
   </si>
   <si>
     <t xml:space="preserve">1.2806236743927</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">1.24735617637634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26696646213531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25015735626221</t>
+    <t xml:space="preserve">1.26696622371674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25015759468079</t>
   </si>
   <si>
     <t xml:space="preserve">1.29112911224365</t>
@@ -3110,37 +3110,37 @@
     <t xml:space="preserve">1.29953348636627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34820914268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42174792289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52260088920593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190053462982</t>
+    <t xml:space="preserve">1.34820902347565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42174780368805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52260076999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190065383911</t>
   </si>
   <si>
     <t xml:space="preserve">1.53240597248077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49808776378632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48898327350616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50088942050934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51629757881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50789332389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5197993516922</t>
+    <t xml:space="preserve">1.49808788299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4889829158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50088930130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51629745960236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50789320468903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51979947090149</t>
   </si>
   <si>
     <t xml:space="preserve">1.54851448535919</t>
@@ -3149,64 +3149,64 @@
     <t xml:space="preserve">1.54361188411713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60594463348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62695574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6206521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59053647518158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59193730354309</t>
+    <t xml:space="preserve">1.60594475269318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62695562839508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62065267562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59053659439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59193742275238</t>
   </si>
   <si>
     <t xml:space="preserve">1.69909381866455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70119452476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7236065864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71029961109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70469653606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71100032329559</t>
+    <t xml:space="preserve">1.70119476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72360646724701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7102997303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70469641685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7110002040863</t>
   </si>
   <si>
     <t xml:space="preserve">1.74881982803345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70539700984955</t>
+    <t xml:space="preserve">1.70539689064026</t>
   </si>
   <si>
     <t xml:space="preserve">1.68998873233795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65356969833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63536024093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6493673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63466000556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62835657596588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6654759645462</t>
+    <t xml:space="preserve">1.65356993675232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63536012172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64936745166779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63465988636017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6283563375473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66547620296478</t>
   </si>
   <si>
     <t xml:space="preserve">1.71505236625671</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">1.61877381801605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5993744134903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6130256652832</t>
+    <t xml:space="preserve">1.59937429428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61302578449249</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308478355408</t>
@@ -3227,67 +3227,67 @@
     <t xml:space="preserve">1.65613555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67337942123413</t>
+    <t xml:space="preserve">1.67337954044342</t>
   </si>
   <si>
     <t xml:space="preserve">1.71936321258545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71289670467377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70283782482147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73445165157318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71145987510681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74522912502289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76822090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81707894802094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83504116535187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85587775707245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86449980735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95934128761292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97299289703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98377013206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94066047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96508884429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99742150306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02400588989258</t>
+    <t xml:space="preserve">1.71289706230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70283770561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73445177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71145975589752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74522924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893961429596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76822113990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81707918643951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83504128456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85587763786316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8644996881485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126095294952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95934152603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97299253940582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98377025127411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94066035747528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96508944034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99742162227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02400612831116</t>
   </si>
   <si>
     <t xml:space="preserve">2.03334641456604</t>
@@ -3296,10 +3296,10 @@
     <t xml:space="preserve">2.08579683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08795237541199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10375881195068</t>
+    <t xml:space="preserve">2.08795213699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10375905036926</t>
   </si>
   <si>
     <t xml:space="preserve">2.12531423568726</t>
@@ -3308,10 +3308,10 @@
     <t xml:space="preserve">2.13465452194214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1540539264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15189838409424</t>
+    <t xml:space="preserve">2.15405416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15189814567566</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423080444336</t>
@@ -3320,28 +3320,28 @@
     <t xml:space="preserve">2.17201638221741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17991971969604</t>
+    <t xml:space="preserve">2.17991995811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.17560887336731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17632746696472</t>
+    <t xml:space="preserve">2.17632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">2.16052055358887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12818789482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08938932418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076691627502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05346465110779</t>
+    <t xml:space="preserve">2.12818813323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08938884735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076739311218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05346441268921</t>
   </si>
   <si>
     <t xml:space="preserve">2.08292269706726</t>
@@ -3356,25 +3356,25 @@
     <t xml:space="preserve">2.01897644996643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04053163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98305141925812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96652626991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94928252696991</t>
+    <t xml:space="preserve">2.04053139686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9830516576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96652615070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94928240776062</t>
   </si>
   <si>
     <t xml:space="preserve">1.9521564245224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90114283561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83288586139679</t>
+    <t xml:space="preserve">1.90114307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83288598060608</t>
   </si>
   <si>
     <t xml:space="preserve">1.93922328948975</t>
@@ -3383,19 +3383,19 @@
     <t xml:space="preserve">1.93634939193726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91766834259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88820993900299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749170303345</t>
+    <t xml:space="preserve">1.91766822338104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88821017742157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749158382416</t>
   </si>
   <si>
     <t xml:space="preserve">1.84653723239899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7876204252243</t>
+    <t xml:space="preserve">1.78762030601501</t>
   </si>
   <si>
     <t xml:space="preserve">1.82641935348511</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">1.8752772808075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85803294181824</t>
+    <t xml:space="preserve">1.85803318023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.90258002281189</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">1.82067143917084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81348645687103</t>
+    <t xml:space="preserve">1.81348621845245</t>
   </si>
   <si>
     <t xml:space="preserve">1.82857477664948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96724474430084</t>
+    <t xml:space="preserve">1.96724462509155</t>
   </si>
   <si>
     <t xml:space="preserve">1.97371113300323</t>
@@ -3434,31 +3434,31 @@
     <t xml:space="preserve">1.95718574523926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03190922737122</t>
+    <t xml:space="preserve">2.03190946578979</t>
   </si>
   <si>
     <t xml:space="preserve">2.00676202774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00388813018799</t>
+    <t xml:space="preserve">2.00388836860657</t>
   </si>
   <si>
     <t xml:space="preserve">1.97155570983887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93347561359406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90904653072357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94209718704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97802197933197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01107311248779</t>
+    <t xml:space="preserve">1.93347537517548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90904629230499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9420975446701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01107287406921</t>
   </si>
   <si>
     <t xml:space="preserve">1.99957716464996</t>
@@ -3470,82 +3470,82 @@
     <t xml:space="preserve">2.03262805938721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03119111061096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99167382717133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01322841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97945940494537</t>
+    <t xml:space="preserve">2.0311906337738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99167370796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01322865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97945928573608</t>
   </si>
   <si>
     <t xml:space="preserve">1.95000076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93778657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96868169307709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92269814014435</t>
+    <t xml:space="preserve">1.9377863407135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96868205070496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92269802093506</t>
   </si>
   <si>
     <t xml:space="preserve">1.94712686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92916429042816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83073043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84078943729401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9205424785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97586679458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92341649532318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94353437423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9442526102066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91838705539703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616167068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02831721305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02185034751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047251701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994176387787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04340553283691</t>
+    <t xml:space="preserve">1.92916405200958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83073031902313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84078919887543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92054259777069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97586667537689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92341637611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94353425502777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94425284862518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91838681697845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616143226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02831697463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0218505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994200229645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04340529441833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10016679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12387704849243</t>
+    <t xml:space="preserve">2.12387728691101</t>
   </si>
   <si>
     <t xml:space="preserve">2.09226322174072</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">2.12315845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1303436756134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1475875377655</t>
+    <t xml:space="preserve">2.13034343719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14758729934692</t>
   </si>
   <si>
     <t xml:space="preserve">2.10950708389282</t>
@@ -3566,49 +3566,49 @@
     <t xml:space="preserve">2.08148598670959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92988276481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93563091754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083723545074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00963616371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08364152908325</t>
+    <t xml:space="preserve">1.92988312244415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93563103675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97083735466003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08364129066467</t>
   </si>
   <si>
     <t xml:space="preserve">2.03765749931335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00316953659058</t>
+    <t xml:space="preserve">2.00316977500916</t>
   </si>
   <si>
     <t xml:space="preserve">1.98592555522919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95143795013428</t>
+    <t xml:space="preserve">1.95143783092499</t>
   </si>
   <si>
     <t xml:space="preserve">1.90042459964752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88318049907684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8537220954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74594783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77181363105774</t>
+    <t xml:space="preserve">1.88318061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85372221469879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7459477186203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540600299835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77181375026703</t>
   </si>
   <si>
     <t xml:space="preserve">1.8084568977356</t>
@@ -3620,22 +3620,22 @@
     <t xml:space="preserve">1.88533616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92557191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88964736461639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88677299022675</t>
+    <t xml:space="preserve">1.92557215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8896472454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88677310943604</t>
   </si>
   <si>
     <t xml:space="preserve">1.8673734664917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89395797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89036560058594</t>
+    <t xml:space="preserve">1.89395809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89036571979523</t>
   </si>
   <si>
     <t xml:space="preserve">1.85444056987762</t>
@@ -3644,34 +3644,34 @@
     <t xml:space="preserve">1.84797418117523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79767954349518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85659646987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85875141620636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85515928268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88605463504791</t>
+    <t xml:space="preserve">1.79767942428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85659635066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85875177383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8472558259964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85515940189362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88605451583862</t>
   </si>
   <si>
     <t xml:space="preserve">1.89683210849762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97874045372009</t>
+    <t xml:space="preserve">1.97874069213867</t>
   </si>
   <si>
     <t xml:space="preserve">2.00101399421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02544283866882</t>
+    <t xml:space="preserve">2.0254430770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280493736267</t>
@@ -3680,40 +3680,40 @@
     <t xml:space="preserve">2.05849409103394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06424188613892</t>
+    <t xml:space="preserve">2.06424164772034</t>
   </si>
   <si>
     <t xml:space="preserve">2.0563383102417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05274605751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02113199234009</t>
+    <t xml:space="preserve">2.0527458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02113175392151</t>
   </si>
   <si>
     <t xml:space="preserve">2.00460648536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01251006126404</t>
+    <t xml:space="preserve">2.01251029968262</t>
   </si>
   <si>
     <t xml:space="preserve">1.99526607990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8997061252594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87958812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93131995201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221518516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91192030906677</t>
+    <t xml:space="preserve">1.89970600605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87958788871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93131983280182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221530437469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91192054748535</t>
   </si>
   <si>
     <t xml:space="preserve">2.02041363716125</t>
@@ -3722,49 +3722,49 @@
     <t xml:space="preserve">2.06855273246765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10447764396667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07645654678345</t>
+    <t xml:space="preserve">2.10447788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07645630836487</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657406806946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15118002891541</t>
+    <t xml:space="preserve">2.15117979049683</t>
   </si>
   <si>
     <t xml:space="preserve">2.32505631446838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32361912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55138301849365</t>
+    <t xml:space="preserve">2.32361936569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55138278007507</t>
   </si>
   <si>
     <t xml:space="preserve">2.53485751152039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60814428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55928635597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52767252922058</t>
+    <t xml:space="preserve">2.6081440448761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55928611755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.527672290802</t>
   </si>
   <si>
     <t xml:space="preserve">2.57509326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52336144447327</t>
+    <t xml:space="preserve">2.52336168289185</t>
   </si>
   <si>
     <t xml:space="preserve">2.5104284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41343116760254</t>
+    <t xml:space="preserve">2.41343140602112</t>
   </si>
   <si>
     <t xml:space="preserve">2.21584486961365</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">2.21368932723999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496047973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120183467865</t>
+    <t xml:space="preserve">2.06496024131775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120207309723</t>
   </si>
   <si>
     <t xml:space="preserve">1.66475737094879</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">1.74954009056091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79480528831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575975894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90186154842377</t>
+    <t xml:space="preserve">1.79480540752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90186166763306</t>
   </si>
   <si>
     <t xml:space="preserve">2.06783437728882</t>
@@ -3803,31 +3803,31 @@
     <t xml:space="preserve">1.96077823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95862293243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98879945278168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95574855804443</t>
+    <t xml:space="preserve">1.9586226940155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98879981040955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95574879646301</t>
   </si>
   <si>
     <t xml:space="preserve">1.95359337329865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06208634376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93275690078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99095511436462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98664450645447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784533977509</t>
+    <t xml:space="preserve">2.06208658218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93275678157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99095487594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9866441488266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9478452205658</t>
   </si>
   <si>
     <t xml:space="preserve">2.16626834869385</t>
@@ -3839,31 +3839,31 @@
     <t xml:space="preserve">2.1957266330719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19860053062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23077535629272</t>
+    <t xml:space="preserve">2.19860076904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2307755947113</t>
   </si>
   <si>
     <t xml:space="preserve">2.33036375045776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35257983207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35181331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36713480949402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.321937084198</t>
+    <t xml:space="preserve">2.35257959365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35181355476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36713457107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32193684577942</t>
   </si>
   <si>
     <t xml:space="preserve">2.35104727745056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31887269020081</t>
+    <t xml:space="preserve">2.31887245178223</t>
   </si>
   <si>
     <t xml:space="preserve">2.27597308158875</t>
@@ -3875,19 +3875,19 @@
     <t xml:space="preserve">2.24839472770691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23383975028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.210857629776</t>
+    <t xml:space="preserve">2.23383951187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21085786819458</t>
   </si>
   <si>
     <t xml:space="preserve">2.13731575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1587655544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25069332122803</t>
+    <t xml:space="preserve">2.15876579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25069308280945</t>
   </si>
   <si>
     <t xml:space="preserve">2.23307371139526</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">2.21545433998108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2828676700592</t>
+    <t xml:space="preserve">2.28286790847778</t>
   </si>
   <si>
     <t xml:space="preserve">2.26448225975037</t>
@@ -3905,25 +3905,25 @@
     <t xml:space="preserve">2.31351017951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38092374801636</t>
+    <t xml:space="preserve">2.38092398643494</t>
   </si>
   <si>
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4552321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47285127639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45293354988098</t>
+    <t xml:space="preserve">2.45523190498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47285151481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45293378829956</t>
   </si>
   <si>
     <t xml:space="preserve">2.4820442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48664093017578</t>
+    <t xml:space="preserve">2.4866406917572</t>
   </si>
   <si>
     <t xml:space="preserve">2.46365880966187</t>
@@ -3932,37 +3932,37 @@
     <t xml:space="preserve">2.47438359260559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41309857368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43071818351746</t>
+    <t xml:space="preserve">2.41309881210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43071794509888</t>
   </si>
   <si>
     <t xml:space="preserve">2.37709331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09058594703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98793351650238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01168155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08062720298767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02623677253723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07832908630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16795802116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315598487854</t>
+    <t xml:space="preserve">2.09058618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98793363571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01168131828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08062744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02623653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07832884788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16795825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315574645996</t>
   </si>
   <si>
     <t xml:space="preserve">2.19936680793762</t>
@@ -3971,58 +3971,58 @@
     <t xml:space="preserve">2.13501763343811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20089912414551</t>
+    <t xml:space="preserve">2.20089888572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.14267802238464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14191222190857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14650845527649</t>
+    <t xml:space="preserve">2.14191246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14650869369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.03159880638123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99406182765961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90290069580078</t>
+    <t xml:space="preserve">1.99406206607819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9029004573822</t>
   </si>
   <si>
     <t xml:space="preserve">1.86919391155243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98410332202911</t>
+    <t xml:space="preserve">1.98410308361053</t>
   </si>
   <si>
     <t xml:space="preserve">1.98563539981842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91592359542847</t>
+    <t xml:space="preserve">1.91592335700989</t>
   </si>
   <si>
     <t xml:space="preserve">1.8684276342392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83472096920013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73743081092834</t>
+    <t xml:space="preserve">1.83472084999084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73743093013763</t>
   </si>
   <si>
     <t xml:space="preserve">1.77420198917389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83012437820435</t>
+    <t xml:space="preserve">1.83012449741364</t>
   </si>
   <si>
     <t xml:space="preserve">1.92435026168823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87915241718292</t>
+    <t xml:space="preserve">1.8791526556015</t>
   </si>
   <si>
     <t xml:space="preserve">1.80331230163574</t>
@@ -4031,28 +4031,28 @@
     <t xml:space="preserve">1.79718387126923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8538726568222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79641771316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84544575214386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86306524276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92894661426544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92051994800568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96954786777496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837010383606</t>
+    <t xml:space="preserve">1.85387253761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79641759395599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84544563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86306500434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92894673347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92052006721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96954810619354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837034225464</t>
   </si>
   <si>
     <t xml:space="preserve">2.00095653533936</t>
@@ -4061,22 +4061,22 @@
     <t xml:space="preserve">2.03466320037842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98869943618774</t>
+    <t xml:space="preserve">1.98869955539703</t>
   </si>
   <si>
     <t xml:space="preserve">1.97184610366821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9565247297287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99176383018494</t>
+    <t xml:space="preserve">1.95652496814728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99176371097565</t>
   </si>
   <si>
     <t xml:space="preserve">2.07220029830933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06530570983887</t>
+    <t xml:space="preserve">2.06530594825745</t>
   </si>
   <si>
     <t xml:space="preserve">2.02240633964539</t>
@@ -4085,52 +4085,52 @@
     <t xml:space="preserve">2.01397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94273567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87762057781219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90826308727264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86076688766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80944085121155</t>
+    <t xml:space="preserve">1.94273579120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87762033939362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90826296806335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86076700687408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80944073200226</t>
   </si>
   <si>
     <t xml:space="preserve">1.86612963676453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89830386638641</t>
+    <t xml:space="preserve">1.89830422401428</t>
   </si>
   <si>
     <t xml:space="preserve">1.90213453769684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87149214744568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96878182888031</t>
+    <t xml:space="preserve">1.87149202823639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9687819480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.90060222148895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90673077106476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89907026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99712634086609</t>
+    <t xml:space="preserve">1.90673089027405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89907014369965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9971262216568</t>
   </si>
   <si>
     <t xml:space="preserve">2.06070947647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12199449539185</t>
+    <t xml:space="preserve">2.12199425697327</t>
   </si>
   <si>
     <t xml:space="preserve">2.08445739746094</t>
@@ -4139,19 +4139,19 @@
     <t xml:space="preserve">2.15033888816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19017386436462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21392202377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15799951553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12965512275696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09288430213928</t>
+    <t xml:space="preserve">2.1901741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21392226219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15799927711487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12965536117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0928840637207</t>
   </si>
   <si>
     <t xml:space="preserve">2.07143425941467</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">2.02700257301331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06377387046814</t>
+    <t xml:space="preserve">2.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">2.1319534778595</t>
@@ -4196,49 +4196,49 @@
     <t xml:space="preserve">2.17255473136902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17332077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19323825836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2261791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21698641777039</t>
+    <t xml:space="preserve">2.17332053184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1932384967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22617888450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21698665618896</t>
   </si>
   <si>
     <t xml:space="preserve">2.3173406124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34415292739868</t>
+    <t xml:space="preserve">2.3441526889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.34491896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37173128128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41922688484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44220876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37785983085632</t>
+    <t xml:space="preserve">2.37173104286194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4192271232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44220900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37785959243774</t>
   </si>
   <si>
     <t xml:space="preserve">2.42152523994446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35564374923706</t>
+    <t xml:space="preserve">2.35564398765564</t>
   </si>
   <si>
     <t xml:space="preserve">2.36177229881287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769504547119</t>
+    <t xml:space="preserve">2.41769480705261</t>
   </si>
   <si>
     <t xml:space="preserve">2.45140171051025</t>
@@ -4253,67 +4253,67 @@
     <t xml:space="preserve">2.51268672943115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56171464920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58086633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53949904441833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55175614356995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52187919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53796672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5372006893158</t>
+    <t xml:space="preserve">2.56171488761902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58086609840393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53949928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55175590515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52187967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53796696662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53720045089722</t>
   </si>
   <si>
     <t xml:space="preserve">2.4759156703949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45982837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44450712203979</t>
+    <t xml:space="preserve">2.45982813835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44450688362122</t>
   </si>
   <si>
     <t xml:space="preserve">2.41386461257935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40390563011169</t>
+    <t xml:space="preserve">2.40390586853027</t>
   </si>
   <si>
     <t xml:space="preserve">2.41080021858215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40313959121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4207592010498</t>
+    <t xml:space="preserve">2.40313982963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42075943946838</t>
   </si>
   <si>
     <t xml:space="preserve">2.51881527900696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50349378585815</t>
+    <t xml:space="preserve">2.50349402427673</t>
   </si>
   <si>
     <t xml:space="preserve">2.44527292251587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48817253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46672296524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5686092376709</t>
+    <t xml:space="preserve">2.48817276954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4667227268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56860947608948</t>
   </si>
   <si>
     <t xml:space="preserve">2.59465551376343</t>
@@ -4340,19 +4340,19 @@
     <t xml:space="preserve">2.67739009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77774453163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78923535346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77468037605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7585928440094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72335410118103</t>
+    <t xml:space="preserve">2.77774429321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78923559188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77468013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75859308242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72335386276245</t>
   </si>
   <si>
     <t xml:space="preserve">2.74020743370056</t>
@@ -4364,7 +4364,7 @@
     <t xml:space="preserve">2.94014978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92176413536072</t>
+    <t xml:space="preserve">2.9217643737793</t>
   </si>
   <si>
     <t xml:space="preserve">2.93172311782837</t>
@@ -4379,19 +4379,19 @@
     <t xml:space="preserve">2.95700311660767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99454021453857</t>
+    <t xml:space="preserve">2.99453997612</t>
   </si>
   <si>
     <t xml:space="preserve">3.00756359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07038021087646</t>
+    <t xml:space="preserve">3.07038044929504</t>
   </si>
   <si>
     <t xml:space="preserve">3.09106421470642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07957339286804</t>
+    <t xml:space="preserve">3.07957315444946</t>
   </si>
   <si>
     <t xml:space="preserve">3.16154193878174</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">3.29024052619934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2243595123291</t>
+    <t xml:space="preserve">3.22435927391052</t>
   </si>
   <si>
     <t xml:space="preserve">3.22052884101868</t>
@@ -4424,19 +4424,19 @@
     <t xml:space="preserve">3.16767072677612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14085841178894</t>
+    <t xml:space="preserve">3.14085817337036</t>
   </si>
   <si>
     <t xml:space="preserve">3.19448280334473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22282671928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10255551338196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04280185699463</t>
+    <t xml:space="preserve">3.22282695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1025550365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04280209541321</t>
   </si>
   <si>
     <t xml:space="preserve">3.11634421348572</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">3.12860155105591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16001009941101</t>
+    <t xml:space="preserve">3.16000986099243</t>
   </si>
   <si>
     <t xml:space="preserve">3.16077589988708</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">3.11711025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15081715583801</t>
+    <t xml:space="preserve">3.15081739425659</t>
   </si>
   <si>
     <t xml:space="preserve">3.22359323501587</t>
@@ -4466,34 +4466,34 @@
     <t xml:space="preserve">3.18912029266357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23355197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17150092124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07727527618408</t>
+    <t xml:space="preserve">3.23355221748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17150068283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07727551460266</t>
   </si>
   <si>
     <t xml:space="preserve">2.82830452919006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8811628818512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67585825920105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71186280250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70573449134827</t>
+    <t xml:space="preserve">2.88116312026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67585802078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71186304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70573472976685</t>
   </si>
   <si>
     <t xml:space="preserve">2.80991911888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039708137512</t>
+    <t xml:space="preserve">2.88039684295654</t>
   </si>
   <si>
     <t xml:space="preserve">2.80379056930542</t>
@@ -4508,10 +4508,10 @@
     <t xml:space="preserve">2.63372468948364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65900468826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75782656669617</t>
+    <t xml:space="preserve">2.65900492668152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75782680511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.79996037483215</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">2.76165723800659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77851057052612</t>
+    <t xml:space="preserve">2.7785108089447</t>
   </si>
   <si>
     <t xml:space="preserve">2.75476264953613</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">2.83979558944702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84132766723633</t>
+    <t xml:space="preserve">2.84132790565491</t>
   </si>
   <si>
     <t xml:space="preserve">2.83519911766052</t>
@@ -4550,19 +4550,19 @@
     <t xml:space="preserve">3.11098170280457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24427676200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31637191772461</t>
+    <t xml:space="preserve">3.24427700042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31637167930603</t>
   </si>
   <si>
     <t xml:space="preserve">3.21511483192444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03609228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11466789245605</t>
+    <t xml:space="preserve">3.03609204292297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11466765403748</t>
   </si>
   <si>
     <t xml:space="preserve">2.98505854606628</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">3.0109806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04905295372009</t>
+    <t xml:space="preserve">3.04905319213867</t>
   </si>
   <si>
     <t xml:space="preserve">3.27910900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15679049491882</t>
+    <t xml:space="preserve">3.1567907333374</t>
   </si>
   <si>
     <t xml:space="preserve">3.1106173992157</t>
@@ -4595,13 +4595,13 @@
     <t xml:space="preserve">3.16003108024597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1738018989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16732144355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13572931289673</t>
+    <t xml:space="preserve">3.17380166053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16732168197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13572907447815</t>
   </si>
   <si>
     <t xml:space="preserve">3.17947220802307</t>
@@ -4610,16 +4610,16 @@
     <t xml:space="preserve">3.1584107875824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21754455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025443077087</t>
+    <t xml:space="preserve">3.21754479408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025419235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631563186646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09684634208679</t>
+    <t xml:space="preserve">3.09684658050537</t>
   </si>
   <si>
     <t xml:space="preserve">3.09441637992859</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">3.03771233558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11142754554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06768465042114</t>
+    <t xml:space="preserve">3.11142778396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06768441200256</t>
   </si>
   <si>
     <t xml:space="preserve">3.11304759979248</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">3.10251688957214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09198617935181</t>
+    <t xml:space="preserve">3.09198594093323</t>
   </si>
   <si>
     <t xml:space="preserve">3.14626002311707</t>
@@ -4667,10 +4667,10 @@
     <t xml:space="preserve">3.16165113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24508690834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26776838302612</t>
+    <t xml:space="preserve">3.24508714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26776814460754</t>
   </si>
   <si>
     <t xml:space="preserve">3.24751687049866</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">3.31556177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29612040519714</t>
+    <t xml:space="preserve">3.29612016677856</t>
   </si>
   <si>
     <t xml:space="preserve">3.22888588905334</t>
@@ -4688,13 +4688,13 @@
     <t xml:space="preserve">3.22240519523621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27586913108826</t>
+    <t xml:space="preserve">3.27586936950684</t>
   </si>
   <si>
     <t xml:space="preserve">3.31070137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40223789215088</t>
+    <t xml:space="preserve">3.4022376537323</t>
   </si>
   <si>
     <t xml:space="preserve">3.44274067878723</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">3.44355058670044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34553408622742</t>
+    <t xml:space="preserve">3.34553384780884</t>
   </si>
   <si>
     <t xml:space="preserve">3.42005920410156</t>
@@ -4733,85 +4733,85 @@
     <t xml:space="preserve">3.61042213439941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62500309944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58531069755554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60475182533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59422135353088</t>
+    <t xml:space="preserve">3.62500333786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58531045913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60475158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5942211151123</t>
   </si>
   <si>
     <t xml:space="preserve">3.59503149986267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5934112071991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63391423225403</t>
+    <t xml:space="preserve">3.59341096878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63391399383545</t>
   </si>
   <si>
     <t xml:space="preserve">3.63634419441223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63553404808044</t>
+    <t xml:space="preserve">3.63553380966187</t>
   </si>
   <si>
     <t xml:space="preserve">3.68413734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64606499671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58774065971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50511503219604</t>
+    <t xml:space="preserve">3.64606475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58774089813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50511527061462</t>
   </si>
   <si>
     <t xml:space="preserve">3.48162317276001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56505942344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24103665351868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41762900352478</t>
+    <t xml:space="preserve">3.56505918502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2410364151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4176287651062</t>
   </si>
   <si>
     <t xml:space="preserve">3.51807570457458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50106501579285</t>
+    <t xml:space="preserve">3.50106477737427</t>
   </si>
   <si>
     <t xml:space="preserve">3.54966807365417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55209851264954</t>
+    <t xml:space="preserve">3.55209875106812</t>
   </si>
   <si>
     <t xml:space="preserve">3.54480767250061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52293610572815</t>
+    <t xml:space="preserve">3.52293634414673</t>
   </si>
   <si>
     <t xml:space="preserve">3.55857872962952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54156804084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5156455039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56667947769165</t>
+    <t xml:space="preserve">3.5415678024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51564598083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56667900085449</t>
   </si>
   <si>
     <t xml:space="preserve">3.5764000415802</t>
@@ -4823,19 +4823,19 @@
     <t xml:space="preserve">3.57720994949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54318737983704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49944472312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46380186080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35687494277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28883004188538</t>
+    <t xml:space="preserve">3.54318785667419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49944496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46380209922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35687470436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2888298034668</t>
   </si>
   <si>
     <t xml:space="preserve">3.32123208045959</t>
@@ -4850,52 +4850,52 @@
     <t xml:space="preserve">3.48324370384216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53994750976562</t>
+    <t xml:space="preserve">3.53994727134705</t>
   </si>
   <si>
     <t xml:space="preserve">3.62743353843689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70843911170959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7724335193634</t>
+    <t xml:space="preserve">3.70843935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77243375778198</t>
   </si>
   <si>
     <t xml:space="preserve">3.7521824836731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82670760154724</t>
+    <t xml:space="preserve">3.82670736312866</t>
   </si>
   <si>
     <t xml:space="preserve">3.75137233734131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68980765342712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74084162712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67360687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68251729011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66712594032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72626042366028</t>
+    <t xml:space="preserve">3.6898078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74084138870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67360639572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68251752853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66712641716003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7262601852417</t>
   </si>
   <si>
     <t xml:space="preserve">3.8550591468811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74570202827454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84452843666077</t>
+    <t xml:space="preserve">3.74570178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84452867507935</t>
   </si>
   <si>
     <t xml:space="preserve">3.84614896774292</t>
@@ -4904,46 +4904,46 @@
     <t xml:space="preserve">3.84776902198792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84938931465149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92634463310242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97818803787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97089791297913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80078554153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8396680355072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76838350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402588844299</t>
+    <t xml:space="preserve">3.84938859939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.926344871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97818756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97089743614197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.800785779953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83966851234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76838326454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402636528015</t>
   </si>
   <si>
     <t xml:space="preserve">3.80726599693298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79349541664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82589745521545</t>
+    <t xml:space="preserve">3.79349517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82589721679688</t>
   </si>
   <si>
     <t xml:space="preserve">3.90690302848816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95793700218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94173574447632</t>
+    <t xml:space="preserve">3.95793676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9417359828949</t>
   </si>
   <si>
     <t xml:space="preserve">3.94659614562988</t>
@@ -4952,10 +4952,10 @@
     <t xml:space="preserve">3.97251749038696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94011521339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99114894866943</t>
+    <t xml:space="preserve">3.94011497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99114918708801</t>
   </si>
   <si>
     <t xml:space="preserve">4.10698747634888</t>
@@ -4973,13 +4973,13 @@
     <t xml:space="preserve">4.31112098693848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25279760360718</t>
+    <t xml:space="preserve">4.25279712677002</t>
   </si>
   <si>
     <t xml:space="preserve">4.27223873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31274127960205</t>
+    <t xml:space="preserve">4.31274175643921</t>
   </si>
   <si>
     <t xml:space="preserve">4.1393895149231</t>
@@ -4988,10 +4988,10 @@
     <t xml:space="preserve">4.11346769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13128900527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642812728882</t>
+    <t xml:space="preserve">4.13128852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642860412598</t>
   </si>
   <si>
     <t xml:space="preserve">4.08916568756104</t>
@@ -5009,16 +5009,16 @@
     <t xml:space="preserve">4.18637323379517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14100933074951</t>
+    <t xml:space="preserve">4.14100980758667</t>
   </si>
   <si>
     <t xml:space="preserve">4.15721035003662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99357914924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04137229919434</t>
+    <t xml:space="preserve">3.99357891082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04137277603149</t>
   </si>
   <si>
     <t xml:space="preserve">4.07296466827393</t>
@@ -5027,79 +5027,79 @@
     <t xml:space="preserve">4.05676364898682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90204262733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8348081111908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.870450258255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89961266517639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84290838241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81617665290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86072969436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88260173797607</t>
+    <t xml:space="preserve">3.90204238891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83480834960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87045049667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89961290359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84290862083435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81617712974548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86072945594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8826014995575</t>
   </si>
   <si>
     <t xml:space="preserve">3.87288093566895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94335579872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9441659450531</t>
+    <t xml:space="preserve">3.94335556030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94416546821594</t>
   </si>
   <si>
     <t xml:space="preserve">4.10374689102173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17503118515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14749002456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9457859992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9506459236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88422131538391</t>
+    <t xml:space="preserve">4.1750316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14748954772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94578552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95064616203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88422155380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.88584160804749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8331880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88665151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93687534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96927785873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94821572303772</t>
+    <t xml:space="preserve">3.83318781852722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88665175437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9368748664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96927738189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94821619987488</t>
   </si>
   <si>
     <t xml:space="preserve">4.01707077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87774133682251</t>
+    <t xml:space="preserve">3.87774157524109</t>
   </si>
   <si>
     <t xml:space="preserve">3.99762940406799</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">4.20581388473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29978084564209</t>
+    <t xml:space="preserve">4.29978036880493</t>
   </si>
   <si>
     <t xml:space="preserve">4.13290929794312</t>
@@ -5141,7 +5141,7 @@
     <t xml:space="preserve">3.98223829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98547887802124</t>
+    <t xml:space="preserve">3.98547863960266</t>
   </si>
   <si>
     <t xml:space="preserve">3.996009349823</t>
@@ -5153,13 +5153,13 @@
     <t xml:space="preserve">4.19933366775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42614984512329</t>
+    <t xml:space="preserve">4.42614936828613</t>
   </si>
   <si>
     <t xml:space="preserve">4.47961330413818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40670776367188</t>
+    <t xml:space="preserve">4.40670824050903</t>
   </si>
   <si>
     <t xml:space="preserve">4.36782550811768</t>
@@ -5186,28 +5186,28 @@
     <t xml:space="preserve">4.45531129837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47313213348389</t>
+    <t xml:space="preserve">4.47313261032104</t>
   </si>
   <si>
     <t xml:space="preserve">4.54765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.576819896698</t>
+    <t xml:space="preserve">4.57682037353516</t>
   </si>
   <si>
     <t xml:space="preserve">4.61570262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69994831085205</t>
+    <t xml:space="preserve">4.69994878768921</t>
   </si>
   <si>
     <t xml:space="preserve">4.81335639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85385942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84899854660034</t>
+    <t xml:space="preserve">4.85385894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8489990234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.88302135467529</t>
@@ -5216,22 +5216,22 @@
     <t xml:space="preserve">4.95916700363159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01100969314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96240663528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99642944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04989290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15358066558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12927865982056</t>
+    <t xml:space="preserve">5.01101016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96240711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99642992019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04989337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15358018875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1292781829834</t>
   </si>
   <si>
     <t xml:space="preserve">5.0709547996521</t>
@@ -5240,7 +5240,7 @@
     <t xml:space="preserve">5.10173654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05151271820068</t>
+    <t xml:space="preserve">5.05151319503784</t>
   </si>
   <si>
     <t xml:space="preserve">5.17140102386475</t>
@@ -5261,7 +5261,7 @@
     <t xml:space="preserve">5.06285381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14709949493408</t>
+    <t xml:space="preserve">5.14709997177124</t>
   </si>
   <si>
     <t xml:space="preserve">5.17626190185547</t>
@@ -6279,6 +6279,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.1850004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3900003433228</t>
   </si>
 </sst>
 </file>
@@ -71513,7 +71516,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.651099537</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>3438289</v>
@@ -71534,6 +71537,32 @@
         <v>2088</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912962963</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>5611502</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>12.3900003433228</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>12.2049999237061</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>12.2600002288818</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>12.3900003433228</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2089</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2073802947998</t>
+    <t xml:space="preserve">6.20738077163696</t>
   </si>
   <si>
     <t xml:space="preserve">BAMI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25302362442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98424053192139</t>
+    <t xml:space="preserve">6.25302267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98424005508423</t>
   </si>
   <si>
     <t xml:space="preserve">5.89802646636963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6545991897583</t>
+    <t xml:space="preserve">5.65459871292114</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967178344727</t>
+    <t xml:space="preserve">5.65967130661011</t>
   </si>
   <si>
     <t xml:space="preserve">5.89295434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.274245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9420690536499</t>
+    <t xml:space="preserve">5.27424573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94206857681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.40450143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85839128494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61496448516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28786039352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55410766601562</t>
+    <t xml:space="preserve">4.85839080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6149640083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28785991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55410718917847</t>
   </si>
   <si>
     <t xml:space="preserve">4.19911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9556839466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32082366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57946443557739</t>
+    <t xml:space="preserve">3.95568370819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32082414627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57946491241455</t>
   </si>
   <si>
     <t xml:space="preserve">4.50339365005493</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">4.0520396232605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11289691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961316108704</t>
+    <t xml:space="preserve">4.11289644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961268424988</t>
   </si>
   <si>
     <t xml:space="preserve">3.52715110778809</t>
@@ -116,28 +116,28 @@
     <t xml:space="preserve">3.22286772727966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58040118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26851081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64379286766052</t>
+    <t xml:space="preserve">3.58040070533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26851058006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64379334449768</t>
   </si>
   <si>
     <t xml:space="preserve">3.91004109382629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04443216323853</t>
+    <t xml:space="preserve">4.04443264007568</t>
   </si>
   <si>
     <t xml:space="preserve">4.14332485198975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91511297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818560600281</t>
+    <t xml:space="preserve">3.91511225700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818512916565</t>
   </si>
   <si>
     <t xml:space="preserve">4.08246850967407</t>
@@ -146,85 +146,85 @@
     <t xml:space="preserve">3.71986436843872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.646329164505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74775671958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84157705307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9201831817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04950428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88468432426453</t>
+    <t xml:space="preserve">3.64632892608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74775648117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84157776832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92018294334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22700262069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04950475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88468480110168</t>
   </si>
   <si>
     <t xml:space="preserve">3.86693429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76043581962585</t>
+    <t xml:space="preserve">3.7604353427887</t>
   </si>
   <si>
     <t xml:space="preserve">3.69957828521729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03682518005371</t>
+    <t xml:space="preserve">4.03682613372803</t>
   </si>
   <si>
     <t xml:space="preserve">3.9480767250061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38768815994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47136569023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67675805091858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197106361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51447296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38261747360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27611756324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06565451622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365646362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49005150794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40586709976196</t>
+    <t xml:space="preserve">3.38768792152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47136545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67675733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51447248458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38261675834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27611780166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06565427780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365622520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812201499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49005174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40586733818054</t>
   </si>
   <si>
     <t xml:space="preserve">2.2243115901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46672320365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72079992294312</t>
+    <t xml:space="preserve">2.46672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72080016136169</t>
   </si>
   <si>
     <t xml:space="preserve">2.700514793396</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">2.91097712516785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02508330345154</t>
+    <t xml:space="preserve">3.02508354187012</t>
   </si>
   <si>
     <t xml:space="preserve">3.16454672813416</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">3.22690272331238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1385657787323</t>
+    <t xml:space="preserve">3.13856601715088</t>
   </si>
   <si>
     <t xml:space="preserve">3.14116311073303</t>
@@ -251,25 +251,25 @@
     <t xml:space="preserve">3.20092105865479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2450897693634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11778020858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23469686508179</t>
+    <t xml:space="preserve">3.24508953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777997016907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23469710350037</t>
   </si>
   <si>
     <t xml:space="preserve">3.19052886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32823038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20351910591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96968626976013</t>
+    <t xml:space="preserve">3.32823014259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20351886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96968603134155</t>
   </si>
   <si>
     <t xml:space="preserve">2.75663733482361</t>
@@ -281,34 +281,34 @@
     <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84497451782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59607172012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51500940322876</t>
+    <t xml:space="preserve">2.84497475624084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59607124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51500964164734</t>
   </si>
   <si>
     <t xml:space="preserve">2.28637218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32378602027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32274651527405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39237666130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23544859886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24584126472473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2208993434906</t>
+    <t xml:space="preserve">2.32378578186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32274627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39237642288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23544812202454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24584150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22089910507202</t>
   </si>
   <si>
     <t xml:space="preserve">2.24480175971985</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">2.2749400138855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47343897819519</t>
+    <t xml:space="preserve">2.47343921661377</t>
   </si>
   <si>
     <t xml:space="preserve">2.47032117843628</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">2.48902797698975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49422407150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31131434440613</t>
+    <t xml:space="preserve">2.49422383308411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31131458282471</t>
   </si>
   <si>
     <t xml:space="preserve">2.16581773757935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16685700416565</t>
+    <t xml:space="preserve">2.16685724258423</t>
   </si>
   <si>
     <t xml:space="preserve">2.05461668968201</t>
@@ -347,19 +347,19 @@
     <t xml:space="preserve">2.15853524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2902045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22156834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433311462402</t>
+    <t xml:space="preserve">2.29020428657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22156882286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433287620544</t>
   </si>
   <si>
     <t xml:space="preserve">2.0422739982605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83636605739594</t>
+    <t xml:space="preserve">1.83636581897736</t>
   </si>
   <si>
     <t xml:space="preserve">1.71590256690979</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">1.83776664733887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07449102401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01846146583557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02546548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99324834346771</t>
+    <t xml:space="preserve">2.07449126243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01846170425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02546501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.993248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.12211608886719</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">1.52680313587189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55481767654419</t>
+    <t xml:space="preserve">1.55481779575348</t>
   </si>
   <si>
     <t xml:space="preserve">1.50439131259918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50158977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540230751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45676624774933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40073680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31459140777588</t>
+    <t xml:space="preserve">1.50158989429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540218830109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45676612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40073657035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31459152698517</t>
   </si>
   <si>
     <t xml:space="preserve">1.28167414665222</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">1.5702258348465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66687679290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55621862411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64166367053986</t>
+    <t xml:space="preserve">1.666876912117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55621838569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64166355133057</t>
   </si>
   <si>
     <t xml:space="preserve">1.66267454624176</t>
@@ -434,70 +434,70 @@
     <t xml:space="preserve">1.6878879070282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67528128623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6640750169754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72990965843201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70329570770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71730303764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75932538509369</t>
+    <t xml:space="preserve">1.67528116703033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66407537460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72991001605988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70329582691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71730327606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7593252658844</t>
   </si>
   <si>
     <t xml:space="preserve">1.70749807357788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76352751255035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50579190254211</t>
+    <t xml:space="preserve">1.76352739334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50579214096069</t>
   </si>
   <si>
     <t xml:space="preserve">1.49738764762878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55201649665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63045740127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59964108467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59263777732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58143186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56882512569427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53100538253784</t>
+    <t xml:space="preserve">1.55201625823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63045763969421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59964120388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59263753890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58143150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56882524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53100526332855</t>
   </si>
   <si>
     <t xml:space="preserve">1.52820372581482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4539647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48758256435394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58003115653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53520739078522</t>
+    <t xml:space="preserve">1.45396482944489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48758244514465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58003091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53520727157593</t>
   </si>
   <si>
     <t xml:space="preserve">1.51559722423553</t>
@@ -506,28 +506,28 @@
     <t xml:space="preserve">1.56742441654205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56182157993317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60384333133698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68088412284851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63886177539825</t>
+    <t xml:space="preserve">1.56182134151459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60384356975555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6808842420578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63886189460754</t>
   </si>
   <si>
     <t xml:space="preserve">1.65707159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65847229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6430641412735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59403848648071</t>
+    <t xml:space="preserve">1.6584724187851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64306402206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59403860569</t>
   </si>
   <si>
     <t xml:space="preserve">1.60944652557373</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">1.50018906593323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46657145023346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40003645420074</t>
+    <t xml:space="preserve">1.46657133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40003621578217</t>
   </si>
   <si>
     <t xml:space="preserve">1.45116329193115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357487678528</t>
+    <t xml:space="preserve">1.47357511520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.4399573802948</t>
@@ -557,73 +557,73 @@
     <t xml:space="preserve">1.40633964538574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37832486629486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39653444290161</t>
+    <t xml:space="preserve">1.37832510471344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3965345621109</t>
   </si>
   <si>
     <t xml:space="preserve">1.40774047374725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46797204017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48057866096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50299048423767</t>
+    <t xml:space="preserve">1.4679719209671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48057889938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50299060344696</t>
   </si>
   <si>
     <t xml:space="preserve">1.55061554908752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65286934375763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78593933582306</t>
+    <t xml:space="preserve">1.65286922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78593945503235</t>
   </si>
   <si>
     <t xml:space="preserve">1.79994666576385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84617078304291</t>
+    <t xml:space="preserve">1.8461709022522</t>
   </si>
   <si>
     <t xml:space="preserve">1.85317480564117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84196889400482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82235825061798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737705230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86297976970673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041027545929</t>
+    <t xml:space="preserve">1.84196901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82235860824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737693309784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86297988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041003704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379596710205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80835103988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67107892036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61224818229675</t>
+    <t xml:space="preserve">1.80835127830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67107880115509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61224794387817</t>
   </si>
   <si>
     <t xml:space="preserve">1.50999414920807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59543907642365</t>
+    <t xml:space="preserve">1.59543931484222</t>
   </si>
   <si>
     <t xml:space="preserve">1.60664498806</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">1.35451245307922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30408585071564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31178998947144</t>
+    <t xml:space="preserve">1.30408596992493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31178987026215</t>
   </si>
   <si>
     <t xml:space="preserve">1.32649767398834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29988372325897</t>
+    <t xml:space="preserve">1.29988360404968</t>
   </si>
   <si>
     <t xml:space="preserve">1.31739294528961</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">1.30268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35871458053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39233243465424</t>
+    <t xml:space="preserve">1.35871469974518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39233231544495</t>
   </si>
   <si>
     <t xml:space="preserve">1.28867781162262</t>
@@ -671,133 +671,133 @@
     <t xml:space="preserve">1.40493905544281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49458634853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64026284217834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56462287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.533806681633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67948317527771</t>
+    <t xml:space="preserve">1.49458611011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64026272296906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56462299823761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53380680084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67948341369629</t>
   </si>
   <si>
     <t xml:space="preserve">1.69769310951233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6514687538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72290635108948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77893579006195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310114860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60524427890778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092113018036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87698721885681</t>
+    <t xml:space="preserve">1.65146851539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7229061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77893543243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310102939606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60524439811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092089176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8769873380661</t>
   </si>
   <si>
     <t xml:space="preserve">1.90500199794769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97643959522247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0310685634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95122611522675</t>
+    <t xml:space="preserve">1.97643947601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03106832504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95122647285461</t>
   </si>
   <si>
     <t xml:space="preserve">1.94982552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90640270709991</t>
+    <t xml:space="preserve">1.9064028263092</t>
   </si>
   <si>
     <t xml:space="preserve">1.94702422618866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89799821376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142115116119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9358184337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01706099510193</t>
+    <t xml:space="preserve">1.89799845218658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142127037048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93581795692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01706075668335</t>
   </si>
   <si>
     <t xml:space="preserve">1.97363805770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02266359329224</t>
+    <t xml:space="preserve">2.02266383171082</t>
   </si>
   <si>
     <t xml:space="preserve">2.08849859237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00585508346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02126312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86017858982086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89099478721619</t>
+    <t xml:space="preserve">2.005854845047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02126288414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86017847061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8909946680069</t>
   </si>
   <si>
     <t xml:space="preserve">1.78033638000488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67388045787811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74251651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73831462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64586567878723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75512301921844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84056830406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77753508090973</t>
+    <t xml:space="preserve">1.67388033866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74251616001129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7383143901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64586555957794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75512337684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84056806564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77753531932831</t>
   </si>
   <si>
     <t xml:space="preserve">1.78173696994781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68368566036224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6220531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51419627666473</t>
+    <t xml:space="preserve">1.68368554115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62205302715302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51419639587402</t>
   </si>
   <si>
     <t xml:space="preserve">1.6500678062439</t>
@@ -806,31 +806,31 @@
     <t xml:space="preserve">1.71870398521423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71450185775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68228495121002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6934906244278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69629216194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80975186824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81535470485687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072609424591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80695044994354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86858296394348</t>
+    <t xml:space="preserve">1.71450197696686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68228483200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69349050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69629204273224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80975198745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81535482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80695033073425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8685827255249</t>
   </si>
   <si>
     <t xml:space="preserve">1.85597622394562</t>
@@ -842,34 +842,34 @@
     <t xml:space="preserve">1.90780353546143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91480708122253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88539171218872</t>
+    <t xml:space="preserve">1.91480684280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88539147377014</t>
   </si>
   <si>
     <t xml:space="preserve">1.88819313049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94562363624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9036009311676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89939868450165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87978851795197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86718213558197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76212680339813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542848110199</t>
+    <t xml:space="preserve">1.94562351703644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90360105037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89939916133881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87978887557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86718201637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76212668418884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95542860031128</t>
   </si>
   <si>
     <t xml:space="preserve">1.86157917976379</t>
@@ -884,34 +884,34 @@
     <t xml:space="preserve">2.04647636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91900932788849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87838792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98204231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96383261680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88259017467499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93021547794342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97783994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09410119056702</t>
+    <t xml:space="preserve">1.91900956630707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87838780879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98204243183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9638329744339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8825900554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93021523952484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97784030437469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09410166740417</t>
   </si>
   <si>
     <t xml:space="preserve">2.17814564704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11371183395386</t>
+    <t xml:space="preserve">2.11371159553528</t>
   </si>
   <si>
     <t xml:space="preserve">2.12491774559021</t>
@@ -926,37 +926,37 @@
     <t xml:space="preserve">1.90220057964325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99885153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95262694358826</t>
+    <t xml:space="preserve">1.99885141849518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95262718200684</t>
   </si>
   <si>
     <t xml:space="preserve">1.95402765274048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93441760540009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920436382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91060471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88679230213165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95822989940643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94422256946564</t>
+    <t xml:space="preserve">1.93441724777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920424461365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91060495376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88679242134094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95823013782501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94422280788422</t>
   </si>
   <si>
     <t xml:space="preserve">1.99184775352478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06048393249512</t>
+    <t xml:space="preserve">2.06048369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.05207943916321</t>
@@ -965,43 +965,43 @@
     <t xml:space="preserve">2.10950970649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14592838287354</t>
+    <t xml:space="preserve">2.14592862129211</t>
   </si>
   <si>
     <t xml:space="preserve">2.0955023765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16974115371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14452767372131</t>
+    <t xml:space="preserve">2.1697416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14452791213989</t>
   </si>
   <si>
     <t xml:space="preserve">2.18795084953308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20616054534912</t>
+    <t xml:space="preserve">2.20616030693054</t>
   </si>
   <si>
     <t xml:space="preserve">2.20896172523499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19915652275085</t>
+    <t xml:space="preserve">2.19915676116943</t>
   </si>
   <si>
     <t xml:space="preserve">2.19635510444641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14172673225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20335865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19215321540833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15573382377625</t>
+    <t xml:space="preserve">2.14172649383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2033588886261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19215297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15573358535767</t>
   </si>
   <si>
     <t xml:space="preserve">2.16413807868958</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">2.20756101608276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22997307777405</t>
+    <t xml:space="preserve">2.22997260093689</t>
   </si>
   <si>
     <t xml:space="preserve">2.28320097923279</t>
@@ -1022,70 +1022,70 @@
     <t xml:space="preserve">2.34063100814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35884070396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33082604408264</t>
+    <t xml:space="preserve">2.35884094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33082580566406</t>
   </si>
   <si>
     <t xml:space="preserve">2.30561280250549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26499128341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29720830917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30981516838074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27339553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32242131233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22717142105103</t>
+    <t xml:space="preserve">2.26499152183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.297208070755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30981492996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27339601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32242155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2271716594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.26078915596008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22016763687134</t>
+    <t xml:space="preserve">2.22016787528992</t>
   </si>
   <si>
     <t xml:space="preserve">2.23277449607849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26218962669373</t>
+    <t xml:space="preserve">2.26219010353088</t>
   </si>
   <si>
     <t xml:space="preserve">2.21036243438721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15993595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15713453292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10110521316528</t>
+    <t xml:space="preserve">2.15993618965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15713429450989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1011049747467</t>
   </si>
   <si>
     <t xml:space="preserve">2.13052082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18935132026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2551863193512</t>
+    <t xml:space="preserve">2.1893515586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25518608093262</t>
   </si>
   <si>
     <t xml:space="preserve">2.29300618171692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30421185493469</t>
+    <t xml:space="preserve">2.30421209335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.30141043663025</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">2.31121563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33782958984375</t>
+    <t xml:space="preserve">2.33782982826233</t>
   </si>
   <si>
     <t xml:space="preserve">2.28180003166199</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">2.33642888069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43448042869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45409083366394</t>
+    <t xml:space="preserve">2.43448066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45409107208252</t>
   </si>
   <si>
     <t xml:space="preserve">2.4568920135498</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">2.43307971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43027853965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24117875099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17954635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13192105293274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23417496681213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2047598361969</t>
+    <t xml:space="preserve">2.43027806282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2411789894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17954659461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1319215297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23417520523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20475959777832</t>
   </si>
   <si>
     <t xml:space="preserve">2.1907525062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15153169631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20195817947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18374848365784</t>
+    <t xml:space="preserve">2.15153193473816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20195841789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18374872207642</t>
   </si>
   <si>
     <t xml:space="preserve">2.21456480026245</t>
@@ -1151,103 +1151,103 @@
     <t xml:space="preserve">2.17674493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16834044456482</t>
+    <t xml:space="preserve">2.1683406829834</t>
   </si>
   <si>
     <t xml:space="preserve">2.09690284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10250616073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13332223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10810852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09129977226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0450758934021</t>
+    <t xml:space="preserve">2.1025059223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13332200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10810875892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09130024909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04507565498352</t>
   </si>
   <si>
     <t xml:space="preserve">1.9708366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9120055437088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9274138212204</t>
+    <t xml:space="preserve">1.91200566291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92741394042969</t>
   </si>
   <si>
     <t xml:space="preserve">1.8895937204361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8755863904953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566004753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97924101352692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96943581104279</t>
+    <t xml:space="preserve">1.87558615207672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566028594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97924077510834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96943593025208</t>
   </si>
   <si>
     <t xml:space="preserve">1.92321145534515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96523344516754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9218111038208</t>
+    <t xml:space="preserve">1.96523368358612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181074619293</t>
   </si>
   <si>
     <t xml:space="preserve">1.83496499061584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76492822170258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75232183933258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77193200588226</t>
+    <t xml:space="preserve">1.76492834091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.752321600914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77193188667297</t>
   </si>
   <si>
     <t xml:space="preserve">1.78313791751862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8265608549118</t>
+    <t xml:space="preserve">1.82656073570251</t>
   </si>
   <si>
     <t xml:space="preserve">1.86438059806824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85177397727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395387649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86578154563904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84897243976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8839910030365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99745070934296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04787731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04367470741272</t>
+    <t xml:space="preserve">1.85177409648895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395411491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86578130722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84897267818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88399064540863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99745047092438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04787707328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0436749458313</t>
   </si>
   <si>
     <t xml:space="preserve">1.99604988098145</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">2.15013098716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17114186286926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18725037574768</t>
+    <t xml:space="preserve">2.17114233970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18725061416626</t>
   </si>
   <si>
     <t xml:space="preserve">2.12701869010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14557862281799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10355663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10320615768433</t>
+    <t xml:space="preserve">2.14557838439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10355615615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10320639610291</t>
   </si>
   <si>
     <t xml:space="preserve">2.0282666683197</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">2.1536328792572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16028642654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10600757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03772163391113</t>
+    <t xml:space="preserve">2.16028618812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10600781440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03772187232971</t>
   </si>
   <si>
     <t xml:space="preserve">2.11721348762512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0800940990448</t>
+    <t xml:space="preserve">2.08009433746338</t>
   </si>
   <si>
     <t xml:space="preserve">2.11266136169434</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">2.12736892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1525821685791</t>
+    <t xml:space="preserve">2.15258240699768</t>
   </si>
   <si>
     <t xml:space="preserve">2.18584990501404</t>
@@ -1322,22 +1322,22 @@
     <t xml:space="preserve">2.19425415992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19005227088928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2030086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17604470252991</t>
+    <t xml:space="preserve">2.19005179405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20300889015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17604446411133</t>
   </si>
   <si>
     <t xml:space="preserve">2.1886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01005744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08709764480591</t>
+    <t xml:space="preserve">2.01005721092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08709788322449</t>
   </si>
   <si>
     <t xml:space="preserve">2.12771916389465</t>
@@ -1346,58 +1346,58 @@
     <t xml:space="preserve">2.07624220848083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06643676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11441230773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08394622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822460174561</t>
+    <t xml:space="preserve">2.0664370059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11441254615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08394575119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822436332703</t>
   </si>
   <si>
     <t xml:space="preserve">2.12036514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12071561813354</t>
+    <t xml:space="preserve">2.12071537971497</t>
   </si>
   <si>
     <t xml:space="preserve">1.9634827375412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98274302482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98729526996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96838533878326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94107091426849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03421998023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00620532035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01601052284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03492045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10915899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10775828361511</t>
+    <t xml:space="preserve">1.98274290561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98729515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293782234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96838521957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9410707950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03422021865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0062050819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01601028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03492021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10915923118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10775876045227</t>
   </si>
   <si>
     <t xml:space="preserve">2.14382743835449</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">2.12421727180481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14662909507751</t>
+    <t xml:space="preserve">2.14662933349609</t>
   </si>
   <si>
     <t xml:space="preserve">2.11791372299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888524055481</t>
+    <t xml:space="preserve">2.15888547897339</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857483863831</t>
@@ -1421,58 +1421,58 @@
     <t xml:space="preserve">2.14487814903259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08289527893066</t>
+    <t xml:space="preserve">2.08289551734924</t>
   </si>
   <si>
     <t xml:space="preserve">2.14347743988037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05453038215637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07028913497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09970426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86087882518768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87523639202118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84442031383514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82165825366974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57687926292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47077357769012</t>
+    <t xml:space="preserve">2.05453062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07028889656067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09970450401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8608785867691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87523651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84442019462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82165813446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57687938213348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47077345848083</t>
   </si>
   <si>
     <t xml:space="preserve">1.51839864253998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55446755886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578696250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641047477722</t>
+    <t xml:space="preserve">1.55446767807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578660488129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641059398651</t>
   </si>
   <si>
     <t xml:space="preserve">1.59648978710175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6801837682724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61259829998016</t>
+    <t xml:space="preserve">1.68018364906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61259818077087</t>
   </si>
   <si>
     <t xml:space="preserve">1.71170043945312</t>
@@ -1481,25 +1481,25 @@
     <t xml:space="preserve">1.69874346256256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72465705871582</t>
+    <t xml:space="preserve">1.72465717792511</t>
   </si>
   <si>
     <t xml:space="preserve">1.69138956069946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67808258533478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81990706920624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804051876068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84792160987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78068649768829</t>
+    <t xml:space="preserve">1.67808270454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81990730762482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804039955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84792172908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068661689758</t>
   </si>
   <si>
     <t xml:space="preserve">1.73481249809265</t>
@@ -1508,34 +1508,34 @@
     <t xml:space="preserve">1.70364582538605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7740330696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80590009689331</t>
+    <t xml:space="preserve">1.77403330802917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80589985847473</t>
   </si>
   <si>
     <t xml:space="preserve">1.82586050033569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87173449993134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87243485450745</t>
+    <t xml:space="preserve">1.87173461914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274561405182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87243497371674</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823272705078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85912775993347</t>
+    <t xml:space="preserve">1.85912799835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.8328640460968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81605529785156</t>
+    <t xml:space="preserve">1.81605505943298</t>
   </si>
   <si>
     <t xml:space="preserve">1.85072338581085</t>
@@ -1544,43 +1544,43 @@
     <t xml:space="preserve">1.83601582050323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85807716846466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.853875041008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76807987689972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75337219238281</t>
+    <t xml:space="preserve">1.85807728767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85387527942657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7680801153183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75337243080139</t>
   </si>
   <si>
     <t xml:space="preserve">1.64901745319366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64621615409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337478160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65216898918152</t>
+    <t xml:space="preserve">1.64621579647064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65216910839081</t>
   </si>
   <si>
     <t xml:space="preserve">1.61960184574127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57092618942261</t>
+    <t xml:space="preserve">1.5709263086319</t>
   </si>
   <si>
     <t xml:space="preserve">1.53030490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4697231054306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42630016803741</t>
+    <t xml:space="preserve">1.46972298622131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4263002872467</t>
   </si>
   <si>
     <t xml:space="preserve">1.42524969577789</t>
@@ -1589,25 +1589,25 @@
     <t xml:space="preserve">1.4550154209137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44380939006805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43190312385559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44415950775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43925702571869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40704011917114</t>
+    <t xml:space="preserve">1.44380950927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43190324306488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44415962696075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43925714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40704023838043</t>
   </si>
   <si>
     <t xml:space="preserve">1.43120276927948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40178728103638</t>
+    <t xml:space="preserve">1.40178716182709</t>
   </si>
   <si>
     <t xml:space="preserve">1.358154296875</t>
@@ -1622,40 +1622,40 @@
     <t xml:space="preserve">1.49493634700775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54326188564301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53555762767792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55026531219482</t>
+    <t xml:space="preserve">1.54326164722443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5355578660965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5502655506134</t>
   </si>
   <si>
     <t xml:space="preserve">1.61084723472595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61539959907532</t>
+    <t xml:space="preserve">1.61539947986603</t>
   </si>
   <si>
     <t xml:space="preserve">1.61609995365143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62625539302826</t>
+    <t xml:space="preserve">1.62625551223755</t>
   </si>
   <si>
     <t xml:space="preserve">1.62415421009064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61715078353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64446485042572</t>
+    <t xml:space="preserve">1.61715054512024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6444650888443</t>
   </si>
   <si>
     <t xml:space="preserve">1.64866709709167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48688209056854</t>
+    <t xml:space="preserve">1.48688185214996</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143704414368</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">1.37356245517731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40283787250519</t>
+    <t xml:space="preserve">1.4028377532959</t>
   </si>
   <si>
     <t xml:space="preserve">1.41439390182495</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">1.38602900505066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29638183116913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31108963489532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30520641803741</t>
+    <t xml:space="preserve">1.29638171195984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31108951568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3052065372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.31136977672577</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">1.30758774280548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29960370063782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22550439834595</t>
+    <t xml:space="preserve">1.29960358142853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22550451755524</t>
   </si>
   <si>
     <t xml:space="preserve">1.20673477649689</t>
@@ -1703,70 +1703,70 @@
     <t xml:space="preserve">1.1690548658371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14692330360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09229445457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134457588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08977317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14440178871155</t>
+    <t xml:space="preserve">1.14692318439484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09229457378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134445667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08977329730988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14440166950226</t>
   </si>
   <si>
     <t xml:space="preserve">1.16345202922821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16331171989441</t>
+    <t xml:space="preserve">1.1633118391037</t>
   </si>
   <si>
     <t xml:space="preserve">1.19608926773071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23965203762054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21317791938782</t>
+    <t xml:space="preserve">1.23965191841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21317827701569</t>
   </si>
   <si>
     <t xml:space="preserve">1.22410380840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25477993488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29217970371246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28139388561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27046823501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26640617847443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23923170566559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22606480121613</t>
+    <t xml:space="preserve">1.25478005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29217982292175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28139400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27046811580658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26640605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23923182487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22606492042542</t>
   </si>
   <si>
     <t xml:space="preserve">1.22256302833557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26262402534485</t>
+    <t xml:space="preserve">1.26262414455414</t>
   </si>
   <si>
     <t xml:space="preserve">1.19412803649902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28517591953278</t>
+    <t xml:space="preserve">1.28517603874207</t>
   </si>
   <si>
     <t xml:space="preserve">1.32341611385345</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">1.41194260120392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47392511367798</t>
+    <t xml:space="preserve">1.47392535209656</t>
   </si>
   <si>
     <t xml:space="preserve">1.47147393226624</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">1.53940963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54571306705475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55796933174133</t>
+    <t xml:space="preserve">1.54571294784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55796945095062</t>
   </si>
   <si>
     <t xml:space="preserve">1.47917807102203</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">1.46376991271973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44801163673401</t>
+    <t xml:space="preserve">1.4480117559433</t>
   </si>
   <si>
     <t xml:space="preserve">1.48478090763092</t>
@@ -1811,25 +1811,25 @@
     <t xml:space="preserve">1.49913859367371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47007322311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44345927238464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4045889377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39401304721832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43155288696289</t>
+    <t xml:space="preserve">1.47007310390472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44345939159393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40458881855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39401316642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4315527677536</t>
   </si>
   <si>
     <t xml:space="preserve">1.39443349838257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35605311393738</t>
+    <t xml:space="preserve">1.35605335235596</t>
   </si>
   <si>
     <t xml:space="preserve">1.32285571098328</t>
@@ -1838,58 +1838,58 @@
     <t xml:space="preserve">1.39177203178406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37118124961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43330383300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44170832633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41509425640106</t>
+    <t xml:space="preserve">1.37118113040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43330371379852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44170844554901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41509437561035</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209804058075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42454934120178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38224709033966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34918963909149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29344046115875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33168041706085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32551729679108</t>
+    <t xml:space="preserve">1.42454922199249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38224697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3491895198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29344022274017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33168053627014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551717758179</t>
   </si>
   <si>
     <t xml:space="preserve">1.30058407783508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2948409318924</t>
+    <t xml:space="preserve">1.29484105110168</t>
   </si>
   <si>
     <t xml:space="preserve">1.25996267795563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26864731311798</t>
+    <t xml:space="preserve">1.26864719390869</t>
   </si>
   <si>
     <t xml:space="preserve">1.24721598625183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27845239639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26206374168396</t>
+    <t xml:space="preserve">1.27845227718353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26206386089325</t>
   </si>
   <si>
     <t xml:space="preserve">1.24917697906494</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">1.21892118453979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2291464805603</t>
+    <t xml:space="preserve">1.22914636135101</t>
   </si>
   <si>
     <t xml:space="preserve">1.20897591114044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3185133934021</t>
+    <t xml:space="preserve">1.29400050640106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31851351261139</t>
   </si>
   <si>
     <t xml:space="preserve">1.31417119503021</t>
@@ -1928,28 +1928,28 @@
     <t xml:space="preserve">1.2770516872406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36571836471558</t>
+    <t xml:space="preserve">1.36571848392487</t>
   </si>
   <si>
     <t xml:space="preserve">1.3850485086441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37706434726715</t>
+    <t xml:space="preserve">1.37706422805786</t>
   </si>
   <si>
     <t xml:space="preserve">1.35969507694244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32775831222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31473159790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3601154088974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40879094600677</t>
+    <t xml:space="preserve">1.32775843143463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3147314786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36011552810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40879082679749</t>
   </si>
   <si>
     <t xml:space="preserve">1.47287464141846</t>
@@ -1958,31 +1958,31 @@
     <t xml:space="preserve">1.49318528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46412014961243</t>
+    <t xml:space="preserve">1.46412026882172</t>
   </si>
   <si>
     <t xml:space="preserve">1.43505489826202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41544425487518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37566351890564</t>
+    <t xml:space="preserve">1.41544437408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37566363811493</t>
   </si>
   <si>
     <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35675358772278</t>
+    <t xml:space="preserve">1.35675346851349</t>
   </si>
   <si>
     <t xml:space="preserve">1.34372675418854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40318810939789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37720429897308</t>
+    <t xml:space="preserve">1.4031879901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37720453739166</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
@@ -1991,91 +1991,91 @@
     <t xml:space="preserve">1.39149177074432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38112640380859</t>
+    <t xml:space="preserve">1.38112652301788</t>
   </si>
   <si>
     <t xml:space="preserve">1.32103478908539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30296528339386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28615665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32019424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28937804698944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28993844985962</t>
+    <t xml:space="preserve">1.30296516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28615653514862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32019448280334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28937816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28993833065033</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824862003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33175039291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.359414935112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36606860160828</t>
+    <t xml:space="preserve">1.3317506313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35941505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36606848239899</t>
   </si>
   <si>
     <t xml:space="preserve">1.36641871929169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221659183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37587380409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37727439403534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37622380256653</t>
+    <t xml:space="preserve">1.36221647262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37587368488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37727451324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37622392177582</t>
   </si>
   <si>
     <t xml:space="preserve">1.43575513362885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45956778526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828279972076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43855667114258</t>
+    <t xml:space="preserve">1.45956790447235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828268051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43855655193329</t>
   </si>
   <si>
     <t xml:space="preserve">1.4917848110199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48127901554108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44205856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38077616691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38532865047455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27221918106079</t>
+    <t xml:space="preserve">1.48127913475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44205844402313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38077628612518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38532876968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2722190618515</t>
   </si>
   <si>
     <t xml:space="preserve">1.24595546722412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1997309923172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19062638282776</t>
+    <t xml:space="preserve">1.19973111152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19062614440918</t>
   </si>
   <si>
     <t xml:space="preserve">1.19798004627228</t>
@@ -2087,22 +2087,22 @@
     <t xml:space="preserve">1.20918607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19587886333466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18082118034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15525770187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17171609401703</t>
+    <t xml:space="preserve">1.19587910175323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18082106113434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15525758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17171621322632</t>
   </si>
   <si>
     <t xml:space="preserve">1.14370155334473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13914906978607</t>
+    <t xml:space="preserve">1.13914918899536</t>
   </si>
   <si>
     <t xml:space="preserve">1.1493045091629</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">1.15350675582886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19377779960632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16716372966766</t>
+    <t xml:space="preserve">1.19377791881561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16716384887695</t>
   </si>
   <si>
     <t xml:space="preserve">1.14160048961639</t>
@@ -2144,103 +2144,103 @@
     <t xml:space="preserve">1.25365936756134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24560523033142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23790121078491</t>
+    <t xml:space="preserve">1.24560511112213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23790109157562</t>
   </si>
   <si>
     <t xml:space="preserve">1.23474943637848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24875688552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26451504230499</t>
+    <t xml:space="preserve">1.24875676631927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26451528072357</t>
   </si>
   <si>
     <t xml:space="preserve">1.24105262756348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23825132846832</t>
+    <t xml:space="preserve">1.23825120925903</t>
   </si>
   <si>
     <t xml:space="preserve">1.31949400901794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36256682872772</t>
+    <t xml:space="preserve">1.36256659030914</t>
   </si>
   <si>
     <t xml:space="preserve">1.36992061138153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33525240421295</t>
+    <t xml:space="preserve">1.33525228500366</t>
   </si>
   <si>
     <t xml:space="preserve">1.32264566421509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33350145816803</t>
+    <t xml:space="preserve">1.33350133895874</t>
   </si>
   <si>
     <t xml:space="preserve">1.33630287647247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34295654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31214010715485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3457578420639</t>
+    <t xml:space="preserve">1.34295630455017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31214022636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34575772285461</t>
   </si>
   <si>
     <t xml:space="preserve">1.32439661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914365291595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22634494304657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23159778118134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2372008562088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23124766349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21163737773895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17241680622101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18222165107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18817496299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18467307090759</t>
+    <t xml:space="preserve">1.31914377212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22634506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23159766197205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23720073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23124754428864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21163725852966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17241668701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18222177028656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18817484378815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1846729516983</t>
   </si>
   <si>
     <t xml:space="preserve">1.1860738992691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24210333824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26731657981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15175580978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13529717922211</t>
+    <t xml:space="preserve">1.24210321903229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26731646060944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15175592899323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13529706001282</t>
   </si>
   <si>
     <t xml:space="preserve">1.18047106266022</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">1.20603430271149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17521798610687</t>
+    <t xml:space="preserve">1.17521810531616</t>
   </si>
   <si>
     <t xml:space="preserve">1.18992590904236</t>
@@ -2267,10 +2267,10 @@
     <t xml:space="preserve">1.21653985977173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23404896259308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27467060089111</t>
+    <t xml:space="preserve">1.23404908180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27467048168182</t>
   </si>
   <si>
     <t xml:space="preserve">1.286576628685</t>
@@ -2285,34 +2285,34 @@
     <t xml:space="preserve">1.27186906337738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26906740665436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30548655986786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32474684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31844353675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3517107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31424117088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34050512313843</t>
+    <t xml:space="preserve">1.26906752586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30548644065857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32474672794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31844341754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35171091556549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31424105167389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34050524234772</t>
   </si>
   <si>
     <t xml:space="preserve">1.36816966533661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35066032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29743242263794</t>
+    <t xml:space="preserve">1.35066056251526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29743218421936</t>
   </si>
   <si>
     <t xml:space="preserve">1.31003904342651</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">1.33210051059723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29007863998413</t>
+    <t xml:space="preserve">1.29007852077484</t>
   </si>
   <si>
     <t xml:space="preserve">1.27081847190857</t>
@@ -2339,16 +2339,16 @@
     <t xml:space="preserve">1.31249034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32789850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28307497501373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3096889257431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42384874820709</t>
+    <t xml:space="preserve">1.32789838314056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28307485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30968880653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42384898662567</t>
   </si>
   <si>
     <t xml:space="preserve">1.50929379463196</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">1.4686723947525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42314863204956</t>
+    <t xml:space="preserve">1.42314851284027</t>
   </si>
   <si>
     <t xml:space="preserve">1.42665040493011</t>
@@ -2375,40 +2375,40 @@
     <t xml:space="preserve">1.47777712345123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49528658390045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49388551712036</t>
+    <t xml:space="preserve">1.49528646469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49388563632965</t>
   </si>
   <si>
     <t xml:space="preserve">1.44766128063202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42104756832123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264307498932</t>
+    <t xml:space="preserve">1.42104744911194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264295578003</t>
   </si>
   <si>
     <t xml:space="preserve">1.41754555702209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41614496707916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44135797023773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536553859711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46517062187195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43085253238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4182460308075</t>
+    <t xml:space="preserve">1.41614484786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44135808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4553656578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46517074108124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43085265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41824591159821</t>
   </si>
   <si>
     <t xml:space="preserve">1.38813018798828</t>
@@ -2417,73 +2417,73 @@
     <t xml:space="preserve">1.3741227388382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41474401950836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40353810787201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4098414182663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45326435565948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42034721374512</t>
+    <t xml:space="preserve">1.41474413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4035382270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40984153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45326447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42034709453583</t>
   </si>
   <si>
     <t xml:space="preserve">1.36851990222931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37797474861145</t>
+    <t xml:space="preserve">1.37797486782074</t>
   </si>
   <si>
     <t xml:space="preserve">1.38637924194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46166861057281</t>
+    <t xml:space="preserve">1.4616687297821</t>
   </si>
   <si>
     <t xml:space="preserve">1.42594993114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43435442447662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43365406990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287723064423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36886990070343</t>
+    <t xml:space="preserve">1.43435454368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4336541891098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287734985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36887001991272</t>
   </si>
   <si>
     <t xml:space="preserve">1.39373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36431741714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29568147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35836434364319</t>
+    <t xml:space="preserve">1.36431753635406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29568135738373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35836458206177</t>
   </si>
   <si>
     <t xml:space="preserve">1.37307226657867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727192401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52049970626831</t>
+    <t xml:space="preserve">1.46727156639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5204998254776</t>
   </si>
   <si>
     <t xml:space="preserve">1.54641330242157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72010457515717</t>
+    <t xml:space="preserve">1.72010469436646</t>
   </si>
   <si>
     <t xml:space="preserve">1.44626080989838</t>
@@ -2495,46 +2495,46 @@
     <t xml:space="preserve">1.30128443241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1423008441925</t>
+    <t xml:space="preserve">1.14230096340179</t>
   </si>
   <si>
     <t xml:space="preserve">1.09397542476654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05755627155304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905926465988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861102998256683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926937520503998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772156119346619</t>
+    <t xml:space="preserve">1.05755615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905926525592804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861102879047394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926937639713287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772156059741974</t>
   </si>
   <si>
     <t xml:space="preserve">0.888417303562164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81803023815155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874409914016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874760031700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885966002941132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877561509609222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870207786560059</t>
+    <t xml:space="preserve">0.818030297756195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874409973621368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874760150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885965943336487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877561688423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870207726955414</t>
   </si>
   <si>
     <t xml:space="preserve">0.926587402820587</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">0.912930250167847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925886988639832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880713284015656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849196672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840442061424255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633253574371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846044898033142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83098703622818</t>
+    <t xml:space="preserve">0.925887048244476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8807133436203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84919661283493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8404421210289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633193969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846045017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830987095832825</t>
   </si>
   <si>
     <t xml:space="preserve">0.851297736167908</t>
@@ -2570,58 +2570,58 @@
     <t xml:space="preserve">0.829936444759369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853048801422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820131421089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777408838272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778459489345551</t>
+    <t xml:space="preserve">0.85304868221283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820131361484528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77740889787674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778459429740906</t>
   </si>
   <si>
     <t xml:space="preserve">0.778809607028961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753246188163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751845479011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771805942058563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743791282176971</t>
+    <t xml:space="preserve">0.753246128559113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751845419406891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771806001663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743791222572327</t>
   </si>
   <si>
     <t xml:space="preserve">0.768304109573364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789665281772614</t>
+    <t xml:space="preserve">0.789665400981903</t>
   </si>
   <si>
     <t xml:space="preserve">0.809625804424286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779860198497772</t>
+    <t xml:space="preserve">0.779860258102417</t>
   </si>
   <si>
     <t xml:space="preserve">0.766553103923798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781611084938049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776008248329163</t>
+    <t xml:space="preserve">0.781611144542694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776008129119873</t>
   </si>
   <si>
     <t xml:space="preserve">0.765152454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803672730922699</t>
+    <t xml:space="preserve">0.803672671318054</t>
   </si>
   <si>
     <t xml:space="preserve">0.812077105045319</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">0.807874858379364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785463094711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781260967254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819080829620361</t>
+    <t xml:space="preserve">0.785463154315948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781260907649994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819080770015717</t>
   </si>
   <si>
     <t xml:space="preserve">0.759199321269989</t>
@@ -2645,58 +2645,58 @@
     <t xml:space="preserve">0.756047606468201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730484127998352</t>
+    <t xml:space="preserve">0.730484187602997</t>
   </si>
   <si>
     <t xml:space="preserve">0.736087143421173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743441045284271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779159724712372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815228700637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805773854255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858301401138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872308671474457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89296966791153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931840062141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99487316608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00853049755096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979114949703217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966858625411987</t>
+    <t xml:space="preserve">0.743440926074982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779159843921661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815228819847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805773913860321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858301341533661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872308790683746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892969727516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931840121746063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994873285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00853037834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979115068912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966858565807343</t>
   </si>
   <si>
     <t xml:space="preserve">0.891218721866608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895070791244507</t>
+    <t xml:space="preserve">0.895070731639862</t>
   </si>
   <si>
     <t xml:space="preserve">0.901724338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967909216880798</t>
+    <t xml:space="preserve">0.967908978462219</t>
   </si>
   <si>
     <t xml:space="preserve">0.964407205581665</t>
@@ -2705,43 +2705,43 @@
     <t xml:space="preserve">0.946897983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.936392545700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938493609428406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96510773897171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913980722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934641659259796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899623155593872</t>
+    <t xml:space="preserve">0.936392486095428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938493669033051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965107619762421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913980782032013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934641480445862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899623095989227</t>
   </si>
   <si>
     <t xml:space="preserve">0.953551590442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930089294910431</t>
+    <t xml:space="preserve">0.930089235305786</t>
   </si>
   <si>
     <t xml:space="preserve">0.909078121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954602181911469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943746268749237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983317255973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973161995410919</t>
+    <t xml:space="preserve">0.954602122306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943746387958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983317196369171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973161816596985</t>
   </si>
   <si>
     <t xml:space="preserve">0.95145046710968</t>
@@ -2753,34 +2753,34 @@
     <t xml:space="preserve">0.933941185474396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948298692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957403540611267</t>
+    <t xml:space="preserve">0.948298871517181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957403421401978</t>
   </si>
   <si>
     <t xml:space="preserve">0.97351211309433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980865836143494</t>
+    <t xml:space="preserve">0.980865895748138</t>
   </si>
   <si>
     <t xml:space="preserve">1.033043384552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03759574890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00012624263763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998725354671478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9609055519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967208802700043</t>
+    <t xml:space="preserve">1.03759586811066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00012600421906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998725235462189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960905373096466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967208623886108</t>
   </si>
   <si>
     <t xml:space="preserve">0.944096565246582</t>
@@ -2795,22 +2795,22 @@
     <t xml:space="preserve">0.874059736728668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913280427455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927637994289398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907677352428436</t>
+    <t xml:space="preserve">0.913280367851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927637815475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907677412033081</t>
   </si>
   <si>
     <t xml:space="preserve">0.890868484973907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915381550788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978764832019806</t>
+    <t xml:space="preserve">0.915381491184235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978764772415161</t>
   </si>
   <si>
     <t xml:space="preserve">0.971060812473297</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">0.997324585914612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981566190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00923073291779</t>
+    <t xml:space="preserve">0.981566250324249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00923085212708</t>
   </si>
   <si>
     <t xml:space="preserve">0.98681902885437</t>
@@ -2837,37 +2837,37 @@
     <t xml:space="preserve">1.00712966918945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996624171733856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999775946140289</t>
+    <t xml:space="preserve">0.996624231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999775826931</t>
   </si>
   <si>
     <t xml:space="preserve">1.00467848777771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988919973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985768616199493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970360398292542</t>
+    <t xml:space="preserve">0.988920152187347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985768437385559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970360219478607</t>
   </si>
   <si>
     <t xml:space="preserve">0.958103954792023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994522929191589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978414535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986118614673615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03724551200867</t>
+    <t xml:space="preserve">0.994523048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97841465473175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986118674278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03724563121796</t>
   </si>
   <si>
     <t xml:space="preserve">1.02148723602295</t>
@@ -2876,19 +2876,19 @@
     <t xml:space="preserve">1.01903605461121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01203238964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99557363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973862290382385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916782200336456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922735333442688</t>
+    <t xml:space="preserve">1.01203227043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9955735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97386223077774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916782259941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922735393047333</t>
   </si>
   <si>
     <t xml:space="preserve">0.888067185878754</t>
@@ -2900,61 +2900,61 @@
     <t xml:space="preserve">0.961605727672577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972811818122864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05405426025391</t>
+    <t xml:space="preserve">0.972811758518219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0540543794632</t>
   </si>
   <si>
     <t xml:space="preserve">1.11113440990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09957826137543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16121065616608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18502342700958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1696150302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15910959243774</t>
+    <t xml:space="preserve">1.09957838058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16121077537537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18502330780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16961514949799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15910971164703</t>
   </si>
   <si>
     <t xml:space="preserve">1.12339091300964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12829351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1279433965683</t>
+    <t xml:space="preserve">1.12829327583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12794327735901</t>
   </si>
   <si>
     <t xml:space="preserve">1.16016018390656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13564741611481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17066562175751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545238018036</t>
+    <t xml:space="preserve">1.13564729690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17066586017609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545249938965</t>
   </si>
   <si>
     <t xml:space="preserve">1.15280640125275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17591845989227</t>
+    <t xml:space="preserve">1.17591857910156</t>
   </si>
   <si>
     <t xml:space="preserve">1.15560781955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13214540481567</t>
+    <t xml:space="preserve">1.13214552402496</t>
   </si>
   <si>
     <t xml:space="preserve">1.08522081375122</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">1.08627128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12899386882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1500049829483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15210592746735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15490758419037</t>
+    <t xml:space="preserve">1.12899374961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15000474452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15210604667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15490746498108</t>
   </si>
   <si>
     <t xml:space="preserve">1.15455734729767</t>
@@ -2987,25 +2987,25 @@
     <t xml:space="preserve">1.25120806694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25611054897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27502059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30793797969818</t>
+    <t xml:space="preserve">1.25611066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27502071857452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
     <t xml:space="preserve">1.32684791088104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35801434516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32334613800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31879365444183</t>
+    <t xml:space="preserve">1.35801422595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32334589958191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31879377365112</t>
   </si>
   <si>
     <t xml:space="preserve">1.29603159427643</t>
@@ -3014,19 +3014,19 @@
     <t xml:space="preserve">1.31389117240906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30723762512207</t>
+    <t xml:space="preserve">1.30723750591278</t>
   </si>
   <si>
     <t xml:space="preserve">1.29498112201691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28482580184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26941752433777</t>
+    <t xml:space="preserve">1.28482592105865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28027319908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26941776275635</t>
   </si>
   <si>
     <t xml:space="preserve">1.2431538105011</t>
@@ -3035,22 +3035,22 @@
     <t xml:space="preserve">1.25435972213745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2725692987442</t>
+    <t xml:space="preserve">1.27256953716278</t>
   </si>
   <si>
     <t xml:space="preserve">1.26136338710785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26661610603333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26416492462158</t>
+    <t xml:space="preserve">1.26661622524261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26416480541229</t>
   </si>
   <si>
     <t xml:space="preserve">1.26521551609039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26766681671143</t>
+    <t xml:space="preserve">1.26766669750214</t>
   </si>
   <si>
     <t xml:space="preserve">1.26626598834991</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">1.32964932918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36957049369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34505748748779</t>
+    <t xml:space="preserve">1.36957037448883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3450573682785</t>
   </si>
   <si>
     <t xml:space="preserve">1.34925961494446</t>
@@ -3077,34 +3077,34 @@
     <t xml:space="preserve">1.33455193042755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31529188156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31809306144714</t>
+    <t xml:space="preserve">1.31529176235199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31809341907501</t>
   </si>
   <si>
     <t xml:space="preserve">1.31073951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31774294376373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2806236743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24735617637634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26696622371674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25015759468079</t>
+    <t xml:space="preserve">1.31774306297302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28062379360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24735605716705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26696646213531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2501574754715</t>
   </si>
   <si>
     <t xml:space="preserve">1.29112911224365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27432024478912</t>
+    <t xml:space="preserve">1.27432036399841</t>
   </si>
   <si>
     <t xml:space="preserve">1.29953348636627</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">1.34820902347565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42174780368805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52260076999664</t>
+    <t xml:space="preserve">1.42174768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52260088920593</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190065383911</t>
@@ -3125,88 +3125,88 @@
     <t xml:space="preserve">1.53240597248077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4889829158783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50088930130005</t>
+    <t xml:space="preserve">1.4980880022049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48898303508759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50088942050934</t>
   </si>
   <si>
     <t xml:space="preserve">1.51629745960236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50789320468903</t>
+    <t xml:space="preserve">1.50789332389832</t>
   </si>
   <si>
     <t xml:space="preserve">1.51979947090149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54851448535919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54361188411713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60594475269318</t>
+    <t xml:space="preserve">1.54851460456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54361200332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6059445142746</t>
   </si>
   <si>
     <t xml:space="preserve">1.62695562839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62065267562866</t>
+    <t xml:space="preserve">1.62065231800079</t>
   </si>
   <si>
     <t xml:space="preserve">1.59053659439087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59193742275238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70119476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72360646724701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7102997303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70469641685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7110002040863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881982803345</t>
+    <t xml:space="preserve">1.59193730354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909369945526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70119488239288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7236065864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71029949188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70469677448273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71100008487701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881994724274</t>
   </si>
   <si>
     <t xml:space="preserve">1.70539689064026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68998873233795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65356993675232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63536012172699</t>
+    <t xml:space="preserve">1.68998908996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65356981754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63536024093628</t>
   </si>
   <si>
     <t xml:space="preserve">1.64936745166779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63465988636017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6283563375473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66547620296478</t>
+    <t xml:space="preserve">1.63466000556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62835621833801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6654759645462</t>
   </si>
   <si>
     <t xml:space="preserve">1.71505236625671</t>
@@ -3218,28 +3218,28 @@
     <t xml:space="preserve">1.59937429428101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61302578449249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308478355408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65613555908203</t>
+    <t xml:space="preserve">1.6130256652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308466434479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65613567829132</t>
   </si>
   <si>
     <t xml:space="preserve">1.67337954044342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71936321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71289706230164</t>
+    <t xml:space="preserve">1.71936309337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71289694309235</t>
   </si>
   <si>
     <t xml:space="preserve">1.70283770561218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445177078247</t>
+    <t xml:space="preserve">1.73445165157318</t>
   </si>
   <si>
     <t xml:space="preserve">1.71145975589752</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">1.74522924423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893961429596</t>
+    <t xml:space="preserve">1.76893973350525</t>
   </si>
   <si>
     <t xml:space="preserve">1.76822113990784</t>
@@ -3260,19 +3260,19 @@
     <t xml:space="preserve">1.83504128456116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85587763786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8644996881485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126095294952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95934152603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97299253940582</t>
+    <t xml:space="preserve">1.85587751865387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86449980735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95934128761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97299265861511</t>
   </si>
   <si>
     <t xml:space="preserve">1.98377025127411</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">1.94066035747528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96508944034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99742162227631</t>
+    <t xml:space="preserve">1.96508920192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9974217414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.02400612831116</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">2.08579683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08795213699341</t>
+    <t xml:space="preserve">2.08795237541199</t>
   </si>
   <si>
     <t xml:space="preserve">2.10375905036926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12531423568726</t>
+    <t xml:space="preserve">2.12531399726868</t>
   </si>
   <si>
     <t xml:space="preserve">2.13465452194214</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">2.15189814567566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423080444336</t>
+    <t xml:space="preserve">2.18423104286194</t>
   </si>
   <si>
     <t xml:space="preserve">2.17201638221741</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">2.17560887336731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17632722854614</t>
+    <t xml:space="preserve">2.17632746696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.16052055358887</t>
@@ -3335,10 +3335,10 @@
     <t xml:space="preserve">2.12818813323975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08938884735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076739311218</t>
+    <t xml:space="preserve">2.08938908576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0807671546936</t>
   </si>
   <si>
     <t xml:space="preserve">2.05346441268921</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">2.04053139686584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9830516576767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96652615070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94928240776062</t>
+    <t xml:space="preserve">1.98305153846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96652626991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94928228855133</t>
   </si>
   <si>
     <t xml:space="preserve">1.9521564245224</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">1.83288598060608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93922328948975</t>
+    <t xml:space="preserve">1.93922340869904</t>
   </si>
   <si>
     <t xml:space="preserve">1.93634939193726</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">1.91766822338104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88821017742157</t>
+    <t xml:space="preserve">1.88821005821228</t>
   </si>
   <si>
     <t xml:space="preserve">1.88749158382416</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">1.84653723239899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78762030601501</t>
+    <t xml:space="preserve">1.78762018680573</t>
   </si>
   <si>
     <t xml:space="preserve">1.82641935348511</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">1.8752772808075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85803318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90258002281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87743246555328</t>
+    <t xml:space="preserve">1.85803306102753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90258014202118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87743234634399</t>
   </si>
   <si>
     <t xml:space="preserve">1.89108383655548</t>
@@ -3419,19 +3419,19 @@
     <t xml:space="preserve">1.82067143917084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81348621845245</t>
+    <t xml:space="preserve">1.81348633766174</t>
   </si>
   <si>
     <t xml:space="preserve">1.82857477664948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96724462509155</t>
+    <t xml:space="preserve">1.96724474430084</t>
   </si>
   <si>
     <t xml:space="preserve">1.97371113300323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95718574523926</t>
+    <t xml:space="preserve">1.95718586444855</t>
   </si>
   <si>
     <t xml:space="preserve">2.03190946578979</t>
@@ -3440,13 +3440,13 @@
     <t xml:space="preserve">2.00676202774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00388836860657</t>
+    <t xml:space="preserve">2.00388813018799</t>
   </si>
   <si>
     <t xml:space="preserve">1.97155570983887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93347537517548</t>
+    <t xml:space="preserve">1.93347549438477</t>
   </si>
   <si>
     <t xml:space="preserve">1.90904629230499</t>
@@ -3455,25 +3455,25 @@
     <t xml:space="preserve">1.9420975446701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97802209854126</t>
+    <t xml:space="preserve">1.97802233695984</t>
   </si>
   <si>
     <t xml:space="preserve">2.01107287406921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99957716464996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01753973960876</t>
+    <t xml:space="preserve">1.99957704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01753950119019</t>
   </si>
   <si>
     <t xml:space="preserve">2.03262805938721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0311906337738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99167370796204</t>
+    <t xml:space="preserve">2.03119087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99167382717133</t>
   </si>
   <si>
     <t xml:space="preserve">2.01322865486145</t>
@@ -3488,22 +3488,22 @@
     <t xml:space="preserve">1.9377863407135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96868205070496</t>
+    <t xml:space="preserve">1.96868193149567</t>
   </si>
   <si>
     <t xml:space="preserve">1.92269802093506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94712686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92916405200958</t>
+    <t xml:space="preserve">1.94712698459625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92916429042816</t>
   </si>
   <si>
     <t xml:space="preserve">1.83073031902313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84078919887543</t>
+    <t xml:space="preserve">1.84078931808472</t>
   </si>
   <si>
     <t xml:space="preserve">1.92054259777069</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">1.97586667537689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92341637611389</t>
+    <t xml:space="preserve">1.92341661453247</t>
   </si>
   <si>
     <t xml:space="preserve">1.94353425502777</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">1.94425284862518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91838681697845</t>
+    <t xml:space="preserve">1.91838693618774</t>
   </si>
   <si>
     <t xml:space="preserve">2.02616143226624</t>
@@ -3536,22 +3536,22 @@
     <t xml:space="preserve">2.03047227859497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93994200229645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04340529441833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10016679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12387728691101</t>
+    <t xml:space="preserve">1.93994188308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04340553283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10016655921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12315845489502</t>
+    <t xml:space="preserve">2.1231586933136</t>
   </si>
   <si>
     <t xml:space="preserve">2.13034343719482</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">2.08148598670959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92988312244415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93563103675842</t>
+    <t xml:space="preserve">1.92988300323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93563091754913</t>
   </si>
   <si>
     <t xml:space="preserve">1.97083735466003</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">2.00316977500916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98592555522919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95143783092499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042459964752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88318061828613</t>
+    <t xml:space="preserve">1.9859254360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042436122894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88318049907684</t>
   </si>
   <si>
     <t xml:space="preserve">1.85372221469879</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">1.7459477186203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77540600299835</t>
+    <t xml:space="preserve">1.77540612220764</t>
   </si>
   <si>
     <t xml:space="preserve">1.77181375026703</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">1.88533616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92557215690613</t>
+    <t xml:space="preserve">1.92557203769684</t>
   </si>
   <si>
     <t xml:space="preserve">1.8896472454071</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">1.8673734664917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89395809173584</t>
+    <t xml:space="preserve">1.89395797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.89036571979523</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">1.85444056987762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84797418117523</t>
+    <t xml:space="preserve">1.84797430038452</t>
   </si>
   <si>
     <t xml:space="preserve">1.79767942428589</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">1.85515940189362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88605451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683210849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97874069213867</t>
+    <t xml:space="preserve">1.88605463504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683222770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97874057292938</t>
   </si>
   <si>
     <t xml:space="preserve">2.00101399421692</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">2.06280493736267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05849409103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06424164772034</t>
+    <t xml:space="preserve">2.05849385261536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06424188613892</t>
   </si>
   <si>
     <t xml:space="preserve">2.0563383102417</t>
@@ -3689,31 +3689,31 @@
     <t xml:space="preserve">2.0527458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02113175392151</t>
+    <t xml:space="preserve">2.02113199234009</t>
   </si>
   <si>
     <t xml:space="preserve">2.00460648536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01251029968262</t>
+    <t xml:space="preserve">2.01251006126404</t>
   </si>
   <si>
     <t xml:space="preserve">1.99526607990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89970600605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87958788871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93131983280182</t>
+    <t xml:space="preserve">1.8997061252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87958800792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93131971359253</t>
   </si>
   <si>
     <t xml:space="preserve">1.96221530437469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91192054748535</t>
+    <t xml:space="preserve">1.91192042827606</t>
   </si>
   <si>
     <t xml:space="preserve">2.02041363716125</t>
@@ -3722,16 +3722,16 @@
     <t xml:space="preserve">2.06855273246765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10447788238525</t>
+    <t xml:space="preserve">2.10447764396667</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645630836487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09657406806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15117979049683</t>
+    <t xml:space="preserve">2.09657430648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15118002891541</t>
   </si>
   <si>
     <t xml:space="preserve">2.32505631446838</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">2.6081440448761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928611755371</t>
+    <t xml:space="preserve">2.55928635597229</t>
   </si>
   <si>
     <t xml:space="preserve">2.527672290802</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">2.21584486961365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26398396492004</t>
+    <t xml:space="preserve">2.26398420333862</t>
   </si>
   <si>
     <t xml:space="preserve">2.21368932723999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496024131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120207309723</t>
+    <t xml:space="preserve">2.06496047973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120195388794</t>
   </si>
   <si>
     <t xml:space="preserve">1.66475737094879</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">1.74954009056091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79480540752411</t>
+    <t xml:space="preserve">1.7948055267334</t>
   </si>
   <si>
     <t xml:space="preserve">1.83575963973999</t>
@@ -3800,25 +3800,25 @@
     <t xml:space="preserve">2.06783437728882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96077823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9586226940155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98879981040955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95574879646301</t>
+    <t xml:space="preserve">1.96077811717987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95862281322479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98879969120026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9557489156723</t>
   </si>
   <si>
     <t xml:space="preserve">1.95359337329865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06208658218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93275678157806</t>
+    <t xml:space="preserve">2.06208634376526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93275666236877</t>
   </si>
   <si>
     <t xml:space="preserve">1.99095487594604</t>
@@ -3830,19 +3830,19 @@
     <t xml:space="preserve">1.9478452205658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16626834869385</t>
+    <t xml:space="preserve">2.16626858711243</t>
   </si>
   <si>
     <t xml:space="preserve">2.12459564208984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1957266330719</t>
+    <t xml:space="preserve">2.19572687149048</t>
   </si>
   <si>
     <t xml:space="preserve">2.19860076904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2307755947113</t>
+    <t xml:space="preserve">2.23077535629272</t>
   </si>
   <si>
     <t xml:space="preserve">2.33036375045776</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">2.24839472770691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23383951187134</t>
+    <t xml:space="preserve">2.23383975028992</t>
   </si>
   <si>
     <t xml:space="preserve">2.21085786819458</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">2.23307371139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21545433998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28286790847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26448225975037</t>
+    <t xml:space="preserve">2.2154541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2828676700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26448249816895</t>
   </si>
   <si>
     <t xml:space="preserve">2.31351017951965</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45523190498352</t>
+    <t xml:space="preserve">2.45523166656494</t>
   </si>
   <si>
     <t xml:space="preserve">2.47285151481628</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">2.4820442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4866406917572</t>
+    <t xml:space="preserve">2.48664045333862</t>
   </si>
   <si>
     <t xml:space="preserve">2.46365880966187</t>
@@ -3935,10 +3935,10 @@
     <t xml:space="preserve">2.41309881210327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43071794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37709331512451</t>
+    <t xml:space="preserve">2.43071818351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37709355354309</t>
   </si>
   <si>
     <t xml:space="preserve">2.09058618545532</t>
@@ -3947,10 +3947,10 @@
     <t xml:space="preserve">1.98793363571167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01168131828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08062744140625</t>
+    <t xml:space="preserve">2.0116810798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08062720298767</t>
   </si>
   <si>
     <t xml:space="preserve">2.02623653411865</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">2.16795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21315574645996</t>
+    <t xml:space="preserve">2.21315598487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.19936680793762</t>
@@ -3974,22 +3974,22 @@
     <t xml:space="preserve">2.20089888572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14267802238464</t>
+    <t xml:space="preserve">2.14267826080322</t>
   </si>
   <si>
     <t xml:space="preserve">2.14191246032715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14650869369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03159880638123</t>
+    <t xml:space="preserve">2.14650845527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0315990447998</t>
   </si>
   <si>
     <t xml:space="preserve">1.99406206607819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9029004573822</t>
+    <t xml:space="preserve">1.90290057659149</t>
   </si>
   <si>
     <t xml:space="preserve">1.86919391155243</t>
@@ -4043,13 +4043,13 @@
     <t xml:space="preserve">1.86306500434875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92894673347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92052006721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96954810619354</t>
+    <t xml:space="preserve">1.92894661426544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92051994800568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96954822540283</t>
   </si>
   <si>
     <t xml:space="preserve">2.06837034225464</t>
@@ -4064,13 +4064,13 @@
     <t xml:space="preserve">1.98869955539703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97184610366821</t>
+    <t xml:space="preserve">1.97184598445892</t>
   </si>
   <si>
     <t xml:space="preserve">1.95652496814728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99176371097565</t>
+    <t xml:space="preserve">1.99176383018494</t>
   </si>
   <si>
     <t xml:space="preserve">2.07220029830933</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">1.87762033939362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90826296806335</t>
+    <t xml:space="preserve">1.90826284885406</t>
   </si>
   <si>
     <t xml:space="preserve">1.86076700687408</t>
@@ -4100,22 +4100,22 @@
     <t xml:space="preserve">1.80944073200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86612963676453</t>
+    <t xml:space="preserve">1.86612951755524</t>
   </si>
   <si>
     <t xml:space="preserve">1.89830422401428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90213453769684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87149202823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9687819480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90060222148895</t>
+    <t xml:space="preserve">1.90213441848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8714919090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96878182888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90060234069824</t>
   </si>
   <si>
     <t xml:space="preserve">1.90673089027405</t>
@@ -4124,13 +4124,13 @@
     <t xml:space="preserve">1.89907014369965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9971262216568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06070947647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12199425697327</t>
+    <t xml:space="preserve">1.99712634086609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06070971488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12199449539185</t>
   </si>
   <si>
     <t xml:space="preserve">2.08445739746094</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">2.1901741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21392226219177</t>
+    <t xml:space="preserve">2.21392202377319</t>
   </si>
   <si>
     <t xml:space="preserve">2.15799927711487</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">2.17791700363159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10820555686951</t>
+    <t xml:space="preserve">2.10820531845093</t>
   </si>
   <si>
     <t xml:space="preserve">2.03006720542908</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">2.07986092567444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05151677131653</t>
+    <t xml:space="preserve">2.05151653289795</t>
   </si>
   <si>
     <t xml:space="preserve">2.05304884910583</t>
@@ -4190,22 +4190,22 @@
     <t xml:space="preserve">2.11893033981323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17485284805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17255473136902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17332053184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1932384967804</t>
+    <t xml:space="preserve">2.17485308647156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17255449295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17332077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19323825836182</t>
   </si>
   <si>
     <t xml:space="preserve">2.22617888450623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21698665618896</t>
+    <t xml:space="preserve">2.21698641777039</t>
   </si>
   <si>
     <t xml:space="preserve">2.3173406124115</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">2.37173104286194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4192271232605</t>
+    <t xml:space="preserve">2.41922688484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.44220900535583</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">2.42152523994446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35564398765564</t>
+    <t xml:space="preserve">2.35564374923706</t>
   </si>
   <si>
     <t xml:space="preserve">2.36177229881287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769480705261</t>
+    <t xml:space="preserve">2.41769456863403</t>
   </si>
   <si>
     <t xml:space="preserve">2.45140171051025</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">2.45906209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48970484733582</t>
+    <t xml:space="preserve">2.48970460891724</t>
   </si>
   <si>
     <t xml:space="preserve">2.51268672943115</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">2.56171488761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58086609840393</t>
+    <t xml:space="preserve">2.58086633682251</t>
   </si>
   <si>
     <t xml:space="preserve">2.53949928283691</t>
@@ -4265,25 +4265,25 @@
     <t xml:space="preserve">2.55175590515137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52187967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53796696662903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53720045089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4759156703949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45982813835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44450688362122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41386461257935</t>
+    <t xml:space="preserve">2.52187943458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53796672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5372006893158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47591543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45982837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44450712203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41386437416077</t>
   </si>
   <si>
     <t xml:space="preserve">2.40390586853027</t>
@@ -4295,22 +4295,22 @@
     <t xml:space="preserve">2.40313982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42075943946838</t>
+    <t xml:space="preserve">2.4207592010498</t>
   </si>
   <si>
     <t xml:space="preserve">2.51881527900696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50349402427673</t>
+    <t xml:space="preserve">2.50349378585815</t>
   </si>
   <si>
     <t xml:space="preserve">2.44527292251587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48817276954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4667227268219</t>
+    <t xml:space="preserve">2.48817253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46672296524048</t>
   </si>
   <si>
     <t xml:space="preserve">2.56860947608948</t>
@@ -4355,31 +4355,31 @@
     <t xml:space="preserve">2.72335386276245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74020743370056</t>
+    <t xml:space="preserve">2.74020719528198</t>
   </si>
   <si>
     <t xml:space="preserve">2.82141017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94014978408813</t>
+    <t xml:space="preserve">2.94014954566956</t>
   </si>
   <si>
     <t xml:space="preserve">2.9217643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93172311782837</t>
+    <t xml:space="preserve">2.93172287940979</t>
   </si>
   <si>
     <t xml:space="preserve">2.89725041389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9263608455658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95700311660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99453997612</t>
+    <t xml:space="preserve">2.92636060714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95700335502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99454021453857</t>
   </si>
   <si>
     <t xml:space="preserve">3.00756359100342</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">3.16154193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19831299781799</t>
+    <t xml:space="preserve">3.19831323623657</t>
   </si>
   <si>
     <t xml:space="preserve">3.14315676689148</t>
@@ -4406,10 +4406,10 @@
     <t xml:space="preserve">3.22895550727844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29024052619934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22435927391052</t>
+    <t xml:space="preserve">3.29024076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2243595123291</t>
   </si>
   <si>
     <t xml:space="preserve">3.22052884101868</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">3.18682217597961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16767072677612</t>
+    <t xml:space="preserve">3.1676709651947</t>
   </si>
   <si>
     <t xml:space="preserve">3.14085817337036</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">3.16000986099243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16077589988708</t>
+    <t xml:space="preserve">3.16077613830566</t>
   </si>
   <si>
     <t xml:space="preserve">3.11711025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15081739425659</t>
+    <t xml:space="preserve">3.15081715583801</t>
   </si>
   <si>
     <t xml:space="preserve">3.22359323501587</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">3.18912029266357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23355221748352</t>
+    <t xml:space="preserve">3.23355197906494</t>
   </si>
   <si>
     <t xml:space="preserve">3.17150068283081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07727551460266</t>
+    <t xml:space="preserve">3.07727527618408</t>
   </si>
   <si>
     <t xml:space="preserve">2.82830452919006</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">2.67585802078247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71186304092407</t>
+    <t xml:space="preserve">2.71186327934265</t>
   </si>
   <si>
     <t xml:space="preserve">2.70573472976685</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">2.80379056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71952366828918</t>
+    <t xml:space="preserve">2.71952342987061</t>
   </si>
   <si>
     <t xml:space="preserve">2.60691261291504</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">2.63372468948364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65900492668152</t>
+    <t xml:space="preserve">2.65900468826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.75782680511475</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">2.79996037483215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76165723800659</t>
+    <t xml:space="preserve">2.76165747642517</t>
   </si>
   <si>
     <t xml:space="preserve">2.7785108089447</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">2.75476264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82370853424072</t>
+    <t xml:space="preserve">2.82370829582214</t>
   </si>
   <si>
     <t xml:space="preserve">2.83979558944702</t>
@@ -71542,7 +71542,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912962963</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>5611502</v>
@@ -71563,6 +71563,32 @@
         <v>2089</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6917476852</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>4416840</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>12.460000038147</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>12.2849998474121</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>12.3549995422363</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>12.460000038147</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>2067</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">BAMI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25302267074585</t>
+    <t xml:space="preserve">6.25302362442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.98424005508423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89802646636963</t>
+    <t xml:space="preserve">5.89802551269531</t>
   </si>
   <si>
     <t xml:space="preserve">5.65459871292114</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89295434951782</t>
+    <t xml:space="preserve">5.65967082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89295387268066</t>
   </si>
   <si>
     <t xml:space="preserve">5.27424573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94206857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40450143814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85839080810547</t>
+    <t xml:space="preserve">4.94206809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40450191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85839128494263</t>
   </si>
   <si>
     <t xml:space="preserve">4.6149640083313</t>
@@ -83,61 +83,61 @@
     <t xml:space="preserve">4.28785991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55410718917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911003112793</t>
+    <t xml:space="preserve">4.55410766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911050796509</t>
   </si>
   <si>
     <t xml:space="preserve">3.95568370819092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32082414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57946491241455</t>
+    <t xml:space="preserve">4.32082366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57946443557739</t>
   </si>
   <si>
     <t xml:space="preserve">4.50339365005493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0520396232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11289644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961268424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52715110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22286772727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040070533752</t>
+    <t xml:space="preserve">4.05203914642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11289691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961220741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52715134620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22286748886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040118217468</t>
   </si>
   <si>
     <t xml:space="preserve">3.26851058006287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64379334449768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004109382629</t>
+    <t xml:space="preserve">3.6437931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004180908203</t>
   </si>
   <si>
     <t xml:space="preserve">4.04443264007568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14332485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91511225700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818512916565</t>
+    <t xml:space="preserve">4.14332580566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91511249542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818536758423</t>
   </si>
   <si>
     <t xml:space="preserve">4.08246850967407</t>
@@ -146,19 +146,19 @@
     <t xml:space="preserve">3.71986436843872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64632892608643</t>
+    <t xml:space="preserve">3.646329164505</t>
   </si>
   <si>
     <t xml:space="preserve">3.74775648117065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84157776832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92018294334412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22700262069702</t>
+    <t xml:space="preserve">3.84157705307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92018365859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22700309753418</t>
   </si>
   <si>
     <t xml:space="preserve">4.04950475692749</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">3.88468480110168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86693429946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7604353427887</t>
+    <t xml:space="preserve">3.86693453788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76043486595154</t>
   </si>
   <si>
     <t xml:space="preserve">3.69957828521729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03682613372803</t>
+    <t xml:space="preserve">4.03682565689087</t>
   </si>
   <si>
     <t xml:space="preserve">3.9480767250061</t>
@@ -185,88 +185,88 @@
     <t xml:space="preserve">3.38768792152405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47136545181274</t>
+    <t xml:space="preserve">3.4713659286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.67675733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69197082519531</t>
+    <t xml:space="preserve">3.69197130203247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51447248458862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38261675834656</t>
+    <t xml:space="preserve">3.3826162815094</t>
   </si>
   <si>
     <t xml:space="preserve">3.27611780166626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06565427780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365622520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812201499939</t>
+    <t xml:space="preserve">3.06565403938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365598678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812177658081</t>
   </si>
   <si>
     <t xml:space="preserve">2.49005174636841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40586733818054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2243115901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46672344207764</t>
+    <t xml:space="preserve">2.40586709976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22431135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46672368049622</t>
   </si>
   <si>
     <t xml:space="preserve">2.72080016136169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.700514793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91097712516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02508354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16454672813416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22690272331238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13856601715088</t>
+    <t xml:space="preserve">2.70051455497742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91097736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0250837802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16454696655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22690296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13856554031372</t>
   </si>
   <si>
     <t xml:space="preserve">3.14116311073303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20092105865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508953094482</t>
+    <t xml:space="preserve">3.20092082023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508929252625</t>
   </si>
   <si>
     <t xml:space="preserve">3.11777997016907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23469710350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19052886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32823014259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20351886749268</t>
+    <t xml:space="preserve">3.23469662666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19052863121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3282299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20351934432983</t>
   </si>
   <si>
     <t xml:space="preserve">2.96968603134155</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">2.75663733482361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86835813522339</t>
+    <t xml:space="preserve">2.86835789680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.72805738449097</t>
@@ -287,25 +287,25 @@
     <t xml:space="preserve">2.59607124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51500964164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28637218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32274627685547</t>
+    <t xml:space="preserve">2.51500940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.286372423172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378602027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32274651527405</t>
   </si>
   <si>
     <t xml:space="preserve">2.39237642288208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23544812202454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24584150314331</t>
+    <t xml:space="preserve">2.23544836044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24584102630615</t>
   </si>
   <si>
     <t xml:space="preserve">2.22089910507202</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">2.24480175971985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24999761581421</t>
+    <t xml:space="preserve">2.24999785423279</t>
   </si>
   <si>
     <t xml:space="preserve">2.2749400138855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47343921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47032117843628</t>
+    <t xml:space="preserve">2.47343897819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4703209400177</t>
   </si>
   <si>
     <t xml:space="preserve">2.48902797698975</t>
@@ -332,25 +332,25 @@
     <t xml:space="preserve">2.49422383308411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31131458282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16581773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16685724258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05461668968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15853524208069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29020428657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22156882286072</t>
+    <t xml:space="preserve">2.31131434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16581749916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16685700416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05461692810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15853548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29020476341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22156834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433287620544</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">2.0422739982605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83636581897736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71590256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83776664733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07449126243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01846170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02546501159668</t>
+    <t xml:space="preserve">1.83636593818665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7159024477005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83776676654816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07449078559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01846146583557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02546525001526</t>
   </si>
   <si>
     <t xml:space="preserve">1.993248462677</t>
@@ -383,31 +383,31 @@
     <t xml:space="preserve">2.12211608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62765598297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52680313587189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55481779575348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50439131259918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50158989429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540218830109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45676612854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40073657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31459152698517</t>
+    <t xml:space="preserve">1.62765610218048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5268030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5548175573349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50439119338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50159001350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540242671967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45676624774933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40073680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31459140777588</t>
   </si>
   <si>
     <t xml:space="preserve">1.28167414665222</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5702258348465</t>
+    <t xml:space="preserve">1.57022595405579</t>
   </si>
   <si>
     <t xml:space="preserve">1.666876912117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55621838569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64166355133057</t>
+    <t xml:space="preserve">1.55621826648712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64166367053986</t>
   </si>
   <si>
     <t xml:space="preserve">1.66267454624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6878879070282</t>
+    <t xml:space="preserve">1.68788778781891</t>
   </si>
   <si>
     <t xml:space="preserve">1.67528116703033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66407537460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72991001605988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70329582691193</t>
+    <t xml:space="preserve">1.66407525539398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72990989685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70329570770264</t>
   </si>
   <si>
     <t xml:space="preserve">1.71730327606201</t>
@@ -452,34 +452,34 @@
     <t xml:space="preserve">1.7593252658844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70749807357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76352739334106</t>
+    <t xml:space="preserve">1.70749819278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76352763175964</t>
   </si>
   <si>
     <t xml:space="preserve">1.50579214096069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49738764762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55201625823975</t>
+    <t xml:space="preserve">1.49738752841949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55201649665833</t>
   </si>
   <si>
     <t xml:space="preserve">1.63045763969421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59964120388031</t>
+    <t xml:space="preserve">1.5996413230896</t>
   </si>
   <si>
     <t xml:space="preserve">1.59263753890991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58143150806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56882524490356</t>
+    <t xml:space="preserve">1.58143162727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56882512569427</t>
   </si>
   <si>
     <t xml:space="preserve">1.53100526332855</t>
@@ -488,124 +488,124 @@
     <t xml:space="preserve">1.52820372581482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45396482944489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48758244514465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58003091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53520727157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559722423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56742441654205</t>
+    <t xml:space="preserve">1.4539647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48758256435394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58003103733063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53520750999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559710502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56742417812347</t>
   </si>
   <si>
     <t xml:space="preserve">1.56182134151459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60384356975555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6808842420578</t>
+    <t xml:space="preserve">1.60384345054626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68088412284851</t>
   </si>
   <si>
     <t xml:space="preserve">1.63886189460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65707159042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6584724187851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64306402206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59403860569</t>
+    <t xml:space="preserve">1.65707147121429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65847229957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6430641412735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59403848648071</t>
   </si>
   <si>
     <t xml:space="preserve">1.60944652557373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57582890987396</t>
+    <t xml:space="preserve">1.57582879066467</t>
   </si>
   <si>
     <t xml:space="preserve">1.50018906593323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46657133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40003621578217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45116329193115</t>
+    <t xml:space="preserve">1.46657145023346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40003633499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45116341114044</t>
   </si>
   <si>
     <t xml:space="preserve">1.47357511520386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4399573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40633964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37832510471344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3965345621109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40774047374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4679719209671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48057889938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50299060344696</t>
+    <t xml:space="preserve">1.43995749950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40633952617645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37832498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39653444290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40774035453796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46797215938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48057878017426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50299036502838</t>
   </si>
   <si>
     <t xml:space="preserve">1.55061554908752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65286922454834</t>
+    <t xml:space="preserve">1.65286934375763</t>
   </si>
   <si>
     <t xml:space="preserve">1.78593945503235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79994666576385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8461709022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317480564117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82235860824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737693309784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86297988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041003704071</t>
+    <t xml:space="preserve">1.79994642734528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84617078304291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317444801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196877479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82235825061798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86297976970673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041015625</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379596710205</t>
@@ -614,43 +614,43 @@
     <t xml:space="preserve">1.80835127830505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67107880115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61224794387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50999414920807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59543931484222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60664498806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5127956867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42735075950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35451245307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30408596992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31178987026215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32649767398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29988360404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31739294528961</t>
+    <t xml:space="preserve">1.67107892036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61224818229675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50999402999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59543919563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60664510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51279580593109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42735087871552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35451233386993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30408573150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31179010868073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32649779319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29988372325897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3173930644989</t>
   </si>
   <si>
     <t xml:space="preserve">1.2508579492569</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">1.30268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35871469974518</t>
+    <t xml:space="preserve">1.35871458053589</t>
   </si>
   <si>
     <t xml:space="preserve">1.39233231544495</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">1.28867781162262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40493905544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49458611011505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64026272296906</t>
+    <t xml:space="preserve">1.40493893623352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49458622932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64026284217834</t>
   </si>
   <si>
     <t xml:space="preserve">1.56462299823761</t>
@@ -686,64 +686,64 @@
     <t xml:space="preserve">1.67948341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69769310951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65146851539612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7229061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77893543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310102939606</t>
+    <t xml:space="preserve">1.69769287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65146863460541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72290635108948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77893579006195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310126781464</t>
   </si>
   <si>
     <t xml:space="preserve">1.60524439811707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75092089176178</t>
+    <t xml:space="preserve">1.75092101097107</t>
   </si>
   <si>
     <t xml:space="preserve">1.8769873380661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90500199794769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643947601318</t>
+    <t xml:space="preserve">1.90500223636627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643983364105</t>
   </si>
   <si>
     <t xml:space="preserve">2.03106832504272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95122647285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94982552528381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9064028263092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94702422618866</t>
+    <t xml:space="preserve">1.95122635364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9498256444931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90640246868134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94702398777008</t>
   </si>
   <si>
     <t xml:space="preserve">1.89799845218658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94142127037048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93581795692444</t>
+    <t xml:space="preserve">1.9414210319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93581819534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.01706075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97363805770874</t>
+    <t xml:space="preserve">1.97363817691803</t>
   </si>
   <si>
     <t xml:space="preserve">2.02266383171082</t>
@@ -752,40 +752,40 @@
     <t xml:space="preserve">2.08849859237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.005854845047</t>
+    <t xml:space="preserve">2.00585532188416</t>
   </si>
   <si>
     <t xml:space="preserve">2.02126288414001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86017847061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8909946680069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78033638000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67388033866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74251616001129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7383143901825</t>
+    <t xml:space="preserve">1.86017835140228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89099478721619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78033661842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67388045787811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74251639842987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73831450939178</t>
   </si>
   <si>
     <t xml:space="preserve">1.64586555957794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75512337684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84056806564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77753531932831</t>
+    <t xml:space="preserve">1.75512325763702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84056794643402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77753484249115</t>
   </si>
   <si>
     <t xml:space="preserve">1.78173696994781</t>
@@ -794,97 +794,97 @@
     <t xml:space="preserve">1.68368554115295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62205302715302</t>
+    <t xml:space="preserve">1.6220531463623</t>
   </si>
   <si>
     <t xml:space="preserve">1.51419639587402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6500678062439</t>
+    <t xml:space="preserve">1.65006768703461</t>
   </si>
   <si>
     <t xml:space="preserve">1.71870398521423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71450197696686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68228483200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69349050521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69629204273224</t>
+    <t xml:space="preserve">1.71450173854828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68228495121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69349074363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69629216194153</t>
   </si>
   <si>
     <t xml:space="preserve">1.80975198745728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81535482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80695033073425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8685827255249</t>
+    <t xml:space="preserve">1.81535494327545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072609424591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80695044994354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86858296394348</t>
   </si>
   <si>
     <t xml:space="preserve">1.85597622394562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91620790958405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90780353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91480684280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88539147377014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88819313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94562351703644</t>
+    <t xml:space="preserve">1.91620802879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90780341625214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91480731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88539171218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88819289207458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94562339782715</t>
   </si>
   <si>
     <t xml:space="preserve">1.90360105037689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89939916133881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87978887557983</t>
+    <t xml:space="preserve">1.89939892292023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87978899478912</t>
   </si>
   <si>
     <t xml:space="preserve">1.86718201637268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76212668418884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542860031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86157917976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86998355388641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00445413589478</t>
+    <t xml:space="preserve">1.76212692260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95542871952057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86157929897308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8699836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00445437431335</t>
   </si>
   <si>
     <t xml:space="preserve">2.04647636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91900956630707</t>
+    <t xml:space="preserve">1.9190092086792</t>
   </si>
   <si>
     <t xml:space="preserve">1.87838780879974</t>
@@ -893,28 +893,28 @@
     <t xml:space="preserve">1.98204243183136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9638329744339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8825900554657</t>
+    <t xml:space="preserve">1.96383285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88259017467499</t>
   </si>
   <si>
     <t xml:space="preserve">1.93021523952484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97784030437469</t>
+    <t xml:space="preserve">1.97784006595612</t>
   </si>
   <si>
     <t xml:space="preserve">2.09410166740417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17814564704895</t>
+    <t xml:space="preserve">2.17814540863037</t>
   </si>
   <si>
     <t xml:space="preserve">2.11371159553528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12491774559021</t>
+    <t xml:space="preserve">2.12491750717163</t>
   </si>
   <si>
     <t xml:space="preserve">1.99464917182922</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">1.99885141849518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95262718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95402765274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93441724777222</t>
+    <t xml:space="preserve">1.95262706279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95402753353119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9344174861908</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920424461365</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">1.95823013782501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94422280788422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99184775352478</t>
+    <t xml:space="preserve">1.94422245025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9918475151062</t>
   </si>
   <si>
     <t xml:space="preserve">2.06048369407654</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">2.14592862129211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0955023765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1697416305542</t>
+    <t xml:space="preserve">2.09550213813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16974139213562</t>
   </si>
   <si>
     <t xml:space="preserve">2.14452791213989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18795084953308</t>
+    <t xml:space="preserve">2.18795108795166</t>
   </si>
   <si>
     <t xml:space="preserve">2.20616030693054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20896172523499</t>
+    <t xml:space="preserve">2.20896196365356</t>
   </si>
   <si>
     <t xml:space="preserve">2.19915676116943</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">2.14172649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2033588886261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19215297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15573358535767</t>
+    <t xml:space="preserve">2.20335865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19215321540833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15573382377625</t>
   </si>
   <si>
     <t xml:space="preserve">2.16413807868958</t>
@@ -1016,34 +1016,34 @@
     <t xml:space="preserve">2.22997260093689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28320097923279</t>
+    <t xml:space="preserve">2.28320074081421</t>
   </si>
   <si>
     <t xml:space="preserve">2.34063100814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35884094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33082580566406</t>
+    <t xml:space="preserve">2.35884070396423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33082604408264</t>
   </si>
   <si>
     <t xml:space="preserve">2.30561280250549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26499152183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.297208070755</t>
+    <t xml:space="preserve">2.26499128341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29720830917358</t>
   </si>
   <si>
     <t xml:space="preserve">2.30981492996216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27339601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32242155075073</t>
+    <t xml:space="preserve">2.27339577674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32242131233215</t>
   </si>
   <si>
     <t xml:space="preserve">2.2271716594696</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">2.22016787528992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23277449607849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26219010353088</t>
+    <t xml:space="preserve">2.23277425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2621898651123</t>
   </si>
   <si>
     <t xml:space="preserve">2.21036243438721</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">2.15993618965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15713429450989</t>
+    <t xml:space="preserve">2.15713453292847</t>
   </si>
   <si>
     <t xml:space="preserve">2.1011049747467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13052082061768</t>
+    <t xml:space="preserve">2.1305205821991</t>
   </si>
   <si>
     <t xml:space="preserve">2.1893515586853</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">2.29300618171692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30421209335327</t>
+    <t xml:space="preserve">2.30421185493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.30141043663025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31121563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33782982826233</t>
+    <t xml:space="preserve">2.3112154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33783006668091</t>
   </si>
   <si>
     <t xml:space="preserve">2.28180003166199</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">2.33642888069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43448066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45409107208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4568920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43307971954346</t>
+    <t xml:space="preserve">2.43448042869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45409059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45689225196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43307948112488</t>
   </si>
   <si>
     <t xml:space="preserve">2.43027806282043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2411789894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17954659461975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1319215297699</t>
+    <t xml:space="preserve">2.24117875099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17954611778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13192105293274</t>
   </si>
   <si>
     <t xml:space="preserve">2.23417520523071</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">2.20475959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1907525062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15153193473816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20195841789246</t>
+    <t xml:space="preserve">2.19075226783752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.151531457901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20195817947388</t>
   </si>
   <si>
     <t xml:space="preserve">2.18374872207642</t>
@@ -1148,58 +1148,58 @@
     <t xml:space="preserve">2.21456480026245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17674493789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1683406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09690284729004</t>
+    <t xml:space="preserve">2.17674469947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16834044456482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09690260887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.1025059223175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13332200050354</t>
+    <t xml:space="preserve">2.13332223892212</t>
   </si>
   <si>
     <t xml:space="preserve">2.10810875892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09130024909973</t>
+    <t xml:space="preserve">2.09130001068115</t>
   </si>
   <si>
     <t xml:space="preserve">2.04507565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9708366394043</t>
+    <t xml:space="preserve">1.97083652019501</t>
   </si>
   <si>
     <t xml:space="preserve">1.91200566291809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92741394042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8895937204361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87558615207672</t>
+    <t xml:space="preserve">1.9274138212204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88959383964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8755863904953</t>
   </si>
   <si>
     <t xml:space="preserve">2.01566028594971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97924077510834</t>
+    <t xml:space="preserve">1.97924101352692</t>
   </si>
   <si>
     <t xml:space="preserve">1.96943593025208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92321145534515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96523368358612</t>
+    <t xml:space="preserve">1.92321169376373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96523356437683</t>
   </si>
   <si>
     <t xml:space="preserve">1.92181074619293</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">1.83496499061584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76492834091187</t>
+    <t xml:space="preserve">1.76492810249329</t>
   </si>
   <si>
     <t xml:space="preserve">1.752321600914</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">1.78313791751862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82656073570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86438059806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177409648895</t>
+    <t xml:space="preserve">1.82656097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86438047885895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177421569824</t>
   </si>
   <si>
     <t xml:space="preserve">1.81395411491394</t>
@@ -1235,22 +1235,22 @@
     <t xml:space="preserve">1.86578130722046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84897267818451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88399064540863</t>
+    <t xml:space="preserve">1.84897255897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8839910030365</t>
   </si>
   <si>
     <t xml:space="preserve">1.99745047092438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04787707328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0436749458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99604988098145</t>
+    <t xml:space="preserve">2.04787731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04367470741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99604976177216</t>
   </si>
   <si>
     <t xml:space="preserve">2.08429622650146</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">2.11931467056274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15013098716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17114233970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18725061416626</t>
+    <t xml:space="preserve">2.15013074874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17114186286926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18725037574768</t>
   </si>
   <si>
     <t xml:space="preserve">2.12701869010925</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.14557838439941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10355615615845</t>
+    <t xml:space="preserve">2.10355663299561</t>
   </si>
   <si>
     <t xml:space="preserve">2.10320639610291</t>
@@ -1283,31 +1283,31 @@
     <t xml:space="preserve">2.0282666683197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04927802085876</t>
+    <t xml:space="preserve">2.04927778244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.1536328792572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16028618812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10600781440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03772187232971</t>
+    <t xml:space="preserve">2.16028594970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10600757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03772163391113</t>
   </si>
   <si>
     <t xml:space="preserve">2.11721348762512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08009433746338</t>
+    <t xml:space="preserve">2.0800940990448</t>
   </si>
   <si>
     <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12736892700195</t>
+    <t xml:space="preserve">2.12736916542053</t>
   </si>
   <si>
     <t xml:space="preserve">2.15258240699768</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">2.14207673072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425415992737</t>
+    <t xml:space="preserve">2.19425392150879</t>
   </si>
   <si>
     <t xml:space="preserve">2.19005179405212</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">2.20300889015198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17604446411133</t>
+    <t xml:space="preserve">2.17604470252991</t>
   </si>
   <si>
     <t xml:space="preserve">2.1886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01005721092224</t>
+    <t xml:space="preserve">2.01005697250366</t>
   </si>
   <si>
     <t xml:space="preserve">2.08709788322449</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">2.0664370059967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11441254615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08394575119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822436332703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12036514282227</t>
+    <t xml:space="preserve">2.11441206932068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08394622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822460174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12036490440369</t>
   </si>
   <si>
     <t xml:space="preserve">2.12071537971497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9634827375412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98274290561676</t>
+    <t xml:space="preserve">1.96348261833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98274278640747</t>
   </si>
   <si>
     <t xml:space="preserve">1.98729515075684</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">1.96838521957397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9410707950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03422021865845</t>
+    <t xml:space="preserve">1.94107115268707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03421974182129</t>
   </si>
   <si>
     <t xml:space="preserve">2.0062050819397</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">2.10915923118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10775876045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14382743835449</t>
+    <t xml:space="preserve">2.10775852203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14382767677307</t>
   </si>
   <si>
     <t xml:space="preserve">2.12421727180481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14662933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11791372299194</t>
+    <t xml:space="preserve">2.14662909507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11791396141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.15888547897339</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.14487814903259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08289551734924</t>
+    <t xml:space="preserve">2.08289575576782</t>
   </si>
   <si>
     <t xml:space="preserve">2.14347743988037</t>
@@ -1430,25 +1430,25 @@
     <t xml:space="preserve">2.05453062057495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07028889656067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09970450401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8608785867691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87523651123047</t>
+    <t xml:space="preserve">2.07028913497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09970426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86087882518768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8752361536026</t>
   </si>
   <si>
     <t xml:space="preserve">1.84442019462585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82165813446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57687938213348</t>
+    <t xml:space="preserve">1.82165825366974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57687950134277</t>
   </si>
   <si>
     <t xml:space="preserve">1.47077345848083</t>
@@ -1460,37 +1460,37 @@
     <t xml:space="preserve">1.55446767807007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68578660488129</t>
+    <t xml:space="preserve">1.68578672409058</t>
   </si>
   <si>
     <t xml:space="preserve">1.63641059398651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59648978710175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68018364906311</t>
+    <t xml:space="preserve">1.59648954868317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68018388748169</t>
   </si>
   <si>
     <t xml:space="preserve">1.61259818077087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71170043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69874346256256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72465717792511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69138956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67808270454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81990730762482</t>
+    <t xml:space="preserve">1.71170020103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69874358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72465705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69138967990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67808246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81990718841553</t>
   </si>
   <si>
     <t xml:space="preserve">1.78804039955139</t>
@@ -1502,64 +1502,64 @@
     <t xml:space="preserve">1.78068661689758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73481249809265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70364582538605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77403330802917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80589985847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82586050033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274561405182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87243497371674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823272705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85912799835205</t>
+    <t xml:space="preserve">1.73481261730194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70364606380463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7740330696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80589962005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82586026191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173426151276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274549484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87243485450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823260784149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85912775993347</t>
   </si>
   <si>
     <t xml:space="preserve">1.8328640460968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81605505943298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85072338581085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601582050323</t>
+    <t xml:space="preserve">1.81605517864227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85072350502014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601570129395</t>
   </si>
   <si>
     <t xml:space="preserve">1.85807728767395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85387527942657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7680801153183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75337243080139</t>
+    <t xml:space="preserve">1.853875041008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76807987689972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75337219238281</t>
   </si>
   <si>
     <t xml:space="preserve">1.64901745319366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64621579647064</t>
+    <t xml:space="preserve">1.64621591567993</t>
   </si>
   <si>
     <t xml:space="preserve">1.66337490081787</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">1.65216910839081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61960184574127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5709263086319</t>
+    <t xml:space="preserve">1.61960172653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57092618942261</t>
   </si>
   <si>
     <t xml:space="preserve">1.53030490875244</t>
@@ -1580,16 +1580,16 @@
     <t xml:space="preserve">1.46972298622131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4263002872467</t>
+    <t xml:space="preserve">1.42630016803741</t>
   </si>
   <si>
     <t xml:space="preserve">1.42524969577789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4550154209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44380950927734</t>
+    <t xml:space="preserve">1.45501530170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44380962848663</t>
   </si>
   <si>
     <t xml:space="preserve">1.43190324306488</t>
@@ -1604,43 +1604,43 @@
     <t xml:space="preserve">1.40704023838043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43120276927948</t>
+    <t xml:space="preserve">1.43120288848877</t>
   </si>
   <si>
     <t xml:space="preserve">1.40178716182709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.358154296875</t>
+    <t xml:space="preserve">1.35815441608429</t>
   </si>
   <si>
     <t xml:space="preserve">1.37132120132446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50719273090363</t>
+    <t xml:space="preserve">1.50719285011292</t>
   </si>
   <si>
     <t xml:space="preserve">1.49493634700775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54326164722443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5355578660965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5502655506134</t>
+    <t xml:space="preserve">1.54326152801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53555774688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55026543140411</t>
   </si>
   <si>
     <t xml:space="preserve">1.61084723472595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61539947986603</t>
+    <t xml:space="preserve">1.61539971828461</t>
   </si>
   <si>
     <t xml:space="preserve">1.61609995365143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62625551223755</t>
+    <t xml:space="preserve">1.62625527381897</t>
   </si>
   <si>
     <t xml:space="preserve">1.62415421009064</t>
@@ -1649,34 +1649,34 @@
     <t xml:space="preserve">1.61715054512024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6444650888443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64866709709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48688185214996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40143704414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37356245517731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4028377532959</t>
+    <t xml:space="preserve">1.64446485042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64866721630096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48688197135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40143716335297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37356233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40283787250519</t>
   </si>
   <si>
     <t xml:space="preserve">1.41439390182495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38602900505066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29638171195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31108951568604</t>
+    <t xml:space="preserve">1.38602912425995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29638195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31108963489532</t>
   </si>
   <si>
     <t xml:space="preserve">1.3052065372467</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">1.30758774280548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29960358142853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22550451755524</t>
+    <t xml:space="preserve">1.29960346221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22550463676453</t>
   </si>
   <si>
     <t xml:space="preserve">1.20673477649689</t>
@@ -1706,46 +1706,46 @@
     <t xml:space="preserve">1.14692318439484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09229457378387</t>
+    <t xml:space="preserve">1.09229445457458</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134445667267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08977329730988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14440166950226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16345202922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1633118391037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19608926773071</t>
+    <t xml:space="preserve">1.0897730588913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14440190792084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16345191001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16331195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19608914852142</t>
   </si>
   <si>
     <t xml:space="preserve">1.23965191841125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21317827701569</t>
+    <t xml:space="preserve">1.21317803859711</t>
   </si>
   <si>
     <t xml:space="preserve">1.22410380840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25478005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29217982292175</t>
+    <t xml:space="preserve">1.25477993488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29217958450317</t>
   </si>
   <si>
     <t xml:space="preserve">1.28139400482178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27046811580658</t>
+    <t xml:space="preserve">1.27046835422516</t>
   </si>
   <si>
     <t xml:space="preserve">1.26640605926514</t>
@@ -1754,58 +1754,58 @@
     <t xml:space="preserve">1.23923182487488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22606492042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256302833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26262414455414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19412803649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28517603874207</t>
+    <t xml:space="preserve">1.22606480121613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256290912628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26262426376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19412815570831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28517615795135</t>
   </si>
   <si>
     <t xml:space="preserve">1.32341611385345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38770997524261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41194260120392</t>
+    <t xml:space="preserve">1.38770985603333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41194272041321</t>
   </si>
   <si>
     <t xml:space="preserve">1.47392535209656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47147393226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836175441742</t>
+    <t xml:space="preserve">1.47147405147552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836187362671</t>
   </si>
   <si>
     <t xml:space="preserve">1.53940963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54571294784546</t>
+    <t xml:space="preserve">1.54571282863617</t>
   </si>
   <si>
     <t xml:space="preserve">1.55796945095062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47917807102203</t>
+    <t xml:space="preserve">1.47917795181274</t>
   </si>
   <si>
     <t xml:space="preserve">1.46376991271973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4480117559433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48478090763092</t>
+    <t xml:space="preserve">1.44801163673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48478078842163</t>
   </si>
   <si>
     <t xml:space="preserve">1.49913859367371</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">1.47007310390472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44345939159393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40458881855011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39401316642761</t>
+    <t xml:space="preserve">1.44345915317535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4045889377594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3940132856369</t>
   </si>
   <si>
     <t xml:space="preserve">1.4315527677536</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">1.39443349838257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35605335235596</t>
+    <t xml:space="preserve">1.35605323314667</t>
   </si>
   <si>
     <t xml:space="preserve">1.32285571098328</t>
@@ -1838,55 +1838,55 @@
     <t xml:space="preserve">1.39177203178406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37118113040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43330371379852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44170844554901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41509437561035</t>
+    <t xml:space="preserve">1.37118124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4333039522171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44170820713043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41509425640106</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209804058075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42454922199249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38224697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3491895198822</t>
+    <t xml:space="preserve">1.42454934120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38224709033966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34918963909149</t>
   </si>
   <si>
     <t xml:space="preserve">1.29344022274017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33168053627014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32551717758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30058407783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29484105110168</t>
+    <t xml:space="preserve">1.33168041706085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551729679108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30058395862579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2948409318924</t>
   </si>
   <si>
     <t xml:space="preserve">1.25996267795563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26864719390869</t>
+    <t xml:space="preserve">1.26864743232727</t>
   </si>
   <si>
     <t xml:space="preserve">1.24721598625183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27845227718353</t>
+    <t xml:space="preserve">1.27845239639282</t>
   </si>
   <si>
     <t xml:space="preserve">1.26206386089325</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">1.24525511264801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18474316596985</t>
+    <t xml:space="preserve">1.18474304676056</t>
   </si>
   <si>
     <t xml:space="preserve">1.1518257856369</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">1.19342768192291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21892118453979</t>
+    <t xml:space="preserve">1.21892106533051</t>
   </si>
   <si>
     <t xml:space="preserve">1.22914636135101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20897591114044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29400050640106</t>
+    <t xml:space="preserve">1.20897579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29400062561035</t>
   </si>
   <si>
     <t xml:space="preserve">1.31851351261139</t>
@@ -1928,52 +1928,52 @@
     <t xml:space="preserve">1.2770516872406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36571848392487</t>
+    <t xml:space="preserve">1.36571836471558</t>
   </si>
   <si>
     <t xml:space="preserve">1.3850485086441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37706422805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969507694244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32775843143463</t>
+    <t xml:space="preserve">1.37706434726715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969519615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32775831222534</t>
   </si>
   <si>
     <t xml:space="preserve">1.3147314786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36011552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40879082679749</t>
+    <t xml:space="preserve">1.3601154088974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40879094600677</t>
   </si>
   <si>
     <t xml:space="preserve">1.47287464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49318528175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46412026882172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43505489826202</t>
+    <t xml:space="preserve">1.49318540096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46412014961243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43505477905273</t>
   </si>
   <si>
     <t xml:space="preserve">1.41544437408447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37566363811493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3837878704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35675346851349</t>
+    <t xml:space="preserve">1.37566351890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38378775119781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35675358772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.34372675418854</t>
@@ -1982,91 +1982,91 @@
     <t xml:space="preserve">1.4031879901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37720453739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43015229701996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39149177074432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38112652301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32103478908539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30296516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28615653514862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32019448280334</t>
+    <t xml:space="preserve">1.37720429897308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43015241622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3914920091629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3811262845993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32103490829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30296528339386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32019424438477</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937816619873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28993833065033</t>
+    <t xml:space="preserve">1.28993844985962</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824862003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3317506313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35941505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36606848239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36641871929169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36221647262573</t>
+    <t xml:space="preserve">1.33175039291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.359414935112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36606860160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3664186000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36221659183502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37587368488312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37727451324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37622392177582</t>
+    <t xml:space="preserve">1.37727439403534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37622380256653</t>
   </si>
   <si>
     <t xml:space="preserve">1.43575513362885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45956790447235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828268051147</t>
+    <t xml:space="preserve">1.45956766605377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828279972076</t>
   </si>
   <si>
     <t xml:space="preserve">1.43855655193329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4917848110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48127913475037</t>
+    <t xml:space="preserve">1.49178469181061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48127901554108</t>
   </si>
   <si>
     <t xml:space="preserve">1.44205844402313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38077628612518</t>
+    <t xml:space="preserve">1.38077640533447</t>
   </si>
   <si>
     <t xml:space="preserve">1.38532876968384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2722190618515</t>
+    <t xml:space="preserve">1.27221918106079</t>
   </si>
   <si>
     <t xml:space="preserve">1.24595546722412</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">1.19973111152649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19062614440918</t>
+    <t xml:space="preserve">1.19062626361847</t>
   </si>
   <si>
     <t xml:space="preserve">1.19798004627228</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">1.20918607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19587910175323</t>
+    <t xml:space="preserve">1.19587898254395</t>
   </si>
   <si>
     <t xml:space="preserve">1.18082106113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15525758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17171621322632</t>
+    <t xml:space="preserve">1.15525770187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17171633243561</t>
   </si>
   <si>
     <t xml:space="preserve">1.14370155334473</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">1.16261148452759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15350675582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19377791881561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16716384887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14160048961639</t>
+    <t xml:space="preserve">1.15350651741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19377779960632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16716372966766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1416003704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.18432295322418</t>
@@ -2141,25 +2141,25 @@
     <t xml:space="preserve">1.20323288440704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25365936756134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24560511112213</t>
+    <t xml:space="preserve">1.25365924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24560499191284</t>
   </si>
   <si>
     <t xml:space="preserve">1.23790109157562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23474943637848</t>
+    <t xml:space="preserve">1.23474955558777</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875676631927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451528072357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24105262756348</t>
+    <t xml:space="preserve">1.26451516151428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24105274677277</t>
   </si>
   <si>
     <t xml:space="preserve">1.23825120925903</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">1.36256659030914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36992061138153</t>
+    <t xml:space="preserve">1.36992037296295</t>
   </si>
   <si>
     <t xml:space="preserve">1.33525228500366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32264566421509</t>
+    <t xml:space="preserve">1.3226455450058</t>
   </si>
   <si>
     <t xml:space="preserve">1.33350133895874</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">1.33630287647247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34295630455017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31214022636414</t>
+    <t xml:space="preserve">1.34295642375946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31213998794556</t>
   </si>
   <si>
     <t xml:space="preserve">1.34575772285461</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">1.23159766197205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23720073699951</t>
+    <t xml:space="preserve">1.23720061779022</t>
   </si>
   <si>
     <t xml:space="preserve">1.23124754428864</t>
@@ -2216,34 +2216,34 @@
     <t xml:space="preserve">1.21163725852966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17241668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18222177028656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18817484378815</t>
+    <t xml:space="preserve">1.17241680622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18222165107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18817508220673</t>
   </si>
   <si>
     <t xml:space="preserve">1.1846729516983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1860738992691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24210321903229</t>
+    <t xml:space="preserve">1.18607378005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24210333824158</t>
   </si>
   <si>
     <t xml:space="preserve">1.26731646060944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15175592899323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13529706001282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18047106266022</t>
+    <t xml:space="preserve">1.15175580978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13529717922211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18047094345093</t>
   </si>
   <si>
     <t xml:space="preserve">1.1342465877533</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">1.18992590904236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21583938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21653985977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23404908180237</t>
+    <t xml:space="preserve">1.21583950519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21653974056244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23404896259308</t>
   </si>
   <si>
     <t xml:space="preserve">1.27467048168182</t>
@@ -2282,55 +2282,55 @@
     <t xml:space="preserve">1.28132390975952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27186906337738</t>
+    <t xml:space="preserve">1.27186894416809</t>
   </si>
   <si>
     <t xml:space="preserve">1.26906752586365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30548644065857</t>
+    <t xml:space="preserve">1.30548655986786</t>
   </si>
   <si>
     <t xml:space="preserve">1.32474672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31844341754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35171091556549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31424105167389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34050524234772</t>
+    <t xml:space="preserve">1.31844353675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35171103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31424117088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34050512313843</t>
   </si>
   <si>
     <t xml:space="preserve">1.36816966533661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35066056251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29743218421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31003904342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33980476856232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33210051059723</t>
+    <t xml:space="preserve">1.35066032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29743242263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31003892421722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33980464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33210062980652</t>
   </si>
   <si>
     <t xml:space="preserve">1.29007852077484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27081847190857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27537083625793</t>
+    <t xml:space="preserve">1.27081835269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27537071704865</t>
   </si>
   <si>
     <t xml:space="preserve">1.28762722015381</t>
@@ -2351,16 +2351,16 @@
     <t xml:space="preserve">1.42384898662567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50929379463196</t>
+    <t xml:space="preserve">1.50929367542267</t>
   </si>
   <si>
     <t xml:space="preserve">1.50859344005585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49598681926727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47707676887512</t>
+    <t xml:space="preserve">1.49598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4770770072937</t>
   </si>
   <si>
     <t xml:space="preserve">1.4686723947525</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">1.42314851284027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42665040493011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47777712345123</t>
+    <t xml:space="preserve">1.42665028572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47777724266052</t>
   </si>
   <si>
     <t xml:space="preserve">1.49528646469116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49388563632965</t>
+    <t xml:space="preserve">1.49388551712036</t>
   </si>
   <si>
     <t xml:space="preserve">1.44766128063202</t>
@@ -2387,37 +2387,37 @@
     <t xml:space="preserve">1.42104744911194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41264295578003</t>
+    <t xml:space="preserve">1.41264307498932</t>
   </si>
   <si>
     <t xml:space="preserve">1.41754555702209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41614484786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44135808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4553656578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46517074108124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43085265159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41824591159821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38813018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3741227388382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41474413871765</t>
+    <t xml:space="preserve">1.41614508628845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4413583278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536553859711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46517062187195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43085253238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4182460308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38813006877899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37412285804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41474401950836</t>
   </si>
   <si>
     <t xml:space="preserve">1.4035382270813</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">1.40984153747559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45326447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42034709453583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36851990222931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37797486782074</t>
+    <t xml:space="preserve">1.45326435565948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42034697532654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36851978302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37797474861145</t>
   </si>
   <si>
     <t xml:space="preserve">1.38637924194336</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">1.42594993114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43435454368591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4336541891098</t>
+    <t xml:space="preserve">1.43435430526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43365406990051</t>
   </si>
   <si>
     <t xml:space="preserve">1.38287734985352</t>
@@ -2459,34 +2459,34 @@
     <t xml:space="preserve">1.36887001991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39373302459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36431753635406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29568135738373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35836458206177</t>
+    <t xml:space="preserve">1.39373290538788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36431765556335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29568159580231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35836446285248</t>
   </si>
   <si>
     <t xml:space="preserve">1.37307226657867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727156639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5204998254776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54641330242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72010469436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626080989838</t>
+    <t xml:space="preserve">1.46727168560028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52049946784973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54641342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72010493278503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626069068909</t>
   </si>
   <si>
     <t xml:space="preserve">1.38848030567169</t>
@@ -2495,76 +2495,76 @@
     <t xml:space="preserve">1.30128443241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14230096340179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09397542476654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05755615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905926525592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861102879047394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926937639713287</t>
+    <t xml:space="preserve">1.1423008441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09397554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05755627155304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905926465988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861103057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926937520503998</t>
   </si>
   <si>
     <t xml:space="preserve">0.772156059741974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888417303562164</t>
+    <t xml:space="preserve">0.888417184352875</t>
   </si>
   <si>
     <t xml:space="preserve">0.818030297756195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874409973621368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874760150909424</t>
+    <t xml:space="preserve">0.874409914016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874760031700134</t>
   </si>
   <si>
     <t xml:space="preserve">0.885965943336487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877561688423157</t>
+    <t xml:space="preserve">0.877561628818512</t>
   </si>
   <si>
     <t xml:space="preserve">0.870207726955414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926587402820587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912930250167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925887048244476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8807133436203</t>
+    <t xml:space="preserve">0.926587224006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912930130958557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925887107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880713224411011</t>
   </si>
   <si>
     <t xml:space="preserve">0.84919661283493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8404421210289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633193969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846045017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830987095832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851297736167908</t>
+    <t xml:space="preserve">0.840442061424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633253574371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846044957637787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83098703622818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851297795772552</t>
   </si>
   <si>
     <t xml:space="preserve">0.829936444759369</t>
@@ -2573,28 +2573,28 @@
     <t xml:space="preserve">0.85304868221283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820131361484528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77740889787674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778459429740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778809607028961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753246128559113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751845419406891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771806001663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743791222572327</t>
+    <t xml:space="preserve">0.820131421089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77740877866745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778459489345551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778809666633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753246188163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751845479011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771805882453918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743791282176971</t>
   </si>
   <si>
     <t xml:space="preserve">0.768304109573364</t>
@@ -2603,34 +2603,34 @@
     <t xml:space="preserve">0.789665400981903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809625804424286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779860258102417</t>
+    <t xml:space="preserve">0.809625864028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779860138893127</t>
   </si>
   <si>
     <t xml:space="preserve">0.766553103923798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781611144542694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776008129119873</t>
+    <t xml:space="preserve">0.781611084938049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776008248329163</t>
   </si>
   <si>
     <t xml:space="preserve">0.765152454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803672671318054</t>
+    <t xml:space="preserve">0.803672730922699</t>
   </si>
   <si>
     <t xml:space="preserve">0.812077105045319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807874858379364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785463154315948</t>
+    <t xml:space="preserve">0.807874917984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785463094711304</t>
   </si>
   <si>
     <t xml:space="preserve">0.781260907649994</t>
@@ -2642,28 +2642,28 @@
     <t xml:space="preserve">0.759199321269989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756047606468201</t>
+    <t xml:space="preserve">0.756047666072845</t>
   </si>
   <si>
     <t xml:space="preserve">0.730484187602997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.736087143421173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743440926074982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779159843921661</t>
+    <t xml:space="preserve">0.736087083816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743440985679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779159724712372</t>
   </si>
   <si>
     <t xml:space="preserve">0.815228819847107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805773913860321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858301341533661</t>
+    <t xml:space="preserve">0.805773794651031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85830146074295</t>
   </si>
   <si>
     <t xml:space="preserve">0.872308790683746</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">0.931840121746063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994873285293579</t>
+    <t xml:space="preserve">0.994873344898224</t>
   </si>
   <si>
     <t xml:space="preserve">1.00853037834167</t>
@@ -2690,22 +2690,22 @@
     <t xml:space="preserve">0.891218721866608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895070731639862</t>
+    <t xml:space="preserve">0.895070791244507</t>
   </si>
   <si>
     <t xml:space="preserve">0.901724338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967908978462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964407205581665</t>
+    <t xml:space="preserve">0.967909097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96440714597702</t>
   </si>
   <si>
     <t xml:space="preserve">0.946897983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.936392486095428</t>
+    <t xml:space="preserve">0.936392545700073</t>
   </si>
   <si>
     <t xml:space="preserve">0.938493669033051</t>
@@ -2714,19 +2714,19 @@
     <t xml:space="preserve">0.965107619762421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913980782032013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934641480445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899623095989227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953551590442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930089235305786</t>
+    <t xml:space="preserve">0.913980722427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934641540050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899623215198517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953551650047302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930089175701141</t>
   </si>
   <si>
     <t xml:space="preserve">0.909078121185303</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">0.943746387958527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983317196369171</t>
+    <t xml:space="preserve">0.983317255973816</t>
   </si>
   <si>
     <t xml:space="preserve">0.973161816596985</t>
@@ -2750,16 +2750,16 @@
     <t xml:space="preserve">0.916432023048401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933941185474396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948298871517181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957403421401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97351211309433</t>
+    <t xml:space="preserve">0.933941245079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948298752307892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957403659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97351199388504</t>
   </si>
   <si>
     <t xml:space="preserve">0.980865895748138</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">0.960905373096466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967208623886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944096565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893670082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890168190002441</t>
+    <t xml:space="preserve">0.967208743095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944096446037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893669962882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890168309211731</t>
   </si>
   <si>
     <t xml:space="preserve">0.874059736728668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913280367851257</t>
+    <t xml:space="preserve">0.913280487060547</t>
   </si>
   <si>
     <t xml:space="preserve">0.927637815475464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.907677412033081</t>
+    <t xml:space="preserve">0.907677471637726</t>
   </si>
   <si>
     <t xml:space="preserve">0.890868484973907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915381491184235</t>
+    <t xml:space="preserve">0.91538143157959</t>
   </si>
   <si>
     <t xml:space="preserve">0.978764772415161</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">0.971060812473297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00572896003723</t>
+    <t xml:space="preserve">1.00572907924652</t>
   </si>
   <si>
     <t xml:space="preserve">0.997324585914612</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">0.981566250324249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00923085212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98681902885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987519383430481</t>
+    <t xml:space="preserve">1.00923073291779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986819088459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987519323825836</t>
   </si>
   <si>
     <t xml:space="preserve">1.00712966918945</t>
@@ -2840,94 +2840,94 @@
     <t xml:space="preserve">0.996624231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999775826931</t>
+    <t xml:space="preserve">0.999775886535645</t>
   </si>
   <si>
     <t xml:space="preserve">1.00467848777771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988920152187347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985768437385559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970360219478607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958103954792023</t>
+    <t xml:space="preserve">0.988920032978058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985768496990204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970360338687897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958104014396667</t>
   </si>
   <si>
     <t xml:space="preserve">0.994523048400879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97841465473175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986118674278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03724563121796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02148723602295</t>
+    <t xml:space="preserve">0.978414475917816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986118733882904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03724539279938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02148735523224</t>
   </si>
   <si>
     <t xml:space="preserve">1.01903605461121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01203227043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9955735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97386223077774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916782259941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922735393047333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888067185878754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939544200897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961605727672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972811758518219</t>
+    <t xml:space="preserve">1.01203238964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995573580265045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973862171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916782379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922735273838043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888067066669464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939544081687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961605846881866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972811698913574</t>
   </si>
   <si>
     <t xml:space="preserve">1.0540543794632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11113440990448</t>
+    <t xml:space="preserve">1.11113452911377</t>
   </si>
   <si>
     <t xml:space="preserve">1.09957838058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16121077537537</t>
+    <t xml:space="preserve">1.16121065616608</t>
   </si>
   <si>
     <t xml:space="preserve">1.18502330780029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16961514949799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15910971164703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12339091300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12829327583313</t>
+    <t xml:space="preserve">1.16961526870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15910959243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12339079380035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12829339504242</t>
   </si>
   <si>
     <t xml:space="preserve">1.12794327735901</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">1.13564729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17066586017609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545249938965</t>
+    <t xml:space="preserve">1.1706657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545226097107</t>
   </si>
   <si>
     <t xml:space="preserve">1.15280640125275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17591857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15560781955719</t>
+    <t xml:space="preserve">1.17591834068298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1556077003479</t>
   </si>
   <si>
     <t xml:space="preserve">1.13214552402496</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">1.15000474452972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15210604667664</t>
+    <t xml:space="preserve">1.15210592746735</t>
   </si>
   <si>
     <t xml:space="preserve">1.15490746498108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15455734729767</t>
+    <t xml:space="preserve">1.15455722808838</t>
   </si>
   <si>
     <t xml:space="preserve">1.26066303253174</t>
@@ -2990,22 +2990,22 @@
     <t xml:space="preserve">1.25611066818237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27502071857452</t>
+    <t xml:space="preserve">1.27502059936523</t>
   </si>
   <si>
     <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32684791088104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35801422595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32334589958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31879377365112</t>
+    <t xml:space="preserve">1.32684779167175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35801434516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3233460187912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31879365444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.29603159427643</t>
@@ -3014,52 +3014,52 @@
     <t xml:space="preserve">1.31389117240906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30723750591278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29498112201691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28482592105865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28027319908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26941776275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2431538105011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25435972213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27256953716278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26136338710785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26661622524261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26416480541229</t>
+    <t xml:space="preserve">1.30723762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29498100280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28482568264008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28027331829071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26941764354706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24315369129181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25435960292816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27256941795349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26136350631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2666163444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26416492462158</t>
   </si>
   <si>
     <t xml:space="preserve">1.26521551609039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26766669750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26626598834991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25856196880341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25821185112</t>
+    <t xml:space="preserve">1.26766681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26626586914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2585620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25821161270142</t>
   </si>
   <si>
     <t xml:space="preserve">1.32964932918549</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">1.36957037448883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3450573682785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34925961494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33455193042755</t>
+    <t xml:space="preserve">1.34505748748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34925973415375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33455204963684</t>
   </si>
   <si>
     <t xml:space="preserve">1.31529176235199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31809341907501</t>
+    <t xml:space="preserve">1.31809318065643</t>
   </si>
   <si>
     <t xml:space="preserve">1.31073951721191</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">1.31774306297302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28062379360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24735605716705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26696646213531</t>
+    <t xml:space="preserve">1.2806236743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24735617637634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26696634292603</t>
   </si>
   <si>
     <t xml:space="preserve">1.2501574754715</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">1.29112911224365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27432036399841</t>
+    <t xml:space="preserve">1.27432024478912</t>
   </si>
   <si>
     <t xml:space="preserve">1.29953348636627</t>
@@ -3113,52 +3113,52 @@
     <t xml:space="preserve">1.34820902347565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42174768447876</t>
+    <t xml:space="preserve">1.42174780368805</t>
   </si>
   <si>
     <t xml:space="preserve">1.52260088920593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52190065383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53240597248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4980880022049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48898303508759</t>
+    <t xml:space="preserve">1.52190053462982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53240585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49808776378632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48898315429688</t>
   </si>
   <si>
     <t xml:space="preserve">1.50088942050934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51629745960236</t>
+    <t xml:space="preserve">1.51629757881165</t>
   </si>
   <si>
     <t xml:space="preserve">1.50789332389832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51979947090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54851460456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54361200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6059445142746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62695562839508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62065231800079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59053659439087</t>
+    <t xml:space="preserve">1.5197993516922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54851448535919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54361176490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60594475269318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62695574760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62065207958221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59053647518158</t>
   </si>
   <si>
     <t xml:space="preserve">1.59193730354309</t>
@@ -3167,43 +3167,43 @@
     <t xml:space="preserve">1.69909369945526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70119488239288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7236065864563</t>
+    <t xml:space="preserve">1.70119452476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72360646724701</t>
   </si>
   <si>
     <t xml:space="preserve">1.71029949188232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70469677448273</t>
+    <t xml:space="preserve">1.70469665527344</t>
   </si>
   <si>
     <t xml:space="preserve">1.71100008487701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74881994724274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70539689064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68998908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65356981754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63536024093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64936745166779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63466000556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62835621833801</t>
+    <t xml:space="preserve">1.74881982803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70539724826813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68998897075653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65356957912445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63536012172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6493673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63465988636017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62835669517517</t>
   </si>
   <si>
     <t xml:space="preserve">1.6654759645462</t>
@@ -3212,79 +3212,79 @@
     <t xml:space="preserve">1.71505236625671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61877381801605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59937429428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6130256652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308466434479</t>
+    <t xml:space="preserve">1.61877369880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5993744134903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61302578449249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308478355408</t>
   </si>
   <si>
     <t xml:space="preserve">1.65613567829132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67337954044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71936309337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71289694309235</t>
+    <t xml:space="preserve">1.67337930202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71936333179474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71289706230164</t>
   </si>
   <si>
     <t xml:space="preserve">1.70283770561218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445165157318</t>
+    <t xml:space="preserve">1.73445177078247</t>
   </si>
   <si>
     <t xml:space="preserve">1.71145975589752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74522924423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893973350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76822113990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81707918643951</t>
+    <t xml:space="preserve">1.74522912502289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893937587738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76822090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81707882881165</t>
   </si>
   <si>
     <t xml:space="preserve">1.83504128456116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85587751865387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86449980735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126083374023</t>
+    <t xml:space="preserve">1.85587775707245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86449956893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126107215881</t>
   </si>
   <si>
     <t xml:space="preserve">1.95934128761292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97299265861511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98377025127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94066035747528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96508920192719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9974217414856</t>
+    <t xml:space="preserve">1.97299253940582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98377013206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94066059589386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650890827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99742162227631</t>
   </si>
   <si>
     <t xml:space="preserve">2.02400612831116</t>
@@ -3293,13 +3293,13 @@
     <t xml:space="preserve">2.03334641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08579683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08795237541199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10375905036926</t>
+    <t xml:space="preserve">2.08579659461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08795213699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10375881195068</t>
   </si>
   <si>
     <t xml:space="preserve">2.12531399726868</t>
@@ -3308,10 +3308,10 @@
     <t xml:space="preserve">2.13465452194214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15405416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15189814567566</t>
+    <t xml:space="preserve">2.1540539264679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15189838409424</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423104286194</t>
@@ -3320,25 +3320,25 @@
     <t xml:space="preserve">2.17201638221741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17991995811462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17560887336731</t>
+    <t xml:space="preserve">2.17991971969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17560911178589</t>
   </si>
   <si>
     <t xml:space="preserve">2.17632746696472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16052055358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12818813323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08938908576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0807671546936</t>
+    <t xml:space="preserve">2.16052031517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12818789482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08938932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076739311218</t>
   </si>
   <si>
     <t xml:space="preserve">2.05346441268921</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">2.08292269706726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04771637916565</t>
+    <t xml:space="preserve">2.04771661758423</t>
   </si>
   <si>
     <t xml:space="preserve">2.04196858406067</t>
@@ -3359,76 +3359,76 @@
     <t xml:space="preserve">2.04053139686584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98305153846741</t>
+    <t xml:space="preserve">1.98305141925812</t>
   </si>
   <si>
     <t xml:space="preserve">1.96652626991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94928228855133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9521564245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90114307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83288598060608</t>
+    <t xml:space="preserve">1.94928240776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95215654373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90114283561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83288586139679</t>
   </si>
   <si>
     <t xml:space="preserve">1.93922340869904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93634939193726</t>
+    <t xml:space="preserve">1.93634951114655</t>
   </si>
   <si>
     <t xml:space="preserve">1.91766822338104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88821005821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749158382416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84653723239899</t>
+    <t xml:space="preserve">1.88821017742157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749146461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8465371131897</t>
   </si>
   <si>
     <t xml:space="preserve">1.78762018680573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82641935348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8752772808075</t>
+    <t xml:space="preserve">1.8264194726944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87527704238892</t>
   </si>
   <si>
     <t xml:space="preserve">1.85803306102753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90258014202118</t>
+    <t xml:space="preserve">1.90258002281189</t>
   </si>
   <si>
     <t xml:space="preserve">1.87743234634399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89108383655548</t>
+    <t xml:space="preserve">1.89108407497406</t>
   </si>
   <si>
     <t xml:space="preserve">1.82067143917084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81348633766174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82857477664948</t>
+    <t xml:space="preserve">1.81348645687103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82857489585876</t>
   </si>
   <si>
     <t xml:space="preserve">1.96724474430084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97371113300323</t>
+    <t xml:space="preserve">1.97371125221252</t>
   </si>
   <si>
     <t xml:space="preserve">1.95718586444855</t>
@@ -3443,28 +3443,28 @@
     <t xml:space="preserve">2.00388813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97155570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93347549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90904629230499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9420975446701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97802233695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01107287406921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01753950119019</t>
+    <t xml:space="preserve">1.97155582904816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93347561359406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90904653072357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94209730625153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01107335090637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957728385925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01753973960876</t>
   </si>
   <si>
     <t xml:space="preserve">2.03262805938721</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">1.99167382717133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01322865486145</t>
+    <t xml:space="preserve">2.01322841644287</t>
   </si>
   <si>
     <t xml:space="preserve">1.97945928573608</t>
@@ -3485,25 +3485,25 @@
     <t xml:space="preserve">1.95000076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9377863407135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96868193149567</t>
+    <t xml:space="preserve">1.93778645992279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96868169307709</t>
   </si>
   <si>
     <t xml:space="preserve">1.92269802093506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94712698459625</t>
+    <t xml:space="preserve">1.94712686538696</t>
   </si>
   <si>
     <t xml:space="preserve">1.92916429042816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83073031902313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84078931808472</t>
+    <t xml:space="preserve">1.83073043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84078943729401</t>
   </si>
   <si>
     <t xml:space="preserve">1.92054259777069</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">1.97586667537689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92341661453247</t>
+    <t xml:space="preserve">1.92341649532318</t>
   </si>
   <si>
     <t xml:space="preserve">1.94353425502777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94425284862518</t>
+    <t xml:space="preserve">1.94425308704376</t>
   </si>
   <si>
     <t xml:space="preserve">1.91838693618774</t>
@@ -3527,148 +3527,148 @@
     <t xml:space="preserve">2.02616143226624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02831697463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0218505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047227859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994188308716</t>
+    <t xml:space="preserve">2.02831721305847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02185034751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047251701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994212150574</t>
   </si>
   <si>
     <t xml:space="preserve">2.04340553283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10016655921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12387704849243</t>
+    <t xml:space="preserve">2.10016679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12387728691101</t>
   </si>
   <si>
     <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1231586933136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13034343719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14758729934692</t>
+    <t xml:space="preserve">2.12315845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1303436756134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1475875377655</t>
   </si>
   <si>
     <t xml:space="preserve">2.10950708389282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08148598670959</t>
+    <t xml:space="preserve">2.08148574829102</t>
   </si>
   <si>
     <t xml:space="preserve">1.92988300323486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93563091754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083735466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00963592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08364129066467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03765749931335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00316977500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9859254360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95143795013428</t>
+    <t xml:space="preserve">1.93563079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97083711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00963616371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08364152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03765726089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00316953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98592555522919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143783092499</t>
   </si>
   <si>
     <t xml:space="preserve">1.90042436122894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88318049907684</t>
+    <t xml:space="preserve">1.88318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">1.85372221469879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7459477186203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540612220764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77181375026703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8084568977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83001172542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88533616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92557203769684</t>
+    <t xml:space="preserve">1.74594783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540600299835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77181363105774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80845701694489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83001184463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8853360414505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92557191848755</t>
   </si>
   <si>
     <t xml:space="preserve">1.8896472454071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88677310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8673734664917</t>
+    <t xml:space="preserve">1.88677299022675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86737358570099</t>
   </si>
   <si>
     <t xml:space="preserve">1.89395797252655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89036571979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85444056987762</t>
+    <t xml:space="preserve">1.89036560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8544408082962</t>
   </si>
   <si>
     <t xml:space="preserve">1.84797430038452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79767942428589</t>
+    <t xml:space="preserve">1.7976793050766</t>
   </si>
   <si>
     <t xml:space="preserve">1.85659635066986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85875177383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8472558259964</t>
+    <t xml:space="preserve">1.85875165462494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84725594520569</t>
   </si>
   <si>
     <t xml:space="preserve">1.85515940189362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88605463504791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683222770691</t>
+    <t xml:space="preserve">1.8860547542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683198928833</t>
   </si>
   <si>
     <t xml:space="preserve">1.97874057292938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00101399421692</t>
+    <t xml:space="preserve">2.0010142326355</t>
   </si>
   <si>
     <t xml:space="preserve">2.0254430770874</t>
@@ -3683,10 +3683,10 @@
     <t xml:space="preserve">2.06424188613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0563383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0527458190918</t>
+    <t xml:space="preserve">2.05633854866028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05274605751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.02113199234009</t>
@@ -3695,22 +3695,22 @@
     <t xml:space="preserve">2.00460648536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01251006126404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99526607990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8997061252594</t>
+    <t xml:space="preserve">2.01251029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99526596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">1.87958800792694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93131971359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221530437469</t>
+    <t xml:space="preserve">1.93131995201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221542358398</t>
   </si>
   <si>
     <t xml:space="preserve">1.91192042827606</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">2.07645630836487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09657430648804</t>
+    <t xml:space="preserve">2.09657406806946</t>
   </si>
   <si>
     <t xml:space="preserve">2.15118002891541</t>
@@ -3737,40 +3737,40 @@
     <t xml:space="preserve">2.32505631446838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32361936569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55138278007507</t>
+    <t xml:space="preserve">2.32361912727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55138301849365</t>
   </si>
   <si>
     <t xml:space="preserve">2.53485751152039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6081440448761</t>
+    <t xml:space="preserve">2.60814428329468</t>
   </si>
   <si>
     <t xml:space="preserve">2.55928635597229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.527672290802</t>
+    <t xml:space="preserve">2.52767252922058</t>
   </si>
   <si>
     <t xml:space="preserve">2.57509326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52336168289185</t>
+    <t xml:space="preserve">2.52336144447327</t>
   </si>
   <si>
     <t xml:space="preserve">2.5104284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41343140602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21584486961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26398420333862</t>
+    <t xml:space="preserve">2.41343116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21584463119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26398372650146</t>
   </si>
   <si>
     <t xml:space="preserve">2.21368932723999</t>
@@ -3782,52 +3782,52 @@
     <t xml:space="preserve">1.91120195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66475737094879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74954009056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7948055267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90186166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06783437728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96077811717987</t>
+    <t xml:space="preserve">1.66475749015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7495402097702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79480540752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575987815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90186154842377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0678346157074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077847480774</t>
   </si>
   <si>
     <t xml:space="preserve">1.95862281322479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879969120026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9557489156723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359337329865</t>
+    <t xml:space="preserve">1.9887992143631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95574867725372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359325408936</t>
   </si>
   <si>
     <t xml:space="preserve">2.06208634376526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93275666236877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99095487594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9866441488266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9478452205658</t>
+    <t xml:space="preserve">1.93275713920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99095511436462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98664426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94784533977509</t>
   </si>
   <si>
     <t xml:space="preserve">2.16626858711243</t>
@@ -3845,25 +3845,25 @@
     <t xml:space="preserve">2.23077535629272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33036375045776</t>
+    <t xml:space="preserve">2.33036351203918</t>
   </si>
   <si>
     <t xml:space="preserve">2.35257959365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35181355476379</t>
+    <t xml:space="preserve">2.35181331634521</t>
   </si>
   <si>
     <t xml:space="preserve">2.36713457107544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32193684577942</t>
+    <t xml:space="preserve">2.321937084198</t>
   </si>
   <si>
     <t xml:space="preserve">2.35104727745056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31887245178223</t>
+    <t xml:space="preserve">2.31887269020081</t>
   </si>
   <si>
     <t xml:space="preserve">2.27597308158875</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">2.13731575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15876579284668</t>
+    <t xml:space="preserve">2.1587655544281</t>
   </si>
   <si>
     <t xml:space="preserve">2.25069308280945</t>
@@ -3902,10 +3902,10 @@
     <t xml:space="preserve">2.26448249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31351017951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38092398643494</t>
+    <t xml:space="preserve">2.31351041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38092374801636</t>
   </si>
   <si>
     <t xml:space="preserve">2.40850210189819</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">2.45523166656494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47285151481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45293378829956</t>
+    <t xml:space="preserve">2.47285127639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45293354988098</t>
   </si>
   <si>
     <t xml:space="preserve">2.4820442199707</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">2.48664045333862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46365880966187</t>
+    <t xml:space="preserve">2.46365857124329</t>
   </si>
   <si>
     <t xml:space="preserve">2.47438359260559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41309881210327</t>
+    <t xml:space="preserve">2.41309857368469</t>
   </si>
   <si>
     <t xml:space="preserve">2.43071818351746</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">2.09058618545532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98793363571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0116810798645</t>
+    <t xml:space="preserve">1.98793339729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01168131828308</t>
   </si>
   <si>
     <t xml:space="preserve">2.08062720298767</t>
@@ -3956,28 +3956,28 @@
     <t xml:space="preserve">2.02623653411865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07832884788513</t>
+    <t xml:space="preserve">2.07832908630371</t>
   </si>
   <si>
     <t xml:space="preserve">2.16795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21315598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19936680793762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13501763343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20089888572693</t>
+    <t xml:space="preserve">2.21315622329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1993670463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13501739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20089912414551</t>
   </si>
   <si>
     <t xml:space="preserve">2.14267826080322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14191246032715</t>
+    <t xml:space="preserve">2.14191222190857</t>
   </si>
   <si>
     <t xml:space="preserve">2.14650845527649</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">2.0315990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99406206607819</t>
+    <t xml:space="preserve">1.99406182765961</t>
   </si>
   <si>
     <t xml:space="preserve">1.90290057659149</t>
@@ -3995,13 +3995,13 @@
     <t xml:space="preserve">1.86919391155243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98410308361053</t>
+    <t xml:space="preserve">1.98410332202911</t>
   </si>
   <si>
     <t xml:space="preserve">1.98563539981842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91592335700989</t>
+    <t xml:space="preserve">1.91592359542847</t>
   </si>
   <si>
     <t xml:space="preserve">1.8684276342392</t>
@@ -4022,13 +4022,13 @@
     <t xml:space="preserve">1.92435026168823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8791526556015</t>
+    <t xml:space="preserve">1.87915241718292</t>
   </si>
   <si>
     <t xml:space="preserve">1.80331230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79718387126923</t>
+    <t xml:space="preserve">1.79718363285065</t>
   </si>
   <si>
     <t xml:space="preserve">1.85387253761292</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">1.79641759395599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84544563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86306500434875</t>
+    <t xml:space="preserve">1.84544575214386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86306524276733</t>
   </si>
   <si>
     <t xml:space="preserve">1.92894661426544</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.98869955539703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97184598445892</t>
+    <t xml:space="preserve">1.9718462228775</t>
   </si>
   <si>
     <t xml:space="preserve">1.95652496814728</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">2.02240633964539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01397967338562</t>
+    <t xml:space="preserve">2.01397943496704</t>
   </si>
   <si>
     <t xml:space="preserve">1.94273579120636</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">1.86612951755524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89830422401428</t>
+    <t xml:space="preserve">1.8983039855957</t>
   </si>
   <si>
     <t xml:space="preserve">1.90213441848755</t>
@@ -4145,16 +4145,16 @@
     <t xml:space="preserve">2.21392202377319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15799927711487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12965536117554</t>
+    <t xml:space="preserve">2.15799951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12965512275696</t>
   </si>
   <si>
     <t xml:space="preserve">2.0928840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07143425941467</t>
+    <t xml:space="preserve">2.07143449783325</t>
   </si>
   <si>
     <t xml:space="preserve">2.02700257301331</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">2.04155778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07986092567444</t>
+    <t xml:space="preserve">2.07986116409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.05151653289795</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">2.22617888450623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21698641777039</t>
+    <t xml:space="preserve">2.21698617935181</t>
   </si>
   <si>
     <t xml:space="preserve">2.3173406124115</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">2.3441526889801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34491896629333</t>
+    <t xml:space="preserve">2.34491872787476</t>
   </si>
   <si>
     <t xml:space="preserve">2.37173104286194</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">2.41922688484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220900535583</t>
+    <t xml:space="preserve">2.44220876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.37785959243774</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">2.42152523994446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35564374923706</t>
+    <t xml:space="preserve">2.35564351081848</t>
   </si>
   <si>
     <t xml:space="preserve">2.36177229881287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769456863403</t>
+    <t xml:space="preserve">2.41769480705261</t>
   </si>
   <si>
     <t xml:space="preserve">2.45140171051025</t>
@@ -4271,10 +4271,10 @@
     <t xml:space="preserve">2.53796672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5372006893158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47591543197632</t>
+    <t xml:space="preserve">2.53720092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4759156703949</t>
   </si>
   <si>
     <t xml:space="preserve">2.45982837677002</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">2.40390586853027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41080021858215</t>
+    <t xml:space="preserve">2.41080045700073</t>
   </si>
   <si>
     <t xml:space="preserve">2.40313982963562</t>
@@ -4298,13 +4298,13 @@
     <t xml:space="preserve">2.4207592010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51881527900696</t>
+    <t xml:space="preserve">2.51881551742554</t>
   </si>
   <si>
     <t xml:space="preserve">2.50349378585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44527292251587</t>
+    <t xml:space="preserve">2.44527316093445</t>
   </si>
   <si>
     <t xml:space="preserve">2.48817253112793</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">2.46672296524048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56860947608948</t>
+    <t xml:space="preserve">2.5686092376709</t>
   </si>
   <si>
     <t xml:space="preserve">2.59465551376343</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">2.57703614234924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55405426025391</t>
+    <t xml:space="preserve">2.55405402183533</t>
   </si>
   <si>
     <t xml:space="preserve">2.62376570701599</t>
@@ -4340,37 +4340,37 @@
     <t xml:space="preserve">2.67739009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77774429321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78923559188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77468013763428</t>
+    <t xml:space="preserve">2.77774453163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78923535346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77468037605286</t>
   </si>
   <si>
     <t xml:space="preserve">2.75859308242798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72335386276245</t>
+    <t xml:space="preserve">2.72335410118103</t>
   </si>
   <si>
     <t xml:space="preserve">2.74020719528198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82141017913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94014954566956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9217643737793</t>
+    <t xml:space="preserve">2.8214099407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94014978408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92176413536072</t>
   </si>
   <si>
     <t xml:space="preserve">2.93172287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89725041389465</t>
+    <t xml:space="preserve">2.89725017547607</t>
   </si>
   <si>
     <t xml:space="preserve">2.92636060714722</t>
@@ -4379,10 +4379,10 @@
     <t xml:space="preserve">2.95700335502625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99454021453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00756359100342</t>
+    <t xml:space="preserve">2.99454045295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00756335258484</t>
   </si>
   <si>
     <t xml:space="preserve">3.07038044929504</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">3.09106421470642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07957315444946</t>
+    <t xml:space="preserve">3.07957339286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.16154193878174</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">3.22282695770264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1025550365448</t>
+    <t xml:space="preserve">3.10255527496338</t>
   </si>
   <si>
     <t xml:space="preserve">3.04280209541321</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">3.05812358856201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12860155105591</t>
+    <t xml:space="preserve">3.12860131263733</t>
   </si>
   <si>
     <t xml:space="preserve">3.16000986099243</t>
@@ -4454,19 +4454,19 @@
     <t xml:space="preserve">3.16077613830566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11711025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15081715583801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22359323501587</t>
+    <t xml:space="preserve">3.11711049079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15081691741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22359347343445</t>
   </si>
   <si>
     <t xml:space="preserve">3.18912029266357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23355197906494</t>
+    <t xml:space="preserve">3.23355174064636</t>
   </si>
   <si>
     <t xml:space="preserve">3.17150068283081</t>
@@ -4484,16 +4484,16 @@
     <t xml:space="preserve">2.67585802078247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71186327934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70573472976685</t>
+    <t xml:space="preserve">2.71186304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70573449134827</t>
   </si>
   <si>
     <t xml:space="preserve">2.80991911888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039684295654</t>
+    <t xml:space="preserve">2.88039708137512</t>
   </si>
   <si>
     <t xml:space="preserve">2.80379056930542</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">2.76165747642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7785108089447</t>
+    <t xml:space="preserve">2.77851057052612</t>
   </si>
   <si>
     <t xml:space="preserve">2.75476264953613</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">2.93019104003906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01828837394714</t>
+    <t xml:space="preserve">3.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">3.08033919334412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11098170280457</t>
+    <t xml:space="preserve">3.11098194122314</t>
   </si>
   <si>
     <t xml:space="preserve">3.24427700042725</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">3.03609204292297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11466765403748</t>
+    <t xml:space="preserve">3.11466789245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.98505854606628</t>
@@ -4595,13 +4595,13 @@
     <t xml:space="preserve">3.16003108024597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17380166053772</t>
+    <t xml:space="preserve">3.1738018989563</t>
   </si>
   <si>
     <t xml:space="preserve">3.16732168197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13572907447815</t>
+    <t xml:space="preserve">3.13572931289673</t>
   </si>
   <si>
     <t xml:space="preserve">3.17947220802307</t>
@@ -4619,25 +4619,25 @@
     <t xml:space="preserve">3.08631563186646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09684658050537</t>
+    <t xml:space="preserve">3.09684634208679</t>
   </si>
   <si>
     <t xml:space="preserve">3.09441637992859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05472350120544</t>
+    <t xml:space="preserve">3.05472373962402</t>
   </si>
   <si>
     <t xml:space="preserve">3.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631872177124</t>
+    <t xml:space="preserve">2.96318697929382</t>
   </si>
   <si>
     <t xml:space="preserve">3.03771233558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11142778396606</t>
+    <t xml:space="preserve">3.11142754554749</t>
   </si>
   <si>
     <t xml:space="preserve">3.06768441200256</t>
@@ -4664,13 +4664,13 @@
     <t xml:space="preserve">3.14626002311707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16165113449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26776814460754</t>
+    <t xml:space="preserve">3.16165137290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508690834045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26776838302612</t>
   </si>
   <si>
     <t xml:space="preserve">3.24751687049866</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">3.31556177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29612016677856</t>
+    <t xml:space="preserve">3.29612040519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.22888588905334</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">3.50673508644104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44031071662903</t>
+    <t xml:space="preserve">3.44031047821045</t>
   </si>
   <si>
     <t xml:space="preserve">3.44355058670044</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">3.34553384780884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42005920410156</t>
+    <t xml:space="preserve">3.42005896568298</t>
   </si>
   <si>
     <t xml:space="preserve">3.46947264671326</t>
@@ -4730,46 +4730,46 @@
     <t xml:space="preserve">3.54075741767883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61042213439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62500333786011</t>
+    <t xml:space="preserve">3.61042189598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62500309944153</t>
   </si>
   <si>
     <t xml:space="preserve">3.58531045913696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60475158691406</t>
+    <t xml:space="preserve">3.60475182533264</t>
   </si>
   <si>
     <t xml:space="preserve">3.5942211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59503149986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59341096878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63391399383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63634419441223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63553380966187</t>
+    <t xml:space="preserve">3.59503173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5934112071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63391423225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63634443283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63553428649902</t>
   </si>
   <si>
     <t xml:space="preserve">3.68413734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64606475830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58774089813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50511527061462</t>
+    <t xml:space="preserve">3.64606499671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58774065971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50511503219604</t>
   </si>
   <si>
     <t xml:space="preserve">3.48162317276001</t>
@@ -4781,19 +4781,19 @@
     <t xml:space="preserve">3.2410364151001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4176287651062</t>
+    <t xml:space="preserve">3.41762900352478</t>
   </si>
   <si>
     <t xml:space="preserve">3.51807570457458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50106477737427</t>
+    <t xml:space="preserve">3.50106501579285</t>
   </si>
   <si>
     <t xml:space="preserve">3.54966807365417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55209875106812</t>
+    <t xml:space="preserve">3.55209851264954</t>
   </si>
   <si>
     <t xml:space="preserve">3.54480767250061</t>
@@ -4808,10 +4808,10 @@
     <t xml:space="preserve">3.5415678024292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51564598083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56667900085449</t>
+    <t xml:space="preserve">3.51564574241638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56667923927307</t>
   </si>
   <si>
     <t xml:space="preserve">3.5764000415802</t>
@@ -4823,19 +4823,19 @@
     <t xml:space="preserve">3.57720994949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54318785667419</t>
+    <t xml:space="preserve">3.54318761825562</t>
   </si>
   <si>
     <t xml:space="preserve">3.49944496154785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46380209922791</t>
+    <t xml:space="preserve">3.46380186080933</t>
   </si>
   <si>
     <t xml:space="preserve">3.35687470436096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2888298034668</t>
+    <t xml:space="preserve">3.28883004188538</t>
   </si>
   <si>
     <t xml:space="preserve">3.32123208045959</t>
@@ -4853,10 +4853,10 @@
     <t xml:space="preserve">3.53994727134705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62743353843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70843935012817</t>
+    <t xml:space="preserve">3.62743377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70843911170959</t>
   </si>
   <si>
     <t xml:space="preserve">3.77243375778198</t>
@@ -4874,19 +4874,19 @@
     <t xml:space="preserve">3.6898078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74084138870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67360639572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68251752853394</t>
+    <t xml:space="preserve">3.74084162712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67360663414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68251729011536</t>
   </si>
   <si>
     <t xml:space="preserve">3.66712641716003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7262601852417</t>
+    <t xml:space="preserve">3.72626042366028</t>
   </si>
   <si>
     <t xml:space="preserve">3.8550591468811</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">3.84776902198792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84938859939575</t>
+    <t xml:space="preserve">3.84938907623291</t>
   </si>
   <si>
     <t xml:space="preserve">3.926344871521</t>
@@ -4916,16 +4916,16 @@
     <t xml:space="preserve">3.97089743614197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.800785779953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83966851234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76838326454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402636528015</t>
+    <t xml:space="preserve">3.80078530311584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8396680355072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76838350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402588844299</t>
   </si>
   <si>
     <t xml:space="preserve">3.80726599693298</t>
@@ -4952,19 +4952,19 @@
     <t xml:space="preserve">3.97251749038696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94011497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99114918708801</t>
+    <t xml:space="preserve">3.94011545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99114871025085</t>
   </si>
   <si>
     <t xml:space="preserve">4.10698747634888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11994791030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30950164794922</t>
+    <t xml:space="preserve">4.119948387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30950117111206</t>
   </si>
   <si>
     <t xml:space="preserve">4.28357934951782</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">4.27223873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31274175643921</t>
+    <t xml:space="preserve">4.31274127960205</t>
   </si>
   <si>
     <t xml:space="preserve">4.1393895149231</t>
@@ -4988,7 +4988,7 @@
     <t xml:space="preserve">4.11346769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13128852844238</t>
+    <t xml:space="preserve">4.13128900527954</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642860412598</t>
@@ -5006,28 +5006,28 @@
     <t xml:space="preserve">4.11022710800171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18637323379517</t>
+    <t xml:space="preserve">4.18637275695801</t>
   </si>
   <si>
     <t xml:space="preserve">4.14100980758667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15721035003662</t>
+    <t xml:space="preserve">4.15721082687378</t>
   </si>
   <si>
     <t xml:space="preserve">3.99357891082764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04137277603149</t>
+    <t xml:space="preserve">4.04137229919434</t>
   </si>
   <si>
     <t xml:space="preserve">4.07296466827393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05676364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90204238891602</t>
+    <t xml:space="preserve">4.05676317214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90204286575317</t>
   </si>
   <si>
     <t xml:space="preserve">3.83480834960938</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">3.84290862083435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81617712974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86072945594788</t>
+    <t xml:space="preserve">3.81617665290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86072969436646</t>
   </si>
   <si>
     <t xml:space="preserve">3.8826014995575</t>
@@ -5054,10 +5054,10 @@
     <t xml:space="preserve">3.87288093566895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94335556030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94416546821594</t>
+    <t xml:space="preserve">3.94335603713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9441659450531</t>
   </si>
   <si>
     <t xml:space="preserve">4.10374689102173</t>
@@ -5066,10 +5066,10 @@
     <t xml:space="preserve">4.1750316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14748954772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94578552246094</t>
+    <t xml:space="preserve">4.14749002456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9457859992981</t>
   </si>
   <si>
     <t xml:space="preserve">3.95064616203308</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">3.88665175437927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9368748664856</t>
+    <t xml:space="preserve">3.93687534332275</t>
   </si>
   <si>
     <t xml:space="preserve">3.96927738189697</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">4.0745849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06810426712036</t>
+    <t xml:space="preserve">4.0681037902832</t>
   </si>
   <si>
     <t xml:space="preserve">4.08592557907104</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">4.45531129837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47313261032104</t>
+    <t xml:space="preserve">4.47313213348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.54765796661377</t>
@@ -5198,13 +5198,13 @@
     <t xml:space="preserve">4.61570262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69994878768921</t>
+    <t xml:space="preserve">4.69994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">4.81335639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85385894775391</t>
+    <t xml:space="preserve">4.85385942459106</t>
   </si>
   <si>
     <t xml:space="preserve">4.8489990234375</t>
@@ -5213,43 +5213,43 @@
     <t xml:space="preserve">4.88302135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95916700363159</t>
+    <t xml:space="preserve">4.95916652679443</t>
   </si>
   <si>
     <t xml:space="preserve">5.01101016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96240711212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99642992019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04989337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15358018875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1292781829834</t>
+    <t xml:space="preserve">4.96240663528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99642944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04989290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15358066558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12927865982056</t>
   </si>
   <si>
     <t xml:space="preserve">5.0709547996521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10173654556274</t>
+    <t xml:space="preserve">5.1017370223999</t>
   </si>
   <si>
     <t xml:space="preserve">5.05151319503784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17140102386475</t>
+    <t xml:space="preserve">5.1714015007019</t>
   </si>
   <si>
     <t xml:space="preserve">4.98832845687866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92838478088379</t>
+    <t xml:space="preserve">4.92838430404663</t>
   </si>
   <si>
     <t xml:space="preserve">4.98670864105225</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">5.14709997177124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17626190185547</t>
+    <t xml:space="preserve">5.17626142501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130989074707</t>
@@ -71568,7 +71568,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6917476852</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>4416840</v>
@@ -71589,6 +71589,32 @@
         <v>2067</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6937847222</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>6235906</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>12.6099996566772</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>12.4250001907349</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>12.4449996948242</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>12.6099996566772</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>2063</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="2094">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2073802947998</t>
+    <t xml:space="preserve">6.20738124847412</t>
   </si>
   <si>
     <t xml:space="preserve">BAMI.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">6.25302314758301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98423957824707</t>
+    <t xml:space="preserve">5.98424005508423</t>
   </si>
   <si>
     <t xml:space="preserve">5.89802598953247</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">5.65967130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89295387268066</t>
+    <t xml:space="preserve">5.89295434951782</t>
   </si>
   <si>
     <t xml:space="preserve">5.274245262146</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">4.9420690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40450191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85839033126831</t>
+    <t xml:space="preserve">4.40450239181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85839128494263</t>
   </si>
   <si>
     <t xml:space="preserve">4.61496448516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28786039352417</t>
+    <t xml:space="preserve">4.28785991668701</t>
   </si>
   <si>
     <t xml:space="preserve">4.55410766601562</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">4.19911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95568370819092</t>
+    <t xml:space="preserve">3.9556839466095</t>
   </si>
   <si>
     <t xml:space="preserve">4.32082414627075</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">4.57946443557739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50339365005493</t>
+    <t xml:space="preserve">4.50339317321777</t>
   </si>
   <si>
     <t xml:space="preserve">4.0520396232605</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">4.11289691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87961292266846</t>
+    <t xml:space="preserve">3.87961268424988</t>
   </si>
   <si>
     <t xml:space="preserve">3.52715134620667</t>
@@ -116,43 +116,43 @@
     <t xml:space="preserve">3.22286772727966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5804009437561</t>
+    <t xml:space="preserve">3.58040070533752</t>
   </si>
   <si>
     <t xml:space="preserve">3.26851058006287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64379286766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004109382629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04443264007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14332437515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91511201858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818536758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08246803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71986389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.646329164505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74775624275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84157752990723</t>
+    <t xml:space="preserve">3.64379262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004157066345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04443311691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1433253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91511273384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08246850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7198646068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64632940292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74775671958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84157729148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.92018342018127</t>
@@ -161,46 +161,46 @@
     <t xml:space="preserve">4.22700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04950475692749</t>
+    <t xml:space="preserve">4.04950428009033</t>
   </si>
   <si>
     <t xml:space="preserve">3.88468432426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86693429946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7604353427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69957804679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03682565689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807696342468</t>
+    <t xml:space="preserve">3.86693453788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76043558120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69957852363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03682613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807720184326</t>
   </si>
   <si>
     <t xml:space="preserve">3.38768815994263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47136545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67675757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51447296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38261699676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27611780166626</t>
+    <t xml:space="preserve">3.47136616706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197106361389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51447319984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38261675834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27611756324768</t>
   </si>
   <si>
     <t xml:space="preserve">3.06565427780151</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">2.92365622520447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70812201499939</t>
+    <t xml:space="preserve">2.70812177658081</t>
   </si>
   <si>
     <t xml:space="preserve">2.49005150794983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40586686134338</t>
+    <t xml:space="preserve">2.40586733818054</t>
   </si>
   <si>
     <t xml:space="preserve">2.22431135177612</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">2.72080016136169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70051455497742</t>
+    <t xml:space="preserve">2.700514793396</t>
   </si>
   <si>
     <t xml:space="preserve">2.91097736358643</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">3.16454672813416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2269024848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13856601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14116287231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20092129707336</t>
+    <t xml:space="preserve">3.22690272331238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1385657787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14116311073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20092082023621</t>
   </si>
   <si>
     <t xml:space="preserve">3.24508953094482</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">3.11778020858765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23469710350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19052910804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32823014259338</t>
+    <t xml:space="preserve">3.23469686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19052886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32823061943054</t>
   </si>
   <si>
     <t xml:space="preserve">3.20351910591125</t>
@@ -272,55 +272,55 @@
     <t xml:space="preserve">2.96968626976013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75663733482361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86835813522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72805714607239</t>
+    <t xml:space="preserve">2.75663757324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86835789680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
     <t xml:space="preserve">2.84497475624084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59607172012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51500964164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28637194633484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32274675369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3923761844635</t>
+    <t xml:space="preserve">2.59607124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51500940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28637218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378602027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32274651527405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39237666130066</t>
   </si>
   <si>
     <t xml:space="preserve">2.23544859886169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24584102630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22089886665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24480199813843</t>
+    <t xml:space="preserve">2.24584078788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22089910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24480175971985</t>
   </si>
   <si>
     <t xml:space="preserve">2.24999785423279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27493977546692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47343897819519</t>
+    <t xml:space="preserve">2.2749400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47343921661377</t>
   </si>
   <si>
     <t xml:space="preserve">2.4703209400177</t>
@@ -329,13 +329,13 @@
     <t xml:space="preserve">2.48902797698975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49422383308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31131434440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16581749916077</t>
+    <t xml:space="preserve">2.49422407150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31131458282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16581773757935</t>
   </si>
   <si>
     <t xml:space="preserve">2.16685700416565</t>
@@ -344,34 +344,34 @@
     <t xml:space="preserve">2.05461692810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15853548049927</t>
+    <t xml:space="preserve">2.15853524208069</t>
   </si>
   <si>
     <t xml:space="preserve">2.29020476341248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22156834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433311462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0422739982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83636605739594</t>
+    <t xml:space="preserve">2.22156858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433287620544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04227423667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83636569976807</t>
   </si>
   <si>
     <t xml:space="preserve">1.7159024477005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83776664733887</t>
+    <t xml:space="preserve">1.83776652812958</t>
   </si>
   <si>
     <t xml:space="preserve">2.07449102401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01846146583557</t>
+    <t xml:space="preserve">2.01846170425415</t>
   </si>
   <si>
     <t xml:space="preserve">2.02546525001526</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">2.12211608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62765598297119</t>
+    <t xml:space="preserve">1.62765610218048</t>
   </si>
   <si>
     <t xml:space="preserve">1.52680313587189</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">1.55481779575348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439119338989</t>
+    <t xml:space="preserve">1.50439131259918</t>
   </si>
   <si>
     <t xml:space="preserve">1.50158989429474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52540230751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45676612854004</t>
+    <t xml:space="preserve">1.52540242671967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45676624774933</t>
   </si>
   <si>
     <t xml:space="preserve">1.40073668956757</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">1.57022595405579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66687679290771</t>
+    <t xml:space="preserve">1.66687667369843</t>
   </si>
   <si>
     <t xml:space="preserve">1.5562185049057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64166355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66267466545105</t>
+    <t xml:space="preserve">1.64166343212128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66267442703247</t>
   </si>
   <si>
     <t xml:space="preserve">1.68788778781891</t>
@@ -437,40 +437,40 @@
     <t xml:space="preserve">1.67528116703033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6640750169754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7299097776413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70329582691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71730303764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75932562351227</t>
+    <t xml:space="preserve">1.66407513618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72990989685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70329570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71730315685272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7593252658844</t>
   </si>
   <si>
     <t xml:space="preserve">1.70749807357788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76352751255035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5057920217514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49738752841949</t>
+    <t xml:space="preserve">1.76352727413177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50579190254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49738776683807</t>
   </si>
   <si>
     <t xml:space="preserve">1.55201637744904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63045763969421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59964120388031</t>
+    <t xml:space="preserve">1.63045752048492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5996413230896</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926376581192</t>
@@ -479,46 +479,46 @@
     <t xml:space="preserve">1.58143174648285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56882512569427</t>
+    <t xml:space="preserve">1.56882524490356</t>
   </si>
   <si>
     <t xml:space="preserve">1.53100538253784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52820384502411</t>
+    <t xml:space="preserve">1.52820372581482</t>
   </si>
   <si>
     <t xml:space="preserve">1.4539647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48758244514465</t>
+    <t xml:space="preserve">1.48758256435394</t>
   </si>
   <si>
     <t xml:space="preserve">1.58003103733063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53520750999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559722423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56742429733276</t>
+    <t xml:space="preserve">1.53520739078522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56742453575134</t>
   </si>
   <si>
     <t xml:space="preserve">1.56182157993317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60384345054626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68088388442993</t>
+    <t xml:space="preserve">1.60384333133698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68088436126709</t>
   </si>
   <si>
     <t xml:space="preserve">1.63886189460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65707159042358</t>
+    <t xml:space="preserve">1.65707147121429</t>
   </si>
   <si>
     <t xml:space="preserve">1.65847229957581</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">1.6430641412735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59403848648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60944664478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57582902908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50018906593323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46657156944275</t>
+    <t xml:space="preserve">1.59403860569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60944640636444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57582879066467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50018894672394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46657133102417</t>
   </si>
   <si>
     <t xml:space="preserve">1.40003633499146</t>
@@ -548,25 +548,25 @@
     <t xml:space="preserve">1.45116329193115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357499599457</t>
+    <t xml:space="preserve">1.47357523441315</t>
   </si>
   <si>
     <t xml:space="preserve">1.4399573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40633964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37832486629486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3965345621109</t>
+    <t xml:space="preserve">1.40633952617645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37832498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39653444290161</t>
   </si>
   <si>
     <t xml:space="preserve">1.40774047374725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46797215938568</t>
+    <t xml:space="preserve">1.46797204017639</t>
   </si>
   <si>
     <t xml:space="preserve">1.48057878017426</t>
@@ -575,49 +575,49 @@
     <t xml:space="preserve">1.50299048423767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55061542987823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65286934375763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78593921661377</t>
+    <t xml:space="preserve">1.55061554908752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65286910533905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78593933582306</t>
   </si>
   <si>
     <t xml:space="preserve">1.79994666576385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8461709022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8531745672226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196877479553</t>
+    <t xml:space="preserve">1.84617078304291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317468643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196901321411</t>
   </si>
   <si>
     <t xml:space="preserve">1.82235848903656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85737693309784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86297988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041003704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89379620552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80835139751434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67107903957367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61224818229675</t>
+    <t xml:space="preserve">1.85737705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86298012733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041027545929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89379608631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80835127830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67107892036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61224794387817</t>
   </si>
   <si>
     <t xml:space="preserve">1.50999414920807</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">1.59543919563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60664498806</t>
+    <t xml:space="preserve">1.60664486885071</t>
   </si>
   <si>
     <t xml:space="preserve">1.5127956867218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42735075950623</t>
+    <t xml:space="preserve">1.42735087871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.35451245307922</t>
@@ -641,19 +641,19 @@
     <t xml:space="preserve">1.30408585071564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31178998947144</t>
+    <t xml:space="preserve">1.31179010868073</t>
   </si>
   <si>
     <t xml:space="preserve">1.32649767398834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29988360404968</t>
+    <t xml:space="preserve">1.29988372325897</t>
   </si>
   <si>
     <t xml:space="preserve">1.31739294528961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25085783004761</t>
+    <t xml:space="preserve">1.25085806846619</t>
   </si>
   <si>
     <t xml:space="preserve">1.30268514156342</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">1.35871481895447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39233243465424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28867781162262</t>
+    <t xml:space="preserve">1.39233231544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28867793083191</t>
   </si>
   <si>
     <t xml:space="preserve">1.40493905544281</t>
@@ -674,43 +674,43 @@
     <t xml:space="preserve">1.49458622932434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64026260375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56462287902832</t>
+    <t xml:space="preserve">1.64026272296906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5646231174469</t>
   </si>
   <si>
     <t xml:space="preserve">1.53380656242371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67948353290558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69769299030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65146851539612</t>
+    <t xml:space="preserve">1.67948317527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69769322872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6514687538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.72290623188019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77893555164337</t>
+    <t xml:space="preserve">1.77893567085266</t>
   </si>
   <si>
     <t xml:space="preserve">1.71310102939606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60524439811707</t>
+    <t xml:space="preserve">1.60524451732635</t>
   </si>
   <si>
     <t xml:space="preserve">1.75092113018036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87698745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90500211715698</t>
+    <t xml:space="preserve">1.87698721885681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90500199794769</t>
   </si>
   <si>
     <t xml:space="preserve">1.97643947601318</t>
@@ -719,22 +719,22 @@
     <t xml:space="preserve">2.03106832504272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95122623443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9498256444931</t>
+    <t xml:space="preserve">1.9512265920639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94982540607452</t>
   </si>
   <si>
     <t xml:space="preserve">1.90640258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94702386856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89799833297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142091274261</t>
+    <t xml:space="preserve">1.94702410697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89799821376801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9414210319519</t>
   </si>
   <si>
     <t xml:space="preserve">1.93581795692444</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">2.01706075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97363805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02266383171082</t>
+    <t xml:space="preserve">1.97363793849945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02266359329224</t>
   </si>
   <si>
     <t xml:space="preserve">2.08849859237671</t>
@@ -755,106 +755,106 @@
     <t xml:space="preserve">2.00585508346558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02126312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86017870903015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8909946680069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78033638000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6738805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74251663684845</t>
+    <t xml:space="preserve">2.02126288414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86017835140228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89099454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78033626079559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67388033866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74251627922058</t>
   </si>
   <si>
     <t xml:space="preserve">1.73831450939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64586579799652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7551234960556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8405681848526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77753520011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78173685073853</t>
+    <t xml:space="preserve">1.64586567878723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75512313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84056806564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77753496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78173696994781</t>
   </si>
   <si>
     <t xml:space="preserve">1.68368566036224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6220531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51419639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006792545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71870410442352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71450173854828</t>
+    <t xml:space="preserve">1.62205302715302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51419651508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006756782532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71870422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71450161933899</t>
   </si>
   <si>
     <t xml:space="preserve">1.68228471279144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69349086284637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69629228115082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80975210666656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81535470485687</t>
+    <t xml:space="preserve">1.69349050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69629204273224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8097517490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81535482406616</t>
   </si>
   <si>
     <t xml:space="preserve">1.7607262134552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80695044994354</t>
+    <t xml:space="preserve">1.80695021152496</t>
   </si>
   <si>
     <t xml:space="preserve">1.86858296394348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85597634315491</t>
+    <t xml:space="preserve">1.85597622394562</t>
   </si>
   <si>
     <t xml:space="preserve">1.91620790958405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90780365467072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91480708122253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88539171218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88819301128387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94562327861786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90360128879547</t>
+    <t xml:space="preserve">1.90780353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91480720043182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88539159297943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88819336891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94562351703644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90360105037689</t>
   </si>
   <si>
     <t xml:space="preserve">1.89939892292023</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">1.87978851795197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86718201637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76212692260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542860031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86157929897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86998355388641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00445413589478</t>
+    <t xml:space="preserve">1.86718225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76212704181671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95542871952057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86157917976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8699836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00445461273193</t>
   </si>
   <si>
     <t xml:space="preserve">2.04647636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91900944709778</t>
+    <t xml:space="preserve">1.9190092086792</t>
   </si>
   <si>
     <t xml:space="preserve">1.87838804721832</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">1.98204207420349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96383273601532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88258993625641</t>
+    <t xml:space="preserve">1.96383309364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8825900554657</t>
   </si>
   <si>
     <t xml:space="preserve">1.93021512031555</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">1.97784018516541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0941014289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17814540863037</t>
+    <t xml:space="preserve">2.09410166740417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17814564704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.11371159553528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12491750717163</t>
+    <t xml:space="preserve">2.12491774559021</t>
   </si>
   <si>
     <t xml:space="preserve">1.99464917182922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00305366516113</t>
+    <t xml:space="preserve">2.00305342674255</t>
   </si>
   <si>
     <t xml:space="preserve">1.90220069885254</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">1.95262718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95402777194977</t>
+    <t xml:space="preserve">1.95402765274048</t>
   </si>
   <si>
     <t xml:space="preserve">1.9344174861908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90920448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91060495376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88679230213165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95823013782501</t>
+    <t xml:space="preserve">1.90920436382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91060507297516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88679206371307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9582302570343</t>
   </si>
   <si>
     <t xml:space="preserve">1.94422280788422</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">1.99184787273407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06048393249512</t>
+    <t xml:space="preserve">2.06048369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.05207943916321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10950970649719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14592862129211</t>
+    <t xml:space="preserve">2.10950922966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14592885971069</t>
   </si>
   <si>
     <t xml:space="preserve">2.0955023765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16974115371704</t>
+    <t xml:space="preserve">2.16974139213562</t>
   </si>
   <si>
     <t xml:space="preserve">2.14452791213989</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">2.19915676116943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19635534286499</t>
+    <t xml:space="preserve">2.19635510444641</t>
   </si>
   <si>
     <t xml:space="preserve">2.14172673225403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2033588886261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19215321540833</t>
+    <t xml:space="preserve">2.20335865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19215297698975</t>
   </si>
   <si>
     <t xml:space="preserve">2.15573382377625</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">2.16273760795593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20756101608276</t>
+    <t xml:space="preserve">2.20756077766418</t>
   </si>
   <si>
     <t xml:space="preserve">2.22997283935547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28320097923279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34063124656677</t>
+    <t xml:space="preserve">2.28320074081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34063100814819</t>
   </si>
   <si>
     <t xml:space="preserve">2.35884046554565</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">2.33082604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30561280250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26499104499817</t>
+    <t xml:space="preserve">2.30561256408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26499152183533</t>
   </si>
   <si>
     <t xml:space="preserve">2.29720830917358</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">2.32242155075073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22717118263245</t>
+    <t xml:space="preserve">2.2271716594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.2607889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22016787528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23277449607849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26218962669373</t>
+    <t xml:space="preserve">2.22016763687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23277425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26219010353088</t>
   </si>
   <si>
     <t xml:space="preserve">2.21036243438721</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">2.15993595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15713477134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1011049747467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305205821991</t>
+    <t xml:space="preserve">2.15713453292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10110521316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13052082061768</t>
   </si>
   <si>
     <t xml:space="preserve">2.18935132026672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25518655776978</t>
+    <t xml:space="preserve">2.25518608093262</t>
   </si>
   <si>
     <t xml:space="preserve">2.29300594329834</t>
@@ -1091,43 +1091,43 @@
     <t xml:space="preserve">2.30141043663025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3112154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33782982826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28180003166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33642888069153</t>
+    <t xml:space="preserve">2.31121563911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33782958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28180027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33642864227295</t>
   </si>
   <si>
     <t xml:space="preserve">2.43448066711426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45409059524536</t>
+    <t xml:space="preserve">2.45409083366394</t>
   </si>
   <si>
     <t xml:space="preserve">2.45689225196838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43307971954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43027830123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2411789894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17954635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13192105293274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23417520523071</t>
+    <t xml:space="preserve">2.43307948112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43027806282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24117875099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17954611778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13192129135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23417544364929</t>
   </si>
   <si>
     <t xml:space="preserve">2.20475959777832</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">2.151531457901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20195841789246</t>
+    <t xml:space="preserve">2.2019579410553</t>
   </si>
   <si>
     <t xml:space="preserve">2.18374872207642</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">2.21456480026245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17674469947815</t>
+    <t xml:space="preserve">2.17674493789673</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834044456482</t>
@@ -1163,88 +1163,88 @@
     <t xml:space="preserve">2.13332200050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10810899734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09130024909973</t>
+    <t xml:space="preserve">2.10810875892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09130001068115</t>
   </si>
   <si>
     <t xml:space="preserve">2.04507565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97083652019501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9120055437088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92741394042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88959407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8755863904953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566028594971</t>
+    <t xml:space="preserve">1.97083640098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91200566291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9274138212204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88959360122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87558650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566004753113</t>
   </si>
   <si>
     <t xml:space="preserve">1.97924101352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96943593025208</t>
+    <t xml:space="preserve">1.96943581104279</t>
   </si>
   <si>
     <t xml:space="preserve">1.92321157455444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96523356437683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181086540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83496475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76492810249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75232172012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77193212509155</t>
+    <t xml:space="preserve">1.96523380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181074619293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83496510982513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76492846012115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.752321600914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77193200588226</t>
   </si>
   <si>
     <t xml:space="preserve">1.78313779830933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82656073570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86438059806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177397727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395399570465</t>
+    <t xml:space="preserve">1.82656061649323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86438071727753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177385807037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395435333252</t>
   </si>
   <si>
     <t xml:space="preserve">1.86578142642975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84897267818451</t>
+    <t xml:space="preserve">1.84897255897522</t>
   </si>
   <si>
     <t xml:space="preserve">1.88399076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99745059013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04787707328796</t>
+    <t xml:space="preserve">1.99745070934296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04787731170654</t>
   </si>
   <si>
     <t xml:space="preserve">2.0436749458313</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.11931467056274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15013098716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17114186286926</t>
+    <t xml:space="preserve">2.15013074874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17114210128784</t>
   </si>
   <si>
     <t xml:space="preserve">2.18725037574768</t>
@@ -1271,28 +1271,28 @@
     <t xml:space="preserve">2.12701869010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14557862281799</t>
+    <t xml:space="preserve">2.14557838439941</t>
   </si>
   <si>
     <t xml:space="preserve">2.10355639457703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10320639610291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0282666683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04927802085876</t>
+    <t xml:space="preserve">2.10320615768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02826642990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04927778244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.1536328792572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16028594970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10600757598877</t>
+    <t xml:space="preserve">2.16028642654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10600781440735</t>
   </si>
   <si>
     <t xml:space="preserve">2.03772187232971</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12736845016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18584990501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14207696914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19425392150879</t>
+    <t xml:space="preserve">2.12736916542053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15258193016052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18584966659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14207673072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19425415992737</t>
   </si>
   <si>
     <t xml:space="preserve">2.1900520324707</t>
@@ -1328,61 +1328,61 @@
     <t xml:space="preserve">2.2030086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17604470252991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18865132331848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01005721092224</t>
+    <t xml:space="preserve">2.17604446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1886510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01005697250366</t>
   </si>
   <si>
     <t xml:space="preserve">2.08709788322449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12771892547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07624197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06643676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11441206932068</t>
+    <t xml:space="preserve">2.12771940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07624173164368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0664370059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11441230773926</t>
   </si>
   <si>
     <t xml:space="preserve">2.08394622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13822484016418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12036490440369</t>
+    <t xml:space="preserve">2.13822436332703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12036538124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.12071561813354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9634827375412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98274290561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98729526996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9683849811554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94107091426849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03421974182129</t>
+    <t xml:space="preserve">1.96348237991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98274302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9872955083847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293770313263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96838545799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94107115268707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03422021865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.00620532035828</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">2.01601052284241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03491997718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10915946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10775876045227</t>
+    <t xml:space="preserve">2.03492045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10915923118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10775852203369</t>
   </si>
   <si>
     <t xml:space="preserve">2.14382767677307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12421703338623</t>
+    <t xml:space="preserve">2.12421751022339</t>
   </si>
   <si>
     <t xml:space="preserve">2.14662909507751</t>
@@ -1412,187 +1412,187 @@
     <t xml:space="preserve">2.11791396141052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888571739197</t>
+    <t xml:space="preserve">2.15888547897339</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857483863831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14487814903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08289527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14347743988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453085899353</t>
+    <t xml:space="preserve">2.14487838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08289575576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14347720146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453062057495</t>
   </si>
   <si>
     <t xml:space="preserve">2.07028889656067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09970426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86087906360626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87523639202118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84442007541656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82165825366974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57687950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47077345848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51839852333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55446755886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578684329987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641047477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59648978710175</t>
+    <t xml:space="preserve">2.09970450401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86087870597839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87523627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84442019462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82165813446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57687926292419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47077357769012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51839876174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55446767807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6364107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59648954868317</t>
   </si>
   <si>
     <t xml:space="preserve">1.68018364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61259841918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71170020103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69874346256256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72465717792511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69138967990875</t>
+    <t xml:space="preserve">1.61259806156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71170043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69874334335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7246572971344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69138956069946</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808270454407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81990730762482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804039955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84792184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78068661689758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73481237888336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70364606380463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7740330696106</t>
+    <t xml:space="preserve">1.81990718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84792172908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068673610687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73481249809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70364582538605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77403318881989</t>
   </si>
   <si>
     <t xml:space="preserve">1.80589997768402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82586050033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173438072205</t>
+    <t xml:space="preserve">1.8258603811264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173449993134</t>
   </si>
   <si>
     <t xml:space="preserve">1.89274549484253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87243509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8682324886322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85912799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83286416530609</t>
+    <t xml:space="preserve">1.87243473529816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823236942291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85912775993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83286392688751</t>
   </si>
   <si>
     <t xml:space="preserve">1.81605517864227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85072350502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601582050323</t>
+    <t xml:space="preserve">1.85072326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601546287537</t>
   </si>
   <si>
     <t xml:space="preserve">1.85807740688324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85387527942657</t>
+    <t xml:space="preserve">1.853875041008</t>
   </si>
   <si>
     <t xml:space="preserve">1.76807987689972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7533723115921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64901733398438</t>
+    <t xml:space="preserve">1.75337219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64901745319366</t>
   </si>
   <si>
     <t xml:space="preserve">1.64621603488922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66337478160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65216886997223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61960172653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5709263086319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53030490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46972298622131</t>
+    <t xml:space="preserve">1.66337490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65216910839081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61960184574127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57092642784119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53030478954315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46972286701202</t>
   </si>
   <si>
     <t xml:space="preserve">1.42630016803741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42524969577789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45501554012299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44380939006805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43190324306488</t>
+    <t xml:space="preserve">1.42524981498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45501530170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44380950927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43190312385559</t>
   </si>
   <si>
     <t xml:space="preserve">1.44415950775146</t>
@@ -1613,34 +1613,34 @@
     <t xml:space="preserve">1.35815441608429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37132120132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50719273090363</t>
+    <t xml:space="preserve">1.37132108211517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50719261169434</t>
   </si>
   <si>
     <t xml:space="preserve">1.49493634700775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54326188564301</t>
+    <t xml:space="preserve">1.54326152801514</t>
   </si>
   <si>
     <t xml:space="preserve">1.53555774688721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55026531219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61084723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61539947986603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61609983444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62625551223755</t>
+    <t xml:space="preserve">1.55026543140411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61084735393524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61539959907532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61610007286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62625539302826</t>
   </si>
   <si>
     <t xml:space="preserve">1.62415432929993</t>
@@ -1652,43 +1652,43 @@
     <t xml:space="preserve">1.64446496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64866709709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48688209056854</t>
+    <t xml:space="preserve">1.64866721630096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48688197135925</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143704414368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37356245517731</t>
+    <t xml:space="preserve">1.37356233596802</t>
   </si>
   <si>
     <t xml:space="preserve">1.40283787250519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41439402103424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38602912425995</t>
+    <t xml:space="preserve">1.41439390182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38602888584137</t>
   </si>
   <si>
     <t xml:space="preserve">1.29638183116913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31108963489532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3052065372467</t>
+    <t xml:space="preserve">1.31108951568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30520641803741</t>
   </si>
   <si>
     <t xml:space="preserve">1.31136977672577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31669270992279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30758786201477</t>
+    <t xml:space="preserve">1.3166925907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30758762359619</t>
   </si>
   <si>
     <t xml:space="preserve">1.29960358142853</t>
@@ -1697,52 +1697,52 @@
     <t xml:space="preserve">1.22550451755524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2067346572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1690548658371</t>
+    <t xml:space="preserve">1.20673477649689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16905474662781</t>
   </si>
   <si>
     <t xml:space="preserve">1.14692330360413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09229445457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134457588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08977317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14440190792084</t>
+    <t xml:space="preserve">1.09229457378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134445667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0897730588913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14440178871155</t>
   </si>
   <si>
     <t xml:space="preserve">1.16345202922821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16331195831299</t>
+    <t xml:space="preserve">1.1633118391037</t>
   </si>
   <si>
     <t xml:space="preserve">1.19608914852142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23965203762054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2131781578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2241039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25477993488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29217970371246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28139388561249</t>
+    <t xml:space="preserve">1.23965191841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21317803859711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22410380840302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25478005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28139400482178</t>
   </si>
   <si>
     <t xml:space="preserve">1.27046823501587</t>
@@ -1751,16 +1751,16 @@
     <t xml:space="preserve">1.26640605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23923194408417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22606480121613</t>
+    <t xml:space="preserve">1.23923182487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2260650396347</t>
   </si>
   <si>
     <t xml:space="preserve">1.22256302833557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26262402534485</t>
+    <t xml:space="preserve">1.26262414455414</t>
   </si>
   <si>
     <t xml:space="preserve">1.19412815570831</t>
@@ -1769,37 +1769,37 @@
     <t xml:space="preserve">1.28517603874207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32341623306274</t>
+    <t xml:space="preserve">1.32341599464417</t>
   </si>
   <si>
     <t xml:space="preserve">1.38770985603333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41194260120392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47392511367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147393226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836175441742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53940975666046</t>
+    <t xml:space="preserve">1.41194272041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47392523288727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147405147552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.448361992836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53940963745117</t>
   </si>
   <si>
     <t xml:space="preserve">1.54571306705475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55796945095062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47917807102203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376991271973</t>
+    <t xml:space="preserve">1.55796957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47917795181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376979351044</t>
   </si>
   <si>
     <t xml:space="preserve">1.44801163673401</t>
@@ -1808,37 +1808,37 @@
     <t xml:space="preserve">1.48478090763092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.499138712883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4700733423233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44345939159393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4045889377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39401304721832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43155288696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39443349838257</t>
+    <t xml:space="preserve">1.49913847446442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47007322311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44345927238464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40458869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39401316642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43155300617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39443325996399</t>
   </si>
   <si>
     <t xml:space="preserve">1.35605323314667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32285583019257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39177203178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37118124961853</t>
+    <t xml:space="preserve">1.32285571098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39177191257477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37118113040924</t>
   </si>
   <si>
     <t xml:space="preserve">1.43330383300781</t>
@@ -1853,10 +1853,10 @@
     <t xml:space="preserve">1.42209792137146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4245491027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38224709033966</t>
+    <t xml:space="preserve">1.42454922199249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38224697113037</t>
   </si>
   <si>
     <t xml:space="preserve">1.34918963909149</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">1.29344034194946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33168029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32551717758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30058395862579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2948409318924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25996279716492</t>
+    <t xml:space="preserve">1.33168041706085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3255170583725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30058419704437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29484105110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25996267795563</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864731311798</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">1.24721598625183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27845239639282</t>
+    <t xml:space="preserve">1.27845251560211</t>
   </si>
   <si>
     <t xml:space="preserve">1.26206386089325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24917697906494</t>
+    <t xml:space="preserve">1.24917709827423</t>
   </si>
   <si>
     <t xml:space="preserve">1.24525511264801</t>
@@ -1901,25 +1901,25 @@
     <t xml:space="preserve">1.18474316596985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1518257856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19342768192291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21892118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22914636135101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20897579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3185133934021</t>
+    <t xml:space="preserve">1.15182590484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19342756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21892106533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2291464805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20897603034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29400050640106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31851351261139</t>
   </si>
   <si>
     <t xml:space="preserve">1.31417119503021</t>
@@ -1931,37 +1931,37 @@
     <t xml:space="preserve">1.36571836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38504862785339</t>
+    <t xml:space="preserve">1.3850485086441</t>
   </si>
   <si>
     <t xml:space="preserve">1.37706422805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969519615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32775831222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31473135948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3601154088974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40879094600677</t>
+    <t xml:space="preserve">1.35969531536102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32775819301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3147314786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36011552810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40879082679749</t>
   </si>
   <si>
     <t xml:space="preserve">1.47287452220917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49318540096283</t>
+    <t xml:space="preserve">1.49318516254425</t>
   </si>
   <si>
     <t xml:space="preserve">1.46412014961243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43505489826202</t>
+    <t xml:space="preserve">1.43505477905273</t>
   </si>
   <si>
     <t xml:space="preserve">1.41544437408447</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35675358772278</t>
+    <t xml:space="preserve">1.35675346851349</t>
   </si>
   <si>
     <t xml:space="preserve">1.34372675418854</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">1.4031879901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37720453739166</t>
+    <t xml:space="preserve">1.37720429897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
@@ -1997,28 +1997,28 @@
     <t xml:space="preserve">1.32103478908539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30296540260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28615665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32019424438477</t>
+    <t xml:space="preserve">1.30296516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28615653514862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32019448280334</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937816619873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28993833065033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824862003326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33175039291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35941505432129</t>
+    <t xml:space="preserve">1.28993844985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824850082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33175051212311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.359414935112</t>
   </si>
   <si>
     <t xml:space="preserve">1.36606848239899</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">1.36641871929169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37587356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37727439403534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37622380256653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43575513362885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45956778526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828279972076</t>
+    <t xml:space="preserve">1.36221659183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37587368488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37727451324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37622392177582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43575525283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45956766605377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828268051147</t>
   </si>
   <si>
     <t xml:space="preserve">1.43855655193329</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">1.48127913475037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44205856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38077616691589</t>
+    <t xml:space="preserve">1.44205844402313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38077628612518</t>
   </si>
   <si>
     <t xml:space="preserve">1.38532876968384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27221918106079</t>
+    <t xml:space="preserve">1.2722190618515</t>
   </si>
   <si>
     <t xml:space="preserve">1.24595534801483</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">1.1997309923172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19062638282776</t>
+    <t xml:space="preserve">1.19062626361847</t>
   </si>
   <si>
     <t xml:space="preserve">1.19798004627228</t>
@@ -2084,16 +2084,16 @@
     <t xml:space="preserve">1.24945724010468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20918595790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19587898254395</t>
+    <t xml:space="preserve">1.20918607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19587910175323</t>
   </si>
   <si>
     <t xml:space="preserve">1.18082106113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15525758266449</t>
+    <t xml:space="preserve">1.15525770187378</t>
   </si>
   <si>
     <t xml:space="preserve">1.17171633243561</t>
@@ -2105,31 +2105,31 @@
     <t xml:space="preserve">1.13914918899536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14930438995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1626113653183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15350663661957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19377779960632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16716384887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14160048961639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18432295322418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19482851028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16821444034576</t>
+    <t xml:space="preserve">1.1493045091629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16261160373688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15350675582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19377791881561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16716396808624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1416003704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18432307243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19482827186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16821432113647</t>
   </si>
   <si>
     <t xml:space="preserve">1.17101585865021</t>
@@ -2141,19 +2141,19 @@
     <t xml:space="preserve">1.20323300361633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25365924835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24560523033142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23790109157562</t>
+    <t xml:space="preserve">1.25365948677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24560511112213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23790121078491</t>
   </si>
   <si>
     <t xml:space="preserve">1.23474943637848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24875676631927</t>
+    <t xml:space="preserve">1.24875688552856</t>
   </si>
   <si>
     <t xml:space="preserve">1.26451516151428</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">1.36992049217224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33525240421295</t>
+    <t xml:space="preserve">1.33525228500366</t>
   </si>
   <si>
     <t xml:space="preserve">1.32264566421509</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">1.33350145816803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33630287647247</t>
+    <t xml:space="preserve">1.33630275726318</t>
   </si>
   <si>
     <t xml:space="preserve">1.34295642375946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31214010715485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3457578420639</t>
+    <t xml:space="preserve">1.31214022636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34575772285461</t>
   </si>
   <si>
     <t xml:space="preserve">1.32439649105072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914389133453</t>
+    <t xml:space="preserve">1.31914377212524</t>
   </si>
   <si>
     <t xml:space="preserve">1.22634506225586</t>
@@ -2228,52 +2228,52 @@
     <t xml:space="preserve">1.18467307090759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18607378005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24210321903229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26731657981873</t>
+    <t xml:space="preserve">1.1860738992691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24210333824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26731646060944</t>
   </si>
   <si>
     <t xml:space="preserve">1.15175592899323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13529706001282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18047094345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13424670696259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18012046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2060341835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17521810531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18992590904236</t>
+    <t xml:space="preserve">1.13529717922211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18047082424164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1342465877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18012082576752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20603430271149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17521822452545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18992578983307</t>
   </si>
   <si>
     <t xml:space="preserve">1.21583950519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21653985977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23404908180237</t>
+    <t xml:space="preserve">1.21653974056244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23404896259308</t>
   </si>
   <si>
     <t xml:space="preserve">1.27467048168182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28657674789429</t>
+    <t xml:space="preserve">1.286576628685</t>
   </si>
   <si>
     <t xml:space="preserve">1.32579731941223</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">1.28132390975952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27186906337738</t>
+    <t xml:space="preserve">1.27186894416809</t>
   </si>
   <si>
     <t xml:space="preserve">1.26906752586365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30548655986786</t>
+    <t xml:space="preserve">1.30548667907715</t>
   </si>
   <si>
     <t xml:space="preserve">1.32474672794342</t>
@@ -2300,37 +2300,37 @@
     <t xml:space="preserve">1.35171091556549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31424129009247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34050500392914</t>
+    <t xml:space="preserve">1.31424117088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34050524234772</t>
   </si>
   <si>
     <t xml:space="preserve">1.36816966533661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35066032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29743230342865</t>
+    <t xml:space="preserve">1.35066056251526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29743254184723</t>
   </si>
   <si>
     <t xml:space="preserve">1.3100391626358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33980476856232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33210062980652</t>
+    <t xml:space="preserve">1.33980464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33210074901581</t>
   </si>
   <si>
     <t xml:space="preserve">1.29007863998413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27081835269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27537071704865</t>
+    <t xml:space="preserve">1.27081847190857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27537095546722</t>
   </si>
   <si>
     <t xml:space="preserve">1.28762722015381</t>
@@ -2339,13 +2339,13 @@
     <t xml:space="preserve">1.31249034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32789850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28307497501373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3096889257431</t>
+    <t xml:space="preserve">1.32789826393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28307485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30968880653381</t>
   </si>
   <si>
     <t xml:space="preserve">1.42384886741638</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">1.50929379463196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50859355926514</t>
+    <t xml:space="preserve">1.50859344005585</t>
   </si>
   <si>
     <t xml:space="preserve">1.49598670005798</t>
@@ -2363,34 +2363,34 @@
     <t xml:space="preserve">1.47707688808441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46867227554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42314863204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42665028572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47777712345123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49528646469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49388551712036</t>
+    <t xml:space="preserve">1.4686723947525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42314851284027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42665040493011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47777736186981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49528658390045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49388563632965</t>
   </si>
   <si>
     <t xml:space="preserve">1.44766128063202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42104744911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264295578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41754555702209</t>
+    <t xml:space="preserve">1.42104732990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264307498932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41754531860352</t>
   </si>
   <si>
     <t xml:space="preserve">1.41614484786987</t>
@@ -2402,22 +2402,22 @@
     <t xml:space="preserve">1.45536553859711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46517050266266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43085253238678</t>
+    <t xml:space="preserve">1.46517062187195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43085265159607</t>
   </si>
   <si>
     <t xml:space="preserve">1.4182460308075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38813018798828</t>
+    <t xml:space="preserve">1.38813006877899</t>
   </si>
   <si>
     <t xml:space="preserve">1.3741227388382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41474413871765</t>
+    <t xml:space="preserve">1.41474401950836</t>
   </si>
   <si>
     <t xml:space="preserve">1.40353810787201</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">1.40984153747559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45326435565948</t>
+    <t xml:space="preserve">1.45326459407806</t>
   </si>
   <si>
     <t xml:space="preserve">1.42034709453583</t>
@@ -2450,10 +2450,10 @@
     <t xml:space="preserve">1.43435454368591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43365395069122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287723064423</t>
+    <t xml:space="preserve">1.43365406990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287711143494</t>
   </si>
   <si>
     <t xml:space="preserve">1.36886990070343</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">1.36431753635406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29568147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35836446285248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37307214736938</t>
+    <t xml:space="preserve">1.29568159580231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35836434364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37307226657867</t>
   </si>
   <si>
     <t xml:space="preserve">1.46727180480957</t>
@@ -2483,19 +2483,19 @@
     <t xml:space="preserve">1.54641330242157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72010481357574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626080989838</t>
+    <t xml:space="preserve">1.72010469436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626069068909</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884801864624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30128443241119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14230096340179</t>
+    <t xml:space="preserve">1.3012843132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1423008441925</t>
   </si>
   <si>
     <t xml:space="preserve">1.09397554397583</t>
@@ -2504,64 +2504,64 @@
     <t xml:space="preserve">1.05755615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905926525592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861102998256683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926937639713287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772156119346619</t>
+    <t xml:space="preserve">0.905926465988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861102938652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926937520503998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772156178951263</t>
   </si>
   <si>
     <t xml:space="preserve">0.88841724395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81803023815155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874409854412079</t>
+    <t xml:space="preserve">0.818030178546906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874409914016724</t>
   </si>
   <si>
     <t xml:space="preserve">0.874760031700134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.885966062545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877561748027802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870207607746124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926587283611298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912930250167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925886988639832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8807133436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84919661283493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840441942214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633074760437</t>
+    <t xml:space="preserve">0.885966002941132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877561569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870207548141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926587343215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912930190563202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925886929035187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880713284015656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849196672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840442180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633253574371</t>
   </si>
   <si>
     <t xml:space="preserve">0.846044957637787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830987095832825</t>
+    <t xml:space="preserve">0.83098703622818</t>
   </si>
   <si>
     <t xml:space="preserve">0.851297795772552</t>
@@ -2573,31 +2573,31 @@
     <t xml:space="preserve">0.853048741817474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820131301879883</t>
+    <t xml:space="preserve">0.820131361484528</t>
   </si>
   <si>
     <t xml:space="preserve">0.77740889787674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778459489345551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778809666633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753246247768402</t>
+    <t xml:space="preserve">0.778459370136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778809607028961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753246188163757</t>
   </si>
   <si>
     <t xml:space="preserve">0.751845479011536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771806001663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743791222572327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768304109573364</t>
+    <t xml:space="preserve">0.771805942058563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743791282176971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768304049968719</t>
   </si>
   <si>
     <t xml:space="preserve">0.789665400981903</t>
@@ -2606,31 +2606,31 @@
     <t xml:space="preserve">0.809625864028931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779860258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766553103923798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611084938049</t>
+    <t xml:space="preserve">0.779860138893127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766553163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611144542694</t>
   </si>
   <si>
     <t xml:space="preserve">0.776008188724518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765152454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803672671318054</t>
+    <t xml:space="preserve">0.765152394771576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803672790527344</t>
   </si>
   <si>
     <t xml:space="preserve">0.812077164649963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807874798774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785463154315948</t>
+    <t xml:space="preserve">0.807874858379364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785463213920593</t>
   </si>
   <si>
     <t xml:space="preserve">0.781260907649994</t>
@@ -2639,40 +2639,40 @@
     <t xml:space="preserve">0.819080829620361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759199261665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756047666072845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730484187602997</t>
+    <t xml:space="preserve">0.759199380874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756047606468201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730484127998352</t>
   </si>
   <si>
     <t xml:space="preserve">0.736087203025818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743441045284271</t>
+    <t xml:space="preserve">0.743440985679626</t>
   </si>
   <si>
     <t xml:space="preserve">0.779159784317017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815228819847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805773854255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858301341533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872308790683746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892969608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931840062141418</t>
+    <t xml:space="preserve">0.815228760242462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805773913860321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858301401138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872308850288391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89296966791153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931839942932129</t>
   </si>
   <si>
     <t xml:space="preserve">0.994873285293579</t>
@@ -2681,34 +2681,34 @@
     <t xml:space="preserve">1.00853037834167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979115068912506</t>
+    <t xml:space="preserve">0.979115128517151</t>
   </si>
   <si>
     <t xml:space="preserve">0.966858565807343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891218662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895070731639862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901724398136139</t>
+    <t xml:space="preserve">0.891218721866608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895070791244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901724219322205</t>
   </si>
   <si>
     <t xml:space="preserve">0.967908978462219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964407026767731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946898102760315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936392664909363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938493728637695</t>
+    <t xml:space="preserve">0.96440714597702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94689804315567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936392486095428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938493609428406</t>
   </si>
   <si>
     <t xml:space="preserve">0.965107560157776</t>
@@ -2717,55 +2717,55 @@
     <t xml:space="preserve">0.913980782032013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934641540050507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899623215198517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953551590442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930089354515076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909078061580658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954602241516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943746268749237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983317315578461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97316187620163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951450526714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916432082653046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933941245079041</t>
+    <t xml:space="preserve">0.934641480445862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899623155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953551530838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930089175701141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909078180789948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954602181911469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943746387958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983317196369171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973161816596985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951450288295746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916431963443756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933941185474396</t>
   </si>
   <si>
     <t xml:space="preserve">0.948298692703247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957403540611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973511934280396</t>
+    <t xml:space="preserve">0.957403600215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973512053489685</t>
   </si>
   <si>
     <t xml:space="preserve">0.980865895748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.033043384552</t>
+    <t xml:space="preserve">1.03304326534271</t>
   </si>
   <si>
     <t xml:space="preserve">1.03759574890137</t>
@@ -2774,73 +2774,73 @@
     <t xml:space="preserve">1.00012600421906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998725295066833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960905432701111</t>
+    <t xml:space="preserve">0.998725354671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960905373096466</t>
   </si>
   <si>
     <t xml:space="preserve">0.967208743095398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944096505641937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89367002248764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890168190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874059736728668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913280367851257</t>
+    <t xml:space="preserve">0.944096684455872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89367014169693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890168130397797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874059796333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913280308246613</t>
   </si>
   <si>
     <t xml:space="preserve">0.927637934684753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.907677352428436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890868425369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91538143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978764832019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971060693264008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00572896003723</t>
+    <t xml:space="preserve">0.907677412033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890868484973907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915381491184235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978764891624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971060872077942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00572907924652</t>
   </si>
   <si>
     <t xml:space="preserve">0.997324585914612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981566250324249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00923073291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98681902885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987519443035126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00712966918945</t>
+    <t xml:space="preserve">0.98156613111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00923085212708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986818969249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987519323825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00712978839874</t>
   </si>
   <si>
     <t xml:space="preserve">0.996624231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999775826931</t>
+    <t xml:space="preserve">0.999775767326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.00467836856842</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">0.988920092582703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985768496990204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970360338687897</t>
+    <t xml:space="preserve">0.985768556594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970360398292542</t>
   </si>
   <si>
     <t xml:space="preserve">0.958103954792023</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">0.994523048400879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97841465473175</t>
+    <t xml:space="preserve">0.978414475917816</t>
   </si>
   <si>
     <t xml:space="preserve">0.986118674278259</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">1.03724551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02148735523224</t>
+    <t xml:space="preserve">1.02148723602295</t>
   </si>
   <si>
     <t xml:space="preserve">1.01903593540192</t>
@@ -2894,19 +2894,19 @@
     <t xml:space="preserve">0.888067126274109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939544141292572</t>
+    <t xml:space="preserve">0.939544260501862</t>
   </si>
   <si>
     <t xml:space="preserve">0.961605787277222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972811639308929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05405449867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11113452911377</t>
+    <t xml:space="preserve">0.972811758518219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0540543794632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11113440990448</t>
   </si>
   <si>
     <t xml:space="preserve">1.09957838058472</t>
@@ -2915,16 +2915,16 @@
     <t xml:space="preserve">1.16121077537537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18502330780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16961526870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15910959243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12339091300964</t>
+    <t xml:space="preserve">1.185023188591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16961514949799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15910971164703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12339079380035</t>
   </si>
   <si>
     <t xml:space="preserve">1.12829339504242</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">1.14545249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15280640125275</t>
+    <t xml:space="preserve">1.15280628204346</t>
   </si>
   <si>
     <t xml:space="preserve">1.17591845989227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1556077003479</t>
+    <t xml:space="preserve">1.15560781955719</t>
   </si>
   <si>
     <t xml:space="preserve">1.13214552402496</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">1.08627128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12899374961853</t>
+    <t xml:space="preserve">1.12899386882782</t>
   </si>
   <si>
     <t xml:space="preserve">1.15000486373901</t>
@@ -2981,19 +2981,19 @@
     <t xml:space="preserve">1.15455722808838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066303253174</t>
+    <t xml:space="preserve">1.26066291332245</t>
   </si>
   <si>
     <t xml:space="preserve">1.25120806694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25611066818237</t>
+    <t xml:space="preserve">1.25611054897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30793797969818</t>
+    <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
     <t xml:space="preserve">1.32684791088104</t>
@@ -3002,10 +3002,10 @@
     <t xml:space="preserve">1.35801434516907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3233460187912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31879377365112</t>
+    <t xml:space="preserve">1.32334613800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31879365444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.29603159427643</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">1.31389105319977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30723750591278</t>
+    <t xml:space="preserve">1.30723762512207</t>
   </si>
   <si>
     <t xml:space="preserve">1.29498112201691</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">1.28482580184937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28027319908142</t>
+    <t xml:space="preserve">1.28027331829071</t>
   </si>
   <si>
     <t xml:space="preserve">1.26941764354706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24315392971039</t>
+    <t xml:space="preserve">1.24315369129181</t>
   </si>
   <si>
     <t xml:space="preserve">1.25435972213745</t>
@@ -3038,22 +3038,22 @@
     <t xml:space="preserve">1.27256941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26136350631714</t>
+    <t xml:space="preserve">1.26136338710785</t>
   </si>
   <si>
     <t xml:space="preserve">1.26661622524261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26416492462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2652153968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26766681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2662661075592</t>
+    <t xml:space="preserve">1.26416480541229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26521551609039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26766669750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26626598834991</t>
   </si>
   <si>
     <t xml:space="preserve">1.25856196880341</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">1.32964932918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36957025527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3450573682785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34925961494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33455204963684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31529176235199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31809318065643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31073951721191</t>
+    <t xml:space="preserve">1.36957049369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34505748748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34925973415375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33455193042755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31529188156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31809329986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31073939800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.31774306297302</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">1.24735617637634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26696634292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2501574754715</t>
+    <t xml:space="preserve">1.26696646213531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25015759468079</t>
   </si>
   <si>
     <t xml:space="preserve">1.29112911224365</t>
@@ -3113,112 +3113,112 @@
     <t xml:space="preserve">1.34820902347565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42174768447876</t>
+    <t xml:space="preserve">1.42174780368805</t>
   </si>
   <si>
     <t xml:space="preserve">1.52260088920593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52190041542053</t>
+    <t xml:space="preserve">1.52190053462982</t>
   </si>
   <si>
     <t xml:space="preserve">1.53240597248077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49808776378632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48898303508759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50088942050934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51629745960236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50789332389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51979947090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5485143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54361200332642</t>
+    <t xml:space="preserve">1.4980880022049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48898315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50088953971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51629734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50789320468903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5197993516922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54851448535919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54361188411713</t>
   </si>
   <si>
     <t xml:space="preserve">1.60594475269318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62695574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62065243721008</t>
+    <t xml:space="preserve">1.62695550918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62065231800079</t>
   </si>
   <si>
     <t xml:space="preserve">1.59053647518158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59193730354309</t>
+    <t xml:space="preserve">1.5919371843338</t>
   </si>
   <si>
     <t xml:space="preserve">1.69909369945526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70119476318359</t>
+    <t xml:space="preserve">1.70119488239288</t>
   </si>
   <si>
     <t xml:space="preserve">1.7236065864563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71029961109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70469653606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71100008487701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881970882416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70539677143097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68998908996582</t>
+    <t xml:space="preserve">1.71029937267303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70469677448273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71099996566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881982803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70539689064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68998885154724</t>
   </si>
   <si>
     <t xml:space="preserve">1.65356969833374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6353600025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64936757087708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63465976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62835645675659</t>
+    <t xml:space="preserve">1.63536012172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64936769008636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63466000556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62835657596588</t>
   </si>
   <si>
     <t xml:space="preserve">1.6654759645462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71505236625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61877381801605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5993744134903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61302554607391</t>
+    <t xml:space="preserve">1.715052485466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61877369880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59937429428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6130256652832</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308478355408</t>
@@ -3227,31 +3227,31 @@
     <t xml:space="preserve">1.65613567829132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67337942123413</t>
+    <t xml:space="preserve">1.67337954044342</t>
   </si>
   <si>
     <t xml:space="preserve">1.71936309337616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71289682388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70283770561218</t>
+    <t xml:space="preserve">1.71289670467377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70283782482147</t>
   </si>
   <si>
     <t xml:space="preserve">1.73445188999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71145975589752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74522912502289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76822090148926</t>
+    <t xml:space="preserve">1.71145987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74522924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893961429596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76822113990784</t>
   </si>
   <si>
     <t xml:space="preserve">1.81707894802094</t>
@@ -3260,19 +3260,19 @@
     <t xml:space="preserve">1.83504128456116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85587751865387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86449980735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126095294952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95934104919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97299265861511</t>
+    <t xml:space="preserve">1.85587763786316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8644996881485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95934092998505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9729927778244</t>
   </si>
   <si>
     <t xml:space="preserve">1.98377025127411</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">1.94066047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96508932113647</t>
+    <t xml:space="preserve">1.9650890827179</t>
   </si>
   <si>
     <t xml:space="preserve">1.9974217414856</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">2.02400588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03334641456604</t>
+    <t xml:space="preserve">2.03334617614746</t>
   </si>
   <si>
     <t xml:space="preserve">2.08579683303833</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">2.08795213699341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10375928878784</t>
+    <t xml:space="preserve">2.10375952720642</t>
   </si>
   <si>
     <t xml:space="preserve">2.12531399726868</t>
@@ -3308,25 +3308,25 @@
     <t xml:space="preserve">2.13465476036072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15405368804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15189862251282</t>
+    <t xml:space="preserve">2.1540539264679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15189838409424</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17201638221741</t>
+    <t xml:space="preserve">2.17201662063599</t>
   </si>
   <si>
     <t xml:space="preserve">2.17991971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17560887336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1763277053833</t>
+    <t xml:space="preserve">2.17560911178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17632746696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.16052055358887</t>
@@ -3338,82 +3338,82 @@
     <t xml:space="preserve">2.08938932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0807671546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05346441268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08292293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04196858406067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01897668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04053139686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9830516576767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96652626991272</t>
+    <t xml:space="preserve">2.08076691627502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05346465110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08292317390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771637916565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04196882247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01897644996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04053115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98305141925812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96652603149414</t>
   </si>
   <si>
     <t xml:space="preserve">1.94928228855133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9521564245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90114283561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83288586139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93922328948975</t>
+    <t xml:space="preserve">1.95215618610382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90114295482635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8328857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93922317028046</t>
   </si>
   <si>
     <t xml:space="preserve">1.93634939193726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91766834259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88821029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749170303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84653699398041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7876204252243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8264194726944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87527704238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85803318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90258002281189</t>
+    <t xml:space="preserve">1.91766822338104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88821005821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749158382416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8465371131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78762030601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82641923427582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8752772808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8580334186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90258014202118</t>
   </si>
   <si>
     <t xml:space="preserve">1.87743246555328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89108407497406</t>
+    <t xml:space="preserve">1.89108383655548</t>
   </si>
   <si>
     <t xml:space="preserve">1.82067131996155</t>
@@ -3422,10 +3422,10 @@
     <t xml:space="preserve">1.81348645687103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82857477664948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96724474430084</t>
+    <t xml:space="preserve">1.82857465744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96724486351013</t>
   </si>
   <si>
     <t xml:space="preserve">1.97371137142181</t>
@@ -3434,67 +3434,67 @@
     <t xml:space="preserve">1.95718574523926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03190946578979</t>
+    <t xml:space="preserve">2.03190970420837</t>
   </si>
   <si>
     <t xml:space="preserve">2.00676202774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00388813018799</t>
+    <t xml:space="preserve">2.00388789176941</t>
   </si>
   <si>
     <t xml:space="preserve">1.97155570983887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93347525596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90904676914215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94209718704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97802221775055</t>
+    <t xml:space="preserve">1.93347537517548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90904641151428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94209742546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97802233695984</t>
   </si>
   <si>
     <t xml:space="preserve">2.01107311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99957716464996</t>
+    <t xml:space="preserve">1.99957692623138</t>
   </si>
   <si>
     <t xml:space="preserve">2.01753973960876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03262805938721</t>
+    <t xml:space="preserve">2.03262829780579</t>
   </si>
   <si>
     <t xml:space="preserve">2.03119087219238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99167382717133</t>
+    <t xml:space="preserve">1.99167370796204</t>
   </si>
   <si>
     <t xml:space="preserve">2.01322865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945916652679</t>
+    <t xml:space="preserve">1.97945940494537</t>
   </si>
   <si>
     <t xml:space="preserve">1.95000100135803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9377863407135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96868145465851</t>
+    <t xml:space="preserve">1.93778645992279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96868169307709</t>
   </si>
   <si>
     <t xml:space="preserve">1.92269814014435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94712686538696</t>
+    <t xml:space="preserve">1.94712674617767</t>
   </si>
   <si>
     <t xml:space="preserve">1.92916452884674</t>
@@ -3503,43 +3503,43 @@
     <t xml:space="preserve">1.83073043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84078943729401</t>
+    <t xml:space="preserve">1.84078931808472</t>
   </si>
   <si>
     <t xml:space="preserve">1.9205424785614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97586679458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92341649532318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94353437423706</t>
+    <t xml:space="preserve">1.9758665561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9234162569046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94353449344635</t>
   </si>
   <si>
     <t xml:space="preserve">1.94425284862518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91838681697845</t>
+    <t xml:space="preserve">1.91838705539703</t>
   </si>
   <si>
     <t xml:space="preserve">2.02616143226624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02831721305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02185082435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047251701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994224071503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04340577125549</t>
+    <t xml:space="preserve">2.02831697463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02185034751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994188308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04340553283691</t>
   </si>
   <si>
     <t xml:space="preserve">2.10016679763794</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">2.1303436756134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1475875377655</t>
+    <t xml:space="preserve">2.14758729934692</t>
   </si>
   <si>
     <t xml:space="preserve">2.1095073223114</t>
@@ -3569,34 +3569,34 @@
     <t xml:space="preserve">1.92988300323486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93563091754913</t>
+    <t xml:space="preserve">1.93563055992126</t>
   </si>
   <si>
     <t xml:space="preserve">1.97083735466003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00963592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08364152908325</t>
+    <t xml:space="preserve">2.00963568687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08364129066467</t>
   </si>
   <si>
     <t xml:space="preserve">2.03765749931335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00316953659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98592555522919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9514377117157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042459964752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88318073749542</t>
+    <t xml:space="preserve">2.00316977500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9859254360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042448043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">1.8537220954895</t>
@@ -3608,31 +3608,31 @@
     <t xml:space="preserve">1.77540600299835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77181351184845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80845701694489</t>
+    <t xml:space="preserve">1.77181363105774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8084568977356</t>
   </si>
   <si>
     <t xml:space="preserve">1.8300119638443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88533616065979</t>
+    <t xml:space="preserve">1.8853360414505</t>
   </si>
   <si>
     <t xml:space="preserve">1.92557191848755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88964712619781</t>
+    <t xml:space="preserve">1.8896472454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.88677299022675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86737370491028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395797252655</t>
+    <t xml:space="preserve">1.86737358570099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395785331726</t>
   </si>
   <si>
     <t xml:space="preserve">1.89036560058594</t>
@@ -3641,40 +3641,40 @@
     <t xml:space="preserve">1.8544408082962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84797441959381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79767954349518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85659623146057</t>
+    <t xml:space="preserve">1.84797430038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79767942428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85659611225128</t>
   </si>
   <si>
     <t xml:space="preserve">1.85875165462494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84725594520569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85515928268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88605451583862</t>
+    <t xml:space="preserve">1.8472558259964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85515940189362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88605463504791</t>
   </si>
   <si>
     <t xml:space="preserve">1.89683210849762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97874069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00101399421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02544283866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06280517578125</t>
+    <t xml:space="preserve">1.97874057292938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0010142326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0254430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06280493736267</t>
   </si>
   <si>
     <t xml:space="preserve">2.05849385261536</t>
@@ -3683,16 +3683,16 @@
     <t xml:space="preserve">2.06424164772034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0563383102417</t>
+    <t xml:space="preserve">2.05633854866028</t>
   </si>
   <si>
     <t xml:space="preserve">2.05274605751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02113175392151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0046067237854</t>
+    <t xml:space="preserve">2.02113199234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00460648536682</t>
   </si>
   <si>
     <t xml:space="preserve">2.01251006126404</t>
@@ -3701,28 +3701,28 @@
     <t xml:space="preserve">1.99526607990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89970624446869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87958812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93131995201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221518516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91192030906677</t>
+    <t xml:space="preserve">1.89970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87958800792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93131971359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221494674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91192018985748</t>
   </si>
   <si>
     <t xml:space="preserve">2.02041339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06855273246765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10447788238525</t>
+    <t xml:space="preserve">2.06855297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10447764396667</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645630836487</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">2.09657430648804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15117979049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3250560760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32361912727356</t>
+    <t xml:space="preserve">2.15118002891541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32505631446838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32361936569214</t>
   </si>
   <si>
     <t xml:space="preserve">2.55138301849365</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">2.53485727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6081440448761</t>
+    <t xml:space="preserve">2.60814428329468</t>
   </si>
   <si>
     <t xml:space="preserve">2.55928635597229</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">2.57509326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52336120605469</t>
+    <t xml:space="preserve">2.52336144447327</t>
   </si>
   <si>
     <t xml:space="preserve">2.51042866706848</t>
@@ -3770,22 +3770,22 @@
     <t xml:space="preserve">2.21584463119507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26398396492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21368932723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496047973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120207309723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66475737094879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74953997135162</t>
+    <t xml:space="preserve">2.26398420333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21368956565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496024131775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120219230652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66475749015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74954009056091</t>
   </si>
   <si>
     <t xml:space="preserve">1.79480528831482</t>
@@ -3800,28 +3800,28 @@
     <t xml:space="preserve">2.06783437728882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96077859401703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95862281322479</t>
+    <t xml:space="preserve">1.96077847480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95862305164337</t>
   </si>
   <si>
     <t xml:space="preserve">1.98879945278168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95574855804443</t>
+    <t xml:space="preserve">1.95574879646301</t>
   </si>
   <si>
     <t xml:space="preserve">1.95359337329865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06208610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93275690078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9909553527832</t>
+    <t xml:space="preserve">2.06208634376526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93275678157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99095523357391</t>
   </si>
   <si>
     <t xml:space="preserve">1.98664426803589</t>
@@ -3830,58 +3830,58 @@
     <t xml:space="preserve">1.94784533977509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16626858711243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12459564208984</t>
+    <t xml:space="preserve">2.16626882553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12459588050842</t>
   </si>
   <si>
     <t xml:space="preserve">2.19572687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19860053062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23077535629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33036398887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35257983207703</t>
+    <t xml:space="preserve">2.19860076904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2307755947113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33036375045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35257959365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.35181331634521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36713480949402</t>
+    <t xml:space="preserve">2.36713457107544</t>
   </si>
   <si>
     <t xml:space="preserve">2.32193684577942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35104727745056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31887269020081</t>
+    <t xml:space="preserve">2.35104751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31887245178223</t>
   </si>
   <si>
     <t xml:space="preserve">2.27597308158875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33572626113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24839472770691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23383975028992</t>
+    <t xml:space="preserve">2.33572602272034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24839496612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23383951187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.21085786819458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13731598854065</t>
+    <t xml:space="preserve">2.13731575012207</t>
   </si>
   <si>
     <t xml:space="preserve">2.1587655544281</t>
@@ -3911,22 +3911,22 @@
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4552321434021</t>
+    <t xml:space="preserve">2.45523190498352</t>
   </si>
   <si>
     <t xml:space="preserve">2.47285151481628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45293378829956</t>
+    <t xml:space="preserve">2.45293354988098</t>
   </si>
   <si>
     <t xml:space="preserve">2.48204398155212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4866406917572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46365880966187</t>
+    <t xml:space="preserve">2.48664045333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46365857124329</t>
   </si>
   <si>
     <t xml:space="preserve">2.47438359260559</t>
@@ -3941,19 +3941,19 @@
     <t xml:space="preserve">2.37709331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09058594703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98793375492096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01168131828308</t>
+    <t xml:space="preserve">2.09058618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98793363571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01168155670166</t>
   </si>
   <si>
     <t xml:space="preserve">2.08062720298767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02623677253723</t>
+    <t xml:space="preserve">2.02623653411865</t>
   </si>
   <si>
     <t xml:space="preserve">2.07832908630371</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">2.16795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21315598487854</t>
+    <t xml:space="preserve">2.21315574645996</t>
   </si>
   <si>
     <t xml:space="preserve">2.1993670463562</t>
@@ -3980,76 +3980,76 @@
     <t xml:space="preserve">2.14191222190857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14650869369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0315990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99406206607819</t>
+    <t xml:space="preserve">2.14650845527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03159928321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99406182765961</t>
   </si>
   <si>
     <t xml:space="preserve">1.9029004573822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86919391155243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98410308361053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98563539981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91592359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8684276342392</t>
+    <t xml:space="preserve">1.86919379234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98410332202911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98563516139984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91592347621918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86842751502991</t>
   </si>
   <si>
     <t xml:space="preserve">1.83472096920013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73743081092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77420198917389</t>
+    <t xml:space="preserve">1.73743093013763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7742018699646</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012437820435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92435026168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8791526556015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79718363285065</t>
+    <t xml:space="preserve">1.92435014247894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87915277481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80331254005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79718387126923</t>
   </si>
   <si>
     <t xml:space="preserve">1.8538726568222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79641771316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84544599056244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86306524276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92894661426544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92051994800568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96954810619354</t>
+    <t xml:space="preserve">1.79641783237457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84544575214386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86306512355804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92894637584686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92052006721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96954822540283</t>
   </si>
   <si>
     <t xml:space="preserve">2.06837034225464</t>
@@ -4058,97 +4058,97 @@
     <t xml:space="preserve">2.00095653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03466320037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98869967460632</t>
+    <t xml:space="preserve">2.034663438797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98869955539703</t>
   </si>
   <si>
     <t xml:space="preserve">1.97184610366821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95652496814728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99176383018494</t>
+    <t xml:space="preserve">1.95652484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99176394939423</t>
   </si>
   <si>
     <t xml:space="preserve">2.07220053672791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06530594825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02240657806396</t>
+    <t xml:space="preserve">2.06530618667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02240633964539</t>
   </si>
   <si>
     <t xml:space="preserve">2.01397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94273567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87762045860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90826284885406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86076700687408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80944073200226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86612963676453</t>
+    <t xml:space="preserve">1.94273579120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87762022018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90826308727264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86076712608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80944097042084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86612951755524</t>
   </si>
   <si>
     <t xml:space="preserve">1.89830410480499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90213453769684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87149214744568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96878206729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90060245990753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90673100948334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89907026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99712646007538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06070947647095</t>
+    <t xml:space="preserve">1.90213441848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87149202823639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96878182888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90060222148895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90673077106476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89907014369965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9971262216568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06070971488953</t>
   </si>
   <si>
     <t xml:space="preserve">2.12199449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08445763587952</t>
+    <t xml:space="preserve">2.08445739746094</t>
   </si>
   <si>
     <t xml:space="preserve">2.15033888816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1901741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21392202377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15799927711487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12965512275696</t>
+    <t xml:space="preserve">2.19017386436462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21392226219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15799951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12965536117554</t>
   </si>
   <si>
     <t xml:space="preserve">2.0928840637207</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">2.02700257301331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06377363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13195323944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17791724205017</t>
+    <t xml:space="preserve">2.06377339363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1319534778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17791700363159</t>
   </si>
   <si>
     <t xml:space="preserve">2.10820555686951</t>
@@ -4181,19 +4181,19 @@
     <t xml:space="preserve">2.07986092567444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05151677131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05304884910583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11893057823181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17485308647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17255473136902</t>
+    <t xml:space="preserve">2.05151653289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05304908752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11893033981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17485284805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17255449295044</t>
   </si>
   <si>
     <t xml:space="preserve">2.17332077026367</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">2.22617888450623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21698617935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31734085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3441526889801</t>
+    <t xml:space="preserve">2.21698641777039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3173406124115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34415292739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.34491896629333</t>
@@ -4223,40 +4223,40 @@
     <t xml:space="preserve">2.41922688484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37785983085632</t>
+    <t xml:space="preserve">2.44220900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37785959243774</t>
   </si>
   <si>
     <t xml:space="preserve">2.42152523994446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35564398765564</t>
+    <t xml:space="preserve">2.35564374923706</t>
   </si>
   <si>
     <t xml:space="preserve">2.36177229881287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769504547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45140194892883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45906209945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970460891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51268672943115</t>
+    <t xml:space="preserve">2.41769480705261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45140171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45906233787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970484733582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51268649101257</t>
   </si>
   <si>
     <t xml:space="preserve">2.56171464920044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58086609840393</t>
+    <t xml:space="preserve">2.58086633682251</t>
   </si>
   <si>
     <t xml:space="preserve">2.53949904441833</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">2.55175590515137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52187919616699</t>
+    <t xml:space="preserve">2.52187967300415</t>
   </si>
   <si>
     <t xml:space="preserve">2.53796672821045</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">2.4759156703949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45982813835144</t>
+    <t xml:space="preserve">2.45982837677002</t>
   </si>
   <si>
     <t xml:space="preserve">2.44450712203979</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">2.40390563011169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41080045700073</t>
+    <t xml:space="preserve">2.41080069541931</t>
   </si>
   <si>
     <t xml:space="preserve">2.40313982963562</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">2.50349378585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44527316093445</t>
+    <t xml:space="preserve">2.44527292251587</t>
   </si>
   <si>
     <t xml:space="preserve">2.48817253112793</t>
@@ -4319,19 +4319,19 @@
     <t xml:space="preserve">2.59465551376343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5793342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58393025398254</t>
+    <t xml:space="preserve">2.57933402061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58393049240112</t>
   </si>
   <si>
     <t xml:space="preserve">2.56477904319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57703614234924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55405426025391</t>
+    <t xml:space="preserve">2.57703590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55405402183533</t>
   </si>
   <si>
     <t xml:space="preserve">2.62376570701599</t>
@@ -4340,55 +4340,55 @@
     <t xml:space="preserve">2.67739009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77774453163147</t>
+    <t xml:space="preserve">2.77774429321289</t>
   </si>
   <si>
     <t xml:space="preserve">2.78923559188843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77468013763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7585928440094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72335410118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74020719528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82141017913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94015002250671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92176413536072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93172311782837</t>
+    <t xml:space="preserve">2.77468061447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75859308242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72335386276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74020743370056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8214099407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94014978408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9217643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93172335624695</t>
   </si>
   <si>
     <t xml:space="preserve">2.89725041389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92636060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95700311660767</t>
+    <t xml:space="preserve">2.9263608455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95700335502625</t>
   </si>
   <si>
     <t xml:space="preserve">2.99454021453857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00756311416626</t>
+    <t xml:space="preserve">3.00756335258484</t>
   </si>
   <si>
     <t xml:space="preserve">3.07038044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09106397628784</t>
+    <t xml:space="preserve">3.09106421470642</t>
   </si>
   <si>
     <t xml:space="preserve">3.07957315444946</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">3.22895550727844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29024076461792</t>
+    <t xml:space="preserve">3.2902410030365</t>
   </si>
   <si>
     <t xml:space="preserve">3.22435927391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22052884101868</t>
+    <t xml:space="preserve">3.22052907943726</t>
   </si>
   <si>
     <t xml:space="preserve">3.18145966529846</t>
@@ -4421,49 +4421,49 @@
     <t xml:space="preserve">3.18682217597961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16767072677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14085817337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19448280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22282695770264</t>
+    <t xml:space="preserve">3.16767048835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14085841178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19448304176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22282719612122</t>
   </si>
   <si>
     <t xml:space="preserve">3.10255527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04280209541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11634397506714</t>
+    <t xml:space="preserve">3.04280233383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11634421348572</t>
   </si>
   <si>
     <t xml:space="preserve">3.05812358856201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12860131263733</t>
+    <t xml:space="preserve">3.12860155105591</t>
   </si>
   <si>
     <t xml:space="preserve">3.16000986099243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16077613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11711049079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15081715583801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22359323501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18912029266357</t>
+    <t xml:space="preserve">3.16077589988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11711025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15081739425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22359347343445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18912053108215</t>
   </si>
   <si>
     <t xml:space="preserve">3.23355197906494</t>
@@ -4472,13 +4472,13 @@
     <t xml:space="preserve">3.17150068283081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07727551460266</t>
+    <t xml:space="preserve">3.07727527618408</t>
   </si>
   <si>
     <t xml:space="preserve">2.82830452919006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88116312026978</t>
+    <t xml:space="preserve">2.8811628818512</t>
   </si>
   <si>
     <t xml:space="preserve">2.67585802078247</t>
@@ -4490,13 +4490,13 @@
     <t xml:space="preserve">2.70573449134827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80991911888123</t>
+    <t xml:space="preserve">2.80991888046265</t>
   </si>
   <si>
     <t xml:space="preserve">2.88039708137512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80379056930542</t>
+    <t xml:space="preserve">2.80379033088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.71952366828918</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">2.60691261291504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63372468948364</t>
+    <t xml:space="preserve">2.63372445106506</t>
   </si>
   <si>
     <t xml:space="preserve">2.65900468826294</t>
@@ -4514,19 +4514,19 @@
     <t xml:space="preserve">2.75782680511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79996013641357</t>
+    <t xml:space="preserve">2.79996037483215</t>
   </si>
   <si>
     <t xml:space="preserve">2.76165723800659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7785108089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75476264953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82370829582214</t>
+    <t xml:space="preserve">2.77851057052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75476241111755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82370853424072</t>
   </si>
   <si>
     <t xml:space="preserve">2.83979535102844</t>
@@ -4547,34 +4547,34 @@
     <t xml:space="preserve">3.08033919334412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11098194122314</t>
+    <t xml:space="preserve">3.11098170280457</t>
   </si>
   <si>
     <t xml:space="preserve">3.24427676200867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31637191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21511483192444</t>
+    <t xml:space="preserve">3.31637167930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21511459350586</t>
   </si>
   <si>
     <t xml:space="preserve">3.03609228134155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11466789245605</t>
+    <t xml:space="preserve">3.11466765403748</t>
   </si>
   <si>
     <t xml:space="preserve">2.98505854606628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92187428474426</t>
+    <t xml:space="preserve">2.92187452316284</t>
   </si>
   <si>
     <t xml:space="preserve">2.96966743469238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89595246315002</t>
+    <t xml:space="preserve">2.89595222473145</t>
   </si>
   <si>
     <t xml:space="preserve">3.0109806060791</t>
@@ -4583,13 +4583,13 @@
     <t xml:space="preserve">3.04905295372009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27910900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15679049491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1106173992157</t>
+    <t xml:space="preserve">3.27910923957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1567907333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11061716079712</t>
   </si>
   <si>
     <t xml:space="preserve">3.16003108024597</t>
@@ -4604,16 +4604,16 @@
     <t xml:space="preserve">3.13572931289673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17947220802307</t>
+    <t xml:space="preserve">3.17947196960449</t>
   </si>
   <si>
     <t xml:space="preserve">3.1584107875824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21754455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025443077087</t>
+    <t xml:space="preserve">3.21754479408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025466918945</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631563186646</t>
@@ -4622,25 +4622,25 @@
     <t xml:space="preserve">3.09684634208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09441637992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05472350120544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02151131629944</t>
+    <t xml:space="preserve">3.09441614151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05472373962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02151107788086</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03771233558655</t>
+    <t xml:space="preserve">3.03771209716797</t>
   </si>
   <si>
     <t xml:space="preserve">3.11142754554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06768465042114</t>
+    <t xml:space="preserve">3.06768441200256</t>
   </si>
   <si>
     <t xml:space="preserve">3.11304759979248</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">3.07983541488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10251688957214</t>
+    <t xml:space="preserve">3.10251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">3.09198617935181</t>
@@ -4673,16 +4673,16 @@
     <t xml:space="preserve">3.26776838302612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24751687049866</t>
+    <t xml:space="preserve">3.24751663208008</t>
   </si>
   <si>
     <t xml:space="preserve">3.31556177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29612040519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22888588905334</t>
+    <t xml:space="preserve">3.29612016677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22888565063477</t>
   </si>
   <si>
     <t xml:space="preserve">3.22240519523621</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">3.31070137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40223789215088</t>
+    <t xml:space="preserve">3.4022376537323</t>
   </si>
   <si>
     <t xml:space="preserve">3.44274067878723</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">3.44031071662903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44355058670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34553408622742</t>
+    <t xml:space="preserve">3.44355082511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34553384780884</t>
   </si>
   <si>
     <t xml:space="preserve">3.42005920410156</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">3.61042213439941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62500309944153</t>
+    <t xml:space="preserve">3.62500333786011</t>
   </si>
   <si>
     <t xml:space="preserve">3.58531069755554</t>
@@ -4742,13 +4742,13 @@
     <t xml:space="preserve">3.60475182533264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59422135353088</t>
+    <t xml:space="preserve">3.5942211151123</t>
   </si>
   <si>
     <t xml:space="preserve">3.59503149986267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5934112071991</t>
+    <t xml:space="preserve">3.59341096878052</t>
   </si>
   <si>
     <t xml:space="preserve">3.63391423225403</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">3.63634419441223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63553404808044</t>
+    <t xml:space="preserve">3.63553428649902</t>
   </si>
   <si>
     <t xml:space="preserve">3.68413734436035</t>
@@ -4769,25 +4769,25 @@
     <t xml:space="preserve">3.58774065971375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50511503219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48162317276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56505942344666</t>
+    <t xml:space="preserve">3.50511527061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48162341117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56505918502808</t>
   </si>
   <si>
     <t xml:space="preserve">3.24103665351868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41762900352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51807570457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50106501579285</t>
+    <t xml:space="preserve">3.4176287651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51807594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50106453895569</t>
   </si>
   <si>
     <t xml:space="preserve">3.54966807365417</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">3.55209851264954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54480767250061</t>
+    <t xml:space="preserve">3.54480791091919</t>
   </si>
   <si>
     <t xml:space="preserve">3.52293610572815</t>
@@ -4805,16 +4805,16 @@
     <t xml:space="preserve">3.55857872962952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54156804084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5156455039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56667947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5764000415802</t>
+    <t xml:space="preserve">3.5415678024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51564598083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56667900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57639980316162</t>
   </si>
   <si>
     <t xml:space="preserve">3.60556244850159</t>
@@ -4823,22 +4823,22 @@
     <t xml:space="preserve">3.57720994949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54318737983704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49944472312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46380186080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35687494277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28883004188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32123208045959</t>
+    <t xml:space="preserve">3.54318785667419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49944496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46380257606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35687446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28882956504822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32123184204102</t>
   </si>
   <si>
     <t xml:space="preserve">3.3852264881134</t>
@@ -4847,22 +4847,22 @@
     <t xml:space="preserve">3.45651173591614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48324370384216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53994750976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62743353843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70843911170959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7724335193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7521824836731</t>
+    <t xml:space="preserve">3.48324346542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53994727134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62743377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70843935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77243375778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75218224525452</t>
   </si>
   <si>
     <t xml:space="preserve">3.82670760154724</t>
@@ -4871,31 +4871,31 @@
     <t xml:space="preserve">3.75137233734131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68980765342712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74084162712097</t>
+    <t xml:space="preserve">3.6898078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74084138870239</t>
   </si>
   <si>
     <t xml:space="preserve">3.67360687255859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68251729011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66712594032288</t>
+    <t xml:space="preserve">3.68251776695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66712617874146</t>
   </si>
   <si>
     <t xml:space="preserve">3.72626042366028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8550591468811</t>
+    <t xml:space="preserve">3.85505962371826</t>
   </si>
   <si>
     <t xml:space="preserve">3.74570202827454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84452843666077</t>
+    <t xml:space="preserve">3.84452867507935</t>
   </si>
   <si>
     <t xml:space="preserve">3.84614896774292</t>
@@ -4904,34 +4904,34 @@
     <t xml:space="preserve">3.84776902198792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84938931465149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92634463310242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97818803787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97089791297913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80078554153442</t>
+    <t xml:space="preserve">3.84938883781433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.926344871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97818779945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97089743614197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.800785779953</t>
   </si>
   <si>
     <t xml:space="preserve">3.8396680355072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76838350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402588844299</t>
+    <t xml:space="preserve">3.76838326454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402612686157</t>
   </si>
   <si>
     <t xml:space="preserve">3.80726599693298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79349541664124</t>
+    <t xml:space="preserve">3.79349493980408</t>
   </si>
   <si>
     <t xml:space="preserve">3.82589745521545</t>
@@ -4940,16 +4940,16 @@
     <t xml:space="preserve">3.90690302848816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95793700218201</t>
+    <t xml:space="preserve">3.95793676376343</t>
   </si>
   <si>
     <t xml:space="preserve">3.94173574447632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94659614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97251749038696</t>
+    <t xml:space="preserve">3.94659638404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97251772880554</t>
   </si>
   <si>
     <t xml:space="preserve">3.94011521339417</t>
@@ -4958,40 +4958,40 @@
     <t xml:space="preserve">3.99114894866943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10698747634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11994791030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30950164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28357934951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31112098693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25279760360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27223873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31274127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1393895149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11346769332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13128900527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642812728882</t>
+    <t xml:space="preserve">4.10698699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.119948387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30950117111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28357982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31112146377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25279712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27223920822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31274175643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13938903808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1134672164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13128852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642860412598</t>
   </si>
   <si>
     <t xml:space="preserve">4.08916568756104</t>
@@ -5000,13 +5000,13 @@
     <t xml:space="preserve">4.09888648986816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12318849563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11022710800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18637323379517</t>
+    <t xml:space="preserve">4.12318801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11022758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18637275695801</t>
   </si>
   <si>
     <t xml:space="preserve">4.14100933074951</t>
@@ -5027,19 +5027,19 @@
     <t xml:space="preserve">4.05676364898682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90204262733459</t>
+    <t xml:space="preserve">3.90204286575317</t>
   </si>
   <si>
     <t xml:space="preserve">3.8348081111908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.870450258255</t>
+    <t xml:space="preserve">3.87045049667358</t>
   </si>
   <si>
     <t xml:space="preserve">3.89961266517639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84290838241577</t>
+    <t xml:space="preserve">3.84290862083435</t>
   </si>
   <si>
     <t xml:space="preserve">3.81617665290833</t>
@@ -5048,40 +5048,40 @@
     <t xml:space="preserve">3.86072969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88260173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87288093566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94335579872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9441659450531</t>
+    <t xml:space="preserve">3.88260197639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87288117408752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94335556030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94416570663452</t>
   </si>
   <si>
     <t xml:space="preserve">4.10374689102173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17503118515015</t>
+    <t xml:space="preserve">4.17503213882446</t>
   </si>
   <si>
     <t xml:space="preserve">4.14749002456665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9457859992981</t>
+    <t xml:space="preserve">3.94578576087952</t>
   </si>
   <si>
     <t xml:space="preserve">3.9506459236145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88422131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88584160804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8331880569458</t>
+    <t xml:space="preserve">3.88422155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88584136962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83318781852722</t>
   </si>
   <si>
     <t xml:space="preserve">3.88665151596069</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">3.93687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96927785873413</t>
+    <t xml:space="preserve">3.96927738189697</t>
   </si>
   <si>
     <t xml:space="preserve">3.94821572303772</t>
@@ -5105,13 +5105,13 @@
     <t xml:space="preserve">3.99762940406799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05838394165039</t>
+    <t xml:space="preserve">4.05838346481323</t>
   </si>
   <si>
     <t xml:space="preserve">4.00573015213013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06486463546753</t>
+    <t xml:space="preserve">4.06486415863037</t>
   </si>
   <si>
     <t xml:space="preserve">4.0745849609375</t>
@@ -5129,10 +5129,10 @@
     <t xml:space="preserve">4.29978084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13290929794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13614892959595</t>
+    <t xml:space="preserve">4.13290882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13614940643311</t>
   </si>
   <si>
     <t xml:space="preserve">4.00897026062012</t>
@@ -5141,10 +5141,10 @@
     <t xml:space="preserve">3.98223829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98547887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.996009349823</t>
+    <t xml:space="preserve">3.98547863960266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99600911140442</t>
   </si>
   <si>
     <t xml:space="preserve">4.03408193588257</t>
@@ -5162,7 +5162,7 @@
     <t xml:space="preserve">4.40670776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36782550811768</t>
+    <t xml:space="preserve">4.36782503128052</t>
   </si>
   <si>
     <t xml:space="preserve">4.35324430465698</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">4.49581432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51363515853882</t>
+    <t xml:space="preserve">4.51363563537598</t>
   </si>
   <si>
     <t xml:space="preserve">4.50553464889526</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">4.45531129837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47313213348389</t>
+    <t xml:space="preserve">4.47313261032104</t>
   </si>
   <si>
     <t xml:space="preserve">4.54765796661377</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">4.61570262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69994831085205</t>
+    <t xml:space="preserve">4.69994878768921</t>
   </si>
   <si>
     <t xml:space="preserve">4.81335639953613</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">4.85385942459106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84899854660034</t>
+    <t xml:space="preserve">4.8489990234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.88302135467529</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">4.95916700363159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01100969314575</t>
+    <t xml:space="preserve">5.01101016998291</t>
   </si>
   <si>
     <t xml:space="preserve">4.96240663528442</t>
@@ -5225,25 +5225,25 @@
     <t xml:space="preserve">4.99642944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04989290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15358066558838</t>
+    <t xml:space="preserve">5.04989337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15358018875122</t>
   </si>
   <si>
     <t xml:space="preserve">5.12927865982056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0709547996521</t>
+    <t xml:space="preserve">5.07095432281494</t>
   </si>
   <si>
     <t xml:space="preserve">5.10173654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05151271820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17140102386475</t>
+    <t xml:space="preserve">5.05151319503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1714015007019</t>
   </si>
   <si>
     <t xml:space="preserve">4.98832845687866</t>
@@ -5252,7 +5252,7 @@
     <t xml:space="preserve">4.92838478088379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98670864105225</t>
+    <t xml:space="preserve">4.9867091178894</t>
   </si>
   <si>
     <t xml:space="preserve">4.96564722061157</t>
@@ -5261,16 +5261,16 @@
     <t xml:space="preserve">5.06285381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14709949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17626190185547</t>
+    <t xml:space="preserve">5.14709997177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17626142501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43019151687622</t>
+    <t xml:space="preserve">5.43019199371338</t>
   </si>
   <si>
     <t xml:space="preserve">5.42486476898193</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">5.51897811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47280979156494</t>
+    <t xml:space="preserve">5.47280931472778</t>
   </si>
   <si>
     <t xml:space="preserve">5.49056673049927</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">5.74449634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80131959915161</t>
+    <t xml:space="preserve">5.80132007598877</t>
   </si>
   <si>
     <t xml:space="preserve">5.96646308898926</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">5.75515079498291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75337553024292</t>
+    <t xml:space="preserve">5.75337505340576</t>
   </si>
   <si>
     <t xml:space="preserve">5.79421710968018</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">5.86347055435181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84571313858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7143087387085</t>
+    <t xml:space="preserve">5.84571361541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71430921554565</t>
   </si>
   <si>
     <t xml:space="preserve">5.66813945770264</t>
@@ -5354,7 +5354,7 @@
     <t xml:space="preserve">5.7622537612915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77645969390869</t>
+    <t xml:space="preserve">5.77646017074585</t>
   </si>
   <si>
     <t xml:space="preserve">5.7160849571228</t>
@@ -5378,34 +5378,34 @@
     <t xml:space="preserve">5.35383558273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40355539321899</t>
+    <t xml:space="preserve">5.40355587005615</t>
   </si>
   <si>
     <t xml:space="preserve">5.48346376419067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38402318954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5047721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43729496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4088830947876</t>
+    <t xml:space="preserve">5.38402271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50477266311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43729448318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40888261795044</t>
   </si>
   <si>
     <t xml:space="preserve">5.3502836227417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33962965011597</t>
+    <t xml:space="preserve">5.33962917327881</t>
   </si>
   <si>
     <t xml:space="preserve">5.51009941101074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57757806777954</t>
+    <t xml:space="preserve">5.57757759094238</t>
   </si>
   <si>
     <t xml:space="preserve">5.61309242248535</t>
@@ -5423,10 +5423,10 @@
     <t xml:space="preserve">5.52075386047363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53673553466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57935285568237</t>
+    <t xml:space="preserve">5.53673601150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57935333251953</t>
   </si>
   <si>
     <t xml:space="preserve">5.6113166809082</t>
@@ -5456,13 +5456,13 @@
     <t xml:space="preserve">5.19401931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08569955825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19046831130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11233520507812</t>
+    <t xml:space="preserve">5.08570003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19046783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11233568191528</t>
   </si>
   <si>
     <t xml:space="preserve">5.14785003662109</t>
@@ -5483,10 +5483,10 @@
     <t xml:space="preserve">5.33075094223022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24906730651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34318065643311</t>
+    <t xml:space="preserve">5.2490668296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34318113327026</t>
   </si>
   <si>
     <t xml:space="preserve">5.401780128479</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">5.45505237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46570634841919</t>
+    <t xml:space="preserve">5.46570682525635</t>
   </si>
   <si>
     <t xml:space="preserve">5.30056285858154</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">5.304114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33785390853882</t>
+    <t xml:space="preserve">5.33785343170166</t>
   </si>
   <si>
     <t xml:space="preserve">5.49411821365356</t>
@@ -5543,13 +5543,13 @@
     <t xml:space="preserve">5.38757371902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39822864532471</t>
+    <t xml:space="preserve">5.39822816848755</t>
   </si>
   <si>
     <t xml:space="preserve">5.57225036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53140878677368</t>
+    <t xml:space="preserve">5.53140830993652</t>
   </si>
   <si>
     <t xml:space="preserve">5.37869548797607</t>
@@ -5558,13 +5558,13 @@
     <t xml:space="preserve">5.14252281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28813314437866</t>
+    <t xml:space="preserve">5.2881326675415</t>
   </si>
   <si>
     <t xml:space="preserve">5.26327276229858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32719898223877</t>
+    <t xml:space="preserve">5.32719945907593</t>
   </si>
   <si>
     <t xml:space="preserve">5.46925783157349</t>
@@ -5585,25 +5585,25 @@
     <t xml:space="preserve">5.51187562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40000438690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40533113479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49766969680786</t>
+    <t xml:space="preserve">5.4000039100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4053316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4976692199707</t>
   </si>
   <si>
     <t xml:space="preserve">5.50122117996216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48879146575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64150381088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78001165390015</t>
+    <t xml:space="preserve">5.48879098892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64150428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78001117706299</t>
   </si>
   <si>
     <t xml:space="preserve">6.10674619674683</t>
@@ -5612,13 +5612,13 @@
     <t xml:space="preserve">5.96291160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06057739257812</t>
+    <t xml:space="preserve">6.06057691574097</t>
   </si>
   <si>
     <t xml:space="preserve">6.01973533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00197839736938</t>
+    <t xml:space="preserve">6.00197792053223</t>
   </si>
   <si>
     <t xml:space="preserve">6.1848783493042</t>
@@ -6291,6 +6291,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.6400003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5950002670288</t>
   </si>
 </sst>
 </file>
@@ -71733,25 +71736,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6912037037</v>
+        <v>45968.691875</v>
       </c>
       <c r="B2505" t="n">
-        <v>8457821</v>
+        <v>6401761</v>
       </c>
       <c r="C2505" t="n">
-        <v>12.8999996185303</v>
+        <v>12.8000001907349</v>
       </c>
       <c r="D2505" t="n">
-        <v>12.4849996566772</v>
+        <v>12.4250001907349</v>
       </c>
       <c r="E2505" t="n">
-        <v>12.8000001907349</v>
+        <v>12.5</v>
       </c>
       <c r="F2505" t="n">
-        <v>12.6400003433228</v>
+        <v>12.5950002670288</v>
       </c>
       <c r="G2505" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="2094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="2095">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">6.25302314758301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98424005508423</t>
+    <t xml:space="preserve">5.98423957824707</t>
   </si>
   <si>
     <t xml:space="preserve">5.89802598953247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6545991897583</t>
+    <t xml:space="preserve">5.65459871292114</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89295434951782</t>
+    <t xml:space="preserve">5.65967082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89295387268066</t>
   </si>
   <si>
     <t xml:space="preserve">5.274245262146</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">4.9420690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40450239181519</t>
+    <t xml:space="preserve">4.40450143814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.85839128494263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61496448516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28785991668701</t>
+    <t xml:space="preserve">4.61496496200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28786087036133</t>
   </si>
   <si>
     <t xml:space="preserve">4.55410766601562</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">4.19911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9556839466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32082414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57946443557739</t>
+    <t xml:space="preserve">3.95568299293518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32082462310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57946395874023</t>
   </si>
   <si>
     <t xml:space="preserve">4.50339317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0520396232605</t>
+    <t xml:space="preserve">4.05204010009766</t>
   </si>
   <si>
     <t xml:space="preserve">4.11289691925049</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">3.87961268424988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52715134620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22286772727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040070533752</t>
+    <t xml:space="preserve">3.52715110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22286796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5804009437561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26851058006287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64379262924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004157066345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04443311691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1433253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91511273384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818489074707</t>
+    <t xml:space="preserve">3.64379334449768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004204750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04443264007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14332485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91511297225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818512916565</t>
   </si>
   <si>
     <t xml:space="preserve">4.08246850967407</t>
@@ -146,94 +146,94 @@
     <t xml:space="preserve">3.7198646068573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64632940292358</t>
+    <t xml:space="preserve">3.64632964134216</t>
   </si>
   <si>
     <t xml:space="preserve">3.74775671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84157729148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92018342018127</t>
+    <t xml:space="preserve">3.84157752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92018365859985</t>
   </si>
   <si>
     <t xml:space="preserve">4.22700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04950428009033</t>
+    <t xml:space="preserve">4.04950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">3.88468432426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86693453788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76043558120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69957852363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03682613372803</t>
+    <t xml:space="preserve">3.86693429946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76043510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69957804679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03682518005371</t>
   </si>
   <si>
     <t xml:space="preserve">3.94807720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38768815994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47136616706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197106361389</t>
+    <t xml:space="preserve">3.38768792152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4713659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67675709724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197130203247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51447319984436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38261675834656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27611756324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06565427780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365622520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49005150794983</t>
+    <t xml:space="preserve">3.38261651992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2761173248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06565475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365598678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812201499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49005174636841</t>
   </si>
   <si>
     <t xml:space="preserve">2.40586733818054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22431135177612</t>
+    <t xml:space="preserve">2.2243115901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.46672344207764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72080016136169</t>
+    <t xml:space="preserve">2.72079992294312</t>
   </si>
   <si>
     <t xml:space="preserve">2.700514793396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91097736358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02508330345154</t>
+    <t xml:space="preserve">2.910977602005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02508354187012</t>
   </si>
   <si>
     <t xml:space="preserve">3.16454672813416</t>
@@ -242,49 +242,49 @@
     <t xml:space="preserve">3.22690272331238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1385657787323</t>
+    <t xml:space="preserve">3.13856601715088</t>
   </si>
   <si>
     <t xml:space="preserve">3.14116311073303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20092082023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508953094482</t>
+    <t xml:space="preserve">3.20092058181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2450897693634</t>
   </si>
   <si>
     <t xml:space="preserve">3.11778020858765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23469686508179</t>
+    <t xml:space="preserve">3.23469710350037</t>
   </si>
   <si>
     <t xml:space="preserve">3.19052886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32823061943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20351910591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96968626976013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75663757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86835789680481</t>
+    <t xml:space="preserve">3.32823014259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20351886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96968603134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75663709640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86835813522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84497475624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59607124328613</t>
+    <t xml:space="preserve">2.84497451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59607172012329</t>
   </si>
   <si>
     <t xml:space="preserve">2.51500940322876</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">2.28637218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32378602027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32274651527405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39237666130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23544859886169</t>
+    <t xml:space="preserve">2.32378578186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32274627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39237642288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23544836044312</t>
   </si>
   <si>
     <t xml:space="preserve">2.24584078788757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22089910507202</t>
+    <t xml:space="preserve">2.22089886665344</t>
   </si>
   <si>
     <t xml:space="preserve">2.24480175971985</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">2.2749400138855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47343921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4703209400177</t>
+    <t xml:space="preserve">2.47343897819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47032117843628</t>
   </si>
   <si>
     <t xml:space="preserve">2.48902797698975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49422407150269</t>
+    <t xml:space="preserve">2.49422383308411</t>
   </si>
   <si>
     <t xml:space="preserve">2.31131458282471</t>
@@ -344,28 +344,28 @@
     <t xml:space="preserve">2.05461692810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15853524208069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29020476341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22156858444214</t>
+    <t xml:space="preserve">2.15853548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2902045249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22156834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433287620544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04227423667908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83636569976807</t>
+    <t xml:space="preserve">2.0422739982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83636605739594</t>
   </si>
   <si>
     <t xml:space="preserve">1.7159024477005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83776652812958</t>
+    <t xml:space="preserve">1.83776664733887</t>
   </si>
   <si>
     <t xml:space="preserve">2.07449102401733</t>
@@ -374,31 +374,31 @@
     <t xml:space="preserve">2.01846170425415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02546525001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.993248462677</t>
+    <t xml:space="preserve">2.02546548843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99324834346771</t>
   </si>
   <si>
     <t xml:space="preserve">2.12211608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62765610218048</t>
+    <t xml:space="preserve">1.62765598297119</t>
   </si>
   <si>
     <t xml:space="preserve">1.52680313587189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55481779575348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50439131259918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50158989429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540242671967</t>
+    <t xml:space="preserve">1.55481791496277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50439143180847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50158977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540230751038</t>
   </si>
   <si>
     <t xml:space="preserve">1.45676624774933</t>
@@ -407,31 +407,31 @@
     <t xml:space="preserve">1.40073668956757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31459152698517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28167402744293</t>
+    <t xml:space="preserve">1.31459140777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28167414665222</t>
   </si>
   <si>
     <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57022595405579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66687667369843</t>
+    <t xml:space="preserve">1.57022607326508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.666876912117</t>
   </si>
   <si>
     <t xml:space="preserve">1.5562185049057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64166343212128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66267442703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68788778781891</t>
+    <t xml:space="preserve">1.64166355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66267490386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6878879070282</t>
   </si>
   <si>
     <t xml:space="preserve">1.67528116703033</t>
@@ -446,25 +446,25 @@
     <t xml:space="preserve">1.70329570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71730315685272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7593252658844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70749807357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76352727413177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50579190254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49738776683807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55201637744904</t>
+    <t xml:space="preserve">1.71730327606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75932538509369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70749795436859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76352751255035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5057920217514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49738764762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55201649665833</t>
   </si>
   <si>
     <t xml:space="preserve">1.63045752048492</t>
@@ -473,46 +473,46 @@
     <t xml:space="preserve">1.5996413230896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5926376581192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58143174648285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56882524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53100538253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52820372581482</t>
+    <t xml:space="preserve">1.59263741970062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58143162727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56882500648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53100526332855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52820384502411</t>
   </si>
   <si>
     <t xml:space="preserve">1.4539647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48758256435394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58003103733063</t>
+    <t xml:space="preserve">1.48758244514465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58003115653992</t>
   </si>
   <si>
     <t xml:space="preserve">1.53520739078522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51559734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56742453575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56182157993317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60384333133698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68088436126709</t>
+    <t xml:space="preserve">1.51559722423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56742441654205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56182134151459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60384356975555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68088412284851</t>
   </si>
   <si>
     <t xml:space="preserve">1.63886189460754</t>
@@ -521,49 +521,49 @@
     <t xml:space="preserve">1.65707147121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65847229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6430641412735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59403860569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60944640636444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57582879066467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50018894672394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46657133102417</t>
+    <t xml:space="preserve">1.65847218036652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64306402206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59403848648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60944652557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57582902908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50018906593323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46657145023346</t>
   </si>
   <si>
     <t xml:space="preserve">1.40003633499146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45116329193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47357523441315</t>
+    <t xml:space="preserve">1.45116317272186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47357511520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.4399573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40633952617645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37832498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39653444290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40774047374725</t>
+    <t xml:space="preserve">1.40633964538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37832486629486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3965345621109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40774035453796</t>
   </si>
   <si>
     <t xml:space="preserve">1.46797204017639</t>
@@ -572,79 +572,79 @@
     <t xml:space="preserve">1.48057878017426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50299048423767</t>
+    <t xml:space="preserve">1.50299036502838</t>
   </si>
   <si>
     <t xml:space="preserve">1.55061554908752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65286910533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78593933582306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79994666576385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84617078304291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317468643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82235848903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737705230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86298012733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041027545929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89379608631134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80835127830505</t>
+    <t xml:space="preserve">1.65286922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78593945503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79994678497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8461709022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8531745672226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196877479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82235860824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737669467926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86298000812531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041003704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89379620552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80835103988647</t>
   </si>
   <si>
     <t xml:space="preserve">1.67107892036438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61224794387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50999414920807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59543919563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60664486885071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5127956867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42735087871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35451245307922</t>
+    <t xml:space="preserve">1.61224782466888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50999402999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59543931484222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60664510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51279580593109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42735075950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35451233386993</t>
   </si>
   <si>
     <t xml:space="preserve">1.30408585071564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31179010868073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32649767398834</t>
+    <t xml:space="preserve">1.31178998947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32649779319763</t>
   </si>
   <si>
     <t xml:space="preserve">1.29988372325897</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">1.31739294528961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25085806846619</t>
+    <t xml:space="preserve">1.2508579492569</t>
   </si>
   <si>
     <t xml:space="preserve">1.30268514156342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35871481895447</t>
+    <t xml:space="preserve">1.35871458053589</t>
   </si>
   <si>
     <t xml:space="preserve">1.39233231544495</t>
@@ -668,19 +668,19 @@
     <t xml:space="preserve">1.28867793083191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40493905544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49458622932434</t>
+    <t xml:space="preserve">1.40493893623352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49458611011505</t>
   </si>
   <si>
     <t xml:space="preserve">1.64026272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5646231174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53380656242371</t>
+    <t xml:space="preserve">1.56462287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.533806681633</t>
   </si>
   <si>
     <t xml:space="preserve">1.67948317527771</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">1.69769322872162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6514687538147</t>
+    <t xml:space="preserve">1.65146863460541</t>
   </si>
   <si>
     <t xml:space="preserve">1.72290623188019</t>
@@ -698,121 +698,121 @@
     <t xml:space="preserve">1.77893567085266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71310102939606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60524451732635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092113018036</t>
+    <t xml:space="preserve">1.71310126781464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60524427890778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092077255249</t>
   </si>
   <si>
     <t xml:space="preserve">1.87698721885681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90500199794769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643947601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03106832504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512265920639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94982540607452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90640258789062</t>
+    <t xml:space="preserve">1.90500175952911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643959522247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03106808662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95122611522675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94982552528381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90640270709991</t>
   </si>
   <si>
     <t xml:space="preserve">1.94702410697937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89799821376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9414210319519</t>
+    <t xml:space="preserve">1.89799845218658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142138957977</t>
   </si>
   <si>
     <t xml:space="preserve">1.93581795692444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01706075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97363793849945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02266359329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849859237671</t>
+    <t xml:space="preserve">2.01706123352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97363829612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02266383171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849883079529</t>
   </si>
   <si>
     <t xml:space="preserve">2.00585508346558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02126288414001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86017835140228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89099454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78033626079559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67388033866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74251627922058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73831450939178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64586567878723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75512313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84056806564331</t>
+    <t xml:space="preserve">2.02126312255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86017858982086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8909946680069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78033649921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67388045787811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74251639842987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73831427097321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64586544036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75512325763702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8405681848526</t>
   </si>
   <si>
     <t xml:space="preserve">1.77753496170044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78173696994781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68368566036224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62205302715302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51419651508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006756782532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71870422363281</t>
+    <t xml:space="preserve">1.78173673152924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68368554115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62205326557159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51419639587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006792545319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71870386600494</t>
   </si>
   <si>
     <t xml:space="preserve">1.71450161933899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68228471279144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69349050521851</t>
+    <t xml:space="preserve">1.68228495121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69349074363708</t>
   </si>
   <si>
     <t xml:space="preserve">1.69629204273224</t>
@@ -821,100 +821,100 @@
     <t xml:space="preserve">1.8097517490387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81535482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7607262134552</t>
+    <t xml:space="preserve">1.81535470485687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072609424591</t>
   </si>
   <si>
     <t xml:space="preserve">1.80695021152496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86858296394348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85597622394562</t>
+    <t xml:space="preserve">1.8685827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85597634315491</t>
   </si>
   <si>
     <t xml:space="preserve">1.91620790958405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90780353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91480720043182</t>
+    <t xml:space="preserve">1.90780329704285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91480708122253</t>
   </si>
   <si>
     <t xml:space="preserve">1.88539159297943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88819336891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94562351703644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90360105037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89939892292023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87978851795197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86718225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76212704181671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542871952057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86157917976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8699836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00445461273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04647636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9190092086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87838804721832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98204207420349</t>
+    <t xml:space="preserve">1.88819313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94562339782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90360116958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89939916133881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87978887557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86718201637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76212668418884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95542848110199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8615790605545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86998355388641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00445413589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04647612571716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91900932788849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87838792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98204231262207</t>
   </si>
   <si>
     <t xml:space="preserve">1.96383309364319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8825900554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93021512031555</t>
+    <t xml:space="preserve">1.88259017467499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93021523952484</t>
   </si>
   <si>
     <t xml:space="preserve">1.97784018516541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09410166740417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17814564704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11371159553528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12491774559021</t>
+    <t xml:space="preserve">2.0941014289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17814540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11371183395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12491750717163</t>
   </si>
   <si>
     <t xml:space="preserve">1.99464917182922</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">2.00305342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90220069885254</t>
+    <t xml:space="preserve">1.90220081806183</t>
   </si>
   <si>
     <t xml:space="preserve">1.99885153770447</t>
@@ -935,67 +935,67 @@
     <t xml:space="preserve">1.95402765274048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9344174861908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920436382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91060507297516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88679206371307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9582302570343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94422280788422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99184787273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06048369407654</t>
+    <t xml:space="preserve">1.93441736698151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920412540436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91060495376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88679254055023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95822989940643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94422256946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99184775352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06048393249512</t>
   </si>
   <si>
     <t xml:space="preserve">2.05207943916321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10950922966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14592885971069</t>
+    <t xml:space="preserve">2.10950970649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14592838287354</t>
   </si>
   <si>
     <t xml:space="preserve">2.0955023765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16974139213562</t>
+    <t xml:space="preserve">2.16974115371704</t>
   </si>
   <si>
     <t xml:space="preserve">2.14452791213989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18795108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20616054534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20896196365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19915676116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19635510444641</t>
+    <t xml:space="preserve">2.18795084953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20616030693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20896172523499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19915699958801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19635486602783</t>
   </si>
   <si>
     <t xml:space="preserve">2.14172673225403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20335865020752</t>
+    <t xml:space="preserve">2.2033588886261</t>
   </si>
   <si>
     <t xml:space="preserve">2.19215297698975</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">2.15573382377625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16413807868958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16273760795593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20756077766418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997283935547</t>
+    <t xml:space="preserve">2.16413831710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16273784637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20756125450134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997307777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.28320074081421</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">2.33082604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30561256408691</t>
+    <t xml:space="preserve">2.30561280250549</t>
   </si>
   <si>
     <t xml:space="preserve">2.26499152183533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29720830917358</t>
+    <t xml:space="preserve">2.297208070755</t>
   </si>
   <si>
     <t xml:space="preserve">2.30981492996216</t>
@@ -1043,28 +1043,28 @@
     <t xml:space="preserve">2.27339577674866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32242155075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2271716594696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2607889175415</t>
+    <t xml:space="preserve">2.32242131233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22717142105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26078939437866</t>
   </si>
   <si>
     <t xml:space="preserve">2.22016763687134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23277425765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26219010353088</t>
+    <t xml:space="preserve">2.23277449607849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2621898651123</t>
   </si>
   <si>
     <t xml:space="preserve">2.21036243438721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15993595123291</t>
+    <t xml:space="preserve">2.15993618965149</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713453292847</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">2.10110521316528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13052082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18935132026672</t>
+    <t xml:space="preserve">2.1305205821991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1893515586853</t>
   </si>
   <si>
     <t xml:space="preserve">2.25518608093262</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">2.29300594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30421209335327</t>
+    <t xml:space="preserve">2.30421185493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.30141043663025</t>
@@ -1094,58 +1094,58 @@
     <t xml:space="preserve">2.31121563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33782958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28180027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33642864227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43448066711426</t>
+    <t xml:space="preserve">2.33782982826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28180003166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33642888069153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43448042869568</t>
   </si>
   <si>
     <t xml:space="preserve">2.45409083366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45689225196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43307948112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43027806282043</t>
+    <t xml:space="preserve">2.4568920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43307971954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43027830123901</t>
   </si>
   <si>
     <t xml:space="preserve">2.24117875099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17954611778259</t>
+    <t xml:space="preserve">2.17954635620117</t>
   </si>
   <si>
     <t xml:space="preserve">2.13192129135132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23417544364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20475959777832</t>
+    <t xml:space="preserve">2.23417520523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2047598361969</t>
   </si>
   <si>
     <t xml:space="preserve">2.1907525062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.151531457901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2019579410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18374872207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21456480026245</t>
+    <t xml:space="preserve">2.15153169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20195817947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.183748960495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21456503868103</t>
   </si>
   <si>
     <t xml:space="preserve">2.17674493789673</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">2.13332200050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10810875892639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09130001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04507565498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083640098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91200566291809</t>
+    <t xml:space="preserve">2.10810852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09130024909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0450758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9708366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9120055437088</t>
   </si>
   <si>
     <t xml:space="preserve">1.9274138212204</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">1.88959360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87558650970459</t>
+    <t xml:space="preserve">1.87558662891388</t>
   </si>
   <si>
     <t xml:space="preserve">2.01566004753113</t>
@@ -1196,61 +1196,61 @@
     <t xml:space="preserve">1.96943581104279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92321157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96523380279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181074619293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83496510982513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76492846012115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.752321600914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77193200588226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78313779830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82656061649323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86438071727753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177385807037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86578142642975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84897255897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88399076461792</t>
+    <t xml:space="preserve">1.92321169376373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96523368358612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181086540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83496499061584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76492834091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75232183933258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77193188667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78313791751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8265608549118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86438059806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177421569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395399570465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86578118801117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84897267818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88399088382721</t>
   </si>
   <si>
     <t xml:space="preserve">1.99745070934296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04787731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0436749458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99604976177216</t>
+    <t xml:space="preserve">2.04787707328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04367470741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99604964256287</t>
   </si>
   <si>
     <t xml:space="preserve">2.08429622650146</t>
@@ -1262,40 +1262,40 @@
     <t xml:space="preserve">2.15013074874878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17114210128784</t>
+    <t xml:space="preserve">2.17114186286926</t>
   </si>
   <si>
     <t xml:space="preserve">2.18725037574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12701869010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14557838439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10355639457703</t>
+    <t xml:space="preserve">2.12701845169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14557862281799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10355663299561</t>
   </si>
   <si>
     <t xml:space="preserve">2.10320615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02826642990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04927778244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1536328792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16028642654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10600781440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03772187232971</t>
+    <t xml:space="preserve">2.0282666683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04927825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15363264083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16028618812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10600757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03772163391113</t>
   </si>
   <si>
     <t xml:space="preserve">2.1172137260437</t>
@@ -1307,25 +1307,25 @@
     <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12736916542053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15258193016052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18584966659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14207673072815</t>
+    <t xml:space="preserve">2.12736892700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1525821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18584990501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14207649230957</t>
   </si>
   <si>
     <t xml:space="preserve">2.19425415992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1900520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2030086517334</t>
+    <t xml:space="preserve">2.19005179405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20300889015198</t>
   </si>
   <si>
     <t xml:space="preserve">2.17604446411133</t>
@@ -1334,19 +1334,19 @@
     <t xml:space="preserve">2.1886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01005697250366</t>
+    <t xml:space="preserve">2.01005721092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.08709788322449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12771940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07624173164368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0664370059967</t>
+    <t xml:space="preserve">2.12771916389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07624220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06643676757812</t>
   </si>
   <si>
     <t xml:space="preserve">2.11441230773926</t>
@@ -1355,46 +1355,46 @@
     <t xml:space="preserve">2.08394622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13822436332703</t>
+    <t xml:space="preserve">2.13822460174561</t>
   </si>
   <si>
     <t xml:space="preserve">2.12036538124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12071561813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96348237991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98274302482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9872955083847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293770313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96838545799255</t>
+    <t xml:space="preserve">2.12071537971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9634827375412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98274278640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98729526996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96838510036469</t>
   </si>
   <si>
     <t xml:space="preserve">1.94107115268707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03422021865845</t>
+    <t xml:space="preserve">2.03421998023987</t>
   </si>
   <si>
     <t xml:space="preserve">2.00620532035828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01601052284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03492045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10915923118591</t>
+    <t xml:space="preserve">2.01601028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03491997718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10915899276733</t>
   </si>
   <si>
     <t xml:space="preserve">2.10775852203369</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">2.14382767677307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12421751022339</t>
+    <t xml:space="preserve">2.12421727180481</t>
   </si>
   <si>
     <t xml:space="preserve">2.14662909507751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11791396141052</t>
+    <t xml:space="preserve">2.11791372299194</t>
   </si>
   <si>
     <t xml:space="preserve">2.15888547897339</t>
@@ -1418,121 +1418,121 @@
     <t xml:space="preserve">2.13857483863831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14487838745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08289575576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14347720146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453062057495</t>
+    <t xml:space="preserve">2.14487791061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08289527893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14347743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453085899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.07028889656067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09970450401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86087870597839</t>
+    <t xml:space="preserve">2.09970426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8608785867691</t>
   </si>
   <si>
     <t xml:space="preserve">1.87523627281189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84442019462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82165813446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57687926292419</t>
+    <t xml:space="preserve">1.84442031383514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82165837287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5768791437149</t>
   </si>
   <si>
     <t xml:space="preserve">1.47077357769012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51839876174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55446767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6364107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59648954868317</t>
+    <t xml:space="preserve">1.51839864253998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55446755886078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578696250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641059398651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59648966789246</t>
   </si>
   <si>
     <t xml:space="preserve">1.68018364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61259806156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71170043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69874334335327</t>
+    <t xml:space="preserve">1.61259829998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71170032024384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69874322414398</t>
   </si>
   <si>
     <t xml:space="preserve">1.7246572971344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69138956069946</t>
+    <t xml:space="preserve">1.69138967990875</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808270454407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81990718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804063796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84792172908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78068673610687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73481249809265</t>
+    <t xml:space="preserve">1.81990730762482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804039955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8479220867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780686378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73481237888336</t>
   </si>
   <si>
     <t xml:space="preserve">1.70364582538605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77403318881989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80589997768402</t>
+    <t xml:space="preserve">1.77403283119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80589962005615</t>
   </si>
   <si>
     <t xml:space="preserve">1.8258603811264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87173449993134</t>
+    <t xml:space="preserve">1.87173461914062</t>
   </si>
   <si>
     <t xml:space="preserve">1.89274549484253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87243473529816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823236942291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85912775993347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83286392688751</t>
+    <t xml:space="preserve">1.87243461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823284626007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85912811756134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8328640460968</t>
   </si>
   <si>
     <t xml:space="preserve">1.81605517864227</t>
@@ -1541,19 +1541,19 @@
     <t xml:space="preserve">1.85072326660156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83601546287537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85807740688324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.853875041008</t>
+    <t xml:space="preserve">1.83601582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85807728767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85387516021729</t>
   </si>
   <si>
     <t xml:space="preserve">1.76807987689972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75337219238281</t>
+    <t xml:space="preserve">1.7533723115921</t>
   </si>
   <si>
     <t xml:space="preserve">1.64901745319366</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">1.64621603488922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66337490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65216910839081</t>
+    <t xml:space="preserve">1.66337478160858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65216886997223</t>
   </si>
   <si>
     <t xml:space="preserve">1.61960184574127</t>
@@ -1577,67 +1577,67 @@
     <t xml:space="preserve">1.53030478954315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46972286701202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42630016803741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42524981498718</t>
+    <t xml:space="preserve">1.4697231054306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42630004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42524969577789</t>
   </si>
   <si>
     <t xml:space="preserve">1.45501530170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44380950927734</t>
+    <t xml:space="preserve">1.44380939006805</t>
   </si>
   <si>
     <t xml:space="preserve">1.43190312385559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44415950775146</t>
+    <t xml:space="preserve">1.44415974617004</t>
   </si>
   <si>
     <t xml:space="preserve">1.43925702571869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40704011917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120276927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40178728103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35815441608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37132108211517</t>
+    <t xml:space="preserve">1.40704023838043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40178716182709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.358154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37132132053375</t>
   </si>
   <si>
     <t xml:space="preserve">1.50719261169434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49493634700775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54326152801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53555774688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55026543140411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61084735393524</t>
+    <t xml:space="preserve">1.49493622779846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54326188564301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5355578660965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55026531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">1.61539959907532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61610007286072</t>
+    <t xml:space="preserve">1.61609983444214</t>
   </si>
   <si>
     <t xml:space="preserve">1.62625539302826</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">1.62415432929993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61715054512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64446496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64866721630096</t>
+    <t xml:space="preserve">1.61715066432953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64446485042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64866733551025</t>
   </si>
   <si>
     <t xml:space="preserve">1.48688197135925</t>
@@ -1661,34 +1661,34 @@
     <t xml:space="preserve">1.40143704414368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37356233596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40283787250519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41439390182495</t>
+    <t xml:space="preserve">1.37356245517731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4028377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41439378261566</t>
   </si>
   <si>
     <t xml:space="preserve">1.38602888584137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29638183116913</t>
+    <t xml:space="preserve">1.29638195037842</t>
   </si>
   <si>
     <t xml:space="preserve">1.31108951568604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30520641803741</t>
+    <t xml:space="preserve">1.3052065372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.31136977672577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3166925907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30758762359619</t>
+    <t xml:space="preserve">1.31669247150421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30758774280548</t>
   </si>
   <si>
     <t xml:space="preserve">1.29960358142853</t>
@@ -1697,115 +1697,115 @@
     <t xml:space="preserve">1.22550451755524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20673477649689</t>
+    <t xml:space="preserve">1.2067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">1.16905474662781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14692330360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09229457378387</t>
+    <t xml:space="preserve">1.14692318439484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09229445457458</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134445667267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0897730588913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14440178871155</t>
+    <t xml:space="preserve">1.08977317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14440190792084</t>
   </si>
   <si>
     <t xml:space="preserve">1.16345202922821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1633118391037</t>
+    <t xml:space="preserve">1.16331195831299</t>
   </si>
   <si>
     <t xml:space="preserve">1.19608914852142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23965191841125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21317803859711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22410380840302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25478005409241</t>
+    <t xml:space="preserve">1.23965203762054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2131781578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22410368919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25477993488312</t>
   </si>
   <si>
     <t xml:space="preserve">1.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28139400482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27046823501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26640605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23923182487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2260650396347</t>
+    <t xml:space="preserve">1.28139388561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27046811580658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26640594005585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2392315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22606468200684</t>
   </si>
   <si>
     <t xml:space="preserve">1.22256302833557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26262414455414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19412815570831</t>
+    <t xml:space="preserve">1.26262402534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1941282749176</t>
   </si>
   <si>
     <t xml:space="preserve">1.28517603874207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32341599464417</t>
+    <t xml:space="preserve">1.32341611385345</t>
   </si>
   <si>
     <t xml:space="preserve">1.38770985603333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41194272041321</t>
+    <t xml:space="preserve">1.41194260120392</t>
   </si>
   <si>
     <t xml:space="preserve">1.47392523288727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47147405147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.448361992836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53940963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54571306705475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55796957015991</t>
+    <t xml:space="preserve">1.47147393226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836175441742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53940987586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54571282863617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55796921253204</t>
   </si>
   <si>
     <t xml:space="preserve">1.47917795181274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46376979351044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44801163673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48478090763092</t>
+    <t xml:space="preserve">1.46376991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4480117559433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48478078842163</t>
   </si>
   <si>
     <t xml:space="preserve">1.49913847446442</t>
@@ -1814,37 +1814,37 @@
     <t xml:space="preserve">1.47007322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44345927238464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40458869934082</t>
+    <t xml:space="preserve">1.44345915317535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4045889377594</t>
   </si>
   <si>
     <t xml:space="preserve">1.39401316642761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43155300617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39443325996399</t>
+    <t xml:space="preserve">1.43155288696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39443349838257</t>
   </si>
   <si>
     <t xml:space="preserve">1.35605323314667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32285571098328</t>
+    <t xml:space="preserve">1.32285594940186</t>
   </si>
   <si>
     <t xml:space="preserve">1.39177191257477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37118113040924</t>
+    <t xml:space="preserve">1.37118136882782</t>
   </si>
   <si>
     <t xml:space="preserve">1.43330383300781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44170844554901</t>
+    <t xml:space="preserve">1.44170832633972</t>
   </si>
   <si>
     <t xml:space="preserve">1.41509425640106</t>
@@ -1856,22 +1856,22 @@
     <t xml:space="preserve">1.42454922199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38224697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34918963909149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29344034194946</t>
+    <t xml:space="preserve">1.38224709033966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3491895198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29344022274017</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168041706085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3255170583725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30058419704437</t>
+    <t xml:space="preserve">1.32551717758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30058407783508</t>
   </si>
   <si>
     <t xml:space="preserve">1.29484105110168</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">1.25996267795563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26864731311798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24721598625183</t>
+    <t xml:space="preserve">1.26864743232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24721586704254</t>
   </si>
   <si>
     <t xml:space="preserve">1.27845251560211</t>
@@ -1892,34 +1892,34 @@
     <t xml:space="preserve">1.26206386089325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24917709827423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24525511264801</t>
+    <t xml:space="preserve">1.24917685985565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24525499343872</t>
   </si>
   <si>
     <t xml:space="preserve">1.18474316596985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15182590484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19342756271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21892106533051</t>
+    <t xml:space="preserve">1.1518257856369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1934278011322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">1.2291464805603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20897603034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29400050640106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31851351261139</t>
+    <t xml:space="preserve">1.20897591114044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29400062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3185133934021</t>
   </si>
   <si>
     <t xml:space="preserve">1.31417119503021</t>
@@ -1937,58 +1937,58 @@
     <t xml:space="preserve">1.37706422805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969531536102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32775819301605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147314786911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36011552810669</t>
+    <t xml:space="preserve">1.35969519615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32775831222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31473135948181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3601154088974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40879082679749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47287452220917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49318516254425</t>
+    <t xml:space="preserve">1.47287464141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49318540096283</t>
   </si>
   <si>
     <t xml:space="preserve">1.46412014961243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43505477905273</t>
+    <t xml:space="preserve">1.43505489826202</t>
   </si>
   <si>
     <t xml:space="preserve">1.41544437408447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37566363811493</t>
+    <t xml:space="preserve">1.37566339969635</t>
   </si>
   <si>
     <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35675346851349</t>
+    <t xml:space="preserve">1.35675358772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.34372675418854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4031879901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37720429897308</t>
+    <t xml:space="preserve">1.40318810939789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37720441818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39149188995361</t>
+    <t xml:space="preserve">1.39149177074432</t>
   </si>
   <si>
     <t xml:space="preserve">1.38112652301788</t>
@@ -1997,55 +1997,55 @@
     <t xml:space="preserve">1.32103478908539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30296516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28615653514862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32019448280334</t>
+    <t xml:space="preserve">1.30296528339386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32019436359406</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937816619873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28993844985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824850082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33175051212311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.359414935112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36606848239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36641871929169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36221659183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37587368488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37727451324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37622392177582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43575525283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45956766605377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828268051147</t>
+    <t xml:space="preserve">1.28993856906891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824862003326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33175039291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35941505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36606860160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3664186000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36221647262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37587356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37727439403534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37622380256653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43575501441956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45956778526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828291893005</t>
   </si>
   <si>
     <t xml:space="preserve">1.43855655193329</t>
@@ -2054,22 +2054,22 @@
     <t xml:space="preserve">1.49178469181061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48127913475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44205844402313</t>
+    <t xml:space="preserve">1.48127925395966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44205856323242</t>
   </si>
   <si>
     <t xml:space="preserve">1.38077628612518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532876968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2722190618515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24595534801483</t>
+    <t xml:space="preserve">1.38532865047455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27221918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24595522880554</t>
   </si>
   <si>
     <t xml:space="preserve">1.1997309923172</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">1.19062626361847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19798004627228</t>
+    <t xml:space="preserve">1.19798016548157</t>
   </si>
   <si>
     <t xml:space="preserve">1.24945724010468</t>
@@ -2087,19 +2087,19 @@
     <t xml:space="preserve">1.20918607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19587910175323</t>
+    <t xml:space="preserve">1.19587898254395</t>
   </si>
   <si>
     <t xml:space="preserve">1.18082106113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15525770187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17171633243561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14370167255402</t>
+    <t xml:space="preserve">1.15525758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17171609401703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14370155334473</t>
   </si>
   <si>
     <t xml:space="preserve">1.13914918899536</t>
@@ -2108,40 +2108,40 @@
     <t xml:space="preserve">1.1493045091629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16261160373688</t>
+    <t xml:space="preserve">1.16261148452759</t>
   </si>
   <si>
     <t xml:space="preserve">1.15350675582886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19377791881561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16716396808624</t>
+    <t xml:space="preserve">1.19377779960632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16716384887695</t>
   </si>
   <si>
     <t xml:space="preserve">1.1416003704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18432307243347</t>
+    <t xml:space="preserve">1.18432295322418</t>
   </si>
   <si>
     <t xml:space="preserve">1.19482827186584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16821432113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101585865021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15700852870941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20323300361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25365948677063</t>
+    <t xml:space="preserve">1.16821444034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1710159778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1570086479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20323288440704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25365936756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.24560511112213</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">1.23474943637848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24875688552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26451516151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24105274677277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23825120925903</t>
+    <t xml:space="preserve">1.24875676631927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26451504230499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24105262756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23825132846832</t>
   </si>
   <si>
     <t xml:space="preserve">1.31949400901794</t>
@@ -2171,31 +2171,31 @@
     <t xml:space="preserve">1.36256659030914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36992049217224</t>
+    <t xml:space="preserve">1.36992061138153</t>
   </si>
   <si>
     <t xml:space="preserve">1.33525228500366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32264566421509</t>
+    <t xml:space="preserve">1.32264578342438</t>
   </si>
   <si>
     <t xml:space="preserve">1.33350145816803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33630275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34295642375946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31214022636414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34575772285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32439649105072</t>
+    <t xml:space="preserve">1.33630287647247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34295630455017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31214010715485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3457578420639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32439661026001</t>
   </si>
   <si>
     <t xml:space="preserve">1.31914377212524</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">1.22634506225586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23159766197205</t>
+    <t xml:space="preserve">1.23159778118134</t>
   </si>
   <si>
     <t xml:space="preserve">1.23720073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23124754428864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21163725852966</t>
+    <t xml:space="preserve">1.23124766349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21163737773895</t>
   </si>
   <si>
     <t xml:space="preserve">1.17241668701172</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">1.18222177028656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18817484378815</t>
+    <t xml:space="preserve">1.18817496299744</t>
   </si>
   <si>
     <t xml:space="preserve">1.18467307090759</t>
@@ -2231,49 +2231,49 @@
     <t xml:space="preserve">1.1860738992691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24210333824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26731646060944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15175592899323</t>
+    <t xml:space="preserve">1.24210321903229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26731669902802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15175580978394</t>
   </si>
   <si>
     <t xml:space="preserve">1.13529717922211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18047082424164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1342465877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18012082576752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20603430271149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17521822452545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18992578983307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21583950519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21653974056244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23404896259308</t>
+    <t xml:space="preserve">1.18047094345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13424670696259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18012070655823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20603442192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17521810531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18992590904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21583938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21653985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23404908180237</t>
   </si>
   <si>
     <t xml:space="preserve">1.27467048168182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.286576628685</t>
+    <t xml:space="preserve">1.28657674789429</t>
   </si>
   <si>
     <t xml:space="preserve">1.32579731941223</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">1.26906752586365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30548667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32474672794342</t>
+    <t xml:space="preserve">1.30548655986786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32474684715271</t>
   </si>
   <si>
     <t xml:space="preserve">1.31844353675842</t>
@@ -2306,31 +2306,31 @@
     <t xml:space="preserve">1.34050524234772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36816966533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35066056251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29743254184723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3100391626358</t>
+    <t xml:space="preserve">1.36816954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35066032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29743242263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31003904342651</t>
   </si>
   <si>
     <t xml:space="preserve">1.33980464935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33210074901581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29007863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27081847190857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27537095546722</t>
+    <t xml:space="preserve">1.33210062980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29007852077484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27081835269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27537083625793</t>
   </si>
   <si>
     <t xml:space="preserve">1.28762722015381</t>
@@ -2339,133 +2339,133 @@
     <t xml:space="preserve">1.31249034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32789826393127</t>
+    <t xml:space="preserve">1.32789838314056</t>
   </si>
   <si>
     <t xml:space="preserve">1.28307485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30968880653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42384886741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50929379463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50859344005585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49598670005798</t>
+    <t xml:space="preserve">1.3096889257431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42384874820709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50929367542267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49598681926727</t>
   </si>
   <si>
     <t xml:space="preserve">1.47707688808441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4686723947525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42314851284027</t>
+    <t xml:space="preserve">1.46867251396179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42314863204956</t>
   </si>
   <si>
     <t xml:space="preserve">1.42665040493011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47777736186981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49528658390045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49388563632965</t>
+    <t xml:space="preserve">1.47777724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49528646469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49388575553894</t>
   </si>
   <si>
     <t xml:space="preserve">1.44766128063202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42104732990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264307498932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41754531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41614484786987</t>
+    <t xml:space="preserve">1.42104756832123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41754555702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41614496707916</t>
   </si>
   <si>
     <t xml:space="preserve">1.44135808944702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45536553859711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46517062187195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43085265159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4182460308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38813006877899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3741227388382</t>
+    <t xml:space="preserve">1.45536541938782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46517074108124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43085253238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41824591159821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38813018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37412261962891</t>
   </si>
   <si>
     <t xml:space="preserve">1.41474401950836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40353810787201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40984153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45326459407806</t>
+    <t xml:space="preserve">1.4035382270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4098414182663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45326447486877</t>
   </si>
   <si>
     <t xml:space="preserve">1.42034709453583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36851978302002</t>
+    <t xml:space="preserve">1.36851990222931</t>
   </si>
   <si>
     <t xml:space="preserve">1.37797474861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38637912273407</t>
+    <t xml:space="preserve">1.38637924194336</t>
   </si>
   <si>
     <t xml:space="preserve">1.46166861057281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.425950050354</t>
+    <t xml:space="preserve">1.42594993114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.43435454368591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43365406990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287711143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36886990070343</t>
+    <t xml:space="preserve">1.43365395069122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287734985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36887001991272</t>
   </si>
   <si>
     <t xml:space="preserve">1.39373314380646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36431753635406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29568159580231</t>
+    <t xml:space="preserve">1.36431741714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29568147659302</t>
   </si>
   <si>
     <t xml:space="preserve">1.35836434364319</t>
@@ -2480,37 +2480,37 @@
     <t xml:space="preserve">1.52049970626831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54641330242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72010469436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626069068909</t>
+    <t xml:space="preserve">1.54641318321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72010457515717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626080989838</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884801864624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3012843132019</t>
+    <t xml:space="preserve">1.30128443241119</t>
   </si>
   <si>
     <t xml:space="preserve">1.1423008441925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09397554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05755615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905926465988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861102938652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926937520503998</t>
+    <t xml:space="preserve">1.09397542476654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05755627155304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905926406383514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861102998256683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926937580108643</t>
   </si>
   <si>
     <t xml:space="preserve">0.772156178951263</t>
@@ -2519,52 +2519,52 @@
     <t xml:space="preserve">0.88841724395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818030178546906</t>
+    <t xml:space="preserve">0.818030297756195</t>
   </si>
   <si>
     <t xml:space="preserve">0.874409914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874760031700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885966002941132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877561569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870207548141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926587343215942</t>
+    <t xml:space="preserve">0.874760150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885965943336487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877561628818512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870207667350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926587283611298</t>
   </si>
   <si>
     <t xml:space="preserve">0.912930190563202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925886929035187</t>
+    <t xml:space="preserve">0.925887107849121</t>
   </si>
   <si>
     <t xml:space="preserve">0.880713284015656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849196672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840442180633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633253574371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846044957637787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83098703622818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851297795772552</t>
+    <t xml:space="preserve">0.84919673204422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840442061424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633313179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846044898033142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830986976623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851297616958618</t>
   </si>
   <si>
     <t xml:space="preserve">0.829936504364014</t>
@@ -2576,28 +2576,28 @@
     <t xml:space="preserve">0.820131361484528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77740889787674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778459370136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778809607028961</t>
+    <t xml:space="preserve">0.777408957481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778459429740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778809547424316</t>
   </si>
   <si>
     <t xml:space="preserve">0.753246188163757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751845479011536</t>
+    <t xml:space="preserve">0.75184553861618</t>
   </si>
   <si>
     <t xml:space="preserve">0.771805942058563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743791282176971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768304049968719</t>
+    <t xml:space="preserve">0.743791222572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768304109573364</t>
   </si>
   <si>
     <t xml:space="preserve">0.789665400981903</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">0.809625864028931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779860138893127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766553163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611144542694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776008188724518</t>
+    <t xml:space="preserve">0.779860198497772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766553044319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776008248329163</t>
   </si>
   <si>
     <t xml:space="preserve">0.765152394771576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803672790527344</t>
+    <t xml:space="preserve">0.803672730922699</t>
   </si>
   <si>
     <t xml:space="preserve">0.812077164649963</t>
@@ -2633,28 +2633,28 @@
     <t xml:space="preserve">0.785463213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781260907649994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819080829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759199380874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756047606468201</t>
+    <t xml:space="preserve">0.781260967254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819080770015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759199321269989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756047666072845</t>
   </si>
   <si>
     <t xml:space="preserve">0.730484127998352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.736087203025818</t>
+    <t xml:space="preserve">0.736087143421173</t>
   </si>
   <si>
     <t xml:space="preserve">0.743440985679626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779159784317017</t>
+    <t xml:space="preserve">0.779159724712372</t>
   </si>
   <si>
     <t xml:space="preserve">0.815228760242462</t>
@@ -2663,109 +2663,109 @@
     <t xml:space="preserve">0.805773913860321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858301401138306</t>
+    <t xml:space="preserve">0.858301520347595</t>
   </si>
   <si>
     <t xml:space="preserve">0.872308850288391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89296966791153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931839942932129</t>
+    <t xml:space="preserve">0.892969727516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931840121746063</t>
   </si>
   <si>
     <t xml:space="preserve">0.994873285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00853037834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979115128517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966858565807343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891218721866608</t>
+    <t xml:space="preserve">1.00853061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979114949703217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966858506202698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891218841075897</t>
   </si>
   <si>
     <t xml:space="preserve">0.895070791244507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901724219322205</t>
+    <t xml:space="preserve">0.901724278926849</t>
   </si>
   <si>
     <t xml:space="preserve">0.967908978462219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96440714597702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94689804315567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936392486095428</t>
+    <t xml:space="preserve">0.964407205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946898102760315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936392605304718</t>
   </si>
   <si>
     <t xml:space="preserve">0.938493609428406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965107560157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913980782032013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934641480445862</t>
+    <t xml:space="preserve">0.965107619762421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913980662822723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934641599655151</t>
   </si>
   <si>
     <t xml:space="preserve">0.899623155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953551530838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930089175701141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909078180789948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954602181911469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943746387958527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983317196369171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973161816596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951450288295746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916431963443756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933941185474396</t>
+    <t xml:space="preserve">0.953551590442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930089294910431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909078061580658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954602062702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943746328353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983317255973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97316187620163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95145046710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916432023048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933941304683685</t>
   </si>
   <si>
     <t xml:space="preserve">0.948298692703247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957403600215912</t>
+    <t xml:space="preserve">0.957403540611267</t>
   </si>
   <si>
     <t xml:space="preserve">0.973512053489685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980865895748138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03304326534271</t>
+    <t xml:space="preserve">0.980865836143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.033043384552</t>
   </si>
   <si>
     <t xml:space="preserve">1.03759574890137</t>
@@ -2777,79 +2777,79 @@
     <t xml:space="preserve">0.998725354671478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960905373096466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967208743095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944096684455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89367014169693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890168130397797</t>
+    <t xml:space="preserve">0.960905432701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967208683490753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944096565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893670082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890168249607086</t>
   </si>
   <si>
     <t xml:space="preserve">0.874059796333313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913280308246613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927637934684753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907677412033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890868484973907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915381491184235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978764891624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971060872077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00572907924652</t>
+    <t xml:space="preserve">0.913280427455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927637994289398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907677352428436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890868365764618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91538143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978764832019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971060812473297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00572896003723</t>
   </si>
   <si>
     <t xml:space="preserve">0.997324585914612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98156613111496</t>
+    <t xml:space="preserve">0.981566190719604</t>
   </si>
   <si>
     <t xml:space="preserve">1.00923085212708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986818969249725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987519323825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00712978839874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996624231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999775767326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00467836856842</t>
+    <t xml:space="preserve">0.98681914806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987519383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00712990760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996624171733856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999775826931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00467848777771</t>
   </si>
   <si>
     <t xml:space="preserve">0.988920092582703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985768556594849</t>
+    <t xml:space="preserve">0.985768616199493</t>
   </si>
   <si>
     <t xml:space="preserve">0.970360398292542</t>
@@ -2858,28 +2858,28 @@
     <t xml:space="preserve">0.958103954792023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994523048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978414475917816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986118674278259</t>
+    <t xml:space="preserve">0.994523167610168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978414535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986118614673615</t>
   </si>
   <si>
     <t xml:space="preserve">1.03724551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02148723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01903593540192</t>
+    <t xml:space="preserve">1.02148735523224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01903605461121</t>
   </si>
   <si>
     <t xml:space="preserve">1.01203238964081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995573580265045</t>
+    <t xml:space="preserve">0.995573699474335</t>
   </si>
   <si>
     <t xml:space="preserve">0.973862171173096</t>
@@ -2888,31 +2888,31 @@
     <t xml:space="preserve">0.916782140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922735393047333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888067126274109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939544260501862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961605787277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972811758518219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0540543794632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11113440990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09957838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16121077537537</t>
+    <t xml:space="preserve">0.922735333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888067066669464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939544200897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961605846881866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972811698913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05405426025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09957849979401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16121065616608</t>
   </si>
   <si>
     <t xml:space="preserve">1.185023188591</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">1.16961514949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15910971164703</t>
+    <t xml:space="preserve">1.15910959243774</t>
   </si>
   <si>
     <t xml:space="preserve">1.12339079380035</t>
@@ -2933,28 +2933,28 @@
     <t xml:space="preserve">1.1279433965683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16016018390656</t>
+    <t xml:space="preserve">1.16016006469727</t>
   </si>
   <si>
     <t xml:space="preserve">1.13564729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15280628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17591845989227</t>
+    <t xml:space="preserve">1.17066562175751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545238018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15280640125275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17591857910156</t>
   </si>
   <si>
     <t xml:space="preserve">1.15560781955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13214552402496</t>
+    <t xml:space="preserve">1.13214540481567</t>
   </si>
   <si>
     <t xml:space="preserve">1.08522081375122</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">1.15000486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15210604667664</t>
+    <t xml:space="preserve">1.15210592746735</t>
   </si>
   <si>
     <t xml:space="preserve">1.15490746498108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15455722808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066291332245</t>
+    <t xml:space="preserve">1.15455734729767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066303253174</t>
   </si>
   <si>
     <t xml:space="preserve">1.25120806694031</t>
@@ -2990,37 +2990,37 @@
     <t xml:space="preserve">1.25611054897308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27502059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30793786048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32684791088104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35801434516907</t>
+    <t xml:space="preserve">1.27502071857452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30793797969818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32684779167175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35801446437836</t>
   </si>
   <si>
     <t xml:space="preserve">1.32334613800049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31879365444183</t>
+    <t xml:space="preserve">1.31879377365112</t>
   </si>
   <si>
     <t xml:space="preserve">1.29603159427643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31389105319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30723762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29498112201691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28482580184937</t>
+    <t xml:space="preserve">1.31389117240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30723750591278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29498100280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28482592105865</t>
   </si>
   <si>
     <t xml:space="preserve">1.28027331829071</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">1.26941764354706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24315369129181</t>
+    <t xml:space="preserve">1.24315392971039</t>
   </si>
   <si>
     <t xml:space="preserve">1.25435972213745</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">1.26521551609039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26766669750214</t>
+    <t xml:space="preserve">1.26766657829285</t>
   </si>
   <si>
     <t xml:space="preserve">1.26626598834991</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">1.25821173191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32964932918549</t>
+    <t xml:space="preserve">1.3296492099762</t>
   </si>
   <si>
     <t xml:space="preserve">1.36957049369812</t>
@@ -3071,19 +3071,19 @@
     <t xml:space="preserve">1.34505748748779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34925973415375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33455193042755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31529188156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31809329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31073939800262</t>
+    <t xml:space="preserve">1.34925961494446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33455204963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31529176235199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31809318065643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31073951721191</t>
   </si>
   <si>
     <t xml:space="preserve">1.31774306297302</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">1.28062355518341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24735617637634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26696646213531</t>
+    <t xml:space="preserve">1.24735605716705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26696634292603</t>
   </si>
   <si>
     <t xml:space="preserve">1.25015759468079</t>
@@ -3110,37 +3110,37 @@
     <t xml:space="preserve">1.29953348636627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34820902347565</t>
+    <t xml:space="preserve">1.34820914268494</t>
   </si>
   <si>
     <t xml:space="preserve">1.42174780368805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52260088920593</t>
+    <t xml:space="preserve">1.52260065078735</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190053462982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53240597248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4980880022049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48898315429688</t>
+    <t xml:space="preserve">1.53240621089935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49808776378632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48898327350616</t>
   </si>
   <si>
     <t xml:space="preserve">1.50088953971863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51629734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50789320468903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5197993516922</t>
+    <t xml:space="preserve">1.51629757881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50789332389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51979947090149</t>
   </si>
   <si>
     <t xml:space="preserve">1.54851448535919</t>
@@ -3149,58 +3149,58 @@
     <t xml:space="preserve">1.54361188411713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60594475269318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62695550918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62065231800079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59053647518158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5919371843338</t>
+    <t xml:space="preserve">1.60594463348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62695562839508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62065243721008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59053659439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59193730354309</t>
   </si>
   <si>
     <t xml:space="preserve">1.69909369945526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70119488239288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7236065864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71029937267303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70469677448273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71099996566772</t>
+    <t xml:space="preserve">1.70119476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72360634803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7102997303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70469653606415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71099984645844</t>
   </si>
   <si>
     <t xml:space="preserve">1.74881982803345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70539689064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68998885154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65356969833374</t>
+    <t xml:space="preserve">1.70539712905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68998897075653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65356981754303</t>
   </si>
   <si>
     <t xml:space="preserve">1.63536012172699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64936769008636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63466000556946</t>
+    <t xml:space="preserve">1.64936745166779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63465988636017</t>
   </si>
   <si>
     <t xml:space="preserve">1.62835657596588</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">1.6654759645462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.715052485466</t>
+    <t xml:space="preserve">1.71505236625671</t>
   </si>
   <si>
     <t xml:space="preserve">1.61877369880676</t>
@@ -3218,28 +3218,28 @@
     <t xml:space="preserve">1.59937429428101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6130256652832</t>
+    <t xml:space="preserve">1.61302578449249</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308478355408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65613567829132</t>
+    <t xml:space="preserve">1.65613555908203</t>
   </si>
   <si>
     <t xml:space="preserve">1.67337954044342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71936309337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71289670467377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70283782482147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73445188999176</t>
+    <t xml:space="preserve">1.71936321258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71289706230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70283770561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73445177078247</t>
   </si>
   <si>
     <t xml:space="preserve">1.71145987510681</t>
@@ -3251,208 +3251,208 @@
     <t xml:space="preserve">1.76893961429596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76822113990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81707894802094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83504128456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85587763786316</t>
+    <t xml:space="preserve">1.76822102069855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81707906723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83504116535187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85587799549103</t>
   </si>
   <si>
     <t xml:space="preserve">1.8644996881485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92126083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95934092998505</t>
+    <t xml:space="preserve">1.92126095294952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95934104919434</t>
   </si>
   <si>
     <t xml:space="preserve">1.9729927778244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98377025127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94066047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9650890827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9974217414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02400588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03334617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08579683303833</t>
+    <t xml:space="preserve">1.98377001285553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94066035747528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96508920192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99742162227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02400612831116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03334641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08579659461975</t>
   </si>
   <si>
     <t xml:space="preserve">2.08795213699341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10375952720642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12531399726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13465476036072</t>
+    <t xml:space="preserve">2.10375905036926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12531423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13465452194214</t>
   </si>
   <si>
     <t xml:space="preserve">2.1540539264679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15189838409424</t>
+    <t xml:space="preserve">2.15189814567566</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17201662063599</t>
+    <t xml:space="preserve">2.17201614379883</t>
   </si>
   <si>
     <t xml:space="preserve">2.17991971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17560911178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17632746696472</t>
+    <t xml:space="preserve">2.17560887336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">2.16052055358887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12818789482117</t>
+    <t xml:space="preserve">2.12818813323975</t>
   </si>
   <si>
     <t xml:space="preserve">2.08938932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08076691627502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05346465110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08292317390442</t>
+    <t xml:space="preserve">2.08076739311218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05346417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08292269706726</t>
   </si>
   <si>
     <t xml:space="preserve">2.04771637916565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04196882247925</t>
+    <t xml:space="preserve">2.04196858406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.01897644996643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04053115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98305141925812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96652603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94928228855133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95215618610382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90114295482635</t>
+    <t xml:space="preserve">2.04053139686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9830516576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96652626991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94928240776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9521564245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90114283561707</t>
   </si>
   <si>
     <t xml:space="preserve">1.8328857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93922317028046</t>
+    <t xml:space="preserve">1.93922328948975</t>
   </si>
   <si>
     <t xml:space="preserve">1.93634939193726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91766822338104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88821005821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749158382416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8465371131897</t>
+    <t xml:space="preserve">1.91766846179962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88821029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749182224274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84653723239899</t>
   </si>
   <si>
     <t xml:space="preserve">1.78762030601501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82641923427582</t>
+    <t xml:space="preserve">1.8264194726944</t>
   </si>
   <si>
     <t xml:space="preserve">1.8752772808075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8580334186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90258014202118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87743246555328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89108383655548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82067131996155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81348645687103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82857465744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96724486351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97371137142181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95718574523926</t>
+    <t xml:space="preserve">1.85803318023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90258002281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87743258476257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89108395576477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82067108154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81348633766174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82857477664948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96724450588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97371113300323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95718550682068</t>
   </si>
   <si>
     <t xml:space="preserve">2.03190970420837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00676202774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00388789176941</t>
+    <t xml:space="preserve">2.00676226615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00388813018799</t>
   </si>
   <si>
     <t xml:space="preserve">1.97155570983887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93347537517548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90904641151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94209742546082</t>
+    <t xml:space="preserve">1.93347549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90904653072357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94209730625153</t>
   </si>
   <si>
     <t xml:space="preserve">1.97802233695984</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">2.01107311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99957692623138</t>
+    <t xml:space="preserve">1.99957716464996</t>
   </si>
   <si>
     <t xml:space="preserve">2.01753973960876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03262829780579</t>
+    <t xml:space="preserve">2.03262782096863</t>
   </si>
   <si>
     <t xml:space="preserve">2.03119087219238</t>
@@ -3479,49 +3479,49 @@
     <t xml:space="preserve">2.01322865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945940494537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95000100135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93778645992279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96868169307709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92269814014435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94712674617767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92916452884674</t>
+    <t xml:space="preserve">1.9794590473175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95000088214874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93778657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96868181228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92269790172577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94712662696838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92916429042816</t>
   </si>
   <si>
     <t xml:space="preserve">1.83073043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84078931808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9205424785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9758665561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9234162569046</t>
+    <t xml:space="preserve">1.84078907966614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92054259777069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97586667537689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92341637611389</t>
   </si>
   <si>
     <t xml:space="preserve">1.94353449344635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94425284862518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91838705539703</t>
+    <t xml:space="preserve">1.94425296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91838681697845</t>
   </si>
   <si>
     <t xml:space="preserve">2.02616143226624</t>
@@ -3530,16 +3530,16 @@
     <t xml:space="preserve">2.02831697463989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02185034751892</t>
+    <t xml:space="preserve">2.0218505859375</t>
   </si>
   <si>
     <t xml:space="preserve">2.03047227859497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93994188308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04340553283691</t>
+    <t xml:space="preserve">1.93994200229645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04340529441833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10016679763794</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">2.12315845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1303436756134</t>
+    <t xml:space="preserve">2.13034343719482</t>
   </si>
   <si>
     <t xml:space="preserve">2.14758729934692</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">2.08148574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92988300323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93563055992126</t>
+    <t xml:space="preserve">1.92988288402557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93563103675842</t>
   </si>
   <si>
     <t xml:space="preserve">1.97083735466003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00963568687439</t>
+    <t xml:space="preserve">2.00963592529297</t>
   </si>
   <si>
     <t xml:space="preserve">2.08364129066467</t>
@@ -3587,22 +3587,22 @@
     <t xml:space="preserve">2.00316977500916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9859254360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95143795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042448043823</t>
+    <t xml:space="preserve">1.98592555522919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143783092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042471885681</t>
   </si>
   <si>
     <t xml:space="preserve">1.88318061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8537220954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7459477186203</t>
+    <t xml:space="preserve">1.85372221469879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74594783782959</t>
   </si>
   <si>
     <t xml:space="preserve">1.77540600299835</t>
@@ -3611,31 +3611,31 @@
     <t xml:space="preserve">1.77181363105774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8084568977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8300119638443</t>
+    <t xml:space="preserve">1.80845665931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83001172542572</t>
   </si>
   <si>
     <t xml:space="preserve">1.8853360414505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92557191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8896472454071</t>
+    <t xml:space="preserve">1.92557215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88964712619781</t>
   </si>
   <si>
     <t xml:space="preserve">1.88677299022675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86737358570099</t>
+    <t xml:space="preserve">1.86737382411957</t>
   </si>
   <si>
     <t xml:space="preserve">1.89395785331726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89036560058594</t>
+    <t xml:space="preserve">1.89036548137665</t>
   </si>
   <si>
     <t xml:space="preserve">1.8544408082962</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">1.84797430038452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79767942428589</t>
+    <t xml:space="preserve">1.79767966270447</t>
   </si>
   <si>
     <t xml:space="preserve">1.85659611225128</t>
@@ -3653,19 +3653,19 @@
     <t xml:space="preserve">1.85875165462494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8472558259964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85515940189362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88605463504791</t>
+    <t xml:space="preserve">1.84725606441498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85515928268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88605451583862</t>
   </si>
   <si>
     <t xml:space="preserve">1.89683210849762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97874057292938</t>
+    <t xml:space="preserve">1.97874069213867</t>
   </si>
   <si>
     <t xml:space="preserve">2.0010142326355</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">2.05849385261536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06424164772034</t>
+    <t xml:space="preserve">2.06424188613892</t>
   </si>
   <si>
     <t xml:space="preserve">2.05633854866028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05274605751038</t>
+    <t xml:space="preserve">2.0527458190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.02113199234009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00460648536682</t>
+    <t xml:space="preserve">2.0046067237854</t>
   </si>
   <si>
     <t xml:space="preserve">2.01251006126404</t>
@@ -3701,19 +3701,19 @@
     <t xml:space="preserve">1.99526607990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89970588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87958800792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93131971359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221494674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91192018985748</t>
+    <t xml:space="preserve">1.89970624446869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87958824634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93131983280182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221530437469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91192054748535</t>
   </si>
   <si>
     <t xml:space="preserve">2.02041339874268</t>
@@ -3725,25 +3725,25 @@
     <t xml:space="preserve">2.10447764396667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07645630836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657430648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15118002891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32505631446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32361936569214</t>
+    <t xml:space="preserve">2.07645654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09657406806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15117979049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32505655288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32361912727356</t>
   </si>
   <si>
     <t xml:space="preserve">2.55138301849365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53485727310181</t>
+    <t xml:space="preserve">2.53485774993896</t>
   </si>
   <si>
     <t xml:space="preserve">2.60814428329468</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">2.55928635597229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52767252922058</t>
+    <t xml:space="preserve">2.527672290802</t>
   </si>
   <si>
     <t xml:space="preserve">2.57509326934814</t>
@@ -3767,73 +3767,73 @@
     <t xml:space="preserve">2.41343140602112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21584463119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26398420333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21368956565857</t>
+    <t xml:space="preserve">2.21584510803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26398396492004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21368932723999</t>
   </si>
   <si>
     <t xml:space="preserve">2.06496024131775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120219230652</t>
+    <t xml:space="preserve">1.91120207309723</t>
   </si>
   <si>
     <t xml:space="preserve">1.66475749015808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74954009056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79480528831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575975894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90186154842377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06783437728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96077847480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95862305164337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98879945278168</t>
+    <t xml:space="preserve">1.7495402097702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7948055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90186142921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06783413887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077835559845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9586226940155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98879957199097</t>
   </si>
   <si>
     <t xml:space="preserve">1.95574879646301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359337329865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06208634376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93275678157806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99095523357391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98664426803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784533977509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16626882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12459588050842</t>
+    <t xml:space="preserve">1.95359361171722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06208658218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93275701999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99095511436462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98664438724518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94784545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16626834869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12459564208984</t>
   </si>
   <si>
     <t xml:space="preserve">2.19572687149048</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">2.19860076904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2307755947113</t>
+    <t xml:space="preserve">2.23077535629272</t>
   </si>
   <si>
     <t xml:space="preserve">2.33036375045776</t>
@@ -3857,25 +3857,25 @@
     <t xml:space="preserve">2.36713457107544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32193684577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35104751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31887245178223</t>
+    <t xml:space="preserve">2.321937084198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35104727745056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31887269020081</t>
   </si>
   <si>
     <t xml:space="preserve">2.27597308158875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33572602272034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24839496612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23383951187134</t>
+    <t xml:space="preserve">2.33572626113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24839472770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23383975028992</t>
   </si>
   <si>
     <t xml:space="preserve">2.21085786819458</t>
@@ -3887,16 +3887,16 @@
     <t xml:space="preserve">2.1587655544281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25069308280945</t>
+    <t xml:space="preserve">2.25069332122803</t>
   </si>
   <si>
     <t xml:space="preserve">2.23307371139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2154541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2828676700592</t>
+    <t xml:space="preserve">2.21545433998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28286790847778</t>
   </si>
   <si>
     <t xml:space="preserve">2.26448225975037</t>
@@ -3905,28 +3905,28 @@
     <t xml:space="preserve">2.31351017951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38092374801636</t>
+    <t xml:space="preserve">2.38092398643494</t>
   </si>
   <si>
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45523190498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47285151481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45293354988098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48204398155212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48664045333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46365857124329</t>
+    <t xml:space="preserve">2.45523166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47285127639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45293378829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4820442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4866406917572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46365880966187</t>
   </si>
   <si>
     <t xml:space="preserve">2.47438359260559</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">2.41309857368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43071794509888</t>
+    <t xml:space="preserve">2.43071818351746</t>
   </si>
   <si>
     <t xml:space="preserve">2.37709331512451</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">2.09058618545532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98793363571167</t>
+    <t xml:space="preserve">1.98793339729309</t>
   </si>
   <si>
     <t xml:space="preserve">2.01168155670166</t>
@@ -3953,16 +3953,16 @@
     <t xml:space="preserve">2.08062720298767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02623653411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07832908630371</t>
+    <t xml:space="preserve">2.02623677253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07832884788513</t>
   </si>
   <si>
     <t xml:space="preserve">2.16795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21315574645996</t>
+    <t xml:space="preserve">2.21315598487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.1993670463562</t>
@@ -3971,22 +3971,22 @@
     <t xml:space="preserve">2.13501763343811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20089888572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14267802238464</t>
+    <t xml:space="preserve">2.20089912414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14267826080322</t>
   </si>
   <si>
     <t xml:space="preserve">2.14191222190857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14650845527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03159928321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99406182765961</t>
+    <t xml:space="preserve">2.14650893211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0315990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99406206607819</t>
   </si>
   <si>
     <t xml:space="preserve">1.9029004573822</t>
@@ -3995,70 +3995,70 @@
     <t xml:space="preserve">1.86919379234314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98410332202911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98563516139984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91592347621918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86842751502991</t>
+    <t xml:space="preserve">1.98410308361053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98563539981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91592335700989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8684276342392</t>
   </si>
   <si>
     <t xml:space="preserve">1.83472096920013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73743093013763</t>
+    <t xml:space="preserve">1.73743081092834</t>
   </si>
   <si>
     <t xml:space="preserve">1.7742018699646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83012437820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92435014247894</t>
+    <t xml:space="preserve">1.83012449741364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92435026168823</t>
   </si>
   <si>
     <t xml:space="preserve">1.87915277481079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80331254005432</t>
+    <t xml:space="preserve">1.80331230163574</t>
   </si>
   <si>
     <t xml:space="preserve">1.79718387126923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8538726568222</t>
+    <t xml:space="preserve">1.85387253761292</t>
   </si>
   <si>
     <t xml:space="preserve">1.79641783237457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84544575214386</t>
+    <t xml:space="preserve">1.84544563293457</t>
   </si>
   <si>
     <t xml:space="preserve">1.86306512355804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92894637584686</t>
+    <t xml:space="preserve">1.92894649505615</t>
   </si>
   <si>
     <t xml:space="preserve">1.92052006721497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96954822540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837034225464</t>
+    <t xml:space="preserve">1.96954810619354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837010383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.00095653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.034663438797</t>
+    <t xml:space="preserve">2.03466320037842</t>
   </si>
   <si>
     <t xml:space="preserve">1.98869955539703</t>
@@ -4067,70 +4067,70 @@
     <t xml:space="preserve">1.97184610366821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95652484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99176394939423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07220053672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06530618667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02240633964539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01397967338562</t>
+    <t xml:space="preserve">1.95652496814728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99176383018494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07220029830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06530570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02240610122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01397943496704</t>
   </si>
   <si>
     <t xml:space="preserve">1.94273579120636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87762022018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90826308727264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86076712608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80944097042084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86612951755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89830410480499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90213441848755</t>
+    <t xml:space="preserve">1.87762033939362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90826284885406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86076700687408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80944085121155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86612975597382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8983039855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90213453769684</t>
   </si>
   <si>
     <t xml:space="preserve">1.87149202823639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96878182888031</t>
+    <t xml:space="preserve">1.9687819480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.90060222148895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90673077106476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89907014369965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9971262216568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06070971488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12199449539185</t>
+    <t xml:space="preserve">1.90673089027405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89907038211823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99712646007538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06070947647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12199425697327</t>
   </si>
   <si>
     <t xml:space="preserve">2.08445739746094</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">2.15033888816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19017386436462</t>
+    <t xml:space="preserve">2.19017434120178</t>
   </si>
   <si>
     <t xml:space="preserve">2.21392226219177</t>
@@ -4148,19 +4148,19 @@
     <t xml:space="preserve">2.15799951553345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12965536117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0928840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07143449783325</t>
+    <t xml:space="preserve">2.12965512275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09288430213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07143425941467</t>
   </si>
   <si>
     <t xml:space="preserve">2.02700257301331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06377339363098</t>
+    <t xml:space="preserve">2.06377387046814</t>
   </si>
   <si>
     <t xml:space="preserve">2.1319534778595</t>
@@ -4181,10 +4181,10 @@
     <t xml:space="preserve">2.07986092567444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05151653289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05304908752441</t>
+    <t xml:space="preserve">2.05151677131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05304861068726</t>
   </si>
   <si>
     <t xml:space="preserve">2.11893033981323</t>
@@ -4193,16 +4193,16 @@
     <t xml:space="preserve">2.17485284805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17255449295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17332077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19323825836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22617888450623</t>
+    <t xml:space="preserve">2.17255473136902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17332053184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1932384967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2261791229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.21698641777039</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">2.3173406124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34415292739868</t>
+    <t xml:space="preserve">2.3441526889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.34491896629333</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">2.41922688484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220900535583</t>
+    <t xml:space="preserve">2.44220876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.37785959243774</t>
@@ -4238,25 +4238,25 @@
     <t xml:space="preserve">2.36177229881287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769480705261</t>
+    <t xml:space="preserve">2.41769504547119</t>
   </si>
   <si>
     <t xml:space="preserve">2.45140171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45906233787537</t>
+    <t xml:space="preserve">2.45906209945679</t>
   </si>
   <si>
     <t xml:space="preserve">2.48970484733582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51268649101257</t>
+    <t xml:space="preserve">2.51268672943115</t>
   </si>
   <si>
     <t xml:space="preserve">2.56171464920044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58086633682251</t>
+    <t xml:space="preserve">2.58086609840393</t>
   </si>
   <si>
     <t xml:space="preserve">2.53949904441833</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">2.40390563011169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41080069541931</t>
+    <t xml:space="preserve">2.41080021858215</t>
   </si>
   <si>
     <t xml:space="preserve">2.40313982963562</t>
@@ -4298,19 +4298,19 @@
     <t xml:space="preserve">2.4207592010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51881504058838</t>
+    <t xml:space="preserve">2.51881527900696</t>
   </si>
   <si>
     <t xml:space="preserve">2.50349378585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44527292251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46672296524048</t>
+    <t xml:space="preserve">2.44527316093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817276954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4667227268219</t>
   </si>
   <si>
     <t xml:space="preserve">2.5686092376709</t>
@@ -4322,31 +4322,31 @@
     <t xml:space="preserve">2.57933402061462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58393049240112</t>
+    <t xml:space="preserve">2.58393025398254</t>
   </si>
   <si>
     <t xml:space="preserve">2.56477904319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57703590393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55405402183533</t>
+    <t xml:space="preserve">2.57703614234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55405426025391</t>
   </si>
   <si>
     <t xml:space="preserve">2.62376570701599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67739009857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77774429321289</t>
+    <t xml:space="preserve">2.67739033699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77774453163147</t>
   </si>
   <si>
     <t xml:space="preserve">2.78923559188843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77468061447144</t>
+    <t xml:space="preserve">2.77468013763428</t>
   </si>
   <si>
     <t xml:space="preserve">2.75859308242798</t>
@@ -4364,37 +4364,37 @@
     <t xml:space="preserve">2.94014978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9217643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93172335624695</t>
+    <t xml:space="preserve">2.92176413536072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93172311782837</t>
   </si>
   <si>
     <t xml:space="preserve">2.89725041389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9263608455658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95700335502625</t>
+    <t xml:space="preserve">2.92636060714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95700311660767</t>
   </si>
   <si>
     <t xml:space="preserve">2.99454021453857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00756335258484</t>
+    <t xml:space="preserve">3.00756359100342</t>
   </si>
   <si>
     <t xml:space="preserve">3.07038044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09106421470642</t>
+    <t xml:space="preserve">3.09106397628784</t>
   </si>
   <si>
     <t xml:space="preserve">3.07957315444946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16154193878174</t>
+    <t xml:space="preserve">3.16154170036316</t>
   </si>
   <si>
     <t xml:space="preserve">3.19831323623657</t>
@@ -4406,37 +4406,37 @@
     <t xml:space="preserve">3.22895550727844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2902410030365</t>
+    <t xml:space="preserve">3.29024052619934</t>
   </si>
   <si>
     <t xml:space="preserve">3.22435927391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22052907943726</t>
+    <t xml:space="preserve">3.22052884101868</t>
   </si>
   <si>
     <t xml:space="preserve">3.18145966529846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18682217597961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16767048835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14085841178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19448304176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22282719612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10255527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04280233383179</t>
+    <t xml:space="preserve">3.18682193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16767072677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14085793495178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19448280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22282671928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1025550365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04280209541321</t>
   </si>
   <si>
     <t xml:space="preserve">3.11634421348572</t>
@@ -4451,52 +4451,52 @@
     <t xml:space="preserve">3.16000986099243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16077589988708</t>
+    <t xml:space="preserve">3.16077613830566</t>
   </si>
   <si>
     <t xml:space="preserve">3.11711025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15081739425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22359347343445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18912053108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23355197906494</t>
+    <t xml:space="preserve">3.15081715583801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22359323501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18912029266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23355221748352</t>
   </si>
   <si>
     <t xml:space="preserve">3.17150068283081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07727527618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82830452919006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8811628818512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67585802078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71186280250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70573449134827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80991888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88039708137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80379033088684</t>
+    <t xml:space="preserve">3.07727551460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82830476760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88116312026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67585825920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71186304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70573472976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80991911888123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88039684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80379056930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.71952366828918</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">2.60691261291504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63372445106506</t>
+    <t xml:space="preserve">2.63372468948364</t>
   </si>
   <si>
     <t xml:space="preserve">2.65900468826294</t>
@@ -4514,40 +4514,40 @@
     <t xml:space="preserve">2.75782680511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79996037483215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76165723800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77851057052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75476241111755</t>
+    <t xml:space="preserve">2.79996013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76165699958801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7785108089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75476288795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.82370853424072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83979535102844</t>
+    <t xml:space="preserve">2.8397958278656</t>
   </si>
   <si>
     <t xml:space="preserve">2.84132790565491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83519911766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93019080162048</t>
+    <t xml:space="preserve">2.8351993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93019104003906</t>
   </si>
   <si>
     <t xml:space="preserve">3.01828837394714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08033919334412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11098170280457</t>
+    <t xml:space="preserve">3.0803394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11098194122314</t>
   </si>
   <si>
     <t xml:space="preserve">3.24427676200867</t>
@@ -6294,6 +6294,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.5950002670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1899995803833</t>
   </si>
 </sst>
 </file>
@@ -71736,27 +71739,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.691875</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>6401761</v>
+        <v>4827488</v>
       </c>
       <c r="C2505" t="n">
-        <v>12.8000001907349</v>
+        <v>12.7200002670288</v>
       </c>
       <c r="D2505" t="n">
-        <v>12.4250001907349</v>
+        <v>12.4700002670288</v>
       </c>
       <c r="E2505" t="n">
         <v>12.5</v>
       </c>
       <c r="F2505" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>2066</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>8457821</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>12.4849996566772</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>12.6400003433228</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>6401761</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>12.4250001907349</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F2507" t="n">
         <v>12.5950002670288</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>2093</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6930439815</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>14526149</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>13.3149995803833</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>12.7650003433228</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>12.7950000762939</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>13.1899995803833</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>2094</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="2095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="2096">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20738124847412</t>
+    <t xml:space="preserve">6.2073802947998</t>
   </si>
   <si>
     <t xml:space="preserve">BAMI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25302314758301</t>
+    <t xml:space="preserve">6.25302410125732</t>
   </si>
   <si>
     <t xml:space="preserve">5.98423957824707</t>
@@ -62,46 +62,46 @@
     <t xml:space="preserve">5.65967082977295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89295387268066</t>
+    <t xml:space="preserve">5.89295482635498</t>
   </si>
   <si>
     <t xml:space="preserve">5.274245262146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9420690536499</t>
+    <t xml:space="preserve">4.94206857681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.40450143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85839128494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61496496200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28786087036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55410766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95568299293518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32082462310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57946395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50339317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05204010009766</t>
+    <t xml:space="preserve">4.85839080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61496448516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28785991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55410718917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95568346977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32082366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57946443557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50339365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05204057693481</t>
   </si>
   <si>
     <t xml:space="preserve">4.11289691925049</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">3.87961268424988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52715110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22286796569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5804009437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26851058006287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64379334449768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004204750061</t>
+    <t xml:space="preserve">3.52715134620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22286748886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040118217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26851081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6437931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004085540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.04443264007568</t>
@@ -137,31 +137,31 @@
     <t xml:space="preserve">3.91511297225952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77818512916565</t>
+    <t xml:space="preserve">3.77818560600281</t>
   </si>
   <si>
     <t xml:space="preserve">4.08246850967407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7198646068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64632964134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74775671958923</t>
+    <t xml:space="preserve">3.71986413002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.646329164505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74775648117065</t>
   </si>
   <si>
     <t xml:space="preserve">3.84157752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92018365859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04950475692749</t>
+    <t xml:space="preserve">3.92018389701843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22700262069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04950523376465</t>
   </si>
   <si>
     <t xml:space="preserve">3.88468432426453</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">3.86693429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76043510437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69957804679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03682518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38768792152405</t>
+    <t xml:space="preserve">3.7604353427887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69957852363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03682613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807696342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38768839836121</t>
   </si>
   <si>
     <t xml:space="preserve">3.4713659286499</t>
@@ -194,85 +194,85 @@
     <t xml:space="preserve">3.69197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51447319984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38261651992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2761173248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06565475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365598678589</t>
+    <t xml:space="preserve">3.51447296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38261675834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27611804008484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06565451622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365622520447</t>
   </si>
   <si>
     <t xml:space="preserve">2.70812201499939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49005174636841</t>
+    <t xml:space="preserve">2.49005150794983</t>
   </si>
   <si>
     <t xml:space="preserve">2.40586733818054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2243115901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46672344207764</t>
+    <t xml:space="preserve">2.22431135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46672320365906</t>
   </si>
   <si>
     <t xml:space="preserve">2.72079992294312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.700514793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910977602005</t>
+    <t xml:space="preserve">2.70051455497742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91097712516785</t>
   </si>
   <si>
     <t xml:space="preserve">3.02508354187012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16454672813416</t>
+    <t xml:space="preserve">3.16454696655273</t>
   </si>
   <si>
     <t xml:space="preserve">3.22690272331238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13856601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14116311073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20092058181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2450897693634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11778020858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23469710350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19052886962891</t>
+    <t xml:space="preserve">3.1385657787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20092082023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508929252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11778044700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23469686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19052910804749</t>
   </si>
   <si>
     <t xml:space="preserve">3.32823014259338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20351886749268</t>
+    <t xml:space="preserve">3.20351934432983</t>
   </si>
   <si>
     <t xml:space="preserve">2.96968603134155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75663709640503</t>
+    <t xml:space="preserve">2.75663733482361</t>
   </si>
   <si>
     <t xml:space="preserve">2.86835813522339</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">2.84497451782227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59607172012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51500940322876</t>
+    <t xml:space="preserve">2.59607148170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51500964164734</t>
   </si>
   <si>
     <t xml:space="preserve">2.28637218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32378578186035</t>
+    <t xml:space="preserve">2.32378554344177</t>
   </si>
   <si>
     <t xml:space="preserve">2.32274627685547</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">2.23544836044312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24584078788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22089886665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24480175971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24999785423279</t>
+    <t xml:space="preserve">2.24584126472473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22089910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24480199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24999761581421</t>
   </si>
   <si>
     <t xml:space="preserve">2.2749400138855</t>
@@ -326,31 +326,31 @@
     <t xml:space="preserve">2.47032117843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48902797698975</t>
+    <t xml:space="preserve">2.48902821540833</t>
   </si>
   <si>
     <t xml:space="preserve">2.49422383308411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31131458282471</t>
+    <t xml:space="preserve">2.31131434440613</t>
   </si>
   <si>
     <t xml:space="preserve">2.16581773757935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16685700416565</t>
+    <t xml:space="preserve">2.16685724258423</t>
   </si>
   <si>
     <t xml:space="preserve">2.05461692810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15853548049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2902045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22156834602356</t>
+    <t xml:space="preserve">2.15853524208069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29020428657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22156858444214</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433287620544</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">1.83636605739594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7159024477005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83776664733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07449102401733</t>
+    <t xml:space="preserve">1.71590256690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83776676654816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07449126243591</t>
   </si>
   <si>
     <t xml:space="preserve">2.01846170425415</t>
@@ -377,37 +377,37 @@
     <t xml:space="preserve">2.02546548843384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99324834346771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12211608886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62765598297119</t>
+    <t xml:space="preserve">1.993248462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12211632728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6276558637619</t>
   </si>
   <si>
     <t xml:space="preserve">1.52680313587189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55481791496277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50439143180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50158977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540230751038</t>
+    <t xml:space="preserve">1.55481779575348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50439119338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50158989429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540218830109</t>
   </si>
   <si>
     <t xml:space="preserve">1.45676624774933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40073668956757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31459140777588</t>
+    <t xml:space="preserve">1.40073680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31459128856659</t>
   </si>
   <si>
     <t xml:space="preserve">1.28167414665222</t>
@@ -416,43 +416,43 @@
     <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57022607326508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.666876912117</t>
+    <t xml:space="preserve">1.5702258348465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66687679290771</t>
   </si>
   <si>
     <t xml:space="preserve">1.5562185049057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64166355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66267490386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6878879070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67528116703033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66407513618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72990989685059</t>
+    <t xml:space="preserve">1.64166367053986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66267466545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68788778781891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67528104782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66407525539398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72991001605988</t>
   </si>
   <si>
     <t xml:space="preserve">1.70329570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71730327606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75932538509369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70749795436859</t>
+    <t xml:space="preserve">1.7173033952713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7593252658844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70749819278717</t>
   </si>
   <si>
     <t xml:space="preserve">1.76352751255035</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">1.55201649665833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63045752048492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5996413230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59263741970062</t>
+    <t xml:space="preserve">1.63045740127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59964120388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59263753890991</t>
   </si>
   <si>
     <t xml:space="preserve">1.58143162727356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56882500648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53100526332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52820384502411</t>
+    <t xml:space="preserve">1.56882524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53100538253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52820372581482</t>
   </si>
   <si>
     <t xml:space="preserve">1.4539647102356</t>
@@ -500,19 +500,19 @@
     <t xml:space="preserve">1.53520739078522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51559722423553</t>
+    <t xml:space="preserve">1.51559710502625</t>
   </si>
   <si>
     <t xml:space="preserve">1.56742441654205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56182134151459</t>
+    <t xml:space="preserve">1.56182157993317</t>
   </si>
   <si>
     <t xml:space="preserve">1.60384356975555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68088412284851</t>
+    <t xml:space="preserve">1.6808842420578</t>
   </si>
   <si>
     <t xml:space="preserve">1.63886189460754</t>
@@ -521,10 +521,10 @@
     <t xml:space="preserve">1.65707147121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65847218036652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64306402206421</t>
+    <t xml:space="preserve">1.65847229957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64306426048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.59403848648071</t>
@@ -533,19 +533,19 @@
     <t xml:space="preserve">1.60944652557373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57582902908325</t>
+    <t xml:space="preserve">1.57582879066467</t>
   </si>
   <si>
     <t xml:space="preserve">1.50018906593323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46657145023346</t>
+    <t xml:space="preserve">1.46657133102417</t>
   </si>
   <si>
     <t xml:space="preserve">1.40003633499146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45116317272186</t>
+    <t xml:space="preserve">1.45116329193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.47357511520386</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">1.40633964538574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37832486629486</t>
+    <t xml:space="preserve">1.37832498550415</t>
   </si>
   <si>
     <t xml:space="preserve">1.3965345621109</t>
@@ -566,61 +566,61 @@
     <t xml:space="preserve">1.40774035453796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46797204017639</t>
+    <t xml:space="preserve">1.4679719209671</t>
   </si>
   <si>
     <t xml:space="preserve">1.48057878017426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50299036502838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55061554908752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65286922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78593945503235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79994678497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8461709022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8531745672226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196877479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82235860824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737669467926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86298000812531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92041003704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89379620552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80835103988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67107892036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61224782466888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50999402999878</t>
+    <t xml:space="preserve">1.50299048423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55061566829681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65286946296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78593921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79994666576385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84617102146149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317480564117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196889400482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82235836982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737681388855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86297988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92041027545929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89379596710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80835115909576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67107903957367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61224806308746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50999426841736</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543931484222</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">1.60664510726929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51279580593109</t>
+    <t xml:space="preserve">1.5127956867218</t>
   </si>
   <si>
     <t xml:space="preserve">1.42735075950623</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">1.35451233386993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30408585071564</t>
+    <t xml:space="preserve">1.30408596992493</t>
   </si>
   <si>
     <t xml:space="preserve">1.31178998947144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32649779319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29988372325897</t>
+    <t xml:space="preserve">1.32649767398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29988360404968</t>
   </si>
   <si>
     <t xml:space="preserve">1.31739294528961</t>
@@ -659,19 +659,19 @@
     <t xml:space="preserve">1.30268514156342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35871458053589</t>
+    <t xml:space="preserve">1.35871469974518</t>
   </si>
   <si>
     <t xml:space="preserve">1.39233231544495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28867793083191</t>
+    <t xml:space="preserve">1.28867781162262</t>
   </si>
   <si>
     <t xml:space="preserve">1.40493893623352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49458611011505</t>
+    <t xml:space="preserve">1.49458622932434</t>
   </si>
   <si>
     <t xml:space="preserve">1.64026272296906</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">1.533806681633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67948317527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69769322872162</t>
+    <t xml:space="preserve">1.67948341369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69769287109375</t>
   </si>
   <si>
     <t xml:space="preserve">1.65146863460541</t>
@@ -698,58 +698,58 @@
     <t xml:space="preserve">1.77893567085266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71310126781464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60524427890778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092077255249</t>
+    <t xml:space="preserve">1.71310114860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60524451732635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092089176178</t>
   </si>
   <si>
     <t xml:space="preserve">1.87698721885681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90500175952911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643959522247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03106808662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95122611522675</t>
+    <t xml:space="preserve">1.9050018787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643971443176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0310685634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95122623443604</t>
   </si>
   <si>
     <t xml:space="preserve">1.94982552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90640270709991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94702410697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89799845218658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142138957977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93581795692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01706123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97363829612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02266383171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849883079529</t>
+    <t xml:space="preserve">1.90640258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94702434539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89799833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9414210319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93581831455231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01706099510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97363805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02266407012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849859237671</t>
   </si>
   <si>
     <t xml:space="preserve">2.00585508346558</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">2.02126312255859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86017858982086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8909946680069</t>
+    <t xml:space="preserve">1.86017847061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89099490642548</t>
   </si>
   <si>
     <t xml:space="preserve">1.78033649921417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67388045787811</t>
+    <t xml:space="preserve">1.6738805770874</t>
   </si>
   <si>
     <t xml:space="preserve">1.74251639842987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73831427097321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64586544036865</t>
+    <t xml:space="preserve">1.7383143901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64586555957794</t>
   </si>
   <si>
     <t xml:space="preserve">1.75512325763702</t>
@@ -785,16 +785,16 @@
     <t xml:space="preserve">1.8405681848526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77753496170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78173673152924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68368554115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62205326557159</t>
+    <t xml:space="preserve">1.77753520011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78173732757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68368542194366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6220531463623</t>
   </si>
   <si>
     <t xml:space="preserve">1.51419639587402</t>
@@ -806,34 +806,34 @@
     <t xml:space="preserve">1.71870386600494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71450161933899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68228495121002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69349074363708</t>
+    <t xml:space="preserve">1.71450173854828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68228471279144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6934906244278</t>
   </si>
   <si>
     <t xml:space="preserve">1.69629204273224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8097517490387</t>
+    <t xml:space="preserve">1.80975222587585</t>
   </si>
   <si>
     <t xml:space="preserve">1.81535470485687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76072609424591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80695021152496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8685827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85597634315491</t>
+    <t xml:space="preserve">1.76072597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80695033073425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86858284473419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85597610473633</t>
   </si>
   <si>
     <t xml:space="preserve">1.91620790958405</t>
@@ -842,37 +842,37 @@
     <t xml:space="preserve">1.90780329704285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91480708122253</t>
+    <t xml:space="preserve">1.91480696201324</t>
   </si>
   <si>
     <t xml:space="preserve">1.88539159297943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88819313049316</t>
+    <t xml:space="preserve">1.88819324970245</t>
   </si>
   <si>
     <t xml:space="preserve">1.94562339782715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90360116958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89939916133881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87978887557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86718201637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76212668418884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542848110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8615790605545</t>
+    <t xml:space="preserve">1.90360105037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89939904212952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87978863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86718213558197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76212680339813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9554283618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86157917976379</t>
   </si>
   <si>
     <t xml:space="preserve">1.86998355388641</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">2.00445413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04647612571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91900932788849</t>
+    <t xml:space="preserve">2.04647636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91900956630707</t>
   </si>
   <si>
     <t xml:space="preserve">1.87838792800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98204231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96383309364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88259017467499</t>
+    <t xml:space="preserve">1.98204243183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9638329744339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88259029388428</t>
   </si>
   <si>
     <t xml:space="preserve">1.93021523952484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97784018516541</t>
+    <t xml:space="preserve">1.97784030437469</t>
   </si>
   <si>
     <t xml:space="preserve">2.0941014289856</t>
@@ -917,19 +917,19 @@
     <t xml:space="preserve">2.12491750717163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99464917182922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00305342674255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90220081806183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99885153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95262718200684</t>
+    <t xml:space="preserve">1.9946494102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00305366516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90220046043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99885141849518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95262670516968</t>
   </si>
   <si>
     <t xml:space="preserve">1.95402765274048</t>
@@ -938,61 +938,61 @@
     <t xml:space="preserve">1.93441736698151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90920412540436</t>
+    <t xml:space="preserve">1.90920424461365</t>
   </si>
   <si>
     <t xml:space="preserve">1.91060495376587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88679254055023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95822989940643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94422256946564</t>
+    <t xml:space="preserve">1.88679230213165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95823001861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94422268867493</t>
   </si>
   <si>
     <t xml:space="preserve">1.99184775352478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06048393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207943916321</t>
+    <t xml:space="preserve">2.06048369407654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207920074463</t>
   </si>
   <si>
     <t xml:space="preserve">2.10950970649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14592838287354</t>
+    <t xml:space="preserve">2.14592862129211</t>
   </si>
   <si>
     <t xml:space="preserve">2.0955023765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16974115371704</t>
+    <t xml:space="preserve">2.16974139213562</t>
   </si>
   <si>
     <t xml:space="preserve">2.14452791213989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18795084953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20616030693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20896172523499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19915699958801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19635486602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14172673225403</t>
+    <t xml:space="preserve">2.18795108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20616054534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20896196365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19915676116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19635534286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14172649383545</t>
   </si>
   <si>
     <t xml:space="preserve">2.2033588886261</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">2.19215297698975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15573382377625</t>
+    <t xml:space="preserve">2.15573358535767</t>
   </si>
   <si>
     <t xml:space="preserve">2.16413831710815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16273784637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20756125450134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997307777405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28320074081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34063100814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35884046554565</t>
+    <t xml:space="preserve">2.16273736953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20756101608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997283935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28320097923279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34063124656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35884094238281</t>
   </si>
   <si>
     <t xml:space="preserve">2.33082604408264</t>
@@ -1031,28 +1031,28 @@
     <t xml:space="preserve">2.30561280250549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26499152183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.297208070755</t>
+    <t xml:space="preserve">2.26499128341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29720830917358</t>
   </si>
   <si>
     <t xml:space="preserve">2.30981492996216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27339577674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32242131233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22717142105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26078939437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22016763687134</t>
+    <t xml:space="preserve">2.27339553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32242178916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2271716594696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26078915596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22016787528992</t>
   </si>
   <si>
     <t xml:space="preserve">2.23277449607849</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">2.21036243438721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15993618965149</t>
+    <t xml:space="preserve">2.15993595123291</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10110521316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305205821991</t>
+    <t xml:space="preserve">2.1011049747467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13052082061768</t>
   </si>
   <si>
     <t xml:space="preserve">2.1893515586853</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">2.29300594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30421185493469</t>
+    <t xml:space="preserve">2.30421209335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.30141043663025</t>
@@ -1100,40 +1100,40 @@
     <t xml:space="preserve">2.28180003166199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33642888069153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43448042869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45409083366394</t>
+    <t xml:space="preserve">2.33642911911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43448066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45409107208252</t>
   </si>
   <si>
     <t xml:space="preserve">2.4568920135498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43307971954346</t>
+    <t xml:space="preserve">2.43307995796204</t>
   </si>
   <si>
     <t xml:space="preserve">2.43027830123901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24117875099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17954635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13192129135132</t>
+    <t xml:space="preserve">2.2411789894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17954611778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1319215297699</t>
   </si>
   <si>
     <t xml:space="preserve">2.23417520523071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2047598361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1907525062561</t>
+    <t xml:space="preserve">2.20475959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19075226783752</t>
   </si>
   <si>
     <t xml:space="preserve">2.15153169631958</t>
@@ -1142,61 +1142,61 @@
     <t xml:space="preserve">2.20195817947388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.183748960495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21456503868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17674493789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16834044456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09690284729004</t>
+    <t xml:space="preserve">2.18374848365784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21456480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17674469947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1683406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09690260887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.1025059223175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13332200050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10810852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09130024909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0450758934021</t>
+    <t xml:space="preserve">2.1333224773407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10810875892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09130001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04507541656494</t>
   </si>
   <si>
     <t xml:space="preserve">1.9708366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9120055437088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9274138212204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88959360122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87558662891388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566004753113</t>
+    <t xml:space="preserve">1.91200578212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92741370201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88959395885468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87558627128601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566028594971</t>
   </si>
   <si>
     <t xml:space="preserve">1.97924101352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96943581104279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92321169376373</t>
+    <t xml:space="preserve">1.9694356918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92321157455444</t>
   </si>
   <si>
     <t xml:space="preserve">1.96523368358612</t>
@@ -1205,43 +1205,43 @@
     <t xml:space="preserve">1.92181086540222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83496499061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76492834091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75232183933258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77193188667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78313791751862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8265608549118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86438059806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177421569824</t>
+    <t xml:space="preserve">1.83496522903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76492810249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75232172012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77193200588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78313803672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82656073570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86438071727753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177385807037</t>
   </si>
   <si>
     <t xml:space="preserve">1.81395399570465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86578118801117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84897267818451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88399088382721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99745070934296</t>
+    <t xml:space="preserve">1.86578142642975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84897243976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88399112224579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99745047092438</t>
   </si>
   <si>
     <t xml:space="preserve">2.04787707328796</t>
@@ -1250,46 +1250,46 @@
     <t xml:space="preserve">2.04367470741272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99604964256287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08429622650146</t>
+    <t xml:space="preserve">1.99604988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08429646492004</t>
   </si>
   <si>
     <t xml:space="preserve">2.11931467056274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15013074874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17114186286926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18725037574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12701845169067</t>
+    <t xml:space="preserve">2.15013098716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17114210128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18725061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12701869010925</t>
   </si>
   <si>
     <t xml:space="preserve">2.14557862281799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10355663299561</t>
+    <t xml:space="preserve">2.10355615615845</t>
   </si>
   <si>
     <t xml:space="preserve">2.10320615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0282666683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04927825927734</t>
+    <t xml:space="preserve">2.02826690673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04927778244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.15363264083862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16028618812561</t>
+    <t xml:space="preserve">2.16028642654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.10600757598877</t>
@@ -1298,40 +1298,40 @@
     <t xml:space="preserve">2.03772163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1172137260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0800940990448</t>
+    <t xml:space="preserve">2.11721348762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08009386062622</t>
   </si>
   <si>
     <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12736892700195</t>
+    <t xml:space="preserve">2.12736868858337</t>
   </si>
   <si>
     <t xml:space="preserve">2.1525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18584990501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14207649230957</t>
+    <t xml:space="preserve">2.18584966659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14207696914673</t>
   </si>
   <si>
     <t xml:space="preserve">2.19425415992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19005179405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20300889015198</t>
+    <t xml:space="preserve">2.19005227088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2030086517334</t>
   </si>
   <si>
     <t xml:space="preserve">2.17604446411133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1886510848999</t>
+    <t xml:space="preserve">2.18865132331848</t>
   </si>
   <si>
     <t xml:space="preserve">2.01005721092224</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">2.12771916389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07624220848083</t>
+    <t xml:space="preserve">2.07624197006226</t>
   </si>
   <si>
     <t xml:space="preserve">2.06643676757812</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">2.11441230773926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08394622802734</t>
+    <t xml:space="preserve">2.08394646644592</t>
   </si>
   <si>
     <t xml:space="preserve">2.13822460174561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12036538124084</t>
+    <t xml:space="preserve">2.12036514282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.12071537971497</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">1.9634827375412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98274278640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98729526996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96838510036469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94107115268707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03421998023987</t>
+    <t xml:space="preserve">1.98274290561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98729538917542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293782234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96838521957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94107091426849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03422021865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.00620532035828</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">2.01601028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03491997718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10915899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10775852203369</t>
+    <t xml:space="preserve">2.03492045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10915946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10775899887085</t>
   </si>
   <si>
     <t xml:space="preserve">2.14382767677307</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">2.13857483863831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14487791061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08289527893066</t>
+    <t xml:space="preserve">2.14487814903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08289551734924</t>
   </si>
   <si>
     <t xml:space="preserve">2.14347743988037</t>
@@ -1436,70 +1436,70 @@
     <t xml:space="preserve">2.09970426559448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8608785867691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87523627281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84442031383514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82165837287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5768791437149</t>
+    <t xml:space="preserve">1.86087882518768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8752361536026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84442019462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82165813446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57687950134277</t>
   </si>
   <si>
     <t xml:space="preserve">1.47077357769012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51839864253998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55446755886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578696250916</t>
+    <t xml:space="preserve">1.51839852333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55446767807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578660488129</t>
   </si>
   <si>
     <t xml:space="preserve">1.63641059398651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59648966789246</t>
+    <t xml:space="preserve">1.59648978710175</t>
   </si>
   <si>
     <t xml:space="preserve">1.68018364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61259829998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71170032024384</t>
+    <t xml:space="preserve">1.61259806156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71170020103455</t>
   </si>
   <si>
     <t xml:space="preserve">1.69874322414398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7246572971344</t>
+    <t xml:space="preserve">1.72465717792511</t>
   </si>
   <si>
     <t xml:space="preserve">1.69138967990875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67808270454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81990730762482</t>
+    <t xml:space="preserve">1.67808258533478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81990718841553</t>
   </si>
   <si>
     <t xml:space="preserve">1.78804039955139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8479220867157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780686378479</t>
+    <t xml:space="preserve">1.84792184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068673610687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73481237888336</t>
@@ -1508,88 +1508,88 @@
     <t xml:space="preserve">1.70364582538605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77403283119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80589962005615</t>
+    <t xml:space="preserve">1.7740330696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80589997768402</t>
   </si>
   <si>
     <t xml:space="preserve">1.8258603811264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87173461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87243461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823284626007</t>
+    <t xml:space="preserve">1.87173438072205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274573326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87243485450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823260784149</t>
   </si>
   <si>
     <t xml:space="preserve">1.85912811756134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8328640460968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81605517864227</t>
+    <t xml:space="preserve">1.83286416530609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81605505943298</t>
   </si>
   <si>
     <t xml:space="preserve">1.85072326660156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83601582050323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85807728767395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85387516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76807987689972</t>
+    <t xml:space="preserve">1.83601593971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85807740688324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85387492179871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76807975769043</t>
   </si>
   <si>
     <t xml:space="preserve">1.7533723115921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64901745319366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64621603488922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337478160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65216886997223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61960184574127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57092642784119</t>
+    <t xml:space="preserve">1.64901733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64621591567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65216898918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61960172653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57092618942261</t>
   </si>
   <si>
     <t xml:space="preserve">1.53030478954315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4697231054306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42630004882812</t>
+    <t xml:space="preserve">1.46972322463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4263002872467</t>
   </si>
   <si>
     <t xml:space="preserve">1.42524969577789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45501530170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44380939006805</t>
+    <t xml:space="preserve">1.4550154209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44380950927734</t>
   </si>
   <si>
     <t xml:space="preserve">1.43190312385559</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">1.43925702571869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40704023838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120288848877</t>
+    <t xml:space="preserve">1.40704011917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120276927948</t>
   </si>
   <si>
     <t xml:space="preserve">1.40178716182709</t>
@@ -1613,22 +1613,22 @@
     <t xml:space="preserve">1.358154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37132132053375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50719261169434</t>
+    <t xml:space="preserve">1.37132108211517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50719273090363</t>
   </si>
   <si>
     <t xml:space="preserve">1.49493622779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54326188564301</t>
+    <t xml:space="preserve">1.54326152801514</t>
   </si>
   <si>
     <t xml:space="preserve">1.5355578660965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55026531219482</t>
+    <t xml:space="preserve">1.5502655506134</t>
   </si>
   <si>
     <t xml:space="preserve">1.61084723472595</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">1.61539959907532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61609983444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62625539302826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62415432929993</t>
+    <t xml:space="preserve">1.61609995365143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62625551223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62415421009064</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715066432953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64446485042572</t>
+    <t xml:space="preserve">1.64446496963501</t>
   </si>
   <si>
     <t xml:space="preserve">1.64866733551025</t>
@@ -1658,34 +1658,34 @@
     <t xml:space="preserve">1.48688197135925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40143704414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37356245517731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4028377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41439378261566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38602888584137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29638195037842</t>
+    <t xml:space="preserve">1.40143716335297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37356233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40283787250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41439414024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38602900505066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29638171195984</t>
   </si>
   <si>
     <t xml:space="preserve">1.31108951568604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3052065372467</t>
+    <t xml:space="preserve">1.30520641803741</t>
   </si>
   <si>
     <t xml:space="preserve">1.31136977672577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31669247150421</t>
+    <t xml:space="preserve">1.3166925907135</t>
   </si>
   <si>
     <t xml:space="preserve">1.30758774280548</t>
@@ -1694,28 +1694,28 @@
     <t xml:space="preserve">1.29960358142853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22550451755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2067346572876</t>
+    <t xml:space="preserve">1.22550463676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20673477649689</t>
   </si>
   <si>
     <t xml:space="preserve">1.16905474662781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14692318439484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09229445457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134445667267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08977317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14440190792084</t>
+    <t xml:space="preserve">1.14692330360413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09229457378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134457588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0897730588913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14440178871155</t>
   </si>
   <si>
     <t xml:space="preserve">1.16345202922821</t>
@@ -1724,46 +1724,46 @@
     <t xml:space="preserve">1.16331195831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19608914852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23965203762054</t>
+    <t xml:space="preserve">1.19608902931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23965191841125</t>
   </si>
   <si>
     <t xml:space="preserve">1.2131781578064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22410368919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25477993488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28139388561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27046811580658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26640594005585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2392315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22606468200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256302833557</t>
+    <t xml:space="preserve">1.22410380840302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25478005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29217970371246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28139400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27046823501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26640605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23923182487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22606480121613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256290912628</t>
   </si>
   <si>
     <t xml:space="preserve">1.26262402534485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1941282749176</t>
+    <t xml:space="preserve">1.19412815570831</t>
   </si>
   <si>
     <t xml:space="preserve">1.28517603874207</t>
@@ -1775,49 +1775,49 @@
     <t xml:space="preserve">1.38770985603333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41194260120392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47392523288727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147393226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836175441742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53940987586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54571282863617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55796921253204</t>
+    <t xml:space="preserve">1.41194272041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47392535209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147405147552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836187362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53940975666046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54571306705475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55796933174133</t>
   </si>
   <si>
     <t xml:space="preserve">1.47917795181274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46376991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4480117559433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48478078842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49913847446442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47007322311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44345915317535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4045889377594</t>
+    <t xml:space="preserve">1.46376979351044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44801151752472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48478090763092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49913859367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47007310390472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44345939159393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40458881855011</t>
   </si>
   <si>
     <t xml:space="preserve">1.39401316642761</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">1.39443349838257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35605323314667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32285594940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39177191257477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37118136882782</t>
+    <t xml:space="preserve">1.35605335235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32285583019257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39177215099335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37118113040924</t>
   </si>
   <si>
     <t xml:space="preserve">1.43330383300781</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">1.42454922199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38224709033966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3491895198822</t>
+    <t xml:space="preserve">1.38224697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34918963909149</t>
   </si>
   <si>
     <t xml:space="preserve">1.29344022274017</t>
@@ -1874,25 +1874,25 @@
     <t xml:space="preserve">1.30058407783508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29484105110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25996267795563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26864743232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24721586704254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845251560211</t>
+    <t xml:space="preserve">1.2948409318924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25996279716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26864719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24721598625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845239639282</t>
   </si>
   <si>
     <t xml:space="preserve">1.26206386089325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24917685985565</t>
+    <t xml:space="preserve">1.24917709827423</t>
   </si>
   <si>
     <t xml:space="preserve">1.24525499343872</t>
@@ -1901,28 +1901,28 @@
     <t xml:space="preserve">1.18474316596985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1518257856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1934278011322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21892118453979</t>
+    <t xml:space="preserve">1.15182590484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19342768192291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21892106533051</t>
   </si>
   <si>
     <t xml:space="preserve">1.2291464805603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20897591114044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3185133934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31417119503021</t>
+    <t xml:space="preserve">1.20897579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29400050640106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31851363182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3141713142395</t>
   </si>
   <si>
     <t xml:space="preserve">1.2770516872406</t>
@@ -1934,19 +1934,19 @@
     <t xml:space="preserve">1.3850485086441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37706422805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969519615173</t>
+    <t xml:space="preserve">1.37706410884857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969531536102</t>
   </si>
   <si>
     <t xml:space="preserve">1.32775831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31473135948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3601154088974</t>
+    <t xml:space="preserve">1.31473159790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36011552810669</t>
   </si>
   <si>
     <t xml:space="preserve">1.40879082679749</t>
@@ -1964,58 +1964,58 @@
     <t xml:space="preserve">1.43505489826202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41544437408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37566339969635</t>
+    <t xml:space="preserve">1.41544449329376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37566363811493</t>
   </si>
   <si>
     <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35675358772278</t>
+    <t xml:space="preserve">1.35675370693207</t>
   </si>
   <si>
     <t xml:space="preserve">1.34372675418854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40318810939789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37720441818237</t>
+    <t xml:space="preserve">1.4031879901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37720429897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39149177074432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38112652301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32103478908539</t>
+    <t xml:space="preserve">1.39149188995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38112640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3210346698761</t>
   </si>
   <si>
     <t xml:space="preserve">1.30296528339386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28615665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32019436359406</t>
+    <t xml:space="preserve">1.28615653514862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32019448280334</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937816619873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28993856906891</t>
+    <t xml:space="preserve">1.28993833065033</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824862003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33175039291382</t>
+    <t xml:space="preserve">1.33175051212311</t>
   </si>
   <si>
     <t xml:space="preserve">1.35941505432129</t>
@@ -2024,28 +2024,28 @@
     <t xml:space="preserve">1.36606860160828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3664186000824</t>
+    <t xml:space="preserve">1.36641848087311</t>
   </si>
   <si>
     <t xml:space="preserve">1.36221647262573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37587356567383</t>
+    <t xml:space="preserve">1.37587368488312</t>
   </si>
   <si>
     <t xml:space="preserve">1.37727439403534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37622380256653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43575501441956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45956778526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828291893005</t>
+    <t xml:space="preserve">1.37622392177582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43575513362885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45956766605377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828279972076</t>
   </si>
   <si>
     <t xml:space="preserve">1.43855655193329</t>
@@ -2060,19 +2060,19 @@
     <t xml:space="preserve">1.44205856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38077628612518</t>
+    <t xml:space="preserve">1.38077616691589</t>
   </si>
   <si>
     <t xml:space="preserve">1.38532865047455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27221918106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24595522880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1997309923172</t>
+    <t xml:space="preserve">1.27221894264221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24595546722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19973111152649</t>
   </si>
   <si>
     <t xml:space="preserve">1.19062626361847</t>
@@ -2087,97 +2087,97 @@
     <t xml:space="preserve">1.20918607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19587898254395</t>
+    <t xml:space="preserve">1.19587910175323</t>
   </si>
   <si>
     <t xml:space="preserve">1.18082106113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15525758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17171609401703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14370155334473</t>
+    <t xml:space="preserve">1.15525770187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17171633243561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14370143413544</t>
   </si>
   <si>
     <t xml:space="preserve">1.13914918899536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1493045091629</t>
+    <t xml:space="preserve">1.14930462837219</t>
   </si>
   <si>
     <t xml:space="preserve">1.16261148452759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15350675582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19377779960632</t>
+    <t xml:space="preserve">1.15350663661957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19377791881561</t>
   </si>
   <si>
     <t xml:space="preserve">1.16716384887695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1416003704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18432295322418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19482827186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16821444034576</t>
+    <t xml:space="preserve">1.14160048961639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18432283401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19482851028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16821455955505</t>
   </si>
   <si>
     <t xml:space="preserve">1.1710159778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1570086479187</t>
+    <t xml:space="preserve">1.15700840950012</t>
   </si>
   <si>
     <t xml:space="preserve">1.20323288440704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25365936756134</t>
+    <t xml:space="preserve">1.25365924835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.24560511112213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23790121078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23474943637848</t>
+    <t xml:space="preserve">1.23790109157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23474955558777</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875676631927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451504230499</t>
+    <t xml:space="preserve">1.26451516151428</t>
   </si>
   <si>
     <t xml:space="preserve">1.24105262756348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23825132846832</t>
+    <t xml:space="preserve">1.23825120925903</t>
   </si>
   <si>
     <t xml:space="preserve">1.31949400901794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36256659030914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36992061138153</t>
+    <t xml:space="preserve">1.36256682872772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36992049217224</t>
   </si>
   <si>
     <t xml:space="preserve">1.33525228500366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32264578342438</t>
+    <t xml:space="preserve">1.32264566421509</t>
   </si>
   <si>
     <t xml:space="preserve">1.33350145816803</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">1.34295630455017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31214010715485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3457578420639</t>
+    <t xml:space="preserve">1.31214022636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34575772285461</t>
   </si>
   <si>
     <t xml:space="preserve">1.32439661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914377212524</t>
+    <t xml:space="preserve">1.31914389133453</t>
   </si>
   <si>
     <t xml:space="preserve">1.22634506225586</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">1.23159778118134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23720073699951</t>
+    <t xml:space="preserve">1.2372008562088</t>
   </si>
   <si>
     <t xml:space="preserve">1.23124766349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163737773895</t>
+    <t xml:space="preserve">1.21163725852966</t>
   </si>
   <si>
     <t xml:space="preserve">1.17241668701172</t>
@@ -2225,37 +2225,37 @@
     <t xml:space="preserve">1.18817496299744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18467307090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1860738992691</t>
+    <t xml:space="preserve">1.1846729516983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18607378005981</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210321903229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26731669902802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15175580978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13529717922211</t>
+    <t xml:space="preserve">1.26731646060944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15175592899323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13529706001282</t>
   </si>
   <si>
     <t xml:space="preserve">1.18047094345093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13424670696259</t>
+    <t xml:space="preserve">1.13424646854401</t>
   </si>
   <si>
     <t xml:space="preserve">1.18012070655823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20603442192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17521810531616</t>
+    <t xml:space="preserve">1.20603430271149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17521822452545</t>
   </si>
   <si>
     <t xml:space="preserve">1.18992590904236</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">1.21583938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21653985977173</t>
+    <t xml:space="preserve">1.21653997898102</t>
   </si>
   <si>
     <t xml:space="preserve">1.23404908180237</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">1.32579731941223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28132390975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27186894416809</t>
+    <t xml:space="preserve">1.28132379055023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27186906337738</t>
   </si>
   <si>
     <t xml:space="preserve">1.26906752586365</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">1.30548655986786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32474684715271</t>
+    <t xml:space="preserve">1.32474672794342</t>
   </si>
   <si>
     <t xml:space="preserve">1.31844353675842</t>
@@ -2300,82 +2300,82 @@
     <t xml:space="preserve">1.35171091556549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31424117088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34050524234772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36816954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35066032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29743242263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31003904342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33980464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33210062980652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29007852077484</t>
+    <t xml:space="preserve">1.31424129009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34050512313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3681697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35066044330597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29743230342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31003892421722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33980476856232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33210074901581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29007863998413</t>
   </si>
   <si>
     <t xml:space="preserve">1.27081835269928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27537083625793</t>
+    <t xml:space="preserve">1.27537095546722</t>
   </si>
   <si>
     <t xml:space="preserve">1.28762722015381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31249034404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32789838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28307485580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3096889257431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42384874820709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50929367542267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50859355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49598681926727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47707688808441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46867251396179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42314863204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42665040493011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47777724266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49528646469116</t>
+    <t xml:space="preserve">1.31249022483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32789850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28307497501373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30968880653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42384898662567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50929379463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50859367847443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49598670005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47707676887512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4686723947525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42314851284027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42665028572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47777712345123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49528634548187</t>
   </si>
   <si>
     <t xml:space="preserve">1.49388575553894</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">1.44766128063202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42104756832123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264295578003</t>
+    <t xml:space="preserve">1.42104744911194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264283657074</t>
   </si>
   <si>
     <t xml:space="preserve">1.41754555702209</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">1.41614496707916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44135808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536541938782</t>
+    <t xml:space="preserve">1.44135820865631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4553656578064</t>
   </si>
   <si>
     <t xml:space="preserve">1.46517074108124</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">1.41824591159821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38813018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37412261962891</t>
+    <t xml:space="preserve">1.38813030719757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37412285804749</t>
   </si>
   <si>
     <t xml:space="preserve">1.41474401950836</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">1.4098414182663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45326447486877</t>
+    <t xml:space="preserve">1.45326459407806</t>
   </si>
   <si>
     <t xml:space="preserve">1.42034709453583</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">1.38637924194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46166861057281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42594993114471</t>
+    <t xml:space="preserve">1.4616687297821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42595016956329</t>
   </si>
   <si>
     <t xml:space="preserve">1.43435454368591</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">1.43365395069122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38287734985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36887001991272</t>
+    <t xml:space="preserve">1.38287711143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36886990070343</t>
   </si>
   <si>
     <t xml:space="preserve">1.39373314380646</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">1.36431741714478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29568147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35836434364319</t>
+    <t xml:space="preserve">1.29568135738373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35836446285248</t>
   </si>
   <si>
     <t xml:space="preserve">1.37307226657867</t>
@@ -2477,121 +2477,121 @@
     <t xml:space="preserve">1.46727180480957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52049970626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54641318321228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72010457515717</t>
+    <t xml:space="preserve">1.5204998254776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54641330242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72010493278503</t>
   </si>
   <si>
     <t xml:space="preserve">1.44626080989838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3884801864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30128443241119</t>
+    <t xml:space="preserve">1.38848030567169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128455162048</t>
   </si>
   <si>
     <t xml:space="preserve">1.1423008441925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09397542476654</t>
+    <t xml:space="preserve">1.09397554397583</t>
   </si>
   <si>
     <t xml:space="preserve">1.05755627155304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905926406383514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861102998256683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926937580108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772156178951263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88841724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818030297756195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874409914016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874760150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885965943336487</t>
+    <t xml:space="preserve">0.905926525592804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861103057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926937460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772156059741974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888417363166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81803023815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874409973621368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874760091304779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885966002941132</t>
   </si>
   <si>
     <t xml:space="preserve">0.877561628818512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870207667350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926587283611298</t>
+    <t xml:space="preserve">0.870207726955414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926587402820587</t>
   </si>
   <si>
     <t xml:space="preserve">0.912930190563202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925887107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880713284015656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84919673204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840442061424255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633313179016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846044898033142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830986976623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851297616958618</t>
+    <t xml:space="preserve">0.925886929035187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880713224411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84919661283493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8404421210289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633134365082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846044957637787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830987095832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851297736167908</t>
   </si>
   <si>
     <t xml:space="preserve">0.829936504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853048741817474</t>
+    <t xml:space="preserve">0.853048801422119</t>
   </si>
   <si>
     <t xml:space="preserve">0.820131361484528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777408957481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778459429740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778809547424316</t>
+    <t xml:space="preserve">0.77740889787674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778459548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778809607028961</t>
   </si>
   <si>
     <t xml:space="preserve">0.753246188163757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75184553861618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771805942058563</t>
+    <t xml:space="preserve">0.751845479011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771805882453918</t>
   </si>
   <si>
     <t xml:space="preserve">0.743791222572327</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">0.768304109573364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789665400981903</t>
+    <t xml:space="preserve">0.789665341377258</t>
   </si>
   <si>
     <t xml:space="preserve">0.809625864028931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779860198497772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766553044319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611204147339</t>
+    <t xml:space="preserve">0.779860138893127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766553103923798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611084938049</t>
   </si>
   <si>
     <t xml:space="preserve">0.776008248329163</t>
@@ -2621,55 +2621,55 @@
     <t xml:space="preserve">0.765152394771576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803672730922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812077164649963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807874858379364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785463213920593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781260967254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819080770015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759199321269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756047666072845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730484127998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736087143421173</t>
+    <t xml:space="preserve">0.803672790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812077105045319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807874917984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785463094711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781260907649994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819080829620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759199261665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75604772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730484187602997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736087203025818</t>
   </si>
   <si>
     <t xml:space="preserve">0.743440985679626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779159724712372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815228760242462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805773913860321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858301520347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872308850288391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892969727516174</t>
+    <t xml:space="preserve">0.779159784317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815228700637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805773854255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858301401138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872308731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892969608306885</t>
   </si>
   <si>
     <t xml:space="preserve">0.931840121746063</t>
@@ -2678,34 +2678,34 @@
     <t xml:space="preserve">0.994873285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00853061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979114949703217</t>
+    <t xml:space="preserve">1.00853049755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979115009307861</t>
   </si>
   <si>
     <t xml:space="preserve">0.966858506202698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891218841075897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895070791244507</t>
+    <t xml:space="preserve">0.891218781471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895070731639862</t>
   </si>
   <si>
     <t xml:space="preserve">0.901724278926849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967908978462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964407205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946898102760315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936392605304718</t>
+    <t xml:space="preserve">0.967909157276154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964407324790955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946897983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936392486095428</t>
   </si>
   <si>
     <t xml:space="preserve">0.938493609428406</t>
@@ -2714,67 +2714,67 @@
     <t xml:space="preserve">0.965107619762421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913980662822723</t>
+    <t xml:space="preserve">0.913980782032013</t>
   </si>
   <si>
     <t xml:space="preserve">0.934641599655151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899623155593872</t>
+    <t xml:space="preserve">0.899623095989227</t>
   </si>
   <si>
     <t xml:space="preserve">0.953551590442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930089294910431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909078061580658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954602062702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943746328353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983317255973816</t>
+    <t xml:space="preserve">0.930089235305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909078121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954602122306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943746447563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983317196369171</t>
   </si>
   <si>
     <t xml:space="preserve">0.97316187620163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95145046710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916432023048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933941304683685</t>
+    <t xml:space="preserve">0.951450407505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916432082653046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933941245079041</t>
   </si>
   <si>
     <t xml:space="preserve">0.948298692703247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957403540611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973512053489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980865836143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.033043384552</t>
+    <t xml:space="preserve">0.957403481006622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973512172698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980866014957428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03304326534271</t>
   </si>
   <si>
     <t xml:space="preserve">1.03759574890137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00012600421906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998725354671478</t>
+    <t xml:space="preserve">1.00012612342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998725235462189</t>
   </si>
   <si>
     <t xml:space="preserve">0.960905432701111</t>
@@ -2783,34 +2783,34 @@
     <t xml:space="preserve">0.967208683490753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944096565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893670082092285</t>
+    <t xml:space="preserve">0.944096624851227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89367002248764</t>
   </si>
   <si>
     <t xml:space="preserve">0.890168249607086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874059796333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913280427455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927637994289398</t>
+    <t xml:space="preserve">0.874059677124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913280367851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927637875080109</t>
   </si>
   <si>
     <t xml:space="preserve">0.907677352428436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890868365764618</t>
+    <t xml:space="preserve">0.890868663787842</t>
   </si>
   <si>
     <t xml:space="preserve">0.91538143157959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978764832019806</t>
+    <t xml:space="preserve">0.978764772415161</t>
   </si>
   <si>
     <t xml:space="preserve">0.971060812473297</t>
@@ -2819,100 +2819,100 @@
     <t xml:space="preserve">1.00572896003723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997324585914612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981566190719604</t>
+    <t xml:space="preserve">0.997324705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981566250324249</t>
   </si>
   <si>
     <t xml:space="preserve">1.00923085212708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98681914806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987519383430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00712990760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996624171733856</t>
+    <t xml:space="preserve">0.98681902885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987519502639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00712966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996624231338501</t>
   </si>
   <si>
     <t xml:space="preserve">0.999775826931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00467848777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988920092582703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985768616199493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970360398292542</t>
+    <t xml:space="preserve">1.00467824935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988920152187347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985768556594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970360338687897</t>
   </si>
   <si>
     <t xml:space="preserve">0.958103954792023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994523167610168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978414535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986118614673615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03724551200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02148735523224</t>
+    <t xml:space="preserve">0.994523048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97841465473175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986118674278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03724563121796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02148723602295</t>
   </si>
   <si>
     <t xml:space="preserve">1.01903605461121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01203238964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995573699474335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973862171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916782140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922735333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888067066669464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939544200897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961605846881866</t>
+    <t xml:space="preserve">1.01203227043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9955735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97386234998703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916782259941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922735273838043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888067126274109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939544260501862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961605787277222</t>
   </si>
   <si>
     <t xml:space="preserve">0.972811698913574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05405426025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11113452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09957849979401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16121065616608</t>
+    <t xml:space="preserve">1.0540543794632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11113440990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09957838058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16121089458466</t>
   </si>
   <si>
     <t xml:space="preserve">1.185023188591</t>
@@ -2924,22 +2924,22 @@
     <t xml:space="preserve">1.15910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12339079380035</t>
+    <t xml:space="preserve">1.12339103221893</t>
   </si>
   <si>
     <t xml:space="preserve">1.12829339504242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1279433965683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16016006469727</t>
+    <t xml:space="preserve">1.12794327735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16016018390656</t>
   </si>
   <si>
     <t xml:space="preserve">1.13564729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17066562175751</t>
+    <t xml:space="preserve">1.1706657409668</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545238018036</t>
@@ -2954,10 +2954,10 @@
     <t xml:space="preserve">1.15560781955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13214540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08522081375122</t>
+    <t xml:space="preserve">1.13214552402496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08522093296051</t>
   </si>
   <si>
     <t xml:space="preserve">1.05965733528137</t>
@@ -2966,28 +2966,28 @@
     <t xml:space="preserve">1.08627128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12899386882782</t>
+    <t xml:space="preserve">1.12899374961853</t>
   </si>
   <si>
     <t xml:space="preserve">1.15000486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15210592746735</t>
+    <t xml:space="preserve">1.15210604667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.15490746498108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15455734729767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25120806694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25611054897308</t>
+    <t xml:space="preserve">1.15455722808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066291332245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2512081861496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25611066818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502071857452</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">1.30793797969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32684779167175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35801446437836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32334613800049</t>
+    <t xml:space="preserve">1.32684791088104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35801422595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32334589958191</t>
   </si>
   <si>
     <t xml:space="preserve">1.31879377365112</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">1.29603159427643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31389117240906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30723750591278</t>
+    <t xml:space="preserve">1.31389105319977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30723774433136</t>
   </si>
   <si>
     <t xml:space="preserve">1.29498100280762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28482592105865</t>
+    <t xml:space="preserve">1.28482580184937</t>
   </si>
   <si>
     <t xml:space="preserve">1.28027331829071</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">1.26941764354706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24315392971039</t>
+    <t xml:space="preserve">1.2431538105011</t>
   </si>
   <si>
     <t xml:space="preserve">1.25435972213745</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">1.27256941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26136338710785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26661622524261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26416480541229</t>
+    <t xml:space="preserve">1.26136350631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26661610603333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26416492462158</t>
   </si>
   <si>
     <t xml:space="preserve">1.26521551609039</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">1.25821173191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3296492099762</t>
+    <t xml:space="preserve">1.32964932918549</t>
   </si>
   <si>
     <t xml:space="preserve">1.36957049369812</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">1.34505748748779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34925961494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33455204963684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31529176235199</t>
+    <t xml:space="preserve">1.34925973415375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33455193042755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31529188156128</t>
   </si>
   <si>
     <t xml:space="preserve">1.31809318065643</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">1.31073951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31774306297302</t>
+    <t xml:space="preserve">1.31774318218231</t>
   </si>
   <si>
     <t xml:space="preserve">1.28062355518341</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">1.26696634292603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25015759468079</t>
+    <t xml:space="preserve">1.2501574754715</t>
   </si>
   <si>
     <t xml:space="preserve">1.29112911224365</t>
@@ -3113,40 +3113,40 @@
     <t xml:space="preserve">1.34820914268494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42174780368805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52260065078735</t>
+    <t xml:space="preserve">1.42174756526947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52260088920593</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190053462982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53240621089935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49808776378632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48898327350616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50088953971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51629757881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50789332389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51979947090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54851448535919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54361188411713</t>
+    <t xml:space="preserve">1.53240585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4980880022049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48898303508759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50088942050934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51629745960236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50789320468903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5197993516922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5485143661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54361176490784</t>
   </si>
   <si>
     <t xml:space="preserve">1.60594463348389</t>
@@ -3158,37 +3158,37 @@
     <t xml:space="preserve">1.62065243721008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59053659439087</t>
+    <t xml:space="preserve">1.59053647518158</t>
   </si>
   <si>
     <t xml:space="preserve">1.59193730354309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69909369945526</t>
+    <t xml:space="preserve">1.69909393787384</t>
   </si>
   <si>
     <t xml:space="preserve">1.70119476318359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72360634803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7102997303009</t>
+    <t xml:space="preserve">1.72360646724701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71029949188232</t>
   </si>
   <si>
     <t xml:space="preserve">1.70469653606415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71099984645844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881982803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70539712905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68998897075653</t>
+    <t xml:space="preserve">1.71099996566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881994724274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70539689064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68998908996582</t>
   </si>
   <si>
     <t xml:space="preserve">1.65356981754303</t>
@@ -3197,28 +3197,28 @@
     <t xml:space="preserve">1.63536012172699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64936745166779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63465988636017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62835657596588</t>
+    <t xml:space="preserve">1.64936757087708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63466012477875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6283563375473</t>
   </si>
   <si>
     <t xml:space="preserve">1.6654759645462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71505236625671</t>
+    <t xml:space="preserve">1.71505224704742</t>
   </si>
   <si>
     <t xml:space="preserve">1.61877369880676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59937429428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61302578449249</t>
+    <t xml:space="preserve">1.5993744134903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6130256652832</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308478355408</t>
@@ -3227,64 +3227,64 @@
     <t xml:space="preserve">1.65613555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67337954044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71936321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71289706230164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70283770561218</t>
+    <t xml:space="preserve">1.67337930202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71936333179474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71289682388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70283782482147</t>
   </si>
   <si>
     <t xml:space="preserve">1.73445177078247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71145987510681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74522924423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893961429596</t>
+    <t xml:space="preserve">1.71145975589752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74522912502289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893973350525</t>
   </si>
   <si>
     <t xml:space="preserve">1.76822102069855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81707906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83504116535187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85587799549103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8644996881485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126095294952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95934104919434</t>
+    <t xml:space="preserve">1.81707882881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83504128456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85587775707245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86449956893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95934128761292</t>
   </si>
   <si>
     <t xml:space="preserve">1.9729927778244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98377001285553</t>
+    <t xml:space="preserve">1.98377013206482</t>
   </si>
   <si>
     <t xml:space="preserve">1.94066035747528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96508920192719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99742162227631</t>
+    <t xml:space="preserve">1.96508932113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99742186069489</t>
   </si>
   <si>
     <t xml:space="preserve">2.02400612831116</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">2.03334641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08579659461975</t>
+    <t xml:space="preserve">2.08579683303833</t>
   </si>
   <si>
     <t xml:space="preserve">2.08795213699341</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">2.10375905036926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12531423568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13465452194214</t>
+    <t xml:space="preserve">2.12531399726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13465476036072</t>
   </si>
   <si>
     <t xml:space="preserve">2.1540539264679</t>
@@ -3314,10 +3314,10 @@
     <t xml:space="preserve">2.15189814567566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17201614379883</t>
+    <t xml:space="preserve">2.18423104286194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17201638221741</t>
   </si>
   <si>
     <t xml:space="preserve">2.17991971969604</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">2.17632722854614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16052055358887</t>
+    <t xml:space="preserve">2.16052031517029</t>
   </si>
   <si>
     <t xml:space="preserve">2.12818813323975</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">2.08076739311218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05346417427063</t>
+    <t xml:space="preserve">2.05346465110779</t>
   </si>
   <si>
     <t xml:space="preserve">2.08292269706726</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">2.04771637916565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04196858406067</t>
+    <t xml:space="preserve">2.04196834564209</t>
   </si>
   <si>
     <t xml:space="preserve">2.01897644996643</t>
@@ -3365,37 +3365,37 @@
     <t xml:space="preserve">1.96652626991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94928240776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9521564245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90114283561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8328857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93922328948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93634939193726</t>
+    <t xml:space="preserve">1.94928228855133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95215630531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90114307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83288598060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93922340869904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93634951114655</t>
   </si>
   <si>
     <t xml:space="preserve">1.91766846179962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88821029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749182224274</t>
+    <t xml:space="preserve">1.88821017742157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749170303345</t>
   </si>
   <si>
     <t xml:space="preserve">1.84653723239899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78762030601501</t>
+    <t xml:space="preserve">1.7876204252243</t>
   </si>
   <si>
     <t xml:space="preserve">1.8264194726944</t>
@@ -3413,88 +3413,88 @@
     <t xml:space="preserve">1.87743258476257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89108395576477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82067108154297</t>
+    <t xml:space="preserve">1.89108407497406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82067131996155</t>
   </si>
   <si>
     <t xml:space="preserve">1.81348633766174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82857477664948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96724450588226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97371113300323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95718550682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03190970420837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00676226615906</t>
+    <t xml:space="preserve">1.82857489585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96724474430084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97371125221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95718562602997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03190946578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00676202774048</t>
   </si>
   <si>
     <t xml:space="preserve">2.00388813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97155570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93347549438477</t>
+    <t xml:space="preserve">1.97155582904816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93347537517548</t>
   </si>
   <si>
     <t xml:space="preserve">1.90904653072357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94209730625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97802233695984</t>
+    <t xml:space="preserve">1.9420975446701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97802209854126</t>
   </si>
   <si>
     <t xml:space="preserve">2.01107311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99957716464996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01753973960876</t>
+    <t xml:space="preserve">1.99957728385925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01753950119019</t>
   </si>
   <si>
     <t xml:space="preserve">2.03262782096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03119087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99167370796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01322865486145</t>
+    <t xml:space="preserve">2.03119111061096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99167358875275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01322841644287</t>
   </si>
   <si>
     <t xml:space="preserve">1.9794590473175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95000088214874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93778657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96868181228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92269790172577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94712662696838</t>
+    <t xml:space="preserve">1.95000076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93778645992279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96868193149567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92269825935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94712686538696</t>
   </si>
   <si>
     <t xml:space="preserve">1.92916429042816</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">1.84078907966614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92054259777069</t>
+    <t xml:space="preserve">1.92054235935211</t>
   </si>
   <si>
     <t xml:space="preserve">1.97586667537689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92341637611389</t>
+    <t xml:space="preserve">1.9234162569046</t>
   </si>
   <si>
     <t xml:space="preserve">1.94353449344635</t>
@@ -3521,28 +3521,28 @@
     <t xml:space="preserve">1.94425296783447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91838681697845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616143226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02831697463989</t>
+    <t xml:space="preserve">1.91838693618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616167068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02831721305847</t>
   </si>
   <si>
     <t xml:space="preserve">2.0218505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03047227859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994200229645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04340529441833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10016679763794</t>
+    <t xml:space="preserve">2.03047251701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994212150574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04340553283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10016655921936</t>
   </si>
   <si>
     <t xml:space="preserve">2.12387704849243</t>
@@ -3551,49 +3551,49 @@
     <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12315845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13034343719482</t>
+    <t xml:space="preserve">2.1231586933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1303436756134</t>
   </si>
   <si>
     <t xml:space="preserve">2.14758729934692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1095073223114</t>
+    <t xml:space="preserve">2.10950708389282</t>
   </si>
   <si>
     <t xml:space="preserve">2.08148574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92988288402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93563103675842</t>
+    <t xml:space="preserve">1.92988300323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93563079833984</t>
   </si>
   <si>
     <t xml:space="preserve">1.97083735466003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00963592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08364129066467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03765749931335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00316977500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98592555522919</t>
+    <t xml:space="preserve">2.00963616371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08364152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03765726089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.003169298172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98592579364777</t>
   </si>
   <si>
     <t xml:space="preserve">1.95143783092499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90042471885681</t>
+    <t xml:space="preserve">1.90042436122894</t>
   </si>
   <si>
     <t xml:space="preserve">1.88318061828613</t>
@@ -3602,70 +3602,70 @@
     <t xml:space="preserve">1.85372221469879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74594783782959</t>
+    <t xml:space="preserve">1.74594759941101</t>
   </si>
   <si>
     <t xml:space="preserve">1.77540600299835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77181363105774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80845665931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83001172542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8853360414505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92557215690613</t>
+    <t xml:space="preserve">1.77181375026703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80845677852631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8300119638443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88533627986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92557191848755</t>
   </si>
   <si>
     <t xml:space="preserve">1.88964712619781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88677299022675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86737382411957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395785331726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89036548137665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8544408082962</t>
+    <t xml:space="preserve">1.88677322864532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86737358570099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89036560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85444068908691</t>
   </si>
   <si>
     <t xml:space="preserve">1.84797430038452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79767966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85659611225128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85875165462494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84725606441498</t>
+    <t xml:space="preserve">1.79767954349518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85659658908844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85875177383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84725570678711</t>
   </si>
   <si>
     <t xml:space="preserve">1.85515928268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88605451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683210849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97874069213867</t>
+    <t xml:space="preserve">1.8860547542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683198928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97874081134796</t>
   </si>
   <si>
     <t xml:space="preserve">2.0010142326355</t>
@@ -3674,58 +3674,58 @@
     <t xml:space="preserve">2.0254430770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06280493736267</t>
+    <t xml:space="preserve">2.06280469894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.05849385261536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06424188613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05633854866028</t>
+    <t xml:space="preserve">2.06424164772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0563383102417</t>
   </si>
   <si>
     <t xml:space="preserve">2.0527458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02113199234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0046067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01251006126404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99526607990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89970624446869</t>
+    <t xml:space="preserve">2.02113223075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00460648536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01251029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99526619911194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">1.87958824634552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93131983280182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221530437469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91192054748535</t>
+    <t xml:space="preserve">1.93131995201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221518516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91192042827606</t>
   </si>
   <si>
     <t xml:space="preserve">2.02041339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06855297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10447764396667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07645654678345</t>
+    <t xml:space="preserve">2.06855273246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10447788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07645630836487</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657406806946</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">2.15117979049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32505655288696</t>
+    <t xml:space="preserve">2.3250560760498</t>
   </si>
   <si>
     <t xml:space="preserve">2.32361912727356</t>
@@ -3743,16 +3743,16 @@
     <t xml:space="preserve">2.55138301849365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53485774993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60814428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55928635597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.527672290802</t>
+    <t xml:space="preserve">2.53485751152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6081440448761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55928611755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52767252922058</t>
   </si>
   <si>
     <t xml:space="preserve">2.57509326934814</t>
@@ -3767,67 +3767,67 @@
     <t xml:space="preserve">2.41343140602112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21584510803223</t>
+    <t xml:space="preserve">2.21584463119507</t>
   </si>
   <si>
     <t xml:space="preserve">2.26398396492004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21368932723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496024131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120207309723</t>
+    <t xml:space="preserve">2.21368908882141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496047973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120195388794</t>
   </si>
   <si>
     <t xml:space="preserve">1.66475749015808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7495402097702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7948055267334</t>
+    <t xml:space="preserve">1.74954009056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79480540752411</t>
   </si>
   <si>
     <t xml:space="preserve">1.83575963973999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90186142921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06783413887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96077835559845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9586226940155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98879957199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95574879646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359361171722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06208658218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93275701999664</t>
+    <t xml:space="preserve">1.90186131000519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06783437728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95862281322479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98879969120026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95574867725372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06208634376526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93275713920593</t>
   </si>
   <si>
     <t xml:space="preserve">1.99095511436462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664438724518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784545898438</t>
+    <t xml:space="preserve">1.98664402961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94784510135651</t>
   </si>
   <si>
     <t xml:space="preserve">2.16626834869385</t>
@@ -3842,40 +3842,40 @@
     <t xml:space="preserve">2.19860076904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23077535629272</t>
+    <t xml:space="preserve">2.2307755947113</t>
   </si>
   <si>
     <t xml:space="preserve">2.33036375045776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35257959365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35181331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36713457107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.321937084198</t>
+    <t xml:space="preserve">2.35257935523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35181355476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36713480949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32193684577942</t>
   </si>
   <si>
     <t xml:space="preserve">2.35104727745056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31887269020081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27597308158875</t>
+    <t xml:space="preserve">2.31887245178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27597332000732</t>
   </si>
   <si>
     <t xml:space="preserve">2.33572626113892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24839472770691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23383975028992</t>
+    <t xml:space="preserve">2.24839496612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23383951187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.21085786819458</t>
@@ -3905,25 +3905,25 @@
     <t xml:space="preserve">2.31351017951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38092398643494</t>
+    <t xml:space="preserve">2.38092374801636</t>
   </si>
   <si>
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45523166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47285127639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45293378829956</t>
+    <t xml:space="preserve">2.45523190498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47285151481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45293354988098</t>
   </si>
   <si>
     <t xml:space="preserve">2.4820442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4866406917572</t>
+    <t xml:space="preserve">2.48664045333862</t>
   </si>
   <si>
     <t xml:space="preserve">2.46365880966187</t>
@@ -3935,13 +3935,13 @@
     <t xml:space="preserve">2.41309857368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43071818351746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37709331512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09058618545532</t>
+    <t xml:space="preserve">2.43071794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37709355354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09058594703674</t>
   </si>
   <si>
     <t xml:space="preserve">1.98793339729309</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">2.08062720298767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02623677253723</t>
+    <t xml:space="preserve">2.02623653411865</t>
   </si>
   <si>
     <t xml:space="preserve">2.07832884788513</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">2.21315598487854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1993670463562</t>
+    <t xml:space="preserve">2.19936680793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.13501763343811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20089912414551</t>
+    <t xml:space="preserve">2.20089888572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.14267826080322</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">2.14191222190857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14650893211365</t>
+    <t xml:space="preserve">2.14650845527649</t>
   </si>
   <si>
     <t xml:space="preserve">2.0315990447998</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">1.98410308361053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98563539981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91592335700989</t>
+    <t xml:space="preserve">1.98563516139984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91592347621918</t>
   </si>
   <si>
     <t xml:space="preserve">1.8684276342392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83472096920013</t>
+    <t xml:space="preserve">1.83472084999084</t>
   </si>
   <si>
     <t xml:space="preserve">1.73743081092834</t>
@@ -4019,13 +4019,13 @@
     <t xml:space="preserve">1.83012449741364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92435026168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87915277481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80331230163574</t>
+    <t xml:space="preserve">1.92435014247894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87915253639221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80331254005432</t>
   </si>
   <si>
     <t xml:space="preserve">1.79718387126923</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">1.85387253761292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79641783237457</t>
+    <t xml:space="preserve">1.79641759395599</t>
   </si>
   <si>
     <t xml:space="preserve">1.84544563293457</t>
@@ -4043,22 +4043,22 @@
     <t xml:space="preserve">1.86306512355804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92894649505615</t>
+    <t xml:space="preserve">1.92894661426544</t>
   </si>
   <si>
     <t xml:space="preserve">1.92052006721497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96954810619354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837010383606</t>
+    <t xml:space="preserve">1.96954798698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837034225464</t>
   </si>
   <si>
     <t xml:space="preserve">2.00095653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03466320037842</t>
+    <t xml:space="preserve">2.034663438797</t>
   </si>
   <si>
     <t xml:space="preserve">1.98869955539703</t>
@@ -4067,22 +4067,22 @@
     <t xml:space="preserve">1.97184610366821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95652496814728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99176383018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07220029830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06530570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02240610122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01397943496704</t>
+    <t xml:space="preserve">1.95652484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99176371097565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07220053672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06530594825745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02240633964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01397967338562</t>
   </si>
   <si>
     <t xml:space="preserve">1.94273579120636</t>
@@ -4097,19 +4097,19 @@
     <t xml:space="preserve">1.86076700687408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80944085121155</t>
+    <t xml:space="preserve">1.80944073200226</t>
   </si>
   <si>
     <t xml:space="preserve">1.86612975597382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8983039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90213453769684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87149202823639</t>
+    <t xml:space="preserve">1.89830410480499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90213441848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8714919090271</t>
   </si>
   <si>
     <t xml:space="preserve">1.9687819480896</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">1.90060222148895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90673089027405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89907038211823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99712646007538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06070947647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12199425697327</t>
+    <t xml:space="preserve">1.90673077106476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89907014369965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99712634086609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06070971488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12199449539185</t>
   </si>
   <si>
     <t xml:space="preserve">2.08445739746094</t>
@@ -4139,16 +4139,16 @@
     <t xml:space="preserve">2.15033888816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19017434120178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21392226219177</t>
+    <t xml:space="preserve">2.1901741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21392202377319</t>
   </si>
   <si>
     <t xml:space="preserve">2.15799951553345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12965512275696</t>
+    <t xml:space="preserve">2.12965536117554</t>
   </si>
   <si>
     <t xml:space="preserve">2.09288430213928</t>
@@ -4157,10 +4157,10 @@
     <t xml:space="preserve">2.07143425941467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02700257301331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06377387046814</t>
+    <t xml:space="preserve">2.02700281143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">2.1319534778595</t>
@@ -4169,22 +4169,22 @@
     <t xml:space="preserve">2.17791700363159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10820555686951</t>
+    <t xml:space="preserve">2.10820531845093</t>
   </si>
   <si>
     <t xml:space="preserve">2.0300669670105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04155778884888</t>
+    <t xml:space="preserve">2.04155802726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.07986092567444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05151677131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05304861068726</t>
+    <t xml:space="preserve">2.05151653289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05304884910583</t>
   </si>
   <si>
     <t xml:space="preserve">2.11893033981323</t>
@@ -4193,16 +4193,16 @@
     <t xml:space="preserve">2.17485284805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17255473136902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17332053184509</t>
+    <t xml:space="preserve">2.17255449295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17332077026367</t>
   </si>
   <si>
     <t xml:space="preserve">2.1932384967804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2261791229248</t>
+    <t xml:space="preserve">2.22617888450623</t>
   </si>
   <si>
     <t xml:space="preserve">2.21698641777039</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">2.3173406124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3441526889801</t>
+    <t xml:space="preserve">2.34415292739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.34491896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37173104286194</t>
+    <t xml:space="preserve">2.37173128128052</t>
   </si>
   <si>
     <t xml:space="preserve">2.41922688484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220876693726</t>
+    <t xml:space="preserve">2.44220900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.37785959243774</t>
@@ -4238,13 +4238,13 @@
     <t xml:space="preserve">2.36177229881287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769504547119</t>
+    <t xml:space="preserve">2.41769480705261</t>
   </si>
   <si>
     <t xml:space="preserve">2.45140171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45906209945679</t>
+    <t xml:space="preserve">2.45906233787537</t>
   </si>
   <si>
     <t xml:space="preserve">2.48970484733582</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">2.56171464920044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58086609840393</t>
+    <t xml:space="preserve">2.58086633682251</t>
   </si>
   <si>
     <t xml:space="preserve">2.53949904441833</t>
@@ -4286,7 +4286,7 @@
     <t xml:space="preserve">2.41386461257935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40390563011169</t>
+    <t xml:space="preserve">2.40390586853027</t>
   </si>
   <si>
     <t xml:space="preserve">2.41080021858215</t>
@@ -4304,31 +4304,31 @@
     <t xml:space="preserve">2.50349378585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44527316093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817276954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4667227268219</t>
+    <t xml:space="preserve">2.44527292251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46672296524048</t>
   </si>
   <si>
     <t xml:space="preserve">2.5686092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59465551376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57933402061462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58393025398254</t>
+    <t xml:space="preserve">2.59465527534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5793342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58393049240112</t>
   </si>
   <si>
     <t xml:space="preserve">2.56477904319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57703614234924</t>
+    <t xml:space="preserve">2.57703590393066</t>
   </si>
   <si>
     <t xml:space="preserve">2.55405426025391</t>
@@ -4337,16 +4337,16 @@
     <t xml:space="preserve">2.62376570701599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67739033699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77774453163147</t>
+    <t xml:space="preserve">2.67739009857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77774405479431</t>
   </si>
   <si>
     <t xml:space="preserve">2.78923559188843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77468013763428</t>
+    <t xml:space="preserve">2.77468037605286</t>
   </si>
   <si>
     <t xml:space="preserve">2.75859308242798</t>
@@ -4358,13 +4358,13 @@
     <t xml:space="preserve">2.74020743370056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8214099407196</t>
+    <t xml:space="preserve">2.82141017913818</t>
   </si>
   <si>
     <t xml:space="preserve">2.94014978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92176413536072</t>
+    <t xml:space="preserve">2.9217643737793</t>
   </si>
   <si>
     <t xml:space="preserve">2.93172311782837</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.95700311660767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99454021453857</t>
+    <t xml:space="preserve">2.99453997612</t>
   </si>
   <si>
     <t xml:space="preserve">3.00756359100342</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">3.07038044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09106397628784</t>
+    <t xml:space="preserve">3.09106421470642</t>
   </si>
   <si>
     <t xml:space="preserve">3.07957315444946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16154170036316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19831323623657</t>
+    <t xml:space="preserve">3.16154193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19831299781799</t>
   </si>
   <si>
     <t xml:space="preserve">3.14315676689148</t>
@@ -4406,52 +4406,52 @@
     <t xml:space="preserve">3.22895550727844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29024052619934</t>
+    <t xml:space="preserve">3.29024076461792</t>
   </si>
   <si>
     <t xml:space="preserve">3.22435927391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22052884101868</t>
+    <t xml:space="preserve">3.22052907943726</t>
   </si>
   <si>
     <t xml:space="preserve">3.18145966529846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18682193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16767072677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14085793495178</t>
+    <t xml:space="preserve">3.18682217597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16767048835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14085817337036</t>
   </si>
   <si>
     <t xml:space="preserve">3.19448280334473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22282671928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1025550365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04280209541321</t>
+    <t xml:space="preserve">3.22282719612122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10255527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04280233383179</t>
   </si>
   <si>
     <t xml:space="preserve">3.11634421348572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05812358856201</t>
+    <t xml:space="preserve">3.05812382698059</t>
   </si>
   <si>
     <t xml:space="preserve">3.12860155105591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16000986099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16077613830566</t>
+    <t xml:space="preserve">3.16001009941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16077589988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.11711025238037</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">3.22359323501587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18912029266357</t>
+    <t xml:space="preserve">3.18912053108215</t>
   </si>
   <si>
     <t xml:space="preserve">3.23355221748352</t>
@@ -4472,13 +4472,13 @@
     <t xml:space="preserve">3.17150068283081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07727551460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82830476760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88116312026978</t>
+    <t xml:space="preserve">3.0772750377655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82830452919006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8811628818512</t>
   </si>
   <si>
     <t xml:space="preserve">2.67585825920105</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">2.80991911888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039684295654</t>
+    <t xml:space="preserve">2.88039708137512</t>
   </si>
   <si>
     <t xml:space="preserve">2.80379056930542</t>
@@ -4511,31 +4511,31 @@
     <t xml:space="preserve">2.65900468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75782680511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79996013641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76165699958801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7785108089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75476288795471</t>
+    <t xml:space="preserve">2.75782656669617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79996037483215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76165747642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77851057052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75476264953613</t>
   </si>
   <si>
     <t xml:space="preserve">2.82370853424072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8397958278656</t>
+    <t xml:space="preserve">2.83979558944702</t>
   </si>
   <si>
     <t xml:space="preserve">2.84132790565491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8351993560791</t>
+    <t xml:space="preserve">2.83519911766052</t>
   </si>
   <si>
     <t xml:space="preserve">2.93019104003906</t>
@@ -4544,22 +4544,22 @@
     <t xml:space="preserve">3.01828837394714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0803394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11098194122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24427676200867</t>
+    <t xml:space="preserve">3.08033919334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11098170280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24427700042725</t>
   </si>
   <si>
     <t xml:space="preserve">3.31637167930603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21511459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03609228134155</t>
+    <t xml:space="preserve">3.21511483192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03609204292297</t>
   </si>
   <si>
     <t xml:space="preserve">3.11466765403748</t>
@@ -4568,13 +4568,13 @@
     <t xml:space="preserve">2.98505854606628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92187452316284</t>
+    <t xml:space="preserve">2.92187428474426</t>
   </si>
   <si>
     <t xml:space="preserve">2.96966743469238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89595222473145</t>
+    <t xml:space="preserve">2.89595246315002</t>
   </si>
   <si>
     <t xml:space="preserve">3.0109806060791</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">3.04905295372009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27910923957825</t>
+    <t xml:space="preserve">3.27910900115967</t>
   </si>
   <si>
     <t xml:space="preserve">3.1567907333374</t>
@@ -4607,16 +4607,16 @@
     <t xml:space="preserve">3.17947196960449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1584107875824</t>
+    <t xml:space="preserve">3.15841054916382</t>
   </si>
   <si>
     <t xml:space="preserve">3.21754479408264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21025466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631563186646</t>
+    <t xml:space="preserve">3.21025443077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631539344788</t>
   </si>
   <si>
     <t xml:space="preserve">3.09684634208679</t>
@@ -4625,25 +4625,25 @@
     <t xml:space="preserve">3.09441614151001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05472373962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02151107788086</t>
+    <t xml:space="preserve">3.05472350120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02151131629944</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03771209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11142754554749</t>
+    <t xml:space="preserve">3.03771233558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11142778396606</t>
   </si>
   <si>
     <t xml:space="preserve">3.06768441200256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11304759979248</t>
+    <t xml:space="preserve">3.1130473613739</t>
   </si>
   <si>
     <t xml:space="preserve">3.09765625</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">3.10251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09198617935181</t>
+    <t xml:space="preserve">3.09198594093323</t>
   </si>
   <si>
     <t xml:space="preserve">3.14626002311707</t>
@@ -4667,22 +4667,22 @@
     <t xml:space="preserve">3.16165113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24508690834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26776838302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24751663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31556177139282</t>
+    <t xml:space="preserve">3.24508714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26776814460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24751687049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31556153297424</t>
   </si>
   <si>
     <t xml:space="preserve">3.29612016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22888565063477</t>
+    <t xml:space="preserve">3.22888588905334</t>
   </si>
   <si>
     <t xml:space="preserve">3.22240519523621</t>
@@ -4700,13 +4700,13 @@
     <t xml:space="preserve">3.44274067878723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50673508644104</t>
+    <t xml:space="preserve">3.50673484802246</t>
   </si>
   <si>
     <t xml:space="preserve">3.44031071662903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44355082511902</t>
+    <t xml:space="preserve">3.44355058670044</t>
   </si>
   <si>
     <t xml:space="preserve">3.34553384780884</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">3.42005920410156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46947264671326</t>
+    <t xml:space="preserve">3.46947240829468</t>
   </si>
   <si>
     <t xml:space="preserve">3.4978244304657</t>
@@ -4724,13 +4724,13 @@
     <t xml:space="preserve">3.57883048057556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61852312088013</t>
+    <t xml:space="preserve">3.61852288246155</t>
   </si>
   <si>
     <t xml:space="preserve">3.54075741767883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61042213439941</t>
+    <t xml:space="preserve">3.61042237281799</t>
   </si>
   <si>
     <t xml:space="preserve">3.62500333786011</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">3.60475182533264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5942211151123</t>
+    <t xml:space="preserve">3.59422135353088</t>
   </si>
   <si>
     <t xml:space="preserve">3.59503149986267</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">3.63634419441223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63553428649902</t>
+    <t xml:space="preserve">3.63553380966187</t>
   </si>
   <si>
     <t xml:space="preserve">3.68413734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64606499671936</t>
+    <t xml:space="preserve">3.64606475830078</t>
   </si>
   <si>
     <t xml:space="preserve">3.58774065971375</t>
@@ -4772,22 +4772,22 @@
     <t xml:space="preserve">3.50511527061462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48162341117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56505918502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24103665351868</t>
+    <t xml:space="preserve">3.48162317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56505942344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2410364151001</t>
   </si>
   <si>
     <t xml:space="preserve">3.4176287651062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51807594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50106453895569</t>
+    <t xml:space="preserve">3.51807570457458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50106501579285</t>
   </si>
   <si>
     <t xml:space="preserve">3.54966807365417</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">3.55209851264954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54480791091919</t>
+    <t xml:space="preserve">3.54480767250061</t>
   </si>
   <si>
     <t xml:space="preserve">3.52293610572815</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">3.5415678024292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51564598083496</t>
+    <t xml:space="preserve">3.51564574241638</t>
   </si>
   <si>
     <t xml:space="preserve">3.56667900085449</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">3.54318785667419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49944496154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46380257606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35687446594238</t>
+    <t xml:space="preserve">3.49944472312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46380233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35687470436096</t>
   </si>
   <si>
     <t xml:space="preserve">3.28882956504822</t>
@@ -4853,10 +4853,10 @@
     <t xml:space="preserve">3.53994727134705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62743377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70843935012817</t>
+    <t xml:space="preserve">3.62743353843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70843958854675</t>
   </si>
   <si>
     <t xml:space="preserve">3.77243375778198</t>
@@ -4865,34 +4865,34 @@
     <t xml:space="preserve">3.75218224525452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82670760154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75137233734131</t>
+    <t xml:space="preserve">3.82670712471008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75137257575989</t>
   </si>
   <si>
     <t xml:space="preserve">3.6898078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74084138870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67360687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68251776695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66712617874146</t>
+    <t xml:space="preserve">3.74084162712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67360663414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68251752853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66712641716003</t>
   </si>
   <si>
     <t xml:space="preserve">3.72626042366028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85505962371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74570202827454</t>
+    <t xml:space="preserve">3.8550591468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74570178985596</t>
   </si>
   <si>
     <t xml:space="preserve">3.84452867507935</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">3.800785779953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8396680355072</t>
+    <t xml:space="preserve">3.83966827392578</t>
   </si>
   <si>
     <t xml:space="preserve">3.76838326454163</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">3.80726599693298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79349493980408</t>
+    <t xml:space="preserve">3.79349541664124</t>
   </si>
   <si>
     <t xml:space="preserve">3.82589745521545</t>
@@ -4955,28 +4955,28 @@
     <t xml:space="preserve">3.94011521339417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99114894866943</t>
+    <t xml:space="preserve">3.99114942550659</t>
   </si>
   <si>
     <t xml:space="preserve">4.10698699951172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.119948387146</t>
+    <t xml:space="preserve">4.11994791030884</t>
   </si>
   <si>
     <t xml:space="preserve">4.30950117111206</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28357982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31112146377563</t>
+    <t xml:space="preserve">4.28357934951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31112098693848</t>
   </si>
   <si>
     <t xml:space="preserve">4.25279712677002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27223920822144</t>
+    <t xml:space="preserve">4.27223873138428</t>
   </si>
   <si>
     <t xml:space="preserve">4.31274175643921</t>
@@ -4985,7 +4985,7 @@
     <t xml:space="preserve">4.13938903808594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1134672164917</t>
+    <t xml:space="preserve">4.11346769332886</t>
   </si>
   <si>
     <t xml:space="preserve">4.13128852844238</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">4.11022758483887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18637275695801</t>
+    <t xml:space="preserve">4.18637323379517</t>
   </si>
   <si>
     <t xml:space="preserve">4.14100933074951</t>
@@ -5027,10 +5027,10 @@
     <t xml:space="preserve">4.05676364898682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90204286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8348081111908</t>
+    <t xml:space="preserve">3.90204238891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83480858802795</t>
   </si>
   <si>
     <t xml:space="preserve">3.87045049667358</t>
@@ -5042,13 +5042,13 @@
     <t xml:space="preserve">3.84290862083435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81617665290833</t>
+    <t xml:space="preserve">3.81617712974548</t>
   </si>
   <si>
     <t xml:space="preserve">3.86072969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88260197639465</t>
+    <t xml:space="preserve">3.8826014995575</t>
   </si>
   <si>
     <t xml:space="preserve">3.87288117408752</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">4.17503213882446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14749002456665</t>
+    <t xml:space="preserve">4.14748954772949</t>
   </si>
   <si>
     <t xml:space="preserve">3.94578576087952</t>
@@ -5075,10 +5075,10 @@
     <t xml:space="preserve">3.9506459236145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88422155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88584136962891</t>
+    <t xml:space="preserve">3.88422179222107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88584184646606</t>
   </si>
   <si>
     <t xml:space="preserve">3.83318781852722</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">3.88665151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93687534332275</t>
+    <t xml:space="preserve">3.93687510490417</t>
   </si>
   <si>
     <t xml:space="preserve">3.96927738189697</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">3.99762940406799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05838346481323</t>
+    <t xml:space="preserve">4.05838394165039</t>
   </si>
   <si>
     <t xml:space="preserve">4.00573015213013</t>
@@ -5126,16 +5126,16 @@
     <t xml:space="preserve">4.20581388473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29978084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13290882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13614940643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00897026062012</t>
+    <t xml:space="preserve">4.29978036880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13290929794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13614892959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00896978378296</t>
   </si>
   <si>
     <t xml:space="preserve">3.98223829269409</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">3.98547863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99600911140442</t>
+    <t xml:space="preserve">3.99600958824158</t>
   </si>
   <si>
     <t xml:space="preserve">4.03408193588257</t>
@@ -5156,7 +5156,7 @@
     <t xml:space="preserve">4.42614984512329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47961330413818</t>
+    <t xml:space="preserve">4.47961282730103</t>
   </si>
   <si>
     <t xml:space="preserve">4.40670776367188</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">5.01101016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96240663528442</t>
+    <t xml:space="preserve">4.96240711212158</t>
   </si>
   <si>
     <t xml:space="preserve">4.99642944335938</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">5.04989337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15358018875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12927865982056</t>
+    <t xml:space="preserve">5.15358066558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1292781829834</t>
   </si>
   <si>
     <t xml:space="preserve">5.07095432281494</t>
@@ -5252,7 +5252,7 @@
     <t xml:space="preserve">4.92838478088379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9867091178894</t>
+    <t xml:space="preserve">4.98670864105225</t>
   </si>
   <si>
     <t xml:space="preserve">4.96564722061157</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">5.14709997177124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17626142501831</t>
+    <t xml:space="preserve">5.17626190185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130989074707</t>
@@ -6297,6 +6297,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.1899995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2700004577637</t>
   </si>
 </sst>
 </file>
@@ -71817,7 +71820,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6930439815</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>14526149</v>
@@ -71838,6 +71841,32 @@
         <v>2094</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6916898148</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>8122601</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>13.3649997711182</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>13.1850004196167</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>13.2650003433228</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>13.2700004577637</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>2095</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="2096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="2097">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,67 +44,67 @@
     <t xml:space="preserve">BAMI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25302410125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98423957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89802598953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65459871292114</t>
+    <t xml:space="preserve">6.25302314758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98424005508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89802646636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6545991897583</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89295482635498</t>
+    <t xml:space="preserve">5.65967130661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89295434951782</t>
   </si>
   <si>
     <t xml:space="preserve">5.274245262146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94206857681274</t>
+    <t xml:space="preserve">4.9420690536499</t>
   </si>
   <si>
     <t xml:space="preserve">4.40450143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85839080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61496448516846</t>
+    <t xml:space="preserve">4.85839128494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61496496200562</t>
   </si>
   <si>
     <t xml:space="preserve">4.28785991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55410718917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95568346977234</t>
+    <t xml:space="preserve">4.55410766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9556839466095</t>
   </si>
   <si>
     <t xml:space="preserve">4.32082366943359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57946443557739</t>
+    <t xml:space="preserve">4.57946491241455</t>
   </si>
   <si>
     <t xml:space="preserve">4.50339365005493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05204057693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11289691925049</t>
+    <t xml:space="preserve">4.05204010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11289739608765</t>
   </si>
   <si>
     <t xml:space="preserve">3.87961268424988</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">3.52715134620667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22286748886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040118217468</t>
+    <t xml:space="preserve">3.22286772727966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5804009437561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26851081848145</t>
@@ -125,22 +125,22 @@
     <t xml:space="preserve">3.6437931060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91004085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04443264007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14332485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91511297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818560600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08246850967407</t>
+    <t xml:space="preserve">3.91004157066345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04443216323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1433253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91511273384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818536758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08246898651123</t>
   </si>
   <si>
     <t xml:space="preserve">3.71986413002014</t>
@@ -149,79 +149,79 @@
     <t xml:space="preserve">3.646329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74775648117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84157752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92018389701843</t>
+    <t xml:space="preserve">3.74775671958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84157681465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92018342018127</t>
   </si>
   <si>
     <t xml:space="preserve">4.22700262069702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04950523376465</t>
+    <t xml:space="preserve">4.04950428009033</t>
   </si>
   <si>
     <t xml:space="preserve">3.88468432426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86693429946899</t>
+    <t xml:space="preserve">3.86693453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.7604353427887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69957852363586</t>
+    <t xml:space="preserve">3.69957780838013</t>
   </si>
   <si>
     <t xml:space="preserve">4.03682613372803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94807696342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38768839836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4713659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67675709724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51447296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38261675834656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27611804008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06565451622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365622520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812201499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49005150794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40586733818054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22431135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46672320365906</t>
+    <t xml:space="preserve">3.9480767250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38768792152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47136569023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67675733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197154045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51447319984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38261723518372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27611780166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06565475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365598678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812177658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49005174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40586709976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2243115901947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46672368049622</t>
   </si>
   <si>
     <t xml:space="preserve">2.72079992294312</t>
@@ -230,16 +230,16 @@
     <t xml:space="preserve">2.70051455497742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91097712516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02508354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16454696655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22690272331238</t>
+    <t xml:space="preserve">2.910977602005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02508330345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16454648971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22690224647522</t>
   </si>
   <si>
     <t xml:space="preserve">3.1385657787323</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">3.14116334915161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20092082023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508929252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11778044700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23469686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19052910804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32823014259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20351934432983</t>
+    <t xml:space="preserve">3.20092105865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777997016907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23469662666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19052886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32823061943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20351910591125</t>
   </si>
   <si>
     <t xml:space="preserve">2.96968603134155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75663733482361</t>
+    <t xml:space="preserve">2.75663709640503</t>
   </si>
   <si>
     <t xml:space="preserve">2.86835813522339</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">2.72805738449097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84497451782227</t>
+    <t xml:space="preserve">2.84497475624084</t>
   </si>
   <si>
     <t xml:space="preserve">2.59607148170471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51500964164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28637218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378554344177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32274627685547</t>
+    <t xml:space="preserve">2.51500940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.286372423172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378602027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32274651527405</t>
   </si>
   <si>
     <t xml:space="preserve">2.39237642288208</t>
@@ -305,46 +305,46 @@
     <t xml:space="preserve">2.23544836044312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24584126472473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22089910507202</t>
+    <t xml:space="preserve">2.24584102630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2208993434906</t>
   </si>
   <si>
     <t xml:space="preserve">2.24480199813843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24999761581421</t>
+    <t xml:space="preserve">2.24999785423279</t>
   </si>
   <si>
     <t xml:space="preserve">2.2749400138855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47343897819519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47032117843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48902821540833</t>
+    <t xml:space="preserve">2.47343921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4703209400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48902797698975</t>
   </si>
   <si>
     <t xml:space="preserve">2.49422383308411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31131434440613</t>
+    <t xml:space="preserve">2.31131458282471</t>
   </si>
   <si>
     <t xml:space="preserve">2.16581773757935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16685724258423</t>
+    <t xml:space="preserve">2.16685748100281</t>
   </si>
   <si>
     <t xml:space="preserve">2.05461692810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15853524208069</t>
+    <t xml:space="preserve">2.15853548049927</t>
   </si>
   <si>
     <t xml:space="preserve">2.29020428657532</t>
@@ -356,34 +356,34 @@
     <t xml:space="preserve">2.15433287620544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0422739982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83636605739594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71590256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83776676654816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07449126243591</t>
+    <t xml:space="preserve">2.04227423667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83636581897736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71590268611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83776664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07449102401733</t>
   </si>
   <si>
     <t xml:space="preserve">2.01846170425415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02546548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.993248462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12211632728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6276558637619</t>
+    <t xml:space="preserve">2.02546525001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99324822425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12211608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62765598297119</t>
   </si>
   <si>
     <t xml:space="preserve">1.52680313587189</t>
@@ -395,91 +395,91 @@
     <t xml:space="preserve">1.50439119338989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50158989429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540218830109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45676624774933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40073680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31459128856659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28167414665222</t>
+    <t xml:space="preserve">1.50158965587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540242671967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45676612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40073668956757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31459140777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28167402744293</t>
   </si>
   <si>
     <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5702258348465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66687679290771</t>
+    <t xml:space="preserve">1.57022595405579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.666876912117</t>
   </si>
   <si>
     <t xml:space="preserve">1.5562185049057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64166367053986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66267466545105</t>
+    <t xml:space="preserve">1.64166355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66267430782318</t>
   </si>
   <si>
     <t xml:space="preserve">1.68788778781891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67528104782104</t>
+    <t xml:space="preserve">1.67528116703033</t>
   </si>
   <si>
     <t xml:space="preserve">1.66407525539398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72991001605988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70329570770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7173033952713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7593252658844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70749819278717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76352751255035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5057920217514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49738764762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55201649665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63045740127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59964120388031</t>
+    <t xml:space="preserve">1.72990989685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70329582691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71730315685272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75932550430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70749807357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76352739334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50579214096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49738752841949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55201625823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63045763969421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5996413230896</t>
   </si>
   <si>
     <t xml:space="preserve">1.59263753890991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58143162727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56882524490356</t>
+    <t xml:space="preserve">1.58143174648285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56882512569427</t>
   </si>
   <si>
     <t xml:space="preserve">1.53100538253784</t>
@@ -494,28 +494,28 @@
     <t xml:space="preserve">1.48758244514465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58003115653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53520739078522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559710502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56742441654205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56182157993317</t>
+    <t xml:space="preserve">1.58003103733063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53520750999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56742429733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56182134151459</t>
   </si>
   <si>
     <t xml:space="preserve">1.60384356975555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6808842420578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63886189460754</t>
+    <t xml:space="preserve">1.68088412284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63886177539825</t>
   </si>
   <si>
     <t xml:space="preserve">1.65707147121429</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">1.65847229957581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64306426048279</t>
+    <t xml:space="preserve">1.6430641412735</t>
   </si>
   <si>
     <t xml:space="preserve">1.59403848648071</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">1.60944652557373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57582879066467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50018906593323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46657133102417</t>
+    <t xml:space="preserve">1.57582890987396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50018894672394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46657145023346</t>
   </si>
   <si>
     <t xml:space="preserve">1.40003633499146</t>
@@ -566,22 +566,22 @@
     <t xml:space="preserve">1.40774035453796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4679719209671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48057878017426</t>
+    <t xml:space="preserve">1.46797204017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48057889938354</t>
   </si>
   <si>
     <t xml:space="preserve">1.50299048423767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55061566829681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65286946296692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78593921661377</t>
+    <t xml:space="preserve">1.55061554908752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65286922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78593945503235</t>
   </si>
   <si>
     <t xml:space="preserve">1.79994666576385</t>
@@ -596,55 +596,55 @@
     <t xml:space="preserve">1.84196889400482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82235836982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737681388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86297988891602</t>
+    <t xml:space="preserve">1.82235860824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737693309784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86298000812531</t>
   </si>
   <si>
     <t xml:space="preserve">1.92041027545929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89379596710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80835115909576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67107903957367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61224806308746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50999426841736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59543931484222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60664510726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5127956867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42735075950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35451233386993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30408596992493</t>
+    <t xml:space="preserve">1.89379608631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80835103988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67107892036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61224782466888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50999414920807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59543943405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60664486885071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51279580593109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42735087871552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35451245307922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30408585071564</t>
   </si>
   <si>
     <t xml:space="preserve">1.31178998947144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32649767398834</t>
+    <t xml:space="preserve">1.32649779319763</t>
   </si>
   <si>
     <t xml:space="preserve">1.29988360404968</t>
@@ -656,97 +656,97 @@
     <t xml:space="preserve">1.2508579492569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30268514156342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35871469974518</t>
+    <t xml:space="preserve">1.30268526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35871481895447</t>
   </si>
   <si>
     <t xml:space="preserve">1.39233231544495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28867781162262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40493893623352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49458622932434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64026272296906</t>
+    <t xml:space="preserve">1.28867793083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40493905544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49458611011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64026284217834</t>
   </si>
   <si>
     <t xml:space="preserve">1.56462287902832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.533806681633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67948341369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65146863460541</t>
+    <t xml:space="preserve">1.53380680084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.679483294487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69769299030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65146851539612</t>
   </si>
   <si>
     <t xml:space="preserve">1.72290623188019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77893567085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310114860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60524451732635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092089176178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87698721885681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9050018787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97643971443176</t>
+    <t xml:space="preserve">1.77893555164337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310102939606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60524439811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092101097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87698709964752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90500199794769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9764392375946</t>
   </si>
   <si>
     <t xml:space="preserve">2.0310685634613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95122623443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94982552528381</t>
+    <t xml:space="preserve">1.95122635364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9498256444931</t>
   </si>
   <si>
     <t xml:space="preserve">1.90640258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94702434539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89799833297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9414210319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93581831455231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01706099510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97363805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02266407012939</t>
+    <t xml:space="preserve">1.94702386856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89799845218658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142127037048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93581795692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01706075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97363817691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02266359329224</t>
   </si>
   <si>
     <t xml:space="preserve">2.08849859237671</t>
@@ -761,37 +761,37 @@
     <t xml:space="preserve">1.86017847061157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89099490642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78033649921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6738805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74251639842987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7383143901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64586555957794</t>
+    <t xml:space="preserve">1.8909946680069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78033638000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67388033866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74251663684845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73831427097321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64586579799652</t>
   </si>
   <si>
     <t xml:space="preserve">1.75512325763702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8405681848526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77753520011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78173732757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68368542194366</t>
+    <t xml:space="preserve">1.84056842327118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77753496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7817370891571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68368566036224</t>
   </si>
   <si>
     <t xml:space="preserve">1.6220531463623</t>
@@ -800,40 +800,40 @@
     <t xml:space="preserve">1.51419639587402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65006792545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71870386600494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71450173854828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68228471279144</t>
+    <t xml:space="preserve">1.65006768703461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71870398521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71450161933899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68228459358215</t>
   </si>
   <si>
     <t xml:space="preserve">1.6934906244278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69629204273224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80975222587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81535470485687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80695033073425</t>
+    <t xml:space="preserve">1.69629216194153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80975198745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81535482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072609424591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80695021152496</t>
   </si>
   <si>
     <t xml:space="preserve">1.86858284473419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85597610473633</t>
+    <t xml:space="preserve">1.85597622394562</t>
   </si>
   <si>
     <t xml:space="preserve">1.91620790958405</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">1.88539159297943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88819324970245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94562339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90360105037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89939904212952</t>
+    <t xml:space="preserve">1.88819336891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94562351703644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90360128879547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89939892292023</t>
   </si>
   <si>
     <t xml:space="preserve">1.87978863716125</t>
@@ -869,40 +869,40 @@
     <t xml:space="preserve">1.76212680339813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9554283618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86157917976379</t>
+    <t xml:space="preserve">1.95542848110199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86157929897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.86998355388641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445413589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04647636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91900956630707</t>
+    <t xml:space="preserve">2.00445437431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04647612571716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9190092086792</t>
   </si>
   <si>
     <t xml:space="preserve">1.87838792800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98204243183136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9638329744339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88259029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93021523952484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97784030437469</t>
+    <t xml:space="preserve">1.98204231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96383285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88258993625641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93021535873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97784018516541</t>
   </si>
   <si>
     <t xml:space="preserve">2.0941014289856</t>
@@ -911,61 +911,61 @@
     <t xml:space="preserve">2.17814540863037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11371183395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12491750717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9946494102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00305366516113</t>
+    <t xml:space="preserve">2.11371159553528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12491774559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99464917182922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00305342674255</t>
   </si>
   <si>
     <t xml:space="preserve">1.90220046043396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99885141849518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95262670516968</t>
+    <t xml:space="preserve">1.99885129928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95262694358826</t>
   </si>
   <si>
     <t xml:space="preserve">1.95402765274048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93441736698151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920424461365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91060495376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88679230213165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95823001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94422268867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99184775352478</t>
+    <t xml:space="preserve">1.9344174861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920412540436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91060507297516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88679254055023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95822978019714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94422256946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99184787273407</t>
   </si>
   <si>
     <t xml:space="preserve">2.06048369407654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05207920074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10950970649719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14592862129211</t>
+    <t xml:space="preserve">2.05207943916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10950946807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14592838287354</t>
   </si>
   <si>
     <t xml:space="preserve">2.0955023765564</t>
@@ -983,52 +983,52 @@
     <t xml:space="preserve">2.20616054534912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20896196365356</t>
+    <t xml:space="preserve">2.20896172523499</t>
   </si>
   <si>
     <t xml:space="preserve">2.19915676116943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19635534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14172649383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2033588886261</t>
+    <t xml:space="preserve">2.19635510444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14172673225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20335865020752</t>
   </si>
   <si>
     <t xml:space="preserve">2.19215297698975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15573358535767</t>
+    <t xml:space="preserve">2.15573406219482</t>
   </si>
   <si>
     <t xml:space="preserve">2.16413831710815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16273736953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20756101608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997283935547</t>
+    <t xml:space="preserve">2.16273760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20756125450134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997260093689</t>
   </si>
   <si>
     <t xml:space="preserve">2.28320097923279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34063124656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35884094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33082604408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30561280250549</t>
+    <t xml:space="preserve">2.34063100814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35884070396423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33082580566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30561256408691</t>
   </si>
   <si>
     <t xml:space="preserve">2.26499128341675</t>
@@ -1040,52 +1040,52 @@
     <t xml:space="preserve">2.30981492996216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27339553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32242178916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2271716594696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26078915596008</t>
+    <t xml:space="preserve">2.27339577674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32242155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22717142105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2607889175415</t>
   </si>
   <si>
     <t xml:space="preserve">2.22016787528992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23277449607849</t>
+    <t xml:space="preserve">2.23277425765991</t>
   </si>
   <si>
     <t xml:space="preserve">2.2621898651123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21036243438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15993595123291</t>
+    <t xml:space="preserve">2.21036267280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15993618965149</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1011049747467</t>
+    <t xml:space="preserve">2.10110545158386</t>
   </si>
   <si>
     <t xml:space="preserve">2.13052082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1893515586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25518608093262</t>
+    <t xml:space="preserve">2.18935132026672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25518584251404</t>
   </si>
   <si>
     <t xml:space="preserve">2.29300594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30421209335327</t>
+    <t xml:space="preserve">2.30421185493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.30141043663025</t>
@@ -1097,34 +1097,34 @@
     <t xml:space="preserve">2.33782982826233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28180003166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33642911911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43448066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45409107208252</t>
+    <t xml:space="preserve">2.28180027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33642888069153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43448042869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45409059524536</t>
   </si>
   <si>
     <t xml:space="preserve">2.4568920135498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43307995796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43027830123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2411789894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17954611778259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1319215297699</t>
+    <t xml:space="preserve">2.43307971954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43027806282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24117875099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17954635620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13192129135132</t>
   </si>
   <si>
     <t xml:space="preserve">2.23417520523071</t>
@@ -1133,25 +1133,25 @@
     <t xml:space="preserve">2.20475959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19075226783752</t>
+    <t xml:space="preserve">2.1907525062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.15153169631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20195817947388</t>
+    <t xml:space="preserve">2.20195841789246</t>
   </si>
   <si>
     <t xml:space="preserve">2.18374848365784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21456480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17674469947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1683406829834</t>
+    <t xml:space="preserve">2.21456456184387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17674493789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16834044456482</t>
   </si>
   <si>
     <t xml:space="preserve">2.09690260887146</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">2.1025059223175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1333224773407</t>
+    <t xml:space="preserve">2.13332200050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.10810875892639</t>
@@ -1169,94 +1169,94 @@
     <t xml:space="preserve">2.09130001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04507541656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9708366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91200578212738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92741370201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88959395885468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87558627128601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566028594971</t>
+    <t xml:space="preserve">2.04507565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97083640098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91200566291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9274138212204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88959383964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8755863904953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566004753113</t>
   </si>
   <si>
     <t xml:space="preserve">1.97924101352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9694356918335</t>
+    <t xml:space="preserve">1.96943593025208</t>
   </si>
   <si>
     <t xml:space="preserve">1.92321157455444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96523368358612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181086540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83496522903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76492810249329</t>
+    <t xml:space="preserve">1.96523332595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181074619293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83496510982513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76492834091187</t>
   </si>
   <si>
     <t xml:space="preserve">1.75232172012329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77193200588226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78313803672791</t>
+    <t xml:space="preserve">1.77193188667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78313791751862</t>
   </si>
   <si>
     <t xml:space="preserve">1.82656073570251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86438071727753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85177385807037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395399570465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86578142642975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84897243976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88399112224579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99745047092438</t>
+    <t xml:space="preserve">1.86438059806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85177409648895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395387649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86578130722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84897255897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88399076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99745070934296</t>
   </si>
   <si>
     <t xml:space="preserve">2.04787707328796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04367470741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99604988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08429646492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11931467056274</t>
+    <t xml:space="preserve">2.0436749458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99604952335358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08429622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11931490898132</t>
   </si>
   <si>
     <t xml:space="preserve">2.15013098716736</t>
@@ -1268,91 +1268,91 @@
     <t xml:space="preserve">2.18725061416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12701869010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14557862281799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10355615615845</t>
+    <t xml:space="preserve">2.12701892852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14557838439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10355639457703</t>
   </si>
   <si>
     <t xml:space="preserve">2.10320615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02826690673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04927778244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363264083862</t>
+    <t xml:space="preserve">2.0282666683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04927802085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1536328792572</t>
   </si>
   <si>
     <t xml:space="preserve">2.16028642654419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10600757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03772163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11721348762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08009386062622</t>
+    <t xml:space="preserve">2.10600781440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03772187232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1172137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08009433746338</t>
   </si>
   <si>
     <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12736868858337</t>
+    <t xml:space="preserve">2.12736916542053</t>
   </si>
   <si>
     <t xml:space="preserve">2.1525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18584966659546</t>
+    <t xml:space="preserve">2.18584990501404</t>
   </si>
   <si>
     <t xml:space="preserve">2.14207696914673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425415992737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19005227088928</t>
+    <t xml:space="preserve">2.19425392150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19005179405212</t>
   </si>
   <si>
     <t xml:space="preserve">2.2030086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17604446411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18865132331848</t>
+    <t xml:space="preserve">2.17604494094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1886510848999</t>
   </si>
   <si>
     <t xml:space="preserve">2.01005721092224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08709788322449</t>
+    <t xml:space="preserve">2.08709764480591</t>
   </si>
   <si>
     <t xml:space="preserve">2.12771916389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07624197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06643676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11441230773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08394646644592</t>
+    <t xml:space="preserve">2.07624173164368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0664370059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11441206932068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08394622802734</t>
   </si>
   <si>
     <t xml:space="preserve">2.13822460174561</t>
@@ -1361,19 +1361,19 @@
     <t xml:space="preserve">2.12036514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12071537971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9634827375412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98274290561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98729538917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293782234192</t>
+    <t xml:space="preserve">2.12071561813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96348261833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98274302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9872955083847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293746471405</t>
   </si>
   <si>
     <t xml:space="preserve">1.96838521957397</t>
@@ -1385,40 +1385,40 @@
     <t xml:space="preserve">2.03422021865845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00620532035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01601028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03492045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10915946960449</t>
+    <t xml:space="preserve">2.0062050819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01601052284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03492021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10915923118591</t>
   </si>
   <si>
     <t xml:space="preserve">2.10775899887085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14382767677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12421727180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14662909507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11791372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15888547897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13857483863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14487814903259</t>
+    <t xml:space="preserve">2.14382743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12421751022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14662933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11791396141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15888524055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13857507705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14487838745117</t>
   </si>
   <si>
     <t xml:space="preserve">2.08289551734924</t>
@@ -1427,34 +1427,34 @@
     <t xml:space="preserve">2.14347743988037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05453085899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07028889656067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09970426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86087882518768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8752361536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84442019462585</t>
+    <t xml:space="preserve">2.05453038215637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07028913497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09970450401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86087870597839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87523627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84442031383514</t>
   </si>
   <si>
     <t xml:space="preserve">1.82165813446045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57687950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47077357769012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51839852333069</t>
+    <t xml:space="preserve">1.57687938213348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47077369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51839864253998</t>
   </si>
   <si>
     <t xml:space="preserve">1.55446767807007</t>
@@ -1466,31 +1466,31 @@
     <t xml:space="preserve">1.63641059398651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59648978710175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68018364906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61259806156158</t>
+    <t xml:space="preserve">1.59648954868317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68018388748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61259818077087</t>
   </si>
   <si>
     <t xml:space="preserve">1.71170020103455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69874322414398</t>
+    <t xml:space="preserve">1.69874346256256</t>
   </si>
   <si>
     <t xml:space="preserve">1.72465717792511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69138967990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67808258533478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81990718841553</t>
+    <t xml:space="preserve">1.69138956069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67808270454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81990730762482</t>
   </si>
   <si>
     <t xml:space="preserve">1.78804039955139</t>
@@ -1499,37 +1499,37 @@
     <t xml:space="preserve">1.84792184829712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78068673610687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73481237888336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70364582538605</t>
+    <t xml:space="preserve">1.780686378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73481225967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70364606380463</t>
   </si>
   <si>
     <t xml:space="preserve">1.7740330696106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80589997768402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8258603811264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173438072205</t>
+    <t xml:space="preserve">1.80589985847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82586073875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173449993134</t>
   </si>
   <si>
     <t xml:space="preserve">1.89274573326111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87243485450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823260784149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85912811756134</t>
+    <t xml:space="preserve">1.87243473529816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823284626007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85912799835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.83286416530609</t>
@@ -1538,64 +1538,64 @@
     <t xml:space="preserve">1.81605505943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85072326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601593971252</t>
+    <t xml:space="preserve">1.85072314739227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601570129395</t>
   </si>
   <si>
     <t xml:space="preserve">1.85807740688324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85387492179871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76807975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7533723115921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64901733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64621591567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65216898918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61960172653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57092618942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53030478954315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46972322463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4263002872467</t>
+    <t xml:space="preserve">1.853875041008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76807987689972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75337207317352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64901745319366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64621579647064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337502002716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65216910839081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61960196495056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5709263086319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53030490875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46972298622131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42630016803741</t>
   </si>
   <si>
     <t xml:space="preserve">1.42524969577789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4550154209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44380950927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43190312385559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44415974617004</t>
+    <t xml:space="preserve">1.45501530170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44380939006805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43190324306488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44415962696075</t>
   </si>
   <si>
     <t xml:space="preserve">1.43925702571869</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">1.43120276927948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40178716182709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.358154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37132108211517</t>
+    <t xml:space="preserve">1.40178728103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35815441608429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37132132053375</t>
   </si>
   <si>
     <t xml:space="preserve">1.50719273090363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49493622779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54326152801514</t>
+    <t xml:space="preserve">1.49493646621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54326176643372</t>
   </si>
   <si>
     <t xml:space="preserve">1.5355578660965</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">1.5502655506134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61084723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61539959907532</t>
+    <t xml:space="preserve">1.61084711551666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61539947986603</t>
   </si>
   <si>
     <t xml:space="preserve">1.61609995365143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62625551223755</t>
+    <t xml:space="preserve">1.62625539302826</t>
   </si>
   <si>
     <t xml:space="preserve">1.62415421009064</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">1.64446496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64866733551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48688197135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40143716335297</t>
+    <t xml:space="preserve">1.64866721630096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48688209056854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40143704414368</t>
   </si>
   <si>
     <t xml:space="preserve">1.37356233596802</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">1.40283787250519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41439414024353</t>
+    <t xml:space="preserve">1.41439390182495</t>
   </si>
   <si>
     <t xml:space="preserve">1.38602900505066</t>
@@ -1679,19 +1679,19 @@
     <t xml:space="preserve">1.31108951568604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30520641803741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31136977672577</t>
+    <t xml:space="preserve">1.3052065372467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31136965751648</t>
   </si>
   <si>
     <t xml:space="preserve">1.3166925907135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30758774280548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29960358142853</t>
+    <t xml:space="preserve">1.30758786201477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29960346221924</t>
   </si>
   <si>
     <t xml:space="preserve">1.22550463676453</t>
@@ -1700,22 +1700,22 @@
     <t xml:space="preserve">1.20673477649689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16905474662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14692330360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09229457378387</t>
+    <t xml:space="preserve">1.1690548658371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14692318439484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09229445457458</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134457588196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0897730588913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14440178871155</t>
+    <t xml:space="preserve">1.08977317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14440190792084</t>
   </si>
   <si>
     <t xml:space="preserve">1.16345202922821</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">1.16331195831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19608902931213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23965191841125</t>
+    <t xml:space="preserve">1.19608926773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23965203762054</t>
   </si>
   <si>
     <t xml:space="preserve">1.2131781578064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22410380840302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25478005409241</t>
+    <t xml:space="preserve">1.22410368919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2547801733017</t>
   </si>
   <si>
     <t xml:space="preserve">1.29217970371246</t>
@@ -1754,22 +1754,22 @@
     <t xml:space="preserve">1.23923182487488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22606480121613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256290912628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26262402534485</t>
+    <t xml:space="preserve">1.22606492042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256302833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26262414455414</t>
   </si>
   <si>
     <t xml:space="preserve">1.19412815570831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28517603874207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32341611385345</t>
+    <t xml:space="preserve">1.28517591953278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32341599464417</t>
   </si>
   <si>
     <t xml:space="preserve">1.38770985603333</t>
@@ -1784,25 +1784,25 @@
     <t xml:space="preserve">1.47147405147552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44836187362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53940975666046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54571306705475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55796933174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47917795181274</t>
+    <t xml:space="preserve">1.44836175441742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53940951824188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54571294784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55796945095062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47917807102203</t>
   </si>
   <si>
     <t xml:space="preserve">1.46376979351044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44801151752472</t>
+    <t xml:space="preserve">1.4480117559433</t>
   </si>
   <si>
     <t xml:space="preserve">1.48478090763092</t>
@@ -1814,16 +1814,16 @@
     <t xml:space="preserve">1.47007310390472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44345939159393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40458881855011</t>
+    <t xml:space="preserve">1.44345927238464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4045889377594</t>
   </si>
   <si>
     <t xml:space="preserve">1.39401316642761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43155288696289</t>
+    <t xml:space="preserve">1.43155300617218</t>
   </si>
   <si>
     <t xml:space="preserve">1.39443349838257</t>
@@ -1835,49 +1835,49 @@
     <t xml:space="preserve">1.32285583019257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39177215099335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37118113040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43330383300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44170832633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41509425640106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209792137146</t>
+    <t xml:space="preserve">1.39177203178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37118124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4333039522171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44170844554901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41509413719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209804058075</t>
   </si>
   <si>
     <t xml:space="preserve">1.42454922199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38224697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34918963909149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29344022274017</t>
+    <t xml:space="preserve">1.38224709033966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3491895198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29344034194946</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168041706085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32551717758179</t>
+    <t xml:space="preserve">1.3255170583725</t>
   </si>
   <si>
     <t xml:space="preserve">1.30058407783508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2948409318924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25996279716492</t>
+    <t xml:space="preserve">1.29484105110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25996267795563</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864719390869</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">1.24721598625183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27845239639282</t>
+    <t xml:space="preserve">1.27845251560211</t>
   </si>
   <si>
     <t xml:space="preserve">1.26206386089325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24917709827423</t>
+    <t xml:space="preserve">1.24917697906494</t>
   </si>
   <si>
     <t xml:space="preserve">1.24525499343872</t>
@@ -1901,70 +1901,70 @@
     <t xml:space="preserve">1.18474316596985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15182590484619</t>
+    <t xml:space="preserve">1.1518257856369</t>
   </si>
   <si>
     <t xml:space="preserve">1.19342768192291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21892106533051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2291464805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20897579193115</t>
+    <t xml:space="preserve">1.21892118453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22914659976959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20897591114044</t>
   </si>
   <si>
     <t xml:space="preserve">1.29400050640106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31851363182068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3141713142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2770516872406</t>
+    <t xml:space="preserve">1.31851351261139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31417119503021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27705156803131</t>
   </si>
   <si>
     <t xml:space="preserve">1.36571836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3850485086441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706410884857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969531536102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32775831222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31473159790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36011552810669</t>
+    <t xml:space="preserve">1.38504838943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706422805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969519615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32775819301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3147314786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3601154088974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40879082679749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47287464141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49318540096283</t>
+    <t xml:space="preserve">1.47287452220917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49318528175354</t>
   </si>
   <si>
     <t xml:space="preserve">1.46412014961243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43505489826202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41544449329376</t>
+    <t xml:space="preserve">1.43505477905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41544437408447</t>
   </si>
   <si>
     <t xml:space="preserve">1.37566363811493</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35675370693207</t>
+    <t xml:space="preserve">1.35675358772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.34372675418854</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">1.4031879901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37720429897308</t>
+    <t xml:space="preserve">1.37720441818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.43015229701996</t>
@@ -1994,16 +1994,16 @@
     <t xml:space="preserve">1.38112640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3210346698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30296528339386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28615653514862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32019448280334</t>
+    <t xml:space="preserve">1.32103490829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30296516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28615641593933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32019436359406</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937816619873</t>
@@ -2018,34 +2018,34 @@
     <t xml:space="preserve">1.33175051212311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35941505432129</t>
+    <t xml:space="preserve">1.359414935112</t>
   </si>
   <si>
     <t xml:space="preserve">1.36606860160828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36641848087311</t>
+    <t xml:space="preserve">1.3664186000824</t>
   </si>
   <si>
     <t xml:space="preserve">1.36221647262573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37587368488312</t>
+    <t xml:space="preserve">1.37587380409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.37727439403534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37622392177582</t>
+    <t xml:space="preserve">1.37622380256653</t>
   </si>
   <si>
     <t xml:space="preserve">1.43575513362885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45956766605377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828279972076</t>
+    <t xml:space="preserve">1.45956778526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828268051147</t>
   </si>
   <si>
     <t xml:space="preserve">1.43855655193329</t>
@@ -2054,31 +2054,31 @@
     <t xml:space="preserve">1.49178469181061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48127925395966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44205856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38077616691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38532865047455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27221894264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24595546722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19973111152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19062626361847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19798016548157</t>
+    <t xml:space="preserve">1.48127913475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44205844402313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38077628612518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38532853126526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2722190618515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24595522880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1997309923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19062614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19798004627228</t>
   </si>
   <si>
     <t xml:space="preserve">1.24945724010468</t>
@@ -2093,28 +2093,28 @@
     <t xml:space="preserve">1.18082106113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15525770187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17171633243561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14370143413544</t>
+    <t xml:space="preserve">1.15525758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17171621322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14370167255402</t>
   </si>
   <si>
     <t xml:space="preserve">1.13914918899536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14930462837219</t>
+    <t xml:space="preserve">1.1493045091629</t>
   </si>
   <si>
     <t xml:space="preserve">1.16261148452759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15350663661957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19377791881561</t>
+    <t xml:space="preserve">1.15350675582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19377779960632</t>
   </si>
   <si>
     <t xml:space="preserve">1.16716384887695</t>
@@ -2123,25 +2123,25 @@
     <t xml:space="preserve">1.14160048961639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18432283401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19482851028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16821455955505</t>
+    <t xml:space="preserve">1.18432295322418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19482839107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16821444034576</t>
   </si>
   <si>
     <t xml:space="preserve">1.1710159778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15700840950012</t>
+    <t xml:space="preserve">1.15700852870941</t>
   </si>
   <si>
     <t xml:space="preserve">1.20323288440704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25365924835205</t>
+    <t xml:space="preserve">1.25365936756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.24560511112213</t>
@@ -2150,31 +2150,31 @@
     <t xml:space="preserve">1.23790109157562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23474955558777</t>
+    <t xml:space="preserve">1.23474943637848</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875676631927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451516151428</t>
+    <t xml:space="preserve">1.26451504230499</t>
   </si>
   <si>
     <t xml:space="preserve">1.24105262756348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23825120925903</t>
+    <t xml:space="preserve">1.23825132846832</t>
   </si>
   <si>
     <t xml:space="preserve">1.31949400901794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36256682872772</t>
+    <t xml:space="preserve">1.36256670951843</t>
   </si>
   <si>
     <t xml:space="preserve">1.36992049217224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33525228500366</t>
+    <t xml:space="preserve">1.33525252342224</t>
   </si>
   <si>
     <t xml:space="preserve">1.32264566421509</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">1.33350145816803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33630287647247</t>
+    <t xml:space="preserve">1.33630275726318</t>
   </si>
   <si>
     <t xml:space="preserve">1.34295630455017</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">1.31214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34575772285461</t>
+    <t xml:space="preserve">1.3457578420639</t>
   </si>
   <si>
     <t xml:space="preserve">1.32439661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914389133453</t>
+    <t xml:space="preserve">1.31914365291595</t>
   </si>
   <si>
     <t xml:space="preserve">1.22634506225586</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">1.23159778118134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2372008562088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23124766349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21163725852966</t>
+    <t xml:space="preserve">1.23720061779022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23124742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21163737773895</t>
   </si>
   <si>
     <t xml:space="preserve">1.17241668701172</t>
@@ -2222,16 +2222,16 @@
     <t xml:space="preserve">1.18222177028656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18817496299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1846729516983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18607378005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24210321903229</t>
+    <t xml:space="preserve">1.18817472457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18467307090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1860738992691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24210333824158</t>
   </si>
   <si>
     <t xml:space="preserve">1.26731646060944</t>
@@ -2240,49 +2240,49 @@
     <t xml:space="preserve">1.15175592899323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13529706001282</t>
+    <t xml:space="preserve">1.13529717922211</t>
   </si>
   <si>
     <t xml:space="preserve">1.18047094345093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13424646854401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18012070655823</t>
+    <t xml:space="preserve">1.13424670696259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18012058734894</t>
   </si>
   <si>
     <t xml:space="preserve">1.20603430271149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17521822452545</t>
+    <t xml:space="preserve">1.17521810531616</t>
   </si>
   <si>
     <t xml:space="preserve">1.18992590904236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21583938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21653997898102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23404908180237</t>
+    <t xml:space="preserve">1.21583950519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21653985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23404896259308</t>
   </si>
   <si>
     <t xml:space="preserve">1.27467048168182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28657674789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32579731941223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28132379055023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27186906337738</t>
+    <t xml:space="preserve">1.286576628685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32579720020294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28132390975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27186894416809</t>
   </si>
   <si>
     <t xml:space="preserve">1.26906752586365</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">1.32474672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31844353675842</t>
+    <t xml:space="preserve">1.31844341754913</t>
   </si>
   <si>
     <t xml:space="preserve">1.35171091556549</t>
@@ -2303,40 +2303,40 @@
     <t xml:space="preserve">1.31424129009247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34050512313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3681697845459</t>
+    <t xml:space="preserve">1.34050500392914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36816954612732</t>
   </si>
   <si>
     <t xml:space="preserve">1.35066044330597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29743230342865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31003892421722</t>
+    <t xml:space="preserve">1.29743242263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31003904342651</t>
   </si>
   <si>
     <t xml:space="preserve">1.33980476856232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33210074901581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29007863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27081835269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27537095546722</t>
+    <t xml:space="preserve">1.33210051059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29007852077484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27081847190857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27537071704865</t>
   </si>
   <si>
     <t xml:space="preserve">1.28762722015381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31249022483826</t>
+    <t xml:space="preserve">1.31249034404755</t>
   </si>
   <si>
     <t xml:space="preserve">1.32789850234985</t>
@@ -2351,16 +2351,16 @@
     <t xml:space="preserve">1.42384898662567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50929379463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50859367847443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49598670005798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47707676887512</t>
+    <t xml:space="preserve">1.50929391384125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50859344005585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49598681926727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47707688808441</t>
   </si>
   <si>
     <t xml:space="preserve">1.4686723947525</t>
@@ -2372,13 +2372,13 @@
     <t xml:space="preserve">1.42665028572083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47777712345123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49528634548187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49388575553894</t>
+    <t xml:space="preserve">1.47777724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49528646469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49388563632965</t>
   </si>
   <si>
     <t xml:space="preserve">1.44766128063202</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">1.42104744911194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41264283657074</t>
+    <t xml:space="preserve">1.41264295578003</t>
   </si>
   <si>
     <t xml:space="preserve">1.41754555702209</t>
@@ -2399,34 +2399,34 @@
     <t xml:space="preserve">1.44135820865631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4553656578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46517074108124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43085253238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41824591159821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38813030719757</t>
+    <t xml:space="preserve">1.45536553859711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46517062187195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43085265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4182460308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38813006877899</t>
   </si>
   <si>
     <t xml:space="preserve">1.37412285804749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41474401950836</t>
+    <t xml:space="preserve">1.41474413871765</t>
   </si>
   <si>
     <t xml:space="preserve">1.4035382270813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4098414182663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45326459407806</t>
+    <t xml:space="preserve">1.40984153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45326447486877</t>
   </si>
   <si>
     <t xml:space="preserve">1.42034709453583</t>
@@ -2435,37 +2435,37 @@
     <t xml:space="preserve">1.36851990222931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37797474861145</t>
+    <t xml:space="preserve">1.37797462940216</t>
   </si>
   <si>
     <t xml:space="preserve">1.38637924194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4616687297821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42595016956329</t>
+    <t xml:space="preserve">1.46166884899139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.425950050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.43435454368591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43365395069122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287711143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36886990070343</t>
+    <t xml:space="preserve">1.43365406990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287723064423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36887001991272</t>
   </si>
   <si>
     <t xml:space="preserve">1.39373314380646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36431741714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29568135738373</t>
+    <t xml:space="preserve">1.36431765556335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29568147659302</t>
   </si>
   <si>
     <t xml:space="preserve">1.35836446285248</t>
@@ -2474,91 +2474,91 @@
     <t xml:space="preserve">1.37307226657867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727180480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5204998254776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54641330242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72010493278503</t>
+    <t xml:space="preserve">1.46727168560028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52049970626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54641342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72010445594788</t>
   </si>
   <si>
     <t xml:space="preserve">1.44626080989838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38848030567169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30128455162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1423008441925</t>
+    <t xml:space="preserve">1.3884801864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128443241119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14230072498322</t>
   </si>
   <si>
     <t xml:space="preserve">1.09397554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05755627155304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905926525592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861103057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926937460899353</t>
+    <t xml:space="preserve">1.05755615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905926406383514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861102998256683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926937520503998</t>
   </si>
   <si>
     <t xml:space="preserve">0.772156059741974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888417363166809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81803023815155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874409973621368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874760091304779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885966002941132</t>
+    <t xml:space="preserve">0.888417303562164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818030297756195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874409794807434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87475997209549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885965943336487</t>
   </si>
   <si>
     <t xml:space="preserve">0.877561628818512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870207726955414</t>
+    <t xml:space="preserve">0.870207607746124</t>
   </si>
   <si>
     <t xml:space="preserve">0.926587402820587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912930190563202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925886929035187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880713224411011</t>
+    <t xml:space="preserve">0.912930369377136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925887048244476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880713284015656</t>
   </si>
   <si>
     <t xml:space="preserve">0.84919661283493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8404421210289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823633134365082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846044957637787</t>
+    <t xml:space="preserve">0.840442061424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823633253574371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846044898033142</t>
   </si>
   <si>
     <t xml:space="preserve">0.830987095832825</t>
@@ -2570,16 +2570,16 @@
     <t xml:space="preserve">0.829936504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853048801422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820131361484528</t>
+    <t xml:space="preserve">0.853048741817474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820131421089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.77740889787674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778459548950195</t>
+    <t xml:space="preserve">0.778459429740906</t>
   </si>
   <si>
     <t xml:space="preserve">0.778809607028961</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">0.751845479011536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771805882453918</t>
+    <t xml:space="preserve">0.771805942058563</t>
   </si>
   <si>
     <t xml:space="preserve">0.743791222572327</t>
@@ -2600,49 +2600,49 @@
     <t xml:space="preserve">0.768304109573364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789665341377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809625864028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779860138893127</t>
+    <t xml:space="preserve">0.789665400981903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809625804424286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779860198497772</t>
   </si>
   <si>
     <t xml:space="preserve">0.766553103923798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781611084938049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776008248329163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765152394771576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803672790527344</t>
+    <t xml:space="preserve">0.781611204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776008129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765152454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803672730922699</t>
   </si>
   <si>
     <t xml:space="preserve">0.812077105045319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807874917984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785463094711304</t>
+    <t xml:space="preserve">0.807874858379364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785463154315948</t>
   </si>
   <si>
     <t xml:space="preserve">0.781260907649994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819080829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759199261665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75604772567749</t>
+    <t xml:space="preserve">0.819080770015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759199321269989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756047666072845</t>
   </si>
   <si>
     <t xml:space="preserve">0.730484187602997</t>
@@ -2651,97 +2651,97 @@
     <t xml:space="preserve">0.736087203025818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743440985679626</t>
+    <t xml:space="preserve">0.743441045284271</t>
   </si>
   <si>
     <t xml:space="preserve">0.779159784317017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815228700637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805773854255676</t>
+    <t xml:space="preserve">0.815228819847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805773913860321</t>
   </si>
   <si>
     <t xml:space="preserve">0.858301401138306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872308731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892969608306885</t>
+    <t xml:space="preserve">0.872308790683746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">0.931840121746063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994873285293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00853049755096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979115009307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966858506202698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891218781471252</t>
+    <t xml:space="preserve">0.994873344898224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00853037834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979114890098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966858446598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891218841075897</t>
   </si>
   <si>
     <t xml:space="preserve">0.895070731639862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901724278926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967909157276154</t>
+    <t xml:space="preserve">0.901724338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967908978462219</t>
   </si>
   <si>
     <t xml:space="preserve">0.964407324790955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946897983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936392486095428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938493609428406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965107619762421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913980782032013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934641599655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899623095989227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953551590442657</t>
+    <t xml:space="preserve">0.94689804315567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936392545700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938493549823761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965107679367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913980722427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934641540050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899623036384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953551650047302</t>
   </si>
   <si>
     <t xml:space="preserve">0.930089235305786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.909078121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954602122306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943746447563171</t>
+    <t xml:space="preserve">0.909078180789948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954602062702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943746268749237</t>
   </si>
   <si>
     <t xml:space="preserve">0.983317196369171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97316187620163</t>
+    <t xml:space="preserve">0.973161935806274</t>
   </si>
   <si>
     <t xml:space="preserve">0.951450407505035</t>
@@ -2753,73 +2753,73 @@
     <t xml:space="preserve">0.933941245079041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948298692703247</t>
+    <t xml:space="preserve">0.948298811912537</t>
   </si>
   <si>
     <t xml:space="preserve">0.957403481006622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973512172698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980866014957428</t>
+    <t xml:space="preserve">0.973511934280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980865776538849</t>
   </si>
   <si>
     <t xml:space="preserve">1.03304326534271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03759574890137</t>
+    <t xml:space="preserve">1.03759586811066</t>
   </si>
   <si>
     <t xml:space="preserve">1.00012612342834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998725235462189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960905432701111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967208683490753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944096624851227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89367002248764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890168249607086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874059677124023</t>
+    <t xml:space="preserve">0.998725354671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960905373096466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967208743095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944096684455872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893670082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890168190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874059855937958</t>
   </si>
   <si>
     <t xml:space="preserve">0.913280367851257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927637875080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907677352428436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890868663787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91538143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978764772415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971060812473297</t>
+    <t xml:space="preserve">0.927637934684753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907677412033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890868544578552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915381491184235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978764891624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971060752868652</t>
   </si>
   <si>
     <t xml:space="preserve">1.00572896003723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997324705123901</t>
+    <t xml:space="preserve">0.997324585914612</t>
   </si>
   <si>
     <t xml:space="preserve">0.981566250324249</t>
@@ -2828,67 +2828,67 @@
     <t xml:space="preserve">1.00923085212708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98681902885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987519502639771</t>
+    <t xml:space="preserve">0.986819088459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987519443035126</t>
   </si>
   <si>
     <t xml:space="preserve">1.00712966918945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996624231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999775826931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00467824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988920152187347</t>
+    <t xml:space="preserve">0.996624112129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999775767326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00467836856842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988920092582703</t>
   </si>
   <si>
     <t xml:space="preserve">0.985768556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970360338687897</t>
+    <t xml:space="preserve">0.970360279083252</t>
   </si>
   <si>
     <t xml:space="preserve">0.958103954792023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994523048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97841465473175</t>
+    <t xml:space="preserve">0.994523167610168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978414595127106</t>
   </si>
   <si>
     <t xml:space="preserve">0.986118674278259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03724563121796</t>
+    <t xml:space="preserve">1.03724551200867</t>
   </si>
   <si>
     <t xml:space="preserve">1.02148723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01903605461121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01203227043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9955735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97386234998703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916782259941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922735273838043</t>
+    <t xml:space="preserve">1.01903593540192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01203238964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995573461055756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973862171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916782140731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922735333442688</t>
   </si>
   <si>
     <t xml:space="preserve">0.888067126274109</t>
@@ -2900,22 +2900,22 @@
     <t xml:space="preserve">0.961605787277222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972811698913574</t>
+    <t xml:space="preserve">0.972811758518219</t>
   </si>
   <si>
     <t xml:space="preserve">1.0540543794632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11113440990448</t>
+    <t xml:space="preserve">1.11113452911377</t>
   </si>
   <si>
     <t xml:space="preserve">1.09957838058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16121089458466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.185023188591</t>
+    <t xml:space="preserve">1.16121077537537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18502330780029</t>
   </si>
   <si>
     <t xml:space="preserve">1.16961514949799</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">1.15910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12339103221893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12829339504242</t>
+    <t xml:space="preserve">1.12339091300964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12829351425171</t>
   </si>
   <si>
     <t xml:space="preserve">1.12794327735901</t>
@@ -2942,10 +2942,10 @@
     <t xml:space="preserve">1.1706657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14545238018036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15280640125275</t>
+    <t xml:space="preserve">1.14545249938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15280628204346</t>
   </si>
   <si>
     <t xml:space="preserve">1.17591857910156</t>
@@ -2954,25 +2954,25 @@
     <t xml:space="preserve">1.15560781955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13214552402496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08522093296051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05965733528137</t>
+    <t xml:space="preserve">1.13214540481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08522081375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05965745449066</t>
   </si>
   <si>
     <t xml:space="preserve">1.08627128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12899374961853</t>
+    <t xml:space="preserve">1.12899386882782</t>
   </si>
   <si>
     <t xml:space="preserve">1.15000486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15210604667664</t>
+    <t xml:space="preserve">1.15210592746735</t>
   </si>
   <si>
     <t xml:space="preserve">1.15490746498108</t>
@@ -2981,43 +2981,43 @@
     <t xml:space="preserve">1.15455722808838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066291332245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2512081861496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25611066818237</t>
+    <t xml:space="preserve">1.26066303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25120806694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25611078739166</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502071857452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30793797969818</t>
+    <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
     <t xml:space="preserve">1.32684791088104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35801422595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32334589958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31879377365112</t>
+    <t xml:space="preserve">1.35801434516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3233460187912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31879365444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.29603159427643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31389105319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30723774433136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29498100280762</t>
+    <t xml:space="preserve">1.31389117240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30723750591278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29498112201691</t>
   </si>
   <si>
     <t xml:space="preserve">1.28482580184937</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">1.26941764354706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2431538105011</t>
+    <t xml:space="preserve">1.24315392971039</t>
   </si>
   <si>
     <t xml:space="preserve">1.25435972213745</t>
@@ -3038,19 +3038,19 @@
     <t xml:space="preserve">1.27256941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26136350631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26661610603333</t>
+    <t xml:space="preserve">1.26136326789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26661622524261</t>
   </si>
   <si>
     <t xml:space="preserve">1.26416492462158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26521551609039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26766657829285</t>
+    <t xml:space="preserve">1.26521563529968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26766681671143</t>
   </si>
   <si>
     <t xml:space="preserve">1.26626598834991</t>
@@ -3059,70 +3059,70 @@
     <t xml:space="preserve">1.25856196880341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25821173191071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32964932918549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957049369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34505748748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34925973415375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33455193042755</t>
+    <t xml:space="preserve">1.25821161270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32964944839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957037448883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3450573682785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34925961494446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33455204963684</t>
   </si>
   <si>
     <t xml:space="preserve">1.31529188156128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31809318065643</t>
+    <t xml:space="preserve">1.31809341907501</t>
   </si>
   <si>
     <t xml:space="preserve">1.31073951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31774318218231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28062355518341</t>
+    <t xml:space="preserve">1.31774306297302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2806236743927</t>
   </si>
   <si>
     <t xml:space="preserve">1.24735605716705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26696634292603</t>
+    <t xml:space="preserve">1.26696646213531</t>
   </si>
   <si>
     <t xml:space="preserve">1.2501574754715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29112911224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27432024478912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29953348636627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34820914268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42174756526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52260088920593</t>
+    <t xml:space="preserve">1.29112923145294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27432036399841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29953360557556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34820926189423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42174780368805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52260100841522</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190053462982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53240585327148</t>
+    <t xml:space="preserve">1.53240609169006</t>
   </si>
   <si>
     <t xml:space="preserve">1.4980880022049</t>
@@ -3137,52 +3137,52 @@
     <t xml:space="preserve">1.51629745960236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50789320468903</t>
+    <t xml:space="preserve">1.50789332389832</t>
   </si>
   <si>
     <t xml:space="preserve">1.5197993516922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5485143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54361176490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60594463348389</t>
+    <t xml:space="preserve">1.54851448535919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54361188411713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60594475269318</t>
   </si>
   <si>
     <t xml:space="preserve">1.62695562839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62065243721008</t>
+    <t xml:space="preserve">1.62065231800079</t>
   </si>
   <si>
     <t xml:space="preserve">1.59053647518158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59193730354309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909393787384</t>
+    <t xml:space="preserve">1.5919371843338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909381866455</t>
   </si>
   <si>
     <t xml:space="preserve">1.70119476318359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72360646724701</t>
+    <t xml:space="preserve">1.72360634803772</t>
   </si>
   <si>
     <t xml:space="preserve">1.71029949188232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70469653606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71099996566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881994724274</t>
+    <t xml:space="preserve">1.70469677448273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71099984645844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881958961487</t>
   </si>
   <si>
     <t xml:space="preserve">1.70539689064026</t>
@@ -3191,34 +3191,34 @@
     <t xml:space="preserve">1.68998908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65356981754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63536012172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64936757087708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63466012477875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6283563375473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6654759645462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71505224704742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61877369880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5993744134903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6130256652832</t>
+    <t xml:space="preserve">1.65356957912445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6353600025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64936769008636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63466000556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62835645675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66547620296478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71505236625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61877381801605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59937429428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61302578449249</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308478355408</t>
@@ -3227,67 +3227,67 @@
     <t xml:space="preserve">1.65613555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67337930202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71936333179474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71289682388306</t>
+    <t xml:space="preserve">1.67337954044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71936309337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71289670467377</t>
   </si>
   <si>
     <t xml:space="preserve">1.70283782482147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445177078247</t>
+    <t xml:space="preserve">1.73445188999176</t>
   </si>
   <si>
     <t xml:space="preserve">1.71145975589752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74522912502289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893973350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76822102069855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81707882881165</t>
+    <t xml:space="preserve">1.74522924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893961429596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76822090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81707894802094</t>
   </si>
   <si>
     <t xml:space="preserve">1.83504128456116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85587775707245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86449956893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95934128761292</t>
+    <t xml:space="preserve">1.85587763786316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8644996881485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126107215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95934116840363</t>
   </si>
   <si>
     <t xml:space="preserve">1.9729927778244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98377013206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94066035747528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96508932113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99742186069489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02400612831116</t>
+    <t xml:space="preserve">1.98377025127411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94066047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96508920192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99742150306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02400588989258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03334641456604</t>
@@ -3299,49 +3299,49 @@
     <t xml:space="preserve">2.08795213699341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10375905036926</t>
+    <t xml:space="preserve">2.10375928878784</t>
   </si>
   <si>
     <t xml:space="preserve">2.12531399726868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13465476036072</t>
+    <t xml:space="preserve">2.13465452194214</t>
   </si>
   <si>
     <t xml:space="preserve">2.1540539264679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15189814567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18423104286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17201638221741</t>
+    <t xml:space="preserve">2.15189838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18423080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17201662063599</t>
   </si>
   <si>
     <t xml:space="preserve">2.17991971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17560887336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17632722854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16052031517029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12818813323975</t>
+    <t xml:space="preserve">2.17560911178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1763277053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16052055358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12818789482117</t>
   </si>
   <si>
     <t xml:space="preserve">2.08938932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08076739311218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05346465110779</t>
+    <t xml:space="preserve">2.0807671546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05346441268921</t>
   </si>
   <si>
     <t xml:space="preserve">2.08292269706726</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">2.04771637916565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04196834564209</t>
+    <t xml:space="preserve">2.04196858406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.01897644996643</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">2.04053139686584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9830516576767</t>
+    <t xml:space="preserve">1.98305153846741</t>
   </si>
   <si>
     <t xml:space="preserve">1.96652626991272</t>
@@ -3371,16 +3371,16 @@
     <t xml:space="preserve">1.95215630531311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90114307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83288598060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93922340869904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93634951114655</t>
+    <t xml:space="preserve">1.90114295482635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8328857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93922317028046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93634915351868</t>
   </si>
   <si>
     <t xml:space="preserve">1.91766846179962</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">1.88821017742157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88749170303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84653723239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7876204252243</t>
+    <t xml:space="preserve">1.88749158382416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8465371131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78762054443359</t>
   </si>
   <si>
     <t xml:space="preserve">1.8264194726944</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">1.85803318023682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90258002281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87743258476257</t>
+    <t xml:space="preserve">1.9025799036026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87743234634399</t>
   </si>
   <si>
     <t xml:space="preserve">1.89108407497406</t>
@@ -3419,22 +3419,22 @@
     <t xml:space="preserve">1.82067131996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81348633766174</t>
+    <t xml:space="preserve">1.81348645687103</t>
   </si>
   <si>
     <t xml:space="preserve">1.82857489585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96724474430084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97371125221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95718562602997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03190946578979</t>
+    <t xml:space="preserve">1.96724486351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97371113300323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95718574523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03190970420837</t>
   </si>
   <si>
     <t xml:space="preserve">2.00676202774048</t>
@@ -3443,16 +3443,16 @@
     <t xml:space="preserve">2.00388813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97155582904816</t>
+    <t xml:space="preserve">1.97155570983887</t>
   </si>
   <si>
     <t xml:space="preserve">1.93347537517548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90904653072357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9420975446701</t>
+    <t xml:space="preserve">1.90904641151428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94209742546082</t>
   </si>
   <si>
     <t xml:space="preserve">1.97802209854126</t>
@@ -3461,25 +3461,25 @@
     <t xml:space="preserve">2.01107311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99957728385925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01753950119019</t>
+    <t xml:space="preserve">1.99957692623138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01753973960876</t>
   </si>
   <si>
     <t xml:space="preserve">2.03262782096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03119111061096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99167358875275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01322841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9794590473175</t>
+    <t xml:space="preserve">2.03119087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99167394638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01322865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97945916652679</t>
   </si>
   <si>
     <t xml:space="preserve">1.95000076293945</t>
@@ -3491,25 +3491,25 @@
     <t xml:space="preserve">1.96868193149567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92269825935364</t>
+    <t xml:space="preserve">1.92269814014435</t>
   </si>
   <si>
     <t xml:space="preserve">1.94712686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92916429042816</t>
+    <t xml:space="preserve">1.92916417121887</t>
   </si>
   <si>
     <t xml:space="preserve">1.83073043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84078907966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92054235935211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97586667537689</t>
+    <t xml:space="preserve">1.84078931808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9205424785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9758665561676</t>
   </si>
   <si>
     <t xml:space="preserve">1.9234162569046</t>
@@ -3518,19 +3518,19 @@
     <t xml:space="preserve">1.94353449344635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94425296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91838693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616167068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02831721305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0218505859375</t>
+    <t xml:space="preserve">1.94425284862518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91838705539703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616143226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02831697463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02185034751892</t>
   </si>
   <si>
     <t xml:space="preserve">2.03047251701355</t>
@@ -3539,19 +3539,19 @@
     <t xml:space="preserve">1.93994212150574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04340553283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10016655921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12387704849243</t>
+    <t xml:space="preserve">2.04340577125549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10016679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12387728691101</t>
   </si>
   <si>
     <t xml:space="preserve">2.09226322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1231586933136</t>
+    <t xml:space="preserve">2.12315845489502</t>
   </si>
   <si>
     <t xml:space="preserve">2.1303436756134</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">2.14758729934692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10950708389282</t>
+    <t xml:space="preserve">2.1095073223114</t>
   </si>
   <si>
     <t xml:space="preserve">2.08148574829102</t>
@@ -3569,67 +3569,67 @@
     <t xml:space="preserve">1.92988300323486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93563079833984</t>
+    <t xml:space="preserve">1.93563103675842</t>
   </si>
   <si>
     <t xml:space="preserve">1.97083735466003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00963616371155</t>
+    <t xml:space="preserve">2.00963592529297</t>
   </si>
   <si>
     <t xml:space="preserve">2.08364152908325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03765726089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.003169298172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98592579364777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95143783092499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042436122894</t>
+    <t xml:space="preserve">2.03765749931335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00316953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98592567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9514377117157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042471885681</t>
   </si>
   <si>
     <t xml:space="preserve">1.88318061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85372221469879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74594759941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540600299835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77181375026703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80845677852631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8300119638443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88533627986908</t>
+    <t xml:space="preserve">1.8537220954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74594748020172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540612220764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77181363105774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80845713615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83001172542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88533616065979</t>
   </si>
   <si>
     <t xml:space="preserve">1.92557191848755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88964712619781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88677322864532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86737358570099</t>
+    <t xml:space="preserve">1.8896472454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88677299022675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86737370491028</t>
   </si>
   <si>
     <t xml:space="preserve">1.89395809173584</t>
@@ -3638,43 +3638,43 @@
     <t xml:space="preserve">1.89036560058594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85444068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84797430038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79767954349518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85659658908844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85875177383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85515928268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8860547542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683198928833</t>
+    <t xml:space="preserve">1.8544408082962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84797406196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7976793050766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85659635066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85875165462494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84725606441498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85515916347504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88605463504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683210849762</t>
   </si>
   <si>
     <t xml:space="preserve">1.97874081134796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0010142326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0254430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06280469894409</t>
+    <t xml:space="preserve">2.00101399421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02544283866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06280493736267</t>
   </si>
   <si>
     <t xml:space="preserve">2.05849385261536</t>
@@ -3695,46 +3695,46 @@
     <t xml:space="preserve">2.00460648536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01251029968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99526619911194</t>
+    <t xml:space="preserve">2.01251006126404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99526607990265</t>
   </si>
   <si>
     <t xml:space="preserve">1.89970588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87958824634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93131995201111</t>
+    <t xml:space="preserve">1.87958800792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93131971359253</t>
   </si>
   <si>
     <t xml:space="preserve">1.96221518516541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91192042827606</t>
+    <t xml:space="preserve">1.91192066669464</t>
   </si>
   <si>
     <t xml:space="preserve">2.02041339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06855273246765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10447788238525</t>
+    <t xml:space="preserve">2.06855297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10447764396667</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645630836487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09657406806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15117979049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3250560760498</t>
+    <t xml:space="preserve">2.09657430648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15118002891541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32505631446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.32361912727356</t>
@@ -3743,13 +3743,13 @@
     <t xml:space="preserve">2.55138301849365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53485751152039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6081440448761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55928611755371</t>
+    <t xml:space="preserve">2.53485727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60814428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55928635597229</t>
   </si>
   <si>
     <t xml:space="preserve">2.52767252922058</t>
@@ -3770,31 +3770,31 @@
     <t xml:space="preserve">2.21584463119507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26398396492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21368908882141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496047973633</t>
+    <t xml:space="preserve">2.26398420333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21368932723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496024131775</t>
   </si>
   <si>
     <t xml:space="preserve">1.91120195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66475749015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74954009056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79480540752411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90186131000519</t>
+    <t xml:space="preserve">1.66475737094879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74954032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79480528831482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575975894928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90186154842377</t>
   </si>
   <si>
     <t xml:space="preserve">2.06783437728882</t>
@@ -3809,37 +3809,37 @@
     <t xml:space="preserve">1.98879969120026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95574867725372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359325408936</t>
+    <t xml:space="preserve">1.95574879646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359337329865</t>
   </si>
   <si>
     <t xml:space="preserve">2.06208634376526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93275713920593</t>
+    <t xml:space="preserve">1.93275678157806</t>
   </si>
   <si>
     <t xml:space="preserve">1.99095511436462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664402961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784510135651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16626834869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12459564208984</t>
+    <t xml:space="preserve">1.98664426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94784533977509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16626858711243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12459588050842</t>
   </si>
   <si>
     <t xml:space="preserve">2.19572687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19860076904297</t>
+    <t xml:space="preserve">2.19860100746155</t>
   </si>
   <si>
     <t xml:space="preserve">2.2307755947113</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">2.33036375045776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35257935523987</t>
+    <t xml:space="preserve">2.35257959365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.35181355476379</t>
@@ -3860,13 +3860,13 @@
     <t xml:space="preserve">2.32193684577942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35104727745056</t>
+    <t xml:space="preserve">2.35104751586914</t>
   </si>
   <si>
     <t xml:space="preserve">2.31887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27597332000732</t>
+    <t xml:space="preserve">2.27597308158875</t>
   </si>
   <si>
     <t xml:space="preserve">2.33572626113892</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">2.1587655544281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25069332122803</t>
+    <t xml:space="preserve">2.25069308280945</t>
   </si>
   <si>
     <t xml:space="preserve">2.23307371139526</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">2.21545433998108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28286790847778</t>
+    <t xml:space="preserve">2.2828676700592</t>
   </si>
   <si>
     <t xml:space="preserve">2.26448225975037</t>
@@ -3917,16 +3917,16 @@
     <t xml:space="preserve">2.47285151481628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45293354988098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4820442199707</t>
+    <t xml:space="preserve">2.45293378829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48204398155212</t>
   </si>
   <si>
     <t xml:space="preserve">2.48664045333862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46365880966187</t>
+    <t xml:space="preserve">2.46365857124329</t>
   </si>
   <si>
     <t xml:space="preserve">2.47438359260559</t>
@@ -3935,16 +3935,16 @@
     <t xml:space="preserve">2.41309857368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43071794509888</t>
+    <t xml:space="preserve">2.43071818351746</t>
   </si>
   <si>
     <t xml:space="preserve">2.37709355354309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09058594703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98793339729309</t>
+    <t xml:space="preserve">2.09058618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98793363571167</t>
   </si>
   <si>
     <t xml:space="preserve">2.01168155670166</t>
@@ -3953,19 +3953,19 @@
     <t xml:space="preserve">2.08062720298767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02623653411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07832884788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16795825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19936680793762</t>
+    <t xml:space="preserve">2.02623677253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07832908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1679584980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1993670463562</t>
   </si>
   <si>
     <t xml:space="preserve">2.13501763343811</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">2.14191222190857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14650845527649</t>
+    <t xml:space="preserve">2.14650869369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.0315990447998</t>
@@ -4004,25 +4004,25 @@
     <t xml:space="preserve">1.91592347621918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8684276342392</t>
+    <t xml:space="preserve">1.86842751502991</t>
   </si>
   <si>
     <t xml:space="preserve">1.83472084999084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73743081092834</t>
+    <t xml:space="preserve">1.73743069171906</t>
   </si>
   <si>
     <t xml:space="preserve">1.7742018699646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83012449741364</t>
+    <t xml:space="preserve">1.83012461662292</t>
   </si>
   <si>
     <t xml:space="preserve">1.92435014247894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87915253639221</t>
+    <t xml:space="preserve">1.87915277481079</t>
   </si>
   <si>
     <t xml:space="preserve">1.80331254005432</t>
@@ -4034,22 +4034,22 @@
     <t xml:space="preserve">1.85387253761292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79641759395599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84544563293457</t>
+    <t xml:space="preserve">1.79641783237457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84544575214386</t>
   </si>
   <si>
     <t xml:space="preserve">1.86306512355804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92894661426544</t>
+    <t xml:space="preserve">1.92894637584686</t>
   </si>
   <si>
     <t xml:space="preserve">1.92052006721497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96954798698425</t>
+    <t xml:space="preserve">1.96954822540283</t>
   </si>
   <si>
     <t xml:space="preserve">2.06837034225464</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">1.97184610366821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95652484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99176371097565</t>
+    <t xml:space="preserve">1.95652508735657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99176394939423</t>
   </si>
   <si>
     <t xml:space="preserve">2.07220053672791</t>
@@ -4088,19 +4088,19 @@
     <t xml:space="preserve">1.94273579120636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87762033939362</t>
+    <t xml:space="preserve">1.87762045860291</t>
   </si>
   <si>
     <t xml:space="preserve">1.90826284885406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86076700687408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80944073200226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86612975597382</t>
+    <t xml:space="preserve">1.86076688766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80944097042084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86612951755524</t>
   </si>
   <si>
     <t xml:space="preserve">1.89830410480499</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">1.90213441848755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8714919090271</t>
+    <t xml:space="preserve">1.87149178981781</t>
   </si>
   <si>
     <t xml:space="preserve">1.9687819480896</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">1.90673077106476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89907014369965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99712634086609</t>
+    <t xml:space="preserve">1.89907026290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9971262216568</t>
   </si>
   <si>
     <t xml:space="preserve">2.06070971488953</t>
@@ -4148,16 +4148,16 @@
     <t xml:space="preserve">2.15799951553345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12965536117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09288430213928</t>
+    <t xml:space="preserve">2.12965512275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0928840637207</t>
   </si>
   <si>
     <t xml:space="preserve">2.07143425941467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02700281143188</t>
+    <t xml:space="preserve">2.02700257301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.06377363204956</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">2.10820531845093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0300669670105</t>
+    <t xml:space="preserve">2.03006720542908</t>
   </si>
   <si>
     <t xml:space="preserve">2.04155802726746</t>
@@ -4181,22 +4181,22 @@
     <t xml:space="preserve">2.07986092567444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05151653289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05304884910583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11893033981323</t>
+    <t xml:space="preserve">2.05151677131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05304908752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11893010139465</t>
   </si>
   <si>
     <t xml:space="preserve">2.17485284805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17255449295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17332077026367</t>
+    <t xml:space="preserve">2.17255473136902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17332053184509</t>
   </si>
   <si>
     <t xml:space="preserve">2.1932384967804</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">2.34491896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37173128128052</t>
+    <t xml:space="preserve">2.37173104286194</t>
   </si>
   <si>
     <t xml:space="preserve">2.41922688484192</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">2.48970484733582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51268672943115</t>
+    <t xml:space="preserve">2.51268649101257</t>
   </si>
   <si>
     <t xml:space="preserve">2.56171464920044</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">2.53949904441833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55175590515137</t>
+    <t xml:space="preserve">2.55175614356995</t>
   </si>
   <si>
     <t xml:space="preserve">2.52187967300415</t>
@@ -4286,28 +4286,28 @@
     <t xml:space="preserve">2.41386461257935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40390586853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41080021858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40313982963562</t>
+    <t xml:space="preserve">2.40390563011169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41080045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40313959121704</t>
   </si>
   <si>
     <t xml:space="preserve">2.4207592010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51881527900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50349378585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44527292251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817253112793</t>
+    <t xml:space="preserve">2.51881504058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50349402427673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44527268409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817276954651</t>
   </si>
   <si>
     <t xml:space="preserve">2.46672296524048</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">2.5686092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59465527534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5793342590332</t>
+    <t xml:space="preserve">2.59465551376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57933402061462</t>
   </si>
   <si>
     <t xml:space="preserve">2.58393049240112</t>
@@ -4331,16 +4331,16 @@
     <t xml:space="preserve">2.57703590393066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55405426025391</t>
+    <t xml:space="preserve">2.55405402183533</t>
   </si>
   <si>
     <t xml:space="preserve">2.62376570701599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67739009857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77774405479431</t>
+    <t xml:space="preserve">2.67739033699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77774429321289</t>
   </si>
   <si>
     <t xml:space="preserve">2.78923559188843</t>
@@ -4355,10 +4355,10 @@
     <t xml:space="preserve">2.72335386276245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74020743370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82141017913818</t>
+    <t xml:space="preserve">2.74020719528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8214099407196</t>
   </si>
   <si>
     <t xml:space="preserve">2.94014978408813</t>
@@ -4367,22 +4367,22 @@
     <t xml:space="preserve">2.9217643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93172311782837</t>
+    <t xml:space="preserve">2.93172335624695</t>
   </si>
   <si>
     <t xml:space="preserve">2.89725041389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92636060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95700311660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99453997612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00756359100342</t>
+    <t xml:space="preserve">2.9263608455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95700335502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99454021453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00756335258484</t>
   </si>
   <si>
     <t xml:space="preserve">3.07038044929504</t>
@@ -4406,7 +4406,7 @@
     <t xml:space="preserve">3.22895550727844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29024076461792</t>
+    <t xml:space="preserve">3.2902410030365</t>
   </si>
   <si>
     <t xml:space="preserve">3.22435927391052</t>
@@ -4421,16 +4421,16 @@
     <t xml:space="preserve">3.18682217597961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16767048835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14085817337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19448280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22282719612122</t>
+    <t xml:space="preserve">3.16767072677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14085841178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19448304176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22282695770264</t>
   </si>
   <si>
     <t xml:space="preserve">3.10255527496338</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">3.11634421348572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05812382698059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12860155105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16001009941101</t>
+    <t xml:space="preserve">3.05812358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12860131263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16000986099243</t>
   </si>
   <si>
     <t xml:space="preserve">3.16077589988708</t>
@@ -4478,16 +4478,16 @@
     <t xml:space="preserve">2.82830452919006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8811628818512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67585825920105</t>
+    <t xml:space="preserve">2.88116264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67585802078247</t>
   </si>
   <si>
     <t xml:space="preserve">2.71186304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70573472976685</t>
+    <t xml:space="preserve">2.70573449134827</t>
   </si>
   <si>
     <t xml:space="preserve">2.80991911888123</t>
@@ -4505,37 +4505,37 @@
     <t xml:space="preserve">2.60691261291504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63372468948364</t>
+    <t xml:space="preserve">2.63372445106506</t>
   </si>
   <si>
     <t xml:space="preserve">2.65900468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75782656669617</t>
+    <t xml:space="preserve">2.75782680511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.79996037483215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76165747642517</t>
+    <t xml:space="preserve">2.76165723800659</t>
   </si>
   <si>
     <t xml:space="preserve">2.77851057052612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75476264953613</t>
+    <t xml:space="preserve">2.75476241111755</t>
   </si>
   <si>
     <t xml:space="preserve">2.82370853424072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83979558944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84132790565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83519911766052</t>
+    <t xml:space="preserve">2.83979535102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84132814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8351993560791</t>
   </si>
   <si>
     <t xml:space="preserve">2.93019104003906</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">3.11098170280457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24427700042725</t>
+    <t xml:space="preserve">3.24427676200867</t>
   </si>
   <si>
     <t xml:space="preserve">3.31637167930603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21511483192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03609204292297</t>
+    <t xml:space="preserve">3.21511459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03609228134155</t>
   </si>
   <si>
     <t xml:space="preserve">3.11466765403748</t>
@@ -4568,13 +4568,13 @@
     <t xml:space="preserve">2.98505854606628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92187428474426</t>
+    <t xml:space="preserve">2.92187452316284</t>
   </si>
   <si>
     <t xml:space="preserve">2.96966743469238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89595246315002</t>
+    <t xml:space="preserve">2.89595222473145</t>
   </si>
   <si>
     <t xml:space="preserve">3.0109806060791</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">3.04905295372009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27910900115967</t>
+    <t xml:space="preserve">3.27910923957825</t>
   </si>
   <si>
     <t xml:space="preserve">3.1567907333374</t>
@@ -4607,16 +4607,16 @@
     <t xml:space="preserve">3.17947196960449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15841054916382</t>
+    <t xml:space="preserve">3.1584107875824</t>
   </si>
   <si>
     <t xml:space="preserve">3.21754479408264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21025443077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631539344788</t>
+    <t xml:space="preserve">3.21025466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631563186646</t>
   </si>
   <si>
     <t xml:space="preserve">3.09684634208679</t>
@@ -4625,25 +4625,25 @@
     <t xml:space="preserve">3.09441614151001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05472350120544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02151131629944</t>
+    <t xml:space="preserve">3.05472373962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02151107788086</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03771233558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11142778396606</t>
+    <t xml:space="preserve">3.03771209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11142754554749</t>
   </si>
   <si>
     <t xml:space="preserve">3.06768441200256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1130473613739</t>
+    <t xml:space="preserve">3.11304759979248</t>
   </si>
   <si>
     <t xml:space="preserve">3.09765625</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">3.10251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09198594093323</t>
+    <t xml:space="preserve">3.09198617935181</t>
   </si>
   <si>
     <t xml:space="preserve">3.14626002311707</t>
@@ -4667,22 +4667,22 @@
     <t xml:space="preserve">3.16165113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24508714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26776814460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24751687049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31556153297424</t>
+    <t xml:space="preserve">3.24508690834045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26776838302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24751663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31556177139282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29612016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22888588905334</t>
+    <t xml:space="preserve">3.22888565063477</t>
   </si>
   <si>
     <t xml:space="preserve">3.22240519523621</t>
@@ -4700,13 +4700,13 @@
     <t xml:space="preserve">3.44274067878723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50673484802246</t>
+    <t xml:space="preserve">3.50673508644104</t>
   </si>
   <si>
     <t xml:space="preserve">3.44031071662903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44355058670044</t>
+    <t xml:space="preserve">3.44355082511902</t>
   </si>
   <si>
     <t xml:space="preserve">3.34553384780884</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">3.42005920410156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46947240829468</t>
+    <t xml:space="preserve">3.46947264671326</t>
   </si>
   <si>
     <t xml:space="preserve">3.4978244304657</t>
@@ -4724,13 +4724,13 @@
     <t xml:space="preserve">3.57883048057556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61852288246155</t>
+    <t xml:space="preserve">3.61852312088013</t>
   </si>
   <si>
     <t xml:space="preserve">3.54075741767883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61042237281799</t>
+    <t xml:space="preserve">3.61042213439941</t>
   </si>
   <si>
     <t xml:space="preserve">3.62500333786011</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">3.60475182533264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59422135353088</t>
+    <t xml:space="preserve">3.5942211151123</t>
   </si>
   <si>
     <t xml:space="preserve">3.59503149986267</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">3.63634419441223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63553380966187</t>
+    <t xml:space="preserve">3.63553428649902</t>
   </si>
   <si>
     <t xml:space="preserve">3.68413734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64606475830078</t>
+    <t xml:space="preserve">3.64606499671936</t>
   </si>
   <si>
     <t xml:space="preserve">3.58774065971375</t>
@@ -4772,22 +4772,22 @@
     <t xml:space="preserve">3.50511527061462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48162317276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56505942344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2410364151001</t>
+    <t xml:space="preserve">3.48162341117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56505918502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24103665351868</t>
   </si>
   <si>
     <t xml:space="preserve">3.4176287651062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51807570457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50106501579285</t>
+    <t xml:space="preserve">3.51807594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50106453895569</t>
   </si>
   <si>
     <t xml:space="preserve">3.54966807365417</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">3.55209851264954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54480767250061</t>
+    <t xml:space="preserve">3.54480791091919</t>
   </si>
   <si>
     <t xml:space="preserve">3.52293610572815</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">3.5415678024292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51564574241638</t>
+    <t xml:space="preserve">3.51564598083496</t>
   </si>
   <si>
     <t xml:space="preserve">3.56667900085449</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">3.54318785667419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49944472312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46380233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35687470436096</t>
+    <t xml:space="preserve">3.49944496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46380257606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35687446594238</t>
   </si>
   <si>
     <t xml:space="preserve">3.28882956504822</t>
@@ -4853,10 +4853,10 @@
     <t xml:space="preserve">3.53994727134705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62743353843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70843958854675</t>
+    <t xml:space="preserve">3.62743377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70843935012817</t>
   </si>
   <si>
     <t xml:space="preserve">3.77243375778198</t>
@@ -4865,34 +4865,34 @@
     <t xml:space="preserve">3.75218224525452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82670712471008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75137257575989</t>
+    <t xml:space="preserve">3.82670760154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75137233734131</t>
   </si>
   <si>
     <t xml:space="preserve">3.6898078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74084162712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67360663414001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68251752853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66712641716003</t>
+    <t xml:space="preserve">3.74084138870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67360687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68251776695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66712617874146</t>
   </si>
   <si>
     <t xml:space="preserve">3.72626042366028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8550591468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74570178985596</t>
+    <t xml:space="preserve">3.85505962371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74570202827454</t>
   </si>
   <si>
     <t xml:space="preserve">3.84452867507935</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">3.800785779953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83966827392578</t>
+    <t xml:space="preserve">3.8396680355072</t>
   </si>
   <si>
     <t xml:space="preserve">3.76838326454163</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">3.80726599693298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79349541664124</t>
+    <t xml:space="preserve">3.79349493980408</t>
   </si>
   <si>
     <t xml:space="preserve">3.82589745521545</t>
@@ -4955,28 +4955,28 @@
     <t xml:space="preserve">3.94011521339417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99114942550659</t>
+    <t xml:space="preserve">3.99114894866943</t>
   </si>
   <si>
     <t xml:space="preserve">4.10698699951172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11994791030884</t>
+    <t xml:space="preserve">4.119948387146</t>
   </si>
   <si>
     <t xml:space="preserve">4.30950117111206</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28357934951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31112098693848</t>
+    <t xml:space="preserve">4.28357982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31112146377563</t>
   </si>
   <si>
     <t xml:space="preserve">4.25279712677002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27223873138428</t>
+    <t xml:space="preserve">4.27223920822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.31274175643921</t>
@@ -4985,7 +4985,7 @@
     <t xml:space="preserve">4.13938903808594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11346769332886</t>
+    <t xml:space="preserve">4.1134672164917</t>
   </si>
   <si>
     <t xml:space="preserve">4.13128852844238</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">4.11022758483887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18637323379517</t>
+    <t xml:space="preserve">4.18637275695801</t>
   </si>
   <si>
     <t xml:space="preserve">4.14100933074951</t>
@@ -5027,10 +5027,10 @@
     <t xml:space="preserve">4.05676364898682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90204238891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83480858802795</t>
+    <t xml:space="preserve">3.90204286575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8348081111908</t>
   </si>
   <si>
     <t xml:space="preserve">3.87045049667358</t>
@@ -5042,13 +5042,13 @@
     <t xml:space="preserve">3.84290862083435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81617712974548</t>
+    <t xml:space="preserve">3.81617665290833</t>
   </si>
   <si>
     <t xml:space="preserve">3.86072969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8826014995575</t>
+    <t xml:space="preserve">3.88260197639465</t>
   </si>
   <si>
     <t xml:space="preserve">3.87288117408752</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">4.17503213882446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14748954772949</t>
+    <t xml:space="preserve">4.14749002456665</t>
   </si>
   <si>
     <t xml:space="preserve">3.94578576087952</t>
@@ -5075,10 +5075,10 @@
     <t xml:space="preserve">3.9506459236145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88422179222107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88584184646606</t>
+    <t xml:space="preserve">3.88422155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88584136962891</t>
   </si>
   <si>
     <t xml:space="preserve">3.83318781852722</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">3.88665151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93687510490417</t>
+    <t xml:space="preserve">3.93687534332275</t>
   </si>
   <si>
     <t xml:space="preserve">3.96927738189697</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">3.99762940406799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05838394165039</t>
+    <t xml:space="preserve">4.05838346481323</t>
   </si>
   <si>
     <t xml:space="preserve">4.00573015213013</t>
@@ -5126,16 +5126,16 @@
     <t xml:space="preserve">4.20581388473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29978036880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13290929794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13614892959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00896978378296</t>
+    <t xml:space="preserve">4.29978084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13290882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13614940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00897026062012</t>
   </si>
   <si>
     <t xml:space="preserve">3.98223829269409</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">3.98547863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99600958824158</t>
+    <t xml:space="preserve">3.99600911140442</t>
   </si>
   <si>
     <t xml:space="preserve">4.03408193588257</t>
@@ -5156,7 +5156,7 @@
     <t xml:space="preserve">4.42614984512329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47961282730103</t>
+    <t xml:space="preserve">4.47961330413818</t>
   </si>
   <si>
     <t xml:space="preserve">4.40670776367188</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">5.01101016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96240711212158</t>
+    <t xml:space="preserve">4.96240663528442</t>
   </si>
   <si>
     <t xml:space="preserve">4.99642944335938</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">5.04989337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15358066558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1292781829834</t>
+    <t xml:space="preserve">5.15358018875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12927865982056</t>
   </si>
   <si>
     <t xml:space="preserve">5.07095432281494</t>
@@ -5252,7 +5252,7 @@
     <t xml:space="preserve">4.92838478088379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98670864105225</t>
+    <t xml:space="preserve">4.9867091178894</t>
   </si>
   <si>
     <t xml:space="preserve">4.96564722061157</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">5.14709997177124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17626190185547</t>
+    <t xml:space="preserve">5.17626142501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130989074707</t>
@@ -6300,6 +6300,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.2700004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2650003433228</t>
   </si>
 </sst>
 </file>
@@ -71846,7 +71849,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6916898148</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>8122601</v>
@@ -71867,6 +71870,32 @@
         <v>2095</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.694375</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>7193546</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>13.4350004196167</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>13.2250003814697</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>13.3199996948242</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>13.2650003433228</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>2096</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAMI.MI.xlsx
+++ b/data/BAMI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="2097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="2098">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">6.25302314758301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98424005508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89802646636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6545991897583</t>
+    <t xml:space="preserve">5.98423957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89802598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65459871292114</t>
   </si>
   <si>
     <t xml:space="preserve">5.53795766830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65967130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89295434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.274245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9420690536499</t>
+    <t xml:space="preserve">5.65967082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89295482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27424573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94206857681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.40450143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85839128494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61496496200562</t>
+    <t xml:space="preserve">4.85839080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61496448516846</t>
   </si>
   <si>
     <t xml:space="preserve">4.28785991668701</t>
@@ -86,127 +86,127 @@
     <t xml:space="preserve">4.55410766601562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19911003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9556839466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32082366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57946491241455</t>
+    <t xml:space="preserve">4.19911050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95568370819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32082414627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57946443557739</t>
   </si>
   <si>
     <t xml:space="preserve">4.50339365005493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05204010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11289739608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961268424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52715134620667</t>
+    <t xml:space="preserve">4.0520396232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11289691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8796124458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52715110778809</t>
   </si>
   <si>
     <t xml:space="preserve">3.22286772727966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5804009437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26851081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6437931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91004157066345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04443216323853</t>
+    <t xml:space="preserve">3.58040118217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26851058006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64379239082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91004109382629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04443264007568</t>
   </si>
   <si>
     <t xml:space="preserve">4.1433253288269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91511273384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77818536758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08246898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71986413002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.646329164505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74775671958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84157681465149</t>
+    <t xml:space="preserve">3.91511297225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77818560600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08246803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71986436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64632964134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74775624275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84157752990723</t>
   </si>
   <si>
     <t xml:space="preserve">3.92018342018127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22700262069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04950428009033</t>
+    <t xml:space="preserve">4.22700309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">3.88468432426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86693453788757</t>
+    <t xml:space="preserve">3.86693477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.7604353427887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69957780838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03682613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9480767250061</t>
+    <t xml:space="preserve">3.69957852363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03682565689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807648658752</t>
   </si>
   <si>
     <t xml:space="preserve">3.38768792152405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47136569023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67675733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69197154045105</t>
+    <t xml:space="preserve">3.4713659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67675709724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69197130203247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51447319984436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38261723518372</t>
+    <t xml:space="preserve">3.38261699676514</t>
   </si>
   <si>
     <t xml:space="preserve">3.27611780166626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06565475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92365598678589</t>
+    <t xml:space="preserve">3.06565427780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92365622520447</t>
   </si>
   <si>
     <t xml:space="preserve">2.70812177658081</t>
@@ -218,46 +218,46 @@
     <t xml:space="preserve">2.40586709976196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2243115901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46672368049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72079992294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70051455497742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910977602005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02508330345154</t>
+    <t xml:space="preserve">2.22431135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72080016136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.700514793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91097712516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0250837802887</t>
   </si>
   <si>
     <t xml:space="preserve">3.16454648971558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22690224647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1385657787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20092105865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24508953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11777997016907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23469662666321</t>
+    <t xml:space="preserve">3.2269024848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13856554031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14116311073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20092129707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24508905410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11778020858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23469686508179</t>
   </si>
   <si>
     <t xml:space="preserve">3.19052886962891</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">3.32823061943054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20351910591125</t>
+    <t xml:space="preserve">3.20351934432983</t>
   </si>
   <si>
     <t xml:space="preserve">2.96968603134155</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">2.86835813522339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72805738449097</t>
+    <t xml:space="preserve">2.72805762290955</t>
   </si>
   <si>
     <t xml:space="preserve">2.84497475624084</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">2.59607148170471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51500940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.286372423172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378602027893</t>
+    <t xml:space="preserve">2.51500916481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28637218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378578186035</t>
   </si>
   <si>
     <t xml:space="preserve">2.32274651527405</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">2.39237642288208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23544836044312</t>
+    <t xml:space="preserve">2.23544859886169</t>
   </si>
   <si>
     <t xml:space="preserve">2.24584102630615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2208993434906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24480199813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24999785423279</t>
+    <t xml:space="preserve">2.22089886665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24480175971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24999761581421</t>
   </si>
   <si>
     <t xml:space="preserve">2.2749400138855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47343921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4703209400177</t>
+    <t xml:space="preserve">2.47343897819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47032117843628</t>
   </si>
   <si>
     <t xml:space="preserve">2.48902797698975</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">2.31131458282471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16581773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16685748100281</t>
+    <t xml:space="preserve">2.16581797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16685700416565</t>
   </si>
   <si>
     <t xml:space="preserve">2.05461692810059</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">2.15853548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29020428657532</t>
+    <t xml:space="preserve">2.2902045249939</t>
   </si>
   <si>
     <t xml:space="preserve">2.22156858444214</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">1.83636581897736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71590268611908</t>
+    <t xml:space="preserve">1.71590256690979</t>
   </si>
   <si>
     <t xml:space="preserve">1.83776664733887</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">2.07449102401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01846170425415</t>
+    <t xml:space="preserve">2.01846146583557</t>
   </si>
   <si>
     <t xml:space="preserve">2.02546525001526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99324822425842</t>
+    <t xml:space="preserve">1.993248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.12211608886719</t>
@@ -392,79 +392,79 @@
     <t xml:space="preserve">1.55481779575348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439119338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50158965587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52540242671967</t>
+    <t xml:space="preserve">1.50439131259918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50158989429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52540230751038</t>
   </si>
   <si>
     <t xml:space="preserve">1.45676612854004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40073668956757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31459140777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28167402744293</t>
+    <t xml:space="preserve">1.40073680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31459152698517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28167414665222</t>
   </si>
   <si>
     <t xml:space="preserve">1.51699781417847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57022595405579</t>
+    <t xml:space="preserve">1.57022607326508</t>
   </si>
   <si>
     <t xml:space="preserve">1.666876912117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5562185049057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64166355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66267430782318</t>
+    <t xml:space="preserve">1.55621838569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64166367053986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66267466545105</t>
   </si>
   <si>
     <t xml:space="preserve">1.68788778781891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67528116703033</t>
+    <t xml:space="preserve">1.67528104782104</t>
   </si>
   <si>
     <t xml:space="preserve">1.66407525539398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72990989685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70329582691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71730315685272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75932550430298</t>
+    <t xml:space="preserve">1.72991001605988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70329570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71730327606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75932538509369</t>
   </si>
   <si>
     <t xml:space="preserve">1.70749807357788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76352739334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50579214096069</t>
+    <t xml:space="preserve">1.76352751255035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5057920217514</t>
   </si>
   <si>
     <t xml:space="preserve">1.49738752841949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55201625823975</t>
+    <t xml:space="preserve">1.55201637744904</t>
   </si>
   <si>
     <t xml:space="preserve">1.63045763969421</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">1.5996413230896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59263753890991</t>
+    <t xml:space="preserve">1.5926376581192</t>
   </si>
   <si>
     <t xml:space="preserve">1.58143174648285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56882512569427</t>
+    <t xml:space="preserve">1.56882524490356</t>
   </si>
   <si>
     <t xml:space="preserve">1.53100538253784</t>
@@ -500,34 +500,34 @@
     <t xml:space="preserve">1.53520750999451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51559734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56742429733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56182134151459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60384356975555</t>
+    <t xml:space="preserve">1.51559722423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56742417812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56182157993317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60384345054626</t>
   </si>
   <si>
     <t xml:space="preserve">1.68088412284851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63886177539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65707147121429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65847229957581</t>
+    <t xml:space="preserve">1.63886189460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65707159042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6584724187851</t>
   </si>
   <si>
     <t xml:space="preserve">1.6430641412735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59403848648071</t>
+    <t xml:space="preserve">1.59403836727142</t>
   </si>
   <si>
     <t xml:space="preserve">1.60944652557373</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">1.57582890987396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50018894672394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46657145023346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40003633499146</t>
+    <t xml:space="preserve">1.50018906593323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46657133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40003621578217</t>
   </si>
   <si>
     <t xml:space="preserve">1.45116329193115</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">1.3965345621109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40774035453796</t>
+    <t xml:space="preserve">1.40774047374725</t>
   </si>
   <si>
     <t xml:space="preserve">1.46797204017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48057889938354</t>
+    <t xml:space="preserve">1.48057878017426</t>
   </si>
   <si>
     <t xml:space="preserve">1.50299048423767</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">1.55061554908752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65286922454834</t>
+    <t xml:space="preserve">1.65286934375763</t>
   </si>
   <si>
     <t xml:space="preserve">1.78593945503235</t>
@@ -587,100 +587,100 @@
     <t xml:space="preserve">1.79994666576385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84617102146149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317480564117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84196889400482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82235860824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737693309784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86298000812531</t>
+    <t xml:space="preserve">1.8461709022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8531745672226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84196901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82235848903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737717151642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86297976970673</t>
   </si>
   <si>
     <t xml:space="preserve">1.92041027545929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89379608631134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80835103988647</t>
+    <t xml:space="preserve">1.89379620552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80835115909576</t>
   </si>
   <si>
     <t xml:space="preserve">1.67107892036438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61224782466888</t>
+    <t xml:space="preserve">1.61224818229675</t>
   </si>
   <si>
     <t xml:space="preserve">1.50999414920807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59543943405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60664486885071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51279580593109</t>
+    <t xml:space="preserve">1.59543919563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60664510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5127956867218</t>
   </si>
   <si>
     <t xml:space="preserve">1.42735087871552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35451245307922</t>
+    <t xml:space="preserve">1.35451257228851</t>
   </si>
   <si>
     <t xml:space="preserve">1.30408585071564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31178998947144</t>
+    <t xml:space="preserve">1.31179010868073</t>
   </si>
   <si>
     <t xml:space="preserve">1.32649779319763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29988360404968</t>
+    <t xml:space="preserve">1.29988372325897</t>
   </si>
   <si>
     <t xml:space="preserve">1.31739294528961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2508579492569</t>
+    <t xml:space="preserve">1.25085806846619</t>
   </si>
   <si>
     <t xml:space="preserve">1.30268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35871481895447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39233231544495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28867793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40493905544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49458611011505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64026284217834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56462287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53380680084229</t>
+    <t xml:space="preserve">1.35871458053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39233243465424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28867781162262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40493893623352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49458622932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64026272296906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56462299823761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.533806681633</t>
   </si>
   <si>
     <t xml:space="preserve">1.679483294487</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">1.69769299030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65146851539612</t>
+    <t xml:space="preserve">1.65146863460541</t>
   </si>
   <si>
     <t xml:space="preserve">1.72290623188019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77893555164337</t>
+    <t xml:space="preserve">1.77893567085266</t>
   </si>
   <si>
     <t xml:space="preserve">1.71310102939606</t>
@@ -707,22 +707,22 @@
     <t xml:space="preserve">1.75092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87698709964752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90500199794769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9764392375946</t>
+    <t xml:space="preserve">1.87698721885681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9050018787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97643947601318</t>
   </si>
   <si>
     <t xml:space="preserve">2.0310685634613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95122635364532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9498256444931</t>
+    <t xml:space="preserve">1.95122623443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94982588291168</t>
   </si>
   <si>
     <t xml:space="preserve">1.90640258789062</t>
@@ -731,28 +731,28 @@
     <t xml:space="preserve">1.94702386856079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89799845218658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142127037048</t>
+    <t xml:space="preserve">1.89799833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142138957977</t>
   </si>
   <si>
     <t xml:space="preserve">1.93581795692444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01706075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97363817691803</t>
+    <t xml:space="preserve">2.01706099510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97363805770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.02266359329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08849859237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00585508346558</t>
+    <t xml:space="preserve">2.08849835395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.005854845047</t>
   </si>
   <si>
     <t xml:space="preserve">2.02126312255859</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">1.86017847061157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8909946680069</t>
+    <t xml:space="preserve">1.89099442958832</t>
   </si>
   <si>
     <t xml:space="preserve">1.78033638000488</t>
@@ -770,19 +770,19 @@
     <t xml:space="preserve">1.67388033866882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74251663684845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73831427097321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64586579799652</t>
+    <t xml:space="preserve">1.74251651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7383143901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64586555957794</t>
   </si>
   <si>
     <t xml:space="preserve">1.75512325763702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84056842327118</t>
+    <t xml:space="preserve">1.84056794643402</t>
   </si>
   <si>
     <t xml:space="preserve">1.77753496170044</t>
@@ -791,85 +791,85 @@
     <t xml:space="preserve">1.7817370891571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68368566036224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6220531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51419639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006768703461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71870398521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71450161933899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68228459358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6934906244278</t>
+    <t xml:space="preserve">1.68368542194366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62205302715302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51419627666473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006792545319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71870386600494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71450173854828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68228507041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69349074363708</t>
   </si>
   <si>
     <t xml:space="preserve">1.69629216194153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80975198745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81535482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072609424591</t>
+    <t xml:space="preserve">1.80975222587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81535470485687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072585582733</t>
   </si>
   <si>
     <t xml:space="preserve">1.80695021152496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86858284473419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85597622394562</t>
+    <t xml:space="preserve">1.86858296394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85597634315491</t>
   </si>
   <si>
     <t xml:space="preserve">1.91620790958405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90780329704285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91480696201324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88539159297943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88819336891174</t>
+    <t xml:space="preserve">1.90780341625214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91480731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88539171218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88819313049316</t>
   </si>
   <si>
     <t xml:space="preserve">1.94562351703644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90360128879547</t>
+    <t xml:space="preserve">1.90360105037689</t>
   </si>
   <si>
     <t xml:space="preserve">1.89939892292023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87978863716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86718213558197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76212680339813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95542848110199</t>
+    <t xml:space="preserve">1.87978887557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86718201637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76212692260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95542860031128</t>
   </si>
   <si>
     <t xml:space="preserve">1.86157929897308</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">1.86998355388641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445437431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04647612571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9190092086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87838792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98204231262207</t>
+    <t xml:space="preserve">2.00445413589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04647636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91900944709778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87838780879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98204255104065</t>
   </si>
   <si>
     <t xml:space="preserve">1.96383285522461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88258993625641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93021535873413</t>
+    <t xml:space="preserve">1.88259017467499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93021512031555</t>
   </si>
   <si>
     <t xml:space="preserve">1.97784018516541</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">2.00305342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90220046043396</t>
+    <t xml:space="preserve">1.90220069885254</t>
   </si>
   <si>
     <t xml:space="preserve">1.99885129928589</t>
@@ -932,28 +932,28 @@
     <t xml:space="preserve">1.95262694358826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95402765274048</t>
+    <t xml:space="preserve">1.95402777194977</t>
   </si>
   <si>
     <t xml:space="preserve">1.9344174861908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90920412540436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91060507297516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88679254055023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95822978019714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94422256946564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99184787273407</t>
+    <t xml:space="preserve">1.90920424461365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91060471534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88679230213165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95822989940643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94422245025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99184763431549</t>
   </si>
   <si>
     <t xml:space="preserve">2.06048369407654</t>
@@ -965,55 +965,55 @@
     <t xml:space="preserve">2.10950946807861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14592838287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955023765564</t>
+    <t xml:space="preserve">2.14592862129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09550213813782</t>
   </si>
   <si>
     <t xml:space="preserve">2.16974139213562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14452791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18795108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20616054534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20896172523499</t>
+    <t xml:space="preserve">2.14452815055847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18795084953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20616030693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20896220207214</t>
   </si>
   <si>
     <t xml:space="preserve">2.19915676116943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19635510444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14172673225403</t>
+    <t xml:space="preserve">2.19635534286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14172649383545</t>
   </si>
   <si>
     <t xml:space="preserve">2.20335865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19215297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15573406219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16413831710815</t>
+    <t xml:space="preserve">2.19215321540833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15573382377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16413807868958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16273760795593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20756125450134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22997260093689</t>
+    <t xml:space="preserve">2.20756077766418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22997283935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.28320097923279</t>
@@ -1025,139 +1025,139 @@
     <t xml:space="preserve">2.35884070396423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33082580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30561256408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26499128341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29720830917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30981492996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27339577674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32242155075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22717142105103</t>
+    <t xml:space="preserve">2.33082604408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30561280250549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26499104499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29720854759216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30981516838074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27339553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32242131233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2271716594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.2607889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22016787528992</t>
+    <t xml:space="preserve">2.22016763687134</t>
   </si>
   <si>
     <t xml:space="preserve">2.23277425765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2621898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21036267280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15993618965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15713453292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10110545158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13052082061768</t>
+    <t xml:space="preserve">2.26219010353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21036243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15993595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15713477134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1011049747467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1305205821991</t>
   </si>
   <si>
     <t xml:space="preserve">2.18935132026672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25518584251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29300594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30421185493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30141043663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31121563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33782982826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28180027008057</t>
+    <t xml:space="preserve">2.25518608093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29300618171692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30421209335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30141067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3112154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33782958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28180003166199</t>
   </si>
   <si>
     <t xml:space="preserve">2.33642888069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43448042869568</t>
+    <t xml:space="preserve">2.43448066711426</t>
   </si>
   <si>
     <t xml:space="preserve">2.45409059524536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4568920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43307971954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43027806282043</t>
+    <t xml:space="preserve">2.45689225196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43307948112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43027830123901</t>
   </si>
   <si>
     <t xml:space="preserve">2.24117875099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17954635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13192129135132</t>
+    <t xml:space="preserve">2.17954659461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13192105293274</t>
   </si>
   <si>
     <t xml:space="preserve">2.23417520523071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20475959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1907525062561</t>
+    <t xml:space="preserve">2.20476007461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19075226783752</t>
   </si>
   <si>
     <t xml:space="preserve">2.15153169631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20195841789246</t>
+    <t xml:space="preserve">2.20195817947388</t>
   </si>
   <si>
     <t xml:space="preserve">2.18374848365784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21456456184387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17674493789673</t>
+    <t xml:space="preserve">2.21456480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17674469947815</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834044456482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09690260887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1025059223175</t>
+    <t xml:space="preserve">2.09690284729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10250568389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.13332200050354</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">2.04507565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97083640098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91200566291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9274138212204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88959383964539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8755863904953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01566004753113</t>
+    <t xml:space="preserve">1.97083628177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91200578212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92741405963898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88959407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87558650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01566028594971</t>
   </si>
   <si>
     <t xml:space="preserve">1.97924101352692</t>
@@ -1196,82 +1196,82 @@
     <t xml:space="preserve">1.96943593025208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92321157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96523332595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181074619293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83496510982513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76492834091187</t>
+    <t xml:space="preserve">1.92321181297302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96523356437683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181062698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83496522903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76492822170258</t>
   </si>
   <si>
     <t xml:space="preserve">1.75232172012329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77193188667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78313791751862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82656073570251</t>
+    <t xml:space="preserve">1.77193200588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78313779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82656097412109</t>
   </si>
   <si>
     <t xml:space="preserve">1.86438059806824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85177409648895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81395387649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86578130722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84897255897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88399076461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99745070934296</t>
+    <t xml:space="preserve">1.85177397727966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81395411491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86578142642975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84897267818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8839910030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99745059013367</t>
   </si>
   <si>
     <t xml:space="preserve">2.04787707328796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0436749458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99604952335358</t>
+    <t xml:space="preserve">2.04367470741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99604976177216</t>
   </si>
   <si>
     <t xml:space="preserve">2.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11931490898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15013098716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17114210128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18725061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12701892852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14557838439941</t>
+    <t xml:space="preserve">2.11931467056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15013074874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17114186286926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18725037574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12701845169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14557862281799</t>
   </si>
   <si>
     <t xml:space="preserve">2.10355639457703</t>
@@ -1289,31 +1289,31 @@
     <t xml:space="preserve">2.1536328792572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16028642654419</t>
+    <t xml:space="preserve">2.16028618812561</t>
   </si>
   <si>
     <t xml:space="preserve">2.10600781440735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03772187232971</t>
+    <t xml:space="preserve">2.03772163391113</t>
   </si>
   <si>
     <t xml:space="preserve">2.1172137260437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08009433746338</t>
+    <t xml:space="preserve">2.08009386062622</t>
   </si>
   <si>
     <t xml:space="preserve">2.11266136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12736916542053</t>
+    <t xml:space="preserve">2.12736892700195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18584990501404</t>
+    <t xml:space="preserve">2.18584966659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.14207696914673</t>
@@ -1328,28 +1328,28 @@
     <t xml:space="preserve">2.2030086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17604494094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1886510848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01005721092224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08709764480591</t>
+    <t xml:space="preserve">2.17604470252991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18865132331848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01005697250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08709812164307</t>
   </si>
   <si>
     <t xml:space="preserve">2.12771916389465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07624173164368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0664370059967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11441206932068</t>
+    <t xml:space="preserve">2.07624220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06643676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11441230773926</t>
   </si>
   <si>
     <t xml:space="preserve">2.08394622802734</t>
@@ -1358,49 +1358,49 @@
     <t xml:space="preserve">2.13822460174561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12036514282227</t>
+    <t xml:space="preserve">2.12036490440369</t>
   </si>
   <si>
     <t xml:space="preserve">2.12071561813354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96348261833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98274302482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9872955083847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97293746471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96838521957397</t>
+    <t xml:space="preserve">1.96348285675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98274290561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98729526996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97293758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9683849811554</t>
   </si>
   <si>
     <t xml:space="preserve">1.94107091426849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03422021865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0062050819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01601052284241</t>
+    <t xml:space="preserve">2.03421974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00620532035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01601028442383</t>
   </si>
   <si>
     <t xml:space="preserve">2.03492021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10915923118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10775899887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14382743835449</t>
+    <t xml:space="preserve">2.10915946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10775852203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14382767677307</t>
   </si>
   <si>
     <t xml:space="preserve">2.12421751022339</t>
@@ -1412,97 +1412,97 @@
     <t xml:space="preserve">2.11791396141052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13857507705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14487838745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08289551734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14347743988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453038215637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07028913497925</t>
+    <t xml:space="preserve">2.15888547897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13857460021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14487814903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08289575576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14347720146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453085899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07028889656067</t>
   </si>
   <si>
     <t xml:space="preserve">2.09970450401306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86087870597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87523627281189</t>
+    <t xml:space="preserve">1.86087882518768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8752361536026</t>
   </si>
   <si>
     <t xml:space="preserve">1.84442031383514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82165813446045</t>
+    <t xml:space="preserve">1.82165837287903</t>
   </si>
   <si>
     <t xml:space="preserve">1.57687938213348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47077369689941</t>
+    <t xml:space="preserve">1.47077345848083</t>
   </si>
   <si>
     <t xml:space="preserve">1.51839864253998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55446767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68578660488129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641059398651</t>
+    <t xml:space="preserve">1.55446779727936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68578672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641047477722</t>
   </si>
   <si>
     <t xml:space="preserve">1.59648954868317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68018388748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61259818077087</t>
+    <t xml:space="preserve">1.68018364906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61259829998016</t>
   </si>
   <si>
     <t xml:space="preserve">1.71170020103455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69874346256256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72465717792511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69138956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67808270454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81990730762482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804039955139</t>
+    <t xml:space="preserve">1.69874358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72465705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69138967990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67808258533478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81990742683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7880402803421</t>
   </si>
   <si>
     <t xml:space="preserve">1.84792184829712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.780686378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73481225967407</t>
+    <t xml:space="preserve">1.78068673610687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73481261730194</t>
   </si>
   <si>
     <t xml:space="preserve">1.70364606380463</t>
@@ -1514,37 +1514,37 @@
     <t xml:space="preserve">1.80589985847473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82586073875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173449993134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274573326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87243473529816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823284626007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85912799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83286416530609</t>
+    <t xml:space="preserve">1.82586050033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173438072205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274525642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87243509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823272705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85912775993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83286428451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.81605505943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85072314739227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601570129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85807740688324</t>
+    <t xml:space="preserve">1.85072326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85807716846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.853875041008</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">1.75337207317352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64901745319366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64621579647064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337502002716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65216910839081</t>
+    <t xml:space="preserve">1.64901721477509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64621603488922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65216898918152</t>
   </si>
   <si>
     <t xml:space="preserve">1.61960196495056</t>
@@ -1577,19 +1577,19 @@
     <t xml:space="preserve">1.53030490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46972298622131</t>
+    <t xml:space="preserve">1.4697231054306</t>
   </si>
   <si>
     <t xml:space="preserve">1.42630016803741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42524969577789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45501530170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44380939006805</t>
+    <t xml:space="preserve">1.42524981498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4550154209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44380950927734</t>
   </si>
   <si>
     <t xml:space="preserve">1.43190324306488</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">1.44415962696075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43925702571869</t>
+    <t xml:space="preserve">1.43925714492798</t>
   </si>
   <si>
     <t xml:space="preserve">1.40704011917114</t>
@@ -1616,34 +1616,34 @@
     <t xml:space="preserve">1.37132132053375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50719273090363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49493646621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54326176643372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5355578660965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5502655506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61084711551666</t>
+    <t xml:space="preserve">1.50719285011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49493634700775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54326164722443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53555774688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55026519298553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">1.61539947986603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61609995365143</t>
+    <t xml:space="preserve">1.61609983444214</t>
   </si>
   <si>
     <t xml:space="preserve">1.62625539302826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62415421009064</t>
+    <t xml:space="preserve">1.62415432929993</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715066432953</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">1.64446496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64866721630096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48688209056854</t>
+    <t xml:space="preserve">1.64866709709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48688197135925</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143704414368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37356233596802</t>
+    <t xml:space="preserve">1.3735625743866</t>
   </si>
   <si>
     <t xml:space="preserve">1.40283787250519</t>
@@ -1670,49 +1670,49 @@
     <t xml:space="preserve">1.41439390182495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38602900505066</t>
+    <t xml:space="preserve">1.38602912425995</t>
   </si>
   <si>
     <t xml:space="preserve">1.29638171195984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31108951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3052065372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31136965751648</t>
+    <t xml:space="preserve">1.31108963489532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30520665645599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31136977672577</t>
   </si>
   <si>
     <t xml:space="preserve">1.3166925907135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30758786201477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29960346221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22550463676453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20673477649689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1690548658371</t>
+    <t xml:space="preserve">1.30758774280548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29960358142853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22550451755524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2067346572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16905474662781</t>
   </si>
   <si>
     <t xml:space="preserve">1.14692318439484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09229445457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134457588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08977317810059</t>
+    <t xml:space="preserve">1.09229457378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134445667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08977329730988</t>
   </si>
   <si>
     <t xml:space="preserve">1.14440190792084</t>
@@ -1727,19 +1727,19 @@
     <t xml:space="preserve">1.19608926773071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23965203762054</t>
+    <t xml:space="preserve">1.23965191841125</t>
   </si>
   <si>
     <t xml:space="preserve">1.2131781578064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22410368919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2547801733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29217970371246</t>
+    <t xml:space="preserve">1.22410380840302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25478005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29217958450317</t>
   </si>
   <si>
     <t xml:space="preserve">1.28139400482178</t>
@@ -1763,16 +1763,16 @@
     <t xml:space="preserve">1.26262414455414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19412815570831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28517591953278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32341599464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38770985603333</t>
+    <t xml:space="preserve">1.19412803649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28517603874207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32341611385345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38770997524261</t>
   </si>
   <si>
     <t xml:space="preserve">1.41194272041321</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">1.47147405147552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44836175441742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53940951824188</t>
+    <t xml:space="preserve">1.448361992836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53940975666046</t>
   </si>
   <si>
     <t xml:space="preserve">1.54571294784546</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">1.55796945095062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47917807102203</t>
+    <t xml:space="preserve">1.47917795181274</t>
   </si>
   <si>
     <t xml:space="preserve">1.46376979351044</t>
@@ -1811,22 +1811,22 @@
     <t xml:space="preserve">1.49913859367371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47007310390472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44345927238464</t>
+    <t xml:space="preserve">1.47007322311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44345939159393</t>
   </si>
   <si>
     <t xml:space="preserve">1.4045889377594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39401316642761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43155300617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39443349838257</t>
+    <t xml:space="preserve">1.3940132856369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4315527677536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39443361759186</t>
   </si>
   <si>
     <t xml:space="preserve">1.35605335235596</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">1.32285583019257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39177203178406</t>
+    <t xml:space="preserve">1.39177215099335</t>
   </si>
   <si>
     <t xml:space="preserve">1.37118124961853</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">1.44170844554901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41509413719177</t>
+    <t xml:space="preserve">1.41509425640106</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209804058075</t>
@@ -1859,64 +1859,64 @@
     <t xml:space="preserve">1.38224709033966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3491895198822</t>
+    <t xml:space="preserve">1.34918963909149</t>
   </si>
   <si>
     <t xml:space="preserve">1.29344034194946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33168041706085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3255170583725</t>
+    <t xml:space="preserve">1.33168029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551729679108</t>
   </si>
   <si>
     <t xml:space="preserve">1.30058407783508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29484105110168</t>
+    <t xml:space="preserve">1.29484117031097</t>
   </si>
   <si>
     <t xml:space="preserve">1.25996267795563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26864719390869</t>
+    <t xml:space="preserve">1.26864731311798</t>
   </si>
   <si>
     <t xml:space="preserve">1.24721598625183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27845251560211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26206386089325</t>
+    <t xml:space="preserve">1.27845239639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26206398010254</t>
   </si>
   <si>
     <t xml:space="preserve">1.24917697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24525499343872</t>
+    <t xml:space="preserve">1.24525511264801</t>
   </si>
   <si>
     <t xml:space="preserve">1.18474316596985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1518257856369</t>
+    <t xml:space="preserve">1.15182590484619</t>
   </si>
   <si>
     <t xml:space="preserve">1.19342768192291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21892118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22914659976959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20897591114044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29400050640106</t>
+    <t xml:space="preserve">1.21892106533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22914636135101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20897579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29400062561035</t>
   </si>
   <si>
     <t xml:space="preserve">1.31851351261139</t>
@@ -1925,46 +1925,46 @@
     <t xml:space="preserve">1.31417119503021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27705156803131</t>
+    <t xml:space="preserve">1.27705180644989</t>
   </si>
   <si>
     <t xml:space="preserve">1.36571836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38504838943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706422805786</t>
+    <t xml:space="preserve">1.3850485086441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706434726715</t>
   </si>
   <si>
     <t xml:space="preserve">1.35969519615173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32775819301605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147314786911</t>
+    <t xml:space="preserve">1.32775843143463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31473159790039</t>
   </si>
   <si>
     <t xml:space="preserve">1.3601154088974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40879082679749</t>
+    <t xml:space="preserve">1.40879094600677</t>
   </si>
   <si>
     <t xml:space="preserve">1.47287452220917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49318528175354</t>
+    <t xml:space="preserve">1.49318540096283</t>
   </si>
   <si>
     <t xml:space="preserve">1.46412014961243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43505477905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41544437408447</t>
+    <t xml:space="preserve">1.43505465984344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41544449329376</t>
   </si>
   <si>
     <t xml:space="preserve">1.37566363811493</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.3837878704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35675358772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34372675418854</t>
+    <t xml:space="preserve">1.35675370693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34372663497925</t>
   </si>
   <si>
     <t xml:space="preserve">1.4031879901886</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">1.32103490829468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30296516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28615641593933</t>
+    <t xml:space="preserve">1.30296540260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28615653514862</t>
   </si>
   <si>
     <t xml:space="preserve">1.32019436359406</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">1.32824862003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33175051212311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.359414935112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36606860160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3664186000824</t>
+    <t xml:space="preserve">1.33175039291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35941505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36606848239899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36641871929169</t>
   </si>
   <si>
     <t xml:space="preserve">1.36221647262573</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">1.37587380409241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37727439403534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37622380256653</t>
+    <t xml:space="preserve">1.37727451324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37622368335724</t>
   </si>
   <si>
     <t xml:space="preserve">1.43575513362885</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">1.45956778526306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48828268051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43855655193329</t>
+    <t xml:space="preserve">1.48828279972076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43855667114258</t>
   </si>
   <si>
     <t xml:space="preserve">1.49178469181061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48127913475037</t>
+    <t xml:space="preserve">1.48127901554108</t>
   </si>
   <si>
     <t xml:space="preserve">1.44205844402313</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">1.38077628612518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532853126526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2722190618515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24595522880554</t>
+    <t xml:space="preserve">1.38532865047455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27221918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24595534801483</t>
   </si>
   <si>
     <t xml:space="preserve">1.1997309923172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19062614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19798004627228</t>
+    <t xml:space="preserve">1.19062626361847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19798016548157</t>
   </si>
   <si>
     <t xml:space="preserve">1.24945724010468</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">1.19587910175323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18082106113434</t>
+    <t xml:space="preserve">1.18082094192505</t>
   </si>
   <si>
     <t xml:space="preserve">1.15525758266449</t>
@@ -2099,19 +2099,19 @@
     <t xml:space="preserve">1.17171621322632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14370167255402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13914918899536</t>
+    <t xml:space="preserve">1.14370143413544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13914906978607</t>
   </si>
   <si>
     <t xml:space="preserve">1.1493045091629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16261148452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15350675582886</t>
+    <t xml:space="preserve">1.1626113653183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15350663661957</t>
   </si>
   <si>
     <t xml:space="preserve">1.19377779960632</t>
@@ -2126,22 +2126,22 @@
     <t xml:space="preserve">1.18432295322418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19482839107513</t>
+    <t xml:space="preserve">1.19482851028442</t>
   </si>
   <si>
     <t xml:space="preserve">1.16821444034576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1710159778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15700852870941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20323288440704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25365936756134</t>
+    <t xml:space="preserve">1.17101609706879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1570086479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20323300361633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25365948677063</t>
   </si>
   <si>
     <t xml:space="preserve">1.24560511112213</t>
@@ -2150,16 +2150,16 @@
     <t xml:space="preserve">1.23790109157562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23474943637848</t>
+    <t xml:space="preserve">1.23474955558777</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875676631927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451504230499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24105262756348</t>
+    <t xml:space="preserve">1.26451516151428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24105286598206</t>
   </si>
   <si>
     <t xml:space="preserve">1.23825132846832</t>
@@ -2171,22 +2171,22 @@
     <t xml:space="preserve">1.36256670951843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36992049217224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33525252342224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32264566421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33350145816803</t>
+    <t xml:space="preserve">1.36992037296295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33525240421295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3226455450058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33350157737732</t>
   </si>
   <si>
     <t xml:space="preserve">1.33630275726318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34295630455017</t>
+    <t xml:space="preserve">1.34295642375946</t>
   </si>
   <si>
     <t xml:space="preserve">1.31214022636414</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">1.32439661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914365291595</t>
+    <t xml:space="preserve">1.31914377212524</t>
   </si>
   <si>
     <t xml:space="preserve">1.22634506225586</t>
@@ -2207,25 +2207,25 @@
     <t xml:space="preserve">1.23159778118134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23720061779022</t>
+    <t xml:space="preserve">1.23720073699951</t>
   </si>
   <si>
     <t xml:space="preserve">1.23124742507935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163737773895</t>
+    <t xml:space="preserve">1.21163725852966</t>
   </si>
   <si>
     <t xml:space="preserve">1.17241668701172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18222177028656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18817472457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18467307090759</t>
+    <t xml:space="preserve">1.18222188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18817484378815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18467319011688</t>
   </si>
   <si>
     <t xml:space="preserve">1.1860738992691</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">1.24210333824158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26731646060944</t>
+    <t xml:space="preserve">1.26731657981873</t>
   </si>
   <si>
     <t xml:space="preserve">1.15175592899323</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">1.13424670696259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18012058734894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20603430271149</t>
+    <t xml:space="preserve">1.18012070655823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20603442192078</t>
   </si>
   <si>
     <t xml:space="preserve">1.17521810531616</t>
@@ -2264,19 +2264,19 @@
     <t xml:space="preserve">1.21583950519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21653985977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23404896259308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27467048168182</t>
+    <t xml:space="preserve">1.21653974056244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23404908180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27467060089111</t>
   </si>
   <si>
     <t xml:space="preserve">1.286576628685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32579720020294</t>
+    <t xml:space="preserve">1.32579731941223</t>
   </si>
   <si>
     <t xml:space="preserve">1.28132390975952</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">1.32474672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31844341754913</t>
+    <t xml:space="preserve">1.31844353675842</t>
   </si>
   <si>
     <t xml:space="preserve">1.35171091556549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31424129009247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34050500392914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36816954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35066044330597</t>
+    <t xml:space="preserve">1.31424140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34050512313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36816966533661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">1.29743242263794</t>
@@ -2318,40 +2318,40 @@
     <t xml:space="preserve">1.31003904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33980476856232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33210051059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29007852077484</t>
+    <t xml:space="preserve">1.33980488777161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33210062980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29007840156555</t>
   </si>
   <si>
     <t xml:space="preserve">1.27081847190857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27537071704865</t>
+    <t xml:space="preserve">1.27537059783936</t>
   </si>
   <si>
     <t xml:space="preserve">1.28762722015381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31249034404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32789850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28307497501373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30968880653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42384898662567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50929391384125</t>
+    <t xml:space="preserve">1.31249022483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32789838314056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28307485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3096889257431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42384886741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50929379463196</t>
   </si>
   <si>
     <t xml:space="preserve">1.50859344005585</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">1.47707688808441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4686723947525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42314851284027</t>
+    <t xml:space="preserve">1.46867227554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42314863204956</t>
   </si>
   <si>
     <t xml:space="preserve">1.42665028572083</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">1.47777724266052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49528646469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49388563632965</t>
+    <t xml:space="preserve">1.49528658390045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49388551712036</t>
   </si>
   <si>
     <t xml:space="preserve">1.44766128063202</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">1.41754555702209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41614496707916</t>
+    <t xml:space="preserve">1.41614472866058</t>
   </si>
   <si>
     <t xml:space="preserve">1.44135820865631</t>
@@ -2402,19 +2402,19 @@
     <t xml:space="preserve">1.45536553859711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46517062187195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43085265159607</t>
+    <t xml:space="preserve">1.46517074108124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43085253238678</t>
   </si>
   <si>
     <t xml:space="preserve">1.4182460308075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38813006877899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37412285804749</t>
+    <t xml:space="preserve">1.38813018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37412261962891</t>
   </si>
   <si>
     <t xml:space="preserve">1.41474413871765</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">1.36851990222931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37797462940216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38637924194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46166884899139</t>
+    <t xml:space="preserve">1.37797474861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38637912273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4616687297821</t>
   </si>
   <si>
     <t xml:space="preserve">1.425950050354</t>
@@ -2450,55 +2450,55 @@
     <t xml:space="preserve">1.43435454368591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43365406990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287723064423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36887001991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39373314380646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36431765556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29568147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35836446285248</t>
+    <t xml:space="preserve">1.43365395069122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287734985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36886990070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39373302459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36431753635406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29568159580231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35836458206177</t>
   </si>
   <si>
     <t xml:space="preserve">1.37307226657867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727168560028</t>
+    <t xml:space="preserve">1.46727180480957</t>
   </si>
   <si>
     <t xml:space="preserve">1.52049970626831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54641342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72010445594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626080989838</t>
+    <t xml:space="preserve">1.54641330242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72010493278503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626069068909</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884801864624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30128443241119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14230072498322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09397554397583</t>
+    <t xml:space="preserve">1.3012843132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14230096340179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09397542476654</t>
   </si>
   <si>
     <t xml:space="preserve">1.05755615234375</t>
@@ -2519,16 +2519,16 @@
     <t xml:space="preserve">0.888417303562164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818030297756195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874409794807434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87475997209549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885965943336487</t>
+    <t xml:space="preserve">0.81803023815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874409973621368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874760031700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885966002941132</t>
   </si>
   <si>
     <t xml:space="preserve">0.877561628818512</t>
@@ -2537,16 +2537,16 @@
     <t xml:space="preserve">0.870207607746124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926587402820587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912930369377136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925887048244476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880713284015656</t>
+    <t xml:space="preserve">0.926587283611298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912930250167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925886988639832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8807133436203</t>
   </si>
   <si>
     <t xml:space="preserve">0.84919661283493</t>
@@ -2558,40 +2558,40 @@
     <t xml:space="preserve">0.823633253574371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846044898033142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830987095832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851297736167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829936504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853048741817474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820131421089172</t>
+    <t xml:space="preserve">0.846045017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83098703622818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851297795772552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829936444759369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85304868221283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820131361484528</t>
   </si>
   <si>
     <t xml:space="preserve">0.77740889787674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778459429740906</t>
+    <t xml:space="preserve">0.778459489345551</t>
   </si>
   <si>
     <t xml:space="preserve">0.778809607028961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753246188163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751845479011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771805942058563</t>
+    <t xml:space="preserve">0.753246247768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751845419406891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771805882453918</t>
   </si>
   <si>
     <t xml:space="preserve">0.743791222572327</t>
@@ -2600,43 +2600,43 @@
     <t xml:space="preserve">0.768304109573364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789665400981903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809625804424286</t>
+    <t xml:space="preserve">0.789665341377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809625864028931</t>
   </si>
   <si>
     <t xml:space="preserve">0.779860198497772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766553103923798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781611204147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776008129119873</t>
+    <t xml:space="preserve">0.766553163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781611144542694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776008188724518</t>
   </si>
   <si>
     <t xml:space="preserve">0.765152454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803672730922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812077105045319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807874858379364</t>
+    <t xml:space="preserve">0.803672671318054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812077164649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807874917984009</t>
   </si>
   <si>
     <t xml:space="preserve">0.785463154315948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781260907649994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819080770015717</t>
+    <t xml:space="preserve">0.781260848045349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819080829620361</t>
   </si>
   <si>
     <t xml:space="preserve">0.759199321269989</t>
@@ -2651,10 +2651,10 @@
     <t xml:space="preserve">0.736087203025818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743441045284271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779159784317017</t>
+    <t xml:space="preserve">0.743440985679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779159843921661</t>
   </si>
   <si>
     <t xml:space="preserve">0.815228819847107</t>
@@ -2672,82 +2672,82 @@
     <t xml:space="preserve">0.892969727516174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931840121746063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994873344898224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00853037834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979114890098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966858446598053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891218841075897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895070731639862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901724338531494</t>
+    <t xml:space="preserve">0.931840062141418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994873285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00853049755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979114949703217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966858565807343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891218721866608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895070910453796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901724398136139</t>
   </si>
   <si>
     <t xml:space="preserve">0.967908978462219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964407324790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94689804315567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936392545700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938493549823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965107679367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913980722427368</t>
+    <t xml:space="preserve">0.96440714597702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946898102760315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936392426490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938493609428406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965107560157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913980782032013</t>
   </si>
   <si>
     <t xml:space="preserve">0.934641540050507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899623036384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953551650047302</t>
+    <t xml:space="preserve">0.899623215198517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953551590442657</t>
   </si>
   <si>
     <t xml:space="preserve">0.930089235305786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.909078180789948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954602062702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943746268749237</t>
+    <t xml:space="preserve">0.909078061580658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954602122306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943746387958527</t>
   </si>
   <si>
     <t xml:space="preserve">0.983317196369171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973161935806274</t>
+    <t xml:space="preserve">0.97316187620163</t>
   </si>
   <si>
     <t xml:space="preserve">0.951450407505035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916432082653046</t>
+    <t xml:space="preserve">0.91643214225769</t>
   </si>
   <si>
     <t xml:space="preserve">0.933941245079041</t>
@@ -2756,67 +2756,67 @@
     <t xml:space="preserve">0.948298811912537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957403481006622</t>
+    <t xml:space="preserve">0.957403659820557</t>
   </si>
   <si>
     <t xml:space="preserve">0.973511934280396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980865776538849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03304326534271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03759586811066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00012612342834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998725354671478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960905373096466</t>
+    <t xml:space="preserve">0.980865895748138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.033043384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03759574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00012600421906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998725295066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960905313491821</t>
   </si>
   <si>
     <t xml:space="preserve">0.967208743095398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944096684455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893670082092285</t>
+    <t xml:space="preserve">0.944096565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893669962882996</t>
   </si>
   <si>
     <t xml:space="preserve">0.890168190002441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874059855937958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913280367851257</t>
+    <t xml:space="preserve">0.874059736728668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913280487060547</t>
   </si>
   <si>
     <t xml:space="preserve">0.927637934684753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.907677412033081</t>
+    <t xml:space="preserve">0.907677352428436</t>
   </si>
   <si>
     <t xml:space="preserve">0.890868544578552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915381491184235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978764891624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971060752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00572896003723</t>
+    <t xml:space="preserve">0.915381550788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978764832019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971060812473297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00572907924652</t>
   </si>
   <si>
     <t xml:space="preserve">0.997324585914612</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">0.981566250324249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00923085212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986819088459015</t>
+    <t xml:space="preserve">1.00923073291779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98681902885437</t>
   </si>
   <si>
     <t xml:space="preserve">0.987519443035126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00712966918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996624112129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999775767326355</t>
+    <t xml:space="preserve">1.00712954998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996624231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999775826931</t>
   </si>
   <si>
     <t xml:space="preserve">1.00467836856842</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">0.988920092582703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985768556594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970360279083252</t>
+    <t xml:space="preserve">0.985768496990204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970360338687897</t>
   </si>
   <si>
     <t xml:space="preserve">0.958103954792023</t>
@@ -2861,43 +2861,43 @@
     <t xml:space="preserve">0.994523167610168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978414595127106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986118674278259</t>
+    <t xml:space="preserve">0.978414535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986118793487549</t>
   </si>
   <si>
     <t xml:space="preserve">1.03724551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02148723602295</t>
+    <t xml:space="preserve">1.02148711681366</t>
   </si>
   <si>
     <t xml:space="preserve">1.01903593540192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01203238964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995573461055756</t>
+    <t xml:space="preserve">1.0120325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995573580265045</t>
   </si>
   <si>
     <t xml:space="preserve">0.973862171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916782140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922735333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888067126274109</t>
+    <t xml:space="preserve">0.916782259941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922735154628754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888067066669464</t>
   </si>
   <si>
     <t xml:space="preserve">0.939544260501862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961605787277222</t>
+    <t xml:space="preserve">0.961605906486511</t>
   </si>
   <si>
     <t xml:space="preserve">0.972811758518219</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">1.09957838058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16121077537537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18502330780029</t>
+    <t xml:space="preserve">1.16121065616608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.185023188591</t>
   </si>
   <si>
     <t xml:space="preserve">1.16961514949799</t>
@@ -2924,61 +2924,61 @@
     <t xml:space="preserve">1.15910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12339091300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12829351425171</t>
+    <t xml:space="preserve">1.12339079380035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12829339504242</t>
   </si>
   <si>
     <t xml:space="preserve">1.12794327735901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16016018390656</t>
+    <t xml:space="preserve">1.16016006469727</t>
   </si>
   <si>
     <t xml:space="preserve">1.13564729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15280628204346</t>
+    <t xml:space="preserve">1.17066562175751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545238018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15280640125275</t>
   </si>
   <si>
     <t xml:space="preserve">1.17591857910156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15560781955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13214540481567</t>
+    <t xml:space="preserve">1.1556077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13214552402496</t>
   </si>
   <si>
     <t xml:space="preserve">1.08522081375122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965745449066</t>
+    <t xml:space="preserve">1.05965733528137</t>
   </si>
   <si>
     <t xml:space="preserve">1.08627128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12899386882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15000486373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15210592746735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15490746498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15455722808838</t>
+    <t xml:space="preserve">1.12899374961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15000474452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15210604667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15490758419037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15455734729767</t>
   </si>
   <si>
     <t xml:space="preserve">1.26066303253174</t>
@@ -2987,37 +2987,37 @@
     <t xml:space="preserve">1.25120806694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25611078739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27502071857452</t>
+    <t xml:space="preserve">1.25611066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27502059936523</t>
   </si>
   <si>
     <t xml:space="preserve">1.30793786048889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32684791088104</t>
+    <t xml:space="preserve">1.32684779167175</t>
   </si>
   <si>
     <t xml:space="preserve">1.35801434516907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3233460187912</t>
+    <t xml:space="preserve">1.32334613800049</t>
   </si>
   <si>
     <t xml:space="preserve">1.31879365444183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29603159427643</t>
+    <t xml:space="preserve">1.29603171348572</t>
   </si>
   <si>
     <t xml:space="preserve">1.31389117240906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30723750591278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29498112201691</t>
+    <t xml:space="preserve">1.30723762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29498100280762</t>
   </si>
   <si>
     <t xml:space="preserve">1.28482580184937</t>
@@ -3035,64 +3035,64 @@
     <t xml:space="preserve">1.25435972213745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27256941795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26136326789856</t>
+    <t xml:space="preserve">1.2725692987442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26136338710785</t>
   </si>
   <si>
     <t xml:space="preserve">1.26661622524261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26416492462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26521563529968</t>
+    <t xml:space="preserve">1.26416480541229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2652153968811</t>
   </si>
   <si>
     <t xml:space="preserve">1.26766681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26626598834991</t>
+    <t xml:space="preserve">1.26626586914062</t>
   </si>
   <si>
     <t xml:space="preserve">1.25856196880341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25821161270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32964944839478</t>
+    <t xml:space="preserve">1.25821185112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32964932918549</t>
   </si>
   <si>
     <t xml:space="preserve">1.36957037448883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3450573682785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34925961494446</t>
+    <t xml:space="preserve">1.34505748748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34925973415375</t>
   </si>
   <si>
     <t xml:space="preserve">1.33455204963684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31529188156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31809341907501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31073951721191</t>
+    <t xml:space="preserve">1.31529176235199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31809318065643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31073939800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.31774306297302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2806236743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24735605716705</t>
+    <t xml:space="preserve">1.28062355518341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24735617637634</t>
   </si>
   <si>
     <t xml:space="preserve">1.26696646213531</t>
@@ -3101,34 +3101,34 @@
     <t xml:space="preserve">1.2501574754715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29112923145294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27432036399841</t>
+    <t xml:space="preserve">1.29112911224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27432024478912</t>
   </si>
   <si>
     <t xml:space="preserve">1.29953360557556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34820926189423</t>
+    <t xml:space="preserve">1.34820914268494</t>
   </si>
   <si>
     <t xml:space="preserve">1.42174780368805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52260100841522</t>
+    <t xml:space="preserve">1.52260088920593</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190053462982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53240609169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4980880022049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48898303508759</t>
+    <t xml:space="preserve">1.53240585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49808788299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48898327350616</t>
   </si>
   <si>
     <t xml:space="preserve">1.50088942050934</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">1.51629745960236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50789332389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5197993516922</t>
+    <t xml:space="preserve">1.50789320468903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51979923248291</t>
   </si>
   <si>
     <t xml:space="preserve">1.54851448535919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54361188411713</t>
+    <t xml:space="preserve">1.54361176490784</t>
   </si>
   <si>
     <t xml:space="preserve">1.60594475269318</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">1.62695562839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62065231800079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59053647518158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5919371843338</t>
+    <t xml:space="preserve">1.62065243721008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59053635597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59193730354309</t>
   </si>
   <si>
     <t xml:space="preserve">1.69909381866455</t>
@@ -3179,34 +3179,34 @@
     <t xml:space="preserve">1.70469677448273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71099984645844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881958961487</t>
+    <t xml:space="preserve">1.7110002040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881994724274</t>
   </si>
   <si>
     <t xml:space="preserve">1.70539689064026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68998908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65356957912445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6353600025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64936769008636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63466000556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62835645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66547620296478</t>
+    <t xml:space="preserve">1.68998897075653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65356969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63536036014557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64936757087708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63465988636017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62835657596588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6654759645462</t>
   </si>
   <si>
     <t xml:space="preserve">1.71505236625671</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">1.61877381801605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59937429428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61302578449249</t>
+    <t xml:space="preserve">1.5993744134903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6130256652832</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308478355408</t>
@@ -3227,10 +3227,10 @@
     <t xml:space="preserve">1.65613555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67337954044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71936309337616</t>
+    <t xml:space="preserve">1.67337942123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71936321258545</t>
   </si>
   <si>
     <t xml:space="preserve">1.71289670467377</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">1.70283782482147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445188999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71145975589752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74522924423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893961429596</t>
+    <t xml:space="preserve">1.73445165157318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71145987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74522912502289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893949508667</t>
   </si>
   <si>
     <t xml:space="preserve">1.76822090148926</t>
@@ -3257,31 +3257,31 @@
     <t xml:space="preserve">1.81707894802094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83504128456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85587763786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8644996881485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92126107215881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95934116840363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9729927778244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98377025127411</t>
+    <t xml:space="preserve">1.83504116535187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85587775707245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86449980735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92126083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95934128761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97299289703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98377013206482</t>
   </si>
   <si>
     <t xml:space="preserve">1.94066047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96508920192719</t>
+    <t xml:space="preserve">1.96508884429932</t>
   </si>
   <si>
     <t xml:space="preserve">1.99742150306702</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">2.08579683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08795213699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10375928878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12531399726868</t>
+    <t xml:space="preserve">2.08795237541199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10375881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12531423568726</t>
   </si>
   <si>
     <t xml:space="preserve">2.13465452194214</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">2.18423080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17201662063599</t>
+    <t xml:space="preserve">2.17201638221741</t>
   </si>
   <si>
     <t xml:space="preserve">2.17991971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17560911178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1763277053833</t>
+    <t xml:space="preserve">2.17560887336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17632746696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.16052055358887</t>
@@ -3338,10 +3338,10 @@
     <t xml:space="preserve">2.08938932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0807671546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05346441268921</t>
+    <t xml:space="preserve">2.08076691627502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05346465110779</t>
   </si>
   <si>
     <t xml:space="preserve">2.08292269706726</t>
@@ -3356,76 +3356,76 @@
     <t xml:space="preserve">2.01897644996643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04053139686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98305153846741</t>
+    <t xml:space="preserve">2.04053163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98305141925812</t>
   </si>
   <si>
     <t xml:space="preserve">1.96652626991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94928228855133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95215630531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90114295482635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8328857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93922317028046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93634915351868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91766846179962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88821017742157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88749158382416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8465371131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78762054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8264194726944</t>
+    <t xml:space="preserve">1.94928252696991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9521564245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90114283561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83288586139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93922328948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93634939193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91766834259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88820993900299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88749170303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84653723239899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7876204252243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82641935348511</t>
   </si>
   <si>
     <t xml:space="preserve">1.8752772808075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85803318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9025799036026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87743234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89108407497406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82067131996155</t>
+    <t xml:space="preserve">1.85803294181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90258002281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87743246555328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89108383655548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82067143917084</t>
   </si>
   <si>
     <t xml:space="preserve">1.81348645687103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82857489585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96724486351013</t>
+    <t xml:space="preserve">1.82857477664948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96724474430084</t>
   </si>
   <si>
     <t xml:space="preserve">1.97371113300323</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">1.95718574523926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03190970420837</t>
+    <t xml:space="preserve">2.03190922737122</t>
   </si>
   <si>
     <t xml:space="preserve">2.00676202774048</t>
@@ -3446,49 +3446,49 @@
     <t xml:space="preserve">1.97155570983887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93347537517548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90904641151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94209742546082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97802209854126</t>
+    <t xml:space="preserve">1.93347561359406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90904653072357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94209718704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97802197933197</t>
   </si>
   <si>
     <t xml:space="preserve">2.01107311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99957692623138</t>
+    <t xml:space="preserve">1.99957716464996</t>
   </si>
   <si>
     <t xml:space="preserve">2.01753973960876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03262782096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03119087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99167394638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01322865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97945916652679</t>
+    <t xml:space="preserve">2.03262805938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03119111061096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99167382717133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01322841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97945940494537</t>
   </si>
   <si>
     <t xml:space="preserve">1.95000076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93778645992279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96868193149567</t>
+    <t xml:space="preserve">1.93778657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96868169307709</t>
   </si>
   <si>
     <t xml:space="preserve">1.92269814014435</t>
@@ -3497,37 +3497,37 @@
     <t xml:space="preserve">1.94712686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92916417121887</t>
+    <t xml:space="preserve">1.92916429042816</t>
   </si>
   <si>
     <t xml:space="preserve">1.83073043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84078931808472</t>
+    <t xml:space="preserve">1.84078943729401</t>
   </si>
   <si>
     <t xml:space="preserve">1.9205424785614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9758665561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9234162569046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94353449344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94425284862518</t>
+    <t xml:space="preserve">1.97586679458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92341649532318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94353437423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9442526102066</t>
   </si>
   <si>
     <t xml:space="preserve">1.91838705539703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02616143226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02831697463989</t>
+    <t xml:space="preserve">2.02616167068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02831721305847</t>
   </si>
   <si>
     <t xml:space="preserve">2.02185034751892</t>
@@ -3536,16 +3536,16 @@
     <t xml:space="preserve">2.03047251701355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93994212150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04340577125549</t>
+    <t xml:space="preserve">1.93994176387787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04340553283691</t>
   </si>
   <si>
     <t xml:space="preserve">2.10016679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12387728691101</t>
+    <t xml:space="preserve">2.12387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">2.09226322174072</t>
@@ -3557,25 +3557,25 @@
     <t xml:space="preserve">2.1303436756134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14758729934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1095073223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08148574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92988300323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93563103675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97083735466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00963592529297</t>
+    <t xml:space="preserve">2.1475875377655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10950708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08148598670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92988276481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93563091754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97083723545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00963616371155</t>
   </si>
   <si>
     <t xml:space="preserve">2.08364152908325</t>
@@ -3587,31 +3587,31 @@
     <t xml:space="preserve">2.00316953659058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98592567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9514377117157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90042471885681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88318061828613</t>
+    <t xml:space="preserve">1.98592555522919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95143795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90042459964752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88318049907684</t>
   </si>
   <si>
     <t xml:space="preserve">1.8537220954895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74594748020172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540612220764</t>
+    <t xml:space="preserve">1.74594783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540588378906</t>
   </si>
   <si>
     <t xml:space="preserve">1.77181363105774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80845713615417</t>
+    <t xml:space="preserve">1.8084568977356</t>
   </si>
   <si>
     <t xml:space="preserve">1.83001172542572</t>
@@ -3623,40 +3623,40 @@
     <t xml:space="preserve">1.92557191848755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8896472454071</t>
+    <t xml:space="preserve">1.88964736461639</t>
   </si>
   <si>
     <t xml:space="preserve">1.88677299022675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86737370491028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395809173584</t>
+    <t xml:space="preserve">1.8673734664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.89036560058594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8544408082962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84797406196594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7976793050766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85659635066986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85875165462494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84725606441498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85515916347504</t>
+    <t xml:space="preserve">1.85444056987762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84797418117523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79767954349518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85659646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85875141620636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84725570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85515928268433</t>
   </si>
   <si>
     <t xml:space="preserve">1.88605463504791</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">1.89683210849762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97874081134796</t>
+    <t xml:space="preserve">1.97874045372009</t>
   </si>
   <si>
     <t xml:space="preserve">2.00101399421692</t>
@@ -3677,19 +3677,19 @@
     <t xml:space="preserve">2.06280493736267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05849385261536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06424164772034</t>
+    <t xml:space="preserve">2.05849409103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06424188613892</t>
   </si>
   <si>
     <t xml:space="preserve">2.0563383102417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0527458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02113223075867</t>
+    <t xml:space="preserve">2.05274605751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02113199234009</t>
   </si>
   <si>
     <t xml:space="preserve">2.00460648536682</t>
@@ -3701,34 +3701,34 @@
     <t xml:space="preserve">1.99526607990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89970588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87958800792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93131971359253</t>
+    <t xml:space="preserve">1.8997061252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87958812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93131995201111</t>
   </si>
   <si>
     <t xml:space="preserve">1.96221518516541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91192066669464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02041339874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06855297088623</t>
+    <t xml:space="preserve">1.91192030906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02041363716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06855273246765</t>
   </si>
   <si>
     <t xml:space="preserve">2.10447764396667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07645630836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657430648804</t>
+    <t xml:space="preserve">2.07645654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09657406806946</t>
   </si>
   <si>
     <t xml:space="preserve">2.15118002891541</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">2.55138301849365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53485727310181</t>
+    <t xml:space="preserve">2.53485751152039</t>
   </si>
   <si>
     <t xml:space="preserve">2.60814428329468</t>
@@ -3761,31 +3761,31 @@
     <t xml:space="preserve">2.52336144447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51042866706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41343140602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21584463119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26398420333862</t>
+    <t xml:space="preserve">2.5104284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21584486961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26398396492004</t>
   </si>
   <si>
     <t xml:space="preserve">2.21368932723999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496024131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120195388794</t>
+    <t xml:space="preserve">2.06496047973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120183467865</t>
   </si>
   <si>
     <t xml:space="preserve">1.66475737094879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74954032897949</t>
+    <t xml:space="preserve">1.74954009056091</t>
   </si>
   <si>
     <t xml:space="preserve">1.79480528831482</t>
@@ -3803,13 +3803,13 @@
     <t xml:space="preserve">1.96077823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95862281322479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98879969120026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95574879646301</t>
+    <t xml:space="preserve">1.95862293243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98879945278168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95574855804443</t>
   </si>
   <si>
     <t xml:space="preserve">1.95359337329865</t>
@@ -3818,52 +3818,52 @@
     <t xml:space="preserve">2.06208634376526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93275678157806</t>
+    <t xml:space="preserve">1.93275690078735</t>
   </si>
   <si>
     <t xml:space="preserve">1.99095511436462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664426803589</t>
+    <t xml:space="preserve">1.98664450645447</t>
   </si>
   <si>
     <t xml:space="preserve">1.94784533977509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16626858711243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12459588050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19572687149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19860100746155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2307755947113</t>
+    <t xml:space="preserve">2.16626834869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12459564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1957266330719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19860053062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23077535629272</t>
   </si>
   <si>
     <t xml:space="preserve">2.33036375045776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35257959365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35181355476379</t>
+    <t xml:space="preserve">2.35257983207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35181331634521</t>
   </si>
   <si>
     <t xml:space="preserve">2.36713480949402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32193684577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35104751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31887245178223</t>
+    <t xml:space="preserve">2.321937084198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35104727745056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31887269020081</t>
   </si>
   <si>
     <t xml:space="preserve">2.27597308158875</t>
@@ -3872,13 +3872,13 @@
     <t xml:space="preserve">2.33572626113892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24839496612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23383951187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21085786819458</t>
+    <t xml:space="preserve">2.24839472770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23383975028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.210857629776</t>
   </si>
   <si>
     <t xml:space="preserve">2.13731575012207</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">2.1587655544281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25069308280945</t>
+    <t xml:space="preserve">2.25069332122803</t>
   </si>
   <si>
     <t xml:space="preserve">2.23307371139526</t>
@@ -3911,22 +3911,22 @@
     <t xml:space="preserve">2.40850210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45523190498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47285151481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45293378829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48204398155212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48664045333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46365857124329</t>
+    <t xml:space="preserve">2.4552321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47285127639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45293354988098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4820442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48664093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46365880966187</t>
   </si>
   <si>
     <t xml:space="preserve">2.47438359260559</t>
@@ -3938,13 +3938,13 @@
     <t xml:space="preserve">2.43071818351746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37709355354309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09058618545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98793363571167</t>
+    <t xml:space="preserve">2.37709331512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09058594703674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98793351650238</t>
   </si>
   <si>
     <t xml:space="preserve">2.01168155670166</t>
@@ -3959,124 +3959,124 @@
     <t xml:space="preserve">2.07832908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1679584980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1993670463562</t>
+    <t xml:space="preserve">2.16795802116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315598487854</t>
+  </si>
+  <si>
+    <t xml:spac